--- a/data/characters.xlsx
+++ b/data/characters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\モノクロビリーフ\外部リンク\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36DB3BDC-2CE3-422F-BE19-EECE350F52D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58124499-156D-4097-9196-84535C4F6DF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{78CF6334-6F78-4A6F-BD14-CB6FA7AB00CF}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3033" uniqueCount="1761">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3036" uniqueCount="1762">
   <si>
     <t>番号</t>
   </si>
@@ -6195,10 +6195,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Ｔくん</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>てぃーくん</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -7344,6 +7340,17 @@
     </rPh>
     <rPh sb="10" eb="12">
       <t>シッポ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Tくん</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>人造人間</t>
+    <rPh sb="0" eb="4">
+      <t>ジンゾウニンゲン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -7686,6 +7693,48 @@
   </cellStyles>
   <dxfs count="71">
     <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B050"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE1FACE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -7740,48 +7789,6 @@
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B050"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE1FACE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -8757,7 +8764,7 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AFDEA6E0-6891-40ED-8736-87CEEF9CED2F}" name="テーブル1" displayName="テーブル1" ref="A1:X439" headerRowDxfId="66" dataDxfId="65" tableBorderDxfId="64">
   <autoFilter ref="A1:X439" xr:uid="{AFDEA6E0-6891-40ED-8736-87CEEF9CED2F}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:X231">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:X439">
     <sortCondition ref="A1:A439"/>
   </sortState>
   <tableColumns count="24">
@@ -8813,43 +8820,43 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{E4C87AB3-D453-4364-A868-37CD257B126C}" name="テーブル2" displayName="テーブル2" ref="A1:L231" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{E4C87AB3-D453-4364-A868-37CD257B126C}" name="テーブル2" displayName="テーブル2" ref="A1:L231" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16">
   <autoFilter ref="A1:L231" xr:uid="{E4C87AB3-D453-4364-A868-37CD257B126C}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{1E92C13E-0744-4588-9D96-A833A7BD4B23}" name="id" dataDxfId="11">
+    <tableColumn id="1" xr3:uid="{1E92C13E-0744-4588-9D96-A833A7BD4B23}" name="id" dataDxfId="15">
       <calculatedColumnFormula>テーブル1[[#This Row],[番号]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{BFFC27FC-5A70-42B5-935F-18B299D9A450}" name="name" dataDxfId="10">
+    <tableColumn id="2" xr3:uid="{BFFC27FC-5A70-42B5-935F-18B299D9A450}" name="name" dataDxfId="14">
       <calculatedColumnFormula>テーブル1[[#This Row],[名前]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{376B9D63-7024-4C39-A1F3-F8A88D986D2E}" name="kana" dataDxfId="9">
+    <tableColumn id="3" xr3:uid="{376B9D63-7024-4C39-A1F3-F8A88D986D2E}" name="kana" dataDxfId="13">
       <calculatedColumnFormula>テーブル1[[#This Row],[なまえ]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{3A4FC950-495C-4C11-B6DB-96CE6A55121C}" name="romaji" dataDxfId="8">
+    <tableColumn id="4" xr3:uid="{3A4FC950-495C-4C11-B6DB-96CE6A55121C}" name="romaji" dataDxfId="12">
       <calculatedColumnFormula>テーブル1[[#This Row],[Name]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{B264791E-28AE-437A-AA33-4258BDE55BAA}" name="icon" dataDxfId="7">
+    <tableColumn id="5" xr3:uid="{B264791E-28AE-437A-AA33-4258BDE55BAA}" name="icon" dataDxfId="11">
       <calculatedColumnFormula>"image/"&amp;テーブル1[[#This Row],[画像]]&amp;".png"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{857A780E-B021-402A-872A-1CBFFEF7F813}" name="url" dataDxfId="6">
+    <tableColumn id="6" xr3:uid="{857A780E-B021-402A-872A-1CBFFEF7F813}" name="url" dataDxfId="10">
       <calculatedColumnFormula>テーブル1[[#This Row],[リンク]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{54796813-8C4A-4907-9B54-8EC5819BC55C}" name="workTags" dataDxfId="5">
+    <tableColumn id="7" xr3:uid="{54796813-8C4A-4907-9B54-8EC5819BC55C}" name="workTags" dataDxfId="9">
       <calculatedColumnFormula>SUBSTITUTE(テーブル1[[#This Row],[作品タグ]]," ","|")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{C71938D1-4F25-43A4-AC89-6B4F6A5026A2}" name="gender" dataDxfId="4">
+    <tableColumn id="8" xr3:uid="{C71938D1-4F25-43A4-AC89-6B4F6A5026A2}" name="gender" dataDxfId="8">
       <calculatedColumnFormula>テーブル1[[#This Row],[性別]]&amp;""</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{39305227-2E4A-4CF9-88DD-B221FEC21124}" name="種族タグ" dataDxfId="3">
+    <tableColumn id="9" xr3:uid="{39305227-2E4A-4CF9-88DD-B221FEC21124}" name="種族タグ" dataDxfId="7">
       <calculatedColumnFormula>テーブル1[[#This Row],[種族タグ]]&amp;""</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{4C1B4E5B-0816-4E7B-B94D-DABFCF9BB4A5}" name="職業タグ" dataDxfId="2">
+    <tableColumn id="10" xr3:uid="{4C1B4E5B-0816-4E7B-B94D-DABFCF9BB4A5}" name="職業タグ" dataDxfId="6">
       <calculatedColumnFormula>テーブル1[[#This Row],[職業タグ]]&amp;""</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{C1145559-52E6-4141-BB43-03D7F9D319F4}" name="小物タグ" dataDxfId="1">
+    <tableColumn id="11" xr3:uid="{C1145559-52E6-4141-BB43-03D7F9D319F4}" name="小物タグ" dataDxfId="5">
       <calculatedColumnFormula>テーブル1[[#This Row],[小物タグ]]&amp;""</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{1869C5D2-E7D3-4710-BDB3-B35F4A761BEE}" name="ワンポイントタグ" dataDxfId="0">
+    <tableColumn id="12" xr3:uid="{1869C5D2-E7D3-4710-BDB3-B35F4A761BEE}" name="ワンポイントタグ" dataDxfId="4">
       <calculatedColumnFormula>テーブル1[[#This Row],[ワンポイントタグ]]&amp;""</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9222,22 +9229,22 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>1629</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>1630</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>1631</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>1632</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>1633</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>1519</v>
@@ -9261,19 +9268,19 @@
         <v>774</v>
       </c>
       <c r="T1" s="1" t="s">
+        <v>1550</v>
+      </c>
+      <c r="U1" s="1" t="s">
         <v>1551</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>1552</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>1553</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>1554</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>1555</v>
       </c>
     </row>
     <row r="2" spans="1:24" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -9300,13 +9307,13 @@
         <v>216</v>
       </c>
       <c r="H2" s="23" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="I2" s="23" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="L2" s="23" t="s">
-        <v>1639</v>
+        <v>1638</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>1517</v>
@@ -9378,19 +9385,19 @@
         <v>190</v>
       </c>
       <c r="H3" s="23" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="I3" s="23" t="s">
+        <v>1636</v>
+      </c>
+      <c r="J3" s="23" t="s">
+        <v>1635</v>
+      </c>
+      <c r="K3" s="23" t="s">
         <v>1637</v>
       </c>
-      <c r="J3" s="23" t="s">
-        <v>1636</v>
-      </c>
-      <c r="K3" s="23" t="s">
-        <v>1638</v>
-      </c>
       <c r="L3" s="23" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="N3" s="1" t="s">
         <v>1443</v>
@@ -9459,16 +9466,16 @@
         <v>94</v>
       </c>
       <c r="H4" s="23" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="I4" s="23" t="s">
+        <v>1639</v>
+      </c>
+      <c r="J4" s="23" t="s">
         <v>1640</v>
       </c>
-      <c r="J4" s="23" t="s">
+      <c r="L4" s="23" t="s">
         <v>1641</v>
-      </c>
-      <c r="L4" s="23" t="s">
-        <v>1642</v>
       </c>
       <c r="M4" s="1" t="s">
         <v>1518</v>
@@ -9540,13 +9547,13 @@
         <v>208</v>
       </c>
       <c r="H5" s="23" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="I5" s="23" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
       <c r="K5" s="23" t="s">
-        <v>1647</v>
+        <v>1646</v>
       </c>
       <c r="N5" s="1" t="s">
         <v>1443</v>
@@ -9615,16 +9622,16 @@
         <v>340</v>
       </c>
       <c r="H6" s="23" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="I6" s="23" t="s">
+        <v>1655</v>
+      </c>
+      <c r="K6" s="23" t="s">
         <v>1656</v>
       </c>
-      <c r="K6" s="23" t="s">
+      <c r="L6" s="23" t="s">
         <v>1657</v>
-      </c>
-      <c r="L6" s="23" t="s">
-        <v>1658</v>
       </c>
       <c r="N6" s="1" t="s">
         <v>1443</v>
@@ -9693,10 +9700,10 @@
         <v>166</v>
       </c>
       <c r="H7" s="23" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
       <c r="I7" s="23" t="s">
-        <v>1637</v>
+        <v>1636</v>
       </c>
       <c r="N7" s="1" t="s">
         <v>1443</v>
@@ -9765,16 +9772,16 @@
         <v>293</v>
       </c>
       <c r="H8" s="23" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
       <c r="I8" s="23" t="s">
-        <v>1650</v>
+        <v>1649</v>
       </c>
       <c r="K8" s="23" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
       <c r="L8" s="23" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
       <c r="M8" s="1" t="s">
         <v>1517</v>
@@ -9846,13 +9853,13 @@
         <v>374</v>
       </c>
       <c r="H9" s="23" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="I9" s="23" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="L9" s="23" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
       <c r="N9" s="1" t="s">
         <v>1443</v>
@@ -9921,16 +9928,16 @@
         <v>288</v>
       </c>
       <c r="H10" s="23" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="I10" s="23" t="s">
-        <v>1637</v>
+        <v>1636</v>
       </c>
       <c r="K10" s="23" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="L10" s="23" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="N10" s="1" t="s">
         <v>1443</v>
@@ -9999,13 +10006,13 @@
         <v>123</v>
       </c>
       <c r="H11" s="23" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="I11" s="23" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="L11" s="23" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="N11" s="1" t="s">
         <v>1443</v>
@@ -10074,16 +10081,16 @@
         <v>348</v>
       </c>
       <c r="H12" s="23" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="I12" s="23" t="s">
+        <v>1636</v>
+      </c>
+      <c r="J12" s="23" t="s">
+        <v>1693</v>
+      </c>
+      <c r="K12" s="23" t="s">
         <v>1637</v>
-      </c>
-      <c r="J12" s="23" t="s">
-        <v>1694</v>
-      </c>
-      <c r="K12" s="23" t="s">
-        <v>1638</v>
       </c>
       <c r="N12" s="1" t="s">
         <v>1443</v>
@@ -10152,10 +10159,10 @@
         <v>411</v>
       </c>
       <c r="H13" s="23" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="K13" s="23" t="s">
-        <v>1696</v>
+        <v>1695</v>
       </c>
       <c r="M13" s="1" t="s">
         <v>1515</v>
@@ -10227,13 +10234,13 @@
         <v>316</v>
       </c>
       <c r="H14" s="23" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="I14" s="23" t="s">
+        <v>1696</v>
+      </c>
+      <c r="L14" s="23" t="s">
         <v>1697</v>
-      </c>
-      <c r="L14" s="23" t="s">
-        <v>1698</v>
       </c>
       <c r="N14" s="1" t="s">
         <v>1443</v>
@@ -10302,16 +10309,16 @@
         <v>340</v>
       </c>
       <c r="H15" s="23" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="I15" s="23" t="s">
+        <v>1658</v>
+      </c>
+      <c r="J15" s="23" t="s">
         <v>1659</v>
       </c>
-      <c r="J15" s="23" t="s">
+      <c r="L15" s="23" t="s">
         <v>1660</v>
-      </c>
-      <c r="L15" s="23" t="s">
-        <v>1661</v>
       </c>
       <c r="N15" s="1" t="s">
         <v>1443</v>
@@ -10380,16 +10387,16 @@
         <v>116</v>
       </c>
       <c r="H16" s="23" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="I16" s="23" t="s">
+        <v>1698</v>
+      </c>
+      <c r="J16" s="23" t="s">
         <v>1699</v>
       </c>
-      <c r="J16" s="23" t="s">
-        <v>1700</v>
-      </c>
       <c r="L16" s="23" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
       <c r="M16" s="1" t="s">
         <v>1517</v>
@@ -10455,16 +10462,16 @@
         <v>413</v>
       </c>
       <c r="F17" s="15" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="G17" s="23" t="s">
         <v>414</v>
       </c>
       <c r="H17" s="23" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
       <c r="I17" s="23" t="s">
-        <v>1650</v>
+        <v>1649</v>
       </c>
       <c r="M17" s="1" t="s">
         <v>1517</v>
@@ -10530,19 +10537,19 @@
         <v>417</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="G18" s="23" t="s">
         <v>414</v>
       </c>
       <c r="H18" s="23" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
       <c r="I18" s="23" t="s">
-        <v>1650</v>
+        <v>1649</v>
       </c>
       <c r="J18" s="23" t="s">
-        <v>1703</v>
+        <v>1702</v>
       </c>
       <c r="M18" s="1" t="s">
         <v>1517</v>
@@ -10608,16 +10615,16 @@
         <v>45</v>
       </c>
       <c r="F19" s="15" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
       <c r="G19" s="23" t="s">
         <v>46</v>
       </c>
       <c r="H19" s="23" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="K19" s="23" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="M19" s="1" t="s">
         <v>1518</v>
@@ -10689,13 +10696,13 @@
         <v>153</v>
       </c>
       <c r="H20" s="23" t="s">
-        <v>1709</v>
+        <v>1708</v>
       </c>
       <c r="I20" s="23" t="s">
-        <v>1650</v>
+        <v>1649</v>
       </c>
       <c r="K20" s="23" t="s">
-        <v>1647</v>
+        <v>1646</v>
       </c>
       <c r="N20" s="1" t="s">
         <v>1443</v>
@@ -10764,10 +10771,10 @@
         <v>157</v>
       </c>
       <c r="H21" s="23" t="s">
-        <v>1709</v>
+        <v>1708</v>
       </c>
       <c r="I21" s="23" t="s">
-        <v>1650</v>
+        <v>1649</v>
       </c>
       <c r="N21" s="1" t="s">
         <v>1443</v>
@@ -10836,13 +10843,13 @@
         <v>71</v>
       </c>
       <c r="H22" s="23" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="I22" s="23" t="s">
+        <v>1709</v>
+      </c>
+      <c r="L22" s="23" t="s">
         <v>1710</v>
-      </c>
-      <c r="L22" s="23" t="s">
-        <v>1711</v>
       </c>
       <c r="M22" s="1" t="s">
         <v>1517</v>
@@ -10980,13 +10987,13 @@
         <v>293</v>
       </c>
       <c r="H24" s="23" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
       <c r="I24" s="23" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="K24" s="23" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
       <c r="M24" s="1" t="s">
         <v>1517</v>
@@ -11523,19 +11530,19 @@
         <v>293</v>
       </c>
       <c r="H32" s="23" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="I32" s="23" t="s">
+        <v>1666</v>
+      </c>
+      <c r="J32" s="23" t="s">
         <v>1667</v>
       </c>
-      <c r="J32" s="23" t="s">
-        <v>1668</v>
-      </c>
       <c r="K32" s="23" t="s">
+        <v>1669</v>
+      </c>
+      <c r="L32" s="23" t="s">
         <v>1670</v>
-      </c>
-      <c r="L32" s="23" t="s">
-        <v>1671</v>
       </c>
       <c r="M32" s="1" t="s">
         <v>1517</v>
@@ -13002,7 +13009,7 @@
         <v>76</v>
       </c>
       <c r="F54" s="15" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="G54" s="23" t="s">
         <v>77</v>
@@ -13755,13 +13762,13 @@
         <v>116</v>
       </c>
       <c r="H65" s="23" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="I65" s="23" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
       <c r="K65" s="23" t="s">
-        <v>1701</v>
+        <v>1700</v>
       </c>
       <c r="M65" s="1" t="s">
         <v>1517</v>
@@ -14502,13 +14509,13 @@
         <v>293</v>
       </c>
       <c r="H76" s="23" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="I76" s="23" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
       <c r="K76" s="23" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
       <c r="M76" s="1" t="s">
         <v>1517</v>
@@ -15250,19 +15257,19 @@
         <v>293</v>
       </c>
       <c r="H87" s="23" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="I87" s="23" t="s">
+        <v>1666</v>
+      </c>
+      <c r="J87" s="23" t="s">
         <v>1667</v>
       </c>
-      <c r="J87" s="23" t="s">
-        <v>1668</v>
-      </c>
       <c r="K87" s="23" t="s">
+        <v>1669</v>
+      </c>
+      <c r="L87" s="23" t="s">
         <v>1670</v>
-      </c>
-      <c r="L87" s="23" t="s">
-        <v>1671</v>
       </c>
       <c r="M87" s="1" t="s">
         <v>1517</v>
@@ -15334,16 +15341,16 @@
         <v>293</v>
       </c>
       <c r="H88" s="23" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="I88" s="23" t="s">
+        <v>1636</v>
+      </c>
+      <c r="K88" s="23" t="s">
         <v>1637</v>
       </c>
-      <c r="K88" s="23" t="s">
-        <v>1638</v>
-      </c>
       <c r="L88" s="23" t="s">
-        <v>1673</v>
+        <v>1672</v>
       </c>
       <c r="M88" s="1" t="s">
         <v>1517</v>
@@ -16222,19 +16229,19 @@
         <v>378</v>
       </c>
       <c r="H101" s="23" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="I101" s="23" t="s">
+        <v>1680</v>
+      </c>
+      <c r="J101" s="23" t="s">
         <v>1681</v>
       </c>
-      <c r="J101" s="23" t="s">
+      <c r="K101" s="23" t="s">
+        <v>1683</v>
+      </c>
+      <c r="L101" s="23" t="s">
         <v>1682</v>
-      </c>
-      <c r="K101" s="23" t="s">
-        <v>1684</v>
-      </c>
-      <c r="L101" s="23" t="s">
-        <v>1683</v>
       </c>
       <c r="N101" s="1" t="s">
         <v>1443</v>
@@ -16363,7 +16370,7 @@
         <v>80</v>
       </c>
       <c r="F103" s="27" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="G103" s="23" t="s">
         <v>77</v>
@@ -16438,16 +16445,16 @@
         <v>348</v>
       </c>
       <c r="H104" s="23" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="I104" s="23" t="s">
+        <v>1636</v>
+      </c>
+      <c r="J104" s="23" t="s">
+        <v>1693</v>
+      </c>
+      <c r="K104" s="23" t="s">
         <v>1637</v>
-      </c>
-      <c r="J104" s="23" t="s">
-        <v>1694</v>
-      </c>
-      <c r="K104" s="23" t="s">
-        <v>1638</v>
       </c>
       <c r="N104" s="1" t="s">
         <v>1443</v>
@@ -16780,16 +16787,16 @@
         <v>293</v>
       </c>
       <c r="H109" s="23" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="I109" s="23" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
       <c r="J109" s="23" t="s">
-        <v>1674</v>
+        <v>1673</v>
       </c>
       <c r="L109" s="23" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
       <c r="M109" s="1" t="s">
         <v>1517</v>
@@ -16993,19 +17000,19 @@
         <v>71</v>
       </c>
       <c r="H112" s="23" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="I112" s="23" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
       <c r="J112" s="23" t="s">
-        <v>1712</v>
+        <v>1711</v>
       </c>
       <c r="K112" s="23" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
       <c r="L112" s="23" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
       <c r="M112" s="1" t="s">
         <v>1517</v>
@@ -17077,19 +17084,19 @@
         <v>94</v>
       </c>
       <c r="H113" s="23" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="I113" s="23" t="s">
-        <v>1637</v>
+        <v>1636</v>
       </c>
       <c r="J113" s="23" t="s">
+        <v>1642</v>
+      </c>
+      <c r="K113" s="23" t="s">
         <v>1643</v>
       </c>
-      <c r="K113" s="23" t="s">
+      <c r="L113" s="23" t="s">
         <v>1644</v>
-      </c>
-      <c r="L113" s="23" t="s">
-        <v>1645</v>
       </c>
       <c r="M113" s="1" t="s">
         <v>1518</v>
@@ -17366,19 +17373,19 @@
         <v>94</v>
       </c>
       <c r="H117" s="23" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="I117" s="23" t="s">
-        <v>1640</v>
+        <v>1639</v>
       </c>
       <c r="J117" s="23" t="s">
-        <v>1646</v>
+        <v>1645</v>
       </c>
       <c r="K117" s="23" t="s">
+        <v>1647</v>
+      </c>
+      <c r="L117" s="23" t="s">
         <v>1648</v>
-      </c>
-      <c r="L117" s="23" t="s">
-        <v>1649</v>
       </c>
       <c r="M117" s="1" t="s">
         <v>1518</v>
@@ -18326,10 +18333,10 @@
         <v>166</v>
       </c>
       <c r="H131" s="23" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="I131" s="23" t="s">
-        <v>1637</v>
+        <v>1636</v>
       </c>
       <c r="N131" s="1" t="s">
         <v>1443</v>
@@ -18794,16 +18801,16 @@
         <v>123</v>
       </c>
       <c r="H138" s="23" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="I138" s="23" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="K138" s="23" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="L138" s="23" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="N138" s="1" t="s">
         <v>1443</v>
@@ -19488,13 +19495,13 @@
         <v>123</v>
       </c>
       <c r="H148" s="23" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="I148" s="23" t="s">
-        <v>1637</v>
+        <v>1636</v>
       </c>
       <c r="L148" s="23" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="N148" s="1" t="s">
         <v>1443</v>
@@ -21040,16 +21047,16 @@
         <v>94</v>
       </c>
       <c r="H171" s="23" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="I171" s="23" t="s">
+        <v>1650</v>
+      </c>
+      <c r="K171" s="23" t="s">
         <v>1651</v>
       </c>
-      <c r="K171" s="23" t="s">
+      <c r="L171" s="23" t="s">
         <v>1652</v>
-      </c>
-      <c r="L171" s="23" t="s">
-        <v>1653</v>
       </c>
       <c r="M171" s="1" t="s">
         <v>1518</v>
@@ -21989,19 +21996,19 @@
         <v>71</v>
       </c>
       <c r="H185" s="23" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="I185" s="23" t="s">
-        <v>1637</v>
+        <v>1636</v>
       </c>
       <c r="J185" s="23" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="K185" s="23" t="s">
-        <v>1713</v>
+        <v>1712</v>
       </c>
       <c r="L185" s="23" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
       <c r="M185" s="1" t="s">
         <v>1517</v>
@@ -22142,13 +22149,13 @@
         <v>293</v>
       </c>
       <c r="H187" s="23" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
       <c r="I187" s="23" t="s">
-        <v>1677</v>
+        <v>1676</v>
       </c>
       <c r="J187" s="23" t="s">
-        <v>1675</v>
+        <v>1674</v>
       </c>
       <c r="M187" s="1" t="s">
         <v>1517</v>
@@ -23432,7 +23439,7 @@
         <v>1440</v>
       </c>
       <c r="L206" s="23" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="N206" s="1" t="s">
         <v>1443</v>
@@ -23765,7 +23772,7 @@
         <v>1522</v>
       </c>
       <c r="F211" s="26" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="G211" s="23" t="s">
         <v>1523</v>
@@ -23825,28 +23832,28 @@
         <v>t-kun</v>
       </c>
       <c r="C212" s="24" t="s">
+        <v>1760</v>
+      </c>
+      <c r="D212" s="23" t="s">
         <v>1525</v>
       </c>
-      <c r="D212" s="23" t="s">
+      <c r="E212" s="23" t="s">
         <v>1526</v>
       </c>
-      <c r="E212" s="23" t="s">
+      <c r="F212" s="15" t="s">
         <v>1527</v>
       </c>
-      <c r="F212" s="15" t="s">
-        <v>1528</v>
-      </c>
       <c r="G212" s="23" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="H212" s="23" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="I212" s="23" t="s">
-        <v>1637</v>
+        <v>1636</v>
       </c>
       <c r="K212" s="23" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="M212" s="1" t="s">
         <v>1518</v>
@@ -23866,9 +23873,12 @@
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
         <v/>
       </c>
-      <c r="S212" s="24">
+      <c r="R212" s="1" t="s">
+        <v>1193</v>
+      </c>
+      <c r="S212" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
-        <v>0.93668751332129163</v>
+        <v/>
       </c>
       <c r="T212" s="23" t="str">
         <f>"|&amp;image("&amp;テーブル1[[#This Row],[画像]]&amp;".png,width=100,height=100)"</f>
@@ -23876,7 +23886,7 @@
       </c>
       <c r="U212" s="23" t="str">
         <f>"|MIDDLE:​"&amp;テーブル1[[#This Row],[名前]]</f>
-        <v>|MIDDLE:​Ｔくん</v>
+        <v>|MIDDLE:​Tくん</v>
       </c>
       <c r="V212" s="23" t="str">
         <f>"|MIDDLE:​"&amp;テーブル1[[#This Row],[なまえ]]</f>
@@ -23903,43 +23913,49 @@
         <v>316</v>
       </c>
       <c r="D213" s="23" t="s">
+        <v>1528</v>
+      </c>
+      <c r="E213" s="23" t="s">
         <v>1529</v>
       </c>
-      <c r="E213" s="23" t="s">
+      <c r="F213" s="15" t="s">
+        <v>1527</v>
+      </c>
+      <c r="G213" s="23" t="s">
         <v>1530</v>
       </c>
-      <c r="F213" s="15" t="s">
-        <v>1528</v>
-      </c>
-      <c r="G213" s="23" t="s">
-        <v>1531</v>
-      </c>
       <c r="H213" s="23" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
       <c r="I213" s="23" t="s">
-        <v>1655</v>
+        <v>1761</v>
       </c>
       <c r="K213" s="23" t="s">
-        <v>1730</v>
+        <v>1729</v>
       </c>
       <c r="L213" s="23" t="s">
-        <v>1760</v>
+        <v>1759</v>
       </c>
       <c r="M213" s="1" t="s">
         <v>1518</v>
       </c>
+      <c r="N213" s="1" t="s">
+        <v>1443</v>
+      </c>
       <c r="O213" s="24" t="str">
         <f>テーブル1[[#This Row],[リンク]]&amp;テーブル1[[#This Row],[描画状況]]</f>
-        <v>https://mackerel178.wixsite.com/yuusensuizokukan</v>
+        <v>https://mackerel178.wixsite.com/yuusensuizokukan済</v>
       </c>
       <c r="P213" s="17">
         <f>1-(COUNTIF(O:O,_xlfn.TEXTJOIN(",",TRUE,テーブル1[[#This Row],[リンク]],テーブル1[[#This Row],[描画状況]]))/COUNTIF(F:F,テーブル1[[#This Row],[リンク]]))</f>
-        <v>0.5</v>
-      </c>
-      <c r="Q213" s="16">
+        <v>1</v>
+      </c>
+      <c r="Q213" s="16" t="str">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>50.03929268745734</v>
+        <v/>
+      </c>
+      <c r="R213" s="1" t="s">
+        <v>1193</v>
       </c>
       <c r="S213" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -23975,19 +23991,19 @@
         <v>fukami-marine</v>
       </c>
       <c r="C214" s="24" t="s">
+        <v>1532</v>
+      </c>
+      <c r="D214" s="23" t="s">
         <v>1533</v>
       </c>
-      <c r="D214" s="23" t="s">
+      <c r="E214" s="23" t="s">
         <v>1534</v>
       </c>
-      <c r="E214" s="23" t="s">
+      <c r="F214" s="15" t="s">
+        <v>1536</v>
+      </c>
+      <c r="G214" s="23" t="s">
         <v>1535</v>
-      </c>
-      <c r="F214" s="15" t="s">
-        <v>1537</v>
-      </c>
-      <c r="G214" s="23" t="s">
-        <v>1536</v>
       </c>
       <c r="M214" s="1" t="s">
         <v>1517</v>
@@ -24044,19 +24060,19 @@
         <v>colorful-sugar-sprinkle</v>
       </c>
       <c r="C215" s="24" t="s">
+        <v>1538</v>
+      </c>
+      <c r="D215" s="23" t="s">
+        <v>1547</v>
+      </c>
+      <c r="E215" s="23" t="s">
         <v>1539</v>
       </c>
-      <c r="D215" s="23" t="s">
-        <v>1548</v>
-      </c>
-      <c r="E215" s="23" t="s">
+      <c r="F215" s="15" t="s">
+        <v>1610</v>
+      </c>
+      <c r="G215" s="23" t="s">
         <v>1540</v>
-      </c>
-      <c r="F215" s="15" t="s">
-        <v>1611</v>
-      </c>
-      <c r="G215" s="23" t="s">
-        <v>1541</v>
       </c>
       <c r="M215" s="1" t="s">
         <v>1517</v>
@@ -24128,16 +24144,16 @@
         <v>71</v>
       </c>
       <c r="H216" s="23" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="I216" s="23" t="s">
-        <v>1650</v>
+        <v>1649</v>
       </c>
       <c r="K216" s="23" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
       <c r="L216" s="23" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="M216" s="1" t="s">
         <v>1517</v>
@@ -24194,19 +24210,19 @@
         <v>nekonari</v>
       </c>
       <c r="C217" s="24" t="s">
+        <v>1541</v>
+      </c>
+      <c r="D217" s="23" t="s">
         <v>1542</v>
       </c>
-      <c r="D217" s="23" t="s">
+      <c r="E217" s="23" t="s">
         <v>1543</v>
       </c>
-      <c r="E217" s="23" t="s">
+      <c r="F217" s="15" t="s">
         <v>1544</v>
       </c>
-      <c r="F217" s="15" t="s">
+      <c r="G217" s="23" t="s">
         <v>1545</v>
-      </c>
-      <c r="G217" s="23" t="s">
-        <v>1546</v>
       </c>
       <c r="M217" s="1" t="s">
         <v>1517</v>
@@ -24263,13 +24279,13 @@
         <v>meganeko-mikketa</v>
       </c>
       <c r="C218" s="24" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="D218" s="23" t="s">
+        <v>1548</v>
+      </c>
+      <c r="E218" s="23" t="s">
         <v>1549</v>
-      </c>
-      <c r="E218" s="23" t="s">
-        <v>1550</v>
       </c>
       <c r="F218" s="15" t="s">
         <v>292</v>
@@ -24278,19 +24294,19 @@
         <v>293</v>
       </c>
       <c r="H218" s="23" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="I218" s="23" t="s">
+        <v>1636</v>
+      </c>
+      <c r="J218" s="23" t="s">
+        <v>1634</v>
+      </c>
+      <c r="K218" s="23" t="s">
         <v>1637</v>
       </c>
-      <c r="J218" s="23" t="s">
-        <v>1635</v>
-      </c>
-      <c r="K218" s="23" t="s">
-        <v>1638</v>
-      </c>
       <c r="L218" s="23" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="M218" s="1" t="s">
         <v>1517</v>
@@ -24347,13 +24363,13 @@
         <v>aster-flores</v>
       </c>
       <c r="C219" s="24" t="s">
+        <v>1564</v>
+      </c>
+      <c r="D219" s="23" t="s">
+        <v>1566</v>
+      </c>
+      <c r="E219" s="23" t="s">
         <v>1565</v>
-      </c>
-      <c r="D219" s="23" t="s">
-        <v>1567</v>
-      </c>
-      <c r="E219" s="23" t="s">
-        <v>1566</v>
       </c>
       <c r="F219" s="2" t="s">
         <v>215</v>
@@ -24416,28 +24432,28 @@
         <v>yoizuki-mikumo</v>
       </c>
       <c r="C220" s="24" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="D220" s="23" t="s">
+        <v>1578</v>
+      </c>
+      <c r="E220" s="23" t="s">
         <v>1579</v>
       </c>
-      <c r="E220" s="23" t="s">
-        <v>1580</v>
-      </c>
       <c r="F220" s="15" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="G220" s="23" t="s">
         <v>414</v>
       </c>
       <c r="H220" s="23" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="I220" s="23" t="s">
-        <v>1650</v>
+        <v>1649</v>
       </c>
       <c r="K220" s="23" t="s">
-        <v>1702</v>
+        <v>1701</v>
       </c>
       <c r="M220" s="1" t="s">
         <v>1517</v>
@@ -24494,22 +24510,22 @@
         <v>kang-unshim</v>
       </c>
       <c r="C221" s="24" t="s">
+        <v>1584</v>
+      </c>
+      <c r="D221" s="23" t="s">
         <v>1585</v>
       </c>
-      <c r="D221" s="23" t="s">
+      <c r="E221" s="23" t="s">
         <v>1586</v>
       </c>
-      <c r="E221" s="23" t="s">
+      <c r="F221" s="15" t="s">
         <v>1587</v>
       </c>
-      <c r="F221" s="15" t="s">
+      <c r="G221" s="23" t="s">
         <v>1588</v>
       </c>
-      <c r="G221" s="23" t="s">
+      <c r="M221" s="1" t="s">
         <v>1589</v>
-      </c>
-      <c r="M221" s="1" t="s">
-        <v>1590</v>
       </c>
       <c r="N221" s="1" t="s">
         <v>1443</v>
@@ -24563,22 +24579,22 @@
         <v>optima-215</v>
       </c>
       <c r="C222" s="24" t="s">
+        <v>1590</v>
+      </c>
+      <c r="D222" s="23" t="s">
         <v>1591</v>
       </c>
-      <c r="D222" s="23" t="s">
+      <c r="E222" s="23" t="s">
         <v>1592</v>
       </c>
-      <c r="E222" s="23" t="s">
+      <c r="F222" s="15" t="s">
+        <v>1587</v>
+      </c>
+      <c r="G222" s="23" t="s">
         <v>1593</v>
       </c>
-      <c r="F222" s="15" t="s">
-        <v>1588</v>
-      </c>
-      <c r="G222" s="23" t="s">
-        <v>1594</v>
-      </c>
       <c r="M222" s="1" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="N222" s="1" t="s">
         <v>1443</v>
@@ -24632,23 +24648,23 @@
         <v>kyle-tyler</v>
       </c>
       <c r="C223" s="24" t="s">
+        <v>1594</v>
+      </c>
+      <c r="D223" s="23" t="s">
         <v>1595</v>
       </c>
-      <c r="D223" s="23" t="s">
+      <c r="E223" s="23" t="s">
         <v>1596</v>
       </c>
-      <c r="E223" s="23" t="s">
-        <v>1597</v>
-      </c>
       <c r="F223" s="15" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="G223" s="23" t="str">
         <f>テーブル1[[#This Row],[名前]]&amp;"(UTAU)"</f>
         <v>カイル・タイラー(UTAU)</v>
       </c>
       <c r="M223" s="1" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="N223" s="1" t="s">
         <v>1443</v>
@@ -24702,19 +24718,19 @@
         <v>tone-too</v>
       </c>
       <c r="C224" s="24" t="s">
+        <v>1597</v>
+      </c>
+      <c r="D224" s="23" t="s">
         <v>1598</v>
       </c>
-      <c r="D224" s="23" t="s">
+      <c r="E224" s="23" t="s">
         <v>1599</v>
       </c>
-      <c r="E224" s="23" t="s">
+      <c r="F224" s="15" t="s">
         <v>1600</v>
       </c>
-      <c r="F224" s="15" t="s">
+      <c r="G224" s="23" t="s">
         <v>1601</v>
-      </c>
-      <c r="G224" s="23" t="s">
-        <v>1602</v>
       </c>
       <c r="N224" s="1" t="s">
         <v>1443</v>
@@ -24768,22 +24784,22 @@
         <v>fuwa-maria</v>
       </c>
       <c r="C225" s="24" t="s">
+        <v>1602</v>
+      </c>
+      <c r="D225" s="23" t="s">
         <v>1603</v>
       </c>
-      <c r="D225" s="23" t="s">
+      <c r="E225" s="23" t="s">
         <v>1604</v>
       </c>
-      <c r="E225" s="23" t="s">
+      <c r="F225" s="15" t="s">
         <v>1605</v>
       </c>
-      <c r="F225" s="15" t="s">
+      <c r="G225" s="23" t="s">
         <v>1606</v>
       </c>
-      <c r="G225" s="23" t="s">
-        <v>1607</v>
-      </c>
       <c r="M225" s="1" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="N225" s="1" t="s">
         <v>1443</v>
@@ -24837,22 +24853,22 @@
         <v>maruaria</v>
       </c>
       <c r="C226" s="24" t="s">
+        <v>1607</v>
+      </c>
+      <c r="D226" s="23" t="s">
         <v>1608</v>
       </c>
-      <c r="D226" s="23" t="s">
+      <c r="E226" s="23" t="s">
         <v>1609</v>
       </c>
-      <c r="E226" s="23" t="s">
+      <c r="F226" s="15" t="s">
         <v>1610</v>
       </c>
-      <c r="F226" s="15" t="s">
+      <c r="G226" s="23" t="s">
         <v>1611</v>
       </c>
-      <c r="G226" s="23" t="s">
-        <v>1612</v>
-      </c>
       <c r="M226" s="1" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="N226" s="1" t="s">
         <v>1443</v>
@@ -24906,22 +24922,22 @@
         <v>sanity-doyou</v>
       </c>
       <c r="C227" s="24" t="s">
+        <v>1612</v>
+      </c>
+      <c r="D227" s="23" t="s">
         <v>1613</v>
       </c>
-      <c r="D227" s="23" t="s">
+      <c r="E227" s="23" t="s">
         <v>1614</v>
       </c>
-      <c r="E227" s="23" t="s">
+      <c r="F227" s="15" t="s">
+        <v>1610</v>
+      </c>
+      <c r="G227" s="23" t="s">
         <v>1615</v>
       </c>
-      <c r="F227" s="15" t="s">
-        <v>1611</v>
-      </c>
-      <c r="G227" s="23" t="s">
-        <v>1616</v>
-      </c>
       <c r="M227" s="1" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="N227" s="1" t="s">
         <v>1443</v>
@@ -24975,37 +24991,37 @@
         <v>iruya-rui</v>
       </c>
       <c r="C228" s="24" t="s">
+        <v>1717</v>
+      </c>
+      <c r="D228" s="23" t="s">
         <v>1718</v>
       </c>
-      <c r="D228" s="23" t="s">
+      <c r="E228" s="23" t="s">
         <v>1719</v>
       </c>
-      <c r="E228" s="23" t="s">
+      <c r="F228" s="15" t="s">
         <v>1720</v>
       </c>
-      <c r="F228" s="15" t="s">
+      <c r="G228" s="23" t="s">
         <v>1721</v>
       </c>
-      <c r="G228" s="23" t="s">
+      <c r="H228" s="23" t="s">
+        <v>1626</v>
+      </c>
+      <c r="I228" s="23" t="s">
+        <v>1649</v>
+      </c>
+      <c r="J228" s="23" t="s">
         <v>1722</v>
       </c>
-      <c r="H228" s="23" t="s">
-        <v>1627</v>
-      </c>
-      <c r="I228" s="23" t="s">
-        <v>1650</v>
-      </c>
-      <c r="J228" s="23" t="s">
+      <c r="K228" s="23" t="s">
         <v>1723</v>
       </c>
-      <c r="K228" s="23" t="s">
-        <v>1724</v>
-      </c>
       <c r="L228" s="23" t="s">
-        <v>1738</v>
+        <v>1737</v>
       </c>
       <c r="M228" s="1" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="N228" s="1" t="s">
         <v>1443</v>
@@ -25059,31 +25075,31 @@
         <v>​hagane-meta</v>
       </c>
       <c r="C229" s="24" t="s">
+        <v>1724</v>
+      </c>
+      <c r="D229" s="23" t="s">
         <v>1725</v>
       </c>
-      <c r="D229" s="23" t="s">
+      <c r="E229" s="23" t="s">
         <v>1726</v>
       </c>
-      <c r="E229" s="23" t="s">
+      <c r="F229" s="3" t="s">
         <v>1727</v>
       </c>
-      <c r="F229" s="3" t="s">
+      <c r="G229" s="23" t="s">
         <v>1728</v>
       </c>
-      <c r="G229" s="23" t="s">
+      <c r="H229" s="23" t="s">
+        <v>1626</v>
+      </c>
+      <c r="I229" s="23" t="s">
+        <v>1636</v>
+      </c>
+      <c r="K229" s="23" t="s">
         <v>1729</v>
       </c>
-      <c r="H229" s="23" t="s">
-        <v>1627</v>
-      </c>
-      <c r="I229" s="23" t="s">
-        <v>1637</v>
-      </c>
-      <c r="K229" s="23" t="s">
+      <c r="M229" s="1" t="s">
         <v>1730</v>
-      </c>
-      <c r="M229" s="1" t="s">
-        <v>1731</v>
       </c>
       <c r="N229" s="1" t="s">
         <v>1443</v>
@@ -25137,31 +25153,31 @@
         <v>the-bard-euphoria</v>
       </c>
       <c r="C230" s="24" t="s">
+        <v>1742</v>
+      </c>
+      <c r="D230" s="23" t="s">
         <v>1743</v>
       </c>
-      <c r="D230" s="23" t="s">
+      <c r="E230" s="23" t="s">
         <v>1744</v>
       </c>
-      <c r="E230" s="23" t="s">
+      <c r="F230" s="30" t="s">
+        <v>1750</v>
+      </c>
+      <c r="G230" s="23" t="s">
+        <v>1746</v>
+      </c>
+      <c r="H230" s="23" t="s">
+        <v>1662</v>
+      </c>
+      <c r="I230" s="23" t="s">
+        <v>1636</v>
+      </c>
+      <c r="J230" s="23" t="s">
         <v>1745</v>
       </c>
-      <c r="F230" s="30" t="s">
-        <v>1751</v>
-      </c>
-      <c r="G230" s="23" t="s">
-        <v>1747</v>
-      </c>
-      <c r="H230" s="23" t="s">
-        <v>1663</v>
-      </c>
-      <c r="I230" s="23" t="s">
-        <v>1637</v>
-      </c>
-      <c r="J230" s="23" t="s">
-        <v>1746</v>
-      </c>
       <c r="M230" s="1" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="N230" s="1" t="s">
         <v>1443</v>
@@ -25215,34 +25231,34 @@
         <v>arujine-sarasa</v>
       </c>
       <c r="C231" s="24" t="s">
+        <v>1751</v>
+      </c>
+      <c r="D231" s="23" t="s">
         <v>1752</v>
       </c>
-      <c r="D231" s="23" t="s">
+      <c r="E231" s="23" t="s">
         <v>1753</v>
       </c>
-      <c r="E231" s="23" t="s">
+      <c r="F231" s="30" t="s">
         <v>1754</v>
       </c>
-      <c r="F231" s="30" t="s">
+      <c r="G231" s="23" t="s">
         <v>1755</v>
       </c>
-      <c r="G231" s="23" t="s">
+      <c r="H231" s="23" t="s">
+        <v>1627</v>
+      </c>
+      <c r="I231" s="23" t="s">
         <v>1756</v>
       </c>
-      <c r="H231" s="23" t="s">
-        <v>1628</v>
-      </c>
-      <c r="I231" s="23" t="s">
+      <c r="K231" s="23" t="s">
+        <v>1758</v>
+      </c>
+      <c r="L231" s="23" t="s">
         <v>1757</v>
       </c>
-      <c r="K231" s="23" t="s">
-        <v>1759</v>
-      </c>
-      <c r="L231" s="23" t="s">
-        <v>1758</v>
-      </c>
       <c r="M231" s="1" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="N231" s="1" t="s">
         <v>1443</v>
@@ -25293,28 +25309,28 @@
         <v>aira</v>
       </c>
       <c r="C232" s="24" t="s">
+        <v>1747</v>
+      </c>
+      <c r="D232" s="23" t="s">
         <v>1748</v>
       </c>
-      <c r="D232" s="23" t="s">
+      <c r="E232" s="23" t="s">
         <v>1749</v>
       </c>
-      <c r="E232" s="23" t="s">
+      <c r="F232" s="3" t="s">
         <v>1750</v>
       </c>
-      <c r="F232" s="3" t="s">
-        <v>1751</v>
-      </c>
       <c r="G232" s="23" t="s">
-        <v>1747</v>
+        <v>1746</v>
       </c>
       <c r="H232" s="23" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="I232" s="23" t="s">
-        <v>1637</v>
+        <v>1636</v>
       </c>
       <c r="M232" s="1" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="O232" s="24" t="str">
         <f>テーブル1[[#This Row],[リンク]]&amp;テーブル1[[#This Row],[描画状況]]</f>
@@ -25326,7 +25342,7 @@
       </c>
       <c r="Q232" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>50.890607279195642</v>
+        <v>50.505607332199496</v>
       </c>
       <c r="S232" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -25359,28 +25375,28 @@
         <v>kagetsuki-reine</v>
       </c>
       <c r="C233" s="24" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
       <c r="D233" s="23" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="E233" s="23" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="F233" s="2" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="G233" s="23" t="s">
         <v>414</v>
       </c>
       <c r="H233" s="23" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="I233" s="23" t="s">
-        <v>1650</v>
+        <v>1649</v>
       </c>
       <c r="L233" s="23" t="s">
-        <v>1673</v>
+        <v>1672</v>
       </c>
       <c r="M233" s="1" t="s">
         <v>1517</v>
@@ -25395,7 +25411,7 @@
       </c>
       <c r="Q233" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>60.759255348963762</v>
+        <v>60.379739512700837</v>
       </c>
       <c r="S233" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -25428,25 +25444,25 @@
         <v>akatsuki-haruki</v>
       </c>
       <c r="C234" s="24" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="D234" s="23" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="E234" s="23" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="F234" s="2" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="G234" s="23" t="s">
         <v>414</v>
       </c>
       <c r="H234" s="23" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="I234" s="23" t="s">
-        <v>1650</v>
+        <v>1649</v>
       </c>
       <c r="M234" s="1" t="s">
         <v>1517</v>
@@ -25461,7 +25477,7 @@
       </c>
       <c r="Q234" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>60.879315291841372</v>
+        <v>60.761685497965345</v>
       </c>
       <c r="S234" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -25521,7 +25537,7 @@
       </c>
       <c r="Q235" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.25498482480194296</v>
+        <v>3.6847691650474745E-2</v>
       </c>
       <c r="S235" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -25581,7 +25597,7 @@
       </c>
       <c r="Q236" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.916184174830647</v>
+        <v>33.553816205173106</v>
       </c>
       <c r="S236" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -25641,7 +25657,7 @@
       </c>
       <c r="Q237" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.932598918742876</v>
+        <v>33.748046259823312</v>
       </c>
       <c r="S237" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -25698,7 +25714,7 @@
       </c>
       <c r="Q238" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.867568521334311</v>
+        <v>12.600196744112752</v>
       </c>
       <c r="S238" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -25758,7 +25774,7 @@
       </c>
       <c r="Q239" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>10.005248584281633</v>
+        <v>10.801227369943678</v>
       </c>
       <c r="S239" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -25818,7 +25834,7 @@
       </c>
       <c r="Q240" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.125242447441277</v>
+        <v>20.236481888558565</v>
       </c>
       <c r="S240" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -25880,7 +25896,7 @@
       </c>
       <c r="Q241" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.381717226842746</v>
+        <v>12.744148905322785</v>
       </c>
       <c r="S241" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -25937,7 +25953,7 @@
       </c>
       <c r="Q242" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.625730980579123</v>
+        <v>13.163728957297048</v>
       </c>
       <c r="S242" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -25997,7 +26013,7 @@
       </c>
       <c r="Q243" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>10.341101625763535</v>
+        <v>10.759946349612452</v>
       </c>
       <c r="S243" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -26057,7 +26073,7 @@
       </c>
       <c r="Q244" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.161519695887876</v>
+        <v>20.76747554676993</v>
       </c>
       <c r="S244" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -26117,7 +26133,7 @@
       </c>
       <c r="Q245" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.92479917075325</v>
+        <v>20.54147063192276</v>
       </c>
       <c r="S245" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -26177,7 +26193,7 @@
       </c>
       <c r="Q246" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.654488593036088</v>
+        <v>20.294052252975913</v>
       </c>
       <c r="S246" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -26237,7 +26253,7 @@
       </c>
       <c r="Q247" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.613932665218929</v>
+        <v>20.55634091617474</v>
       </c>
       <c r="S247" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -26297,7 +26313,7 @@
       </c>
       <c r="Q248" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.582199625045224</v>
+        <v>20.241643881731068</v>
       </c>
       <c r="S248" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -26357,7 +26373,7 @@
       </c>
       <c r="Q249" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.095712316057096</v>
+        <v>20.876848128224914</v>
       </c>
       <c r="S249" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -26417,7 +26433,7 @@
       </c>
       <c r="Q250" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.087647733145069</v>
+        <v>20.601577740571482</v>
       </c>
       <c r="S250" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -26477,7 +26493,7 @@
       </c>
       <c r="Q251" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.091269064235462</v>
+        <v>20.921289336430242</v>
       </c>
       <c r="S251" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -26537,7 +26553,7 @@
       </c>
       <c r="Q252" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.937372145192139</v>
+        <v>20.827787313882833</v>
       </c>
       <c r="S252" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -26597,7 +26613,7 @@
       </c>
       <c r="Q253" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.128479695156127</v>
+        <v>20.400826340699119</v>
       </c>
       <c r="S253" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -26657,7 +26673,7 @@
       </c>
       <c r="Q254" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.178492142783419</v>
+        <v>20.227377896992486</v>
       </c>
       <c r="S254" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -26717,7 +26733,7 @@
       </c>
       <c r="Q255" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.168256944724853</v>
+        <v>20.363099930158619</v>
       </c>
       <c r="S255" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -26775,7 +26791,7 @@
       </c>
       <c r="Q256" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.24334009923203</v>
+        <v>13.019108266830987</v>
       </c>
       <c r="S256" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -26832,7 +26848,7 @@
       </c>
       <c r="Q257" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>40.802569070013348</v>
+        <v>40.862023503965752</v>
       </c>
       <c r="S257" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -26889,7 +26905,7 @@
       </c>
       <c r="Q258" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.7442579136087009</v>
+        <v>7.8716226887227219</v>
       </c>
       <c r="S258" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -26946,7 +26962,7 @@
       </c>
       <c r="Q259" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>50.888715228297187</v>
+        <v>50.363600526426005</v>
       </c>
       <c r="S259" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27003,7 +27019,7 @@
       </c>
       <c r="Q260" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.57720774487603299</v>
+        <v>0.42927306868497828</v>
       </c>
       <c r="S260" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27060,7 +27076,7 @@
       </c>
       <c r="Q261" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.86105825745776732</v>
+        <v>0.89495362663275346</v>
       </c>
       <c r="S261" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27117,7 +27133,7 @@
       </c>
       <c r="Q262" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>8.1058866960289038</v>
+        <v>7.8121697112288579</v>
       </c>
       <c r="S262" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27178,7 +27194,7 @@
       </c>
       <c r="Q263" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>50.531011816306943</v>
+        <v>50.159399366455091</v>
       </c>
       <c r="S263" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27235,7 +27251,7 @@
       </c>
       <c r="Q264" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>34.052214271678004</v>
+        <v>34.15273129108764</v>
       </c>
       <c r="S264" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27292,7 +27308,7 @@
       </c>
       <c r="Q265" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.4337839912613664</v>
+        <v>7.3148100908519362</v>
       </c>
       <c r="S265" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27349,7 +27365,7 @@
       </c>
       <c r="Q266" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.624505814423092</v>
+        <v>13.285674487660776</v>
       </c>
       <c r="S266" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27406,7 +27422,7 @@
       </c>
       <c r="Q267" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.331330830451749</v>
+        <v>12.563655017480718</v>
       </c>
       <c r="S267" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27463,7 +27479,7 @@
       </c>
       <c r="Q268" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.939900333250561</v>
+        <v>13.065589078640542</v>
       </c>
       <c r="S268" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27520,7 +27536,7 @@
       </c>
       <c r="Q269" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>75.707711022476488</v>
+        <v>75.692836953828305</v>
       </c>
       <c r="S269" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27577,7 +27593,7 @@
       </c>
       <c r="Q270" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.231225701970937</v>
+        <v>12.884278208867073</v>
       </c>
       <c r="S270" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27634,7 +27650,7 @@
       </c>
       <c r="Q271" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.452827522487521</v>
+        <v>12.539185959864758</v>
       </c>
       <c r="S271" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27691,7 +27707,7 @@
       </c>
       <c r="Q272" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.40337077243495723</v>
+        <v>0.96239675487816589</v>
       </c>
       <c r="S272" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27748,7 +27764,7 @@
       </c>
       <c r="Q273" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.580992826750212</v>
+        <v>33.47376924721928</v>
       </c>
       <c r="S273" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27805,7 +27821,7 @@
       </c>
       <c r="Q274" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.312793284816227</v>
+        <v>12.653752968922811</v>
       </c>
       <c r="S274" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27862,7 +27878,7 @@
       </c>
       <c r="Q275" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.783913974853713</v>
+        <v>12.760978725125243</v>
       </c>
       <c r="S275" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27922,7 +27938,7 @@
       </c>
       <c r="Q276" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>50.262855184699738</v>
+        <v>50.667118032572851</v>
       </c>
       <c r="S276" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27979,7 +27995,7 @@
       </c>
       <c r="Q277" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.43126043259734825</v>
+        <v>0.29342687512017862</v>
       </c>
       <c r="S277" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28036,7 +28052,7 @@
       </c>
       <c r="Q278" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.20616120984099562</v>
+        <v>0.42866372387114249</v>
       </c>
       <c r="S278" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28097,7 +28113,7 @@
       </c>
       <c r="Q279" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>9.586799598469355</v>
+        <v>9.85104960497228</v>
       </c>
       <c r="S279" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28145,16 +28161,16 @@
         <v>1013</v>
       </c>
       <c r="H280" s="23" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="I280" s="23" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
       <c r="J280" s="23" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
       <c r="K280" s="23" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="O280" s="24" t="str">
         <f>テーブル1[[#This Row],[リンク]]&amp;テーブル1[[#This Row],[描画状況]]</f>
@@ -28166,7 +28182,7 @@
       </c>
       <c r="Q280" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>57.207867360089338</v>
+        <v>58.072498992451344</v>
       </c>
       <c r="S280" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28224,7 +28240,7 @@
       </c>
       <c r="Q281" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.299579347882297</v>
+        <v>20.929513670916119</v>
       </c>
       <c r="S281" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28281,7 +28297,7 @@
       </c>
       <c r="Q282" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.3803480347002015E-2</v>
+        <v>0.7111454928111286</v>
       </c>
       <c r="S282" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28341,7 +28357,7 @@
       </c>
       <c r="Q283" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>10.715300782603745</v>
+        <v>10.575091841546062</v>
       </c>
       <c r="S283" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28389,13 +28405,13 @@
         <v>94</v>
       </c>
       <c r="H284" s="23" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="I284" s="23" t="s">
-        <v>1651</v>
+        <v>1650</v>
       </c>
       <c r="K284" s="23" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="M284" s="1" t="s">
         <v>1518</v>
@@ -28410,7 +28426,7 @@
       </c>
       <c r="Q284" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>80.067502622123783</v>
+        <v>80.327031586752639</v>
       </c>
       <c r="S284" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28467,7 +28483,7 @@
       </c>
       <c r="Q285" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.292563970063723</v>
+        <v>7.8108017882645457</v>
       </c>
       <c r="S285" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28524,7 +28540,7 @@
       </c>
       <c r="Q286" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.076586628868005</v>
+        <v>12.907269447359893</v>
       </c>
       <c r="S286" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28584,7 +28600,7 @@
       </c>
       <c r="Q287" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>9.5144253304864659</v>
+        <v>10.052739782889818</v>
       </c>
       <c r="S287" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28641,7 +28657,7 @@
       </c>
       <c r="Q288" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.0537948300409714E-2</v>
+        <v>0.18718799119007179</v>
       </c>
       <c r="S288" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28689,16 +28705,16 @@
         <v>1013</v>
       </c>
       <c r="H289" s="23" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="I289" s="23" t="s">
+        <v>1636</v>
+      </c>
+      <c r="J289" s="23" t="s">
+        <v>1716</v>
+      </c>
+      <c r="K289" s="23" t="s">
         <v>1637</v>
-      </c>
-      <c r="J289" s="23" t="s">
-        <v>1717</v>
-      </c>
-      <c r="K289" s="23" t="s">
-        <v>1638</v>
       </c>
       <c r="O289" s="24" t="str">
         <f>テーブル1[[#This Row],[リンク]]&amp;テーブル1[[#This Row],[描画状況]]</f>
@@ -28710,7 +28726,7 @@
       </c>
       <c r="Q289" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>57.428002021772159</v>
+        <v>57.802313011755835</v>
       </c>
       <c r="S289" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28767,7 +28783,7 @@
       </c>
       <c r="Q290" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.244409123165241</v>
+        <v>12.657432988738165</v>
       </c>
       <c r="S290" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28827,7 +28843,7 @@
       </c>
       <c r="Q291" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>22.656884968866809</v>
+        <v>22.66494282707124</v>
       </c>
       <c r="S291" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28887,7 +28903,7 @@
       </c>
       <c r="Q292" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>60.732285090675077</v>
+        <v>60.44351925151097</v>
       </c>
       <c r="S292" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28944,7 +28960,7 @@
       </c>
       <c r="Q293" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.93902866580457078</v>
+        <v>0.35448288397834782</v>
       </c>
       <c r="S293" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29001,7 +29017,7 @@
       </c>
       <c r="Q294" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>50.898840225516395</v>
+        <v>50.912154310231287</v>
       </c>
       <c r="S294" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29061,7 +29077,7 @@
       </c>
       <c r="Q295" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>10.074706391191803</v>
+        <v>10.809357212872804</v>
       </c>
       <c r="S295" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29118,7 +29134,7 @@
       </c>
       <c r="Q296" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.88441431109024982</v>
+        <v>0.96725752563173162</v>
       </c>
       <c r="S296" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29178,7 +29194,7 @@
       </c>
       <c r="Q297" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>8.7932366847816024E-2</v>
+        <v>0.59639176790913384</v>
       </c>
       <c r="S297" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29226,10 +29242,10 @@
         <v>71</v>
       </c>
       <c r="H298" s="23" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
       <c r="I298" s="23" t="s">
-        <v>1716</v>
+        <v>1715</v>
       </c>
       <c r="O298" s="24" t="str">
         <f>テーブル1[[#This Row],[リンク]]&amp;テーブル1[[#This Row],[描画状況]]</f>
@@ -29241,7 +29257,7 @@
       </c>
       <c r="Q298" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>57.56736147644704</v>
+        <v>57.498433400865942</v>
       </c>
       <c r="S298" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29298,7 +29314,7 @@
       </c>
       <c r="Q299" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.26475531756347381</v>
+        <v>0.22089293289388279</v>
       </c>
       <c r="S299" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29355,7 +29371,7 @@
       </c>
       <c r="Q300" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.91437819042476942</v>
+        <v>0.50295647655085263</v>
       </c>
       <c r="S300" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29412,7 +29428,7 @@
       </c>
       <c r="Q301" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.6444951138925743</v>
+        <v>3.1283859010291071E-2</v>
       </c>
       <c r="S301" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29469,7 +29485,7 @@
       </c>
       <c r="Q302" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.95265229701961507</v>
+        <v>0.5127274892946605</v>
       </c>
       <c r="S302" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29529,7 +29545,7 @@
       </c>
       <c r="Q303" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.371953965367922</v>
+        <v>33.70699293225897</v>
       </c>
       <c r="S303" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29589,7 +29605,7 @@
       </c>
       <c r="Q304" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.23561834489373</v>
+        <v>20.747937142409807</v>
       </c>
       <c r="S304" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29646,7 +29662,7 @@
       </c>
       <c r="Q305" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.97855724409280376</v>
+        <v>7.7611351463603317E-2</v>
       </c>
       <c r="S305" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29703,7 +29719,7 @@
       </c>
       <c r="Q306" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>34.169378240487582</v>
+        <v>33.953076417006478</v>
       </c>
       <c r="S306" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29760,7 +29776,7 @@
       </c>
       <c r="Q307" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>34.026252507059688</v>
+        <v>33.555860054128523</v>
       </c>
       <c r="S307" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29821,7 +29837,7 @@
       </c>
       <c r="Q308" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>9.1947397766038144</v>
+        <v>9.3196104097097816</v>
       </c>
       <c r="S308" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29879,7 +29895,7 @@
       </c>
       <c r="Q309" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.12244101598033896</v>
+        <v>0.63560505382364019</v>
       </c>
       <c r="S309" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29941,7 +29957,7 @@
       </c>
       <c r="Q310" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.047730492557884</v>
+        <v>13.308108025142776</v>
       </c>
       <c r="S310" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29998,7 +30014,7 @@
       </c>
       <c r="Q311" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.61564117260620932</v>
+        <v>0.86232011635957895</v>
       </c>
       <c r="S311" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30055,7 +30071,7 @@
       </c>
       <c r="Q312" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>4.5101949136687747E-2</v>
+        <v>0.33439993828062342</v>
       </c>
       <c r="S312" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30112,7 +30128,7 @@
       </c>
       <c r="Q313" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.832482332830795</v>
+        <v>13.124590491090194</v>
       </c>
       <c r="S313" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30170,7 +30186,7 @@
       </c>
       <c r="Q314" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.3724646068466787</v>
+        <v>0.37366214959361033</v>
       </c>
       <c r="S314" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30228,7 +30244,7 @@
       </c>
       <c r="Q315" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.39199787139963282</v>
+        <v>6.9796111534978E-2</v>
       </c>
       <c r="S315" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30286,7 +30302,7 @@
       </c>
       <c r="Q316" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.90836063411962842</v>
+        <v>0.77908526277663437</v>
       </c>
       <c r="S316" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30344,7 +30360,7 @@
       </c>
       <c r="Q317" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>4.705855967952477E-3</v>
+        <v>0.52113780089249029</v>
       </c>
       <c r="S317" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30402,7 +30418,7 @@
       </c>
       <c r="Q318" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.26472569524369416</v>
+        <v>0.56646757362727929</v>
       </c>
       <c r="S318" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30460,7 +30476,7 @@
       </c>
       <c r="Q319" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>34.288418316444371</v>
+        <v>34.22183241395313</v>
       </c>
       <c r="S319" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30520,7 +30536,7 @@
       </c>
       <c r="Q320" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>22.968833337129219</v>
+        <v>22.747830117247503</v>
       </c>
       <c r="S320" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30580,7 +30596,7 @@
       </c>
       <c r="Q321" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>22.864580378825657</v>
+        <v>23.213316798559074</v>
       </c>
       <c r="S321" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30637,7 +30653,7 @@
       </c>
       <c r="Q322" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.44170948737492921</v>
+        <v>0.94926958510494774</v>
       </c>
       <c r="S322" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30694,7 +30710,7 @@
       </c>
       <c r="Q323" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.49692310080036384</v>
+        <v>0.38556454995192702</v>
       </c>
       <c r="S323" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30736,17 +30752,17 @@
         <v>972</v>
       </c>
       <c r="F324" s="2" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
       <c r="G324" s="23" t="str">
         <f>テーブル1[[#This Row],[名前]]&amp;"(UTAU)"</f>
         <v>死nu音サン(UTAU)</v>
       </c>
       <c r="H324" s="23" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
       <c r="I324" s="23" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
       <c r="M324" s="1" t="s">
         <v>1518</v>
@@ -30761,7 +30777,7 @@
       </c>
       <c r="Q324" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>17.506829333270034</v>
+        <v>16.790832987908605</v>
       </c>
       <c r="S324" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30819,7 +30835,7 @@
       </c>
       <c r="Q325" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>50.818931958474849</v>
+        <v>50.945340645669425</v>
       </c>
       <c r="S325" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30876,7 +30892,7 @@
       </c>
       <c r="Q326" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.971229322923465</v>
+        <v>12.586316512484331</v>
       </c>
       <c r="S326" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30933,7 +30949,7 @@
       </c>
       <c r="Q327" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.916094109340788</v>
+        <v>13.458703026207322</v>
       </c>
       <c r="S327" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30993,7 +31009,7 @@
       </c>
       <c r="Q328" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.442575028277034</v>
+        <v>20.75323277714601</v>
       </c>
       <c r="S328" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31053,7 +31069,7 @@
       </c>
       <c r="Q329" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.875892230695804</v>
+        <v>20.298169586500006</v>
       </c>
       <c r="S329" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31113,7 +31129,7 @@
       </c>
       <c r="Q330" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>22.611983675311251</v>
+        <v>22.536081950760863</v>
       </c>
       <c r="S330" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31173,7 +31189,7 @@
       </c>
       <c r="Q331" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.91278194020736</v>
+        <v>34.256084131538181</v>
       </c>
       <c r="S331" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31231,7 +31247,7 @@
       </c>
       <c r="Q332" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.82702350441506867</v>
+        <v>0.71070343871245323</v>
       </c>
       <c r="S332" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31291,7 +31307,7 @@
       </c>
       <c r="Q333" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.787399759122707</v>
+        <v>34.266514101779627</v>
       </c>
       <c r="S333" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31339,10 +31355,10 @@
         <v>166</v>
       </c>
       <c r="H334" s="23" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="I334" s="23" t="s">
-        <v>1637</v>
+        <v>1636</v>
       </c>
       <c r="O334" s="24" t="str">
         <f>テーブル1[[#This Row],[リンク]]&amp;テーブル1[[#This Row],[描画状況]]</f>
@@ -31354,7 +31370,7 @@
       </c>
       <c r="Q334" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>67.009533802884363</v>
+        <v>67.47269131718781</v>
       </c>
       <c r="S334" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31411,7 +31427,7 @@
       </c>
       <c r="Q335" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.47148983917729326</v>
+        <v>0.93635047288253404</v>
       </c>
       <c r="S335" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31468,7 +31484,7 @@
       </c>
       <c r="Q336" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.8241258594453971</v>
+        <v>7.9578446923378321</v>
       </c>
       <c r="S336" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31525,7 +31541,7 @@
       </c>
       <c r="Q337" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.374446888730978</v>
+        <v>13.296227950631103</v>
       </c>
       <c r="S337" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31586,7 +31602,7 @@
       </c>
       <c r="Q338" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>9.792481680282755</v>
+        <v>9.8881999745559099</v>
       </c>
       <c r="S338" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31646,7 +31662,7 @@
       </c>
       <c r="Q339" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.969665934652724</v>
+        <v>33.665066092647997</v>
       </c>
       <c r="S339" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31703,7 +31719,7 @@
       </c>
       <c r="Q340" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.57529607749019263</v>
+        <v>0.63370371311624518</v>
       </c>
       <c r="S340" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31760,7 +31776,7 @@
       </c>
       <c r="Q341" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.615192799491419</v>
+        <v>12.683735613930688</v>
       </c>
       <c r="S341" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31820,7 +31836,7 @@
       </c>
       <c r="Q342" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.006806858188085</v>
+        <v>20.827369066814011</v>
       </c>
       <c r="S342" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31877,7 +31893,7 @@
       </c>
       <c r="Q343" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.475318076468774</v>
+        <v>13.200660503421615</v>
       </c>
       <c r="S343" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31934,7 +31950,7 @@
       </c>
       <c r="Q344" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.392952368768476</v>
+        <v>20.54522118279824</v>
       </c>
       <c r="S344" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31994,7 +32010,7 @@
       </c>
       <c r="Q345" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.502632435402376</v>
+        <v>33.907538221922302</v>
       </c>
       <c r="S345" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32054,7 +32070,7 @@
       </c>
       <c r="Q346" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>23.145936507744846</v>
+        <v>22.568764244520775</v>
       </c>
       <c r="S346" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32111,7 +32127,7 @@
       </c>
       <c r="Q347" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.22959600046034057</v>
+        <v>0.46490637840158366</v>
       </c>
       <c r="S347" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32168,7 +32184,7 @@
       </c>
       <c r="Q348" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.78136923310596618</v>
+        <v>0.94925637641066962</v>
       </c>
       <c r="S348" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32226,7 +32242,7 @@
       </c>
       <c r="Q349" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.375754871058859</v>
+        <v>13.054438572244663</v>
       </c>
       <c r="S349" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32286,7 +32302,7 @@
       </c>
       <c r="Q350" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>22.963409610815127</v>
+        <v>22.495957545301639</v>
       </c>
       <c r="S350" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32343,7 +32359,7 @@
       </c>
       <c r="Q351" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.633892520597392</v>
+        <v>34.257869607726548</v>
       </c>
       <c r="S351" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32400,7 +32416,7 @@
       </c>
       <c r="Q352" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.87156931495704715</v>
+        <v>3.6690154191395319E-2</v>
       </c>
       <c r="S352" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32460,7 +32476,7 @@
       </c>
       <c r="Q353" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>60.644046961988927</v>
+        <v>60.612631115007758</v>
       </c>
       <c r="S353" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32521,7 +32537,7 @@
       </c>
       <c r="Q354" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>10.032333101897576</v>
+        <v>9.3773412186034211</v>
       </c>
       <c r="S354" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32579,7 +32595,7 @@
       </c>
       <c r="Q355" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.894678877446324</v>
+        <v>33.695629031075228</v>
       </c>
       <c r="S355" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32636,7 +32652,7 @@
       </c>
       <c r="Q356" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.774329688697424</v>
+        <v>12.604908136967769</v>
       </c>
       <c r="S356" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32693,7 +32709,7 @@
       </c>
       <c r="Q357" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>40.897607715565414</v>
+        <v>40.09054507644079</v>
       </c>
       <c r="S357" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32751,7 +32767,7 @@
       </c>
       <c r="Q358" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.86829237060570674</v>
+        <v>0.88527476579971798</v>
       </c>
       <c r="S358" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32808,7 +32824,7 @@
       </c>
       <c r="Q359" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.59903028027533867</v>
+        <v>0.96647340195578335</v>
       </c>
       <c r="S359" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32865,7 +32881,7 @@
       </c>
       <c r="Q360" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.41609936013977</v>
+        <v>13.083124835202369</v>
       </c>
       <c r="S360" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32925,7 +32941,7 @@
       </c>
       <c r="Q361" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>10.067188837288585</v>
+        <v>10.745124539149479</v>
       </c>
       <c r="S361" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32982,7 +32998,7 @@
       </c>
       <c r="Q362" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.5790148288220616E-3</v>
+        <v>0.64450202254585431</v>
       </c>
       <c r="S362" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33039,7 +33055,7 @@
       </c>
       <c r="Q363" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.292991800633935</v>
+        <v>12.846337598140463</v>
       </c>
       <c r="S363" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33099,7 +33115,7 @@
       </c>
       <c r="Q364" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.586505153454389</v>
+        <v>34.28919815908634</v>
       </c>
       <c r="S364" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33161,7 +33177,7 @@
       </c>
       <c r="Q365" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.230218942297581</v>
+        <v>12.662436011886447</v>
       </c>
       <c r="S365" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33223,7 +33239,7 @@
       </c>
       <c r="Q366" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.813227462412257</v>
+        <v>12.90067048774268</v>
       </c>
       <c r="S366" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33283,7 +33299,7 @@
       </c>
       <c r="Q367" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.957888758625572</v>
+        <v>34.242612248698158</v>
       </c>
       <c r="S367" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33343,7 +33359,7 @@
       </c>
       <c r="Q368" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>22.357939626404836</v>
+        <v>22.264028517708613</v>
       </c>
       <c r="S368" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33400,7 +33416,7 @@
       </c>
       <c r="Q369" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.622116235123119</v>
+        <v>13.413869080301287</v>
       </c>
       <c r="S369" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33457,7 +33473,7 @@
       </c>
       <c r="Q370" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.723465182342695</v>
+        <v>13.016142596507274</v>
       </c>
       <c r="S370" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33514,7 +33530,7 @@
       </c>
       <c r="Q371" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.67623289895577043</v>
+        <v>0.66862589169914544</v>
       </c>
       <c r="S371" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33571,7 +33587,7 @@
       </c>
       <c r="Q372" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.86140712239082617</v>
+        <v>0.40610882467626597</v>
       </c>
       <c r="S372" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33628,7 +33644,7 @@
       </c>
       <c r="Q373" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.5597957788059569</v>
+        <v>7.6698349947429696</v>
       </c>
       <c r="S373" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33685,7 +33701,7 @@
       </c>
       <c r="Q374" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.3364386731574651</v>
+        <v>7.9474017464782882</v>
       </c>
       <c r="S374" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33745,7 +33761,7 @@
       </c>
       <c r="Q375" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>10.280980357341461</v>
+        <v>10.67031657953847</v>
       </c>
       <c r="S375" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33805,7 +33821,7 @@
       </c>
       <c r="Q376" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.700170559937412</v>
+        <v>20.022674165610763</v>
       </c>
       <c r="S376" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33865,7 +33881,7 @@
       </c>
       <c r="Q377" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>34.290275571034179</v>
+        <v>33.958967410904698</v>
       </c>
       <c r="S377" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33923,7 +33939,7 @@
       </c>
       <c r="Q378" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.885367120577698</v>
+        <v>13.041178552436328</v>
       </c>
       <c r="S378" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33980,7 +33996,7 @@
       </c>
       <c r="Q379" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.282543155997036</v>
+        <v>13.438980841684884</v>
       </c>
       <c r="S379" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34042,7 +34058,7 @@
       </c>
       <c r="Q380" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.967074209376216</v>
+        <v>13.23280908659526</v>
       </c>
       <c r="S380" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34100,7 +34116,7 @@
       </c>
       <c r="Q381" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.177299312803754</v>
+        <v>20.466003444629184</v>
       </c>
       <c r="S381" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34157,7 +34173,7 @@
       </c>
       <c r="Q382" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.80441143035168483</v>
+        <v>0.40472279741123218</v>
       </c>
       <c r="S382" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34214,7 +34230,7 @@
       </c>
       <c r="Q383" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.902578590332617</v>
+        <v>33.343344144983192</v>
       </c>
       <c r="S383" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34274,7 +34290,7 @@
       </c>
       <c r="Q384" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>10.084707762673741</v>
+        <v>10.212508741909074</v>
       </c>
       <c r="S384" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34331,7 +34347,7 @@
       </c>
       <c r="Q385" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.049265864165324</v>
+        <v>12.681619071129008</v>
       </c>
       <c r="S385" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34389,7 +34405,7 @@
       </c>
       <c r="Q386" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.602578182050202</v>
+        <v>20.987165416632518</v>
       </c>
       <c r="S386" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34446,7 +34462,7 @@
       </c>
       <c r="Q387" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.67743465728959751</v>
+        <v>0.8936536109805423</v>
       </c>
       <c r="S387" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34503,7 +34519,7 @@
       </c>
       <c r="Q388" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.5625375668892403</v>
+        <v>7.4482867247305071</v>
       </c>
       <c r="S388" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34560,7 +34576,7 @@
       </c>
       <c r="Q389" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.77003751833417466</v>
+        <v>0.18920793537896097</v>
       </c>
       <c r="S389" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34618,7 +34634,7 @@
       </c>
       <c r="Q390" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.761230466808241</v>
+        <v>13.444813999867877</v>
       </c>
       <c r="S390" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34675,7 +34691,7 @@
       </c>
       <c r="Q391" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.8197588075448277</v>
+        <v>7.4457740246545603</v>
       </c>
       <c r="S391" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34732,7 +34748,7 @@
       </c>
       <c r="Q392" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.1900973352771977</v>
+        <v>7.9290034363653312</v>
       </c>
       <c r="S392" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34794,7 +34810,7 @@
       </c>
       <c r="Q393" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.260414057395579</v>
+        <v>12.639545099982435</v>
       </c>
       <c r="S393" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34851,7 +34867,7 @@
       </c>
       <c r="Q394" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.38876121153868681</v>
+        <v>0.33533898389586814</v>
       </c>
       <c r="S394" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34913,7 +34929,7 @@
       </c>
       <c r="Q395" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.20760936962504</v>
+        <v>12.706853723347521</v>
       </c>
       <c r="S395" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34970,7 +34986,7 @@
       </c>
       <c r="Q396" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.566623885738476</v>
+        <v>12.660119229831865</v>
       </c>
       <c r="S396" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35012,17 +35028,17 @@
         <v>963</v>
       </c>
       <c r="F397" s="2" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
       <c r="G397" s="23" t="str">
         <f>テーブル1[[#This Row],[名前]]&amp;"(UTAU)"</f>
         <v>メジロ・メイホァ(UTAU)</v>
       </c>
       <c r="H397" s="23" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="K397" s="23" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
       <c r="M397" s="1" t="s">
         <v>1518</v>
@@ -35037,7 +35053,7 @@
       </c>
       <c r="Q397" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>17.212747129944439</v>
+        <v>16.669451582758715</v>
       </c>
       <c r="S397" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35095,7 +35111,7 @@
       </c>
       <c r="Q398" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.48302827515941738</v>
+        <v>0.70369208470974853</v>
       </c>
       <c r="S398" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35137,20 +35153,20 @@
         <v>968</v>
       </c>
       <c r="F399" s="2" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
       <c r="G399" s="23" t="str">
         <f>テーブル1[[#This Row],[名前]]&amp;"(UTAU)"</f>
         <v>メタ・クアドラ(UTAU)</v>
       </c>
       <c r="H399" s="23" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="I399" s="23" t="s">
-        <v>1706</v>
+        <v>1705</v>
       </c>
       <c r="L399" s="23" t="s">
-        <v>1673</v>
+        <v>1672</v>
       </c>
       <c r="M399" s="1" t="s">
         <v>1518</v>
@@ -35165,7 +35181,7 @@
       </c>
       <c r="Q399" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>17.024738128595654</v>
+        <v>16.800870861758355</v>
       </c>
       <c r="S399" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35222,7 +35238,7 @@
       </c>
       <c r="Q400" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.463328323207044</v>
+        <v>12.769823948153483</v>
       </c>
       <c r="S400" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35264,14 +35280,14 @@
         <v>975</v>
       </c>
       <c r="F401" s="2" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
       <c r="G401" s="23" t="str">
         <f>テーブル1[[#This Row],[名前]]&amp;"(UTAU)"</f>
         <v>メルジ・ハクア(UTAU)</v>
       </c>
       <c r="H401" s="23" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="M401" s="1" t="s">
         <v>1518</v>
@@ -35286,7 +35302,7 @@
       </c>
       <c r="Q401" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>17.173682546034062</v>
+        <v>17.377965053892321</v>
       </c>
       <c r="S401" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35343,7 +35359,7 @@
       </c>
       <c r="Q402" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.6193782892202655</v>
+        <v>0.52602936570870706</v>
       </c>
       <c r="S402" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35400,7 +35416,7 @@
       </c>
       <c r="Q403" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.32453525222935053</v>
+        <v>6.7288652666561588E-2</v>
       </c>
       <c r="S403" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35457,7 +35473,7 @@
       </c>
       <c r="Q404" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.65060058418392808</v>
+        <v>0.8499131998657059</v>
       </c>
       <c r="S404" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35514,7 +35530,7 @@
       </c>
       <c r="Q405" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.6137698504617668</v>
+        <v>0.99777405819055864</v>
       </c>
       <c r="S405" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35571,7 +35587,7 @@
       </c>
       <c r="Q406" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.61549206965235925</v>
+        <v>0.89381374198286279</v>
       </c>
       <c r="S406" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35629,7 +35645,7 @@
       </c>
       <c r="Q407" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.289864534899097</v>
+        <v>12.647297766692933</v>
       </c>
       <c r="S407" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35689,7 +35705,7 @@
       </c>
       <c r="Q408" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.10498620475490861</v>
+        <v>9.012815678224928E-2</v>
       </c>
       <c r="S408" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35746,7 +35762,7 @@
       </c>
       <c r="Q409" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.9884124521954375</v>
+        <v>0.40285681091425052</v>
       </c>
       <c r="S409" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35803,7 +35819,7 @@
       </c>
       <c r="Q410" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>40.184451434164671</v>
+        <v>40.038791315541367</v>
       </c>
       <c r="S410" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35860,7 +35876,7 @@
       </c>
       <c r="Q411" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.9039853279554038</v>
+        <v>7.4030919841767364</v>
       </c>
       <c r="S411" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35920,7 +35936,7 @@
       </c>
       <c r="Q412" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>10.039635486172793</v>
+        <v>10.86290280150835</v>
       </c>
       <c r="S412" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35977,7 +35993,7 @@
       </c>
       <c r="Q413" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.15603149349352108</v>
+        <v>0.92980899995206268</v>
       </c>
       <c r="S413" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36038,7 +36054,7 @@
       </c>
       <c r="Q414" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>9.9289866107503411</v>
+        <v>9.4324890784123898</v>
       </c>
       <c r="S414" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36099,7 +36115,7 @@
       </c>
       <c r="Q415" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>9.3244958329250363</v>
+        <v>9.2432006439268442</v>
       </c>
       <c r="S415" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36156,7 +36172,7 @@
       </c>
       <c r="Q416" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.3245348217076307</v>
+        <v>7.4066356371707389</v>
       </c>
       <c r="S416" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36213,7 +36229,7 @@
       </c>
       <c r="Q417" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.3938071872379805</v>
+        <v>8.1265958625041392</v>
       </c>
       <c r="S417" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36270,7 +36286,7 @@
       </c>
       <c r="Q418" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.737265611645928</v>
+        <v>13.006951266841494</v>
       </c>
       <c r="S418" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36327,7 +36343,7 @@
       </c>
       <c r="Q419" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>66.883770419337964</v>
+        <v>67.619004541395057</v>
       </c>
       <c r="S419" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36388,7 +36404,7 @@
       </c>
       <c r="Q420" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>9.569372544793195</v>
+        <v>9.8261585320900178</v>
       </c>
       <c r="S420" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36446,7 +36462,7 @@
       </c>
       <c r="Q421" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.093638913569986</v>
+        <v>12.844506403766887</v>
       </c>
       <c r="S421" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36504,7 +36520,7 @@
       </c>
       <c r="Q422" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.64981231100478143</v>
+        <v>0.26933049625032468</v>
       </c>
       <c r="S422" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36565,7 +36581,7 @@
       </c>
       <c r="Q423" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>9.546209861207581</v>
+        <v>9.175168795379113</v>
       </c>
       <c r="S423" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36626,7 +36642,7 @@
       </c>
       <c r="Q424" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>9.8515286984468329</v>
+        <v>9.8397827374964866</v>
       </c>
       <c r="S424" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36684,7 +36700,7 @@
       </c>
       <c r="Q425" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.038839804121491</v>
+        <v>12.888375518795836</v>
       </c>
       <c r="S425" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36726,20 +36742,20 @@
         <v>969</v>
       </c>
       <c r="F426" s="2" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
       <c r="G426" s="23" t="str">
         <f>テーブル1[[#This Row],[名前]]&amp;"(UTAU)"</f>
         <v>レフア・アパパネ(UTAU)</v>
       </c>
       <c r="H426" s="23" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="I426" s="23" t="s">
+        <v>1706</v>
+      </c>
+      <c r="L426" s="23" t="s">
         <v>1707</v>
-      </c>
-      <c r="L426" s="23" t="s">
-        <v>1708</v>
       </c>
       <c r="M426" s="1" t="s">
         <v>1518</v>
@@ -36754,7 +36770,7 @@
       </c>
       <c r="Q426" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>16.760955754650809</v>
+        <v>16.978424950158161</v>
       </c>
       <c r="S426" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36814,7 +36830,7 @@
       </c>
       <c r="Q427" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>10.099842406354837</v>
+        <v>10.277722133206874</v>
       </c>
       <c r="S427" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36871,7 +36887,7 @@
       </c>
       <c r="Q428" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.7034649951991071</v>
+        <v>0.28633421861841468</v>
       </c>
       <c r="S428" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36928,7 +36944,7 @@
       </c>
       <c r="Q429" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.216762065038013</v>
+        <v>13.183991691483865</v>
       </c>
       <c r="S429" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36985,7 +37001,7 @@
       </c>
       <c r="Q430" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.16696333840756239</v>
+        <v>0.57681940386449204</v>
       </c>
       <c r="S430" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37043,7 +37059,7 @@
       </c>
       <c r="Q431" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.68463824461934575</v>
+        <v>0.24975722404537481</v>
       </c>
       <c r="S431" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37076,13 +37092,13 @@
         <v>seido-ao</v>
       </c>
       <c r="C432" s="24" t="s">
+        <v>1555</v>
+      </c>
+      <c r="D432" s="23" t="s">
         <v>1556</v>
       </c>
-      <c r="D432" s="23" t="s">
+      <c r="E432" s="23" t="s">
         <v>1557</v>
-      </c>
-      <c r="E432" s="23" t="s">
-        <v>1558</v>
       </c>
       <c r="F432" s="2" t="s">
         <v>215</v>
@@ -37103,7 +37119,7 @@
       </c>
       <c r="Q432" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.172372514861372</v>
+        <v>20.798449828619113</v>
       </c>
       <c r="S432" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37136,13 +37152,13 @@
         <v>uraha</v>
       </c>
       <c r="C433" s="24" t="s">
+        <v>1558</v>
+      </c>
+      <c r="D433" s="23" t="s">
         <v>1559</v>
       </c>
-      <c r="D433" s="23" t="s">
+      <c r="E433" s="23" t="s">
         <v>1560</v>
-      </c>
-      <c r="E433" s="23" t="s">
-        <v>1561</v>
       </c>
       <c r="F433" s="2" t="s">
         <v>215</v>
@@ -37163,7 +37179,7 @@
       </c>
       <c r="Q433" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.321803732161722</v>
+        <v>20.022572958412141</v>
       </c>
       <c r="S433" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37196,13 +37212,13 @@
         <v>koga-hizuki</v>
       </c>
       <c r="C434" s="24" t="s">
+        <v>1561</v>
+      </c>
+      <c r="D434" s="23" t="s">
         <v>1562</v>
       </c>
-      <c r="D434" s="23" t="s">
+      <c r="E434" s="23" t="s">
         <v>1563</v>
-      </c>
-      <c r="E434" s="23" t="s">
-        <v>1564</v>
       </c>
       <c r="F434" s="2" t="s">
         <v>215</v>
@@ -37223,7 +37239,7 @@
       </c>
       <c r="Q434" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.241515589440532</v>
+        <v>20.437626669628152</v>
       </c>
       <c r="S434" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37256,13 +37272,13 @@
         <v>anima</v>
       </c>
       <c r="C435" s="24" t="s">
+        <v>1567</v>
+      </c>
+      <c r="D435" s="23" t="s">
+        <v>1569</v>
+      </c>
+      <c r="E435" s="23" t="s">
         <v>1568</v>
-      </c>
-      <c r="D435" s="23" t="s">
-        <v>1570</v>
-      </c>
-      <c r="E435" s="23" t="s">
-        <v>1569</v>
       </c>
       <c r="F435" s="2" t="s">
         <v>215</v>
@@ -37283,7 +37299,7 @@
       </c>
       <c r="Q435" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.979602722880752</v>
+        <v>20.807710857785612</v>
       </c>
       <c r="S435" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37316,13 +37332,13 @@
         <v>riimao</v>
       </c>
       <c r="C436" s="24" t="s">
+        <v>1570</v>
+      </c>
+      <c r="D436" s="23" t="s">
+        <v>1570</v>
+      </c>
+      <c r="E436" s="23" t="s">
         <v>1571</v>
-      </c>
-      <c r="D436" s="23" t="s">
-        <v>1571</v>
-      </c>
-      <c r="E436" s="23" t="s">
-        <v>1572</v>
       </c>
       <c r="F436" s="2" t="s">
         <v>215</v>
@@ -37343,7 +37359,7 @@
       </c>
       <c r="Q436" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.430312696840375</v>
+        <v>20.558799036260897</v>
       </c>
       <c r="S436" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37376,13 +37392,13 @@
         <v>shirane-aoi</v>
       </c>
       <c r="C437" s="24" t="s">
+        <v>1572</v>
+      </c>
+      <c r="D437" s="23" t="s">
         <v>1573</v>
       </c>
-      <c r="D437" s="23" t="s">
+      <c r="E437" s="23" t="s">
         <v>1574</v>
-      </c>
-      <c r="E437" s="23" t="s">
-        <v>1575</v>
       </c>
       <c r="F437" s="2" t="s">
         <v>215</v>
@@ -37403,7 +37419,7 @@
       </c>
       <c r="Q437" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.429767474223876</v>
+        <v>20.200181645089494</v>
       </c>
       <c r="S437" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37436,37 +37452,37 @@
         <v>yashiro-shiya</v>
       </c>
       <c r="C438" s="24" t="s">
+        <v>1733</v>
+      </c>
+      <c r="D438" s="23" t="s">
         <v>1734</v>
       </c>
-      <c r="D438" s="23" t="s">
+      <c r="E438" s="23" t="s">
+        <v>1732</v>
+      </c>
+      <c r="F438" s="30" t="s">
+        <v>1720</v>
+      </c>
+      <c r="G438" s="23" t="s">
+        <v>1721</v>
+      </c>
+      <c r="H438" s="23" t="s">
+        <v>1626</v>
+      </c>
+      <c r="I438" s="23" t="s">
+        <v>1649</v>
+      </c>
+      <c r="J438" s="23" t="s">
+        <v>1738</v>
+      </c>
+      <c r="K438" s="23" t="s">
         <v>1735</v>
       </c>
-      <c r="E438" s="23" t="s">
-        <v>1733</v>
-      </c>
-      <c r="F438" s="30" t="s">
-        <v>1721</v>
-      </c>
-      <c r="G438" s="23" t="s">
-        <v>1722</v>
-      </c>
-      <c r="H438" s="23" t="s">
-        <v>1627</v>
-      </c>
-      <c r="I438" s="23" t="s">
-        <v>1650</v>
-      </c>
-      <c r="J438" s="23" t="s">
-        <v>1739</v>
-      </c>
-      <c r="K438" s="23" t="s">
+      <c r="L438" s="23" t="s">
         <v>1736</v>
       </c>
-      <c r="L438" s="23" t="s">
-        <v>1737</v>
-      </c>
       <c r="M438" s="1" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="O438" s="24" t="str">
         <f>テーブル1[[#This Row],[リンク]]&amp;テーブル1[[#This Row],[描画状況]]</f>
@@ -37478,7 +37494,7 @@
       </c>
       <c r="Q438" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.878093672986822</v>
+        <v>33.892644258173512</v>
       </c>
       <c r="S438" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37511,31 +37527,31 @@
         <v>katazu-taka</v>
       </c>
       <c r="C439" s="24" t="s">
+        <v>1739</v>
+      </c>
+      <c r="D439" s="23" t="s">
         <v>1740</v>
       </c>
-      <c r="D439" s="23" t="s">
+      <c r="E439" s="23" t="s">
         <v>1741</v>
       </c>
-      <c r="E439" s="23" t="s">
-        <v>1742</v>
-      </c>
       <c r="F439" s="30" t="s">
+        <v>1720</v>
+      </c>
+      <c r="G439" s="23" t="s">
         <v>1721</v>
       </c>
-      <c r="G439" s="23" t="s">
-        <v>1722</v>
-      </c>
       <c r="H439" s="23" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="I439" s="23" t="s">
-        <v>1650</v>
+        <v>1649</v>
       </c>
       <c r="L439" s="23" t="s">
-        <v>1737</v>
+        <v>1736</v>
       </c>
       <c r="M439" s="1" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="O439" s="24" t="str">
         <f>テーブル1[[#This Row],[リンク]]&amp;テーブル1[[#This Row],[描画状況]]</f>
@@ -37547,7 +37563,7 @@
       </c>
       <c r="Q439" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.544085695598291</v>
+        <v>33.979159063312672</v>
       </c>
       <c r="S439" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37577,16 +37593,16 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="17" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1 B3:B1048576">
-    <cfRule type="duplicateValues" dxfId="16" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="15" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1:S1048576">
-    <cfRule type="cellIs" dxfId="14" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="10" operator="equal">
       <formula>"済"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -37953,7 +37969,7 @@
       </c>
       <c r="C4" s="7">
         <f ca="1">MATCH(C5,キャラ情報!C:C,0)</f>
-        <v>317</v>
+        <v>301</v>
       </c>
     </row>
     <row r="5" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -37962,7 +37978,7 @@
       </c>
       <c r="C5" s="6" t="str">
         <f ca="1">INDEX(キャラ情報!C:Q,MATCH(MIN(キャラ情報!Q:Q),キャラ情報!Q:Q,0),1)</f>
-        <v>三色家のぼうしさん</v>
+        <v>携帯ロン</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -37971,7 +37987,7 @@
       </c>
       <c r="C6" s="6" t="str">
         <f ca="1">INDEX(キャラ情報!C:Q,MATCH(MIN(キャラ情報!Q:Q),キャラ情報!Q:Q,0),4)</f>
-        <v>https://harujpg.wixsite.com/sanshoku</v>
+        <v>https://keitaiware.com</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -37984,18 +38000,18 @@
       <c r="B11" s="4" t="s">
         <v>718</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="7" t="e">
         <f ca="1">MATCH(C12,キャラ情報!C:C,0)</f>
-        <v>212</v>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="12" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="4" t="s">
         <v>715</v>
       </c>
-      <c r="C12" s="6" t="str">
+      <c r="C12" s="6" t="e">
         <f ca="1">INDEX(キャラ情報!C:S,MATCH(MIN(キャラ情報!S:S),キャラ情報!S:S,0),1)</f>
-        <v>Ｔくん</v>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="14" spans="2:3" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -38018,15 +38034,15 @@
         <f>"No."&amp;MAX(キャラ情報!A:A)+1&amp;"｜"</f>
         <v>No.231｜</v>
       </c>
-      <c r="C17" s="12" t="str">
+      <c r="C17" s="12" t="e">
         <f ca="1">C12</f>
-        <v>Ｔくん</v>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="11" t="str">
+      <c r="B18" s="11" t="e">
         <f ca="1">INDEX(キャラ情報!C:G,MATCH(C12,キャラ情報!C:C,0),5)</f>
-        <v>#有線水族館</v>
+        <v>#N/A</v>
       </c>
       <c r="C18" s="12"/>
     </row>
@@ -38042,7 +38058,7 @@
     </row>
     <row r="21" spans="2:3" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B21" s="13" t="s">
-        <v>1732</v>
+        <v>1731</v>
       </c>
       <c r="C21" s="14"/>
     </row>
@@ -38079,40 +38095,40 @@
   <sheetData>
     <row r="1" spans="1:12" s="18" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="18" t="s">
+        <v>1620</v>
+      </c>
+      <c r="B1" s="18" t="s">
+        <v>1616</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>1617</v>
+      </c>
+      <c r="D1" s="18" t="s">
+        <v>1618</v>
+      </c>
+      <c r="E1" s="18" t="s">
+        <v>1619</v>
+      </c>
+      <c r="F1" s="18" t="s">
         <v>1621</v>
       </c>
-      <c r="B1" s="18" t="s">
-        <v>1617</v>
-      </c>
-      <c r="C1" s="18" t="s">
-        <v>1618</v>
-      </c>
-      <c r="D1" s="18" t="s">
-        <v>1619</v>
-      </c>
-      <c r="E1" s="18" t="s">
-        <v>1620</v>
-      </c>
-      <c r="F1" s="18" t="s">
+      <c r="G1" s="18" t="s">
         <v>1622</v>
       </c>
-      <c r="G1" s="18" t="s">
+      <c r="H1" s="18" t="s">
         <v>1623</v>
       </c>
-      <c r="H1" s="18" t="s">
-        <v>1624</v>
-      </c>
       <c r="I1" s="1" t="s">
+        <v>1629</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>1630</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>1631</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>1632</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>1633</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -48622,7 +48638,7 @@
       </c>
       <c r="B212" s="19" t="str">
         <f>テーブル1[[#This Row],[名前]]</f>
-        <v>Ｔくん</v>
+        <v>Tくん</v>
       </c>
       <c r="C212" s="19" t="str">
         <f>テーブル1[[#This Row],[なまえ]]</f>
@@ -48700,7 +48716,7 @@
       </c>
       <c r="I213" s="19" t="str">
         <f>テーブル1[[#This Row],[種族タグ]]&amp;""</f>
-        <v>機械</v>
+        <v>人造人間</v>
       </c>
       <c r="J213" s="19" t="str">
         <f>テーブル1[[#This Row],[職業タグ]]&amp;""</f>

--- a/data/characters.xlsx
+++ b/data/characters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\モノクロビリーフ\外部リンク\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{409FEDF0-64BD-407F-BA54-A59A1F5FF912}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36F37BE7-6C22-4689-BFD4-58EAF1B8BFE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{78CF6334-6F78-4A6F-BD14-CB6FA7AB00CF}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3294" uniqueCount="1857">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3293" uniqueCount="1857">
   <si>
     <t>番号</t>
   </si>
@@ -6893,9 +6893,6 @@
     <t>吸血鬼</t>
   </si>
   <si>
-    <t>ケモ耳</t>
-  </si>
-  <si>
     <t>渦巻き目、アホ毛</t>
   </si>
   <si>
@@ -7984,6 +7981,13 @@
   </si>
   <si>
     <t>ひなき ぶい どらぎにえ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カチューシャ|髪飾り</t>
+    <rPh sb="7" eb="9">
+      <t>カミカザ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -8311,11 +8315,11 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -9916,7 +9920,7 @@
         <v>1619</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>1761</v>
+        <v>1760</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>1620</v>
@@ -10153,7 +10157,7 @@
         <v>1629</v>
       </c>
       <c r="J4" s="23" t="s">
-        <v>1757</v>
+        <v>1756</v>
       </c>
       <c r="K4" s="23" t="s">
         <v>1630</v>
@@ -10312,10 +10316,10 @@
         <v>1645</v>
       </c>
       <c r="J6" s="23" t="s">
-        <v>1758</v>
+        <v>1757</v>
       </c>
       <c r="L6" s="23" t="s">
-        <v>1833</v>
+        <v>1832</v>
       </c>
       <c r="M6" s="23" t="s">
         <v>1647</v>
@@ -10621,13 +10625,13 @@
         <v>1626</v>
       </c>
       <c r="J10" s="23" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
       <c r="L10" s="23" t="s">
-        <v>1752</v>
+        <v>1751</v>
       </c>
       <c r="M10" s="23" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
       <c r="O10" s="1" t="s">
         <v>1433</v>
@@ -10699,10 +10703,10 @@
         <v>1617</v>
       </c>
       <c r="I11" s="23" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="M11" s="23" t="s">
-        <v>1673</v>
+        <v>1672</v>
       </c>
       <c r="O11" s="1" t="s">
         <v>1433</v>
@@ -10777,7 +10781,7 @@
         <v>1626</v>
       </c>
       <c r="K12" s="23" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="L12" s="23" t="s">
         <v>1627</v>
@@ -10852,7 +10856,7 @@
         <v>1616</v>
       </c>
       <c r="L13" s="23" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
       <c r="N13" s="1" t="s">
         <v>1505</v>
@@ -10927,13 +10931,13 @@
         <v>1616</v>
       </c>
       <c r="I14" s="23" t="s">
+        <v>1682</v>
+      </c>
+      <c r="J14" s="23" t="s">
+        <v>1759</v>
+      </c>
+      <c r="M14" s="23" t="s">
         <v>1683</v>
-      </c>
-      <c r="J14" s="23" t="s">
-        <v>1760</v>
-      </c>
-      <c r="M14" s="23" t="s">
-        <v>1684</v>
       </c>
       <c r="O14" s="1" t="s">
         <v>1433</v>
@@ -11083,10 +11087,10 @@
         <v>1616</v>
       </c>
       <c r="I16" s="23" t="s">
+        <v>1684</v>
+      </c>
+      <c r="K16" s="23" t="s">
         <v>1685</v>
-      </c>
-      <c r="K16" s="23" t="s">
-        <v>1686</v>
       </c>
       <c r="M16" s="23" t="s">
         <v>1642</v>
@@ -11242,7 +11246,7 @@
         <v>1639</v>
       </c>
       <c r="K18" s="23" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="N18" s="1" t="s">
         <v>1507</v>
@@ -11308,7 +11312,7 @@
         <v>45</v>
       </c>
       <c r="F19" s="15" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="G19" s="23" t="s">
         <v>46</v>
@@ -11317,7 +11321,7 @@
         <v>1616</v>
       </c>
       <c r="L19" s="23" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="N19" s="1" t="s">
         <v>1508</v>
@@ -11389,7 +11393,7 @@
         <v>150</v>
       </c>
       <c r="H20" s="23" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="I20" s="23" t="s">
         <v>1639</v>
@@ -11464,7 +11468,7 @@
         <v>154</v>
       </c>
       <c r="H21" s="23" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="I21" s="23" t="s">
         <v>1639</v>
@@ -11539,10 +11543,10 @@
         <v>1616</v>
       </c>
       <c r="I22" s="23" t="s">
+        <v>1695</v>
+      </c>
+      <c r="M22" s="23" t="s">
         <v>1696</v>
-      </c>
-      <c r="M22" s="23" t="s">
-        <v>1697</v>
       </c>
       <c r="N22" s="1" t="s">
         <v>1507</v>
@@ -11620,10 +11624,10 @@
         <v>1626</v>
       </c>
       <c r="K23" s="23" t="s">
+        <v>1768</v>
+      </c>
+      <c r="L23" s="23" t="s">
         <v>1769</v>
-      </c>
-      <c r="L23" s="23" t="s">
-        <v>1770</v>
       </c>
       <c r="M23" s="23" t="s">
         <v>1662</v>
@@ -11782,7 +11786,7 @@
         <v>1644</v>
       </c>
       <c r="L25" s="23" t="s">
-        <v>1774</v>
+        <v>1773</v>
       </c>
       <c r="M25" s="23" t="s">
         <v>1662</v>
@@ -11863,10 +11867,10 @@
         <v>1626</v>
       </c>
       <c r="K26" s="23" t="s">
+        <v>1779</v>
+      </c>
+      <c r="M26" s="23" t="s">
         <v>1780</v>
-      </c>
-      <c r="M26" s="23" t="s">
-        <v>1781</v>
       </c>
       <c r="N26" s="1" t="s">
         <v>1579</v>
@@ -11944,10 +11948,10 @@
         <v>1626</v>
       </c>
       <c r="K27" s="23" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
       <c r="M27" s="23" t="s">
-        <v>1783</v>
+        <v>1782</v>
       </c>
       <c r="N27" s="1" t="s">
         <v>1579</v>
@@ -12010,10 +12014,10 @@
         <v>62</v>
       </c>
       <c r="E28" s="23" t="s">
-        <v>1785</v>
+        <v>1784</v>
       </c>
       <c r="F28" s="15" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
       <c r="G28" s="23" t="s">
         <v>63</v>
@@ -12025,10 +12029,10 @@
         <v>1626</v>
       </c>
       <c r="J28" s="23" t="s">
-        <v>1787</v>
+        <v>1786</v>
       </c>
       <c r="K28" s="23" t="s">
-        <v>1786</v>
+        <v>1785</v>
       </c>
       <c r="N28" s="1" t="s">
         <v>1507</v>
@@ -12178,7 +12182,7 @@
         <v>1626</v>
       </c>
       <c r="L30" s="23" t="s">
-        <v>1798</v>
+        <v>1797</v>
       </c>
       <c r="O30" s="1" t="s">
         <v>1433</v>
@@ -12250,7 +12254,7 @@
         <v>1616</v>
       </c>
       <c r="I31" s="23" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="O31" s="1" t="s">
         <v>1433</v>
@@ -12406,16 +12410,16 @@
         <v>1617</v>
       </c>
       <c r="I33" s="23" t="s">
+        <v>1801</v>
+      </c>
+      <c r="K33" s="23" t="s">
         <v>1802</v>
       </c>
-      <c r="K33" s="23" t="s">
+      <c r="L33" s="23" t="s">
         <v>1803</v>
       </c>
-      <c r="L33" s="23" t="s">
+      <c r="M33" s="23" t="s">
         <v>1804</v>
-      </c>
-      <c r="M33" s="23" t="s">
-        <v>1805</v>
       </c>
       <c r="N33" s="1" t="s">
         <v>1579</v>
@@ -12478,10 +12482,10 @@
         <v>65</v>
       </c>
       <c r="E34" s="23" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
       <c r="G34" s="23" t="s">
         <v>63</v>
@@ -12493,10 +12497,10 @@
         <v>1626</v>
       </c>
       <c r="L34" s="23" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="M34" s="23" t="s">
-        <v>1815</v>
+        <v>1814</v>
       </c>
       <c r="N34" s="1" t="s">
         <v>1507</v>
@@ -12571,13 +12575,13 @@
         <v>1617</v>
       </c>
       <c r="I35" s="23" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="K35" s="23" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="L35" s="23" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="M35" s="23" t="s">
         <v>1650</v>
@@ -12652,16 +12656,16 @@
         <v>1617</v>
       </c>
       <c r="I36" s="23" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="K36" s="23" t="s">
+        <v>1805</v>
+      </c>
+      <c r="L36" s="23" t="s">
+        <v>1772</v>
+      </c>
+      <c r="M36" s="23" t="s">
         <v>1806</v>
-      </c>
-      <c r="L36" s="23" t="s">
-        <v>1773</v>
-      </c>
-      <c r="M36" s="23" t="s">
-        <v>1807</v>
       </c>
       <c r="N36" s="1" t="s">
         <v>1579</v>
@@ -12739,10 +12743,10 @@
         <v>1626</v>
       </c>
       <c r="K37" s="23" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="L37" s="23" t="s">
-        <v>1752</v>
+        <v>1751</v>
       </c>
       <c r="N37" s="1" t="s">
         <v>1507</v>
@@ -12820,10 +12824,10 @@
         <v>1644</v>
       </c>
       <c r="K38" s="23" t="s">
+        <v>1815</v>
+      </c>
+      <c r="M38" s="23" t="s">
         <v>1816</v>
-      </c>
-      <c r="M38" s="23" t="s">
-        <v>1817</v>
       </c>
       <c r="N38" s="1" t="s">
         <v>1579</v>
@@ -12973,7 +12977,7 @@
         <v>1626</v>
       </c>
       <c r="K40" s="23" t="s">
-        <v>1810</v>
+        <v>1809</v>
       </c>
       <c r="N40" s="1" t="s">
         <v>1508</v>
@@ -13038,7 +13042,7 @@
       <c r="E41" s="23" t="s">
         <v>157</v>
       </c>
-      <c r="F41" s="31" t="s">
+      <c r="F41" s="30" t="s">
         <v>158</v>
       </c>
       <c r="G41" s="23" t="s">
@@ -13123,10 +13127,10 @@
         <v>1626</v>
       </c>
       <c r="L42" s="23" t="s">
+        <v>1770</v>
+      </c>
+      <c r="M42" s="23" t="s">
         <v>1771</v>
-      </c>
-      <c r="M42" s="23" t="s">
-        <v>1772</v>
       </c>
       <c r="N42" s="1" t="s">
         <v>1579</v>
@@ -13276,13 +13280,13 @@
         <v>1617</v>
       </c>
       <c r="I44" s="23" t="s">
-        <v>1830</v>
+        <v>1829</v>
       </c>
       <c r="J44" s="23" t="s">
-        <v>1829</v>
+        <v>1828</v>
       </c>
       <c r="M44" s="23" t="s">
-        <v>1828</v>
+        <v>1827</v>
       </c>
       <c r="N44" s="1" t="s">
         <v>1508</v>
@@ -13360,7 +13364,7 @@
         <v>1626</v>
       </c>
       <c r="K45" s="23" t="s">
-        <v>1810</v>
+        <v>1809</v>
       </c>
       <c r="L45" s="23" t="s">
         <v>1646</v>
@@ -13438,10 +13442,10 @@
         <v>1626</v>
       </c>
       <c r="K46" s="23" t="s">
+        <v>1844</v>
+      </c>
+      <c r="L46" s="23" t="s">
         <v>1845</v>
-      </c>
-      <c r="L46" s="23" t="s">
-        <v>1846</v>
       </c>
       <c r="N46" s="1" t="s">
         <v>1507</v>
@@ -13582,13 +13586,13 @@
         <v>1616</v>
       </c>
       <c r="I48" s="23" t="s">
+        <v>1817</v>
+      </c>
+      <c r="L48" s="23" t="s">
+        <v>1767</v>
+      </c>
+      <c r="M48" s="23" t="s">
         <v>1818</v>
-      </c>
-      <c r="L48" s="23" t="s">
-        <v>1768</v>
-      </c>
-      <c r="M48" s="23" t="s">
-        <v>1819</v>
       </c>
       <c r="N48" s="1" t="s">
         <v>1579</v>
@@ -13930,7 +13934,7 @@
         <v>1644</v>
       </c>
       <c r="K53" s="23" t="s">
-        <v>1812</v>
+        <v>1811</v>
       </c>
       <c r="N53" s="1" t="s">
         <v>1579</v>
@@ -14080,7 +14084,7 @@
       <c r="K55" s="28"/>
       <c r="L55" s="28"/>
       <c r="M55" s="28" t="s">
-        <v>1827</v>
+        <v>1826</v>
       </c>
       <c r="N55" s="1" t="s">
         <v>1579</v>
@@ -14491,10 +14495,10 @@
         <v>1617</v>
       </c>
       <c r="I61" s="23" t="s">
+        <v>1823</v>
+      </c>
+      <c r="J61" s="23" t="s">
         <v>1824</v>
-      </c>
-      <c r="J61" s="23" t="s">
-        <v>1825</v>
       </c>
       <c r="N61" s="1" t="s">
         <v>1508</v>
@@ -14773,7 +14777,7 @@
         <v>1644</v>
       </c>
       <c r="L65" s="23" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="N65" s="1" t="s">
         <v>1507</v>
@@ -14851,7 +14855,7 @@
         <v>1670</v>
       </c>
       <c r="M66" s="23" t="s">
-        <v>1831</v>
+        <v>1830</v>
       </c>
       <c r="N66" s="1" t="s">
         <v>1508</v>
@@ -15805,16 +15809,16 @@
         <v>1616</v>
       </c>
       <c r="I80" s="23" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
       <c r="J80" s="23" t="s">
-        <v>1826</v>
+        <v>1825</v>
       </c>
       <c r="L80" s="23" t="s">
         <v>1658</v>
       </c>
       <c r="M80" s="23" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="N80" s="1" t="s">
         <v>1508</v>
@@ -15955,13 +15959,13 @@
         <v>1653</v>
       </c>
       <c r="I82" s="23" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="J82" s="23" t="s">
+        <v>1807</v>
+      </c>
+      <c r="M82" s="23" t="s">
         <v>1808</v>
-      </c>
-      <c r="M82" s="23" t="s">
-        <v>1809</v>
       </c>
       <c r="N82" s="1" t="s">
         <v>1579</v>
@@ -16604,13 +16608,13 @@
         <v>1616</v>
       </c>
       <c r="I91" s="23" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="K91" s="23" t="s">
-        <v>1810</v>
+        <v>1809</v>
       </c>
       <c r="L91" s="23" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="N91" s="1" t="s">
         <v>1579</v>
@@ -16685,13 +16689,13 @@
         <v>1616</v>
       </c>
       <c r="I92" s="23" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="K92" s="23" t="s">
-        <v>1806</v>
+        <v>1805</v>
       </c>
       <c r="L92" s="23" t="s">
-        <v>1752</v>
+        <v>1751</v>
       </c>
       <c r="N92" s="1" t="s">
         <v>1579</v>
@@ -16838,7 +16842,7 @@
         <v>1626</v>
       </c>
       <c r="K94" s="23" t="s">
-        <v>1810</v>
+        <v>1809</v>
       </c>
       <c r="N94" s="1" t="s">
         <v>1508</v>
@@ -17054,10 +17058,10 @@
         <v>1626</v>
       </c>
       <c r="K97" s="23" t="s">
+        <v>1819</v>
+      </c>
+      <c r="M97" s="23" t="s">
         <v>1820</v>
-      </c>
-      <c r="M97" s="23" t="s">
-        <v>1821</v>
       </c>
       <c r="N97" s="1" t="s">
         <v>1579</v>
@@ -17201,7 +17205,7 @@
         <v>1626</v>
       </c>
       <c r="M99" s="23" t="s">
-        <v>1843</v>
+        <v>1842</v>
       </c>
       <c r="O99" s="1" t="s">
         <v>1433</v>
@@ -17273,10 +17277,10 @@
         <v>1653</v>
       </c>
       <c r="I100" s="23" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="K100" s="23" t="s">
-        <v>1844</v>
+        <v>1843</v>
       </c>
       <c r="O100" s="1" t="s">
         <v>1433</v>
@@ -17351,16 +17355,13 @@
         <v>1670</v>
       </c>
       <c r="J101" s="23" t="s">
-        <v>1767</v>
+        <v>1766</v>
       </c>
       <c r="K101" s="23" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="L101" s="23" t="s">
-        <v>1768</v>
-      </c>
-      <c r="M101" s="23" t="s">
-        <v>1671</v>
+        <v>1856</v>
       </c>
       <c r="O101" s="1" t="s">
         <v>1433</v>
@@ -17435,7 +17436,7 @@
         <v>1644</v>
       </c>
       <c r="L102" s="23" t="s">
-        <v>1699</v>
+        <v>1698</v>
       </c>
       <c r="M102" s="23" t="s">
         <v>1650</v>
@@ -17585,7 +17586,7 @@
         <v>1626</v>
       </c>
       <c r="K104" s="23" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="L104" s="23" t="s">
         <v>1627</v>
@@ -17792,13 +17793,13 @@
         <v>1616</v>
       </c>
       <c r="I107" s="23" t="s">
+        <v>1821</v>
+      </c>
+      <c r="K107" s="23" t="s">
         <v>1822</v>
       </c>
-      <c r="K107" s="23" t="s">
-        <v>1823</v>
-      </c>
       <c r="L107" s="23" t="s">
-        <v>1770</v>
+        <v>1769</v>
       </c>
       <c r="M107" s="23" t="s">
         <v>1668</v>
@@ -18023,7 +18024,7 @@
         <v>1617</v>
       </c>
       <c r="M110" s="23" t="s">
-        <v>1782</v>
+        <v>1781</v>
       </c>
       <c r="N110" s="1" t="s">
         <v>1579</v>
@@ -18167,10 +18168,10 @@
         <v>1644</v>
       </c>
       <c r="K112" s="23" t="s">
-        <v>1698</v>
+        <v>1697</v>
       </c>
       <c r="L112" s="23" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="M112" s="23" t="s">
         <v>1650</v>
@@ -18540,7 +18541,7 @@
         <v>1629</v>
       </c>
       <c r="J117" s="23" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="K117" s="23" t="s">
         <v>1635</v>
@@ -19437,7 +19438,7 @@
         <v>1626</v>
       </c>
       <c r="L130" s="23" t="s">
-        <v>1798</v>
+        <v>1797</v>
       </c>
       <c r="O130" s="1" t="s">
         <v>1433</v>
@@ -19977,13 +19978,13 @@
         <v>1616</v>
       </c>
       <c r="I138" s="23" t="s">
-        <v>1675</v>
+        <v>1674</v>
       </c>
       <c r="L138" s="23" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="M138" s="23" t="s">
-        <v>1677</v>
+        <v>1676</v>
       </c>
       <c r="O138" s="1" t="s">
         <v>1433</v>
@@ -20386,10 +20387,10 @@
         <v>1005</v>
       </c>
       <c r="E144" s="23" t="s">
-        <v>1790</v>
+        <v>1789</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
       <c r="G144" s="23" t="s">
         <v>63</v>
@@ -20398,13 +20399,13 @@
         <v>1616</v>
       </c>
       <c r="I144" s="23" t="s">
-        <v>1795</v>
+        <v>1794</v>
       </c>
       <c r="K144" s="23" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="L144" s="23" t="s">
-        <v>1791</v>
+        <v>1790</v>
       </c>
       <c r="N144" s="1" t="s">
         <v>1507</v>
@@ -20686,10 +20687,10 @@
         <v>1626</v>
       </c>
       <c r="J148" s="23" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
       <c r="M148" s="23" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="O148" s="1" t="s">
         <v>1433</v>
@@ -21236,7 +21237,7 @@
         <v>1616</v>
       </c>
       <c r="I156" s="23" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="O156" s="1" t="s">
         <v>1433</v>
@@ -21380,13 +21381,13 @@
         <v>1644</v>
       </c>
       <c r="J158" s="23" t="s">
-        <v>1811</v>
+        <v>1810</v>
       </c>
       <c r="K158" s="23" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="M158" s="23" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="N158" s="1" t="s">
         <v>1579</v>
@@ -23217,7 +23218,7 @@
         <v>1624</v>
       </c>
       <c r="L185" s="23" t="s">
-        <v>1699</v>
+        <v>1698</v>
       </c>
       <c r="M185" s="23" t="s">
         <v>1650</v>
@@ -23850,13 +23851,13 @@
         <v>1616</v>
       </c>
       <c r="I194" s="23" t="s">
+        <v>1774</v>
+      </c>
+      <c r="J194" s="23" t="s">
         <v>1775</v>
       </c>
-      <c r="J194" s="23" t="s">
+      <c r="M194" s="23" t="s">
         <v>1776</v>
-      </c>
-      <c r="M194" s="23" t="s">
-        <v>1777</v>
       </c>
       <c r="N194" s="1" t="s">
         <v>1579</v>
@@ -24666,7 +24667,7 @@
         <v>1430</v>
       </c>
       <c r="M206" s="23" t="s">
-        <v>1674</v>
+        <v>1673</v>
       </c>
       <c r="O206" s="1" t="s">
         <v>1433</v>
@@ -25059,7 +25060,7 @@
         <v>t-kun</v>
       </c>
       <c r="C212" s="24" t="s">
-        <v>1745</v>
+        <v>1744</v>
       </c>
       <c r="D212" s="23" t="s">
         <v>1515</v>
@@ -25080,7 +25081,7 @@
         <v>1626</v>
       </c>
       <c r="L212" s="23" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
       <c r="N212" s="1" t="s">
         <v>1508</v>
@@ -25155,13 +25156,13 @@
         <v>1653</v>
       </c>
       <c r="I213" s="23" t="s">
-        <v>1746</v>
+        <v>1745</v>
       </c>
       <c r="L213" s="23" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="M213" s="23" t="s">
-        <v>1837</v>
+        <v>1836</v>
       </c>
       <c r="N213" s="1" t="s">
         <v>1508</v>
@@ -25380,7 +25381,7 @@
         <v>1627</v>
       </c>
       <c r="M216" s="23" t="s">
-        <v>1701</v>
+        <v>1700</v>
       </c>
       <c r="N216" s="1" t="s">
         <v>1507</v>
@@ -25680,7 +25681,7 @@
         <v>1639</v>
       </c>
       <c r="L220" s="23" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="N220" s="1" t="s">
         <v>1507</v>
@@ -26218,19 +26219,19 @@
         <v>iruya-rui</v>
       </c>
       <c r="C228" s="24" t="s">
+        <v>1702</v>
+      </c>
+      <c r="D228" s="23" t="s">
         <v>1703</v>
       </c>
-      <c r="D228" s="23" t="s">
+      <c r="E228" s="23" t="s">
         <v>1704</v>
       </c>
-      <c r="E228" s="23" t="s">
+      <c r="F228" s="15" t="s">
         <v>1705</v>
       </c>
-      <c r="F228" s="15" t="s">
+      <c r="G228" s="23" t="s">
         <v>1706</v>
-      </c>
-      <c r="G228" s="23" t="s">
-        <v>1707</v>
       </c>
       <c r="H228" s="23" t="s">
         <v>1616</v>
@@ -26239,13 +26240,13 @@
         <v>1639</v>
       </c>
       <c r="K228" s="23" t="s">
+        <v>1707</v>
+      </c>
+      <c r="L228" s="23" t="s">
         <v>1708</v>
       </c>
-      <c r="L228" s="23" t="s">
-        <v>1709</v>
-      </c>
       <c r="M228" s="23" t="s">
-        <v>1723</v>
+        <v>1722</v>
       </c>
       <c r="N228" s="1" t="s">
         <v>1579</v>
@@ -26302,19 +26303,19 @@
         <v>​hagane-meta</v>
       </c>
       <c r="C229" s="24" t="s">
+        <v>1709</v>
+      </c>
+      <c r="D229" s="23" t="s">
         <v>1710</v>
       </c>
-      <c r="D229" s="23" t="s">
+      <c r="E229" s="23" t="s">
         <v>1711</v>
       </c>
-      <c r="E229" s="23" t="s">
+      <c r="F229" s="3" t="s">
         <v>1712</v>
       </c>
-      <c r="F229" s="3" t="s">
+      <c r="G229" s="23" t="s">
         <v>1713</v>
-      </c>
-      <c r="G229" s="23" t="s">
-        <v>1714</v>
       </c>
       <c r="H229" s="23" t="s">
         <v>1616</v>
@@ -26323,10 +26324,10 @@
         <v>1626</v>
       </c>
       <c r="L229" s="23" t="s">
+        <v>1714</v>
+      </c>
+      <c r="N229" s="1" t="s">
         <v>1715</v>
-      </c>
-      <c r="N229" s="1" t="s">
-        <v>1716</v>
       </c>
       <c r="O229" s="1" t="s">
         <v>1433</v>
@@ -26380,19 +26381,19 @@
         <v>the-bard-euphoria</v>
       </c>
       <c r="C230" s="24" t="s">
+        <v>1727</v>
+      </c>
+      <c r="D230" s="23" t="s">
         <v>1728</v>
       </c>
-      <c r="D230" s="23" t="s">
+      <c r="E230" s="23" t="s">
         <v>1729</v>
       </c>
-      <c r="E230" s="23" t="s">
-        <v>1730</v>
-      </c>
       <c r="F230" s="29" t="s">
-        <v>1736</v>
+        <v>1735</v>
       </c>
       <c r="G230" s="23" t="s">
-        <v>1732</v>
+        <v>1731</v>
       </c>
       <c r="H230" s="23" t="s">
         <v>1652</v>
@@ -26401,7 +26402,7 @@
         <v>1626</v>
       </c>
       <c r="K230" s="23" t="s">
-        <v>1731</v>
+        <v>1730</v>
       </c>
       <c r="N230" s="1" t="s">
         <v>1579</v>
@@ -26458,34 +26459,34 @@
         <v>arujine-sarasa</v>
       </c>
       <c r="C231" s="24" t="s">
+        <v>1736</v>
+      </c>
+      <c r="D231" s="23" t="s">
         <v>1737</v>
       </c>
-      <c r="D231" s="23" t="s">
+      <c r="E231" s="23" t="s">
         <v>1738</v>
       </c>
-      <c r="E231" s="23" t="s">
+      <c r="F231" s="29" t="s">
         <v>1739</v>
       </c>
-      <c r="F231" s="29" t="s">
+      <c r="G231" s="23" t="s">
         <v>1740</v>
-      </c>
-      <c r="G231" s="23" t="s">
-        <v>1741</v>
       </c>
       <c r="H231" s="23" t="s">
         <v>1617</v>
       </c>
       <c r="I231" s="23" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
       <c r="J231" s="23" t="s">
+        <v>1741</v>
+      </c>
+      <c r="L231" s="23" t="s">
+        <v>1743</v>
+      </c>
+      <c r="M231" s="23" t="s">
         <v>1742</v>
-      </c>
-      <c r="L231" s="23" t="s">
-        <v>1744</v>
-      </c>
-      <c r="M231" s="23" t="s">
-        <v>1743</v>
       </c>
       <c r="N231" s="1" t="s">
         <v>1579</v>
@@ -26542,19 +26543,19 @@
         <v>amaga-eru</v>
       </c>
       <c r="C232" s="24" t="s">
+        <v>1746</v>
+      </c>
+      <c r="D232" s="23" t="s">
         <v>1747</v>
       </c>
-      <c r="D232" s="23" t="s">
+      <c r="E232" s="23" t="s">
         <v>1748</v>
       </c>
-      <c r="E232" s="23" t="s">
+      <c r="F232" s="29" t="s">
         <v>1749</v>
       </c>
-      <c r="F232" s="29" t="s">
+      <c r="G232" s="23" t="s">
         <v>1750</v>
-      </c>
-      <c r="G232" s="23" t="s">
-        <v>1751</v>
       </c>
       <c r="H232" s="23" t="s">
         <v>1616</v>
@@ -26563,10 +26564,10 @@
         <v>1626</v>
       </c>
       <c r="J232" s="23" t="s">
-        <v>1764</v>
+        <v>1763</v>
       </c>
       <c r="L232" s="23" t="s">
-        <v>1768</v>
+        <v>1767</v>
       </c>
       <c r="N232" s="1" t="s">
         <v>1579</v>
@@ -26623,16 +26624,16 @@
         <v>narukami-kyou</v>
       </c>
       <c r="C233" s="24" t="s">
+        <v>1752</v>
+      </c>
+      <c r="D233" s="23" t="s">
         <v>1753</v>
       </c>
-      <c r="D233" s="23" t="s">
+      <c r="E233" s="23" t="s">
         <v>1754</v>
       </c>
-      <c r="E233" s="23" t="s">
+      <c r="F233" s="29" t="s">
         <v>1755</v>
-      </c>
-      <c r="F233" s="29" t="s">
-        <v>1756</v>
       </c>
       <c r="G233" s="23" t="str">
         <f>テーブル1[[#This Row],[名前]]&amp;"(UTAU)"</f>
@@ -26696,19 +26697,19 @@
         <v>aira</v>
       </c>
       <c r="C234" s="24" t="s">
+        <v>1732</v>
+      </c>
+      <c r="D234" s="23" t="s">
         <v>1733</v>
       </c>
-      <c r="D234" s="23" t="s">
+      <c r="E234" s="23" t="s">
         <v>1734</v>
       </c>
-      <c r="E234" s="23" t="s">
+      <c r="F234" s="3" t="s">
         <v>1735</v>
       </c>
-      <c r="F234" s="3" t="s">
-        <v>1736</v>
-      </c>
       <c r="G234" s="23" t="s">
-        <v>1732</v>
+        <v>1731</v>
       </c>
       <c r="H234" s="23" t="s">
         <v>1616</v>
@@ -26729,7 +26730,7 @@
       </c>
       <c r="R234" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>50.486282792535803</v>
+        <v>50.089153120370995</v>
       </c>
       <c r="T234" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -26798,7 +26799,7 @@
       </c>
       <c r="R235" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>60.565172289448213</v>
+        <v>60.330091045217493</v>
       </c>
       <c r="T235" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -26864,7 +26865,7 @@
       </c>
       <c r="R236" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>60.003682230270435</v>
+        <v>60.027184846758495</v>
       </c>
       <c r="T236" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -26924,7 +26925,7 @@
       </c>
       <c r="R237" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>1.5291819300212173E-2</v>
+        <v>0.98048526512834555</v>
       </c>
       <c r="T237" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -26984,7 +26985,7 @@
       </c>
       <c r="R238" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.440000682071926</v>
+        <v>34.31195702997865</v>
       </c>
       <c r="T238" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27044,7 +27045,7 @@
       </c>
       <c r="R239" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.730759264784666</v>
+        <v>34.099315097180373</v>
       </c>
       <c r="T239" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27101,7 +27102,7 @@
       </c>
       <c r="R240" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.350635995292675</v>
+        <v>12.761743919833039</v>
       </c>
       <c r="T240" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27161,7 +27162,7 @@
       </c>
       <c r="R241" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>10.709926054380587</v>
+        <v>10.550067058402242</v>
       </c>
       <c r="T241" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27221,7 +27222,7 @@
       </c>
       <c r="R242" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.795956393279855</v>
+        <v>20.474251742334072</v>
       </c>
       <c r="T242" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27284,7 +27285,7 @@
       </c>
       <c r="R243" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.370684567022497</v>
+        <v>13.024335115177962</v>
       </c>
       <c r="T243" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27341,7 +27342,7 @@
       </c>
       <c r="R244" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.997437464468542</v>
+        <v>12.683984430219224</v>
       </c>
       <c r="T244" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27401,7 +27402,7 @@
       </c>
       <c r="R245" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>10.81232251051448</v>
+        <v>10.451690819462611</v>
       </c>
       <c r="T245" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27434,13 +27435,13 @@
         <v>amaze-maze-noisette</v>
       </c>
       <c r="C246" s="24" t="s">
+        <v>1846</v>
+      </c>
+      <c r="D246" s="23" t="s">
         <v>1847</v>
       </c>
-      <c r="D246" s="23" t="s">
+      <c r="E246" s="23" t="s">
         <v>1848</v>
-      </c>
-      <c r="E246" s="23" t="s">
-        <v>1849</v>
       </c>
       <c r="F246" s="2" t="s">
         <v>97</v>
@@ -27452,10 +27453,10 @@
         <v>1616</v>
       </c>
       <c r="I246" s="23" t="s">
+        <v>1849</v>
+      </c>
+      <c r="L246" s="23" t="s">
         <v>1850</v>
-      </c>
-      <c r="L246" s="23" t="s">
-        <v>1851</v>
       </c>
       <c r="M246" s="23" t="s">
         <v>1647</v>
@@ -27473,7 +27474,7 @@
       </c>
       <c r="R246" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.677255561910766</v>
+        <v>20.421608034398052</v>
       </c>
       <c r="T246" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27533,7 +27534,7 @@
       </c>
       <c r="R247" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.130661788201515</v>
+        <v>20.965204798302</v>
       </c>
       <c r="T247" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27593,7 +27594,7 @@
       </c>
       <c r="R248" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.215659228751548</v>
+        <v>20.467900289962561</v>
       </c>
       <c r="T248" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27653,7 +27654,7 @@
       </c>
       <c r="R249" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.680464964198993</v>
+        <v>20.780047932139269</v>
       </c>
       <c r="T249" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27713,7 +27714,7 @@
       </c>
       <c r="R250" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.048182921046706</v>
+        <v>20.10582401367882</v>
       </c>
       <c r="T250" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27773,7 +27774,7 @@
       </c>
       <c r="R251" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.810104844221531</v>
+        <v>20.04896632197838</v>
       </c>
       <c r="T251" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27833,7 +27834,7 @@
       </c>
       <c r="R252" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.548484196117705</v>
+        <v>20.574871027300606</v>
       </c>
       <c r="T252" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27893,7 +27894,7 @@
       </c>
       <c r="R253" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.604872609834121</v>
+        <v>20.571751412021015</v>
       </c>
       <c r="T253" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27953,7 +27954,7 @@
       </c>
       <c r="R254" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.498067499933512</v>
+        <v>20.748001814644748</v>
       </c>
       <c r="T254" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28013,7 +28014,7 @@
       </c>
       <c r="R255" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.270268616623188</v>
+        <v>20.922035014366429</v>
       </c>
       <c r="T255" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28073,7 +28074,7 @@
       </c>
       <c r="R256" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.818220331679115</v>
+        <v>20.599556995715524</v>
       </c>
       <c r="T256" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28133,7 +28134,7 @@
       </c>
       <c r="R257" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.036916734794854</v>
+        <v>20.595808366214612</v>
       </c>
       <c r="T257" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28191,7 +28192,7 @@
       </c>
       <c r="R258" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.664549549094788</v>
+        <v>13.043983828965118</v>
       </c>
       <c r="T258" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28248,7 +28249,7 @@
       </c>
       <c r="R259" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>40.296210686915011</v>
+        <v>40.052905858898534</v>
       </c>
       <c r="T259" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28305,7 +28306,7 @@
       </c>
       <c r="R260" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.1923298060270318</v>
+        <v>7.6490050880459961</v>
       </c>
       <c r="T260" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28362,7 +28363,7 @@
       </c>
       <c r="R261" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>50.810391899480187</v>
+        <v>50.950969087882235</v>
       </c>
       <c r="T261" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28419,7 +28420,7 @@
       </c>
       <c r="R262" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.23594571998679859</v>
+        <v>0.5579253026449692</v>
       </c>
       <c r="T262" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28476,7 +28477,7 @@
       </c>
       <c r="R263" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.65130923820690656</v>
+        <v>0.82538949944544138</v>
       </c>
       <c r="T263" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28533,7 +28534,7 @@
       </c>
       <c r="R264" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.903716321677142</v>
+        <v>7.5974610838840038</v>
       </c>
       <c r="T264" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28594,7 +28595,7 @@
       </c>
       <c r="R265" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>50.134357454921386</v>
+        <v>50.93669511380233</v>
       </c>
       <c r="T265" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28651,7 +28652,7 @@
       </c>
       <c r="R266" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.475095542034502</v>
+        <v>34.330557926902635</v>
       </c>
       <c r="T266" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28708,7 +28709,7 @@
       </c>
       <c r="R267" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.1856178553427039</v>
+        <v>7.4186539934119526</v>
       </c>
       <c r="T267" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28765,7 +28766,7 @@
       </c>
       <c r="R268" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.462233545587818</v>
+        <v>13.491400077144949</v>
       </c>
       <c r="T268" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28822,7 +28823,7 @@
       </c>
       <c r="R269" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.882623971794285</v>
+        <v>12.960013942845334</v>
       </c>
       <c r="T269" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28879,7 +28880,7 @@
       </c>
       <c r="R270" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.477485851945238</v>
+        <v>12.834105390773347</v>
       </c>
       <c r="T270" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28933,7 +28934,7 @@
         <v>1639</v>
       </c>
       <c r="K271" s="23" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
       <c r="L271" s="23" t="s">
         <v>1627</v>
@@ -28954,7 +28955,7 @@
       </c>
       <c r="R271" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>75.941223249731848</v>
+        <v>75.595820454174387</v>
       </c>
       <c r="T271" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29011,7 +29012,7 @@
       </c>
       <c r="R272" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.371655923751435</v>
+        <v>13.152660136648874</v>
       </c>
       <c r="T272" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29068,7 +29069,7 @@
       </c>
       <c r="R273" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.608893866335036</v>
+        <v>12.672954924772798</v>
       </c>
       <c r="T273" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29125,7 +29126,7 @@
       </c>
       <c r="R274" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.21040149245384454</v>
+        <v>0.89907718569464834</v>
       </c>
       <c r="T274" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29182,7 +29183,7 @@
       </c>
       <c r="R275" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>34.224302109572093</v>
+        <v>34.267459388912961</v>
       </c>
       <c r="T275" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29239,7 +29240,7 @@
       </c>
       <c r="R276" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.60193998017675</v>
+        <v>12.739408592099652</v>
       </c>
       <c r="T276" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29296,7 +29297,7 @@
       </c>
       <c r="R277" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.81862051172245</v>
+        <v>12.696707215771362</v>
       </c>
       <c r="T277" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29356,7 +29357,7 @@
       </c>
       <c r="R278" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>50.026495889797125</v>
+        <v>50.632774771261239</v>
       </c>
       <c r="T278" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29413,7 +29414,7 @@
       </c>
       <c r="R279" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.22992330810141548</v>
+        <v>0.34751940217963073</v>
       </c>
       <c r="T279" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29470,7 +29471,7 @@
       </c>
       <c r="R280" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.79785211757701469</v>
+        <v>0.5788920569471141</v>
       </c>
       <c r="T280" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29531,7 +29532,7 @@
       </c>
       <c r="R281" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>9.2187906798839983</v>
+        <v>9.6884706201781405</v>
       </c>
       <c r="T281" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29585,10 +29586,10 @@
         <v>1644</v>
       </c>
       <c r="K282" s="23" t="s">
-        <v>1702</v>
+        <v>1701</v>
       </c>
       <c r="L282" s="23" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
       <c r="P282" s="24" t="str">
         <f>テーブル1[[#This Row],[リンク]]&amp;テーブル1[[#This Row],[描画状況]]</f>
@@ -29600,7 +29601,7 @@
       </c>
       <c r="R282" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>57.51831723072366</v>
+        <v>57.44276208034546</v>
       </c>
       <c r="T282" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29658,7 +29659,7 @@
       </c>
       <c r="R283" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.675203684835374</v>
+        <v>20.996865336766909</v>
       </c>
       <c r="T283" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29715,7 +29716,7 @@
       </c>
       <c r="R284" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.48839704332486811</v>
+        <v>0.83706565885490081</v>
       </c>
       <c r="T284" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29775,7 +29776,7 @@
       </c>
       <c r="R285" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>10.375971781664111</v>
+        <v>10.395369024971581</v>
       </c>
       <c r="T285" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29844,7 +29845,7 @@
       </c>
       <c r="R286" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>80.480891167273171</v>
+        <v>80.902351917133416</v>
       </c>
       <c r="T286" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29901,7 +29902,7 @@
       </c>
       <c r="R287" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.1592310720064614</v>
+        <v>7.5029649281983337</v>
       </c>
       <c r="T287" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29958,7 +29959,7 @@
       </c>
       <c r="R288" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.757145207573229</v>
+        <v>12.586966605222065</v>
       </c>
       <c r="T288" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30018,7 +30019,7 @@
       </c>
       <c r="R289" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>9.8675061074492181</v>
+        <v>9.3603950433407093</v>
       </c>
       <c r="T289" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30075,7 +30076,7 @@
       </c>
       <c r="R290" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>9.2309643396316088E-2</v>
+        <v>0.78246597586283506</v>
       </c>
       <c r="T290" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30129,7 +30130,7 @@
         <v>1626</v>
       </c>
       <c r="K291" s="23" t="s">
-        <v>1702</v>
+        <v>1701</v>
       </c>
       <c r="L291" s="23" t="s">
         <v>1627</v>
@@ -30144,7 +30145,7 @@
       </c>
       <c r="R291" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>58.134401115147554</v>
+        <v>57.987747829064062</v>
       </c>
       <c r="T291" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30201,7 +30202,7 @@
       </c>
       <c r="R292" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.731574397817502</v>
+        <v>13.197329068554174</v>
       </c>
       <c r="T292" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30261,7 +30262,7 @@
       </c>
       <c r="R293" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>22.878338667081735</v>
+        <v>23.169028889890495</v>
       </c>
       <c r="T293" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30303,7 +30304,7 @@
         <v>1004</v>
       </c>
       <c r="F294" s="2" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
       <c r="G294" s="23" t="s">
         <v>63</v>
@@ -30315,10 +30316,10 @@
         <v>1626</v>
       </c>
       <c r="J294" s="23" t="s">
+        <v>1792</v>
+      </c>
+      <c r="M294" s="23" t="s">
         <v>1793</v>
-      </c>
-      <c r="M294" s="23" t="s">
-        <v>1794</v>
       </c>
       <c r="N294" s="1" t="s">
         <v>1507</v>
@@ -30333,7 +30334,7 @@
       </c>
       <c r="R294" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>60.762203915853142</v>
+        <v>60.322105228669038</v>
       </c>
       <c r="T294" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30390,7 +30391,7 @@
       </c>
       <c r="R295" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.5985380883455993</v>
+        <v>0.94331296531349063</v>
       </c>
       <c r="T295" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30447,7 +30448,7 @@
       </c>
       <c r="R296" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>50.927363206607311</v>
+        <v>50.814522399768336</v>
       </c>
       <c r="T296" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30507,7 +30508,7 @@
       </c>
       <c r="R297" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>10.708044137873674</v>
+        <v>10.93246802480383</v>
       </c>
       <c r="T297" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30564,7 +30565,7 @@
       </c>
       <c r="R298" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.24018219621019643</v>
+        <v>0.72890066594459579</v>
       </c>
       <c r="T298" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30624,7 +30625,7 @@
       </c>
       <c r="R299" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.21206506303260975</v>
+        <v>0.58028924173365848</v>
       </c>
       <c r="T299" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30675,10 +30676,10 @@
         <v>1653</v>
       </c>
       <c r="I300" s="23" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
       <c r="J300" s="23" t="s">
-        <v>1765</v>
+        <v>1764</v>
       </c>
       <c r="P300" s="24" t="str">
         <f>テーブル1[[#This Row],[リンク]]&amp;テーブル1[[#This Row],[描画状況]]</f>
@@ -30690,7 +30691,7 @@
       </c>
       <c r="R300" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>58.081287606154298</v>
+        <v>57.352557766851085</v>
       </c>
       <c r="T300" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30747,7 +30748,7 @@
       </c>
       <c r="R301" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.24260551252630136</v>
+        <v>0.21109723212857123</v>
       </c>
       <c r="T301" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30804,7 +30805,7 @@
       </c>
       <c r="R302" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>2.6986259110839517E-2</v>
+        <v>0.8209101625814661</v>
       </c>
       <c r="T302" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30861,7 +30862,7 @@
       </c>
       <c r="R303" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.29896955899620392</v>
+        <v>0.60593645335335999</v>
       </c>
       <c r="T303" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30918,7 +30919,7 @@
       </c>
       <c r="R304" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>3.4626935394300951E-2</v>
+        <v>0.70595167402415737</v>
       </c>
       <c r="T304" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30969,16 +30970,16 @@
         <v>1616</v>
       </c>
       <c r="I305" s="23" t="s">
+        <v>1831</v>
+      </c>
+      <c r="J305" s="23" t="s">
+        <v>1828</v>
+      </c>
+      <c r="L305" s="23" t="s">
         <v>1832</v>
       </c>
-      <c r="J305" s="23" t="s">
-        <v>1829</v>
-      </c>
-      <c r="L305" s="23" t="s">
+      <c r="M305" s="23" t="s">
         <v>1833</v>
-      </c>
-      <c r="M305" s="23" t="s">
-        <v>1834</v>
       </c>
       <c r="N305" s="1" t="s">
         <v>1508</v>
@@ -30993,7 +30994,7 @@
       </c>
       <c r="R305" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.366642830910045</v>
+        <v>34.108683262236561</v>
       </c>
       <c r="T305" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31059,7 +31060,7 @@
       </c>
       <c r="R306" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.332668753916614</v>
+        <v>20.706149365933992</v>
       </c>
       <c r="T306" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31116,7 +31117,7 @@
       </c>
       <c r="R307" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.90073502848010834</v>
+        <v>0.23896249770403255</v>
       </c>
       <c r="T307" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31173,7 +31174,7 @@
       </c>
       <c r="R308" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.407700011415507</v>
+        <v>34.211771684720283</v>
       </c>
       <c r="T308" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31230,7 +31231,7 @@
       </c>
       <c r="R309" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>34.106114414929152</v>
+        <v>34.303608897108852</v>
       </c>
       <c r="T309" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31291,7 +31292,7 @@
       </c>
       <c r="R310" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>9.878689146988556</v>
+        <v>9.472378963312611</v>
       </c>
       <c r="T310" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31349,7 +31350,7 @@
       </c>
       <c r="R311" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>3.6179797621252452E-2</v>
+        <v>0.4727727956777491</v>
       </c>
       <c r="T311" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31412,7 +31413,7 @@
       </c>
       <c r="R312" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.946192894127424</v>
+        <v>12.785258495811139</v>
       </c>
       <c r="T312" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31469,7 +31470,7 @@
       </c>
       <c r="R313" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.69268857601486544</v>
+        <v>0.20231242076793021</v>
       </c>
       <c r="T313" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31526,7 +31527,7 @@
       </c>
       <c r="R314" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.80130192365982811</v>
+        <v>0.11587023326012325</v>
       </c>
       <c r="T314" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31583,7 +31584,7 @@
       </c>
       <c r="R315" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.795595435333437</v>
+        <v>12.972242728570553</v>
       </c>
       <c r="T315" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31641,7 +31642,7 @@
       </c>
       <c r="R316" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.45706255301422649</v>
+        <v>0.78260853422500321</v>
       </c>
       <c r="T316" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31699,7 +31700,7 @@
       </c>
       <c r="R317" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>6.3962083567593697E-2</v>
+        <v>0.91417665634403722</v>
       </c>
       <c r="T317" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31757,7 +31758,7 @@
       </c>
       <c r="R318" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.21279379776490837</v>
+        <v>0.80790809751240544</v>
       </c>
       <c r="T318" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31815,7 +31816,7 @@
       </c>
       <c r="R319" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.98085135629397524</v>
+        <v>0.2005439882899569</v>
       </c>
       <c r="T319" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31873,7 +31874,7 @@
       </c>
       <c r="R320" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.93049593556234877</v>
+        <v>0.37598321138777246</v>
       </c>
       <c r="T320" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31931,7 +31932,7 @@
       </c>
       <c r="R321" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>34.006053407922629</v>
+        <v>34.014923571995205</v>
       </c>
       <c r="T321" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31991,7 +31992,7 @@
       </c>
       <c r="R322" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>22.634133219917775</v>
+        <v>22.245388174831</v>
       </c>
       <c r="T322" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32051,7 +32052,7 @@
       </c>
       <c r="R323" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>22.914954691248379</v>
+        <v>22.353516731173702</v>
       </c>
       <c r="T323" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32108,7 +32109,7 @@
       </c>
       <c r="R324" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.68001320399803789</v>
+        <v>0.97226262663676422</v>
       </c>
       <c r="T324" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32165,7 +32166,7 @@
       </c>
       <c r="R325" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.47176950344042246</v>
+        <v>0.16811616455877632</v>
       </c>
       <c r="T325" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32207,7 +32208,7 @@
         <v>969</v>
       </c>
       <c r="F326" s="2" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="G326" s="23" t="str">
         <f>テーブル1[[#This Row],[名前]]&amp;"(UTAU)"</f>
@@ -32232,7 +32233,7 @@
       </c>
       <c r="R326" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>16.968324743936684</v>
+        <v>17.132008245103364</v>
       </c>
       <c r="T326" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32290,7 +32291,7 @@
       </c>
       <c r="R327" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>50.597333371618163</v>
+        <v>50.59354183449863</v>
       </c>
       <c r="T327" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32347,7 +32348,7 @@
       </c>
       <c r="R328" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.189471906748828</v>
+        <v>12.889574173268656</v>
       </c>
       <c r="T328" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32404,7 +32405,7 @@
       </c>
       <c r="R329" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.398854744197774</v>
+        <v>12.596137027624776</v>
       </c>
       <c r="T329" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32464,7 +32465,7 @@
       </c>
       <c r="R330" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.740098697330719</v>
+        <v>20.652226345901418</v>
       </c>
       <c r="T330" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32515,10 +32516,10 @@
         <v>1616</v>
       </c>
       <c r="I331" s="23" t="s">
+        <v>1851</v>
+      </c>
+      <c r="M331" s="23" t="s">
         <v>1852</v>
-      </c>
-      <c r="M331" s="23" t="s">
-        <v>1853</v>
       </c>
       <c r="N331" s="1" t="s">
         <v>1507</v>
@@ -32533,7 +32534,7 @@
       </c>
       <c r="R331" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.313045268906528</v>
+        <v>20.07405382803066</v>
       </c>
       <c r="T331" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32593,7 +32594,7 @@
       </c>
       <c r="R332" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>22.711187591342267</v>
+        <v>22.33972548250664</v>
       </c>
       <c r="T332" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32644,7 +32645,7 @@
         <v>1652</v>
       </c>
       <c r="I333" s="23" t="s">
-        <v>1835</v>
+        <v>1834</v>
       </c>
       <c r="N333" s="1" t="s">
         <v>1508</v>
@@ -32659,7 +32660,7 @@
       </c>
       <c r="R333" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.370474205034</v>
+        <v>33.406335744076387</v>
       </c>
       <c r="T333" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32717,7 +32718,7 @@
       </c>
       <c r="R334" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.25805238067492786</v>
+        <v>0.89602869942267727</v>
       </c>
       <c r="T334" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32777,7 +32778,7 @@
       </c>
       <c r="R335" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.587156378036269</v>
+        <v>33.868401868098658</v>
       </c>
       <c r="T335" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32840,7 +32841,7 @@
       </c>
       <c r="R336" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>67.33391856630719</v>
+        <v>66.696828484577125</v>
       </c>
       <c r="T336" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32897,7 +32898,7 @@
       </c>
       <c r="R337" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.68773869402882026</v>
+        <v>0.40518237938867618</v>
       </c>
       <c r="T337" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32954,7 +32955,7 @@
       </c>
       <c r="R338" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.4560346050967476</v>
+        <v>8.0538431312333163</v>
       </c>
       <c r="T338" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33011,7 +33012,7 @@
       </c>
       <c r="R339" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.43470672058436</v>
+        <v>13.24078931465449</v>
       </c>
       <c r="T339" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33072,7 +33073,7 @@
       </c>
       <c r="R340" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>9.6553694301994302</v>
+        <v>9.5417160469538409</v>
       </c>
       <c r="T340" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33132,7 +33133,7 @@
       </c>
       <c r="R341" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.50315104356536</v>
+        <v>34.322788386258217</v>
       </c>
       <c r="T341" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33189,7 +33190,7 @@
       </c>
       <c r="R342" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.76998464268596845</v>
+        <v>0.84564004806439252</v>
       </c>
       <c r="T342" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33246,7 +33247,7 @@
       </c>
       <c r="R343" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.188161273398688</v>
+        <v>13.08122123966743</v>
       </c>
       <c r="T343" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33306,7 +33307,7 @@
       </c>
       <c r="R344" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.059161842543194</v>
+        <v>20.898030413019733</v>
       </c>
       <c r="T344" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33363,7 +33364,7 @@
       </c>
       <c r="R345" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.960820761046458</v>
+        <v>13.153016831476764</v>
       </c>
       <c r="T345" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33420,7 +33421,7 @@
       </c>
       <c r="R346" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.645154026753001</v>
+        <v>20.574304564955884</v>
       </c>
       <c r="T346" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33471,16 +33472,16 @@
         <v>1617</v>
       </c>
       <c r="I347" s="23" t="s">
-        <v>1842</v>
+        <v>1841</v>
       </c>
       <c r="J347" s="23" t="s">
-        <v>1836</v>
+        <v>1835</v>
       </c>
       <c r="L347" s="23" t="s">
+        <v>1837</v>
+      </c>
+      <c r="M347" s="23" t="s">
         <v>1838</v>
-      </c>
-      <c r="M347" s="23" t="s">
-        <v>1839</v>
       </c>
       <c r="N347" s="1" t="s">
         <v>1508</v>
@@ -33495,7 +33496,7 @@
       </c>
       <c r="R347" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.919932664954331</v>
+        <v>34.267224195313645</v>
       </c>
       <c r="T347" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33555,7 +33556,7 @@
       </c>
       <c r="R348" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>23.027586558396372</v>
+        <v>22.835623811732212</v>
       </c>
       <c r="T348" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33612,7 +33613,7 @@
       </c>
       <c r="R349" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.9554507015768372</v>
+        <v>0.91392265229698</v>
       </c>
       <c r="T349" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33669,7 +33670,7 @@
       </c>
       <c r="R350" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.1494279964225298</v>
+        <v>0.26028481275352122</v>
       </c>
       <c r="T350" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33727,7 +33728,7 @@
       </c>
       <c r="R351" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.908308629703633</v>
+        <v>12.947207376853163</v>
       </c>
       <c r="T351" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33787,7 +33788,7 @@
       </c>
       <c r="R352" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>23.059533374125866</v>
+        <v>22.797627068127181</v>
       </c>
       <c r="T352" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33844,7 +33845,7 @@
       </c>
       <c r="R353" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.374537450628061</v>
+        <v>33.514829311283215</v>
       </c>
       <c r="T353" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33901,7 +33902,7 @@
       </c>
       <c r="R354" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.57598260632279119</v>
+        <v>0.96025109267335906</v>
       </c>
       <c r="T354" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33943,7 +33944,7 @@
         <v>1007</v>
       </c>
       <c r="F355" s="2" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
       <c r="G355" s="23" t="s">
         <v>63</v>
@@ -33952,10 +33953,10 @@
         <v>1617</v>
       </c>
       <c r="I355" s="23" t="s">
+        <v>1795</v>
+      </c>
+      <c r="L355" s="23" t="s">
         <v>1796</v>
-      </c>
-      <c r="L355" s="23" t="s">
-        <v>1797</v>
       </c>
       <c r="N355" s="1" t="s">
         <v>1507</v>
@@ -33970,7 +33971,7 @@
       </c>
       <c r="R355" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>60.123251206933084</v>
+        <v>60.825838026114383</v>
       </c>
       <c r="T355" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34031,7 +34032,7 @@
       </c>
       <c r="R356" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>9.1667066823373577</v>
+        <v>9.717454274855525</v>
       </c>
       <c r="T356" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34089,7 +34090,7 @@
       </c>
       <c r="R357" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>34.143795017063177</v>
+        <v>33.879397940241262</v>
       </c>
       <c r="T357" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34146,7 +34147,7 @@
       </c>
       <c r="R358" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.752625687546285</v>
+        <v>12.904007678994907</v>
       </c>
       <c r="T358" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34203,7 +34204,7 @@
       </c>
       <c r="R359" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>40.004079495386883</v>
+        <v>40.900626537803063</v>
       </c>
       <c r="T359" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34261,7 +34262,7 @@
       </c>
       <c r="R360" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>3.0741284777972444E-2</v>
+        <v>0.7277089830836172</v>
       </c>
       <c r="T360" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34318,7 +34319,7 @@
       </c>
       <c r="R361" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.53707055542471749</v>
+        <v>0.25179257057287419</v>
       </c>
       <c r="T361" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34375,7 +34376,7 @@
       </c>
       <c r="R362" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.023737214234478</v>
+        <v>12.672665638834061</v>
       </c>
       <c r="T362" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34435,7 +34436,7 @@
       </c>
       <c r="R363" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>10.427955625102513</v>
+        <v>10.609756041034746</v>
       </c>
       <c r="T363" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34492,7 +34493,7 @@
       </c>
       <c r="R364" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.95137583985588148</v>
+        <v>5.1567261757817118E-2</v>
       </c>
       <c r="T364" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34549,7 +34550,7 @@
       </c>
       <c r="R365" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.900389095097781</v>
+        <v>13.334906181859433</v>
       </c>
       <c r="T365" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34603,10 +34604,10 @@
         <v>1626</v>
       </c>
       <c r="K366" s="23" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="M366" s="23" t="s">
-        <v>1814</v>
+        <v>1813</v>
       </c>
       <c r="N366" s="1" t="s">
         <v>1507</v>
@@ -34621,7 +34622,7 @@
       </c>
       <c r="R366" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.681885642856869</v>
+        <v>34.167314818079802</v>
       </c>
       <c r="T366" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34684,7 +34685,7 @@
       </c>
       <c r="R367" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.158756477123042</v>
+        <v>13.021808260242242</v>
       </c>
       <c r="T367" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34747,7 +34748,7 @@
       </c>
       <c r="R368" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.876629370066594</v>
+        <v>13.046159637013428</v>
       </c>
       <c r="T368" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34798,13 +34799,13 @@
         <v>1616</v>
       </c>
       <c r="I369" s="23" t="s">
-        <v>1830</v>
+        <v>1829</v>
       </c>
       <c r="J369" s="23" t="s">
+        <v>1839</v>
+      </c>
+      <c r="K369" s="23" t="s">
         <v>1840</v>
-      </c>
-      <c r="K369" s="23" t="s">
-        <v>1841</v>
       </c>
       <c r="L369" s="23" t="s">
         <v>1627</v>
@@ -34822,7 +34823,7 @@
       </c>
       <c r="R369" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>34.108865150140765</v>
+        <v>33.558478967092213</v>
       </c>
       <c r="T369" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34882,7 +34883,7 @@
       </c>
       <c r="R370" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>22.629091065363465</v>
+        <v>22.274958445279886</v>
       </c>
       <c r="T370" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34939,7 +34940,7 @@
       </c>
       <c r="R371" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.734121896675028</v>
+        <v>12.98136739302918</v>
       </c>
       <c r="T371" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34996,7 +34997,7 @@
       </c>
       <c r="R372" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.333163999607459</v>
+        <v>12.801659588057763</v>
       </c>
       <c r="T372" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35053,7 +35054,7 @@
       </c>
       <c r="R373" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.78299742761686775</v>
+        <v>0.46520303574498523</v>
       </c>
       <c r="T373" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35110,7 +35111,7 @@
       </c>
       <c r="R374" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.57131539319896185</v>
+        <v>0.18221006706771758</v>
       </c>
       <c r="T374" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35167,7 +35168,7 @@
       </c>
       <c r="R375" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.170096662172158</v>
+        <v>7.5193206543864264</v>
       </c>
       <c r="T375" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35224,7 +35225,7 @@
       </c>
       <c r="R376" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>8.0083781614446075</v>
+        <v>7.9684014090152635</v>
       </c>
       <c r="T376" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35284,7 +35285,7 @@
       </c>
       <c r="R377" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>10.170403298613802</v>
+        <v>10.649513187836112</v>
       </c>
       <c r="T377" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35317,13 +35318,13 @@
         <v>hinaki-v-draginie</v>
       </c>
       <c r="C378" s="24" t="s">
+        <v>1853</v>
+      </c>
+      <c r="D378" s="23" t="s">
+        <v>1855</v>
+      </c>
+      <c r="E378" s="23" t="s">
         <v>1854</v>
-      </c>
-      <c r="D378" s="23" t="s">
-        <v>1856</v>
-      </c>
-      <c r="E378" s="23" t="s">
-        <v>1855</v>
       </c>
       <c r="F378" s="2" t="s">
         <v>97</v>
@@ -35350,7 +35351,7 @@
       </c>
       <c r="R378" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.298168641286729</v>
+        <v>20.360662166875876</v>
       </c>
       <c r="T378" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35404,13 +35405,13 @@
         <v>1626</v>
       </c>
       <c r="K379" s="23" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="L379" s="23" t="s">
         <v>1627</v>
       </c>
       <c r="M379" s="23" t="s">
-        <v>1814</v>
+        <v>1813</v>
       </c>
       <c r="N379" s="1" t="s">
         <v>1507</v>
@@ -35425,7 +35426,7 @@
       </c>
       <c r="R379" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.900330260258087</v>
+        <v>34.129156566699123</v>
       </c>
       <c r="T379" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35483,7 +35484,7 @@
       </c>
       <c r="R380" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.408708550304048</v>
+        <v>13.007271868880865</v>
       </c>
       <c r="T380" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35540,7 +35541,7 @@
       </c>
       <c r="R381" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.806447854654463</v>
+        <v>13.320450089508999</v>
       </c>
       <c r="T381" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35603,7 +35604,7 @@
       </c>
       <c r="R382" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.905721991813904</v>
+        <v>12.929948839171004</v>
       </c>
       <c r="T382" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35661,7 +35662,7 @@
       </c>
       <c r="R383" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.123150973943829</v>
+        <v>20.023487068081376</v>
       </c>
       <c r="T383" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35718,7 +35719,7 @@
       </c>
       <c r="R384" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.44406755894333916</v>
+        <v>0.71848524063755947</v>
       </c>
       <c r="T384" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35775,7 +35776,7 @@
       </c>
       <c r="R385" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>34.08827892258347</v>
+        <v>33.831606813299082</v>
       </c>
       <c r="T385" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35835,7 +35836,7 @@
       </c>
       <c r="R386" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>10.655146163913152</v>
+        <v>10.722319985901175</v>
       </c>
       <c r="T386" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35892,7 +35893,7 @@
       </c>
       <c r="R387" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.134913562629192</v>
+        <v>12.84339484646982</v>
       </c>
       <c r="T387" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35950,7 +35951,7 @@
       </c>
       <c r="R388" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.596194452253126</v>
+        <v>20.539166099073352</v>
       </c>
       <c r="T388" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36007,7 +36008,7 @@
       </c>
       <c r="R389" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.42841535691716004</v>
+        <v>0.22203807551331911</v>
       </c>
       <c r="T389" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36064,7 +36065,7 @@
       </c>
       <c r="R390" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.1957230077637195</v>
+        <v>7.8967782057372231</v>
       </c>
       <c r="T390" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36121,7 +36122,7 @@
       </c>
       <c r="R391" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.50968713473945648</v>
+        <v>0.48193635058891948</v>
       </c>
       <c r="T391" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36179,7 +36180,7 @@
       </c>
       <c r="R392" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.77042372516898</v>
+        <v>13.293656339723217</v>
       </c>
       <c r="T392" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36236,7 +36237,7 @@
       </c>
       <c r="R393" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.2999490768257562</v>
+        <v>7.940663894680732</v>
       </c>
       <c r="T393" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36293,7 +36294,7 @@
       </c>
       <c r="R394" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.2416394866391656</v>
+        <v>7.8837554797856857</v>
       </c>
       <c r="T394" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36356,7 +36357,7 @@
       </c>
       <c r="R395" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.433641289355291</v>
+        <v>12.687241881684439</v>
       </c>
       <c r="T395" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36413,7 +36414,7 @@
       </c>
       <c r="R396" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.45009825345774901</v>
+        <v>0.97990346321524768</v>
       </c>
       <c r="T396" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36476,7 +36477,7 @@
       </c>
       <c r="R397" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.00054946532838</v>
+        <v>12.567750101349747</v>
       </c>
       <c r="T397" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36533,7 +36534,7 @@
       </c>
       <c r="R398" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.534342532067301</v>
+        <v>12.641016602817345</v>
       </c>
       <c r="T398" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36575,7 +36576,7 @@
         <v>960</v>
       </c>
       <c r="F399" s="2" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="G399" s="23" t="str">
         <f>テーブル1[[#This Row],[名前]]&amp;"(UTAU)"</f>
@@ -36600,7 +36601,7 @@
       </c>
       <c r="R399" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>16.678707433104144</v>
+        <v>17.382591251098642</v>
       </c>
       <c r="T399" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36658,7 +36659,7 @@
       </c>
       <c r="R400" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.96785705013653789</v>
+        <v>0.48422193699535687</v>
       </c>
       <c r="T400" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36700,7 +36701,7 @@
         <v>965</v>
       </c>
       <c r="F401" s="2" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="G401" s="23" t="str">
         <f>テーブル1[[#This Row],[名前]]&amp;"(UTAU)"</f>
@@ -36710,7 +36711,7 @@
         <v>1616</v>
       </c>
       <c r="I401" s="23" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="M401" s="23" t="s">
         <v>1662</v>
@@ -36728,7 +36729,7 @@
       </c>
       <c r="R401" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>16.995855585252915</v>
+        <v>16.790413078703722</v>
       </c>
       <c r="T401" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36785,7 +36786,7 @@
       </c>
       <c r="R402" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.748070999585495</v>
+        <v>13.006319827479661</v>
       </c>
       <c r="T402" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36827,7 +36828,7 @@
         <v>972</v>
       </c>
       <c r="F403" s="2" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="G403" s="23" t="str">
         <f>テーブル1[[#This Row],[名前]]&amp;"(UTAU)"</f>
@@ -36849,7 +36850,7 @@
       </c>
       <c r="R403" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>17.345036987636597</v>
+        <v>16.692438280889043</v>
       </c>
       <c r="T403" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36906,7 +36907,7 @@
       </c>
       <c r="R404" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>5.8102672778481579E-2</v>
+        <v>8.6042328722149675E-2</v>
       </c>
       <c r="T404" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36963,7 +36964,7 @@
       </c>
       <c r="R405" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.59198404423482498</v>
+        <v>0.60603753964549611</v>
       </c>
       <c r="T405" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37020,7 +37021,7 @@
       </c>
       <c r="R406" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.88707152952664459</v>
+        <v>0.9410527325411473</v>
       </c>
       <c r="T406" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37077,7 +37078,7 @@
       </c>
       <c r="R407" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.46634277459162343</v>
+        <v>0.99051240588486744</v>
       </c>
       <c r="T407" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37134,7 +37135,7 @@
       </c>
       <c r="R408" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.14739681258830695</v>
+        <v>0.41906235875663556</v>
       </c>
       <c r="T408" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37192,7 +37193,7 @@
       </c>
       <c r="R409" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.407602500171976</v>
+        <v>13.321215577058748</v>
       </c>
       <c r="T409" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37252,7 +37253,7 @@
       </c>
       <c r="R410" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.82935288460780687</v>
+        <v>0.59983054783317225</v>
       </c>
       <c r="T410" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37309,7 +37310,7 @@
       </c>
       <c r="R411" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.95256450448043284</v>
+        <v>0.32854058352294746</v>
       </c>
       <c r="T411" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37366,7 +37367,7 @@
       </c>
       <c r="R412" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>40.429966004872078</v>
+        <v>40.354371641622002</v>
       </c>
       <c r="T412" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37423,7 +37424,7 @@
       </c>
       <c r="R413" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.6638816273386929</v>
+        <v>7.8807072516560028</v>
       </c>
       <c r="T413" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37483,7 +37484,7 @@
       </c>
       <c r="R414" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>10.140283066650193</v>
+        <v>10.325201271024786</v>
       </c>
       <c r="T414" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37540,7 +37541,7 @@
       </c>
       <c r="R415" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>1.833153354773509E-2</v>
+        <v>1.4460289770275692E-2</v>
       </c>
       <c r="T415" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37601,7 +37602,7 @@
       </c>
       <c r="R416" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>9.8687590419422282</v>
+        <v>9.2860800638619683</v>
       </c>
       <c r="T416" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37662,7 +37663,7 @@
       </c>
       <c r="R417" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>9.2921597510708036</v>
+        <v>10.027974931023019</v>
       </c>
       <c r="T417" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37719,7 +37720,7 @@
       </c>
       <c r="R418" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.8690083413181764</v>
+        <v>7.8348385970419177</v>
       </c>
       <c r="T418" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37776,7 +37777,7 @@
       </c>
       <c r="R419" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.4862778555138165</v>
+        <v>7.9929900903917765</v>
       </c>
       <c r="T419" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37833,7 +37834,7 @@
       </c>
       <c r="R420" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.445168848901629</v>
+        <v>13.254940700969229</v>
       </c>
       <c r="T420" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37890,7 +37891,7 @@
       </c>
       <c r="R421" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>66.891349282059025</v>
+        <v>67.117624262807965</v>
       </c>
       <c r="T421" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37951,7 +37952,7 @@
       </c>
       <c r="R422" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>9.9667211572554368</v>
+        <v>9.9587929801546888</v>
       </c>
       <c r="T422" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38009,7 +38010,7 @@
       </c>
       <c r="R423" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.106606795105854</v>
+        <v>12.981481862555263</v>
       </c>
       <c r="T423" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38067,7 +38068,7 @@
       </c>
       <c r="R424" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.577170631102363</v>
+        <v>0.91564026841235835</v>
       </c>
       <c r="T424" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38128,7 +38129,7 @@
       </c>
       <c r="R425" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>9.2072792026253474</v>
+        <v>10.010314076179201</v>
       </c>
       <c r="T425" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38189,7 +38190,7 @@
       </c>
       <c r="R426" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>9.1287629144107179</v>
+        <v>9.5859379070242241</v>
       </c>
       <c r="T426" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38247,7 +38248,7 @@
       </c>
       <c r="R427" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.322864200948311</v>
+        <v>12.805564723149899</v>
       </c>
       <c r="T427" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38289,7 +38290,7 @@
         <v>966</v>
       </c>
       <c r="F428" s="2" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="G428" s="23" t="str">
         <f>テーブル1[[#This Row],[名前]]&amp;"(UTAU)"</f>
@@ -38299,10 +38300,10 @@
         <v>1616</v>
       </c>
       <c r="I428" s="23" t="s">
+        <v>1692</v>
+      </c>
+      <c r="M428" s="23" t="s">
         <v>1693</v>
-      </c>
-      <c r="M428" s="23" t="s">
-        <v>1694</v>
       </c>
       <c r="N428" s="1" t="s">
         <v>1508</v>
@@ -38317,7 +38318,7 @@
       </c>
       <c r="R428" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>16.940965011419674</v>
+        <v>16.951082278464305</v>
       </c>
       <c r="T428" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38377,7 +38378,7 @@
       </c>
       <c r="R429" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>10.823578151328906</v>
+        <v>10.97674513637573</v>
       </c>
       <c r="T429" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38434,7 +38435,7 @@
       </c>
       <c r="R430" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.10764949214159925</v>
+        <v>0.36620016555853097</v>
       </c>
       <c r="T430" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38491,7 +38492,7 @@
       </c>
       <c r="R431" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.832251763196769</v>
+        <v>12.825739518638885</v>
       </c>
       <c r="T431" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38548,7 +38549,7 @@
       </c>
       <c r="R432" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.41394215912497301</v>
+        <v>0.41442417875203297</v>
       </c>
       <c r="T432" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38606,7 +38607,7 @@
       </c>
       <c r="R433" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.400463795772107</v>
+        <v>0.79355560740344444</v>
       </c>
       <c r="T433" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38666,7 +38667,7 @@
       </c>
       <c r="R434" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.954465410239489</v>
+        <v>20.799968054228</v>
       </c>
       <c r="T434" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38726,7 +38727,7 @@
       </c>
       <c r="R435" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.559091536804843</v>
+        <v>20.096639940986261</v>
       </c>
       <c r="T435" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38786,7 +38787,7 @@
       </c>
       <c r="R436" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.387798994769291</v>
+        <v>20.461555145025876</v>
       </c>
       <c r="T436" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38846,7 +38847,7 @@
       </c>
       <c r="R437" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.411291307237249</v>
+        <v>20.834710862546256</v>
       </c>
       <c r="T437" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38906,7 +38907,7 @@
       </c>
       <c r="R438" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.285055207877694</v>
+        <v>20.813164877932881</v>
       </c>
       <c r="T438" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38966,7 +38967,7 @@
       </c>
       <c r="R439" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.386976880457301</v>
+        <v>20.414082692085724</v>
       </c>
       <c r="T439" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38999,19 +39000,19 @@
         <v>yashiro-shiya</v>
       </c>
       <c r="C440" s="24" t="s">
+        <v>1718</v>
+      </c>
+      <c r="D440" s="23" t="s">
         <v>1719</v>
       </c>
-      <c r="D440" s="23" t="s">
-        <v>1720</v>
-      </c>
       <c r="E440" s="23" t="s">
-        <v>1718</v>
+        <v>1717</v>
       </c>
       <c r="F440" s="29" t="s">
+        <v>1705</v>
+      </c>
+      <c r="G440" s="23" t="s">
         <v>1706</v>
-      </c>
-      <c r="G440" s="23" t="s">
-        <v>1707</v>
       </c>
       <c r="H440" s="23" t="s">
         <v>1616</v>
@@ -39020,13 +39021,13 @@
         <v>1639</v>
       </c>
       <c r="K440" s="23" t="s">
-        <v>1724</v>
+        <v>1723</v>
       </c>
       <c r="L440" s="23" t="s">
+        <v>1720</v>
+      </c>
+      <c r="M440" s="23" t="s">
         <v>1721</v>
-      </c>
-      <c r="M440" s="23" t="s">
-        <v>1722</v>
       </c>
       <c r="N440" s="1" t="s">
         <v>1579</v>
@@ -39041,7 +39042,7 @@
       </c>
       <c r="R440" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>34.053836194956567</v>
+        <v>33.64386208428062</v>
       </c>
       <c r="T440" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -39074,19 +39075,19 @@
         <v>katazu-taka</v>
       </c>
       <c r="C441" s="24" t="s">
+        <v>1724</v>
+      </c>
+      <c r="D441" s="23" t="s">
         <v>1725</v>
       </c>
-      <c r="D441" s="23" t="s">
+      <c r="E441" s="23" t="s">
         <v>1726</v>
       </c>
-      <c r="E441" s="23" t="s">
-        <v>1727</v>
-      </c>
       <c r="F441" s="29" t="s">
+        <v>1705</v>
+      </c>
+      <c r="G441" s="23" t="s">
         <v>1706</v>
-      </c>
-      <c r="G441" s="23" t="s">
-        <v>1707</v>
       </c>
       <c r="H441" s="23" t="s">
         <v>1617</v>
@@ -39095,7 +39096,7 @@
         <v>1639</v>
       </c>
       <c r="M441" s="23" t="s">
-        <v>1722</v>
+        <v>1721</v>
       </c>
       <c r="N441" s="1" t="s">
         <v>1579</v>
@@ -39110,7 +39111,7 @@
       </c>
       <c r="R441" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.657005066724992</v>
+        <v>33.885305419949233</v>
       </c>
       <c r="T441" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -39517,10 +39518,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="31" t="s">
         <v>711</v>
       </c>
-      <c r="C2" s="30"/>
+      <c r="C2" s="31"/>
     </row>
     <row r="4" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="4" t="s">
@@ -39528,7 +39529,7 @@
       </c>
       <c r="C4" s="7">
         <f ca="1">MATCH(C5,キャラ情報!C:C,0)</f>
-        <v>237</v>
+        <v>415</v>
       </c>
     </row>
     <row r="5" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -39537,7 +39538,7 @@
       </c>
       <c r="C5" s="6" t="str">
         <f ca="1">INDEX(キャラ情報!C:R,MATCH(MIN(キャラ情報!R:R),キャラ情報!R:R,0),1)</f>
-        <v>旭橋渚</v>
+        <v>夜打キーボ</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -39546,14 +39547,14 @@
       </c>
       <c r="C6" s="6" t="str">
         <f ca="1">INDEX(キャラ情報!C:R,MATCH(MIN(キャラ情報!R:R),キャラ情報!R:R,0),4)</f>
-        <v>https://coyukimachi.wixsite.com/my-site</v>
+        <v>https://alceaakaza.wixsite.com/artkashic-uni-verse</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="30" t="s">
+      <c r="B9" s="31" t="s">
         <v>769</v>
       </c>
-      <c r="C9" s="30"/>
+      <c r="C9" s="31"/>
     </row>
     <row r="11" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="4" t="s">
@@ -39617,7 +39618,7 @@
     </row>
     <row r="21" spans="2:3" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B21" s="13" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
       <c r="C21" s="14"/>
     </row>
@@ -39682,7 +39683,7 @@
         <v>1619</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>1761</v>
+        <v>1760</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>1620</v>
@@ -45087,11 +45088,11 @@
       </c>
       <c r="L101" s="19" t="str">
         <f>テーブル1[[#This Row],[小物タグ]]&amp;""</f>
-        <v>髪飾り</v>
+        <v>カチューシャ|髪飾り</v>
       </c>
       <c r="M101" s="19" t="str">
         <f>テーブル1[[#This Row],[ワンポイントタグ]]&amp;""</f>
-        <v>ケモ耳</v>
+        <v/>
       </c>
     </row>
     <row r="102" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">

--- a/data/characters.xlsx
+++ b/data/characters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\モノクロビリーフ\外部リンク\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36F37BE7-6C22-4689-BFD4-58EAF1B8BFE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB811F6E-7934-4226-AB52-18E71157BFAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{78CF6334-6F78-4A6F-BD14-CB6FA7AB00CF}"/>
   </bookViews>
@@ -7427,9 +7427,6 @@
   </si>
   <si>
     <t>ヘアピン|眼鏡</t>
-  </si>
-  <si>
-    <t>ヘアピン|眼鏡</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -7987,6 +7984,16 @@
     <t>カチューシャ|髪飾り</t>
     <rPh sb="7" eb="9">
       <t>カミカザ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>宇宙人|元ヤン</t>
+    <rPh sb="0" eb="3">
+      <t>ウチュウジン</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>モト</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -10319,7 +10326,7 @@
         <v>1757</v>
       </c>
       <c r="L6" s="23" t="s">
-        <v>1832</v>
+        <v>1831</v>
       </c>
       <c r="M6" s="23" t="s">
         <v>1647</v>
@@ -11786,7 +11793,7 @@
         <v>1644</v>
       </c>
       <c r="L25" s="23" t="s">
-        <v>1773</v>
+        <v>1772</v>
       </c>
       <c r="M25" s="23" t="s">
         <v>1662</v>
@@ -11867,10 +11874,10 @@
         <v>1626</v>
       </c>
       <c r="K26" s="23" t="s">
+        <v>1778</v>
+      </c>
+      <c r="M26" s="23" t="s">
         <v>1779</v>
-      </c>
-      <c r="M26" s="23" t="s">
-        <v>1780</v>
       </c>
       <c r="N26" s="1" t="s">
         <v>1579</v>
@@ -11948,10 +11955,10 @@
         <v>1626</v>
       </c>
       <c r="K27" s="23" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="M27" s="23" t="s">
-        <v>1782</v>
+        <v>1781</v>
       </c>
       <c r="N27" s="1" t="s">
         <v>1579</v>
@@ -12014,10 +12021,10 @@
         <v>62</v>
       </c>
       <c r="E28" s="23" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
       <c r="F28" s="15" t="s">
-        <v>1783</v>
+        <v>1782</v>
       </c>
       <c r="G28" s="23" t="s">
         <v>63</v>
@@ -12029,10 +12036,10 @@
         <v>1626</v>
       </c>
       <c r="J28" s="23" t="s">
-        <v>1786</v>
+        <v>1785</v>
       </c>
       <c r="K28" s="23" t="s">
-        <v>1785</v>
+        <v>1784</v>
       </c>
       <c r="N28" s="1" t="s">
         <v>1507</v>
@@ -12182,7 +12189,7 @@
         <v>1626</v>
       </c>
       <c r="L30" s="23" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="O30" s="1" t="s">
         <v>1433</v>
@@ -12410,16 +12417,16 @@
         <v>1617</v>
       </c>
       <c r="I33" s="23" t="s">
+        <v>1800</v>
+      </c>
+      <c r="K33" s="23" t="s">
         <v>1801</v>
       </c>
-      <c r="K33" s="23" t="s">
+      <c r="L33" s="23" t="s">
         <v>1802</v>
       </c>
-      <c r="L33" s="23" t="s">
+      <c r="M33" s="23" t="s">
         <v>1803</v>
-      </c>
-      <c r="M33" s="23" t="s">
-        <v>1804</v>
       </c>
       <c r="N33" s="1" t="s">
         <v>1579</v>
@@ -12482,10 +12489,10 @@
         <v>65</v>
       </c>
       <c r="E34" s="23" t="s">
-        <v>1787</v>
+        <v>1786</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>1783</v>
+        <v>1782</v>
       </c>
       <c r="G34" s="23" t="s">
         <v>63</v>
@@ -12497,10 +12504,10 @@
         <v>1626</v>
       </c>
       <c r="L34" s="23" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="M34" s="23" t="s">
-        <v>1814</v>
+        <v>1813</v>
       </c>
       <c r="N34" s="1" t="s">
         <v>1507</v>
@@ -12578,10 +12585,10 @@
         <v>1675</v>
       </c>
       <c r="K35" s="23" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="L35" s="23" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="M35" s="23" t="s">
         <v>1650</v>
@@ -12656,16 +12663,16 @@
         <v>1617</v>
       </c>
       <c r="I36" s="23" t="s">
-        <v>1774</v>
+        <v>1856</v>
       </c>
       <c r="K36" s="23" t="s">
-        <v>1805</v>
+        <v>1804</v>
       </c>
       <c r="L36" s="23" t="s">
         <v>1772</v>
       </c>
       <c r="M36" s="23" t="s">
-        <v>1806</v>
+        <v>1805</v>
       </c>
       <c r="N36" s="1" t="s">
         <v>1579</v>
@@ -12743,7 +12750,7 @@
         <v>1626</v>
       </c>
       <c r="K37" s="23" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
       <c r="L37" s="23" t="s">
         <v>1751</v>
@@ -12824,10 +12831,10 @@
         <v>1644</v>
       </c>
       <c r="K38" s="23" t="s">
+        <v>1814</v>
+      </c>
+      <c r="M38" s="23" t="s">
         <v>1815</v>
-      </c>
-      <c r="M38" s="23" t="s">
-        <v>1816</v>
       </c>
       <c r="N38" s="1" t="s">
         <v>1579</v>
@@ -12977,7 +12984,7 @@
         <v>1626</v>
       </c>
       <c r="K40" s="23" t="s">
-        <v>1809</v>
+        <v>1808</v>
       </c>
       <c r="N40" s="1" t="s">
         <v>1508</v>
@@ -13280,13 +13287,13 @@
         <v>1617</v>
       </c>
       <c r="I44" s="23" t="s">
-        <v>1829</v>
+        <v>1828</v>
       </c>
       <c r="J44" s="23" t="s">
-        <v>1828</v>
+        <v>1827</v>
       </c>
       <c r="M44" s="23" t="s">
-        <v>1827</v>
+        <v>1826</v>
       </c>
       <c r="N44" s="1" t="s">
         <v>1508</v>
@@ -13364,7 +13371,7 @@
         <v>1626</v>
       </c>
       <c r="K45" s="23" t="s">
-        <v>1809</v>
+        <v>1808</v>
       </c>
       <c r="L45" s="23" t="s">
         <v>1646</v>
@@ -13442,10 +13449,10 @@
         <v>1626</v>
       </c>
       <c r="K46" s="23" t="s">
+        <v>1843</v>
+      </c>
+      <c r="L46" s="23" t="s">
         <v>1844</v>
-      </c>
-      <c r="L46" s="23" t="s">
-        <v>1845</v>
       </c>
       <c r="N46" s="1" t="s">
         <v>1507</v>
@@ -13586,13 +13593,13 @@
         <v>1616</v>
       </c>
       <c r="I48" s="23" t="s">
-        <v>1817</v>
+        <v>1816</v>
       </c>
       <c r="L48" s="23" t="s">
         <v>1767</v>
       </c>
       <c r="M48" s="23" t="s">
-        <v>1818</v>
+        <v>1817</v>
       </c>
       <c r="N48" s="1" t="s">
         <v>1579</v>
@@ -13934,7 +13941,7 @@
         <v>1644</v>
       </c>
       <c r="K53" s="23" t="s">
-        <v>1811</v>
+        <v>1810</v>
       </c>
       <c r="N53" s="1" t="s">
         <v>1579</v>
@@ -14084,7 +14091,7 @@
       <c r="K55" s="28"/>
       <c r="L55" s="28"/>
       <c r="M55" s="28" t="s">
-        <v>1826</v>
+        <v>1825</v>
       </c>
       <c r="N55" s="1" t="s">
         <v>1579</v>
@@ -14495,10 +14502,10 @@
         <v>1617</v>
       </c>
       <c r="I61" s="23" t="s">
+        <v>1822</v>
+      </c>
+      <c r="J61" s="23" t="s">
         <v>1823</v>
-      </c>
-      <c r="J61" s="23" t="s">
-        <v>1824</v>
       </c>
       <c r="N61" s="1" t="s">
         <v>1508</v>
@@ -14855,7 +14862,7 @@
         <v>1670</v>
       </c>
       <c r="M66" s="23" t="s">
-        <v>1830</v>
+        <v>1829</v>
       </c>
       <c r="N66" s="1" t="s">
         <v>1508</v>
@@ -15812,7 +15819,7 @@
         <v>1762</v>
       </c>
       <c r="J80" s="23" t="s">
-        <v>1825</v>
+        <v>1824</v>
       </c>
       <c r="L80" s="23" t="s">
         <v>1658</v>
@@ -15959,13 +15966,13 @@
         <v>1653</v>
       </c>
       <c r="I82" s="23" t="s">
-        <v>1774</v>
+        <v>1773</v>
       </c>
       <c r="J82" s="23" t="s">
+        <v>1806</v>
+      </c>
+      <c r="M82" s="23" t="s">
         <v>1807</v>
-      </c>
-      <c r="M82" s="23" t="s">
-        <v>1808</v>
       </c>
       <c r="N82" s="1" t="s">
         <v>1579</v>
@@ -16608,10 +16615,10 @@
         <v>1616</v>
       </c>
       <c r="I91" s="23" t="s">
-        <v>1774</v>
+        <v>1773</v>
       </c>
       <c r="K91" s="23" t="s">
-        <v>1809</v>
+        <v>1808</v>
       </c>
       <c r="L91" s="23" t="s">
         <v>1687</v>
@@ -16689,10 +16696,10 @@
         <v>1616</v>
       </c>
       <c r="I92" s="23" t="s">
-        <v>1774</v>
+        <v>1773</v>
       </c>
       <c r="K92" s="23" t="s">
-        <v>1805</v>
+        <v>1804</v>
       </c>
       <c r="L92" s="23" t="s">
         <v>1751</v>
@@ -16842,7 +16849,7 @@
         <v>1626</v>
       </c>
       <c r="K94" s="23" t="s">
-        <v>1809</v>
+        <v>1808</v>
       </c>
       <c r="N94" s="1" t="s">
         <v>1508</v>
@@ -17058,10 +17065,10 @@
         <v>1626</v>
       </c>
       <c r="K97" s="23" t="s">
+        <v>1818</v>
+      </c>
+      <c r="M97" s="23" t="s">
         <v>1819</v>
-      </c>
-      <c r="M97" s="23" t="s">
-        <v>1820</v>
       </c>
       <c r="N97" s="1" t="s">
         <v>1579</v>
@@ -17205,7 +17212,7 @@
         <v>1626</v>
       </c>
       <c r="M99" s="23" t="s">
-        <v>1842</v>
+        <v>1841</v>
       </c>
       <c r="O99" s="1" t="s">
         <v>1433</v>
@@ -17277,10 +17284,10 @@
         <v>1653</v>
       </c>
       <c r="I100" s="23" t="s">
-        <v>1798</v>
+        <v>1797</v>
       </c>
       <c r="K100" s="23" t="s">
-        <v>1843</v>
+        <v>1842</v>
       </c>
       <c r="O100" s="1" t="s">
         <v>1433</v>
@@ -17358,10 +17365,10 @@
         <v>1766</v>
       </c>
       <c r="K101" s="23" t="s">
-        <v>1791</v>
+        <v>1790</v>
       </c>
       <c r="L101" s="23" t="s">
-        <v>1856</v>
+        <v>1855</v>
       </c>
       <c r="O101" s="1" t="s">
         <v>1433</v>
@@ -17793,10 +17800,10 @@
         <v>1616</v>
       </c>
       <c r="I107" s="23" t="s">
+        <v>1820</v>
+      </c>
+      <c r="K107" s="23" t="s">
         <v>1821</v>
-      </c>
-      <c r="K107" s="23" t="s">
-        <v>1822</v>
       </c>
       <c r="L107" s="23" t="s">
         <v>1769</v>
@@ -18024,7 +18031,7 @@
         <v>1617</v>
       </c>
       <c r="M110" s="23" t="s">
-        <v>1781</v>
+        <v>1780</v>
       </c>
       <c r="N110" s="1" t="s">
         <v>1579</v>
@@ -19438,7 +19445,7 @@
         <v>1626</v>
       </c>
       <c r="L130" s="23" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="O130" s="1" t="s">
         <v>1433</v>
@@ -20387,10 +20394,10 @@
         <v>1005</v>
       </c>
       <c r="E144" s="23" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>1783</v>
+        <v>1782</v>
       </c>
       <c r="G144" s="23" t="s">
         <v>63</v>
@@ -20399,13 +20406,13 @@
         <v>1616</v>
       </c>
       <c r="I144" s="23" t="s">
-        <v>1794</v>
+        <v>1793</v>
       </c>
       <c r="K144" s="23" t="s">
-        <v>1791</v>
+        <v>1790</v>
       </c>
       <c r="L144" s="23" t="s">
-        <v>1790</v>
+        <v>1789</v>
       </c>
       <c r="N144" s="1" t="s">
         <v>1507</v>
@@ -21237,7 +21244,7 @@
         <v>1616</v>
       </c>
       <c r="I156" s="23" t="s">
-        <v>1798</v>
+        <v>1797</v>
       </c>
       <c r="O156" s="1" t="s">
         <v>1433</v>
@@ -21381,10 +21388,10 @@
         <v>1644</v>
       </c>
       <c r="J158" s="23" t="s">
-        <v>1810</v>
+        <v>1809</v>
       </c>
       <c r="K158" s="23" t="s">
-        <v>1812</v>
+        <v>1811</v>
       </c>
       <c r="M158" s="23" t="s">
         <v>1683</v>
@@ -23851,13 +23858,13 @@
         <v>1616</v>
       </c>
       <c r="I194" s="23" t="s">
+        <v>1773</v>
+      </c>
+      <c r="J194" s="23" t="s">
         <v>1774</v>
       </c>
-      <c r="J194" s="23" t="s">
+      <c r="M194" s="23" t="s">
         <v>1775</v>
-      </c>
-      <c r="M194" s="23" t="s">
-        <v>1776</v>
       </c>
       <c r="N194" s="1" t="s">
         <v>1579</v>
@@ -25162,7 +25169,7 @@
         <v>1714</v>
       </c>
       <c r="M213" s="23" t="s">
-        <v>1836</v>
+        <v>1835</v>
       </c>
       <c r="N213" s="1" t="s">
         <v>1508</v>
@@ -26730,7 +26737,7 @@
       </c>
       <c r="R234" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>50.089153120370995</v>
+        <v>50.552913621291133</v>
       </c>
       <c r="T234" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -26799,7 +26806,7 @@
       </c>
       <c r="R235" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>60.330091045217493</v>
+        <v>60.402813108569028</v>
       </c>
       <c r="T235" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -26865,7 +26872,7 @@
       </c>
       <c r="R236" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>60.027184846758495</v>
+        <v>60.968015658377475</v>
       </c>
       <c r="T236" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -26925,7 +26932,7 @@
       </c>
       <c r="R237" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.98048526512834555</v>
+        <v>0.39552556354662671</v>
       </c>
       <c r="T237" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -26985,7 +26992,7 @@
       </c>
       <c r="R238" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>34.31195702997865</v>
+        <v>33.66336703481106</v>
       </c>
       <c r="T238" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27045,7 +27052,7 @@
       </c>
       <c r="R239" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>34.099315097180373</v>
+        <v>33.60921860705745</v>
       </c>
       <c r="T239" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27102,7 +27109,7 @@
       </c>
       <c r="R240" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.761743919833039</v>
+        <v>13.245154986828336</v>
       </c>
       <c r="T240" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27162,7 +27169,7 @@
       </c>
       <c r="R241" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>10.550067058402242</v>
+        <v>10.126997179496831</v>
       </c>
       <c r="T241" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27222,7 +27229,7 @@
       </c>
       <c r="R242" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.474251742334072</v>
+        <v>20.812323225489411</v>
       </c>
       <c r="T242" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27285,7 +27292,7 @@
       </c>
       <c r="R243" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.024335115177962</v>
+        <v>13.327806680642416</v>
       </c>
       <c r="T243" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27342,7 +27349,7 @@
       </c>
       <c r="R244" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.683984430219224</v>
+        <v>12.560909885232968</v>
       </c>
       <c r="T244" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27402,7 +27409,7 @@
       </c>
       <c r="R245" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>10.451690819462611</v>
+        <v>10.242299010465052</v>
       </c>
       <c r="T245" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27435,13 +27442,13 @@
         <v>amaze-maze-noisette</v>
       </c>
       <c r="C246" s="24" t="s">
+        <v>1845</v>
+      </c>
+      <c r="D246" s="23" t="s">
         <v>1846</v>
       </c>
-      <c r="D246" s="23" t="s">
+      <c r="E246" s="23" t="s">
         <v>1847</v>
-      </c>
-      <c r="E246" s="23" t="s">
-        <v>1848</v>
       </c>
       <c r="F246" s="2" t="s">
         <v>97</v>
@@ -27453,10 +27460,10 @@
         <v>1616</v>
       </c>
       <c r="I246" s="23" t="s">
+        <v>1848</v>
+      </c>
+      <c r="L246" s="23" t="s">
         <v>1849</v>
-      </c>
-      <c r="L246" s="23" t="s">
-        <v>1850</v>
       </c>
       <c r="M246" s="23" t="s">
         <v>1647</v>
@@ -27474,7 +27481,7 @@
       </c>
       <c r="R246" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.421608034398052</v>
+        <v>20.748689690141422</v>
       </c>
       <c r="T246" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27534,7 +27541,7 @@
       </c>
       <c r="R247" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.965204798302</v>
+        <v>20.312465263679332</v>
       </c>
       <c r="T247" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27594,7 +27601,7 @@
       </c>
       <c r="R248" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.467900289962561</v>
+        <v>20.630312514845372</v>
       </c>
       <c r="T248" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27654,7 +27661,7 @@
       </c>
       <c r="R249" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.780047932139269</v>
+        <v>20.925028274766838</v>
       </c>
       <c r="T249" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27714,7 +27721,7 @@
       </c>
       <c r="R250" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.10582401367882</v>
+        <v>20.756490045431836</v>
       </c>
       <c r="T250" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27774,7 +27781,7 @@
       </c>
       <c r="R251" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.04896632197838</v>
+        <v>20.1204754558348</v>
       </c>
       <c r="T251" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27834,7 +27841,7 @@
       </c>
       <c r="R252" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.574871027300606</v>
+        <v>20.103259412861302</v>
       </c>
       <c r="T252" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27894,7 +27901,7 @@
       </c>
       <c r="R253" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.571751412021015</v>
+        <v>20.243691632763419</v>
       </c>
       <c r="T253" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27954,7 +27961,7 @@
       </c>
       <c r="R254" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.748001814644748</v>
+        <v>20.775900414294195</v>
       </c>
       <c r="T254" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28014,7 +28021,7 @@
       </c>
       <c r="R255" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.922035014366429</v>
+        <v>20.287849837340566</v>
       </c>
       <c r="T255" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28074,7 +28081,7 @@
       </c>
       <c r="R256" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.599556995715524</v>
+        <v>20.099328250172075</v>
       </c>
       <c r="T256" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28134,7 +28141,7 @@
       </c>
       <c r="R257" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.595808366214612</v>
+        <v>20.897752230737169</v>
       </c>
       <c r="T257" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28192,7 +28199,7 @@
       </c>
       <c r="R258" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.043983828965118</v>
+        <v>13.234664146887873</v>
       </c>
       <c r="T258" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28249,7 +28256,7 @@
       </c>
       <c r="R259" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>40.052905858898534</v>
+        <v>40.196835479839663</v>
       </c>
       <c r="T259" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28306,7 +28313,7 @@
       </c>
       <c r="R260" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.6490050880459961</v>
+        <v>7.9675738893789934</v>
       </c>
       <c r="T260" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28363,7 +28370,7 @@
       </c>
       <c r="R261" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>50.950969087882235</v>
+        <v>50.346688475517915</v>
       </c>
       <c r="T261" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28420,7 +28427,7 @@
       </c>
       <c r="R262" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.5579253026449692</v>
+        <v>0.21030080927563877</v>
       </c>
       <c r="T262" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28477,7 +28484,7 @@
       </c>
       <c r="R263" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.82538949944544138</v>
+        <v>0.629002670174583</v>
       </c>
       <c r="T263" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28534,7 +28541,7 @@
       </c>
       <c r="R264" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.5974610838840038</v>
+        <v>7.2123264259286275</v>
       </c>
       <c r="T264" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28595,7 +28602,7 @@
       </c>
       <c r="R265" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>50.93669511380233</v>
+        <v>50.376689683291453</v>
       </c>
       <c r="T265" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28652,7 +28659,7 @@
       </c>
       <c r="R266" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>34.330557926902635</v>
+        <v>33.528115116173915</v>
       </c>
       <c r="T266" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28709,7 +28716,7 @@
       </c>
       <c r="R267" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.4186539934119526</v>
+        <v>8.0433284277432922</v>
       </c>
       <c r="T267" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28766,7 +28773,7 @@
       </c>
       <c r="R268" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.491400077144949</v>
+        <v>13.1772796438381</v>
       </c>
       <c r="T268" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28823,7 +28830,7 @@
       </c>
       <c r="R269" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.960013942845334</v>
+        <v>13.487186373049706</v>
       </c>
       <c r="T269" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28880,7 +28887,7 @@
       </c>
       <c r="R270" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.834105390773347</v>
+        <v>13.267790869830005</v>
       </c>
       <c r="T270" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28934,7 +28941,7 @@
         <v>1639</v>
       </c>
       <c r="K271" s="23" t="s">
-        <v>1777</v>
+        <v>1776</v>
       </c>
       <c r="L271" s="23" t="s">
         <v>1627</v>
@@ -28955,7 +28962,7 @@
       </c>
       <c r="R271" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>75.595820454174387</v>
+        <v>75.721983509252226</v>
       </c>
       <c r="T271" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29012,7 +29019,7 @@
       </c>
       <c r="R272" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.152660136648874</v>
+        <v>13.051961250828407</v>
       </c>
       <c r="T272" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29069,7 +29076,7 @@
       </c>
       <c r="R273" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.672954924772798</v>
+        <v>12.529081502755949</v>
       </c>
       <c r="T273" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29126,7 +29133,7 @@
       </c>
       <c r="R274" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.89907718569464834</v>
+        <v>5.6057531756342205E-2</v>
       </c>
       <c r="T274" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29183,7 +29190,7 @@
       </c>
       <c r="R275" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>34.267459388912961</v>
+        <v>33.380013598676669</v>
       </c>
       <c r="T275" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29240,7 +29247,7 @@
       </c>
       <c r="R276" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.739408592099652</v>
+        <v>13.329664348728601</v>
       </c>
       <c r="T276" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29297,7 +29304,7 @@
       </c>
       <c r="R277" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.696707215771362</v>
+        <v>13.130746769918915</v>
       </c>
       <c r="T277" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29357,7 +29364,7 @@
       </c>
       <c r="R278" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>50.632774771261239</v>
+        <v>50.699741481947925</v>
       </c>
       <c r="T278" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29414,7 +29421,7 @@
       </c>
       <c r="R279" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.34751940217963073</v>
+        <v>5.360178745198485E-2</v>
       </c>
       <c r="T279" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29471,7 +29478,7 @@
       </c>
       <c r="R280" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.5788920569471141</v>
+        <v>0.17107243499880742</v>
       </c>
       <c r="T280" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29532,7 +29539,7 @@
       </c>
       <c r="R281" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>9.6884706201781405</v>
+        <v>9.8728282759867376</v>
       </c>
       <c r="T281" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29601,7 +29608,7 @@
       </c>
       <c r="R282" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>57.44276208034546</v>
+        <v>57.377782422752126</v>
       </c>
       <c r="T282" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29659,7 +29666,7 @@
       </c>
       <c r="R283" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.996865336766909</v>
+        <v>20.559289248530899</v>
       </c>
       <c r="T283" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29716,7 +29723,7 @@
       </c>
       <c r="R284" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.83706565885490081</v>
+        <v>7.7638656517664884E-2</v>
       </c>
       <c r="T284" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29776,7 +29783,7 @@
       </c>
       <c r="R285" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>10.395369024971581</v>
+        <v>10.311187287369959</v>
       </c>
       <c r="T285" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29845,7 +29852,7 @@
       </c>
       <c r="R286" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>80.902351917133416</v>
+        <v>80.030501033546173</v>
       </c>
       <c r="T286" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29902,7 +29909,7 @@
       </c>
       <c r="R287" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.5029649281983337</v>
+        <v>7.8939341122425608</v>
       </c>
       <c r="T287" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29959,7 +29966,7 @@
       </c>
       <c r="R288" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.586966605222065</v>
+        <v>12.695541596904006</v>
       </c>
       <c r="T288" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30019,7 +30026,7 @@
       </c>
       <c r="R289" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>9.3603950433407093</v>
+        <v>9.9925574525767615</v>
       </c>
       <c r="T289" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30076,7 +30083,7 @@
       </c>
       <c r="R290" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.78246597586283506</v>
+        <v>0.90599553999182336</v>
       </c>
       <c r="T290" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30145,7 +30152,7 @@
       </c>
       <c r="R291" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>57.987747829064062</v>
+        <v>58.127581232765941</v>
       </c>
       <c r="T291" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30202,7 +30209,7 @@
       </c>
       <c r="R292" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.197329068554174</v>
+        <v>12.969523288790638</v>
       </c>
       <c r="T292" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30262,7 +30269,7 @@
       </c>
       <c r="R293" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>23.169028889890495</v>
+        <v>22.450867940223741</v>
       </c>
       <c r="T293" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30304,7 +30311,7 @@
         <v>1004</v>
       </c>
       <c r="F294" s="2" t="s">
-        <v>1783</v>
+        <v>1782</v>
       </c>
       <c r="G294" s="23" t="s">
         <v>63</v>
@@ -30316,10 +30323,10 @@
         <v>1626</v>
       </c>
       <c r="J294" s="23" t="s">
+        <v>1791</v>
+      </c>
+      <c r="M294" s="23" t="s">
         <v>1792</v>
-      </c>
-      <c r="M294" s="23" t="s">
-        <v>1793</v>
       </c>
       <c r="N294" s="1" t="s">
         <v>1507</v>
@@ -30334,7 +30341,7 @@
       </c>
       <c r="R294" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>60.322105228669038</v>
+        <v>60.566084464746268</v>
       </c>
       <c r="T294" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30391,7 +30398,7 @@
       </c>
       <c r="R295" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.94331296531349063</v>
+        <v>0.15310427620615163</v>
       </c>
       <c r="T295" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30448,7 +30455,7 @@
       </c>
       <c r="R296" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>50.814522399768336</v>
+        <v>50.463161250071167</v>
       </c>
       <c r="T296" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30508,7 +30515,7 @@
       </c>
       <c r="R297" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>10.93246802480383</v>
+        <v>10.407553947719427</v>
       </c>
       <c r="T297" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30565,7 +30572,7 @@
       </c>
       <c r="R298" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.72890066594459579</v>
+        <v>0.83002782383675511</v>
       </c>
       <c r="T298" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30625,7 +30632,7 @@
       </c>
       <c r="R299" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.58028924173365848</v>
+        <v>3.5701552353442634E-2</v>
       </c>
       <c r="T299" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30691,7 +30698,7 @@
       </c>
       <c r="R300" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>57.352557766851085</v>
+        <v>58.026645394534448</v>
       </c>
       <c r="T300" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30748,7 +30755,7 @@
       </c>
       <c r="R301" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.21109723212857123</v>
+        <v>0.50414486457717655</v>
       </c>
       <c r="T301" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30805,7 +30812,7 @@
       </c>
       <c r="R302" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.8209101625814661</v>
+        <v>0.32785475197966762</v>
       </c>
       <c r="T302" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30862,7 +30869,7 @@
       </c>
       <c r="R303" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.60593645335335999</v>
+        <v>0.76651477364161213</v>
       </c>
       <c r="T303" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30919,7 +30926,7 @@
       </c>
       <c r="R304" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.70595167402415737</v>
+        <v>0.37022795091357774</v>
       </c>
       <c r="T304" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30970,16 +30977,16 @@
         <v>1616</v>
       </c>
       <c r="I305" s="23" t="s">
+        <v>1830</v>
+      </c>
+      <c r="J305" s="23" t="s">
+        <v>1827</v>
+      </c>
+      <c r="L305" s="23" t="s">
         <v>1831</v>
       </c>
-      <c r="J305" s="23" t="s">
-        <v>1828</v>
-      </c>
-      <c r="L305" s="23" t="s">
+      <c r="M305" s="23" t="s">
         <v>1832</v>
-      </c>
-      <c r="M305" s="23" t="s">
-        <v>1833</v>
       </c>
       <c r="N305" s="1" t="s">
         <v>1508</v>
@@ -30994,7 +31001,7 @@
       </c>
       <c r="R305" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>34.108683262236561</v>
+        <v>33.539446470292752</v>
       </c>
       <c r="T305" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31060,7 +31067,7 @@
       </c>
       <c r="R306" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.706149365933992</v>
+        <v>20.633153909045792</v>
       </c>
       <c r="T306" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31117,7 +31124,7 @@
       </c>
       <c r="R307" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.23896249770403255</v>
+        <v>0.61158431798872814</v>
       </c>
       <c r="T307" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31174,7 +31181,7 @@
       </c>
       <c r="R308" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>34.211771684720283</v>
+        <v>33.917388133772512</v>
       </c>
       <c r="T308" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31231,7 +31238,7 @@
       </c>
       <c r="R309" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>34.303608897108852</v>
+        <v>33.97849691559491</v>
       </c>
       <c r="T309" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31292,7 +31299,7 @@
       </c>
       <c r="R310" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>9.472378963312611</v>
+        <v>9.6656132468522333</v>
       </c>
       <c r="T310" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31350,7 +31357,7 @@
       </c>
       <c r="R311" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.4727727956777491</v>
+        <v>0.77344123142107268</v>
       </c>
       <c r="T311" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31413,7 +31420,7 @@
       </c>
       <c r="R312" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.785258495811139</v>
+        <v>12.65030842391497</v>
       </c>
       <c r="T312" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31470,7 +31477,7 @@
       </c>
       <c r="R313" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.20231242076793021</v>
+        <v>0.69260530271836462</v>
       </c>
       <c r="T313" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31527,7 +31534,7 @@
       </c>
       <c r="R314" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.11587023326012325</v>
+        <v>0.70659036722320723</v>
       </c>
       <c r="T314" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31584,7 +31591,7 @@
       </c>
       <c r="R315" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.972242728570553</v>
+        <v>12.756786195796129</v>
       </c>
       <c r="T315" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31642,7 +31649,7 @@
       </c>
       <c r="R316" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.78260853422500321</v>
+        <v>0.49431596327136662</v>
       </c>
       <c r="T316" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31700,7 +31707,7 @@
       </c>
       <c r="R317" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.91417665634403722</v>
+        <v>0.40703501209495507</v>
       </c>
       <c r="T317" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31758,7 +31765,7 @@
       </c>
       <c r="R318" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.80790809751240544</v>
+        <v>0.52175077045249063</v>
       </c>
       <c r="T318" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31816,7 +31823,7 @@
       </c>
       <c r="R319" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.2005439882899569</v>
+        <v>0.58617130399375317</v>
       </c>
       <c r="T319" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31874,7 +31881,7 @@
       </c>
       <c r="R320" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.37598321138777246</v>
+        <v>0.86984981735912625</v>
       </c>
       <c r="T320" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31932,7 +31939,7 @@
       </c>
       <c r="R321" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>34.014923571995205</v>
+        <v>33.367701180690887</v>
       </c>
       <c r="T321" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31992,7 +31999,7 @@
       </c>
       <c r="R322" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>22.245388174831</v>
+        <v>22.592622957253322</v>
       </c>
       <c r="T322" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32052,7 +32059,7 @@
       </c>
       <c r="R323" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>22.353516731173702</v>
+        <v>23.162079200192995</v>
       </c>
       <c r="T323" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32109,7 +32116,7 @@
       </c>
       <c r="R324" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.97226262663676422</v>
+        <v>0.66867176467973799</v>
       </c>
       <c r="T324" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32166,7 +32173,7 @@
       </c>
       <c r="R325" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.16811616455877632</v>
+        <v>3.380460815002706E-2</v>
       </c>
       <c r="T325" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32233,7 +32240,7 @@
       </c>
       <c r="R326" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>17.132008245103364</v>
+        <v>17.334376513391923</v>
       </c>
       <c r="T326" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32291,7 +32298,7 @@
       </c>
       <c r="R327" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>50.59354183449863</v>
+        <v>50.417703459805693</v>
       </c>
       <c r="T327" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32348,7 +32355,7 @@
       </c>
       <c r="R328" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.889574173268656</v>
+        <v>12.893979570896951</v>
       </c>
       <c r="T328" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32405,7 +32412,7 @@
       </c>
       <c r="R329" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.596137027624776</v>
+        <v>13.176475450419277</v>
       </c>
       <c r="T329" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32465,7 +32472,7 @@
       </c>
       <c r="R330" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.652226345901418</v>
+        <v>20.105322966490412</v>
       </c>
       <c r="T330" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32516,10 +32523,10 @@
         <v>1616</v>
       </c>
       <c r="I331" s="23" t="s">
+        <v>1850</v>
+      </c>
+      <c r="M331" s="23" t="s">
         <v>1851</v>
-      </c>
-      <c r="M331" s="23" t="s">
-        <v>1852</v>
       </c>
       <c r="N331" s="1" t="s">
         <v>1507</v>
@@ -32534,7 +32541,7 @@
       </c>
       <c r="R331" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.07405382803066</v>
+        <v>20.581740269244932</v>
       </c>
       <c r="T331" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32594,7 +32601,7 @@
       </c>
       <c r="R332" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>22.33972548250664</v>
+        <v>23.069445959927346</v>
       </c>
       <c r="T332" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32645,7 +32652,7 @@
         <v>1652</v>
       </c>
       <c r="I333" s="23" t="s">
-        <v>1834</v>
+        <v>1833</v>
       </c>
       <c r="N333" s="1" t="s">
         <v>1508</v>
@@ -32660,7 +32667,7 @@
       </c>
       <c r="R333" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.406335744076387</v>
+        <v>33.35644284104859</v>
       </c>
       <c r="T333" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32718,7 +32725,7 @@
       </c>
       <c r="R334" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.89602869942267727</v>
+        <v>0.42557127581566823</v>
       </c>
       <c r="T334" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32778,7 +32785,7 @@
       </c>
       <c r="R335" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.868401868098658</v>
+        <v>33.3364791689594</v>
       </c>
       <c r="T335" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32841,7 +32848,7 @@
       </c>
       <c r="R336" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>66.696828484577125</v>
+        <v>66.834383570340052</v>
       </c>
       <c r="T336" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32898,7 +32905,7 @@
       </c>
       <c r="R337" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.40518237938867618</v>
+        <v>0.80353351149105734</v>
       </c>
       <c r="T337" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32955,7 +32962,7 @@
       </c>
       <c r="R338" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>8.0538431312333163</v>
+        <v>7.194692930035119</v>
       </c>
       <c r="T338" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33012,7 +33019,7 @@
       </c>
       <c r="R339" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.24078931465449</v>
+        <v>12.61922450203193</v>
       </c>
       <c r="T339" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33073,7 +33080,7 @@
       </c>
       <c r="R340" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>9.5417160469538409</v>
+        <v>9.2140069505980904</v>
       </c>
       <c r="T340" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33133,7 +33140,7 @@
       </c>
       <c r="R341" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>34.322788386258217</v>
+        <v>34.128844656878933</v>
       </c>
       <c r="T341" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33190,7 +33197,7 @@
       </c>
       <c r="R342" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.84564004806439252</v>
+        <v>0.21464892949390957</v>
       </c>
       <c r="T342" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33247,7 +33254,7 @@
       </c>
       <c r="R343" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.08122123966743</v>
+        <v>12.605674917145011</v>
       </c>
       <c r="T343" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33307,7 +33314,7 @@
       </c>
       <c r="R344" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.898030413019733</v>
+        <v>20.942666426617514</v>
       </c>
       <c r="T344" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33364,7 +33371,7 @@
       </c>
       <c r="R345" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.153016831476764</v>
+        <v>13.447042819952234</v>
       </c>
       <c r="T345" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33421,7 +33428,7 @@
       </c>
       <c r="R346" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.574304564955884</v>
+        <v>20.171418516778349</v>
       </c>
       <c r="T346" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33472,16 +33479,16 @@
         <v>1617</v>
       </c>
       <c r="I347" s="23" t="s">
-        <v>1841</v>
+        <v>1840</v>
       </c>
       <c r="J347" s="23" t="s">
-        <v>1835</v>
+        <v>1834</v>
       </c>
       <c r="L347" s="23" t="s">
+        <v>1836</v>
+      </c>
+      <c r="M347" s="23" t="s">
         <v>1837</v>
-      </c>
-      <c r="M347" s="23" t="s">
-        <v>1838</v>
       </c>
       <c r="N347" s="1" t="s">
         <v>1508</v>
@@ -33496,7 +33503,7 @@
       </c>
       <c r="R347" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>34.267224195313645</v>
+        <v>33.404691607709786</v>
       </c>
       <c r="T347" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33556,7 +33563,7 @@
       </c>
       <c r="R348" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>22.835623811732212</v>
+        <v>22.98607661522761</v>
       </c>
       <c r="T348" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33613,7 +33620,7 @@
       </c>
       <c r="R349" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.91392265229698</v>
+        <v>0.75516021113119403</v>
       </c>
       <c r="T349" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33670,7 +33677,7 @@
       </c>
       <c r="R350" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.26028481275352122</v>
+        <v>1.0817941910008622E-2</v>
       </c>
       <c r="T350" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33728,7 +33735,7 @@
       </c>
       <c r="R351" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.947207376853163</v>
+        <v>13.165663958719069</v>
       </c>
       <c r="T351" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33788,7 +33795,7 @@
       </c>
       <c r="R352" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>22.797627068127181</v>
+        <v>22.665945350962353</v>
       </c>
       <c r="T352" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33845,7 +33852,7 @@
       </c>
       <c r="R353" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.514829311283215</v>
+        <v>34.276864920668672</v>
       </c>
       <c r="T353" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33902,7 +33909,7 @@
       </c>
       <c r="R354" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.96025109267335906</v>
+        <v>0.56825622573686396</v>
       </c>
       <c r="T354" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33944,7 +33951,7 @@
         <v>1007</v>
       </c>
       <c r="F355" s="2" t="s">
-        <v>1783</v>
+        <v>1782</v>
       </c>
       <c r="G355" s="23" t="s">
         <v>63</v>
@@ -33953,10 +33960,10 @@
         <v>1617</v>
       </c>
       <c r="I355" s="23" t="s">
+        <v>1794</v>
+      </c>
+      <c r="L355" s="23" t="s">
         <v>1795</v>
-      </c>
-      <c r="L355" s="23" t="s">
-        <v>1796</v>
       </c>
       <c r="N355" s="1" t="s">
         <v>1507</v>
@@ -33971,7 +33978,7 @@
       </c>
       <c r="R355" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>60.825838026114383</v>
+        <v>60.117509264586538</v>
       </c>
       <c r="T355" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34032,7 +34039,7 @@
       </c>
       <c r="R356" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>9.717454274855525</v>
+        <v>9.3223348398905923</v>
       </c>
       <c r="T356" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34090,7 +34097,7 @@
       </c>
       <c r="R357" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.879397940241262</v>
+        <v>33.97672758061443</v>
       </c>
       <c r="T357" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34147,7 +34154,7 @@
       </c>
       <c r="R358" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.904007678994907</v>
+        <v>12.937576631866547</v>
       </c>
       <c r="T358" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34204,7 +34211,7 @@
       </c>
       <c r="R359" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>40.900626537803063</v>
+        <v>40.105088793795289</v>
       </c>
       <c r="T359" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34262,7 +34269,7 @@
       </c>
       <c r="R360" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.7277089830836172</v>
+        <v>0.61139159846676294</v>
       </c>
       <c r="T360" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34319,7 +34326,7 @@
       </c>
       <c r="R361" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.25179257057287419</v>
+        <v>0.60002874464780287</v>
       </c>
       <c r="T361" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34376,7 +34383,7 @@
       </c>
       <c r="R362" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.672665638834061</v>
+        <v>13.294722422260238</v>
       </c>
       <c r="T362" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34436,7 +34443,7 @@
       </c>
       <c r="R363" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>10.609756041034746</v>
+        <v>10.554408390853352</v>
       </c>
       <c r="T363" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34493,7 +34500,7 @@
       </c>
       <c r="R364" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>5.1567261757817118E-2</v>
+        <v>0.59061394143402923</v>
       </c>
       <c r="T364" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34550,7 +34557,7 @@
       </c>
       <c r="R365" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.334906181859433</v>
+        <v>13.14042467178138</v>
       </c>
       <c r="T365" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34604,10 +34611,10 @@
         <v>1626</v>
       </c>
       <c r="K366" s="23" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
       <c r="M366" s="23" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="N366" s="1" t="s">
         <v>1507</v>
@@ -34622,7 +34629,7 @@
       </c>
       <c r="R366" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>34.167314818079802</v>
+        <v>33.486198346974625</v>
       </c>
       <c r="T366" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34685,7 +34692,7 @@
       </c>
       <c r="R367" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.021808260242242</v>
+        <v>12.757305112177173</v>
       </c>
       <c r="T367" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34748,7 +34755,7 @@
       </c>
       <c r="R368" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.046159637013428</v>
+        <v>13.232672772095162</v>
       </c>
       <c r="T368" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34799,13 +34806,13 @@
         <v>1616</v>
       </c>
       <c r="I369" s="23" t="s">
-        <v>1829</v>
+        <v>1828</v>
       </c>
       <c r="J369" s="23" t="s">
+        <v>1838</v>
+      </c>
+      <c r="K369" s="23" t="s">
         <v>1839</v>
-      </c>
-      <c r="K369" s="23" t="s">
-        <v>1840</v>
       </c>
       <c r="L369" s="23" t="s">
         <v>1627</v>
@@ -34823,7 +34830,7 @@
       </c>
       <c r="R369" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.558478967092213</v>
+        <v>34.023329753607484</v>
       </c>
       <c r="T369" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34883,7 +34890,7 @@
       </c>
       <c r="R370" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>22.274958445279886</v>
+        <v>22.649489288374948</v>
       </c>
       <c r="T370" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34940,7 +34947,7 @@
       </c>
       <c r="R371" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.98136739302918</v>
+        <v>13.403441031296312</v>
       </c>
       <c r="T371" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34997,7 +35004,7 @@
       </c>
       <c r="R372" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.801659588057763</v>
+        <v>13.287559423452688</v>
       </c>
       <c r="T372" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35054,7 +35061,7 @@
       </c>
       <c r="R373" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.46520303574498523</v>
+        <v>0.16190493083056268</v>
       </c>
       <c r="T373" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35111,7 +35118,7 @@
       </c>
       <c r="R374" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.18221006706771758</v>
+        <v>0.77911024905532467</v>
       </c>
       <c r="T374" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35168,7 +35175,7 @@
       </c>
       <c r="R375" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.5193206543864264</v>
+        <v>7.9898947202480697</v>
       </c>
       <c r="T375" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35225,7 +35232,7 @@
       </c>
       <c r="R376" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.9684014090152635</v>
+        <v>7.7468845751462183</v>
       </c>
       <c r="T376" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35285,7 +35292,7 @@
       </c>
       <c r="R377" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>10.649513187836112</v>
+        <v>10.547753104226794</v>
       </c>
       <c r="T377" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35318,13 +35325,13 @@
         <v>hinaki-v-draginie</v>
       </c>
       <c r="C378" s="24" t="s">
+        <v>1852</v>
+      </c>
+      <c r="D378" s="23" t="s">
+        <v>1854</v>
+      </c>
+      <c r="E378" s="23" t="s">
         <v>1853</v>
-      </c>
-      <c r="D378" s="23" t="s">
-        <v>1855</v>
-      </c>
-      <c r="E378" s="23" t="s">
-        <v>1854</v>
       </c>
       <c r="F378" s="2" t="s">
         <v>97</v>
@@ -35351,7 +35358,7 @@
       </c>
       <c r="R378" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.360662166875876</v>
+        <v>20.682915601444371</v>
       </c>
       <c r="T378" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35405,13 +35412,13 @@
         <v>1626</v>
       </c>
       <c r="K379" s="23" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
       <c r="L379" s="23" t="s">
         <v>1627</v>
       </c>
       <c r="M379" s="23" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="N379" s="1" t="s">
         <v>1507</v>
@@ -35426,7 +35433,7 @@
       </c>
       <c r="R379" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>34.129156566699123</v>
+        <v>34.009411939493575</v>
       </c>
       <c r="T379" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35484,7 +35491,7 @@
       </c>
       <c r="R380" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.007271868880865</v>
+        <v>13.094806595922073</v>
       </c>
       <c r="T380" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35541,7 +35548,7 @@
       </c>
       <c r="R381" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.320450089508999</v>
+        <v>13.486236370901413</v>
       </c>
       <c r="T381" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35604,7 +35611,7 @@
       </c>
       <c r="R382" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.929948839171004</v>
+        <v>12.96217991815799</v>
       </c>
       <c r="T382" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35662,7 +35669,7 @@
       </c>
       <c r="R383" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.023487068081376</v>
+        <v>20.950665441507461</v>
       </c>
       <c r="T383" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35719,7 +35726,7 @@
       </c>
       <c r="R384" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.71848524063755947</v>
+        <v>0.97119768612168766</v>
       </c>
       <c r="T384" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35776,7 +35783,7 @@
       </c>
       <c r="R385" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.831606813299082</v>
+        <v>33.663292607321466</v>
       </c>
       <c r="T385" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35836,7 +35843,7 @@
       </c>
       <c r="R386" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>10.722319985901175</v>
+        <v>10.965086401529105</v>
       </c>
       <c r="T386" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35893,7 +35900,7 @@
       </c>
       <c r="R387" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.84339484646982</v>
+        <v>13.303568613349125</v>
       </c>
       <c r="T387" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35951,7 +35958,7 @@
       </c>
       <c r="R388" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.539166099073352</v>
+        <v>20.468210456587631</v>
       </c>
       <c r="T388" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36008,7 +36015,7 @@
       </c>
       <c r="R389" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.22203807551331911</v>
+        <v>0.39812964063244127</v>
       </c>
       <c r="T389" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36065,7 +36072,7 @@
       </c>
       <c r="R390" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.8967782057372231</v>
+        <v>8.0424793184458618</v>
       </c>
       <c r="T390" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36122,7 +36129,7 @@
       </c>
       <c r="R391" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.48193635058891948</v>
+        <v>0.40910265920379363</v>
       </c>
       <c r="T391" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36180,7 +36187,7 @@
       </c>
       <c r="R392" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.293656339723217</v>
+        <v>13.480155464323365</v>
       </c>
       <c r="T392" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36237,7 +36244,7 @@
       </c>
       <c r="R393" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.940663894680732</v>
+        <v>7.7696496558897223</v>
       </c>
       <c r="T393" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36294,7 +36301,7 @@
       </c>
       <c r="R394" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.8837554797856857</v>
+        <v>7.2820369566483709</v>
       </c>
       <c r="T394" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36357,7 +36364,7 @@
       </c>
       <c r="R395" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.687241881684439</v>
+        <v>13.350358384396243</v>
       </c>
       <c r="T395" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36414,7 +36421,7 @@
       </c>
       <c r="R396" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.97990346321524768</v>
+        <v>0.78492788105171685</v>
       </c>
       <c r="T396" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36477,7 +36484,7 @@
       </c>
       <c r="R397" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.567750101349747</v>
+        <v>12.746523416327728</v>
       </c>
       <c r="T397" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36534,7 +36541,7 @@
       </c>
       <c r="R398" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.641016602817345</v>
+        <v>12.614430590885334</v>
       </c>
       <c r="T398" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36601,7 +36608,7 @@
       </c>
       <c r="R399" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>17.382591251098642</v>
+        <v>17.427685648190817</v>
       </c>
       <c r="T399" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36659,7 +36666,7 @@
       </c>
       <c r="R400" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.48422193699535687</v>
+        <v>0.23694855478173149</v>
       </c>
       <c r="T400" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36729,7 +36736,7 @@
       </c>
       <c r="R401" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>16.790413078703722</v>
+        <v>17.094247448536628</v>
       </c>
       <c r="T401" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36786,7 +36793,7 @@
       </c>
       <c r="R402" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.006319827479661</v>
+        <v>13.370547078300763</v>
       </c>
       <c r="T402" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36850,7 +36857,7 @@
       </c>
       <c r="R403" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>16.692438280889043</v>
+        <v>16.958517612948143</v>
       </c>
       <c r="T403" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36907,7 +36914,7 @@
       </c>
       <c r="R404" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>8.6042328722149675E-2</v>
+        <v>0.51194315830655235</v>
       </c>
       <c r="T404" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36964,7 +36971,7 @@
       </c>
       <c r="R405" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.60603753964549611</v>
+        <v>0.13039573946695104</v>
       </c>
       <c r="T405" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37021,7 +37028,7 @@
       </c>
       <c r="R406" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.9410527325411473</v>
+        <v>4.8549923739114043E-3</v>
       </c>
       <c r="T406" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37078,7 +37085,7 @@
       </c>
       <c r="R407" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.99051240588486744</v>
+        <v>0.37558155821189376</v>
       </c>
       <c r="T407" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37135,7 +37142,7 @@
       </c>
       <c r="R408" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.41906235875663556</v>
+        <v>0.70515313438880323</v>
       </c>
       <c r="T408" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37193,7 +37200,7 @@
       </c>
       <c r="R409" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.321215577058748</v>
+        <v>13.438306619265164</v>
       </c>
       <c r="T409" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37253,7 +37260,7 @@
       </c>
       <c r="R410" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.59983054783317225</v>
+        <v>0.70039046547396899</v>
       </c>
       <c r="T410" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37310,7 +37317,7 @@
       </c>
       <c r="R411" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.32854058352294746</v>
+        <v>0.97105849696953772</v>
       </c>
       <c r="T411" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37367,7 +37374,7 @@
       </c>
       <c r="R412" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>40.354371641622002</v>
+        <v>40.021932166903255</v>
       </c>
       <c r="T412" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37424,7 +37431,7 @@
       </c>
       <c r="R413" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.8807072516560028</v>
+        <v>8.0523249230228622</v>
       </c>
       <c r="T413" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37484,7 +37491,7 @@
       </c>
       <c r="R414" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>10.325201271024786</v>
+        <v>10.188598644088705</v>
       </c>
       <c r="T414" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37541,7 +37548,7 @@
       </c>
       <c r="R415" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>1.4460289770275692E-2</v>
+        <v>0.46488648612481065</v>
       </c>
       <c r="T415" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37602,7 +37609,7 @@
       </c>
       <c r="R416" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>9.2860800638619683</v>
+        <v>9.1816119840472634</v>
       </c>
       <c r="T416" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37663,7 +37670,7 @@
       </c>
       <c r="R417" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>10.027974931023019</v>
+        <v>9.5688164237770525</v>
       </c>
       <c r="T417" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37720,7 +37727,7 @@
       </c>
       <c r="R418" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.8348385970419177</v>
+        <v>7.4419154093545945</v>
       </c>
       <c r="T418" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37777,7 +37784,7 @@
       </c>
       <c r="R419" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.9929900903917765</v>
+        <v>7.813960463128871</v>
       </c>
       <c r="T419" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37834,7 +37841,7 @@
       </c>
       <c r="R420" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.254940700969229</v>
+        <v>13.408603779017078</v>
       </c>
       <c r="T420" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37891,7 +37898,7 @@
       </c>
       <c r="R421" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>67.117624262807965</v>
+        <v>67.069800072113466</v>
       </c>
       <c r="T421" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37952,7 +37959,7 @@
       </c>
       <c r="R422" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>9.9587929801546888</v>
+        <v>9.8578422698946362</v>
       </c>
       <c r="T422" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38010,7 +38017,7 @@
       </c>
       <c r="R423" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.981481862555263</v>
+        <v>12.866733288002559</v>
       </c>
       <c r="T423" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38068,7 +38075,7 @@
       </c>
       <c r="R424" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.91564026841235835</v>
+        <v>0.50121833647469083</v>
       </c>
       <c r="T424" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38129,7 +38136,7 @@
       </c>
       <c r="R425" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>10.010314076179201</v>
+        <v>9.8824234089689522</v>
       </c>
       <c r="T425" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38190,7 +38197,7 @@
       </c>
       <c r="R426" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>9.5859379070242241</v>
+        <v>9.2643116939564507</v>
       </c>
       <c r="T426" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38248,7 +38255,7 @@
       </c>
       <c r="R427" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.805564723149899</v>
+        <v>13.475434634349687</v>
       </c>
       <c r="T427" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38318,7 +38325,7 @@
       </c>
       <c r="R428" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>16.951082278464305</v>
+        <v>16.994605344910799</v>
       </c>
       <c r="T428" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38378,7 +38385,7 @@
       </c>
       <c r="R429" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>10.97674513637573</v>
+        <v>10.204700347487679</v>
       </c>
       <c r="T429" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38435,7 +38442,7 @@
       </c>
       <c r="R430" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.36620016555853097</v>
+        <v>0.73909741672994778</v>
       </c>
       <c r="T430" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38492,7 +38499,7 @@
       </c>
       <c r="R431" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.825739518638885</v>
+        <v>12.924975797042812</v>
       </c>
       <c r="T431" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38549,7 +38556,7 @@
       </c>
       <c r="R432" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.41442417875203297</v>
+        <v>5.4700191273596377E-2</v>
       </c>
       <c r="T432" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38607,7 +38614,7 @@
       </c>
       <c r="R433" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.79355560740344444</v>
+        <v>0.42751376324173851</v>
       </c>
       <c r="T433" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38667,7 +38674,7 @@
       </c>
       <c r="R434" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.799968054228</v>
+        <v>20.764015272632836</v>
       </c>
       <c r="T434" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38727,7 +38734,7 @@
       </c>
       <c r="R435" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.096639940986261</v>
+        <v>20.017972673225209</v>
       </c>
       <c r="T435" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38787,7 +38794,7 @@
       </c>
       <c r="R436" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.461555145025876</v>
+        <v>20.535788578844439</v>
       </c>
       <c r="T436" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38847,7 +38854,7 @@
       </c>
       <c r="R437" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.834710862546256</v>
+        <v>20.436520770360776</v>
       </c>
       <c r="T437" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38907,7 +38914,7 @@
       </c>
       <c r="R438" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.813164877932881</v>
+        <v>20.220270430991558</v>
       </c>
       <c r="T438" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38967,7 +38974,7 @@
       </c>
       <c r="R439" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.414082692085724</v>
+        <v>20.155842218388742</v>
       </c>
       <c r="T439" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -39042,7 +39049,7 @@
       </c>
       <c r="R440" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.64386208428062</v>
+        <v>33.793003209669187</v>
       </c>
       <c r="T440" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -39111,7 +39118,7 @@
       </c>
       <c r="R441" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.885305419949233</v>
+        <v>34.075947409686378</v>
       </c>
       <c r="T441" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -39529,7 +39536,7 @@
       </c>
       <c r="C4" s="7">
         <f ca="1">MATCH(C5,キャラ情報!C:C,0)</f>
-        <v>415</v>
+        <v>406</v>
       </c>
     </row>
     <row r="5" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -39538,7 +39545,7 @@
       </c>
       <c r="C5" s="6" t="str">
         <f ca="1">INDEX(キャラ情報!C:R,MATCH(MIN(キャラ情報!R:R),キャラ情報!R:R,0),1)</f>
-        <v>夜打キーボ</v>
+        <v>闇音レンリ</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -39547,7 +39554,7 @@
       </c>
       <c r="C6" s="6" t="str">
         <f ca="1">INDEX(キャラ情報!C:R,MATCH(MIN(キャラ情報!R:R),キャラ情報!R:R,0),4)</f>
-        <v>https://alceaakaza.wixsite.com/artkashic-uni-verse</v>
+        <v>https://renrivoice.wixsite.com/renri-voice</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -41566,7 +41573,7 @@
       </c>
       <c r="I36" s="19" t="str">
         <f>テーブル1[[#This Row],[種族タグ]]&amp;""</f>
-        <v>宇宙人</v>
+        <v>宇宙人|元ヤン</v>
       </c>
       <c r="J36" s="19" t="str">
         <f>テーブル1[[#This Row],[モチーフタグ]]&amp;""</f>

--- a/data/characters.xlsx
+++ b/data/characters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\モノクロビリーフ\外部リンク\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C591846-69C8-4078-B1E5-5AE28E33F3EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B045E374-1794-4585-A260-8DFBDF787113}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{78CF6334-6F78-4A6F-BD14-CB6FA7AB00CF}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3307" uniqueCount="1860">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3313" uniqueCount="1861">
   <si>
     <t>番号</t>
   </si>
@@ -8007,6 +8007,10 @@
   </si>
   <si>
     <t>グラデーションカラー|オッドアイ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ドッペルゲンガー</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -8243,7 +8247,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -8339,9 +8343,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -14657,6 +14658,24 @@
       <c r="G63" s="23" t="s">
         <v>175</v>
       </c>
+      <c r="H63" s="23" t="s">
+        <v>1616</v>
+      </c>
+      <c r="I63" s="23" t="s">
+        <v>1625</v>
+      </c>
+      <c r="J63" s="23" t="s">
+        <v>1860</v>
+      </c>
+      <c r="K63" s="23" t="s">
+        <v>1807</v>
+      </c>
+      <c r="L63" s="24" t="s">
+        <v>1857</v>
+      </c>
+      <c r="M63" s="23" t="s">
+        <v>1661</v>
+      </c>
       <c r="O63" s="1" t="s">
         <v>1432</v>
       </c>
@@ -26837,7 +26856,7 @@
       </c>
       <c r="R235" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>50.508724346227666</v>
+        <v>50.388695506908164</v>
       </c>
       <c r="T235" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -26906,7 +26925,7 @@
       </c>
       <c r="R236" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>60.508440221927579</v>
+        <v>60.961601750411752</v>
       </c>
       <c r="T236" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -26972,7 +26991,7 @@
       </c>
       <c r="R237" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>60.017475440378568</v>
+        <v>60.058847717363534</v>
       </c>
       <c r="T237" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27032,7 +27051,7 @@
       </c>
       <c r="R238" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.9459618157855092</v>
+        <v>0.6907742033400549</v>
       </c>
       <c r="T238" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27092,7 +27111,7 @@
       </c>
       <c r="R239" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.680143342437084</v>
+        <v>33.469948867144474</v>
       </c>
       <c r="T239" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27152,7 +27171,7 @@
       </c>
       <c r="R240" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.857308279815996</v>
+        <v>34.017509563683035</v>
       </c>
       <c r="T240" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27209,7 +27228,7 @@
       </c>
       <c r="R241" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.943273756512802</v>
+        <v>13.332551782969235</v>
       </c>
       <c r="T241" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27269,7 +27288,7 @@
       </c>
       <c r="R242" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>10.591428639003956</v>
+        <v>10.140618480859107</v>
       </c>
       <c r="T242" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27329,7 +27348,7 @@
       </c>
       <c r="R243" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.039082652287341</v>
+        <v>20.001244603232593</v>
       </c>
       <c r="T243" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27395,7 +27414,7 @@
       </c>
       <c r="R244" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>25.182277127826037</v>
+        <v>25.513809836662457</v>
       </c>
       <c r="T244" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27452,7 +27471,7 @@
       </c>
       <c r="R245" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.973580067924818</v>
+        <v>13.224562950997713</v>
       </c>
       <c r="T245" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27512,7 +27531,7 @@
       </c>
       <c r="R246" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>10.176078712526673</v>
+        <v>10.514703875988399</v>
       </c>
       <c r="T246" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27584,7 +27603,7 @@
       </c>
       <c r="R247" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.592851627287295</v>
+        <v>20.953799285009531</v>
       </c>
       <c r="T247" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27644,7 +27663,7 @@
       </c>
       <c r="R248" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.354697537799051</v>
+        <v>20.129481009746435</v>
       </c>
       <c r="T248" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27704,7 +27723,7 @@
       </c>
       <c r="R249" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.375434115674818</v>
+        <v>20.676009997183321</v>
       </c>
       <c r="T249" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27764,7 +27783,7 @@
       </c>
       <c r="R250" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.74916956434777</v>
+        <v>20.617723198417721</v>
       </c>
       <c r="T250" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27824,7 +27843,7 @@
       </c>
       <c r="R251" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.765956265150841</v>
+        <v>20.204755981135882</v>
       </c>
       <c r="T251" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27884,7 +27903,7 @@
       </c>
       <c r="R252" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.857125992623885</v>
+        <v>20.593324863126671</v>
       </c>
       <c r="T252" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27944,7 +27963,7 @@
       </c>
       <c r="R253" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.611848981001756</v>
+        <v>20.341584142758755</v>
       </c>
       <c r="T253" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28004,7 +28023,7 @@
       </c>
       <c r="R254" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.508579399718041</v>
+        <v>20.639449493659797</v>
       </c>
       <c r="T254" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28064,7 +28083,7 @@
       </c>
       <c r="R255" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.395882174437393</v>
+        <v>20.240337200335802</v>
       </c>
       <c r="T255" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28124,7 +28143,7 @@
       </c>
       <c r="R256" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.648758030004633</v>
+        <v>20.324715024828006</v>
       </c>
       <c r="T256" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28184,7 +28203,7 @@
       </c>
       <c r="R257" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.887903741677704</v>
+        <v>20.336622163237568</v>
       </c>
       <c r="T257" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28244,7 +28263,7 @@
       </c>
       <c r="R258" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.167159154101796</v>
+        <v>20.044088998782613</v>
       </c>
       <c r="T258" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28302,7 +28321,7 @@
       </c>
       <c r="R259" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.666520255939384</v>
+        <v>13.3012659505188</v>
       </c>
       <c r="T259" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28359,7 +28378,7 @@
       </c>
       <c r="R260" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>40.294950246475523</v>
+        <v>40.700710108442088</v>
       </c>
       <c r="T260" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28416,7 +28435,7 @@
       </c>
       <c r="R261" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.9255494894760874</v>
+        <v>7.7025995682866615</v>
       </c>
       <c r="T261" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28473,7 +28492,7 @@
       </c>
       <c r="R262" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>50.299903382191793</v>
+        <v>50.324196004274931</v>
       </c>
       <c r="T262" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28530,7 +28549,7 @@
       </c>
       <c r="R263" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.21486581693210804</v>
+        <v>0.86589079380405942</v>
       </c>
       <c r="T263" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28587,7 +28606,7 @@
       </c>
       <c r="R264" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.19544137192636457</v>
+        <v>9.2124438862497993E-2</v>
       </c>
       <c r="T264" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28644,7 +28663,7 @@
       </c>
       <c r="R265" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.6063086888389186</v>
+        <v>7.5066947600245353</v>
       </c>
       <c r="T265" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28705,7 +28724,7 @@
       </c>
       <c r="R266" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>50.512733385930332</v>
+        <v>50.928312647646358</v>
       </c>
       <c r="T266" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28762,7 +28781,7 @@
       </c>
       <c r="R267" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.786791040482342</v>
+        <v>34.20504356459049</v>
       </c>
       <c r="T267" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28819,7 +28838,7 @@
       </c>
       <c r="R268" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.3257443386572083</v>
+        <v>7.7857525837457553</v>
       </c>
       <c r="T268" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28876,7 +28895,7 @@
       </c>
       <c r="R269" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.309044624224084</v>
+        <v>13.105957993605356</v>
       </c>
       <c r="T269" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28933,7 +28952,7 @@
       </c>
       <c r="R270" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.327682934852312</v>
+        <v>13.359210501808201</v>
       </c>
       <c r="T270" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28990,7 +29009,7 @@
       </c>
       <c r="R271" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.386204087885075</v>
+        <v>13.075039503044867</v>
       </c>
       <c r="T271" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29065,7 +29084,7 @@
       </c>
       <c r="R272" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>75.025173355589814</v>
+        <v>75.752259349575837</v>
       </c>
       <c r="T272" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29122,7 +29141,7 @@
       </c>
       <c r="R273" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.100065811558295</v>
+        <v>12.531184895361154</v>
       </c>
       <c r="T273" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29179,7 +29198,7 @@
       </c>
       <c r="R274" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.078992237203943</v>
+        <v>13.046964222017992</v>
       </c>
       <c r="T274" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29236,7 +29255,7 @@
       </c>
       <c r="R275" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.57126702009483354</v>
+        <v>0.75801114581775542</v>
       </c>
       <c r="T275" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29293,7 +29312,7 @@
       </c>
       <c r="R276" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>34.304177878758253</v>
+        <v>33.968678777923955</v>
       </c>
       <c r="T276" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29350,7 +29369,7 @@
       </c>
       <c r="R277" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.019847419567631</v>
+        <v>12.559853224257893</v>
       </c>
       <c r="T277" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29407,7 +29426,7 @@
       </c>
       <c r="R278" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.872310468790943</v>
+        <v>12.688966534412669</v>
       </c>
       <c r="T278" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29467,7 +29486,7 @@
       </c>
       <c r="R279" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>50.812095262878785</v>
+        <v>50.893968487907671</v>
       </c>
       <c r="T279" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29524,7 +29543,7 @@
       </c>
       <c r="R280" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.84973232472883786</v>
+        <v>0.58780414126595182</v>
       </c>
       <c r="T280" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29581,7 +29600,7 @@
       </c>
       <c r="R281" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.48646522819531224</v>
+        <v>2.4701724241950052E-3</v>
       </c>
       <c r="T281" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29642,7 +29661,7 @@
       </c>
       <c r="R282" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>10.078510786521228</v>
+        <v>9.4878279409236459</v>
       </c>
       <c r="T282" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29711,7 +29730,7 @@
       </c>
       <c r="R283" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>57.695525931920677</v>
+        <v>57.488452632709404</v>
       </c>
       <c r="T283" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29769,7 +29788,7 @@
       </c>
       <c r="R284" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.661292840951663</v>
+        <v>20.622131970224931</v>
       </c>
       <c r="T284" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29826,7 +29845,7 @@
       </c>
       <c r="R285" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.36659754022189306</v>
+        <v>0.16119315321408167</v>
       </c>
       <c r="T285" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29886,7 +29905,7 @@
       </c>
       <c r="R286" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>10.909339335653176</v>
+        <v>10.209386162596129</v>
       </c>
       <c r="T286" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29955,7 +29974,7 @@
       </c>
       <c r="R287" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>80.74994739231326</v>
+        <v>80.525612252050095</v>
       </c>
       <c r="T287" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30012,7 +30031,7 @@
       </c>
       <c r="R288" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.1946989882172199</v>
+        <v>8.0231745081495944</v>
       </c>
       <c r="T288" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30069,7 +30088,7 @@
       </c>
       <c r="R289" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.829182657101285</v>
+        <v>12.863290219256889</v>
       </c>
       <c r="T289" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30129,7 +30148,7 @@
       </c>
       <c r="R290" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>9.3461884056392268</v>
+        <v>9.5685016671533543</v>
       </c>
       <c r="T290" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30186,7 +30205,7 @@
       </c>
       <c r="R291" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.22985765426911953</v>
+        <v>0.6943842358496386</v>
       </c>
       <c r="T291" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30255,7 +30274,7 @@
       </c>
       <c r="R292" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>57.594199467064811</v>
+        <v>57.999321914200664</v>
       </c>
       <c r="T292" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30312,7 +30331,7 @@
       </c>
       <c r="R293" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.627199457311253</v>
+        <v>13.377759696972003</v>
       </c>
       <c r="T293" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30372,7 +30391,7 @@
       </c>
       <c r="R294" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>22.634910183193909</v>
+        <v>22.619201240606927</v>
       </c>
       <c r="T294" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30444,7 +30463,7 @@
       </c>
       <c r="R295" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>60.036421568934337</v>
+        <v>60.926102519179871</v>
       </c>
       <c r="T295" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30501,7 +30520,7 @@
       </c>
       <c r="R296" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.93374610863946961</v>
+        <v>0.89358467144733345</v>
       </c>
       <c r="T296" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30558,7 +30577,7 @@
       </c>
       <c r="R297" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>50.324096759672635</v>
+        <v>50.992066261856486</v>
       </c>
       <c r="T297" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30618,7 +30637,7 @@
       </c>
       <c r="R298" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>10.687536995445502</v>
+        <v>10.363535343224694</v>
       </c>
       <c r="T298" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30675,7 +30694,7 @@
       </c>
       <c r="R299" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.39955195290340273</v>
+        <v>0.99568470922512875</v>
       </c>
       <c r="T299" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30735,7 +30754,7 @@
       </c>
       <c r="R300" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.47559579999272139</v>
+        <v>0.98819993416639285</v>
       </c>
       <c r="T300" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30801,7 +30820,7 @@
       </c>
       <c r="R301" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>57.859472351708803</v>
+        <v>57.428381810366012</v>
       </c>
       <c r="T301" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30858,7 +30877,7 @@
       </c>
       <c r="R302" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.39483330697243924</v>
+        <v>0.37857312818129807</v>
       </c>
       <c r="T302" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30915,7 +30934,7 @@
       </c>
       <c r="R303" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.82426989393598449</v>
+        <v>0.59378956363391788</v>
       </c>
       <c r="T303" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30972,7 +30991,7 @@
       </c>
       <c r="R304" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.69141317898506938</v>
+        <v>0.64190245111928079</v>
       </c>
       <c r="T304" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31029,7 +31048,7 @@
       </c>
       <c r="R305" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.27289852734180808</v>
+        <v>0.77488141321830961</v>
       </c>
       <c r="T305" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31104,7 +31123,7 @@
       </c>
       <c r="R306" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.42532172631924</v>
+        <v>34.221112704323311</v>
       </c>
       <c r="T306" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31170,7 +31189,7 @@
       </c>
       <c r="R307" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.864217903383082</v>
+        <v>20.170266096651915</v>
       </c>
       <c r="T307" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31227,7 +31246,7 @@
       </c>
       <c r="R308" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.59344588804958309</v>
+        <v>0.53273530067408814</v>
       </c>
       <c r="T308" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31284,7 +31303,7 @@
       </c>
       <c r="R309" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.73858071014228</v>
+        <v>33.486499162032167</v>
       </c>
       <c r="T309" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31341,7 +31360,7 @@
       </c>
       <c r="R310" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>34.269090951725552</v>
+        <v>33.424045977533353</v>
       </c>
       <c r="T310" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31402,7 +31421,7 @@
       </c>
       <c r="R311" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>9.5499781356344489</v>
+        <v>10.020013767482945</v>
       </c>
       <c r="T311" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31460,7 +31479,7 @@
       </c>
       <c r="R312" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.90733960871342356</v>
+        <v>0.61496342371494073</v>
       </c>
       <c r="T312" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31517,7 +31536,7 @@
       </c>
       <c r="R313" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.81514061851290487</v>
+        <v>0.31432988160990805</v>
       </c>
       <c r="T313" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31574,7 +31593,7 @@
       </c>
       <c r="R314" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.40738419750970545</v>
+        <v>0.20516500122827952</v>
       </c>
       <c r="T314" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31631,7 +31650,7 @@
       </c>
       <c r="R315" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.662716787797009</v>
+        <v>13.429489491616884</v>
       </c>
       <c r="T315" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31689,7 +31708,7 @@
       </c>
       <c r="R316" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.8501028031177591</v>
+        <v>6.4915267272055655E-2</v>
       </c>
       <c r="T316" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31747,7 +31766,7 @@
       </c>
       <c r="R317" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.73360505244778806</v>
+        <v>0.67607028866666874</v>
       </c>
       <c r="T317" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31805,7 +31824,7 @@
       </c>
       <c r="R318" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.89512490669897371</v>
+        <v>0.77172138299184212</v>
       </c>
       <c r="T318" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31863,7 +31882,7 @@
       </c>
       <c r="R319" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.10908204192944082</v>
+        <v>0.38856231967912791</v>
       </c>
       <c r="T319" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31921,7 +31940,7 @@
       </c>
       <c r="R320" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.3372722345450595</v>
+        <v>0.50977542156570343</v>
       </c>
       <c r="T320" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31979,7 +31998,7 @@
       </c>
       <c r="R321" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>34.07956246291738</v>
+        <v>34.169051813600461</v>
       </c>
       <c r="T321" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32039,7 +32058,7 @@
       </c>
       <c r="R322" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>22.815978787416981</v>
+        <v>22.227230592518524</v>
       </c>
       <c r="T322" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32099,7 +32118,7 @@
       </c>
       <c r="R323" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>22.466582929670828</v>
+        <v>22.820622780853505</v>
       </c>
       <c r="T323" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32156,7 +32175,7 @@
       </c>
       <c r="R324" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.1079773111368465</v>
+        <v>0.91073255398812702</v>
       </c>
       <c r="T324" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32213,7 +32232,7 @@
       </c>
       <c r="R325" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.51418564661308619</v>
+        <v>0.88578242245204053</v>
       </c>
       <c r="T325" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32280,7 +32299,7 @@
       </c>
       <c r="R326" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>17.481989810882162</v>
+        <v>16.689040543427478</v>
       </c>
       <c r="T326" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32338,7 +32357,7 @@
       </c>
       <c r="R327" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>50.408493300589647</v>
+        <v>50.524637763955205</v>
       </c>
       <c r="T327" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32395,7 +32414,7 @@
       </c>
       <c r="R328" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.504482545528594</v>
+        <v>12.540899606710839</v>
       </c>
       <c r="T328" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32452,7 +32471,7 @@
       </c>
       <c r="R329" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.289281578965754</v>
+        <v>13.238815040645289</v>
       </c>
       <c r="T329" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32512,7 +32531,7 @@
       </c>
       <c r="R330" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.498075797505145</v>
+        <v>20.394757949902637</v>
       </c>
       <c r="T330" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32581,7 +32600,7 @@
       </c>
       <c r="R331" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.10829682021032</v>
+        <v>20.448541042719473</v>
       </c>
       <c r="T331" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32641,7 +32660,7 @@
       </c>
       <c r="R332" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>22.497871242461116</v>
+        <v>22.391909853468906</v>
       </c>
       <c r="T332" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32707,7 +32726,7 @@
       </c>
       <c r="R333" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.918586962022431</v>
+        <v>33.99968655605656</v>
       </c>
       <c r="T333" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32765,7 +32784,7 @@
       </c>
       <c r="R334" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.74885942670849459</v>
+        <v>0.94970830551000673</v>
       </c>
       <c r="T334" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32825,7 +32844,7 @@
       </c>
       <c r="R335" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.552983724569366</v>
+        <v>34.020979430797361</v>
       </c>
       <c r="T335" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32888,7 +32907,7 @@
       </c>
       <c r="R336" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>66.767931838216484</v>
+        <v>66.680865624237697</v>
       </c>
       <c r="T336" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32945,7 +32964,7 @@
       </c>
       <c r="R337" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.6658522943313161</v>
+        <v>2.3493916926541458E-2</v>
       </c>
       <c r="T337" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33002,7 +33021,7 @@
       </c>
       <c r="R338" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.1740934643762282</v>
+        <v>7.68591375220646</v>
       </c>
       <c r="T338" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33059,7 +33078,7 @@
       </c>
       <c r="R339" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.512412819725755</v>
+        <v>13.120470457523917</v>
       </c>
       <c r="T339" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33120,7 +33139,7 @@
       </c>
       <c r="R340" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>9.2707935516983593</v>
+        <v>9.6684213115943027</v>
       </c>
       <c r="T340" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33180,7 +33199,7 @@
       </c>
       <c r="R341" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.669471528938566</v>
+        <v>34.275157117259482</v>
       </c>
       <c r="T341" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33237,7 +33256,7 @@
       </c>
       <c r="R342" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.5042597259407096E-3</v>
+        <v>0.88398522495127618</v>
       </c>
       <c r="T342" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33294,7 +33313,7 @@
       </c>
       <c r="R343" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.390651171728612</v>
+        <v>12.939573395985912</v>
       </c>
       <c r="T343" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33354,7 +33373,7 @@
       </c>
       <c r="R344" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.952719780267739</v>
+        <v>20.810254412018956</v>
       </c>
       <c r="T344" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33411,7 +33430,7 @@
       </c>
       <c r="R345" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.377431072958222</v>
+        <v>12.827053490180214</v>
       </c>
       <c r="T345" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33468,7 +33487,7 @@
       </c>
       <c r="R346" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.373009647727873</v>
+        <v>20.977689729113415</v>
       </c>
       <c r="T346" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33543,7 +33562,7 @@
       </c>
       <c r="R347" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.373452091521735</v>
+        <v>33.670319504130603</v>
       </c>
       <c r="T347" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33603,7 +33622,7 @@
       </c>
       <c r="R348" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>22.852283332726273</v>
+        <v>22.955257071900927</v>
       </c>
       <c r="T348" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33660,7 +33679,7 @@
       </c>
       <c r="R349" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.72156131405745128</v>
+        <v>0.67429345194344259</v>
       </c>
       <c r="T349" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33717,7 +33736,7 @@
       </c>
       <c r="R350" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>1.6275976806059744E-2</v>
+        <v>6.717397176105766E-2</v>
       </c>
       <c r="T350" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33775,7 +33794,7 @@
       </c>
       <c r="R351" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.852391221921275</v>
+        <v>13.197019195929375</v>
       </c>
       <c r="T351" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33835,7 +33854,7 @@
       </c>
       <c r="R352" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>22.726229124437801</v>
+        <v>22.701660283814086</v>
       </c>
       <c r="T352" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33892,7 +33911,7 @@
       </c>
       <c r="R353" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.817387764374082</v>
+        <v>33.993920509305347</v>
       </c>
       <c r="T353" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33949,7 +33968,7 @@
       </c>
       <c r="R354" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.24884893865872815</v>
+        <v>2.787046284664918E-2</v>
       </c>
       <c r="T354" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34018,7 +34037,7 @@
       </c>
       <c r="R355" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>60.247499545473971</v>
+        <v>60.20052920347991</v>
       </c>
       <c r="T355" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34079,7 +34098,7 @@
       </c>
       <c r="R356" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>9.147830450138791</v>
+        <v>9.9819878716425201</v>
       </c>
       <c r="T356" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34137,7 +34156,7 @@
       </c>
       <c r="R357" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>34.281896836361682</v>
+        <v>33.959947635065383</v>
       </c>
       <c r="T357" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34194,7 +34213,7 @@
       </c>
       <c r="R358" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.272091212258582</v>
+        <v>13.338030834567959</v>
       </c>
       <c r="T358" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34251,7 +34270,7 @@
       </c>
       <c r="R359" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>40.438591087870016</v>
+        <v>40.944303235434177</v>
       </c>
       <c r="T359" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34309,7 +34328,7 @@
       </c>
       <c r="R360" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.28828140588672468</v>
+        <v>9.57677387343292E-3</v>
       </c>
       <c r="T360" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34366,7 +34385,7 @@
       </c>
       <c r="R361" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.47802977195288077</v>
+        <v>0.53961486192129615</v>
       </c>
       <c r="T361" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34423,7 +34442,7 @@
       </c>
       <c r="R362" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.934896366573033</v>
+        <v>13.401875876787125</v>
       </c>
       <c r="T362" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34483,7 +34502,7 @@
       </c>
       <c r="R363" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>10.246509154264272</v>
+        <v>10.837678888166552</v>
       </c>
       <c r="T363" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34540,7 +34559,7 @@
       </c>
       <c r="R364" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.58543840962778371</v>
+        <v>0.69759531608151693</v>
       </c>
       <c r="T364" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34597,7 +34616,7 @@
       </c>
       <c r="R365" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.18086943657368</v>
+        <v>12.784533860401574</v>
       </c>
       <c r="T365" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34669,7 +34688,7 @@
       </c>
       <c r="R366" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.872356275365291</v>
+        <v>33.925376911154721</v>
       </c>
       <c r="T366" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34735,7 +34754,7 @@
       </c>
       <c r="R367" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>25.346875582703856</v>
+        <v>25.130626275706678</v>
       </c>
       <c r="T367" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34801,7 +34820,7 @@
       </c>
       <c r="R368" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>25.379278541368294</v>
+        <v>25.105326464436541</v>
       </c>
       <c r="T368" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34876,7 +34895,7 @@
       </c>
       <c r="R369" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>34.075734160362266</v>
+        <v>34.270545402460343</v>
       </c>
       <c r="T369" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34936,7 +34955,7 @@
       </c>
       <c r="R370" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>22.269521205097568</v>
+        <v>23.01537562937019</v>
       </c>
       <c r="T370" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34993,7 +35012,7 @@
       </c>
       <c r="R371" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.932915976240842</v>
+        <v>12.874188485680939</v>
       </c>
       <c r="T371" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35050,7 +35069,7 @@
       </c>
       <c r="R372" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.274566874834504</v>
+        <v>13.120323698197536</v>
       </c>
       <c r="T372" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35107,7 +35126,7 @@
       </c>
       <c r="R373" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.17252724255146934</v>
+        <v>0.73814514542753562</v>
       </c>
       <c r="T373" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35164,7 +35183,7 @@
       </c>
       <c r="R374" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.91096002166758905</v>
+        <v>0.22781983112839499</v>
       </c>
       <c r="T374" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35221,7 +35240,7 @@
       </c>
       <c r="R375" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.8198534067911893</v>
+        <v>7.750507572151462</v>
       </c>
       <c r="T375" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35278,7 +35297,7 @@
       </c>
       <c r="R376" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>8.0418016618166916</v>
+        <v>7.2582722513463107</v>
       </c>
       <c r="T376" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35338,7 +35357,7 @@
       </c>
       <c r="R377" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>10.238043510754126</v>
+        <v>10.201038866692713</v>
       </c>
       <c r="T377" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35404,7 +35423,7 @@
       </c>
       <c r="R378" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.70542751925888</v>
+        <v>20.392141907402685</v>
       </c>
       <c r="T378" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35479,7 +35498,7 @@
       </c>
       <c r="R379" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.505668686160575</v>
+        <v>33.734611364679274</v>
       </c>
       <c r="T379" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35537,7 +35556,7 @@
       </c>
       <c r="R380" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.219488049467051</v>
+        <v>13.092828548110795</v>
       </c>
       <c r="T380" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35594,7 +35613,7 @@
       </c>
       <c r="R381" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.286083723416077</v>
+        <v>12.668384516594623</v>
       </c>
       <c r="T381" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35660,7 +35679,7 @@
       </c>
       <c r="R382" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>25.127541640563813</v>
+        <v>25.706646007179739</v>
       </c>
       <c r="T382" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35718,7 +35737,7 @@
       </c>
       <c r="R383" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.52271252363672</v>
+        <v>20.782770677728404</v>
       </c>
       <c r="T383" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35775,7 +35794,7 @@
       </c>
       <c r="R384" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.59390142372436794</v>
+        <v>0.77256589787867003</v>
       </c>
       <c r="T384" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35832,7 +35851,7 @@
       </c>
       <c r="R385" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.361773006720952</v>
+        <v>34.105091463719567</v>
       </c>
       <c r="T385" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35892,7 +35911,7 @@
       </c>
       <c r="R386" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>10.304290090029204</v>
+        <v>10.560245270884216</v>
       </c>
       <c r="T386" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35949,7 +35968,7 @@
       </c>
       <c r="R387" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.620083943977773</v>
+        <v>12.773425185979924</v>
       </c>
       <c r="T387" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36007,7 +36026,7 @@
       </c>
       <c r="R388" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.572213503682345</v>
+        <v>20.962138693447717</v>
       </c>
       <c r="T388" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36064,7 +36083,7 @@
       </c>
       <c r="R389" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.84175914957784936</v>
+        <v>0.65757618847714994</v>
       </c>
       <c r="T389" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36121,7 +36140,7 @@
       </c>
       <c r="R390" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.7935449292816523</v>
+        <v>7.9955049548919117</v>
       </c>
       <c r="T390" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36178,7 +36197,7 @@
       </c>
       <c r="R391" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.54859385845122832</v>
+        <v>0.96217792568876348</v>
       </c>
       <c r="T391" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36236,7 +36255,7 @@
       </c>
       <c r="R392" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.721438340760653</v>
+        <v>12.694089860273454</v>
       </c>
       <c r="T392" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36293,7 +36312,7 @@
       </c>
       <c r="R393" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.8706806286169231</v>
+        <v>7.8239173340906465</v>
       </c>
       <c r="T393" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36350,7 +36369,7 @@
       </c>
       <c r="R394" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.5165716766439923</v>
+        <v>7.9592817813665278</v>
       </c>
       <c r="T394" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36416,7 +36435,7 @@
       </c>
       <c r="R395" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>25.070964132390369</v>
+        <v>25.163457041843852</v>
       </c>
       <c r="T395" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36473,7 +36492,7 @@
       </c>
       <c r="R396" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.69312522979859403</v>
+        <v>0.87125480274395617</v>
       </c>
       <c r="T396" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36539,7 +36558,7 @@
       </c>
       <c r="R397" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>25.165859757368889</v>
+        <v>25.667029389619426</v>
       </c>
       <c r="T397" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36596,7 +36615,7 @@
       </c>
       <c r="R398" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.48259104857916</v>
+        <v>12.738067136038227</v>
       </c>
       <c r="T398" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36663,7 +36682,7 @@
       </c>
       <c r="R399" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>17.115826908569204</v>
+        <v>16.990711912360553</v>
       </c>
       <c r="T399" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36721,7 +36740,7 @@
       </c>
       <c r="R400" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.94017230200248003</v>
+        <v>0.48471835591506318</v>
       </c>
       <c r="T400" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36791,7 +36810,7 @@
       </c>
       <c r="R401" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>17.028263348549128</v>
+        <v>16.727525365410756</v>
       </c>
       <c r="T401" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36848,7 +36867,7 @@
       </c>
       <c r="R402" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.970724476954201</v>
+        <v>13.181549097320199</v>
       </c>
       <c r="T402" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36912,7 +36931,7 @@
       </c>
       <c r="R403" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>17.418097085831338</v>
+        <v>17.160877849967548</v>
       </c>
       <c r="T403" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36969,7 +36988,7 @@
       </c>
       <c r="R404" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.17005887458419167</v>
+        <v>0.20147039611828632</v>
       </c>
       <c r="T404" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37026,7 +37045,7 @@
       </c>
       <c r="R405" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.0867632470318354E-3</v>
+        <v>1.1675169475877323E-2</v>
       </c>
       <c r="T405" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37083,7 +37102,7 @@
       </c>
       <c r="R406" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.41044125213482652</v>
+        <v>0.7336230422787583</v>
       </c>
       <c r="T406" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37140,7 +37159,7 @@
       </c>
       <c r="R407" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.26235958396352632</v>
+        <v>0.97227845376383326</v>
       </c>
       <c r="T407" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37197,7 +37216,7 @@
       </c>
       <c r="R408" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.59691179556077378</v>
+        <v>8.9866383779329984E-2</v>
       </c>
       <c r="T408" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37255,7 +37274,7 @@
       </c>
       <c r="R409" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.547058787913468</v>
+        <v>13.391482768527332</v>
       </c>
       <c r="T409" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37315,7 +37334,7 @@
       </c>
       <c r="R410" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.67957356322693208</v>
+        <v>0.83257245363120624</v>
       </c>
       <c r="T410" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37372,7 +37391,7 @@
       </c>
       <c r="R411" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.82895013471510481</v>
+        <v>0.98457802084697477</v>
       </c>
       <c r="T411" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37429,7 +37448,7 @@
       </c>
       <c r="R412" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>40.228737195532453</v>
+        <v>40.843679645688454</v>
       </c>
       <c r="T412" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37486,7 +37505,7 @@
       </c>
       <c r="R413" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.3533169262464417</v>
+        <v>7.8718000318692782</v>
       </c>
       <c r="T413" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37546,7 +37565,7 @@
       </c>
       <c r="R414" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>10.631075422567081</v>
+        <v>10.301678665707167</v>
       </c>
       <c r="T414" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37603,7 +37622,7 @@
       </c>
       <c r="R415" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.46704165558368582</v>
+        <v>0.81731539266613296</v>
       </c>
       <c r="T415" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37664,7 +37683,7 @@
       </c>
       <c r="R416" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>9.5952814883868953</v>
+        <v>9.9994976267415989</v>
       </c>
       <c r="T416" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37725,7 +37744,7 @@
       </c>
       <c r="R417" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>9.1184097685941232</v>
+        <v>9.5691540463234581</v>
       </c>
       <c r="T417" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37782,7 +37801,7 @@
       </c>
       <c r="R418" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.4966427742777348</v>
+        <v>7.3034620832900492</v>
       </c>
       <c r="T418" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37839,7 +37858,7 @@
       </c>
       <c r="R419" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.4969655045658428</v>
+        <v>7.8777586617141084</v>
       </c>
       <c r="T419" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37896,7 +37915,7 @@
       </c>
       <c r="R420" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.641938613497379</v>
+        <v>12.606493700385778</v>
       </c>
       <c r="T420" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37953,7 +37972,7 @@
       </c>
       <c r="R421" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>67.380253085787245</v>
+        <v>67.560906760142771</v>
       </c>
       <c r="T421" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38014,7 +38033,7 @@
       </c>
       <c r="R422" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>9.7100628193431042</v>
+        <v>9.2963765882691938</v>
       </c>
       <c r="T422" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38072,7 +38091,7 @@
       </c>
       <c r="R423" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.0832589730844</v>
+        <v>13.139967092425207</v>
       </c>
       <c r="T423" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38130,7 +38149,7 @@
       </c>
       <c r="R424" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.83131888906493812</v>
+        <v>0.57217369286211561</v>
       </c>
       <c r="T424" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38191,7 +38210,7 @@
       </c>
       <c r="R425" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>9.8110460550416523</v>
+        <v>9.9189262114941901</v>
       </c>
       <c r="T425" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38252,7 +38271,7 @@
       </c>
       <c r="R426" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>10.057464455778874</v>
+        <v>9.6293914211129934</v>
       </c>
       <c r="T426" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38310,7 +38329,7 @@
       </c>
       <c r="R427" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.630312829165982</v>
+        <v>12.81269527130614</v>
       </c>
       <c r="T427" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38380,7 +38399,7 @@
       </c>
       <c r="R428" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>16.708703040976381</v>
+        <v>16.830750674137843</v>
       </c>
       <c r="T428" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38440,7 +38459,7 @@
       </c>
       <c r="R429" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>10.861496959987903</v>
+        <v>10.157811724252793</v>
       </c>
       <c r="T429" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38497,7 +38516,7 @@
       </c>
       <c r="R430" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.40281963037304591</v>
+        <v>0.77245227698861973</v>
       </c>
       <c r="T430" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38554,7 +38573,7 @@
       </c>
       <c r="R431" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.347987320475518</v>
+        <v>12.71407347773253</v>
       </c>
       <c r="T431" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38611,7 +38630,7 @@
       </c>
       <c r="R432" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.27309165443036876</v>
+        <v>0.38370733541844015</v>
       </c>
       <c r="T432" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38669,7 +38688,7 @@
       </c>
       <c r="R433" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.96417451646776975</v>
+        <v>2.2708419167409066E-2</v>
       </c>
       <c r="T433" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38729,7 +38748,7 @@
       </c>
       <c r="R434" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.159133247627953</v>
+        <v>20.464058174861243</v>
       </c>
       <c r="T434" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38789,7 +38808,7 @@
       </c>
       <c r="R435" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.064802825871169</v>
+        <v>20.789880313727277</v>
       </c>
       <c r="T435" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38849,7 +38868,7 @@
       </c>
       <c r="R436" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.560636104607489</v>
+        <v>20.830660962938346</v>
       </c>
       <c r="T436" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38909,7 +38928,7 @@
       </c>
       <c r="R437" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.668188224293935</v>
+        <v>20.298528383553528</v>
       </c>
       <c r="T437" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38969,7 +38988,7 @@
       </c>
       <c r="R438" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.115848005514597</v>
+        <v>20.964061355112801</v>
       </c>
       <c r="T438" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -39029,7 +39048,7 @@
       </c>
       <c r="R439" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.249116680852033</v>
+        <v>20.75531330452187</v>
       </c>
       <c r="T439" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -39104,7 +39123,7 @@
       </c>
       <c r="R440" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.902727674818145</v>
+        <v>34.247814153894389</v>
       </c>
       <c r="T440" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -39173,7 +39192,7 @@
       </c>
       <c r="R441" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>34.011679746133886</v>
+        <v>33.505879535931797</v>
       </c>
       <c r="T441" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -39561,10 +39580,11 @@
     <hyperlink ref="F158" r:id="rId313" xr:uid="{820134B8-ED42-4B4C-A25A-8338EF6EEEB0}"/>
     <hyperlink ref="F55" r:id="rId314" xr:uid="{CA4A437D-844A-4B30-BA65-9BDA11F750D9}"/>
     <hyperlink ref="F110" r:id="rId315" xr:uid="{6199CBBA-251A-4B48-8FCD-16DAC0BDCA3D}"/>
+    <hyperlink ref="F63" r:id="rId316" xr:uid="{F7F8E687-6C4F-43B0-8BCD-CFD5182A4526}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId316"/>
+    <tablePart r:id="rId317"/>
   </tableParts>
 </worksheet>
 </file>
@@ -39591,7 +39611,7 @@
       </c>
       <c r="C4" s="7">
         <f ca="1">MATCH(C5,キャラ情報!C:C,0)</f>
-        <v>405</v>
+        <v>281</v>
       </c>
     </row>
     <row r="5" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -39600,7 +39620,7 @@
       </c>
       <c r="C5" s="6" t="str">
         <f ca="1">INDEX(キャラ情報!C:R,MATCH(MIN(キャラ情報!R:R),キャラ情報!R:R,0),1)</f>
-        <v>優音モフ</v>
+        <v>音通コウジ</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -39609,7 +39629,7 @@
       </c>
       <c r="C6" s="6" t="str">
         <f ca="1">INDEX(キャラ情報!C:R,MATCH(MIN(キャラ情報!R:R),キャラ情報!R:R,0),4)</f>
-        <v>https://sites.google.com/view/report1023</v>
+        <v>https://bowlroll.net/user/253605</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -43082,27 +43102,27 @@
       </c>
       <c r="H63" s="19" t="str">
         <f>テーブル1[[#This Row],[性別]]&amp;""</f>
-        <v/>
+        <v>男性</v>
       </c>
       <c r="I63" s="19" t="str">
         <f>テーブル1[[#This Row],[種族タグ]]&amp;""</f>
-        <v/>
+        <v>人間</v>
       </c>
       <c r="J63" s="19" t="str">
         <f>テーブル1[[#This Row],[モチーフタグ]]&amp;""</f>
-        <v/>
+        <v>ドッペルゲンガー</v>
       </c>
       <c r="K63" s="19" t="str">
         <f>テーブル1[[#This Row],[職業タグ]]&amp;""</f>
-        <v/>
+        <v>学生</v>
       </c>
       <c r="L63" s="19" t="str">
         <f>テーブル1[[#This Row],[小物タグ]]&amp;""</f>
-        <v/>
+        <v>耳標</v>
       </c>
       <c r="M63" s="19" t="str">
         <f>テーブル1[[#This Row],[ワンポイントタグ]]&amp;""</f>
-        <v/>
+        <v>片目隠れ</v>
       </c>
     </row>
     <row r="64" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -52286,55 +52306,55 @@
       </c>
     </row>
     <row r="234" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A234" s="32">
+      <c r="A234" s="19">
         <f>テーブル1[[#This Row],[番号]]</f>
         <v>233</v>
       </c>
-      <c r="B234" s="32" t="str">
+      <c r="B234" s="19" t="str">
         <f>テーブル1[[#This Row],[名前]]</f>
         <v>榊れを</v>
       </c>
-      <c r="C234" s="32" t="str">
+      <c r="C234" s="19" t="str">
         <f>テーブル1[[#This Row],[なまえ]]</f>
         <v>さかき れを</v>
       </c>
-      <c r="D234" s="32" t="str">
+      <c r="D234" s="19" t="str">
         <f>テーブル1[[#This Row],[Name]]</f>
         <v>Sakaki Leo</v>
       </c>
-      <c r="E234" s="32" t="str">
+      <c r="E234" s="19" t="str">
         <f>"image/"&amp;テーブル1[[#This Row],[画像]]&amp;".png"</f>
         <v>image/sakaki-leo.png</v>
       </c>
-      <c r="F234" s="32" t="str">
+      <c r="F234" s="19" t="str">
         <f>テーブル1[[#This Row],[リンク]]</f>
         <v>https://lenskkpb.wixsite.com/len-sakaki-official</v>
       </c>
-      <c r="G234" s="32" t="str">
+      <c r="G234" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[作品タグ]]," ","|")</f>
         <v>#榊れを</v>
       </c>
-      <c r="H234" s="32" t="str">
+      <c r="H234" s="19" t="str">
         <f>テーブル1[[#This Row],[性別]]&amp;""</f>
         <v>男性</v>
       </c>
-      <c r="I234" s="32" t="str">
+      <c r="I234" s="19" t="str">
         <f>テーブル1[[#This Row],[種族タグ]]&amp;""</f>
         <v>機械</v>
       </c>
-      <c r="J234" s="32" t="str">
+      <c r="J234" s="19" t="str">
         <f>テーブル1[[#This Row],[モチーフタグ]]&amp;""</f>
         <v/>
       </c>
-      <c r="K234" s="32" t="str">
+      <c r="K234" s="19" t="str">
         <f>テーブル1[[#This Row],[職業タグ]]&amp;""</f>
         <v>メイド</v>
       </c>
-      <c r="L234" s="32" t="str">
+      <c r="L234" s="19" t="str">
         <f>テーブル1[[#This Row],[小物タグ]]&amp;""</f>
         <v>耳標</v>
       </c>
-      <c r="M234" s="32" t="str">
+      <c r="M234" s="19" t="str">
         <f>テーブル1[[#This Row],[ワンポイントタグ]]&amp;""</f>
         <v>グラデーションカラー|オッドアイ</v>
       </c>

--- a/data/characters.xlsx
+++ b/data/characters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\モノクロビリーフ\外部リンク\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B045E374-1794-4585-A260-8DFBDF787113}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C3FA625-ED40-4064-B5EC-7B9F8401F0F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{78CF6334-6F78-4A6F-BD14-CB6FA7AB00CF}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3313" uniqueCount="1861">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3314" uniqueCount="1861">
   <si>
     <t>番号</t>
   </si>
@@ -14674,7 +14674,10 @@
         <v>1857</v>
       </c>
       <c r="M63" s="23" t="s">
-        <v>1661</v>
+        <v>1667</v>
+      </c>
+      <c r="N63" s="1" t="s">
+        <v>1578</v>
       </c>
       <c r="O63" s="1" t="s">
         <v>1432</v>
@@ -26856,7 +26859,7 @@
       </c>
       <c r="R235" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>50.388695506908164</v>
+        <v>50.208886384865451</v>
       </c>
       <c r="T235" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -26925,7 +26928,7 @@
       </c>
       <c r="R236" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>60.961601750411752</v>
+        <v>60.530385415659694</v>
       </c>
       <c r="T236" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -26991,7 +26994,7 @@
       </c>
       <c r="R237" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>60.058847717363534</v>
+        <v>60.028422292092039</v>
       </c>
       <c r="T237" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27051,7 +27054,7 @@
       </c>
       <c r="R238" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.6907742033400549</v>
+        <v>0.26060533017868914</v>
       </c>
       <c r="T238" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27111,7 +27114,7 @@
       </c>
       <c r="R239" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.469948867144474</v>
+        <v>33.361057432228641</v>
       </c>
       <c r="T239" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27171,7 +27174,7 @@
       </c>
       <c r="R240" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>34.017509563683035</v>
+        <v>33.383519583548683</v>
       </c>
       <c r="T240" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27228,7 +27231,7 @@
       </c>
       <c r="R241" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.332551782969235</v>
+        <v>13.161391199930451</v>
       </c>
       <c r="T241" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27288,7 +27291,7 @@
       </c>
       <c r="R242" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>10.140618480859107</v>
+        <v>10.110243507858936</v>
       </c>
       <c r="T242" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27348,7 +27351,7 @@
       </c>
       <c r="R243" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.001244603232593</v>
+        <v>20.833519126633757</v>
       </c>
       <c r="T243" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27414,7 +27417,7 @@
       </c>
       <c r="R244" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>25.513809836662457</v>
+        <v>25.616652249011825</v>
       </c>
       <c r="T244" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27471,7 +27474,7 @@
       </c>
       <c r="R245" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.224562950997713</v>
+        <v>12.690392047934607</v>
       </c>
       <c r="T245" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27531,7 +27534,7 @@
       </c>
       <c r="R246" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>10.514703875988399</v>
+        <v>10.291387573023655</v>
       </c>
       <c r="T246" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27603,7 +27606,7 @@
       </c>
       <c r="R247" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.953799285009531</v>
+        <v>20.103355714892707</v>
       </c>
       <c r="T247" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27663,7 +27666,7 @@
       </c>
       <c r="R248" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.129481009746435</v>
+        <v>20.639551414096619</v>
       </c>
       <c r="T248" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27723,7 +27726,7 @@
       </c>
       <c r="R249" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.676009997183321</v>
+        <v>20.841641073110601</v>
       </c>
       <c r="T249" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27783,7 +27786,7 @@
       </c>
       <c r="R250" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.617723198417721</v>
+        <v>20.852793994733926</v>
       </c>
       <c r="T250" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27843,7 +27846,7 @@
       </c>
       <c r="R251" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.204755981135882</v>
+        <v>20.147659280499585</v>
       </c>
       <c r="T251" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27903,7 +27906,7 @@
       </c>
       <c r="R252" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.593324863126671</v>
+        <v>20.034534734079593</v>
       </c>
       <c r="T252" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27963,7 +27966,7 @@
       </c>
       <c r="R253" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.341584142758755</v>
+        <v>20.090320496365027</v>
       </c>
       <c r="T253" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28023,7 +28026,7 @@
       </c>
       <c r="R254" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.639449493659797</v>
+        <v>20.529758352092749</v>
       </c>
       <c r="T254" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28083,7 +28086,7 @@
       </c>
       <c r="R255" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.240337200335802</v>
+        <v>20.619248750236569</v>
       </c>
       <c r="T255" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28143,7 +28146,7 @@
       </c>
       <c r="R256" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.324715024828006</v>
+        <v>20.599114743265023</v>
       </c>
       <c r="T256" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28203,7 +28206,7 @@
       </c>
       <c r="R257" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.336622163237568</v>
+        <v>20.366388374963176</v>
       </c>
       <c r="T257" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28263,7 +28266,7 @@
       </c>
       <c r="R258" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.044088998782613</v>
+        <v>20.523348352897582</v>
       </c>
       <c r="T258" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28321,7 +28324,7 @@
       </c>
       <c r="R259" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.3012659505188</v>
+        <v>13.34234956096517</v>
       </c>
       <c r="T259" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28378,7 +28381,7 @@
       </c>
       <c r="R260" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>40.700710108442088</v>
+        <v>40.448054272517844</v>
       </c>
       <c r="T260" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28435,7 +28438,7 @@
       </c>
       <c r="R261" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.7025995682866615</v>
+        <v>7.1987962134894667</v>
       </c>
       <c r="T261" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28492,7 +28495,7 @@
       </c>
       <c r="R262" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>50.324196004274931</v>
+        <v>50.283879795562257</v>
       </c>
       <c r="T262" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28549,7 +28552,7 @@
       </c>
       <c r="R263" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.86589079380405942</v>
+        <v>0.17876280588162652</v>
       </c>
       <c r="T263" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28606,7 +28609,7 @@
       </c>
       <c r="R264" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>9.2124438862497993E-2</v>
+        <v>0.81802358437667566</v>
       </c>
       <c r="T264" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28663,7 +28666,7 @@
       </c>
       <c r="R265" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.5066947600245353</v>
+        <v>7.494372735430133</v>
       </c>
       <c r="T265" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28724,7 +28727,7 @@
       </c>
       <c r="R266" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>50.928312647646358</v>
+        <v>50.396102590222839</v>
       </c>
       <c r="T266" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28781,7 +28784,7 @@
       </c>
       <c r="R267" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>34.20504356459049</v>
+        <v>33.906872011819104</v>
       </c>
       <c r="T267" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28838,7 +28841,7 @@
       </c>
       <c r="R268" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.7857525837457553</v>
+        <v>7.5518812090917651</v>
       </c>
       <c r="T268" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28895,7 +28898,7 @@
       </c>
       <c r="R269" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.105957993605356</v>
+        <v>13.258912022390277</v>
       </c>
       <c r="T269" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28952,7 +28955,7 @@
       </c>
       <c r="R270" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.359210501808201</v>
+        <v>13.170306445108215</v>
       </c>
       <c r="T270" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29009,7 +29012,7 @@
       </c>
       <c r="R271" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.075039503044867</v>
+        <v>12.571987732781761</v>
       </c>
       <c r="T271" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29084,7 +29087,7 @@
       </c>
       <c r="R272" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>75.752259349575837</v>
+        <v>75.38651978902567</v>
       </c>
       <c r="T272" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29141,7 +29144,7 @@
       </c>
       <c r="R273" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.531184895361154</v>
+        <v>13.40408884815762</v>
       </c>
       <c r="T273" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29198,7 +29201,7 @@
       </c>
       <c r="R274" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.046964222017992</v>
+        <v>13.056732398540483</v>
       </c>
       <c r="T274" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29255,7 +29258,7 @@
       </c>
       <c r="R275" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.75801114581775542</v>
+        <v>0.27763198037654213</v>
       </c>
       <c r="T275" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29312,7 +29315,7 @@
       </c>
       <c r="R276" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.968678777923955</v>
+        <v>33.375482666829754</v>
       </c>
       <c r="T276" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29369,7 +29372,7 @@
       </c>
       <c r="R277" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.559853224257893</v>
+        <v>13.049553971498124</v>
       </c>
       <c r="T277" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29426,7 +29429,7 @@
       </c>
       <c r="R278" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.688966534412669</v>
+        <v>12.904282448996751</v>
       </c>
       <c r="T278" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29486,7 +29489,7 @@
       </c>
       <c r="R279" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>50.893968487907671</v>
+        <v>50.167813528081076</v>
       </c>
       <c r="T279" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29543,7 +29546,7 @@
       </c>
       <c r="R280" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.58780414126595182</v>
+        <v>0.36282141205477991</v>
       </c>
       <c r="T280" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29600,7 +29603,7 @@
       </c>
       <c r="R281" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>2.4701724241950052E-3</v>
+        <v>0.90384915056319004</v>
       </c>
       <c r="T281" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29661,7 +29664,7 @@
       </c>
       <c r="R282" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>9.4878279409236459</v>
+        <v>9.1370146655747195</v>
       </c>
       <c r="T282" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29730,7 +29733,7 @@
       </c>
       <c r="R283" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>57.488452632709404</v>
+        <v>57.181636018887112</v>
       </c>
       <c r="T283" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29788,7 +29791,7 @@
       </c>
       <c r="R284" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.622131970224931</v>
+        <v>20.766392384736648</v>
       </c>
       <c r="T284" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29845,7 +29848,7 @@
       </c>
       <c r="R285" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.16119315321408167</v>
+        <v>0.65208328282865569</v>
       </c>
       <c r="T285" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29905,7 +29908,7 @@
       </c>
       <c r="R286" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>10.209386162596129</v>
+        <v>10.475900392832486</v>
       </c>
       <c r="T286" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29974,7 +29977,7 @@
       </c>
       <c r="R287" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>80.525612252050095</v>
+        <v>80.551894665598738</v>
       </c>
       <c r="T287" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30031,7 +30034,7 @@
       </c>
       <c r="R288" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>8.0231745081495944</v>
+        <v>7.9319650291901622</v>
       </c>
       <c r="T288" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30088,7 +30091,7 @@
       </c>
       <c r="R289" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.863290219256889</v>
+        <v>13.101466051372118</v>
       </c>
       <c r="T289" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30148,7 +30151,7 @@
       </c>
       <c r="R290" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>9.5685016671533543</v>
+        <v>9.5185528986623424</v>
       </c>
       <c r="T290" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30205,7 +30208,7 @@
       </c>
       <c r="R291" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.6943842358496386</v>
+        <v>0.30596725297013982</v>
       </c>
       <c r="T291" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30274,7 +30277,7 @@
       </c>
       <c r="R292" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>57.999321914200664</v>
+        <v>57.805232712160624</v>
       </c>
       <c r="T292" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30331,7 +30334,7 @@
       </c>
       <c r="R293" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.377759696972003</v>
+        <v>12.675907215304729</v>
       </c>
       <c r="T293" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30391,7 +30394,7 @@
       </c>
       <c r="R294" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>22.619201240606927</v>
+        <v>22.824548646186503</v>
       </c>
       <c r="T294" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30463,7 +30466,7 @@
       </c>
       <c r="R295" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>60.926102519179871</v>
+        <v>60.636821449806291</v>
       </c>
       <c r="T295" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30520,7 +30523,7 @@
       </c>
       <c r="R296" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.89358467144733345</v>
+        <v>0.90946251279756396</v>
       </c>
       <c r="T296" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30577,7 +30580,7 @@
       </c>
       <c r="R297" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>50.992066261856486</v>
+        <v>50.076124070313895</v>
       </c>
       <c r="T297" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30637,7 +30640,7 @@
       </c>
       <c r="R298" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>10.363535343224694</v>
+        <v>10.864303819408748</v>
       </c>
       <c r="T298" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30694,7 +30697,7 @@
       </c>
       <c r="R299" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.99568470922512875</v>
+        <v>0.27095728645063433</v>
       </c>
       <c r="T299" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30754,7 +30757,7 @@
       </c>
       <c r="R300" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.98819993416639285</v>
+        <v>0.59828397721023063</v>
       </c>
       <c r="T300" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30820,7 +30823,7 @@
       </c>
       <c r="R301" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>57.428381810366012</v>
+        <v>57.985969034945818</v>
       </c>
       <c r="T301" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30877,7 +30880,7 @@
       </c>
       <c r="R302" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.37857312818129807</v>
+        <v>0.55119371692696806</v>
       </c>
       <c r="T302" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30934,7 +30937,7 @@
       </c>
       <c r="R303" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.59378956363391788</v>
+        <v>0.55808451648936697</v>
       </c>
       <c r="T303" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30991,7 +30994,7 @@
       </c>
       <c r="R304" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.64190245111928079</v>
+        <v>0.60023383967896593</v>
       </c>
       <c r="T304" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31048,7 +31051,7 @@
       </c>
       <c r="R305" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.77488141321830961</v>
+        <v>0.40584600117145342</v>
       </c>
       <c r="T305" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31123,7 +31126,7 @@
       </c>
       <c r="R306" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>34.221112704323311</v>
+        <v>33.339217617609691</v>
       </c>
       <c r="T306" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31189,7 +31192,7 @@
       </c>
       <c r="R307" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.170266096651915</v>
+        <v>20.988565155978947</v>
       </c>
       <c r="T307" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31246,7 +31249,7 @@
       </c>
       <c r="R308" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.53273530067408814</v>
+        <v>0.47838998851562176</v>
       </c>
       <c r="T308" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31303,7 +31306,7 @@
       </c>
       <c r="R309" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.486499162032167</v>
+        <v>33.92565885262939</v>
       </c>
       <c r="T309" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31360,7 +31363,7 @@
       </c>
       <c r="R310" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.424045977533353</v>
+        <v>33.435490491274173</v>
       </c>
       <c r="T310" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31421,7 +31424,7 @@
       </c>
       <c r="R311" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>10.020013767482945</v>
+        <v>10.060943395844141</v>
       </c>
       <c r="T311" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31479,7 +31482,7 @@
       </c>
       <c r="R312" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.61496342371494073</v>
+        <v>0.62163868371759923</v>
       </c>
       <c r="T312" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31536,7 +31539,7 @@
       </c>
       <c r="R313" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.31432988160990805</v>
+        <v>0.14226231798662725</v>
       </c>
       <c r="T313" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31593,7 +31596,7 @@
       </c>
       <c r="R314" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.20516500122827952</v>
+        <v>0.88648166723283695</v>
       </c>
       <c r="T314" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31650,7 +31653,7 @@
       </c>
       <c r="R315" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.429489491616884</v>
+        <v>12.812288682594954</v>
       </c>
       <c r="T315" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31708,7 +31711,7 @@
       </c>
       <c r="R316" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>6.4915267272055655E-2</v>
+        <v>7.9841499847764563E-2</v>
       </c>
       <c r="T316" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31766,7 +31769,7 @@
       </c>
       <c r="R317" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.67607028866666874</v>
+        <v>0.61163490683292066</v>
       </c>
       <c r="T317" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31824,7 +31827,7 @@
       </c>
       <c r="R318" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.77172138299184212</v>
+        <v>0.58387534453858847</v>
       </c>
       <c r="T318" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31882,7 +31885,7 @@
       </c>
       <c r="R319" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.38856231967912791</v>
+        <v>0.44392665726125102</v>
       </c>
       <c r="T319" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31940,7 +31943,7 @@
       </c>
       <c r="R320" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.50977542156570343</v>
+        <v>0.85991753510634195</v>
       </c>
       <c r="T320" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31998,7 +32001,7 @@
       </c>
       <c r="R321" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>34.169051813600461</v>
+        <v>33.954340283177103</v>
       </c>
       <c r="T321" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32058,7 +32061,7 @@
       </c>
       <c r="R322" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>22.227230592518524</v>
+        <v>22.763782907705465</v>
       </c>
       <c r="T322" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32118,7 +32121,7 @@
       </c>
       <c r="R323" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>22.820622780853505</v>
+        <v>22.280414454613549</v>
       </c>
       <c r="T323" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32175,7 +32178,7 @@
       </c>
       <c r="R324" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.91073255398812702</v>
+        <v>0.37359119172523081</v>
       </c>
       <c r="T324" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32232,7 +32235,7 @@
       </c>
       <c r="R325" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.88578242245204053</v>
+        <v>0.86616055731609509</v>
       </c>
       <c r="T325" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32299,7 +32302,7 @@
       </c>
       <c r="R326" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>16.689040543427478</v>
+        <v>17.12443096102583</v>
       </c>
       <c r="T326" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32357,7 +32360,7 @@
       </c>
       <c r="R327" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>50.524637763955205</v>
+        <v>50.50898443772607</v>
       </c>
       <c r="T327" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32414,7 +32417,7 @@
       </c>
       <c r="R328" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.540899606710839</v>
+        <v>12.607341040611585</v>
       </c>
       <c r="T328" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32471,7 +32474,7 @@
       </c>
       <c r="R329" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.238815040645289</v>
+        <v>12.745723478316387</v>
       </c>
       <c r="T329" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32531,7 +32534,7 @@
       </c>
       <c r="R330" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.394757949902637</v>
+        <v>20.611390148220142</v>
       </c>
       <c r="T330" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32600,7 +32603,7 @@
       </c>
       <c r="R331" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.448541042719473</v>
+        <v>20.912806635577038</v>
       </c>
       <c r="T331" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32660,7 +32663,7 @@
       </c>
       <c r="R332" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>22.391909853468906</v>
+        <v>23.08715370061007</v>
       </c>
       <c r="T332" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32726,7 +32729,7 @@
       </c>
       <c r="R333" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.99968655605656</v>
+        <v>33.408420836235955</v>
       </c>
       <c r="T333" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32784,7 +32787,7 @@
       </c>
       <c r="R334" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.94970830551000673</v>
+        <v>0.41479913589301953</v>
       </c>
       <c r="T334" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32844,7 +32847,7 @@
       </c>
       <c r="R335" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>34.020979430797361</v>
+        <v>33.904945704465256</v>
       </c>
       <c r="T335" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32907,7 +32910,7 @@
       </c>
       <c r="R336" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>66.680865624237697</v>
+        <v>67.161441511984506</v>
       </c>
       <c r="T336" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32964,7 +32967,7 @@
       </c>
       <c r="R337" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>2.3493916926541458E-2</v>
+        <v>0.63945189770244082</v>
       </c>
       <c r="T337" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33021,7 +33024,7 @@
       </c>
       <c r="R338" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.68591375220646</v>
+        <v>8.033977886124422</v>
       </c>
       <c r="T338" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33078,7 +33081,7 @@
       </c>
       <c r="R339" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.120470457523917</v>
+        <v>12.910631804547693</v>
       </c>
       <c r="T339" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33139,7 +33142,7 @@
       </c>
       <c r="R340" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>9.6684213115943027</v>
+        <v>9.9712695951963717</v>
       </c>
       <c r="T340" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33199,7 +33202,7 @@
       </c>
       <c r="R341" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>34.275157117259482</v>
+        <v>33.776465638924037</v>
       </c>
       <c r="T341" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33256,7 +33259,7 @@
       </c>
       <c r="R342" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.88398522495127618</v>
+        <v>0.38108493245595609</v>
       </c>
       <c r="T342" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33313,7 +33316,7 @@
       </c>
       <c r="R343" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.939573395985912</v>
+        <v>12.632310139783137</v>
       </c>
       <c r="T343" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33373,7 +33376,7 @@
       </c>
       <c r="R344" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.810254412018956</v>
+        <v>20.636045917726538</v>
       </c>
       <c r="T344" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33430,7 +33433,7 @@
       </c>
       <c r="R345" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.827053490180214</v>
+        <v>13.491184191799515</v>
       </c>
       <c r="T345" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33487,7 +33490,7 @@
       </c>
       <c r="R346" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.977689729113415</v>
+        <v>20.889112350026917</v>
       </c>
       <c r="T346" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33562,7 +33565,7 @@
       </c>
       <c r="R347" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.670319504130603</v>
+        <v>33.814743948433694</v>
       </c>
       <c r="T347" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33622,7 +33625,7 @@
       </c>
       <c r="R348" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>22.955257071900927</v>
+        <v>22.943768937887189</v>
       </c>
       <c r="T348" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33679,7 +33682,7 @@
       </c>
       <c r="R349" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.67429345194344259</v>
+        <v>0.61930427758819895</v>
       </c>
       <c r="T349" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33736,7 +33739,7 @@
       </c>
       <c r="R350" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>6.717397176105766E-2</v>
+        <v>0.53255930316357614</v>
       </c>
       <c r="T350" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33794,7 +33797,7 @@
       </c>
       <c r="R351" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.197019195929375</v>
+        <v>12.726716238622744</v>
       </c>
       <c r="T351" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33854,7 +33857,7 @@
       </c>
       <c r="R352" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>22.701660283814086</v>
+        <v>22.456144339952491</v>
       </c>
       <c r="T352" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33911,7 +33914,7 @@
       </c>
       <c r="R353" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.993920509305347</v>
+        <v>34.18961427192415</v>
       </c>
       <c r="T353" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33968,7 +33971,7 @@
       </c>
       <c r="R354" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>2.787046284664918E-2</v>
+        <v>0.53031027492134086</v>
       </c>
       <c r="T354" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34037,7 +34040,7 @@
       </c>
       <c r="R355" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>60.20052920347991</v>
+        <v>60.261557983630013</v>
       </c>
       <c r="T355" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34098,7 +34101,7 @@
       </c>
       <c r="R356" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>9.9819878716425201</v>
+        <v>9.9266019694910135</v>
       </c>
       <c r="T356" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34156,7 +34159,7 @@
       </c>
       <c r="R357" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.959947635065383</v>
+        <v>33.348133681776957</v>
       </c>
       <c r="T357" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34213,7 +34216,7 @@
       </c>
       <c r="R358" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.338030834567959</v>
+        <v>13.032536928407932</v>
       </c>
       <c r="T358" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34270,7 +34273,7 @@
       </c>
       <c r="R359" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>40.944303235434177</v>
+        <v>40.953162578591169</v>
       </c>
       <c r="T359" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34328,7 +34331,7 @@
       </c>
       <c r="R360" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>9.57677387343292E-3</v>
+        <v>2.0395185355042145E-3</v>
       </c>
       <c r="T360" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34385,7 +34388,7 @@
       </c>
       <c r="R361" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.53961486192129615</v>
+        <v>0.55459061824841538</v>
       </c>
       <c r="T361" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34442,7 +34445,7 @@
       </c>
       <c r="R362" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.401875876787125</v>
+        <v>13.340522125880179</v>
       </c>
       <c r="T362" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34502,7 +34505,7 @@
       </c>
       <c r="R363" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>10.837678888166552</v>
+        <v>10.058506114946212</v>
       </c>
       <c r="T363" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34559,7 +34562,7 @@
       </c>
       <c r="R364" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.69759531608151693</v>
+        <v>0.20286540781053553</v>
       </c>
       <c r="T364" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34616,7 +34619,7 @@
       </c>
       <c r="R365" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.784533860401574</v>
+        <v>13.270734567661165</v>
       </c>
       <c r="T365" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34688,7 +34691,7 @@
       </c>
       <c r="R366" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.925376911154721</v>
+        <v>33.491287402759049</v>
       </c>
       <c r="T366" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34754,7 +34757,7 @@
       </c>
       <c r="R367" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>25.130626275706678</v>
+        <v>25.596507234104124</v>
       </c>
       <c r="T367" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34820,7 +34823,7 @@
       </c>
       <c r="R368" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>25.105326464436541</v>
+        <v>25.805599989387179</v>
       </c>
       <c r="T368" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34895,7 +34898,7 @@
       </c>
       <c r="R369" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>34.270545402460343</v>
+        <v>33.953967878228504</v>
       </c>
       <c r="T369" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34955,7 +34958,7 @@
       </c>
       <c r="R370" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>23.01537562937019</v>
+        <v>22.475636741685609</v>
       </c>
       <c r="T370" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35012,7 +35015,7 @@
       </c>
       <c r="R371" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.874188485680939</v>
+        <v>13.047211976721805</v>
       </c>
       <c r="T371" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35069,7 +35072,7 @@
       </c>
       <c r="R372" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.120323698197536</v>
+        <v>13.057384147310124</v>
       </c>
       <c r="T372" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35126,7 +35129,7 @@
       </c>
       <c r="R373" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.73814514542753562</v>
+        <v>5.9941419446212008E-2</v>
       </c>
       <c r="T373" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35183,7 +35186,7 @@
       </c>
       <c r="R374" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.22781983112839499</v>
+        <v>0.64037991452445775</v>
       </c>
       <c r="T374" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35240,7 +35243,7 @@
       </c>
       <c r="R375" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.750507572151462</v>
+        <v>7.7615815991950798</v>
       </c>
       <c r="T375" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35297,7 +35300,7 @@
       </c>
       <c r="R376" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.2582722513463107</v>
+        <v>7.2940328234489433</v>
       </c>
       <c r="T376" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35357,7 +35360,7 @@
       </c>
       <c r="R377" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>10.201038866692713</v>
+        <v>10.759135138591168</v>
       </c>
       <c r="T377" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35423,7 +35426,7 @@
       </c>
       <c r="R378" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.392141907402685</v>
+        <v>20.663452969499179</v>
       </c>
       <c r="T378" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35498,7 +35501,7 @@
       </c>
       <c r="R379" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.734611364679274</v>
+        <v>34.135128387391283</v>
       </c>
       <c r="T379" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35556,7 +35559,7 @@
       </c>
       <c r="R380" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.092828548110795</v>
+        <v>12.818344335953483</v>
       </c>
       <c r="T380" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35613,7 +35616,7 @@
       </c>
       <c r="R381" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.668384516594623</v>
+        <v>13.340826872580196</v>
       </c>
       <c r="T381" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35679,7 +35682,7 @@
       </c>
       <c r="R382" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>25.706646007179739</v>
+        <v>25.675735262718973</v>
       </c>
       <c r="T382" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35737,7 +35740,7 @@
       </c>
       <c r="R383" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.782770677728404</v>
+        <v>20.237060650928417</v>
       </c>
       <c r="T383" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35794,7 +35797,7 @@
       </c>
       <c r="R384" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.77256589787867003</v>
+        <v>8.995515514053376E-2</v>
       </c>
       <c r="T384" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35851,7 +35854,7 @@
       </c>
       <c r="R385" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>34.105091463719567</v>
+        <v>33.927896530525352</v>
       </c>
       <c r="T385" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35911,7 +35914,7 @@
       </c>
       <c r="R386" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>10.560245270884216</v>
+        <v>10.928052833108142</v>
       </c>
       <c r="T386" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35968,7 +35971,7 @@
       </c>
       <c r="R387" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.773425185979924</v>
+        <v>13.047529469486101</v>
       </c>
       <c r="T387" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36026,7 +36029,7 @@
       </c>
       <c r="R388" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.962138693447717</v>
+        <v>20.847016768262034</v>
       </c>
       <c r="T388" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36083,7 +36086,7 @@
       </c>
       <c r="R389" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.65757618847714994</v>
+        <v>0.65139502876066369</v>
       </c>
       <c r="T389" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36140,7 +36143,7 @@
       </c>
       <c r="R390" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.9955049548919117</v>
+        <v>7.8749658961830749</v>
       </c>
       <c r="T390" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36197,7 +36200,7 @@
       </c>
       <c r="R391" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.96217792568876348</v>
+        <v>0.48930237567187795</v>
       </c>
       <c r="T391" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36255,7 +36258,7 @@
       </c>
       <c r="R392" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.694089860273454</v>
+        <v>12.904211834167224</v>
       </c>
       <c r="T392" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36312,7 +36315,7 @@
       </c>
       <c r="R393" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.8239173340906465</v>
+        <v>7.9539232560952771</v>
       </c>
       <c r="T393" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36369,7 +36372,7 @@
       </c>
       <c r="R394" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.9592817813665278</v>
+        <v>7.2998958192921091</v>
       </c>
       <c r="T394" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36435,7 +36438,7 @@
       </c>
       <c r="R395" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>25.163457041843852</v>
+        <v>25.387144991255628</v>
       </c>
       <c r="T395" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36492,7 +36495,7 @@
       </c>
       <c r="R396" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.87125480274395617</v>
+        <v>0.31930872610582295</v>
       </c>
       <c r="T396" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36558,7 +36561,7 @@
       </c>
       <c r="R397" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>25.667029389619426</v>
+        <v>25.434363552938187</v>
       </c>
       <c r="T397" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36615,7 +36618,7 @@
       </c>
       <c r="R398" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.738067136038227</v>
+        <v>12.595623736349321</v>
       </c>
       <c r="T398" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36682,7 +36685,7 @@
       </c>
       <c r="R399" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>16.990711912360553</v>
+        <v>17.149383284537993</v>
       </c>
       <c r="T399" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36740,7 +36743,7 @@
       </c>
       <c r="R400" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.48471835591506318</v>
+        <v>0.91374055617638339</v>
       </c>
       <c r="T400" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36810,7 +36813,7 @@
       </c>
       <c r="R401" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>16.727525365410756</v>
+        <v>17.158107328425565</v>
       </c>
       <c r="T401" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36867,7 +36870,7 @@
       </c>
       <c r="R402" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.181549097320199</v>
+        <v>12.774010595001002</v>
       </c>
       <c r="T402" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36931,7 +36934,7 @@
       </c>
       <c r="R403" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>17.160877849967548</v>
+        <v>17.562273831021706</v>
       </c>
       <c r="T403" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36988,7 +36991,7 @@
       </c>
       <c r="R404" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.20147039611828632</v>
+        <v>0.47771470988634412</v>
       </c>
       <c r="T404" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37045,7 +37048,7 @@
       </c>
       <c r="R405" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>1.1675169475877323E-2</v>
+        <v>0.54932795866815898</v>
       </c>
       <c r="T405" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37102,7 +37105,7 @@
       </c>
       <c r="R406" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.7336230422787583</v>
+        <v>0.79237264193509438</v>
       </c>
       <c r="T406" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37159,7 +37162,7 @@
       </c>
       <c r="R407" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.97227845376383326</v>
+        <v>0.89596951375567147</v>
       </c>
       <c r="T407" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37216,7 +37219,7 @@
       </c>
       <c r="R408" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>8.9866383779329984E-2</v>
+        <v>0.885125158589393</v>
       </c>
       <c r="T408" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37274,7 +37277,7 @@
       </c>
       <c r="R409" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.391482768527332</v>
+        <v>12.870409448173712</v>
       </c>
       <c r="T409" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37334,7 +37337,7 @@
       </c>
       <c r="R410" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.83257245363120624</v>
+        <v>0.31439458281787047</v>
       </c>
       <c r="T410" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37391,7 +37394,7 @@
       </c>
       <c r="R411" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.98457802084697477</v>
+        <v>7.0176627023730509E-2</v>
       </c>
       <c r="T411" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37448,7 +37451,7 @@
       </c>
       <c r="R412" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>40.843679645688454</v>
+        <v>40.049976841724714</v>
       </c>
       <c r="T412" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37505,7 +37508,7 @@
       </c>
       <c r="R413" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.8718000318692782</v>
+        <v>7.2026386890214429</v>
       </c>
       <c r="T413" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37565,7 +37568,7 @@
       </c>
       <c r="R414" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>10.301678665707167</v>
+        <v>10.266228036986433</v>
       </c>
       <c r="T414" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37622,7 +37625,7 @@
       </c>
       <c r="R415" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.81731539266613296</v>
+        <v>0.50432625758586169</v>
       </c>
       <c r="T415" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37683,7 +37686,7 @@
       </c>
       <c r="R416" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>9.9994976267415989</v>
+        <v>9.1159727080642536</v>
       </c>
       <c r="T416" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37744,7 +37747,7 @@
       </c>
       <c r="R417" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>9.5691540463234581</v>
+        <v>10.089461605351341</v>
       </c>
       <c r="T417" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37801,7 +37804,7 @@
       </c>
       <c r="R418" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.3034620832900492</v>
+        <v>7.3114938322322489</v>
       </c>
       <c r="T418" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37858,7 +37861,7 @@
       </c>
       <c r="R419" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.8777586617141084</v>
+        <v>7.3235912718351219</v>
       </c>
       <c r="T419" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37915,7 +37918,7 @@
       </c>
       <c r="R420" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.606493700385778</v>
+        <v>13.289484185603834</v>
       </c>
       <c r="T420" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37972,7 +37975,7 @@
       </c>
       <c r="R421" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>67.560906760142771</v>
+        <v>67.657071391107934</v>
       </c>
       <c r="T421" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38033,7 +38036,7 @@
       </c>
       <c r="R422" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>9.2963765882691938</v>
+        <v>9.9494207757032243</v>
       </c>
       <c r="T422" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38091,7 +38094,7 @@
       </c>
       <c r="R423" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.139967092425207</v>
+        <v>13.182820681644568</v>
       </c>
       <c r="T423" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38149,7 +38152,7 @@
       </c>
       <c r="R424" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.57217369286211561</v>
+        <v>5.815348759155925E-2</v>
       </c>
       <c r="T424" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38210,7 +38213,7 @@
       </c>
       <c r="R425" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>9.9189262114941901</v>
+        <v>9.6803081059909495</v>
       </c>
       <c r="T425" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38271,7 +38274,7 @@
       </c>
       <c r="R426" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>9.6293914211129934</v>
+        <v>9.4268889804829179</v>
       </c>
       <c r="T426" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38329,7 +38332,7 @@
       </c>
       <c r="R427" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.81269527130614</v>
+        <v>13.223398702354482</v>
       </c>
       <c r="T427" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38399,7 +38402,7 @@
       </c>
       <c r="R428" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>16.830750674137843</v>
+        <v>16.92909650224528</v>
       </c>
       <c r="T428" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38459,7 +38462,7 @@
       </c>
       <c r="R429" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>10.157811724252793</v>
+        <v>10.086390692339515</v>
       </c>
       <c r="T429" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38516,7 +38519,7 @@
       </c>
       <c r="R430" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.77245227698861973</v>
+        <v>0.75286334676413047</v>
       </c>
       <c r="T430" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38573,7 +38576,7 @@
       </c>
       <c r="R431" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.71407347773253</v>
+        <v>13.432112414628106</v>
       </c>
       <c r="T431" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38630,7 +38633,7 @@
       </c>
       <c r="R432" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.38370733541844015</v>
+        <v>0.74434920463917142</v>
       </c>
       <c r="T432" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38688,7 +38691,7 @@
       </c>
       <c r="R433" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>2.2708419167409066E-2</v>
+        <v>0.83701576537710287</v>
       </c>
       <c r="T433" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38748,7 +38751,7 @@
       </c>
       <c r="R434" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.464058174861243</v>
+        <v>20.625314228308973</v>
       </c>
       <c r="T434" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38808,7 +38811,7 @@
       </c>
       <c r="R435" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.789880313727277</v>
+        <v>20.030396485755343</v>
       </c>
       <c r="T435" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38868,7 +38871,7 @@
       </c>
       <c r="R436" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.830660962938346</v>
+        <v>20.889024788784742</v>
       </c>
       <c r="T436" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38928,7 +38931,7 @@
       </c>
       <c r="R437" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.298528383553528</v>
+        <v>20.723098643213724</v>
       </c>
       <c r="T437" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38988,7 +38991,7 @@
       </c>
       <c r="R438" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.964061355112801</v>
+        <v>20.976656552146995</v>
       </c>
       <c r="T438" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -39048,7 +39051,7 @@
       </c>
       <c r="R439" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.75531330452187</v>
+        <v>20.694433413090891</v>
       </c>
       <c r="T439" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -39123,7 +39126,7 @@
       </c>
       <c r="R440" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>34.247814153894389</v>
+        <v>33.912941501238336</v>
       </c>
       <c r="T440" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -39192,7 +39195,7 @@
       </c>
       <c r="R441" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.505879535931797</v>
+        <v>33.704231806069288</v>
       </c>
       <c r="T441" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -39611,7 +39614,7 @@
       </c>
       <c r="C4" s="7">
         <f ca="1">MATCH(C5,キャラ情報!C:C,0)</f>
-        <v>281</v>
+        <v>360</v>
       </c>
     </row>
     <row r="5" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -39620,7 +39623,7 @@
       </c>
       <c r="C5" s="6" t="str">
         <f ca="1">INDEX(キャラ情報!C:R,MATCH(MIN(キャラ情報!R:R),キャラ情報!R:R,0),1)</f>
-        <v>音通コウジ</v>
+        <v>夏霜</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -39629,7 +39632,7 @@
       </c>
       <c r="C6" s="6" t="str">
         <f ca="1">INDEX(キャラ情報!C:R,MATCH(MIN(キャラ情報!R:R),キャラ情報!R:R,0),4)</f>
-        <v>https://bowlroll.net/user/253605</v>
+        <v>https://harujpg.wixsite.com/sanshoku</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -43122,7 +43125,7 @@
       </c>
       <c r="M63" s="19" t="str">
         <f>テーブル1[[#This Row],[ワンポイントタグ]]&amp;""</f>
-        <v>片目隠れ</v>
+        <v>インナーカラー|片目隠れ</v>
       </c>
     </row>
     <row r="64" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">

--- a/data/characters.xlsx
+++ b/data/characters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\モノクロビリーフ\外部リンク\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C3FA625-ED40-4064-B5EC-7B9F8401F0F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1139E853-3A8E-4237-95B6-D5F55C2B0E11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{78CF6334-6F78-4A6F-BD14-CB6FA7AB00CF}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3314" uniqueCount="1861">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3313" uniqueCount="1861">
   <si>
     <t>番号</t>
   </si>
@@ -8010,7 +8010,10 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ドッペルゲンガー</t>
+    <t>人間|ドッペルゲンガー</t>
+    <rPh sb="0" eb="2">
+      <t>ニンゲン</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -14662,9 +14665,6 @@
         <v>1616</v>
       </c>
       <c r="I63" s="23" t="s">
-        <v>1625</v>
-      </c>
-      <c r="J63" s="23" t="s">
         <v>1860</v>
       </c>
       <c r="K63" s="23" t="s">
@@ -26859,7 +26859,7 @@
       </c>
       <c r="R235" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>50.208886384865451</v>
+        <v>50.065246922674888</v>
       </c>
       <c r="T235" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -26928,7 +26928,7 @@
       </c>
       <c r="R236" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>60.530385415659694</v>
+        <v>60.415415354073431</v>
       </c>
       <c r="T236" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -26994,7 +26994,7 @@
       </c>
       <c r="R237" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>60.028422292092039</v>
+        <v>60.563652262397333</v>
       </c>
       <c r="T237" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27054,7 +27054,7 @@
       </c>
       <c r="R238" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.26060533017868914</v>
+        <v>0.43366709951126137</v>
       </c>
       <c r="T238" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27114,7 +27114,7 @@
       </c>
       <c r="R239" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.361057432228641</v>
+        <v>34.266251496419969</v>
       </c>
       <c r="T239" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27174,7 +27174,7 @@
       </c>
       <c r="R240" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.383519583548683</v>
+        <v>33.508904574051904</v>
       </c>
       <c r="T240" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27231,7 +27231,7 @@
       </c>
       <c r="R241" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.161391199930451</v>
+        <v>13.264475466830246</v>
       </c>
       <c r="T241" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27291,7 +27291,7 @@
       </c>
       <c r="R242" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>10.110243507858936</v>
+        <v>10.471061795279565</v>
       </c>
       <c r="T242" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27351,7 +27351,7 @@
       </c>
       <c r="R243" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.833519126633757</v>
+        <v>20.747126167385716</v>
       </c>
       <c r="T243" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27417,7 +27417,7 @@
       </c>
       <c r="R244" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>25.616652249011825</v>
+        <v>25.025991041155756</v>
       </c>
       <c r="T244" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27474,7 +27474,7 @@
       </c>
       <c r="R245" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.690392047934607</v>
+        <v>12.971407631229892</v>
       </c>
       <c r="T245" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27534,7 +27534,7 @@
       </c>
       <c r="R246" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>10.291387573023655</v>
+        <v>10.156876045884179</v>
       </c>
       <c r="T246" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27606,7 +27606,7 @@
       </c>
       <c r="R247" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.103355714892707</v>
+        <v>20.178023244286674</v>
       </c>
       <c r="T247" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27666,7 +27666,7 @@
       </c>
       <c r="R248" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.639551414096619</v>
+        <v>20.035319008246358</v>
       </c>
       <c r="T248" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27726,7 +27726,7 @@
       </c>
       <c r="R249" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.841641073110601</v>
+        <v>20.719222515777059</v>
       </c>
       <c r="T249" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27786,7 +27786,7 @@
       </c>
       <c r="R250" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.852793994733926</v>
+        <v>20.991272604124081</v>
       </c>
       <c r="T250" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27846,7 +27846,7 @@
       </c>
       <c r="R251" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.147659280499585</v>
+        <v>20.010977163327674</v>
       </c>
       <c r="T251" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27906,7 +27906,7 @@
       </c>
       <c r="R252" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.034534734079593</v>
+        <v>20.309798979436621</v>
       </c>
       <c r="T252" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27966,7 +27966,7 @@
       </c>
       <c r="R253" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.090320496365027</v>
+        <v>20.247343794226047</v>
       </c>
       <c r="T253" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28026,7 +28026,7 @@
       </c>
       <c r="R254" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.529758352092749</v>
+        <v>20.194035608790578</v>
       </c>
       <c r="T254" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28086,7 +28086,7 @@
       </c>
       <c r="R255" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.619248750236569</v>
+        <v>20.503097695627407</v>
       </c>
       <c r="T255" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28146,7 +28146,7 @@
       </c>
       <c r="R256" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.599114743265023</v>
+        <v>20.198289660306585</v>
       </c>
       <c r="T256" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28206,7 +28206,7 @@
       </c>
       <c r="R257" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.366388374963176</v>
+        <v>20.840621490921521</v>
       </c>
       <c r="T257" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28266,7 +28266,7 @@
       </c>
       <c r="R258" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.523348352897582</v>
+        <v>20.180608685596056</v>
       </c>
       <c r="T258" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28324,7 +28324,7 @@
       </c>
       <c r="R259" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.34234956096517</v>
+        <v>12.523068220844532</v>
       </c>
       <c r="T259" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28381,7 +28381,7 @@
       </c>
       <c r="R260" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>40.448054272517844</v>
+        <v>40.141091744151382</v>
       </c>
       <c r="T260" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28438,7 +28438,7 @@
       </c>
       <c r="R261" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.1987962134894667</v>
+        <v>7.2380966490513714</v>
       </c>
       <c r="T261" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28495,7 +28495,7 @@
       </c>
       <c r="R262" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>50.283879795562257</v>
+        <v>50.789666155095816</v>
       </c>
       <c r="T262" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28552,7 +28552,7 @@
       </c>
       <c r="R263" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.17876280588162652</v>
+        <v>0.79265615382338583</v>
       </c>
       <c r="T263" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28609,7 +28609,7 @@
       </c>
       <c r="R264" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.81802358437667566</v>
+        <v>0.83448650089098653</v>
       </c>
       <c r="T264" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28666,7 +28666,7 @@
       </c>
       <c r="R265" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.494372735430133</v>
+        <v>7.8484296858182114</v>
       </c>
       <c r="T265" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28727,7 +28727,7 @@
       </c>
       <c r="R266" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>50.396102590222839</v>
+        <v>50.619874810930767</v>
       </c>
       <c r="T266" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28784,7 +28784,7 @@
       </c>
       <c r="R267" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.906872011819104</v>
+        <v>33.783485907647176</v>
       </c>
       <c r="T267" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28841,7 +28841,7 @@
       </c>
       <c r="R268" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.5518812090917651</v>
+        <v>8.1409397119986853</v>
       </c>
       <c r="T268" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28898,7 +28898,7 @@
       </c>
       <c r="R269" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.258912022390277</v>
+        <v>12.634020837095822</v>
       </c>
       <c r="T269" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28955,7 +28955,7 @@
       </c>
       <c r="R270" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.170306445108215</v>
+        <v>13.140790172613235</v>
       </c>
       <c r="T270" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29012,7 +29012,7 @@
       </c>
       <c r="R271" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.571987732781761</v>
+        <v>12.609911156589558</v>
       </c>
       <c r="T271" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29087,7 +29087,7 @@
       </c>
       <c r="R272" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>75.38651978902567</v>
+        <v>75.647244240937596</v>
       </c>
       <c r="T272" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29144,7 +29144,7 @@
       </c>
       <c r="R273" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.40408884815762</v>
+        <v>12.933076717993535</v>
       </c>
       <c r="T273" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29201,7 +29201,7 @@
       </c>
       <c r="R274" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.056732398540483</v>
+        <v>12.798144005202296</v>
       </c>
       <c r="T274" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29258,7 +29258,7 @@
       </c>
       <c r="R275" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.27763198037654213</v>
+        <v>0.1652878259952032</v>
       </c>
       <c r="T275" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29315,7 +29315,7 @@
       </c>
       <c r="R276" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.375482666829754</v>
+        <v>34.181483436907477</v>
       </c>
       <c r="T276" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29372,7 +29372,7 @@
       </c>
       <c r="R277" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.049553971498124</v>
+        <v>12.569962987634867</v>
       </c>
       <c r="T277" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29429,7 +29429,7 @@
       </c>
       <c r="R278" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.904282448996751</v>
+        <v>13.181754353622635</v>
       </c>
       <c r="T278" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29489,7 +29489,7 @@
       </c>
       <c r="R279" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>50.167813528081076</v>
+        <v>50.43256635234998</v>
       </c>
       <c r="T279" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29546,7 +29546,7 @@
       </c>
       <c r="R280" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.36282141205477991</v>
+        <v>0.77158982257095698</v>
       </c>
       <c r="T280" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29603,7 +29603,7 @@
       </c>
       <c r="R281" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.90384915056319004</v>
+        <v>0.43239755764225918</v>
       </c>
       <c r="T281" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29664,7 +29664,7 @@
       </c>
       <c r="R282" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>9.1370146655747195</v>
+        <v>9.5098905910106897</v>
       </c>
       <c r="T282" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29733,7 +29733,7 @@
       </c>
       <c r="R283" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>57.181636018887112</v>
+        <v>57.365467244221101</v>
       </c>
       <c r="T283" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29791,7 +29791,7 @@
       </c>
       <c r="R284" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.766392384736648</v>
+        <v>20.174478029709849</v>
       </c>
       <c r="T284" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29848,7 +29848,7 @@
       </c>
       <c r="R285" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.65208328282865569</v>
+        <v>0.44642712510688387</v>
       </c>
       <c r="T285" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29908,7 +29908,7 @@
       </c>
       <c r="R286" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>10.475900392832486</v>
+        <v>10.099395202285073</v>
       </c>
       <c r="T286" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29977,7 +29977,7 @@
       </c>
       <c r="R287" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>80.551894665598738</v>
+        <v>80.672945810549336</v>
       </c>
       <c r="T287" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30034,7 +30034,7 @@
       </c>
       <c r="R288" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.9319650291901622</v>
+        <v>7.7691199303503158</v>
       </c>
       <c r="T288" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30091,7 +30091,7 @@
       </c>
       <c r="R289" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.101466051372118</v>
+        <v>13.422502084682405</v>
       </c>
       <c r="T289" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30151,7 +30151,7 @@
       </c>
       <c r="R290" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>9.5185528986623424</v>
+        <v>9.7713408555801529</v>
       </c>
       <c r="T290" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30208,7 +30208,7 @@
       </c>
       <c r="R291" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.30596725297013982</v>
+        <v>0.66176867932106698</v>
       </c>
       <c r="T291" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30277,7 +30277,7 @@
       </c>
       <c r="R292" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>57.805232712160624</v>
+        <v>57.261431866317729</v>
       </c>
       <c r="T292" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30334,7 +30334,7 @@
       </c>
       <c r="R293" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.675907215304729</v>
+        <v>12.811635443279394</v>
       </c>
       <c r="T293" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30394,7 +30394,7 @@
       </c>
       <c r="R294" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>22.824548646186503</v>
+        <v>23.214646034781492</v>
       </c>
       <c r="T294" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30466,7 +30466,7 @@
       </c>
       <c r="R295" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>60.636821449806291</v>
+        <v>60.415869705487168</v>
       </c>
       <c r="T295" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30523,7 +30523,7 @@
       </c>
       <c r="R296" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.90946251279756396</v>
+        <v>0.95644075102469062</v>
       </c>
       <c r="T296" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30580,7 +30580,7 @@
       </c>
       <c r="R297" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>50.076124070313895</v>
+        <v>50.806063112203582</v>
       </c>
       <c r="T297" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30640,7 +30640,7 @@
       </c>
       <c r="R298" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>10.864303819408748</v>
+        <v>10.254597964867537</v>
       </c>
       <c r="T298" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30697,7 +30697,7 @@
       </c>
       <c r="R299" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.27095728645063433</v>
+        <v>0.89027377773859084</v>
       </c>
       <c r="T299" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30757,7 +30757,7 @@
       </c>
       <c r="R300" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.59828397721023063</v>
+        <v>0.17315867533811757</v>
       </c>
       <c r="T300" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30823,7 +30823,7 @@
       </c>
       <c r="R301" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>57.985969034945818</v>
+        <v>57.476280242727015</v>
       </c>
       <c r="T301" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30880,7 +30880,7 @@
       </c>
       <c r="R302" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.55119371692696806</v>
+        <v>0.95982774931382131</v>
       </c>
       <c r="T302" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30937,7 +30937,7 @@
       </c>
       <c r="R303" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.55808451648936697</v>
+        <v>0.44084421057906764</v>
       </c>
       <c r="T303" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30994,7 +30994,7 @@
       </c>
       <c r="R304" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.60023383967896593</v>
+        <v>0.20954773375644542</v>
       </c>
       <c r="T304" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31051,7 +31051,7 @@
       </c>
       <c r="R305" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.40584600117145342</v>
+        <v>3.4228776390137772E-2</v>
       </c>
       <c r="T305" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31126,7 +31126,7 @@
       </c>
       <c r="R306" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.339217617609691</v>
+        <v>34.136118327310797</v>
       </c>
       <c r="T306" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31192,7 +31192,7 @@
       </c>
       <c r="R307" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.988565155978947</v>
+        <v>20.01109109667302</v>
       </c>
       <c r="T307" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31249,7 +31249,7 @@
       </c>
       <c r="R308" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.47838998851562176</v>
+        <v>0.4505026395522076</v>
       </c>
       <c r="T308" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31306,7 +31306,7 @@
       </c>
       <c r="R309" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.92565885262939</v>
+        <v>34.171325100294752</v>
       </c>
       <c r="T309" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31363,7 +31363,7 @@
       </c>
       <c r="R310" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.435490491274173</v>
+        <v>34.297380581647381</v>
       </c>
       <c r="T310" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31424,7 +31424,7 @@
       </c>
       <c r="R311" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>10.060943395844141</v>
+        <v>10.072147233200994</v>
       </c>
       <c r="T311" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31482,7 +31482,7 @@
       </c>
       <c r="R312" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.62163868371759923</v>
+        <v>0.12247151918561239</v>
       </c>
       <c r="T312" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31539,7 +31539,7 @@
       </c>
       <c r="R313" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.14226231798662725</v>
+        <v>0.68034532912708545</v>
       </c>
       <c r="T313" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31596,7 +31596,7 @@
       </c>
       <c r="R314" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.88648166723283695</v>
+        <v>0.9610009579873201</v>
       </c>
       <c r="T314" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31653,7 +31653,7 @@
       </c>
       <c r="R315" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.812288682594954</v>
+        <v>12.915473812132689</v>
       </c>
       <c r="T315" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31711,7 +31711,7 @@
       </c>
       <c r="R316" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.9841499847764563E-2</v>
+        <v>0.64191572106481032</v>
       </c>
       <c r="T316" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31769,7 +31769,7 @@
       </c>
       <c r="R317" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.61163490683292066</v>
+        <v>0.32172013294367541</v>
       </c>
       <c r="T317" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31827,7 +31827,7 @@
       </c>
       <c r="R318" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.58387534453858847</v>
+        <v>0.33854808414355475</v>
       </c>
       <c r="T318" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31885,7 +31885,7 @@
       </c>
       <c r="R319" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.44392665726125102</v>
+        <v>0.65313823821370354</v>
       </c>
       <c r="T319" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31943,7 +31943,7 @@
       </c>
       <c r="R320" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.85991753510634195</v>
+        <v>0.75558302736451277</v>
       </c>
       <c r="T320" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32001,7 +32001,7 @@
       </c>
       <c r="R321" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.954340283177103</v>
+        <v>33.759103195854088</v>
       </c>
       <c r="T321" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32061,7 +32061,7 @@
       </c>
       <c r="R322" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>22.763782907705465</v>
+        <v>23.028642666060268</v>
       </c>
       <c r="T322" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32121,7 +32121,7 @@
       </c>
       <c r="R323" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>22.280414454613549</v>
+        <v>22.414270285258098</v>
       </c>
       <c r="T323" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32178,7 +32178,7 @@
       </c>
       <c r="R324" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.37359119172523081</v>
+        <v>0.18597204357835506</v>
       </c>
       <c r="T324" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32235,7 +32235,7 @@
       </c>
       <c r="R325" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.86616055731609509</v>
+        <v>0.94804673515096549</v>
       </c>
       <c r="T325" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32302,7 +32302,7 @@
       </c>
       <c r="R326" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>17.12443096102583</v>
+        <v>17.434258851617024</v>
       </c>
       <c r="T326" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32360,7 +32360,7 @@
       </c>
       <c r="R327" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>50.50898443772607</v>
+        <v>50.573612422616748</v>
       </c>
       <c r="T327" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32417,7 +32417,7 @@
       </c>
       <c r="R328" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.607341040611585</v>
+        <v>13.304701595295159</v>
       </c>
       <c r="T328" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32474,7 +32474,7 @@
       </c>
       <c r="R329" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.745723478316387</v>
+        <v>12.542371503987917</v>
       </c>
       <c r="T329" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32534,7 +32534,7 @@
       </c>
       <c r="R330" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.611390148220142</v>
+        <v>20.699231353873873</v>
       </c>
       <c r="T330" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32603,7 +32603,7 @@
       </c>
       <c r="R331" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.912806635577038</v>
+        <v>20.45103642216727</v>
       </c>
       <c r="T331" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32663,7 +32663,7 @@
       </c>
       <c r="R332" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>23.08715370061007</v>
+        <v>22.897794438153444</v>
       </c>
       <c r="T332" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32729,7 +32729,7 @@
       </c>
       <c r="R333" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.408420836235955</v>
+        <v>34.079702508902692</v>
       </c>
       <c r="T333" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32787,7 +32787,7 @@
       </c>
       <c r="R334" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.41479913589301953</v>
+        <v>0.90243732125001097</v>
       </c>
       <c r="T334" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32847,7 +32847,7 @@
       </c>
       <c r="R335" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.904945704465256</v>
+        <v>34.252482005748618</v>
       </c>
       <c r="T335" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32910,7 +32910,7 @@
       </c>
       <c r="R336" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>67.161441511984506</v>
+        <v>67.404027058329561</v>
       </c>
       <c r="T336" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32967,7 +32967,7 @@
       </c>
       <c r="R337" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.63945189770244082</v>
+        <v>0.85395221561769086</v>
       </c>
       <c r="T337" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33024,7 +33024,7 @@
       </c>
       <c r="R338" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>8.033977886124422</v>
+        <v>7.2913393497917935</v>
       </c>
       <c r="T338" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33081,7 +33081,7 @@
       </c>
       <c r="R339" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.910631804547693</v>
+        <v>12.65369785937842</v>
       </c>
       <c r="T339" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33142,7 +33142,7 @@
       </c>
       <c r="R340" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>9.9712695951963717</v>
+        <v>9.4100486171465825</v>
       </c>
       <c r="T340" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33202,7 +33202,7 @@
       </c>
       <c r="R341" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.776465638924037</v>
+        <v>34.133033198472461</v>
       </c>
       <c r="T341" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33259,7 +33259,7 @@
       </c>
       <c r="R342" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.38108493245595609</v>
+        <v>9.6816065928348127E-2</v>
       </c>
       <c r="T342" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33316,7 +33316,7 @@
       </c>
       <c r="R343" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.632310139783137</v>
+        <v>12.931146020916627</v>
       </c>
       <c r="T343" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33376,7 +33376,7 @@
       </c>
       <c r="R344" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.636045917726538</v>
+        <v>20.30530269980764</v>
       </c>
       <c r="T344" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33433,7 +33433,7 @@
       </c>
       <c r="R345" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.491184191799515</v>
+        <v>13.370208276381106</v>
       </c>
       <c r="T345" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33490,7 +33490,7 @@
       </c>
       <c r="R346" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.889112350026917</v>
+        <v>20.309248450137201</v>
       </c>
       <c r="T346" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33565,7 +33565,7 @@
       </c>
       <c r="R347" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.814743948433694</v>
+        <v>34.000466387585028</v>
       </c>
       <c r="T347" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33625,7 +33625,7 @@
       </c>
       <c r="R348" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>22.943768937887189</v>
+        <v>22.27274186076</v>
       </c>
       <c r="T348" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33682,7 +33682,7 @@
       </c>
       <c r="R349" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.61930427758819895</v>
+        <v>0.27305400778065536</v>
       </c>
       <c r="T349" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33739,7 +33739,7 @@
       </c>
       <c r="R350" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.53255930316357614</v>
+        <v>0.16619463960386394</v>
       </c>
       <c r="T350" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33797,7 +33797,7 @@
       </c>
       <c r="R351" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.726716238622744</v>
+        <v>13.163060872632855</v>
       </c>
       <c r="T351" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33857,7 +33857,7 @@
       </c>
       <c r="R352" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>22.456144339952491</v>
+        <v>22.348301170037892</v>
       </c>
       <c r="T352" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33914,7 +33914,7 @@
       </c>
       <c r="R353" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>34.18961427192415</v>
+        <v>33.379563091144</v>
       </c>
       <c r="T353" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33971,7 +33971,7 @@
       </c>
       <c r="R354" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.53031027492134086</v>
+        <v>9.8424954184862634E-2</v>
       </c>
       <c r="T354" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34040,7 +34040,7 @@
       </c>
       <c r="R355" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>60.261557983630013</v>
+        <v>60.220274609876824</v>
       </c>
       <c r="T355" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34101,7 +34101,7 @@
       </c>
       <c r="R356" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>9.9266019694910135</v>
+        <v>9.3550539281434766</v>
       </c>
       <c r="T356" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34159,7 +34159,7 @@
       </c>
       <c r="R357" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.348133681776957</v>
+        <v>34.117401740239529</v>
       </c>
       <c r="T357" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34216,7 +34216,7 @@
       </c>
       <c r="R358" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.032536928407932</v>
+        <v>13.105107725659112</v>
       </c>
       <c r="T358" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34273,7 +34273,7 @@
       </c>
       <c r="R359" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>40.953162578591169</v>
+        <v>40.780135285096499</v>
       </c>
       <c r="T359" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34331,7 +34331,7 @@
       </c>
       <c r="R360" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>2.0395185355042145E-3</v>
+        <v>6.1236657246757309E-2</v>
       </c>
       <c r="T360" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34388,7 +34388,7 @@
       </c>
       <c r="R361" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.55459061824841538</v>
+        <v>0.11613117525157568</v>
       </c>
       <c r="T361" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34445,7 +34445,7 @@
       </c>
       <c r="R362" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.340522125880179</v>
+        <v>13.330889011446455</v>
       </c>
       <c r="T362" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34505,7 +34505,7 @@
       </c>
       <c r="R363" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>10.058506114946212</v>
+        <v>10.379875344491635</v>
       </c>
       <c r="T363" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34562,7 +34562,7 @@
       </c>
       <c r="R364" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.20286540781053553</v>
+        <v>0.64984974795404271</v>
       </c>
       <c r="T364" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34619,7 +34619,7 @@
       </c>
       <c r="R365" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.270734567661165</v>
+        <v>12.640478877399747</v>
       </c>
       <c r="T365" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34691,7 +34691,7 @@
       </c>
       <c r="R366" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.491287402759049</v>
+        <v>33.587705686425032</v>
       </c>
       <c r="T366" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34757,7 +34757,7 @@
       </c>
       <c r="R367" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>25.596507234104124</v>
+        <v>25.865413836572092</v>
       </c>
       <c r="T367" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34823,7 +34823,7 @@
       </c>
       <c r="R368" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>25.805599989387179</v>
+        <v>25.045250381339859</v>
       </c>
       <c r="T368" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34898,7 +34898,7 @@
       </c>
       <c r="R369" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.953967878228504</v>
+        <v>33.619807787343689</v>
       </c>
       <c r="T369" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34958,7 +34958,7 @@
       </c>
       <c r="R370" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>22.475636741685609</v>
+        <v>23.206535439166949</v>
       </c>
       <c r="T370" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35015,7 +35015,7 @@
       </c>
       <c r="R371" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.047211976721805</v>
+        <v>12.700963790756031</v>
       </c>
       <c r="T371" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35072,7 +35072,7 @@
       </c>
       <c r="R372" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.057384147310124</v>
+        <v>13.389223096797432</v>
       </c>
       <c r="T372" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35129,7 +35129,7 @@
       </c>
       <c r="R373" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>5.9941419446212008E-2</v>
+        <v>0.48363837353425987</v>
       </c>
       <c r="T373" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35186,7 +35186,7 @@
       </c>
       <c r="R374" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.64037991452445775</v>
+        <v>1.7670023320933703E-2</v>
       </c>
       <c r="T374" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35243,7 +35243,7 @@
       </c>
       <c r="R375" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.7615815991950798</v>
+        <v>7.2704253264652223</v>
       </c>
       <c r="T375" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35300,7 +35300,7 @@
       </c>
       <c r="R376" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.2940328234489433</v>
+        <v>7.2212924071771418</v>
       </c>
       <c r="T376" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35360,7 +35360,7 @@
       </c>
       <c r="R377" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>10.759135138591168</v>
+        <v>10.255023394906381</v>
       </c>
       <c r="T377" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35426,7 +35426,7 @@
       </c>
       <c r="R378" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.663452969499179</v>
+        <v>20.679898327216129</v>
       </c>
       <c r="T378" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35501,7 +35501,7 @@
       </c>
       <c r="R379" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>34.135128387391283</v>
+        <v>33.570681437350807</v>
       </c>
       <c r="T379" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35559,7 +35559,7 @@
       </c>
       <c r="R380" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.818344335953483</v>
+        <v>13.465249979151258</v>
       </c>
       <c r="T380" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35616,7 +35616,7 @@
       </c>
       <c r="R381" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.340826872580196</v>
+        <v>13.136709074285937</v>
       </c>
       <c r="T381" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35682,7 +35682,7 @@
       </c>
       <c r="R382" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>25.675735262718973</v>
+        <v>25.719613302538686</v>
       </c>
       <c r="T382" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35740,7 +35740,7 @@
       </c>
       <c r="R383" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.237060650928417</v>
+        <v>20.5353665168427</v>
       </c>
       <c r="T383" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35797,7 +35797,7 @@
       </c>
       <c r="R384" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>8.995515514053376E-2</v>
+        <v>0.89081991275970718</v>
       </c>
       <c r="T384" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35854,7 +35854,7 @@
       </c>
       <c r="R385" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.927896530525352</v>
+        <v>33.69126640377003</v>
       </c>
       <c r="T385" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35914,7 +35914,7 @@
       </c>
       <c r="R386" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>10.928052833108142</v>
+        <v>10.549920451789733</v>
       </c>
       <c r="T386" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35971,7 +35971,7 @@
       </c>
       <c r="R387" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.047529469486101</v>
+        <v>13.062702462090591</v>
       </c>
       <c r="T387" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36029,7 +36029,7 @@
       </c>
       <c r="R388" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.847016768262034</v>
+        <v>20.586698372769316</v>
       </c>
       <c r="T388" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36086,7 +36086,7 @@
       </c>
       <c r="R389" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.65139502876066369</v>
+        <v>0.68166326672901889</v>
       </c>
       <c r="T389" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36143,7 +36143,7 @@
       </c>
       <c r="R390" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.8749658961830749</v>
+        <v>7.8082872250326618</v>
       </c>
       <c r="T390" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36200,7 +36200,7 @@
       </c>
       <c r="R391" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.48930237567187795</v>
+        <v>0.20302049289909663</v>
       </c>
       <c r="T391" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36258,7 +36258,7 @@
       </c>
       <c r="R392" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.904211834167224</v>
+        <v>12.952248348480841</v>
       </c>
       <c r="T392" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36315,7 +36315,7 @@
       </c>
       <c r="R393" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.9539232560952771</v>
+        <v>7.6668862410479335</v>
       </c>
       <c r="T393" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36372,7 +36372,7 @@
       </c>
       <c r="R394" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.2998958192921091</v>
+        <v>7.6487880379306361</v>
       </c>
       <c r="T394" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36438,7 +36438,7 @@
       </c>
       <c r="R395" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>25.387144991255628</v>
+        <v>25.589487525327584</v>
       </c>
       <c r="T395" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36495,7 +36495,7 @@
       </c>
       <c r="R396" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.31930872610582295</v>
+        <v>0.62340631072047459</v>
       </c>
       <c r="T396" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36561,7 +36561,7 @@
       </c>
       <c r="R397" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>25.434363552938187</v>
+        <v>25.985266895830666</v>
       </c>
       <c r="T397" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36618,7 +36618,7 @@
       </c>
       <c r="R398" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.595623736349321</v>
+        <v>13.298804621172742</v>
       </c>
       <c r="T398" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36685,7 +36685,7 @@
       </c>
       <c r="R399" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>17.149383284537993</v>
+        <v>17.20802102261376</v>
       </c>
       <c r="T399" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36743,7 +36743,7 @@
       </c>
       <c r="R400" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.91374055617638339</v>
+        <v>0.17516613468821696</v>
       </c>
       <c r="T400" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36813,7 +36813,7 @@
       </c>
       <c r="R401" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>17.158107328425565</v>
+        <v>17.501179394054926</v>
       </c>
       <c r="T401" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36870,7 +36870,7 @@
       </c>
       <c r="R402" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.774010595001002</v>
+        <v>13.330962114533564</v>
       </c>
       <c r="T402" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36934,7 +36934,7 @@
       </c>
       <c r="R403" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>17.562273831021706</v>
+        <v>17.642270119287407</v>
       </c>
       <c r="T403" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36991,7 +36991,7 @@
       </c>
       <c r="R404" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.47771470988634412</v>
+        <v>0.93359704630605767</v>
       </c>
       <c r="T404" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37048,7 +37048,7 @@
       </c>
       <c r="R405" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.54932795866815898</v>
+        <v>1.6130078417667892E-2</v>
       </c>
       <c r="T405" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37105,7 +37105,7 @@
       </c>
       <c r="R406" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.79237264193509438</v>
+        <v>0.2179587895442483</v>
       </c>
       <c r="T406" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37162,7 +37162,7 @@
       </c>
       <c r="R407" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.89596951375567147</v>
+        <v>0.9258252942002887</v>
       </c>
       <c r="T407" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37219,7 +37219,7 @@
       </c>
       <c r="R408" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.885125158589393</v>
+        <v>0.67827266888615678</v>
       </c>
       <c r="T408" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37277,7 +37277,7 @@
       </c>
       <c r="R409" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.870409448173712</v>
+        <v>13.361779293667581</v>
       </c>
       <c r="T409" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37337,7 +37337,7 @@
       </c>
       <c r="R410" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.31439458281787047</v>
+        <v>0.4600153687701487</v>
       </c>
       <c r="T410" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37394,7 +37394,7 @@
       </c>
       <c r="R411" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.0176627023730509E-2</v>
+        <v>0.93351412923991761</v>
       </c>
       <c r="T411" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37451,7 +37451,7 @@
       </c>
       <c r="R412" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>40.049976841724714</v>
+        <v>40.281252634195283</v>
       </c>
       <c r="T412" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37508,7 +37508,7 @@
       </c>
       <c r="R413" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.2026386890214429</v>
+        <v>7.8565436137175393</v>
       </c>
       <c r="T413" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37568,7 +37568,7 @@
       </c>
       <c r="R414" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>10.266228036986433</v>
+        <v>10.403674825290274</v>
       </c>
       <c r="T414" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37625,7 +37625,7 @@
       </c>
       <c r="R415" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.50432625758586169</v>
+        <v>0.40823480056257322</v>
       </c>
       <c r="T415" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37686,7 +37686,7 @@
       </c>
       <c r="R416" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>9.1159727080642536</v>
+        <v>9.9856708362534974</v>
       </c>
       <c r="T416" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37747,7 +37747,7 @@
       </c>
       <c r="R417" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>10.089461605351341</v>
+        <v>9.4225799885267669</v>
       </c>
       <c r="T417" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37804,7 +37804,7 @@
       </c>
       <c r="R418" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.3114938322322489</v>
+        <v>7.63479464107753</v>
       </c>
       <c r="T418" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37861,7 +37861,7 @@
       </c>
       <c r="R419" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.3235912718351219</v>
+        <v>7.7356783323957439</v>
       </c>
       <c r="T419" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37918,7 +37918,7 @@
       </c>
       <c r="R420" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.289484185603834</v>
+        <v>12.978625948757845</v>
       </c>
       <c r="T420" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37975,7 +37975,7 @@
       </c>
       <c r="R421" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>67.657071391107934</v>
+        <v>66.945001150570633</v>
       </c>
       <c r="T421" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38036,7 +38036,7 @@
       </c>
       <c r="R422" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>9.9494207757032243</v>
+        <v>9.7030246746381366</v>
       </c>
       <c r="T422" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38094,7 +38094,7 @@
       </c>
       <c r="R423" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.182820681644568</v>
+        <v>13.441715792693293</v>
       </c>
       <c r="T423" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38152,7 +38152,7 @@
       </c>
       <c r="R424" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>5.815348759155925E-2</v>
+        <v>0.22523384060518903</v>
       </c>
       <c r="T424" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38213,7 +38213,7 @@
       </c>
       <c r="R425" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>9.6803081059909495</v>
+        <v>9.1626301657322937</v>
       </c>
       <c r="T425" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38274,7 +38274,7 @@
       </c>
       <c r="R426" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>9.4268889804829179</v>
+        <v>9.3572550686718365</v>
       </c>
       <c r="T426" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38332,7 +38332,7 @@
       </c>
       <c r="R427" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.223398702354482</v>
+        <v>13.278076727168314</v>
       </c>
       <c r="T427" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38402,7 +38402,7 @@
       </c>
       <c r="R428" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>16.92909650224528</v>
+        <v>17.101012048932692</v>
       </c>
       <c r="T428" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38462,7 +38462,7 @@
       </c>
       <c r="R429" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>10.086390692339515</v>
+        <v>10.935957750474852</v>
       </c>
       <c r="T429" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38519,7 +38519,7 @@
       </c>
       <c r="R430" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.75286334676413047</v>
+        <v>0.94246693683397964</v>
       </c>
       <c r="T430" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38576,7 +38576,7 @@
       </c>
       <c r="R431" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.432112414628106</v>
+        <v>12.65549313924633</v>
       </c>
       <c r="T431" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38633,7 +38633,7 @@
       </c>
       <c r="R432" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.74434920463917142</v>
+        <v>0.524786797032192</v>
       </c>
       <c r="T432" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38691,7 +38691,7 @@
       </c>
       <c r="R433" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.83701576537710287</v>
+        <v>0.78023351371090333</v>
       </c>
       <c r="T433" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38751,7 +38751,7 @@
       </c>
       <c r="R434" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.625314228308973</v>
+        <v>20.581932703138683</v>
       </c>
       <c r="T434" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38811,7 +38811,7 @@
       </c>
       <c r="R435" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.030396485755343</v>
+        <v>20.427519741089295</v>
       </c>
       <c r="T435" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38871,7 +38871,7 @@
       </c>
       <c r="R436" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.889024788784742</v>
+        <v>20.763740707837798</v>
       </c>
       <c r="T436" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38931,7 +38931,7 @@
       </c>
       <c r="R437" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.723098643213724</v>
+        <v>20.902567407202454</v>
       </c>
       <c r="T437" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38991,7 +38991,7 @@
       </c>
       <c r="R438" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.976656552146995</v>
+        <v>20.372135403128468</v>
       </c>
       <c r="T438" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -39051,7 +39051,7 @@
       </c>
       <c r="R439" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.694433413090891</v>
+        <v>20.385751794767742</v>
       </c>
       <c r="T439" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -39126,7 +39126,7 @@
       </c>
       <c r="R440" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.912941501238336</v>
+        <v>34.288974493375044</v>
       </c>
       <c r="T440" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -39195,7 +39195,7 @@
       </c>
       <c r="R441" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.704231806069288</v>
+        <v>34.262576252033583</v>
       </c>
       <c r="T441" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -39614,7 +39614,7 @@
       </c>
       <c r="C4" s="7">
         <f ca="1">MATCH(C5,キャラ情報!C:C,0)</f>
-        <v>360</v>
+        <v>405</v>
       </c>
     </row>
     <row r="5" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -39623,7 +39623,7 @@
       </c>
       <c r="C5" s="6" t="str">
         <f ca="1">INDEX(キャラ情報!C:R,MATCH(MIN(キャラ情報!R:R),キャラ情報!R:R,0),1)</f>
-        <v>夏霜</v>
+        <v>優音モフ</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -39632,7 +39632,7 @@
       </c>
       <c r="C6" s="6" t="str">
         <f ca="1">INDEX(キャラ情報!C:R,MATCH(MIN(キャラ情報!R:R),キャラ情報!R:R,0),4)</f>
-        <v>https://harujpg.wixsite.com/sanshoku</v>
+        <v>https://sites.google.com/view/report1023</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -43109,11 +43109,11 @@
       </c>
       <c r="I63" s="19" t="str">
         <f>テーブル1[[#This Row],[種族タグ]]&amp;""</f>
-        <v>人間</v>
+        <v>人間|ドッペルゲンガー</v>
       </c>
       <c r="J63" s="19" t="str">
         <f>テーブル1[[#This Row],[モチーフタグ]]&amp;""</f>
-        <v>ドッペルゲンガー</v>
+        <v/>
       </c>
       <c r="K63" s="19" t="str">
         <f>テーブル1[[#This Row],[職業タグ]]&amp;""</f>

--- a/data/characters.xlsx
+++ b/data/characters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\モノクロビリーフ\外部リンク\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1139E853-3A8E-4237-95B6-D5F55C2B0E11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE51A5F0-BB68-4DAB-AC08-2A054C29DAA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{78CF6334-6F78-4A6F-BD14-CB6FA7AB00CF}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3313" uniqueCount="1861">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3314" uniqueCount="1862">
   <si>
     <t>番号</t>
   </si>
@@ -8010,10 +8010,14 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>人間|ドッペルゲンガー</t>
+    <t>人間|怪異</t>
     <rPh sb="0" eb="2">
       <t>ニンゲン</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ドッペルゲンガー</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -14667,6 +14671,9 @@
       <c r="I63" s="23" t="s">
         <v>1860</v>
       </c>
+      <c r="J63" s="23" t="s">
+        <v>1861</v>
+      </c>
       <c r="K63" s="23" t="s">
         <v>1807</v>
       </c>
@@ -26859,7 +26866,7 @@
       </c>
       <c r="R235" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>50.065246922674888</v>
+        <v>50.333016823605369</v>
       </c>
       <c r="T235" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -26928,7 +26935,7 @@
       </c>
       <c r="R236" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>60.415415354073431</v>
+        <v>60.521421977471149</v>
       </c>
       <c r="T236" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -26994,7 +27001,7 @@
       </c>
       <c r="R237" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>60.563652262397333</v>
+        <v>60.599905844237064</v>
       </c>
       <c r="T237" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27054,7 +27061,7 @@
       </c>
       <c r="R238" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.43366709951126137</v>
+        <v>0.65116538710031802</v>
       </c>
       <c r="T238" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27114,7 +27121,7 @@
       </c>
       <c r="R239" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>34.266251496419969</v>
+        <v>34.186643537265716</v>
       </c>
       <c r="T239" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27174,7 +27181,7 @@
       </c>
       <c r="R240" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.508904574051904</v>
+        <v>33.861428169090964</v>
       </c>
       <c r="T240" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27231,7 +27238,7 @@
       </c>
       <c r="R241" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.264475466830246</v>
+        <v>13.415489157910562</v>
       </c>
       <c r="T241" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27291,7 +27298,7 @@
       </c>
       <c r="R242" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>10.471061795279565</v>
+        <v>10.124231241928278</v>
       </c>
       <c r="T242" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27351,7 +27358,7 @@
       </c>
       <c r="R243" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.747126167385716</v>
+        <v>20.493175110307241</v>
       </c>
       <c r="T243" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27417,7 +27424,7 @@
       </c>
       <c r="R244" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>25.025991041155756</v>
+        <v>25.461133610631784</v>
       </c>
       <c r="T244" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27474,7 +27481,7 @@
       </c>
       <c r="R245" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.971407631229892</v>
+        <v>12.975734445090293</v>
       </c>
       <c r="T245" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27534,7 +27541,7 @@
       </c>
       <c r="R246" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>10.156876045884179</v>
+        <v>10.150664649718172</v>
       </c>
       <c r="T246" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27606,7 +27613,7 @@
       </c>
       <c r="R247" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.178023244286674</v>
+        <v>20.965978690840402</v>
       </c>
       <c r="T247" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27666,7 +27673,7 @@
       </c>
       <c r="R248" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.035319008246358</v>
+        <v>20.729534688987613</v>
       </c>
       <c r="T248" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27726,7 +27733,7 @@
       </c>
       <c r="R249" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.719222515777059</v>
+        <v>20.030129091502953</v>
       </c>
       <c r="T249" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27786,7 +27793,7 @@
       </c>
       <c r="R250" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.991272604124081</v>
+        <v>20.014191146887608</v>
       </c>
       <c r="T250" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27846,7 +27853,7 @@
       </c>
       <c r="R251" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.010977163327674</v>
+        <v>20.197591336968731</v>
       </c>
       <c r="T251" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27906,7 +27913,7 @@
       </c>
       <c r="R252" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.309798979436621</v>
+        <v>20.086683130858209</v>
       </c>
       <c r="T252" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27966,7 +27973,7 @@
       </c>
       <c r="R253" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.247343794226047</v>
+        <v>20.88444077555377</v>
       </c>
       <c r="T253" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28026,7 +28033,7 @@
       </c>
       <c r="R254" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.194035608790578</v>
+        <v>20.306311095708036</v>
       </c>
       <c r="T254" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28086,7 +28093,7 @@
       </c>
       <c r="R255" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.503097695627407</v>
+        <v>20.629594307749787</v>
       </c>
       <c r="T255" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28146,7 +28153,7 @@
       </c>
       <c r="R256" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.198289660306585</v>
+        <v>20.09358420502447</v>
       </c>
       <c r="T256" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28206,7 +28213,7 @@
       </c>
       <c r="R257" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.840621490921521</v>
+        <v>20.049476733916336</v>
       </c>
       <c r="T257" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28266,7 +28273,7 @@
       </c>
       <c r="R258" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.180608685596056</v>
+        <v>20.132167739549569</v>
       </c>
       <c r="T258" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28324,7 +28331,7 @@
       </c>
       <c r="R259" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.523068220844532</v>
+        <v>13.145352640931875</v>
       </c>
       <c r="T259" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28381,7 +28388,7 @@
       </c>
       <c r="R260" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>40.141091744151382</v>
+        <v>40.09843965443612</v>
       </c>
       <c r="T260" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28438,7 +28445,7 @@
       </c>
       <c r="R261" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.2380966490513714</v>
+        <v>8.1306470931502073</v>
       </c>
       <c r="T261" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28495,7 +28502,7 @@
       </c>
       <c r="R262" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>50.789666155095816</v>
+        <v>50.730252946260258</v>
       </c>
       <c r="T262" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28552,7 +28559,7 @@
       </c>
       <c r="R263" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.79265615382338583</v>
+        <v>0.28454655255790251</v>
       </c>
       <c r="T263" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28609,7 +28616,7 @@
       </c>
       <c r="R264" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.83448650089098653</v>
+        <v>4.2378597596803624E-2</v>
       </c>
       <c r="T264" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28666,7 +28673,7 @@
       </c>
       <c r="R265" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.8484296858182114</v>
+        <v>7.7464485837642982</v>
       </c>
       <c r="T265" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28727,7 +28734,7 @@
       </c>
       <c r="R266" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>50.619874810930767</v>
+        <v>50.82442353200981</v>
       </c>
       <c r="T266" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28784,7 +28791,7 @@
       </c>
       <c r="R267" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.783485907647176</v>
+        <v>33.824719640601366</v>
       </c>
       <c r="T267" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28841,7 +28848,7 @@
       </c>
       <c r="R268" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>8.1409397119986853</v>
+        <v>7.9347903631015519</v>
       </c>
       <c r="T268" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28898,7 +28905,7 @@
       </c>
       <c r="R269" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.634020837095822</v>
+        <v>13.029704118184833</v>
       </c>
       <c r="T269" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -28955,7 +28962,7 @@
       </c>
       <c r="R270" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.140790172613235</v>
+        <v>13.022079251915626</v>
       </c>
       <c r="T270" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29012,7 +29019,7 @@
       </c>
       <c r="R271" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.609911156589558</v>
+        <v>13.495493902359806</v>
       </c>
       <c r="T271" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29087,7 +29094,7 @@
       </c>
       <c r="R272" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>75.647244240937596</v>
+        <v>75.180719185175803</v>
       </c>
       <c r="T272" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29144,7 +29151,7 @@
       </c>
       <c r="R273" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.933076717993535</v>
+        <v>13.020967300243079</v>
       </c>
       <c r="T273" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29201,7 +29208,7 @@
       </c>
       <c r="R274" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.798144005202296</v>
+        <v>13.314473589162985</v>
       </c>
       <c r="T274" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29258,7 +29265,7 @@
       </c>
       <c r="R275" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.1652878259952032</v>
+        <v>0.88684949254476697</v>
       </c>
       <c r="T275" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29315,7 +29322,7 @@
       </c>
       <c r="R276" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>34.181483436907477</v>
+        <v>33.730118352265869</v>
       </c>
       <c r="T276" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29372,7 +29379,7 @@
       </c>
       <c r="R277" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.569962987634867</v>
+        <v>13.361658686927763</v>
       </c>
       <c r="T277" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29429,7 +29436,7 @@
       </c>
       <c r="R278" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.181754353622635</v>
+        <v>13.077233562795259</v>
       </c>
       <c r="T278" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29489,7 +29496,7 @@
       </c>
       <c r="R279" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>50.43256635234998</v>
+        <v>50.082419940712178</v>
       </c>
       <c r="T279" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29546,7 +29553,7 @@
       </c>
       <c r="R280" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.77158982257095698</v>
+        <v>0.32654016767207306</v>
       </c>
       <c r="T280" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29603,7 +29610,7 @@
       </c>
       <c r="R281" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.43239755764225918</v>
+        <v>0.34384973059590684</v>
       </c>
       <c r="T281" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29664,7 +29671,7 @@
       </c>
       <c r="R282" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>9.5098905910106897</v>
+        <v>9.4426572206974733</v>
       </c>
       <c r="T282" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29733,7 +29740,7 @@
       </c>
       <c r="R283" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>57.365467244221101</v>
+        <v>58.093177546738062</v>
       </c>
       <c r="T283" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29791,7 +29798,7 @@
       </c>
       <c r="R284" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.174478029709849</v>
+        <v>20.256933960385417</v>
       </c>
       <c r="T284" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29848,7 +29855,7 @@
       </c>
       <c r="R285" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.44642712510688387</v>
+        <v>0.57271986031662347</v>
       </c>
       <c r="T285" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29908,7 +29915,7 @@
       </c>
       <c r="R286" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>10.099395202285073</v>
+        <v>10.923788128479023</v>
       </c>
       <c r="T286" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -29977,7 +29984,7 @@
       </c>
       <c r="R287" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>80.672945810549336</v>
+        <v>80.018980548855026</v>
       </c>
       <c r="T287" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30034,7 +30041,7 @@
       </c>
       <c r="R288" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.7691199303503158</v>
+        <v>7.9986169310589554</v>
       </c>
       <c r="T288" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30091,7 +30098,7 @@
       </c>
       <c r="R289" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.422502084682405</v>
+        <v>12.619636502279103</v>
       </c>
       <c r="T289" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30151,7 +30158,7 @@
       </c>
       <c r="R290" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>9.7713408555801529</v>
+        <v>9.5624675383867892</v>
       </c>
       <c r="T290" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30208,7 +30215,7 @@
       </c>
       <c r="R291" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.66176867932106698</v>
+        <v>0.14545625063866996</v>
       </c>
       <c r="T291" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30277,7 +30284,7 @@
       </c>
       <c r="R292" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>57.261431866317729</v>
+        <v>57.929554546578252</v>
       </c>
       <c r="T292" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30334,7 +30341,7 @@
       </c>
       <c r="R293" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.811635443279394</v>
+        <v>13.191622839225305</v>
       </c>
       <c r="T293" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30394,7 +30401,7 @@
       </c>
       <c r="R294" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>23.214646034781492</v>
+        <v>22.57651000900141</v>
       </c>
       <c r="T294" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30466,7 +30473,7 @@
       </c>
       <c r="R295" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>60.415869705487168</v>
+        <v>60.55667884841727</v>
       </c>
       <c r="T295" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30523,7 +30530,7 @@
       </c>
       <c r="R296" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.95644075102469062</v>
+        <v>0.45817611914300038</v>
       </c>
       <c r="T296" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30580,7 +30587,7 @@
       </c>
       <c r="R297" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>50.806063112203582</v>
+        <v>50.565300156291279</v>
       </c>
       <c r="T297" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30640,7 +30647,7 @@
       </c>
       <c r="R298" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>10.254597964867537</v>
+        <v>10.102782785558606</v>
       </c>
       <c r="T298" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30697,7 +30704,7 @@
       </c>
       <c r="R299" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.89027377773859084</v>
+        <v>0.35371308949951719</v>
       </c>
       <c r="T299" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30757,7 +30764,7 @@
       </c>
       <c r="R300" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.17315867533811757</v>
+        <v>0.15358549913119757</v>
       </c>
       <c r="T300" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30823,7 +30830,7 @@
       </c>
       <c r="R301" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>57.476280242727015</v>
+        <v>57.193721387938645</v>
       </c>
       <c r="T301" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30880,7 +30887,7 @@
       </c>
       <c r="R302" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.95982774931382131</v>
+        <v>0.19311031338217666</v>
       </c>
       <c r="T302" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30937,7 +30944,7 @@
       </c>
       <c r="R303" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.44084421057906764</v>
+        <v>0.34502949722903509</v>
       </c>
       <c r="T303" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -30994,7 +31001,7 @@
       </c>
       <c r="R304" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.20954773375644542</v>
+        <v>0.34343847409543693</v>
       </c>
       <c r="T304" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31051,7 +31058,7 @@
       </c>
       <c r="R305" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>3.4228776390137772E-2</v>
+        <v>0.1867812839034193</v>
       </c>
       <c r="T305" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31126,7 +31133,7 @@
       </c>
       <c r="R306" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>34.136118327310797</v>
+        <v>34.065051425193758</v>
       </c>
       <c r="T306" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31192,7 +31199,7 @@
       </c>
       <c r="R307" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.01109109667302</v>
+        <v>20.879817393946915</v>
       </c>
       <c r="T307" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31249,7 +31256,7 @@
       </c>
       <c r="R308" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.4505026395522076</v>
+        <v>0.83541392775817802</v>
       </c>
       <c r="T308" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31306,7 +31313,7 @@
       </c>
       <c r="R309" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>34.171325100294752</v>
+        <v>34.128487144202801</v>
       </c>
       <c r="T309" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31363,7 +31370,7 @@
       </c>
       <c r="R310" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>34.297380581647381</v>
+        <v>33.427617799130061</v>
       </c>
       <c r="T310" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31424,7 +31431,7 @@
       </c>
       <c r="R311" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>10.072147233200994</v>
+        <v>9.6068997984799172</v>
       </c>
       <c r="T311" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31482,7 +31489,7 @@
       </c>
       <c r="R312" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.12247151918561239</v>
+        <v>0.66048547025924709</v>
       </c>
       <c r="T312" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31539,7 +31546,7 @@
       </c>
       <c r="R313" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.68034532912708545</v>
+        <v>0.54514744370134849</v>
       </c>
       <c r="T313" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31596,7 +31603,7 @@
       </c>
       <c r="R314" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.9610009579873201</v>
+        <v>0.20658326750769918</v>
       </c>
       <c r="T314" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31653,7 +31660,7 @@
       </c>
       <c r="R315" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.915473812132689</v>
+        <v>13.227819907885429</v>
       </c>
       <c r="T315" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31711,7 +31718,7 @@
       </c>
       <c r="R316" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.64191572106481032</v>
+        <v>0.92126259066993577</v>
       </c>
       <c r="T316" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31769,7 +31776,7 @@
       </c>
       <c r="R317" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.32172013294367541</v>
+        <v>0.20945986377476422</v>
       </c>
       <c r="T317" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31827,7 +31834,7 @@
       </c>
       <c r="R318" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.33854808414355475</v>
+        <v>0.64468140706279509</v>
       </c>
       <c r="T318" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31885,7 +31892,7 @@
       </c>
       <c r="R319" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.65313823821370354</v>
+        <v>2.9487813776742033E-2</v>
       </c>
       <c r="T319" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -31943,7 +31950,7 @@
       </c>
       <c r="R320" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.75558302736451277</v>
+        <v>0.83477462509484046</v>
       </c>
       <c r="T320" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32001,7 +32008,7 @@
       </c>
       <c r="R321" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.759103195854088</v>
+        <v>33.765753782750899</v>
       </c>
       <c r="T321" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32061,7 +32068,7 @@
       </c>
       <c r="R322" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>23.028642666060268</v>
+        <v>23.122273759800819</v>
       </c>
       <c r="T322" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32121,7 +32128,7 @@
       </c>
       <c r="R323" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>22.414270285258098</v>
+        <v>22.724126310960923</v>
       </c>
       <c r="T323" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32178,7 +32185,7 @@
       </c>
       <c r="R324" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.18597204357835506</v>
+        <v>0.82827945910137613</v>
       </c>
       <c r="T324" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32235,7 +32242,7 @@
       </c>
       <c r="R325" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.94804673515096549</v>
+        <v>0.65555952767303127</v>
       </c>
       <c r="T325" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32302,7 +32309,7 @@
       </c>
       <c r="R326" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>17.434258851617024</v>
+        <v>17.471331120147958</v>
       </c>
       <c r="T326" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32360,7 +32367,7 @@
       </c>
       <c r="R327" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>50.573612422616748</v>
+        <v>50.348374742117237</v>
       </c>
       <c r="T327" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32417,7 +32424,7 @@
       </c>
       <c r="R328" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.304701595295159</v>
+        <v>13.390291801480615</v>
       </c>
       <c r="T328" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32474,7 +32481,7 @@
       </c>
       <c r="R329" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.542371503987917</v>
+        <v>13.411707004569418</v>
       </c>
       <c r="T329" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32534,7 +32541,7 @@
       </c>
       <c r="R330" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.699231353873873</v>
+        <v>20.028225001797058</v>
       </c>
       <c r="T330" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32603,7 +32610,7 @@
       </c>
       <c r="R331" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.45103642216727</v>
+        <v>20.754137805463859</v>
       </c>
       <c r="T331" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32663,7 +32670,7 @@
       </c>
       <c r="R332" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>22.897794438153444</v>
+        <v>22.973562347200261</v>
       </c>
       <c r="T332" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32729,7 +32736,7 @@
       </c>
       <c r="R333" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>34.079702508902692</v>
+        <v>33.849536576064594</v>
       </c>
       <c r="T333" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32787,7 +32794,7 @@
       </c>
       <c r="R334" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.90243732125001097</v>
+        <v>0.24876938635526269</v>
       </c>
       <c r="T334" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32847,7 +32854,7 @@
       </c>
       <c r="R335" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>34.252482005748618</v>
+        <v>33.506755355826421</v>
       </c>
       <c r="T335" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32910,7 +32917,7 @@
       </c>
       <c r="R336" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>67.404027058329561</v>
+        <v>66.692011475947936</v>
       </c>
       <c r="T336" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -32967,7 +32974,7 @@
       </c>
       <c r="R337" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.85395221561769086</v>
+        <v>0.67761420797102911</v>
       </c>
       <c r="T337" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33024,7 +33031,7 @@
       </c>
       <c r="R338" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.2913393497917935</v>
+        <v>7.9721435933584086</v>
       </c>
       <c r="T338" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33081,7 +33088,7 @@
       </c>
       <c r="R339" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.65369785937842</v>
+        <v>12.767864381567373</v>
       </c>
       <c r="T339" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33142,7 +33149,7 @@
       </c>
       <c r="R340" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>9.4100486171465825</v>
+        <v>9.0970860349902232</v>
       </c>
       <c r="T340" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33202,7 +33209,7 @@
       </c>
       <c r="R341" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>34.133033198472461</v>
+        <v>33.634672696683715</v>
       </c>
       <c r="T341" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33259,7 +33266,7 @@
       </c>
       <c r="R342" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>9.6816065928348127E-2</v>
+        <v>0.51423048030642249</v>
       </c>
       <c r="T342" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33316,7 +33323,7 @@
       </c>
       <c r="R343" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.931146020916627</v>
+        <v>13.263678251529873</v>
       </c>
       <c r="T343" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33376,7 +33383,7 @@
       </c>
       <c r="R344" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.30530269980764</v>
+        <v>20.439875555501292</v>
       </c>
       <c r="T344" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33433,7 +33440,7 @@
       </c>
       <c r="R345" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.370208276381106</v>
+        <v>12.740236961491027</v>
       </c>
       <c r="T345" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33490,7 +33497,7 @@
       </c>
       <c r="R346" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.309248450137201</v>
+        <v>20.117837137328753</v>
       </c>
       <c r="T346" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33565,7 +33572,7 @@
       </c>
       <c r="R347" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>34.000466387585028</v>
+        <v>34.067687157540306</v>
       </c>
       <c r="T347" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33625,7 +33632,7 @@
       </c>
       <c r="R348" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>22.27274186076</v>
+        <v>23.099445190747158</v>
       </c>
       <c r="T348" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33682,7 +33689,7 @@
       </c>
       <c r="R349" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.27305400778065536</v>
+        <v>0.77578955030352814</v>
       </c>
       <c r="T349" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33739,7 +33746,7 @@
       </c>
       <c r="R350" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.16619463960386394</v>
+        <v>0.25553172092921295</v>
       </c>
       <c r="T350" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33797,7 +33804,7 @@
       </c>
       <c r="R351" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.163060872632855</v>
+        <v>12.572103906401981</v>
       </c>
       <c r="T351" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33857,7 +33864,7 @@
       </c>
       <c r="R352" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>22.348301170037892</v>
+        <v>23.018889553714462</v>
       </c>
       <c r="T352" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33914,7 +33921,7 @@
       </c>
       <c r="R353" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.379563091144</v>
+        <v>34.132982230000295</v>
       </c>
       <c r="T353" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -33971,7 +33978,7 @@
       </c>
       <c r="R354" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>9.8424954184862634E-2</v>
+        <v>0.50207023962095654</v>
       </c>
       <c r="T354" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34040,7 +34047,7 @@
       </c>
       <c r="R355" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>60.220274609876824</v>
+        <v>60.809514501022832</v>
       </c>
       <c r="T355" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34101,7 +34108,7 @@
       </c>
       <c r="R356" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>9.3550539281434766</v>
+        <v>9.1440826488988822</v>
       </c>
       <c r="T356" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34159,7 +34166,7 @@
       </c>
       <c r="R357" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>34.117401740239529</v>
+        <v>34.069692707546501</v>
       </c>
       <c r="T357" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34216,7 +34223,7 @@
       </c>
       <c r="R358" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.105107725659112</v>
+        <v>13.226071355462629</v>
       </c>
       <c r="T358" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34273,7 +34280,7 @@
       </c>
       <c r="R359" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>40.780135285096499</v>
+        <v>40.605974778160395</v>
       </c>
       <c r="T359" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34331,7 +34338,7 @@
       </c>
       <c r="R360" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>6.1236657246757309E-2</v>
+        <v>0.98966990073162053</v>
       </c>
       <c r="T360" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34388,7 +34395,7 @@
       </c>
       <c r="R361" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.11613117525157568</v>
+        <v>0.8933296822749488</v>
       </c>
       <c r="T361" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34445,7 +34452,7 @@
       </c>
       <c r="R362" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.330889011446455</v>
+        <v>12.841183455866984</v>
       </c>
       <c r="T362" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34505,7 +34512,7 @@
       </c>
       <c r="R363" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>10.379875344491635</v>
+        <v>10.181840021546201</v>
       </c>
       <c r="T363" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34562,7 +34569,7 @@
       </c>
       <c r="R364" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.64984974795404271</v>
+        <v>0.45815435552154571</v>
       </c>
       <c r="T364" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34619,7 +34626,7 @@
       </c>
       <c r="R365" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.640478877399747</v>
+        <v>12.924699222449039</v>
       </c>
       <c r="T365" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34691,7 +34698,7 @@
       </c>
       <c r="R366" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.587705686425032</v>
+        <v>33.469229086323956</v>
       </c>
       <c r="T366" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34757,7 +34764,7 @@
       </c>
       <c r="R367" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>25.865413836572092</v>
+        <v>25.98746948265196</v>
       </c>
       <c r="T367" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34823,7 +34830,7 @@
       </c>
       <c r="R368" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>25.045250381339859</v>
+        <v>25.662215819874529</v>
       </c>
       <c r="T368" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34898,7 +34905,7 @@
       </c>
       <c r="R369" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.619807787343689</v>
+        <v>33.761203556753969</v>
       </c>
       <c r="T369" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -34958,7 +34965,7 @@
       </c>
       <c r="R370" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>23.206535439166949</v>
+        <v>22.335436538549729</v>
       </c>
       <c r="T370" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35015,7 +35022,7 @@
       </c>
       <c r="R371" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.700963790756031</v>
+        <v>12.681812400063743</v>
       </c>
       <c r="T371" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35072,7 +35079,7 @@
       </c>
       <c r="R372" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.389223096797432</v>
+        <v>13.482801986767154</v>
       </c>
       <c r="T372" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35129,7 +35136,7 @@
       </c>
       <c r="R373" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.48363837353425987</v>
+        <v>0.67195306475040084</v>
       </c>
       <c r="T373" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35186,7 +35193,7 @@
       </c>
       <c r="R374" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>1.7670023320933703E-2</v>
+        <v>0.44795698664712269</v>
       </c>
       <c r="T374" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35243,7 +35250,7 @@
       </c>
       <c r="R375" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.2704253264652223</v>
+        <v>7.5616236798151064</v>
       </c>
       <c r="T375" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35300,7 +35307,7 @@
       </c>
       <c r="R376" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.2212924071771418</v>
+        <v>8.1355737574679861</v>
       </c>
       <c r="T376" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35360,7 +35367,7 @@
       </c>
       <c r="R377" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>10.255023394906381</v>
+        <v>10.274173140295016</v>
       </c>
       <c r="T377" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35426,7 +35433,7 @@
       </c>
       <c r="R378" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.679898327216129</v>
+        <v>20.745403339306861</v>
       </c>
       <c r="T378" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35501,7 +35508,7 @@
       </c>
       <c r="R379" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.570681437350807</v>
+        <v>33.632690050128112</v>
       </c>
       <c r="T379" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35559,7 +35566,7 @@
       </c>
       <c r="R380" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.465249979151258</v>
+        <v>13.125032586505</v>
       </c>
       <c r="T380" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35616,7 +35623,7 @@
       </c>
       <c r="R381" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.136709074285937</v>
+        <v>13.017002102254994</v>
       </c>
       <c r="T381" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35682,7 +35689,7 @@
       </c>
       <c r="R382" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>25.719613302538686</v>
+        <v>25.381351475049655</v>
       </c>
       <c r="T382" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35740,7 +35747,7 @@
       </c>
       <c r="R383" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.5353665168427</v>
+        <v>20.617607165526067</v>
       </c>
       <c r="T383" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35797,7 +35804,7 @@
       </c>
       <c r="R384" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.89081991275970718</v>
+        <v>0.547084089136879</v>
       </c>
       <c r="T384" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35854,7 +35861,7 @@
       </c>
       <c r="R385" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>33.69126640377003</v>
+        <v>33.900266829918287</v>
       </c>
       <c r="T385" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35914,7 +35921,7 @@
       </c>
       <c r="R386" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>10.549920451789733</v>
+        <v>10.470303046464045</v>
       </c>
       <c r="T386" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -35971,7 +35978,7 @@
       </c>
       <c r="R387" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.062702462090591</v>
+        <v>12.619348420646794</v>
       </c>
       <c r="T387" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36029,7 +36036,7 @@
       </c>
       <c r="R388" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.586698372769316</v>
+        <v>20.18239141465013</v>
       </c>
       <c r="T388" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36086,7 +36093,7 @@
       </c>
       <c r="R389" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.68166326672901889</v>
+        <v>0.9666789940899887</v>
       </c>
       <c r="T389" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36143,7 +36150,7 @@
       </c>
       <c r="R390" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.8082872250326618</v>
+        <v>7.3727583268916348</v>
       </c>
       <c r="T390" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36200,7 +36207,7 @@
       </c>
       <c r="R391" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.20302049289909663</v>
+        <v>0.70917018901605344</v>
       </c>
       <c r="T391" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36258,7 +36265,7 @@
       </c>
       <c r="R392" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.952248348480841</v>
+        <v>13.312645480739093</v>
       </c>
       <c r="T392" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36315,7 +36322,7 @@
       </c>
       <c r="R393" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.6668862410479335</v>
+        <v>7.4787595972489225</v>
       </c>
       <c r="T393" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36372,7 +36379,7 @@
       </c>
       <c r="R394" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.6487880379306361</v>
+        <v>7.2864224195985567</v>
       </c>
       <c r="T394" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36438,7 +36445,7 @@
       </c>
       <c r="R395" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>25.589487525327584</v>
+        <v>25.222026465953984</v>
       </c>
       <c r="T395" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36495,7 +36502,7 @@
       </c>
       <c r="R396" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.62340631072047459</v>
+        <v>0.89557253430598061</v>
       </c>
       <c r="T396" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36561,7 +36568,7 @@
       </c>
       <c r="R397" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>25.985266895830666</v>
+        <v>25.122493939229177</v>
       </c>
       <c r="T397" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36618,7 +36625,7 @@
       </c>
       <c r="R398" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.298804621172742</v>
+        <v>13.263133667862709</v>
       </c>
       <c r="T398" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36685,7 +36692,7 @@
       </c>
       <c r="R399" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>17.20802102261376</v>
+        <v>17.415266914871346</v>
       </c>
       <c r="T399" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36743,7 +36750,7 @@
       </c>
       <c r="R400" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.17516613468821696</v>
+        <v>0.9987943563098397</v>
       </c>
       <c r="T400" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36813,7 +36820,7 @@
       </c>
       <c r="R401" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>17.501179394054926</v>
+        <v>17.66488174564579</v>
       </c>
       <c r="T401" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36870,7 +36877,7 @@
       </c>
       <c r="R402" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.330962114533564</v>
+        <v>12.940576427532054</v>
       </c>
       <c r="T402" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36934,7 +36941,7 @@
       </c>
       <c r="R403" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>17.642270119287407</v>
+        <v>17.531301150263012</v>
       </c>
       <c r="T403" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -36991,7 +36998,7 @@
       </c>
       <c r="R404" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.93359704630605767</v>
+        <v>0.8919790747974502</v>
       </c>
       <c r="T404" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37048,7 +37055,7 @@
       </c>
       <c r="R405" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>1.6130078417667892E-2</v>
+        <v>0.68233937759731345</v>
       </c>
       <c r="T405" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37105,7 +37112,7 @@
       </c>
       <c r="R406" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.2179587895442483</v>
+        <v>0.70548078892423915</v>
       </c>
       <c r="T406" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37162,7 +37169,7 @@
       </c>
       <c r="R407" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.9258252942002887</v>
+        <v>0.44077390664402516</v>
       </c>
       <c r="T407" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37219,7 +37226,7 @@
       </c>
       <c r="R408" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.67827266888615678</v>
+        <v>0.75049623519021236</v>
       </c>
       <c r="T408" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37277,7 +37284,7 @@
       </c>
       <c r="R409" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.361779293667581</v>
+        <v>12.991455485441994</v>
       </c>
       <c r="T409" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37337,7 +37344,7 @@
       </c>
       <c r="R410" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.4600153687701487</v>
+        <v>0.35674941383677938</v>
       </c>
       <c r="T410" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37394,7 +37401,7 @@
       </c>
       <c r="R411" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.93351412923991761</v>
+        <v>5.5544464331976684E-2</v>
       </c>
       <c r="T411" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37451,7 +37458,7 @@
       </c>
       <c r="R412" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>40.281252634195283</v>
+        <v>40.211457649164736</v>
       </c>
       <c r="T412" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37508,7 +37515,7 @@
       </c>
       <c r="R413" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.8565436137175393</v>
+        <v>7.4647831382447176</v>
       </c>
       <c r="T413" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37568,7 +37575,7 @@
       </c>
       <c r="R414" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>10.403674825290274</v>
+        <v>10.838597158730947</v>
       </c>
       <c r="T414" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37625,7 +37632,7 @@
       </c>
       <c r="R415" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.40823480056257322</v>
+        <v>4.5365641125158285E-2</v>
       </c>
       <c r="T415" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37686,7 +37693,7 @@
       </c>
       <c r="R416" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>9.9856708362534974</v>
+        <v>9.2847377289066273</v>
       </c>
       <c r="T416" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37747,7 +37754,7 @@
       </c>
       <c r="R417" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>9.4225799885267669</v>
+        <v>9.4479086791826266</v>
       </c>
       <c r="T417" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37804,7 +37811,7 @@
       </c>
       <c r="R418" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.63479464107753</v>
+        <v>7.1433344478397816</v>
       </c>
       <c r="T418" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37861,7 +37868,7 @@
       </c>
       <c r="R419" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>7.7356783323957439</v>
+        <v>7.6299587310770347</v>
       </c>
       <c r="T419" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37918,7 +37925,7 @@
       </c>
       <c r="R420" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.978625948757845</v>
+        <v>13.113278396103869</v>
       </c>
       <c r="T420" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -37975,7 +37982,7 @@
       </c>
       <c r="R421" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>66.945001150570633</v>
+        <v>66.748966333864132</v>
       </c>
       <c r="T421" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38036,7 +38043,7 @@
       </c>
       <c r="R422" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>9.7030246746381366</v>
+        <v>9.7432554886283036</v>
       </c>
       <c r="T422" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38094,7 +38101,7 @@
       </c>
       <c r="R423" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.441715792693293</v>
+        <v>12.57785941971062</v>
       </c>
       <c r="T423" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38152,7 +38159,7 @@
       </c>
       <c r="R424" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.22523384060518903</v>
+        <v>0.74235982310029547</v>
       </c>
       <c r="T424" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38213,7 +38220,7 @@
       </c>
       <c r="R425" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>9.1626301657322937</v>
+        <v>9.9369506433161092</v>
       </c>
       <c r="T425" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38274,7 +38281,7 @@
       </c>
       <c r="R426" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>9.3572550686718365</v>
+        <v>9.5112989175344431</v>
       </c>
       <c r="T426" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38332,7 +38339,7 @@
       </c>
       <c r="R427" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>13.278076727168314</v>
+        <v>13.016956304050696</v>
       </c>
       <c r="T427" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38402,7 +38409,7 @@
       </c>
       <c r="R428" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>17.101012048932692</v>
+        <v>16.699533252298995</v>
       </c>
       <c r="T428" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38462,7 +38469,7 @@
       </c>
       <c r="R429" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>10.935957750474852</v>
+        <v>10.148312746719881</v>
       </c>
       <c r="T429" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38519,7 +38526,7 @@
       </c>
       <c r="R430" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.94246693683397964</v>
+        <v>0.1866397921134012</v>
       </c>
       <c r="T430" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38576,7 +38583,7 @@
       </c>
       <c r="R431" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>12.65549313924633</v>
+        <v>12.778084671722921</v>
       </c>
       <c r="T431" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38633,7 +38640,7 @@
       </c>
       <c r="R432" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.524786797032192</v>
+        <v>0.71997443764758895</v>
       </c>
       <c r="T432" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38691,7 +38698,7 @@
       </c>
       <c r="R433" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.78023351371090333</v>
+        <v>0.71966690884014273</v>
       </c>
       <c r="T433" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38751,7 +38758,7 @@
       </c>
       <c r="R434" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.581932703138683</v>
+        <v>20.919778699541208</v>
       </c>
       <c r="T434" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38811,7 +38818,7 @@
       </c>
       <c r="R435" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.427519741089295</v>
+        <v>20.660846790815739</v>
       </c>
       <c r="T435" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38871,7 +38878,7 @@
       </c>
       <c r="R436" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.763740707837798</v>
+        <v>20.764356484439389</v>
       </c>
       <c r="T436" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38931,7 +38938,7 @@
       </c>
       <c r="R437" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.902567407202454</v>
+        <v>20.372631982850713</v>
       </c>
       <c r="T437" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -38991,7 +38998,7 @@
       </c>
       <c r="R438" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.372135403128468</v>
+        <v>20.691442178520919</v>
       </c>
       <c r="T438" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -39051,7 +39058,7 @@
       </c>
       <c r="R439" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>20.385751794767742</v>
+        <v>20.179849119034113</v>
       </c>
       <c r="T439" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -39126,7 +39133,7 @@
       </c>
       <c r="R440" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>34.288974493375044</v>
+        <v>34.321295609818918</v>
       </c>
       <c r="T440" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -39195,7 +39202,7 @@
       </c>
       <c r="R441" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>34.262576252033583</v>
+        <v>33.527681924058719</v>
       </c>
       <c r="T441" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -39614,7 +39621,7 @@
       </c>
       <c r="C4" s="7">
         <f ca="1">MATCH(C5,キャラ情報!C:C,0)</f>
-        <v>405</v>
+        <v>319</v>
       </c>
     </row>
     <row r="5" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -39623,7 +39630,7 @@
       </c>
       <c r="C5" s="6" t="str">
         <f ca="1">INDEX(キャラ情報!C:R,MATCH(MIN(キャラ情報!R:R),キャラ情報!R:R,0),1)</f>
-        <v>優音モフ</v>
+        <v>三色家のぼうしさん</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -39632,7 +39639,7 @@
       </c>
       <c r="C6" s="6" t="str">
         <f ca="1">INDEX(キャラ情報!C:R,MATCH(MIN(キャラ情報!R:R),キャラ情報!R:R,0),4)</f>
-        <v>https://sites.google.com/view/report1023</v>
+        <v>https://harujpg.wixsite.com/sanshoku</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -43109,11 +43116,11 @@
       </c>
       <c r="I63" s="19" t="str">
         <f>テーブル1[[#This Row],[種族タグ]]&amp;""</f>
-        <v>人間|ドッペルゲンガー</v>
+        <v>人間|怪異</v>
       </c>
       <c r="J63" s="19" t="str">
         <f>テーブル1[[#This Row],[モチーフタグ]]&amp;""</f>
-        <v/>
+        <v>ドッペルゲンガー</v>
       </c>
       <c r="K63" s="19" t="str">
         <f>テーブル1[[#This Row],[職業タグ]]&amp;""</f>

--- a/data/characters.xlsx
+++ b/data/characters.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\モノクロビリーフ\外部リンク\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E12CABE-3656-4797-B1DD-6F5A8F14B5A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E078B56-03CA-46F5-A07D-870B5C6EF9E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{78CF6334-6F78-4A6F-BD14-CB6FA7AB00CF}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2489" uniqueCount="1306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2554" uniqueCount="1322">
   <si>
     <t>番号</t>
   </si>
@@ -2831,13 +2831,6 @@
     <t>地磁気調査</t>
   </si>
   <si>
-    <t>イヤーユニット</t>
-  </si>
-  <si>
-    <t>イヤーユニット</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>バーチャル</t>
   </si>
   <si>
@@ -2853,10 +2846,6 @@
     <rPh sb="0" eb="2">
       <t>キカイ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>マスク</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -2978,10 +2967,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>アイバンド</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>書店員</t>
     <rPh sb="0" eb="3">
       <t>ショテンイン</t>
@@ -2990,9 +2975,6 @@
   </si>
   <si>
     <t>ヘッドセット</t>
-  </si>
-  <si>
-    <t>ヘッドセット</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -3018,14 +3000,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ヘッドホン</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ヘアピン</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ヤンキー</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -3054,13 +3028,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ゴーグル</t>
-  </si>
-  <si>
-    <t>ゴーグル</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>黒肌</t>
     <rPh sb="0" eb="2">
       <t>クロハダ</t>
@@ -3094,9 +3061,6 @@
   <si>
     <t>#夕焼け研究所</t>
     <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ヘッドホン</t>
   </si>
   <si>
     <t>〇 / 必要</t>
@@ -3185,9 +3149,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ヘアピン</t>
-  </si>
-  <si>
     <t>鳴上キョウ</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -3236,13 +3197,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>髪飾り</t>
-    <rPh sb="0" eb="2">
-      <t>カミカザ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>司祭</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -3290,13 +3244,6 @@
     <t>星</t>
     <rPh sb="0" eb="1">
       <t>ホシ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>杖</t>
-    <rPh sb="0" eb="1">
-      <t>ツエ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -3311,17 +3258,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>銃</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>骨</t>
-    <rPh sb="0" eb="1">
-      <t>ホネ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>人喰い</t>
     <rPh sb="0" eb="2">
       <t>ヒトク</t>
@@ -3333,10 +3269,6 @@
     <rPh sb="0" eb="3">
       <t>ハンザイシャ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ナイフ</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -3423,18 +3355,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>仮面</t>
-    <rPh sb="0" eb="2">
-      <t>カメン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>隻眼</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>耳標</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -3512,13 +3433,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ヘアピン、拡声器</t>
-    <rPh sb="5" eb="8">
-      <t>カクセイキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>バーチャル、キメラ</t>
   </si>
   <si>
@@ -3535,21 +3449,11 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ヘイロー、十字架</t>
-    <rPh sb="5" eb="8">
-      <t>ジュウジカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>人間、双子</t>
     <rPh sb="0" eb="2">
       <t>ニンゲン</t>
     </rPh>
     <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ヘアピン、眼鏡</t>
   </si>
   <si>
     <t>オッドアイ、ほくろ</t>
@@ -3568,16 +3472,6 @@
     <t>傷、ほくろ</t>
     <rPh sb="0" eb="1">
       <t>キズ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ピアス、首輪、指輪</t>
-    <rPh sb="4" eb="6">
-      <t>クビワ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ユビワ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -3595,24 +3489,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>宇宙人、元ヤン</t>
-    <rPh sb="0" eb="3">
-      <t>ウチュウジン</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>モト</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>サポーター、カウンセラー</t>
-  </si>
-  <si>
-    <t>ヘイロー、包帯</t>
-    <rPh sb="5" eb="7">
-      <t>ホウタイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>妖怪、長寿</t>
@@ -3640,9 +3517,6 @@
       <t>ガクセイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>リボン、カチューシャ</t>
   </si>
   <si>
     <t>インナーカラー、羽</t>
@@ -3723,13 +3597,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>カチューシャ、髪飾り</t>
-    <rPh sb="7" eb="9">
-      <t>カミカザ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>天使、長寿</t>
     <rPh sb="0" eb="2">
       <t>テンシ</t>
@@ -3738,9 +3605,6 @@
       <t>チョウジュ</t>
     </rPh>
     <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ヘイロー、カチューシャ</t>
   </si>
   <si>
     <t>羽、尖耳、ギザ歯</t>
@@ -3832,28 +3696,11 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>イヤーユニット、鍵</t>
-    <rPh sb="8" eb="9">
-      <t>カギ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>グラデーションカラー、まろ眉</t>
   </si>
   <si>
-    <t>ピアス、首輪</t>
-    <rPh sb="4" eb="6">
-      <t>クビワ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>灰咲囁</t>
     <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>耳標</t>
   </si>
   <si>
     <t>ツートンカラー</t>
@@ -3943,13 +3790,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>鍵</t>
-    <rPh sb="0" eb="1">
-      <t>カギ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>メッシュ、両目隠れ</t>
     <rPh sb="5" eb="7">
       <t>リョウメ</t>
@@ -3991,13 +3831,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>拳銃</t>
-    <rPh sb="0" eb="2">
-      <t>ケンジュウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ちくさ</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -4095,16 +3928,6 @@
   </si>
   <si>
     <t>#APUDANG</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>包帯、注射器</t>
-    <rPh sb="0" eb="2">
-      <t>ホウタイ</t>
-    </rPh>
-    <rPh sb="3" eb="6">
-      <t>チュウシャキ</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -5280,10 +5103,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ヘイロー、ボタン</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ケモ耳、片目隠れ、尻尾</t>
     <rPh sb="4" eb="6">
       <t>カタメ</t>
@@ -5448,16 +5267,206 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ヘッドセット、眼鏡、マフラー</t>
-    <rPh sb="7" eb="9">
-      <t>メガネ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>歌手</t>
     <rPh sb="0" eb="2">
       <t>カシュ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>終歌カツエα</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>有部音ゴエμ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>うぶおん ごえ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Ubuon Goe</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>しゅうた かつえ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Shuta Katsue</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>鳴音ベルy</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>なるね べる</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Narune Bell</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>型式番号α-01</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>けいしきばんごうα-01</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>keishikibangoα-01</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>一色スウ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>いっしき すう</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Isshiki Su</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>亜音サイコ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>つぎね さいこ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Tsugine Saiko</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://aisupiku.wixsite.com/tsuginesaiko</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>#亜音サイコ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>http://utau.wikidot.com/utau:isshiki-suu</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>#一色スウ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アーティスト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">#返り子の町 </t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://nagimachi.wixsite.com/kairikonomachi</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ベル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>環境音</t>
+    <rPh sb="0" eb="3">
+      <t>カンキョウオン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>髪飾り</t>
+  </si>
+  <si>
+    <t>眼部</t>
+  </si>
+  <si>
+    <t>眼部</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>仮面・マスク</t>
+  </si>
+  <si>
+    <t>耳装備</t>
+  </si>
+  <si>
+    <t>髪飾り、眼部</t>
+  </si>
+  <si>
+    <t>髪飾り</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>髪飾り、耳装備</t>
+  </si>
+  <si>
+    <t>リボン、髪飾り</t>
+  </si>
+  <si>
+    <t>ヘイロー、髪飾り</t>
+  </si>
+  <si>
+    <t>耳装備、眼部、首装飾</t>
+  </si>
+  <si>
+    <t>ヘイロー、首装飾</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>装身具、首装飾</t>
+  </si>
+  <si>
+    <t>武器</t>
+  </si>
+  <si>
+    <t>武器</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>道具</t>
+  </si>
+  <si>
+    <t>道具</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>耳装備、道具</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>髪飾り、道具</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ヘイロー、服飾</t>
+  </si>
+  <si>
+    <t>ヘイロー、服飾</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>服飾、道具</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>モチーフ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>警察官、元ヤン</t>
+    <rPh sb="0" eb="3">
+      <t>ケイサツカン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -6943,10 +6952,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AFDEA6E0-6891-40ED-8736-87CEEF9CED2F}" name="テーブル1" displayName="テーブル1" ref="A1:Y263" headerRowDxfId="71" dataDxfId="70" tableBorderDxfId="69">
-  <autoFilter ref="A1:Y263" xr:uid="{AFDEA6E0-6891-40ED-8736-87CEEF9CED2F}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Y263">
-    <sortCondition ref="A1:A263"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AFDEA6E0-6891-40ED-8736-87CEEF9CED2F}" name="テーブル1" displayName="テーブル1" ref="A1:Y269" headerRowDxfId="71" dataDxfId="70" tableBorderDxfId="69">
+  <autoFilter ref="A1:Y269" xr:uid="{AFDEA6E0-6891-40ED-8736-87CEEF9CED2F}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Y269">
+    <sortCondition ref="A1:A269"/>
   </sortState>
   <tableColumns count="25">
     <tableColumn id="7" xr3:uid="{9D671CE8-205F-4EC4-AF57-C49043815D5D}" name="番号" totalsRowLabel="集計" dataDxfId="68" totalsRowDxfId="67"/>
@@ -7002,8 +7011,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{E4C87AB3-D453-4364-A868-37CD257B126C}" name="テーブル2" displayName="テーブル2" ref="A1:M263" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
-  <autoFilter ref="A1:M263" xr:uid="{E4C87AB3-D453-4364-A868-37CD257B126C}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{E4C87AB3-D453-4364-A868-37CD257B126C}" name="テーブル2" displayName="テーブル2" ref="A1:M269" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
+  <autoFilter ref="A1:M269" xr:uid="{E4C87AB3-D453-4364-A868-37CD257B126C}"/>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{1E92C13E-0744-4588-9D96-A833A7BD4B23}" name="id" dataDxfId="18">
       <calculatedColumnFormula>テーブル1[[#This Row],[番号]]</calculatedColumnFormula>
@@ -7367,7 +7376,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AF4E8EB-3C8D-4E6A-9E6F-612216DEE289}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:Y263"/>
+  <dimension ref="A1:Y280"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="6.86328125" style="20" bestFit="1" customWidth="1"/>
@@ -7423,7 +7432,7 @@
         <v>663</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>753</v>
+        <v>742</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>664</v>
@@ -7483,10 +7492,10 @@
         <v>460</v>
       </c>
       <c r="D2" s="23" t="s">
-        <v>913</v>
+        <v>880</v>
       </c>
       <c r="E2" s="23" t="s">
-        <v>1081</v>
+        <v>1048</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>149</v>
@@ -7561,10 +7570,10 @@
         <v>461</v>
       </c>
       <c r="D3" s="23" t="s">
-        <v>914</v>
+        <v>881</v>
       </c>
       <c r="E3" s="23" t="s">
-        <v>1082</v>
+        <v>1049</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>129</v>
@@ -7582,10 +7591,10 @@
         <v>668</v>
       </c>
       <c r="L3" s="23" t="s">
-        <v>670</v>
+        <v>1300</v>
       </c>
       <c r="M3" s="23" t="s">
-        <v>797</v>
+        <v>779</v>
       </c>
       <c r="O3" s="1" t="s">
         <v>549</v>
@@ -7657,16 +7666,16 @@
         <v>661</v>
       </c>
       <c r="I4" s="23" t="s">
-        <v>798</v>
+        <v>780</v>
       </c>
       <c r="J4" s="23" t="s">
-        <v>749</v>
+        <v>738</v>
       </c>
       <c r="K4" s="23" t="s">
         <v>672</v>
       </c>
       <c r="M4" s="23" t="s">
-        <v>799</v>
+        <v>781</v>
       </c>
       <c r="N4" s="1" t="s">
         <v>595</v>
@@ -7726,10 +7735,10 @@
         <v>142</v>
       </c>
       <c r="D5" s="23" t="s">
-        <v>915</v>
+        <v>882</v>
       </c>
       <c r="E5" s="23" t="s">
-        <v>1083</v>
+        <v>1050</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>143</v>
@@ -7741,10 +7750,10 @@
         <v>660</v>
       </c>
       <c r="I5" s="23" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="L5" s="23" t="s">
-        <v>675</v>
+        <v>1302</v>
       </c>
       <c r="O5" s="1" t="s">
         <v>549</v>
@@ -7801,10 +7810,10 @@
         <v>230</v>
       </c>
       <c r="D6" s="23" t="s">
-        <v>916</v>
+        <v>883</v>
       </c>
       <c r="E6" s="23" t="s">
-        <v>1084</v>
+        <v>1051</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>231</v>
@@ -7816,16 +7825,16 @@
         <v>660</v>
       </c>
       <c r="I6" s="23" t="s">
-        <v>1266</v>
+        <v>1233</v>
       </c>
       <c r="J6" s="23" t="s">
-        <v>750</v>
+        <v>739</v>
       </c>
       <c r="L6" s="23" t="s">
-        <v>789</v>
+        <v>1301</v>
       </c>
       <c r="M6" s="23" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="O6" s="1" t="s">
         <v>549</v>
@@ -7894,7 +7903,7 @@
         <v>113</v>
       </c>
       <c r="H7" s="23" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="I7" s="23" t="s">
         <v>669</v>
@@ -7954,10 +7963,10 @@
         <v>197</v>
       </c>
       <c r="D8" s="23" t="s">
-        <v>917</v>
+        <v>884</v>
       </c>
       <c r="E8" s="23" t="s">
-        <v>1085</v>
+        <v>1052</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>198</v>
@@ -7966,16 +7975,16 @@
         <v>199</v>
       </c>
       <c r="H8" s="23" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="I8" s="23" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="L8" s="23" t="s">
-        <v>670</v>
+        <v>1300</v>
       </c>
       <c r="M8" s="23" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="N8" s="1" t="s">
         <v>594</v>
@@ -8035,10 +8044,10 @@
         <v>248</v>
       </c>
       <c r="D9" s="23" t="s">
-        <v>918</v>
+        <v>885</v>
       </c>
       <c r="E9" s="23" t="s">
-        <v>1086</v>
+        <v>1053</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>249</v>
@@ -8050,10 +8059,10 @@
         <v>660</v>
       </c>
       <c r="I9" s="23" t="s">
-        <v>800</v>
+        <v>782</v>
       </c>
       <c r="M9" s="23" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="O9" s="1" t="s">
         <v>549</v>
@@ -8110,10 +8119,10 @@
         <v>194</v>
       </c>
       <c r="D10" s="23" t="s">
-        <v>919</v>
+        <v>886</v>
       </c>
       <c r="E10" s="23" t="s">
-        <v>1087</v>
+        <v>1054</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>195</v>
@@ -8128,13 +8137,13 @@
         <v>669</v>
       </c>
       <c r="J10" s="23" t="s">
-        <v>751</v>
+        <v>740</v>
       </c>
       <c r="L10" s="23" t="s">
-        <v>746</v>
+        <v>1298</v>
       </c>
       <c r="M10" s="23" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="O10" s="1" t="s">
         <v>549</v>
@@ -8206,10 +8215,10 @@
         <v>661</v>
       </c>
       <c r="I11" s="23" t="s">
-        <v>801</v>
+        <v>783</v>
       </c>
       <c r="M11" s="23" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="O11" s="1" t="s">
         <v>549</v>
@@ -8266,10 +8275,10 @@
         <v>234</v>
       </c>
       <c r="D12" s="23" t="s">
-        <v>920</v>
+        <v>887</v>
       </c>
       <c r="E12" s="23" t="s">
-        <v>1088</v>
+        <v>1055</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>235</v>
@@ -8284,10 +8293,10 @@
         <v>669</v>
       </c>
       <c r="K12" s="23" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="L12" s="23" t="s">
-        <v>670</v>
+        <v>1300</v>
       </c>
       <c r="N12" s="1" t="s">
         <v>631</v>
@@ -8347,10 +8356,10 @@
         <v>274</v>
       </c>
       <c r="D13" s="23" t="s">
-        <v>921</v>
+        <v>888</v>
       </c>
       <c r="E13" s="23" t="s">
-        <v>1089</v>
+        <v>1056</v>
       </c>
       <c r="F13" s="23" t="s">
         <v>279</v>
@@ -8362,7 +8371,7 @@
         <v>660</v>
       </c>
       <c r="L13" s="23" t="s">
-        <v>707</v>
+        <v>1302</v>
       </c>
       <c r="N13" s="1" t="s">
         <v>592</v>
@@ -8437,13 +8446,13 @@
         <v>660</v>
       </c>
       <c r="I14" s="23" t="s">
-        <v>708</v>
+        <v>703</v>
       </c>
       <c r="J14" s="23" t="s">
-        <v>752</v>
+        <v>741</v>
       </c>
       <c r="M14" s="23" t="s">
-        <v>709</v>
+        <v>704</v>
       </c>
       <c r="O14" s="1" t="s">
         <v>549</v>
@@ -8500,10 +8509,10 @@
         <v>233</v>
       </c>
       <c r="D15" s="23" t="s">
-        <v>922</v>
+        <v>889</v>
       </c>
       <c r="E15" s="23" t="s">
-        <v>1090</v>
+        <v>1057</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>231</v>
@@ -8515,13 +8524,13 @@
         <v>661</v>
       </c>
       <c r="I15" s="23" t="s">
-        <v>802</v>
+        <v>784</v>
       </c>
       <c r="K15" s="23" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="M15" s="23" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="O15" s="1" t="s">
         <v>549</v>
@@ -8593,13 +8602,13 @@
         <v>660</v>
       </c>
       <c r="I16" s="23" t="s">
-        <v>710</v>
+        <v>705</v>
       </c>
       <c r="K16" s="23" t="s">
-        <v>711</v>
+        <v>706</v>
       </c>
       <c r="M16" s="23" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="N16" s="1" t="s">
         <v>594</v>
@@ -8659,10 +8668,10 @@
         <v>593</v>
       </c>
       <c r="D17" s="23" t="s">
-        <v>923</v>
+        <v>890</v>
       </c>
       <c r="E17" s="23" t="s">
-        <v>1091</v>
+        <v>1058</v>
       </c>
       <c r="F17" s="15" t="s">
         <v>611</v>
@@ -8671,13 +8680,13 @@
         <v>276</v>
       </c>
       <c r="H17" s="23" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="I17" s="23" t="s">
-        <v>859</v>
+        <v>829</v>
       </c>
       <c r="L17" s="23" t="s">
-        <v>860</v>
+        <v>1314</v>
       </c>
       <c r="N17" s="1" t="s">
         <v>594</v>
@@ -8737,10 +8746,10 @@
         <v>277</v>
       </c>
       <c r="D18" s="23" t="s">
-        <v>924</v>
+        <v>891</v>
       </c>
       <c r="E18" s="23" t="s">
-        <v>1092</v>
+        <v>1059</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>611</v>
@@ -8749,16 +8758,16 @@
         <v>276</v>
       </c>
       <c r="H18" s="23" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="I18" s="23" t="s">
-        <v>859</v>
+        <v>829</v>
       </c>
       <c r="K18" s="23" t="s">
-        <v>714</v>
+        <v>707</v>
       </c>
       <c r="L18" s="23" t="s">
-        <v>860</v>
+        <v>1314</v>
       </c>
       <c r="N18" s="1" t="s">
         <v>594</v>
@@ -8821,10 +8830,10 @@
         <v>38</v>
       </c>
       <c r="E19" s="23" t="s">
-        <v>1093</v>
+        <v>1060</v>
       </c>
       <c r="F19" s="15" t="s">
-        <v>715</v>
+        <v>708</v>
       </c>
       <c r="G19" s="23" t="s">
         <v>39</v>
@@ -8833,7 +8842,7 @@
         <v>660</v>
       </c>
       <c r="L19" s="23" t="s">
-        <v>803</v>
+        <v>1316</v>
       </c>
       <c r="N19" s="1" t="s">
         <v>595</v>
@@ -8893,10 +8902,10 @@
         <v>102</v>
       </c>
       <c r="D20" s="23" t="s">
-        <v>925</v>
+        <v>892</v>
       </c>
       <c r="E20" s="23" t="s">
-        <v>1094</v>
+        <v>1061</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>103</v>
@@ -8905,13 +8914,13 @@
         <v>104</v>
       </c>
       <c r="H20" s="23" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="I20" s="23" t="s">
-        <v>804</v>
+        <v>785</v>
       </c>
       <c r="L20" s="23" t="s">
-        <v>675</v>
+        <v>1302</v>
       </c>
       <c r="O20" s="1" t="s">
         <v>549</v>
@@ -8968,10 +8977,10 @@
         <v>105</v>
       </c>
       <c r="D21" s="23" t="s">
-        <v>926</v>
+        <v>893</v>
       </c>
       <c r="E21" s="23" t="s">
-        <v>1095</v>
+        <v>1062</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>103</v>
@@ -8980,10 +8989,10 @@
         <v>106</v>
       </c>
       <c r="H21" s="23" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="I21" s="23" t="s">
-        <v>804</v>
+        <v>785</v>
       </c>
       <c r="O21" s="1" t="s">
         <v>549</v>
@@ -9040,10 +9049,10 @@
         <v>517</v>
       </c>
       <c r="D22" s="23" t="s">
-        <v>927</v>
+        <v>894</v>
       </c>
       <c r="E22" s="23" t="s">
-        <v>1096</v>
+        <v>1063</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>329</v>
@@ -9055,10 +9064,10 @@
         <v>660</v>
       </c>
       <c r="I22" s="23" t="s">
-        <v>717</v>
+        <v>710</v>
       </c>
       <c r="M22" s="23" t="s">
-        <v>805</v>
+        <v>786</v>
       </c>
       <c r="N22" s="1" t="s">
         <v>594</v>
@@ -9136,13 +9145,13 @@
         <v>669</v>
       </c>
       <c r="K23" s="23" t="s">
-        <v>757</v>
+        <v>745</v>
       </c>
       <c r="L23" s="23" t="s">
-        <v>806</v>
+        <v>1309</v>
       </c>
       <c r="M23" s="23" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="N23" s="1" t="s">
         <v>631</v>
@@ -9214,13 +9223,13 @@
         <v>199</v>
       </c>
       <c r="H24" s="23" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="I24" s="23" t="s">
-        <v>807</v>
+        <v>787</v>
       </c>
       <c r="L24" s="23" t="s">
-        <v>670</v>
+        <v>1300</v>
       </c>
       <c r="N24" s="1" t="s">
         <v>594</v>
@@ -9295,13 +9304,13 @@
         <v>661</v>
       </c>
       <c r="I25" s="23" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="L25" s="23" t="s">
-        <v>808</v>
+        <v>1303</v>
       </c>
       <c r="M25" s="23" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="N25" s="1" t="s">
         <v>631</v>
@@ -9361,10 +9370,10 @@
         <v>85</v>
       </c>
       <c r="D26" s="23" t="s">
-        <v>928</v>
+        <v>895</v>
       </c>
       <c r="E26" s="23" t="s">
-        <v>1097</v>
+        <v>1064</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>86</v>
@@ -9379,10 +9388,10 @@
         <v>669</v>
       </c>
       <c r="K26" s="23" t="s">
-        <v>762</v>
+        <v>750</v>
       </c>
       <c r="M26" s="23" t="s">
-        <v>809</v>
+        <v>788</v>
       </c>
       <c r="N26" s="1" t="s">
         <v>631</v>
@@ -9442,10 +9451,10 @@
         <v>88</v>
       </c>
       <c r="D27" s="23" t="s">
-        <v>929</v>
+        <v>896</v>
       </c>
       <c r="E27" s="23" t="s">
-        <v>1098</v>
+        <v>1065</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>86</v>
@@ -9460,10 +9469,10 @@
         <v>669</v>
       </c>
       <c r="K27" s="23" t="s">
-        <v>762</v>
+        <v>750</v>
       </c>
       <c r="M27" s="23" t="s">
-        <v>764</v>
+        <v>752</v>
       </c>
       <c r="N27" s="1" t="s">
         <v>631</v>
@@ -9523,28 +9532,28 @@
         <v>46</v>
       </c>
       <c r="D28" s="23" t="s">
-        <v>930</v>
+        <v>897</v>
       </c>
       <c r="E28" s="23" t="s">
-        <v>1099</v>
+        <v>1066</v>
       </c>
       <c r="F28" s="15" t="s">
-        <v>765</v>
+        <v>753</v>
       </c>
       <c r="G28" s="23" t="s">
         <v>47</v>
       </c>
       <c r="H28" s="23" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="I28" s="23" t="s">
         <v>669</v>
       </c>
       <c r="J28" s="23" t="s">
-        <v>767</v>
+        <v>755</v>
       </c>
       <c r="K28" s="23" t="s">
-        <v>766</v>
+        <v>754</v>
       </c>
       <c r="N28" s="1" t="s">
         <v>594</v>
@@ -9604,10 +9613,10 @@
         <v>520</v>
       </c>
       <c r="D29" s="23" t="s">
-        <v>931</v>
+        <v>898</v>
       </c>
       <c r="E29" s="23" t="s">
-        <v>1100</v>
+        <v>1067</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>90</v>
@@ -9676,10 +9685,10 @@
         <v>521</v>
       </c>
       <c r="D30" s="23" t="s">
-        <v>932</v>
+        <v>899</v>
       </c>
       <c r="E30" s="23" t="s">
-        <v>1101</v>
+        <v>1068</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>90</v>
@@ -9688,13 +9697,13 @@
         <v>91</v>
       </c>
       <c r="H30" s="23" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="I30" s="23" t="s">
         <v>669</v>
       </c>
       <c r="L30" s="23" t="s">
-        <v>770</v>
+        <v>1311</v>
       </c>
       <c r="O30" s="1" t="s">
         <v>549</v>
@@ -9766,7 +9775,7 @@
         <v>660</v>
       </c>
       <c r="I31" s="23" t="s">
-        <v>716</v>
+        <v>709</v>
       </c>
       <c r="O31" s="1" t="s">
         <v>549</v>
@@ -9823,10 +9832,10 @@
         <v>523</v>
       </c>
       <c r="D32" s="23" t="s">
-        <v>933</v>
+        <v>900</v>
       </c>
       <c r="E32" s="23" t="s">
-        <v>1102</v>
+        <v>1069</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>198</v>
@@ -9838,16 +9847,16 @@
         <v>660</v>
       </c>
       <c r="I32" s="23" t="s">
-        <v>810</v>
+        <v>789</v>
       </c>
       <c r="K32" s="23" t="s">
+        <v>687</v>
+      </c>
+      <c r="L32" s="23" t="s">
+        <v>689</v>
+      </c>
+      <c r="M32" s="23" t="s">
         <v>690</v>
-      </c>
-      <c r="L32" s="23" t="s">
-        <v>692</v>
-      </c>
-      <c r="M32" s="23" t="s">
-        <v>693</v>
       </c>
       <c r="N32" s="1" t="s">
         <v>594</v>
@@ -9907,10 +9916,10 @@
         <v>175</v>
       </c>
       <c r="D33" s="23" t="s">
-        <v>934</v>
+        <v>901</v>
       </c>
       <c r="E33" s="23" t="s">
-        <v>1103</v>
+        <v>1070</v>
       </c>
       <c r="F33" s="15" t="s">
         <v>176</v>
@@ -9922,16 +9931,16 @@
         <v>661</v>
       </c>
       <c r="I33" s="23" t="s">
-        <v>849</v>
+        <v>819</v>
       </c>
       <c r="K33" s="23" t="s">
-        <v>773</v>
+        <v>758</v>
       </c>
       <c r="L33" s="23" t="s">
-        <v>774</v>
+        <v>1311</v>
       </c>
       <c r="M33" s="23" t="s">
-        <v>811</v>
+        <v>790</v>
       </c>
       <c r="N33" s="1" t="s">
         <v>631</v>
@@ -9991,13 +10000,13 @@
         <v>48</v>
       </c>
       <c r="D34" s="23" t="s">
-        <v>935</v>
+        <v>902</v>
       </c>
       <c r="E34" s="23" t="s">
-        <v>1104</v>
+        <v>1071</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>765</v>
+        <v>753</v>
       </c>
       <c r="G34" s="23" t="s">
         <v>47</v>
@@ -10009,10 +10018,10 @@
         <v>669</v>
       </c>
       <c r="L34" s="23" t="s">
-        <v>812</v>
+        <v>1310</v>
       </c>
       <c r="M34" s="23" t="s">
-        <v>813</v>
+        <v>791</v>
       </c>
       <c r="N34" s="1" t="s">
         <v>594</v>
@@ -10072,10 +10081,10 @@
         <v>524</v>
       </c>
       <c r="D35" s="23" t="s">
-        <v>936</v>
+        <v>903</v>
       </c>
       <c r="E35" s="23" t="s">
-        <v>1105</v>
+        <v>1072</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>246</v>
@@ -10087,16 +10096,16 @@
         <v>661</v>
       </c>
       <c r="I35" s="23" t="s">
-        <v>801</v>
+        <v>783</v>
       </c>
       <c r="K35" s="23" t="s">
-        <v>772</v>
+        <v>757</v>
       </c>
       <c r="L35" s="23" t="s">
-        <v>771</v>
+        <v>1320</v>
       </c>
       <c r="M35" s="23" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="O35" s="1" t="s">
         <v>549</v>
@@ -10153,10 +10162,10 @@
         <v>178</v>
       </c>
       <c r="D36" s="23" t="s">
-        <v>937</v>
+        <v>904</v>
       </c>
       <c r="E36" s="23" t="s">
-        <v>1106</v>
+        <v>1073</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>176</v>
@@ -10168,16 +10177,16 @@
         <v>661</v>
       </c>
       <c r="I36" s="23" t="s">
-        <v>814</v>
+        <v>747</v>
       </c>
       <c r="K36" s="23" t="s">
-        <v>775</v>
+        <v>1321</v>
       </c>
       <c r="L36" s="23" t="s">
-        <v>808</v>
+        <v>1303</v>
       </c>
       <c r="M36" s="23" t="s">
-        <v>776</v>
+        <v>760</v>
       </c>
       <c r="N36" s="1" t="s">
         <v>631</v>
@@ -10237,16 +10246,16 @@
         <v>71</v>
       </c>
       <c r="D37" s="23" t="s">
-        <v>938</v>
+        <v>905</v>
       </c>
       <c r="E37" s="23" t="s">
-        <v>1107</v>
+        <v>1074</v>
       </c>
       <c r="F37" s="15" t="s">
         <v>72</v>
       </c>
       <c r="G37" s="23" t="s">
-        <v>1252</v>
+        <v>1219</v>
       </c>
       <c r="H37" s="23" t="s">
         <v>661</v>
@@ -10255,10 +10264,10 @@
         <v>669</v>
       </c>
       <c r="K37" s="23" t="s">
-        <v>761</v>
+        <v>749</v>
       </c>
       <c r="L37" s="23" t="s">
-        <v>746</v>
+        <v>1298</v>
       </c>
       <c r="N37" s="1" t="s">
         <v>594</v>
@@ -10318,10 +10327,10 @@
         <v>525</v>
       </c>
       <c r="D38" s="23" t="s">
-        <v>939</v>
+        <v>906</v>
       </c>
       <c r="E38" s="23" t="s">
-        <v>1108</v>
+        <v>1075</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>167</v>
@@ -10333,13 +10342,13 @@
         <v>660</v>
       </c>
       <c r="I38" s="23" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="K38" s="23" t="s">
-        <v>815</v>
+        <v>792</v>
       </c>
       <c r="M38" s="23" t="s">
-        <v>781</v>
+        <v>765</v>
       </c>
       <c r="N38" s="1" t="s">
         <v>631</v>
@@ -10489,7 +10498,7 @@
         <v>669</v>
       </c>
       <c r="K40" s="23" t="s">
-        <v>777</v>
+        <v>761</v>
       </c>
       <c r="N40" s="1" t="s">
         <v>595</v>
@@ -10549,10 +10558,10 @@
         <v>107</v>
       </c>
       <c r="D41" s="23" t="s">
-        <v>940</v>
+        <v>907</v>
       </c>
       <c r="E41" s="23" t="s">
-        <v>1109</v>
+        <v>1076</v>
       </c>
       <c r="F41" s="30" t="s">
         <v>108</v>
@@ -10639,10 +10648,10 @@
         <v>669</v>
       </c>
       <c r="L42" s="23" t="s">
-        <v>816</v>
+        <v>1318</v>
       </c>
       <c r="M42" s="23" t="s">
-        <v>758</v>
+        <v>746</v>
       </c>
       <c r="N42" s="1" t="s">
         <v>631</v>
@@ -10777,10 +10786,10 @@
         <v>526</v>
       </c>
       <c r="D44" s="23" t="s">
-        <v>941</v>
+        <v>908</v>
       </c>
       <c r="E44" s="23" t="s">
-        <v>1110</v>
+        <v>1077</v>
       </c>
       <c r="F44" s="27" t="s">
         <v>57</v>
@@ -10792,13 +10801,13 @@
         <v>661</v>
       </c>
       <c r="I44" s="23" t="s">
-        <v>817</v>
+        <v>793</v>
       </c>
       <c r="J44" s="23" t="s">
-        <v>788</v>
+        <v>772</v>
       </c>
       <c r="M44" s="23" t="s">
-        <v>818</v>
+        <v>794</v>
       </c>
       <c r="N44" s="1" t="s">
         <v>595</v>
@@ -10876,10 +10885,10 @@
         <v>669</v>
       </c>
       <c r="K45" s="23" t="s">
-        <v>777</v>
+        <v>761</v>
       </c>
       <c r="L45" s="23" t="s">
-        <v>681</v>
+        <v>1301</v>
       </c>
       <c r="O45" s="1" t="s">
         <v>549</v>
@@ -10936,10 +10945,10 @@
         <v>528</v>
       </c>
       <c r="D46" s="23" t="s">
-        <v>942</v>
+        <v>909</v>
       </c>
       <c r="E46" s="23" t="s">
-        <v>1111</v>
+        <v>1078</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>66</v>
@@ -10954,10 +10963,10 @@
         <v>669</v>
       </c>
       <c r="K46" s="23" t="s">
-        <v>819</v>
+        <v>795</v>
       </c>
       <c r="L46" s="23" t="s">
-        <v>820</v>
+        <v>1306</v>
       </c>
       <c r="N46" s="1" t="s">
         <v>594</v>
@@ -11017,10 +11026,10 @@
         <v>529</v>
       </c>
       <c r="D47" s="23" t="s">
-        <v>943</v>
+        <v>910</v>
       </c>
       <c r="E47" s="23" t="s">
-        <v>1112</v>
+        <v>1079</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>158</v>
@@ -11098,13 +11107,13 @@
         <v>660</v>
       </c>
       <c r="I48" s="23" t="s">
-        <v>782</v>
+        <v>766</v>
       </c>
       <c r="L48" s="23" t="s">
-        <v>756</v>
+        <v>1304</v>
       </c>
       <c r="M48" s="23" t="s">
-        <v>821</v>
+        <v>796</v>
       </c>
       <c r="N48" s="1" t="s">
         <v>631</v>
@@ -11296,10 +11305,10 @@
         <v>532</v>
       </c>
       <c r="D51" s="23" t="s">
-        <v>944</v>
+        <v>911</v>
       </c>
       <c r="E51" s="23" t="s">
-        <v>1113</v>
+        <v>1080</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>262</v>
@@ -11362,10 +11371,10 @@
         <v>533</v>
       </c>
       <c r="D52" s="23" t="s">
-        <v>945</v>
+        <v>912</v>
       </c>
       <c r="E52" s="23" t="s">
-        <v>1114</v>
+        <v>1081</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>238</v>
@@ -11443,10 +11452,10 @@
         <v>661</v>
       </c>
       <c r="I53" s="23" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="K53" s="23" t="s">
-        <v>779</v>
+        <v>763</v>
       </c>
       <c r="N53" s="1" t="s">
         <v>631</v>
@@ -11506,10 +11515,10 @@
         <v>535</v>
       </c>
       <c r="D54" s="23" t="s">
-        <v>946</v>
+        <v>913</v>
       </c>
       <c r="E54" s="23" t="s">
-        <v>1115</v>
+        <v>1082</v>
       </c>
       <c r="F54" s="15" t="s">
         <v>662</v>
@@ -11596,7 +11605,7 @@
       <c r="K55" s="28"/>
       <c r="L55" s="28"/>
       <c r="M55" s="28" t="s">
-        <v>822</v>
+        <v>797</v>
       </c>
       <c r="N55" s="1" t="s">
         <v>631</v>
@@ -11788,10 +11797,10 @@
         <v>538</v>
       </c>
       <c r="D58" s="23" t="s">
-        <v>947</v>
+        <v>914</v>
       </c>
       <c r="E58" s="23" t="s">
-        <v>1116</v>
+        <v>1083</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>43</v>
@@ -11857,10 +11866,10 @@
         <v>539</v>
       </c>
       <c r="D59" s="23" t="s">
-        <v>948</v>
+        <v>915</v>
       </c>
       <c r="E59" s="23" t="s">
-        <v>1117</v>
+        <v>1084</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>43</v>
@@ -11926,10 +11935,10 @@
         <v>188</v>
       </c>
       <c r="D60" s="23" t="s">
-        <v>949</v>
+        <v>916</v>
       </c>
       <c r="E60" s="23" t="s">
-        <v>1118</v>
+        <v>1085</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>189</v>
@@ -11992,10 +12001,10 @@
         <v>22</v>
       </c>
       <c r="D61" s="23" t="s">
-        <v>950</v>
+        <v>917</v>
       </c>
       <c r="E61" s="23" t="s">
-        <v>1119</v>
+        <v>1086</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>20</v>
@@ -12007,10 +12016,10 @@
         <v>661</v>
       </c>
       <c r="I61" s="23" t="s">
-        <v>785</v>
+        <v>769</v>
       </c>
       <c r="J61" s="23" t="s">
-        <v>786</v>
+        <v>770</v>
       </c>
       <c r="N61" s="1" t="s">
         <v>595</v>
@@ -12070,10 +12079,10 @@
         <v>563</v>
       </c>
       <c r="D62" s="23" t="s">
-        <v>951</v>
+        <v>918</v>
       </c>
       <c r="E62" s="23" t="s">
-        <v>1120</v>
+        <v>1087</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>191</v>
@@ -12136,34 +12145,34 @@
         <v>470</v>
       </c>
       <c r="D63" s="23" t="s">
-        <v>952</v>
+        <v>919</v>
       </c>
       <c r="E63" s="23" t="s">
-        <v>1121</v>
+        <v>1088</v>
       </c>
       <c r="F63" s="15" t="s">
         <v>122</v>
       </c>
       <c r="G63" s="24" t="s">
-        <v>796</v>
+        <v>778</v>
       </c>
       <c r="H63" s="23" t="s">
         <v>661</v>
       </c>
       <c r="I63" s="23" t="s">
-        <v>862</v>
+        <v>831</v>
       </c>
       <c r="J63" s="23" t="s">
-        <v>793</v>
+        <v>775</v>
       </c>
       <c r="K63" s="23" t="s">
-        <v>777</v>
+        <v>761</v>
       </c>
       <c r="L63" s="24" t="s">
-        <v>791</v>
+        <v>1302</v>
       </c>
       <c r="M63" s="23" t="s">
-        <v>797</v>
+        <v>779</v>
       </c>
       <c r="N63" s="1" t="s">
         <v>631</v>
@@ -12223,10 +12232,10 @@
         <v>564</v>
       </c>
       <c r="D64" s="23" t="s">
-        <v>953</v>
+        <v>920</v>
       </c>
       <c r="E64" s="23" t="s">
-        <v>1122</v>
+        <v>1089</v>
       </c>
       <c r="F64" s="26" t="s">
         <v>55</v>
@@ -12307,10 +12316,10 @@
         <v>661</v>
       </c>
       <c r="I65" s="23" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="L65" s="23" t="s">
-        <v>712</v>
+        <v>1302</v>
       </c>
       <c r="N65" s="1" t="s">
         <v>594</v>
@@ -12370,10 +12379,10 @@
         <v>566</v>
       </c>
       <c r="D66" s="23" t="s">
-        <v>954</v>
+        <v>921</v>
       </c>
       <c r="E66" s="23" t="s">
-        <v>1123</v>
+        <v>1090</v>
       </c>
       <c r="F66" s="27" t="s">
         <v>57</v>
@@ -12385,10 +12394,10 @@
         <v>660</v>
       </c>
       <c r="I66" s="23" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="M66" s="23" t="s">
-        <v>823</v>
+        <v>798</v>
       </c>
       <c r="N66" s="1" t="s">
         <v>595</v>
@@ -12448,10 +12457,10 @@
         <v>567</v>
       </c>
       <c r="D67" s="23" t="s">
-        <v>955</v>
+        <v>922</v>
       </c>
       <c r="E67" s="23" t="s">
-        <v>1124</v>
+        <v>1091</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>272</v>
@@ -12514,10 +12523,10 @@
         <v>568</v>
       </c>
       <c r="D68" s="23" t="s">
-        <v>956</v>
+        <v>923</v>
       </c>
       <c r="E68" s="23" t="s">
-        <v>1125</v>
+        <v>1092</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>158</v>
@@ -12580,10 +12589,10 @@
         <v>45</v>
       </c>
       <c r="D69" s="23" t="s">
-        <v>957</v>
+        <v>924</v>
       </c>
       <c r="E69" s="23" t="s">
-        <v>1126</v>
+        <v>1093</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>43</v>
@@ -12649,10 +12658,10 @@
         <v>569</v>
       </c>
       <c r="D70" s="23" t="s">
-        <v>958</v>
+        <v>925</v>
       </c>
       <c r="E70" s="23" t="s">
-        <v>1127</v>
+        <v>1094</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>262</v>
@@ -12715,10 +12724,10 @@
         <v>570</v>
       </c>
       <c r="D71" s="23" t="s">
-        <v>959</v>
+        <v>926</v>
       </c>
       <c r="E71" s="23" t="s">
-        <v>1128</v>
+        <v>1095</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>272</v>
@@ -12781,10 +12790,10 @@
         <v>571</v>
       </c>
       <c r="D72" s="23" t="s">
-        <v>960</v>
+        <v>927</v>
       </c>
       <c r="E72" s="23" t="s">
-        <v>1129</v>
+        <v>1096</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>224</v>
@@ -12847,10 +12856,10 @@
         <v>572</v>
       </c>
       <c r="D73" s="23" t="s">
-        <v>961</v>
+        <v>928</v>
       </c>
       <c r="E73" s="23" t="s">
-        <v>1130</v>
+        <v>1097</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>224</v>
@@ -12913,10 +12922,10 @@
         <v>573</v>
       </c>
       <c r="D74" s="23" t="s">
-        <v>962</v>
+        <v>929</v>
       </c>
       <c r="E74" s="23" t="s">
-        <v>1131</v>
+        <v>1098</v>
       </c>
       <c r="F74" s="2" t="s">
         <v>123</v>
@@ -12979,10 +12988,10 @@
         <v>40</v>
       </c>
       <c r="D75" s="23" t="s">
-        <v>963</v>
+        <v>930</v>
       </c>
       <c r="E75" s="23" t="s">
-        <v>1132</v>
+        <v>1099</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>41</v>
@@ -13063,10 +13072,10 @@
         <v>660</v>
       </c>
       <c r="I76" s="23" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="L76" s="23" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="N76" s="1" t="s">
         <v>594</v>
@@ -13192,10 +13201,10 @@
         <v>29</v>
       </c>
       <c r="D78" s="23" t="s">
-        <v>964</v>
+        <v>931</v>
       </c>
       <c r="E78" s="23" t="s">
-        <v>1133</v>
+        <v>1100</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>30</v>
@@ -13261,10 +13270,10 @@
         <v>193</v>
       </c>
       <c r="D79" s="23" t="s">
-        <v>965</v>
+        <v>932</v>
       </c>
       <c r="E79" s="23" t="s">
-        <v>1134</v>
+        <v>1101</v>
       </c>
       <c r="F79" s="2" t="s">
         <v>191</v>
@@ -13327,10 +13336,10 @@
         <v>24</v>
       </c>
       <c r="D80" s="23" t="s">
-        <v>966</v>
+        <v>933</v>
       </c>
       <c r="E80" s="23" t="s">
-        <v>1135</v>
+        <v>1102</v>
       </c>
       <c r="F80" s="2" t="s">
         <v>20</v>
@@ -13342,16 +13351,16 @@
         <v>660</v>
       </c>
       <c r="I80" s="23" t="s">
-        <v>1266</v>
+        <v>1233</v>
       </c>
       <c r="J80" s="23" t="s">
-        <v>787</v>
+        <v>771</v>
       </c>
       <c r="L80" s="23" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="M80" s="23" t="s">
-        <v>824</v>
+        <v>799</v>
       </c>
       <c r="N80" s="1" t="s">
         <v>595</v>
@@ -13411,10 +13420,10 @@
         <v>134</v>
       </c>
       <c r="D81" s="23" t="s">
-        <v>967</v>
+        <v>934</v>
       </c>
       <c r="E81" s="23" t="s">
-        <v>1136</v>
+        <v>1103</v>
       </c>
       <c r="F81" s="2" t="s">
         <v>135</v>
@@ -13489,16 +13498,16 @@
         <v>183</v>
       </c>
       <c r="H82" s="23" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="I82" s="23" t="s">
-        <v>759</v>
+        <v>747</v>
       </c>
       <c r="J82" s="23" t="s">
-        <v>825</v>
+        <v>800</v>
       </c>
       <c r="M82" s="23" t="s">
-        <v>905</v>
+        <v>872</v>
       </c>
       <c r="N82" s="1" t="s">
         <v>631</v>
@@ -13558,10 +13567,10 @@
         <v>226</v>
       </c>
       <c r="D83" s="23" t="s">
-        <v>968</v>
+        <v>935</v>
       </c>
       <c r="E83" s="23" t="s">
-        <v>1137</v>
+        <v>1104</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>227</v>
@@ -13624,10 +13633,10 @@
         <v>229</v>
       </c>
       <c r="D84" s="23" t="s">
-        <v>969</v>
+        <v>936</v>
       </c>
       <c r="E84" s="23" t="s">
-        <v>1138</v>
+        <v>1105</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>227</v>
@@ -13756,10 +13765,10 @@
         <v>278</v>
       </c>
       <c r="D86" s="23" t="s">
-        <v>970</v>
+        <v>937</v>
       </c>
       <c r="E86" s="23" t="s">
-        <v>1139</v>
+        <v>1106</v>
       </c>
       <c r="F86" s="23" t="s">
         <v>279</v>
@@ -13829,7 +13838,7 @@
         <v>205</v>
       </c>
       <c r="E87" s="23" t="s">
-        <v>1140</v>
+        <v>1107</v>
       </c>
       <c r="F87" s="2" t="s">
         <v>198</v>
@@ -13841,16 +13850,16 @@
         <v>661</v>
       </c>
       <c r="I87" s="23" t="s">
-        <v>810</v>
+        <v>789</v>
       </c>
       <c r="K87" s="23" t="s">
+        <v>687</v>
+      </c>
+      <c r="L87" s="23" t="s">
+        <v>689</v>
+      </c>
+      <c r="M87" s="23" t="s">
         <v>690</v>
-      </c>
-      <c r="L87" s="23" t="s">
-        <v>692</v>
-      </c>
-      <c r="M87" s="23" t="s">
-        <v>693</v>
       </c>
       <c r="N87" s="1" t="s">
         <v>594</v>
@@ -13928,10 +13937,10 @@
         <v>669</v>
       </c>
       <c r="L88" s="23" t="s">
-        <v>670</v>
+        <v>1300</v>
       </c>
       <c r="M88" s="23" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="N88" s="1" t="s">
         <v>594</v>
@@ -14060,10 +14069,10 @@
         <v>241</v>
       </c>
       <c r="D90" s="23" t="s">
-        <v>971</v>
+        <v>938</v>
       </c>
       <c r="E90" s="23" t="s">
-        <v>1141</v>
+        <v>1108</v>
       </c>
       <c r="F90" s="2" t="s">
         <v>242</v>
@@ -14126,10 +14135,10 @@
         <v>184</v>
       </c>
       <c r="D91" s="23" t="s">
-        <v>972</v>
+        <v>939</v>
       </c>
       <c r="E91" s="23" t="s">
-        <v>1142</v>
+        <v>1109</v>
       </c>
       <c r="F91" s="2" t="s">
         <v>176</v>
@@ -14141,13 +14150,13 @@
         <v>660</v>
       </c>
       <c r="I91" s="23" t="s">
-        <v>759</v>
+        <v>747</v>
       </c>
       <c r="K91" s="23" t="s">
-        <v>777</v>
+        <v>761</v>
       </c>
       <c r="L91" s="23" t="s">
-        <v>713</v>
+        <v>1298</v>
       </c>
       <c r="N91" s="1" t="s">
         <v>631</v>
@@ -14207,10 +14216,10 @@
         <v>186</v>
       </c>
       <c r="D92" s="23" t="s">
-        <v>973</v>
+        <v>940</v>
       </c>
       <c r="E92" s="23" t="s">
-        <v>1143</v>
+        <v>1110</v>
       </c>
       <c r="F92" s="2" t="s">
         <v>176</v>
@@ -14222,13 +14231,13 @@
         <v>660</v>
       </c>
       <c r="I92" s="23" t="s">
+        <v>747</v>
+      </c>
+      <c r="K92" s="23" t="s">
         <v>759</v>
       </c>
-      <c r="K92" s="23" t="s">
-        <v>775</v>
-      </c>
       <c r="L92" s="23" t="s">
-        <v>746</v>
+        <v>1298</v>
       </c>
       <c r="N92" s="1" t="s">
         <v>631</v>
@@ -14288,10 +14297,10 @@
         <v>68</v>
       </c>
       <c r="D93" s="23" t="s">
-        <v>974</v>
+        <v>941</v>
       </c>
       <c r="E93" s="23" t="s">
-        <v>1144</v>
+        <v>1111</v>
       </c>
       <c r="F93" s="2" t="s">
         <v>69</v>
@@ -14375,7 +14384,7 @@
         <v>669</v>
       </c>
       <c r="K94" s="23" t="s">
-        <v>777</v>
+        <v>761</v>
       </c>
       <c r="N94" s="1" t="s">
         <v>595</v>
@@ -14573,10 +14582,10 @@
         <v>173</v>
       </c>
       <c r="D97" s="23" t="s">
-        <v>975</v>
+        <v>942</v>
       </c>
       <c r="E97" s="23" t="s">
-        <v>1145</v>
+        <v>1112</v>
       </c>
       <c r="F97" s="2" t="s">
         <v>167</v>
@@ -14591,10 +14600,10 @@
         <v>669</v>
       </c>
       <c r="K97" s="23" t="s">
-        <v>783</v>
+        <v>767</v>
       </c>
       <c r="M97" s="23" t="s">
-        <v>826</v>
+        <v>801</v>
       </c>
       <c r="N97" s="1" t="s">
         <v>631</v>
@@ -14654,10 +14663,10 @@
         <v>269</v>
       </c>
       <c r="D98" s="23" t="s">
-        <v>976</v>
+        <v>943</v>
       </c>
       <c r="E98" s="23" t="s">
-        <v>1146</v>
+        <v>1113</v>
       </c>
       <c r="F98" s="2" t="s">
         <v>270</v>
@@ -14738,7 +14747,7 @@
         <v>669</v>
       </c>
       <c r="M99" s="23" t="s">
-        <v>790</v>
+        <v>773</v>
       </c>
       <c r="O99" s="1" t="s">
         <v>549</v>
@@ -14795,7 +14804,7 @@
         <v>260</v>
       </c>
       <c r="D100" s="23" t="s">
-        <v>977</v>
+        <v>944</v>
       </c>
       <c r="E100" s="23" t="s">
         <v>261</v>
@@ -14807,13 +14816,13 @@
         <v>256</v>
       </c>
       <c r="H100" s="23" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="I100" s="23" t="s">
-        <v>827</v>
+        <v>802</v>
       </c>
       <c r="K100" s="23" t="s">
-        <v>828</v>
+        <v>803</v>
       </c>
       <c r="O100" s="1" t="s">
         <v>549</v>
@@ -14870,10 +14879,10 @@
         <v>251</v>
       </c>
       <c r="D101" s="23" t="s">
-        <v>978</v>
+        <v>945</v>
       </c>
       <c r="E101" s="23" t="s">
-        <v>1147</v>
+        <v>1114</v>
       </c>
       <c r="F101" s="2" t="s">
         <v>249</v>
@@ -14885,16 +14894,16 @@
         <v>660</v>
       </c>
       <c r="I101" s="23" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="J101" s="23" t="s">
-        <v>829</v>
+        <v>804</v>
       </c>
       <c r="K101" s="23" t="s">
-        <v>769</v>
+        <v>756</v>
       </c>
       <c r="L101" s="23" t="s">
-        <v>830</v>
+        <v>1298</v>
       </c>
       <c r="O101" s="1" t="s">
         <v>549</v>
@@ -14966,13 +14975,13 @@
         <v>661</v>
       </c>
       <c r="I102" s="23" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="L102" s="23" t="s">
-        <v>719</v>
+        <v>1299</v>
       </c>
       <c r="M102" s="23" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="N102" s="1" t="s">
         <v>631</v>
@@ -15032,10 +15041,10 @@
         <v>54</v>
       </c>
       <c r="D103" s="23" t="s">
-        <v>979</v>
+        <v>946</v>
       </c>
       <c r="E103" s="23" t="s">
-        <v>1148</v>
+        <v>1115</v>
       </c>
       <c r="F103" s="27" t="s">
         <v>662</v>
@@ -15101,10 +15110,10 @@
         <v>237</v>
       </c>
       <c r="D104" s="23" t="s">
-        <v>980</v>
+        <v>947</v>
       </c>
       <c r="E104" s="23" t="s">
-        <v>1149</v>
+        <v>1116</v>
       </c>
       <c r="F104" s="2" t="s">
         <v>235</v>
@@ -15119,10 +15128,10 @@
         <v>669</v>
       </c>
       <c r="K104" s="23" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="L104" s="23" t="s">
-        <v>670</v>
+        <v>1300</v>
       </c>
       <c r="N104" s="1" t="s">
         <v>631</v>
@@ -15182,10 +15191,10 @@
         <v>160</v>
       </c>
       <c r="D105" s="23" t="s">
-        <v>981</v>
+        <v>948</v>
       </c>
       <c r="E105" s="23" t="s">
-        <v>1150</v>
+        <v>1117</v>
       </c>
       <c r="F105" s="2" t="s">
         <v>161</v>
@@ -15248,10 +15257,10 @@
         <v>280</v>
       </c>
       <c r="D106" s="23" t="s">
-        <v>982</v>
+        <v>949</v>
       </c>
       <c r="E106" s="23" t="s">
-        <v>1151</v>
+        <v>1118</v>
       </c>
       <c r="F106" s="15" t="s">
         <v>516</v>
@@ -15314,10 +15323,10 @@
         <v>174</v>
       </c>
       <c r="D107" s="23" t="s">
-        <v>983</v>
+        <v>950</v>
       </c>
       <c r="E107" s="23" t="s">
-        <v>1152</v>
+        <v>1119</v>
       </c>
       <c r="F107" s="2" t="s">
         <v>167</v>
@@ -15329,16 +15338,16 @@
         <v>660</v>
       </c>
       <c r="I107" s="23" t="s">
-        <v>831</v>
+        <v>805</v>
       </c>
       <c r="K107" s="23" t="s">
-        <v>784</v>
+        <v>768</v>
       </c>
       <c r="L107" s="23" t="s">
-        <v>806</v>
+        <v>1309</v>
       </c>
       <c r="M107" s="23" t="s">
-        <v>797</v>
+        <v>779</v>
       </c>
       <c r="N107" s="1" t="s">
         <v>631</v>
@@ -15464,10 +15473,10 @@
         <v>209</v>
       </c>
       <c r="D109" s="23" t="s">
-        <v>984</v>
+        <v>951</v>
       </c>
       <c r="E109" s="23" t="s">
-        <v>1153</v>
+        <v>1120</v>
       </c>
       <c r="F109" s="2" t="s">
         <v>198</v>
@@ -15479,13 +15488,13 @@
         <v>661</v>
       </c>
       <c r="I109" s="23" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="K109" s="23" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="M109" s="23" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="N109" s="1" t="s">
         <v>594</v>
@@ -15560,7 +15569,7 @@
         <v>661</v>
       </c>
       <c r="M110" s="23" t="s">
-        <v>763</v>
+        <v>751</v>
       </c>
       <c r="N110" s="1" t="s">
         <v>631</v>
@@ -15620,10 +15629,10 @@
         <v>240</v>
       </c>
       <c r="D111" s="23" t="s">
-        <v>985</v>
+        <v>952</v>
       </c>
       <c r="E111" s="23" t="s">
-        <v>1154</v>
+        <v>1121</v>
       </c>
       <c r="F111" s="2" t="s">
         <v>238</v>
@@ -15701,16 +15710,16 @@
         <v>661</v>
       </c>
       <c r="I112" s="23" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="K112" s="23" t="s">
-        <v>718</v>
+        <v>711</v>
       </c>
       <c r="L112" s="23" t="s">
-        <v>720</v>
+        <v>1299</v>
       </c>
       <c r="M112" s="23" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="N112" s="1" t="s">
         <v>594</v>
@@ -15791,10 +15800,10 @@
         <v>673</v>
       </c>
       <c r="L113" s="23" t="s">
-        <v>832</v>
+        <v>1307</v>
       </c>
       <c r="M113" s="23" t="s">
-        <v>833</v>
+        <v>806</v>
       </c>
       <c r="N113" s="1" t="s">
         <v>595</v>
@@ -15854,10 +15863,10 @@
         <v>580</v>
       </c>
       <c r="D114" s="23" t="s">
-        <v>986</v>
+        <v>953</v>
       </c>
       <c r="E114" s="23" t="s">
-        <v>1155</v>
+        <v>1122</v>
       </c>
       <c r="F114" s="2" t="s">
         <v>43</v>
@@ -15923,10 +15932,10 @@
         <v>418</v>
       </c>
       <c r="D115" s="23" t="s">
-        <v>987</v>
+        <v>954</v>
       </c>
       <c r="E115" s="23" t="s">
-        <v>1156</v>
+        <v>1123</v>
       </c>
       <c r="F115" s="15" t="s">
         <v>419</v>
@@ -15993,16 +16002,16 @@
         <v>334</v>
       </c>
       <c r="D116" s="23" t="s">
-        <v>988</v>
+        <v>955</v>
       </c>
       <c r="E116" s="23" t="s">
-        <v>1157</v>
+        <v>1124</v>
       </c>
       <c r="F116" s="2" t="s">
         <v>165</v>
       </c>
       <c r="G116" s="23" t="s">
-        <v>1253</v>
+        <v>1220</v>
       </c>
       <c r="O116" s="1" t="s">
         <v>549</v>
@@ -16074,19 +16083,19 @@
         <v>661</v>
       </c>
       <c r="I117" s="23" t="s">
-        <v>798</v>
+        <v>780</v>
       </c>
       <c r="J117" s="23" t="s">
-        <v>754</v>
+        <v>743</v>
       </c>
       <c r="K117" s="23" t="s">
         <v>674</v>
       </c>
       <c r="L117" s="23" t="s">
-        <v>676</v>
+        <v>1302</v>
       </c>
       <c r="M117" s="23" t="s">
-        <v>834</v>
+        <v>807</v>
       </c>
       <c r="N117" s="1" t="s">
         <v>595</v>
@@ -16215,10 +16224,10 @@
         <v>385</v>
       </c>
       <c r="D119" s="23" t="s">
-        <v>989</v>
+        <v>956</v>
       </c>
       <c r="E119" s="23" t="s">
-        <v>1158</v>
+        <v>1125</v>
       </c>
       <c r="F119" s="15" t="s">
         <v>386</v>
@@ -16284,10 +16293,10 @@
         <v>581</v>
       </c>
       <c r="D120" s="23" t="s">
-        <v>990</v>
+        <v>957</v>
       </c>
       <c r="E120" s="23" t="s">
-        <v>1159</v>
+        <v>1126</v>
       </c>
       <c r="F120" s="2" t="s">
         <v>43</v>
@@ -16419,10 +16428,10 @@
         <v>399</v>
       </c>
       <c r="D122" s="23" t="s">
-        <v>991</v>
+        <v>958</v>
       </c>
       <c r="E122" s="23" t="s">
-        <v>1160</v>
+        <v>1127</v>
       </c>
       <c r="F122" s="2" t="s">
         <v>397</v>
@@ -16485,10 +16494,10 @@
         <v>582</v>
       </c>
       <c r="D123" s="23" t="s">
-        <v>992</v>
+        <v>959</v>
       </c>
       <c r="E123" s="23" t="s">
-        <v>1161</v>
+        <v>1128</v>
       </c>
       <c r="F123" s="2" t="s">
         <v>43</v>
@@ -16554,10 +16563,10 @@
         <v>302</v>
       </c>
       <c r="D124" s="23" t="s">
-        <v>993</v>
+        <v>960</v>
       </c>
       <c r="E124" s="23" t="s">
-        <v>1162</v>
+        <v>1129</v>
       </c>
       <c r="F124" s="15" t="s">
         <v>161</v>
@@ -16887,10 +16896,10 @@
         <v>584</v>
       </c>
       <c r="D129" s="23" t="s">
-        <v>994</v>
+        <v>961</v>
       </c>
       <c r="E129" s="23" t="s">
-        <v>1163</v>
+        <v>1130</v>
       </c>
       <c r="F129" s="2" t="s">
         <v>43</v>
@@ -16956,10 +16965,10 @@
         <v>322</v>
       </c>
       <c r="D130" s="23" t="s">
-        <v>995</v>
+        <v>962</v>
       </c>
       <c r="E130" s="23" t="s">
-        <v>1164</v>
+        <v>1131</v>
       </c>
       <c r="F130" s="2" t="s">
         <v>90</v>
@@ -16974,7 +16983,7 @@
         <v>669</v>
       </c>
       <c r="L130" s="23" t="s">
-        <v>770</v>
+        <v>1311</v>
       </c>
       <c r="O130" s="1" t="s">
         <v>549</v>
@@ -17103,10 +17112,10 @@
         <v>394</v>
       </c>
       <c r="D132" s="23" t="s">
-        <v>996</v>
+        <v>963</v>
       </c>
       <c r="E132" s="23" t="s">
-        <v>1165</v>
+        <v>1132</v>
       </c>
       <c r="F132" s="2" t="s">
         <v>393</v>
@@ -17169,10 +17178,10 @@
         <v>326</v>
       </c>
       <c r="D133" s="23" t="s">
-        <v>997</v>
+        <v>964</v>
       </c>
       <c r="E133" s="23" t="s">
-        <v>1166</v>
+        <v>1133</v>
       </c>
       <c r="F133" s="2" t="s">
         <v>224</v>
@@ -17235,10 +17244,10 @@
         <v>301</v>
       </c>
       <c r="D134" s="23" t="s">
-        <v>998</v>
+        <v>965</v>
       </c>
       <c r="E134" s="23" t="s">
-        <v>1167</v>
+        <v>1134</v>
       </c>
       <c r="F134" s="2" t="s">
         <v>161</v>
@@ -17301,10 +17310,10 @@
         <v>457</v>
       </c>
       <c r="D135" s="23" t="s">
-        <v>999</v>
+        <v>966</v>
       </c>
       <c r="E135" s="23" t="s">
-        <v>1168</v>
+        <v>1135</v>
       </c>
       <c r="F135" s="2" t="s">
         <v>456</v>
@@ -17367,10 +17376,10 @@
         <v>313</v>
       </c>
       <c r="D136" s="23" t="s">
-        <v>1000</v>
+        <v>967</v>
       </c>
       <c r="E136" s="23" t="s">
-        <v>1169</v>
+        <v>1136</v>
       </c>
       <c r="F136" s="2" t="s">
         <v>314</v>
@@ -17433,10 +17442,10 @@
         <v>327</v>
       </c>
       <c r="D137" s="23" t="s">
-        <v>1001</v>
+        <v>968</v>
       </c>
       <c r="E137" s="23" t="s">
-        <v>1170</v>
+        <v>1137</v>
       </c>
       <c r="F137" s="2" t="s">
         <v>224</v>
@@ -17499,10 +17508,10 @@
         <v>350</v>
       </c>
       <c r="D138" s="23" t="s">
-        <v>1002</v>
+        <v>969</v>
       </c>
       <c r="E138" s="23" t="s">
-        <v>1171</v>
+        <v>1138</v>
       </c>
       <c r="F138" s="2" t="s">
         <v>83</v>
@@ -17514,13 +17523,13 @@
         <v>660</v>
       </c>
       <c r="I138" s="23" t="s">
-        <v>835</v>
+        <v>808</v>
       </c>
       <c r="L138" s="23" t="s">
-        <v>704</v>
+        <v>1299</v>
       </c>
       <c r="M138" s="23" t="s">
-        <v>836</v>
+        <v>809</v>
       </c>
       <c r="O138" s="1" t="s">
         <v>549</v>
@@ -17577,10 +17586,10 @@
         <v>445</v>
       </c>
       <c r="D139" s="23" t="s">
-        <v>1003</v>
+        <v>970</v>
       </c>
       <c r="E139" s="23" t="s">
-        <v>1172</v>
+        <v>1139</v>
       </c>
       <c r="F139" s="2" t="s">
         <v>389</v>
@@ -17646,10 +17655,10 @@
         <v>283</v>
       </c>
       <c r="D140" s="23" t="s">
-        <v>1004</v>
+        <v>971</v>
       </c>
       <c r="E140" s="23" t="s">
-        <v>1173</v>
+        <v>1140</v>
       </c>
       <c r="F140" s="2" t="s">
         <v>43</v>
@@ -17715,10 +17724,10 @@
         <v>335</v>
       </c>
       <c r="D141" s="23" t="s">
-        <v>1005</v>
+        <v>972</v>
       </c>
       <c r="E141" s="23" t="s">
-        <v>1174</v>
+        <v>1141</v>
       </c>
       <c r="F141" s="2" t="s">
         <v>336</v>
@@ -17784,10 +17793,10 @@
         <v>367</v>
       </c>
       <c r="D142" s="23" t="s">
-        <v>1006</v>
+        <v>973</v>
       </c>
       <c r="E142" s="23" t="s">
-        <v>1175</v>
+        <v>1142</v>
       </c>
       <c r="F142" s="2" t="s">
         <v>365</v>
@@ -17850,10 +17859,10 @@
         <v>339</v>
       </c>
       <c r="D143" s="23" t="s">
-        <v>1007</v>
+        <v>974</v>
       </c>
       <c r="E143" s="23" t="s">
-        <v>1176</v>
+        <v>1143</v>
       </c>
       <c r="F143" s="2" t="s">
         <v>338</v>
@@ -17920,13 +17929,13 @@
         <v>447</v>
       </c>
       <c r="D144" s="23" t="s">
-        <v>1008</v>
+        <v>975</v>
       </c>
       <c r="E144" s="23" t="s">
-        <v>1177</v>
+        <v>1144</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>765</v>
+        <v>753</v>
       </c>
       <c r="G144" s="23" t="s">
         <v>47</v>
@@ -17935,13 +17944,13 @@
         <v>660</v>
       </c>
       <c r="I144" s="23" t="s">
-        <v>837</v>
+        <v>810</v>
       </c>
       <c r="K144" s="23" t="s">
-        <v>769</v>
+        <v>756</v>
       </c>
       <c r="L144" s="23" t="s">
-        <v>768</v>
+        <v>1312</v>
       </c>
       <c r="N144" s="1" t="s">
         <v>594</v>
@@ -18001,10 +18010,10 @@
         <v>585</v>
       </c>
       <c r="D145" s="23" t="s">
-        <v>1009</v>
+        <v>976</v>
       </c>
       <c r="E145" s="23" t="s">
-        <v>1178</v>
+        <v>1145</v>
       </c>
       <c r="F145" s="2" t="s">
         <v>43</v>
@@ -18070,10 +18079,10 @@
         <v>358</v>
       </c>
       <c r="D146" s="23" t="s">
-        <v>1010</v>
+        <v>977</v>
       </c>
       <c r="E146" s="23" t="s">
-        <v>1179</v>
+        <v>1146</v>
       </c>
       <c r="F146" s="2" t="s">
         <v>356</v>
@@ -18136,10 +18145,10 @@
         <v>388</v>
       </c>
       <c r="D147" s="23" t="s">
-        <v>1011</v>
+        <v>978</v>
       </c>
       <c r="E147" s="23" t="s">
-        <v>1180</v>
+        <v>1147</v>
       </c>
       <c r="F147" s="2" t="s">
         <v>389</v>
@@ -18205,10 +18214,10 @@
         <v>349</v>
       </c>
       <c r="D148" s="23" t="s">
-        <v>1012</v>
+        <v>979</v>
       </c>
       <c r="E148" s="23" t="s">
-        <v>1181</v>
+        <v>1148</v>
       </c>
       <c r="F148" s="2" t="s">
         <v>83</v>
@@ -18223,10 +18232,10 @@
         <v>669</v>
       </c>
       <c r="J148" s="23" t="s">
-        <v>751</v>
+        <v>740</v>
       </c>
       <c r="M148" s="23" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="O148" s="1" t="s">
         <v>549</v>
@@ -18353,10 +18362,10 @@
         <v>508</v>
       </c>
       <c r="D150" s="23" t="s">
-        <v>1013</v>
+        <v>980</v>
       </c>
       <c r="E150" s="23" t="s">
-        <v>1182</v>
+        <v>1149</v>
       </c>
       <c r="F150" s="15" t="s">
         <v>509</v>
@@ -18422,10 +18431,10 @@
         <v>396</v>
       </c>
       <c r="D151" s="23" t="s">
-        <v>1014</v>
+        <v>981</v>
       </c>
       <c r="E151" s="23" t="s">
-        <v>1183</v>
+        <v>1150</v>
       </c>
       <c r="F151" s="2" t="s">
         <v>397</v>
@@ -18488,10 +18497,10 @@
         <v>586</v>
       </c>
       <c r="D152" s="23" t="s">
-        <v>1015</v>
+        <v>982</v>
       </c>
       <c r="E152" s="23" t="s">
-        <v>1184</v>
+        <v>1151</v>
       </c>
       <c r="F152" s="2" t="s">
         <v>43</v>
@@ -18623,10 +18632,10 @@
         <v>436</v>
       </c>
       <c r="D154" s="23" t="s">
-        <v>1016</v>
+        <v>983</v>
       </c>
       <c r="E154" s="23" t="s">
-        <v>1185</v>
+        <v>1152</v>
       </c>
       <c r="F154" s="2" t="s">
         <v>434</v>
@@ -18689,10 +18698,10 @@
         <v>348</v>
       </c>
       <c r="D155" s="23" t="s">
-        <v>1017</v>
+        <v>984</v>
       </c>
       <c r="E155" s="23" t="s">
-        <v>1186</v>
+        <v>1153</v>
       </c>
       <c r="F155" s="2" t="s">
         <v>346</v>
@@ -18758,10 +18767,10 @@
         <v>321</v>
       </c>
       <c r="D156" s="23" t="s">
-        <v>1018</v>
+        <v>985</v>
       </c>
       <c r="E156" s="23" t="s">
-        <v>1187</v>
+        <v>1154</v>
       </c>
       <c r="F156" s="2" t="s">
         <v>90</v>
@@ -18773,7 +18782,7 @@
         <v>660</v>
       </c>
       <c r="I156" s="23" t="s">
-        <v>827</v>
+        <v>802</v>
       </c>
       <c r="O156" s="1" t="s">
         <v>549</v>
@@ -18830,10 +18839,10 @@
         <v>319</v>
       </c>
       <c r="D157" s="23" t="s">
-        <v>1019</v>
+        <v>986</v>
       </c>
       <c r="E157" s="23" t="s">
-        <v>1188</v>
+        <v>1155</v>
       </c>
       <c r="F157" s="2" t="s">
         <v>317</v>
@@ -18911,19 +18920,19 @@
         <v>405</v>
       </c>
       <c r="H158" s="23" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="I158" s="23" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="J158" s="23" t="s">
-        <v>778</v>
+        <v>762</v>
       </c>
       <c r="K158" s="23" t="s">
-        <v>780</v>
+        <v>764</v>
       </c>
       <c r="M158" s="23" t="s">
-        <v>709</v>
+        <v>704</v>
       </c>
       <c r="N158" s="1" t="s">
         <v>631</v>
@@ -18983,10 +18992,10 @@
         <v>448</v>
       </c>
       <c r="D159" s="23" t="s">
-        <v>1020</v>
+        <v>987</v>
       </c>
       <c r="E159" s="24" t="s">
-        <v>1189</v>
+        <v>1156</v>
       </c>
       <c r="F159" s="15" t="s">
         <v>386</v>
@@ -19052,10 +19061,10 @@
         <v>400</v>
       </c>
       <c r="D160" s="23" t="s">
-        <v>1021</v>
+        <v>988</v>
       </c>
       <c r="E160" s="23" t="s">
-        <v>1190</v>
+        <v>1157</v>
       </c>
       <c r="F160" s="2" t="s">
         <v>401</v>
@@ -19119,10 +19128,10 @@
         <v>284</v>
       </c>
       <c r="D161" s="23" t="s">
-        <v>1022</v>
+        <v>989</v>
       </c>
       <c r="E161" s="23" t="s">
-        <v>1191</v>
+        <v>1158</v>
       </c>
       <c r="F161" s="2" t="s">
         <v>43</v>
@@ -19188,10 +19197,10 @@
         <v>391</v>
       </c>
       <c r="D162" s="23" t="s">
-        <v>1023</v>
+        <v>990</v>
       </c>
       <c r="E162" s="23" t="s">
-        <v>1192</v>
+        <v>1159</v>
       </c>
       <c r="F162" s="2" t="s">
         <v>392</v>
@@ -19321,10 +19330,10 @@
         <v>515</v>
       </c>
       <c r="D164" s="23" t="s">
-        <v>1024</v>
+        <v>991</v>
       </c>
       <c r="E164" s="23" t="s">
-        <v>1193</v>
+        <v>1160</v>
       </c>
       <c r="F164" s="15" t="s">
         <v>481</v>
@@ -19387,10 +19396,10 @@
         <v>511</v>
       </c>
       <c r="D165" s="23" t="s">
-        <v>1025</v>
+        <v>992</v>
       </c>
       <c r="E165" s="23" t="s">
-        <v>1194</v>
+        <v>1161</v>
       </c>
       <c r="F165" s="2" t="s">
         <v>512</v>
@@ -19586,10 +19595,10 @@
         <v>433</v>
       </c>
       <c r="D168" s="23" t="s">
-        <v>1026</v>
+        <v>993</v>
       </c>
       <c r="E168" s="23" t="s">
-        <v>1195</v>
+        <v>1162</v>
       </c>
       <c r="F168" s="2" t="s">
         <v>434</v>
@@ -19718,10 +19727,10 @@
         <v>442</v>
       </c>
       <c r="D170" s="23" t="s">
-        <v>1027</v>
+        <v>994</v>
       </c>
       <c r="E170" s="23" t="s">
-        <v>1196</v>
+        <v>1163</v>
       </c>
       <c r="F170" s="2" t="s">
         <v>440</v>
@@ -19799,13 +19808,13 @@
         <v>661</v>
       </c>
       <c r="I171" s="23" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="L171" s="23" t="s">
-        <v>794</v>
+        <v>776</v>
       </c>
       <c r="M171" s="23" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="N171" s="1" t="s">
         <v>595</v>
@@ -19865,10 +19874,10 @@
         <v>364</v>
       </c>
       <c r="D172" s="23" t="s">
-        <v>1028</v>
+        <v>995</v>
       </c>
       <c r="E172" s="23" t="s">
-        <v>1197</v>
+        <v>1164</v>
       </c>
       <c r="F172" s="2" t="s">
         <v>365</v>
@@ -20063,10 +20072,10 @@
         <v>316</v>
       </c>
       <c r="D175" s="23" t="s">
-        <v>1029</v>
+        <v>996</v>
       </c>
       <c r="E175" s="23" t="s">
-        <v>1198</v>
+        <v>1165</v>
       </c>
       <c r="F175" s="2" t="s">
         <v>317</v>
@@ -20132,10 +20141,10 @@
         <v>443</v>
       </c>
       <c r="D176" s="23" t="s">
-        <v>1030</v>
+        <v>997</v>
       </c>
       <c r="E176" s="23" t="s">
-        <v>1199</v>
+        <v>1166</v>
       </c>
       <c r="F176" s="15" t="s">
         <v>502</v>
@@ -20264,10 +20273,10 @@
         <v>588</v>
       </c>
       <c r="D178" s="23" t="s">
-        <v>1031</v>
+        <v>998</v>
       </c>
       <c r="E178" s="23" t="s">
-        <v>1200</v>
+        <v>1167</v>
       </c>
       <c r="F178" s="2" t="s">
         <v>43</v>
@@ -20333,10 +20342,10 @@
         <v>402</v>
       </c>
       <c r="D179" s="23" t="s">
-        <v>1032</v>
+        <v>999</v>
       </c>
       <c r="E179" s="23" t="s">
-        <v>1201</v>
+        <v>1168</v>
       </c>
       <c r="F179" s="2" t="s">
         <v>401</v>
@@ -20466,10 +20475,10 @@
         <v>438</v>
       </c>
       <c r="D181" s="23" t="s">
-        <v>1033</v>
+        <v>1000</v>
       </c>
       <c r="E181" s="23" t="s">
-        <v>1202</v>
+        <v>1169</v>
       </c>
       <c r="F181" s="15" t="s">
         <v>437</v>
@@ -20532,10 +20541,10 @@
         <v>490</v>
       </c>
       <c r="D182" s="23" t="s">
-        <v>1034</v>
+        <v>1001</v>
       </c>
       <c r="E182" s="23" t="s">
-        <v>1203</v>
+        <v>1170</v>
       </c>
       <c r="F182" s="15" t="s">
         <v>491</v>
@@ -20598,10 +20607,10 @@
         <v>541</v>
       </c>
       <c r="D183" s="23" t="s">
-        <v>1035</v>
+        <v>1002</v>
       </c>
       <c r="E183" s="23" t="s">
-        <v>1204</v>
+        <v>1171</v>
       </c>
       <c r="F183" s="15" t="s">
         <v>540</v>
@@ -20664,10 +20673,10 @@
         <v>446</v>
       </c>
       <c r="D184" s="23" t="s">
-        <v>1036</v>
+        <v>1003</v>
       </c>
       <c r="E184" s="23" t="s">
-        <v>1205</v>
+        <v>1172</v>
       </c>
       <c r="F184" s="2" t="s">
         <v>389</v>
@@ -20733,10 +20742,10 @@
         <v>330</v>
       </c>
       <c r="D185" s="23" t="s">
-        <v>1037</v>
+        <v>1004</v>
       </c>
       <c r="E185" s="23" t="s">
-        <v>1206</v>
+        <v>1173</v>
       </c>
       <c r="F185" s="2" t="s">
         <v>329</v>
@@ -20754,10 +20763,10 @@
         <v>668</v>
       </c>
       <c r="L185" s="23" t="s">
-        <v>719</v>
+        <v>1299</v>
       </c>
       <c r="M185" s="23" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="N185" s="1" t="s">
         <v>594</v>
@@ -20817,10 +20826,10 @@
         <v>285</v>
       </c>
       <c r="D186" s="23" t="s">
-        <v>1038</v>
+        <v>1005</v>
       </c>
       <c r="E186" s="23" t="s">
-        <v>1207</v>
+        <v>1174</v>
       </c>
       <c r="F186" s="2" t="s">
         <v>43</v>
@@ -20898,13 +20907,13 @@
         <v>199</v>
       </c>
       <c r="H187" s="23" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="I187" s="23" t="s">
-        <v>838</v>
+        <v>811</v>
       </c>
       <c r="K187" s="23" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="N187" s="1" t="s">
         <v>594</v>
@@ -21030,10 +21039,10 @@
         <v>589</v>
       </c>
       <c r="D189" s="23" t="s">
-        <v>1039</v>
+        <v>1006</v>
       </c>
       <c r="E189" s="23" t="s">
-        <v>1208</v>
+        <v>1175</v>
       </c>
       <c r="F189" s="2" t="s">
         <v>43</v>
@@ -21168,10 +21177,10 @@
         <v>412</v>
       </c>
       <c r="D191" s="23" t="s">
-        <v>1040</v>
+        <v>1007</v>
       </c>
       <c r="E191" s="23" t="s">
-        <v>1209</v>
+        <v>1176</v>
       </c>
       <c r="F191" s="15" t="s">
         <v>413</v>
@@ -21303,10 +21312,10 @@
         <v>590</v>
       </c>
       <c r="D193" s="23" t="s">
-        <v>1041</v>
+        <v>1008</v>
       </c>
       <c r="E193" s="23" t="s">
-        <v>1210</v>
+        <v>1177</v>
       </c>
       <c r="F193" s="2" t="s">
         <v>43</v>
@@ -21387,13 +21396,13 @@
         <v>660</v>
       </c>
       <c r="I194" s="23" t="s">
-        <v>759</v>
+        <v>747</v>
       </c>
       <c r="J194" s="23" t="s">
-        <v>760</v>
+        <v>748</v>
       </c>
       <c r="M194" s="23" t="s">
-        <v>839</v>
+        <v>812</v>
       </c>
       <c r="N194" s="1" t="s">
         <v>631</v>
@@ -21453,10 +21462,10 @@
         <v>591</v>
       </c>
       <c r="D195" s="23" t="s">
-        <v>1042</v>
+        <v>1009</v>
       </c>
       <c r="E195" s="23" t="s">
-        <v>1211</v>
+        <v>1178</v>
       </c>
       <c r="F195" s="2" t="s">
         <v>43</v>
@@ -21588,10 +21597,10 @@
         <v>377</v>
       </c>
       <c r="D197" s="23" t="s">
-        <v>1043</v>
+        <v>1010</v>
       </c>
       <c r="E197" s="23" t="s">
-        <v>1212</v>
+        <v>1179</v>
       </c>
       <c r="F197" s="2" t="s">
         <v>378</v>
@@ -21654,10 +21663,10 @@
         <v>282</v>
       </c>
       <c r="D198" s="23" t="s">
-        <v>1044</v>
+        <v>1011</v>
       </c>
       <c r="E198" s="23" t="s">
-        <v>1213</v>
+        <v>1180</v>
       </c>
       <c r="F198" s="2" t="s">
         <v>43</v>
@@ -21723,10 +21732,10 @@
         <v>420</v>
       </c>
       <c r="D199" s="23" t="s">
-        <v>1045</v>
+        <v>1012</v>
       </c>
       <c r="E199" s="23" t="s">
-        <v>1214</v>
+        <v>1181</v>
       </c>
       <c r="F199" s="15" t="s">
         <v>421</v>
@@ -21792,10 +21801,10 @@
         <v>451</v>
       </c>
       <c r="D200" s="23" t="s">
-        <v>1046</v>
+        <v>1013</v>
       </c>
       <c r="E200" s="23" t="s">
-        <v>1215</v>
+        <v>1182</v>
       </c>
       <c r="F200" s="15" t="s">
         <v>449</v>
@@ -21924,10 +21933,10 @@
         <v>577</v>
       </c>
       <c r="D202" s="23" t="s">
-        <v>1047</v>
+        <v>1014</v>
       </c>
       <c r="E202" s="23" t="s">
-        <v>1216</v>
+        <v>1183</v>
       </c>
       <c r="F202" s="2" t="s">
         <v>578</v>
@@ -21990,10 +21999,10 @@
         <v>559</v>
       </c>
       <c r="D203" s="23" t="s">
-        <v>1048</v>
+        <v>1015</v>
       </c>
       <c r="E203" s="23" t="s">
-        <v>1217</v>
+        <v>1184</v>
       </c>
       <c r="F203" s="15" t="s">
         <v>560</v>
@@ -22125,13 +22134,13 @@
         <v>575</v>
       </c>
       <c r="D205" s="23" t="s">
-        <v>1049</v>
+        <v>1016</v>
       </c>
       <c r="E205" s="23" t="s">
-        <v>1218</v>
+        <v>1185</v>
       </c>
       <c r="F205" s="30" t="s">
-        <v>911</v>
+        <v>878</v>
       </c>
       <c r="G205" s="23" t="s">
         <v>576</v>
@@ -22191,10 +22200,10 @@
         <v>545</v>
       </c>
       <c r="D206" s="23" t="s">
-        <v>1050</v>
+        <v>1017</v>
       </c>
       <c r="E206" s="23" t="s">
-        <v>1219</v>
+        <v>1186</v>
       </c>
       <c r="F206" s="15" t="s">
         <v>540</v>
@@ -22203,7 +22212,7 @@
         <v>546</v>
       </c>
       <c r="M206" s="23" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="O206" s="1" t="s">
         <v>549</v>
@@ -22273,10 +22282,10 @@
         <v>16号(UTAU)</v>
       </c>
       <c r="H207" s="23" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="I207" s="23" t="s">
-        <v>904</v>
+        <v>871</v>
       </c>
       <c r="N207" s="1" t="s">
         <v>631</v>
@@ -22403,10 +22412,10 @@
         <v>286</v>
       </c>
       <c r="D209" s="23" t="s">
-        <v>1051</v>
+        <v>1018</v>
       </c>
       <c r="E209" s="23" t="s">
-        <v>1220</v>
+        <v>1187</v>
       </c>
       <c r="F209" s="2" t="s">
         <v>43</v>
@@ -22472,10 +22481,10 @@
         <v>562</v>
       </c>
       <c r="D210" s="23" t="s">
-        <v>1052</v>
+        <v>1019</v>
       </c>
       <c r="E210" s="23" t="s">
-        <v>1221</v>
+        <v>1188</v>
       </c>
       <c r="F210" s="15" t="s">
         <v>557</v>
@@ -22485,10 +22494,10 @@
         <v>ろんく1号(UTAU)</v>
       </c>
       <c r="H210" s="23" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="I210" s="23" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="N210" s="1" t="s">
         <v>631</v>
@@ -22614,13 +22623,13 @@
         <v>t-kun</v>
       </c>
       <c r="C212" s="24" t="s">
-        <v>741</v>
+        <v>731</v>
       </c>
       <c r="D212" s="23" t="s">
         <v>602</v>
       </c>
       <c r="E212" s="23" t="s">
-        <v>1222</v>
+        <v>1189</v>
       </c>
       <c r="F212" s="15" t="s">
         <v>603</v>
@@ -22635,7 +22644,7 @@
         <v>669</v>
       </c>
       <c r="L212" s="23" t="s">
-        <v>706</v>
+        <v>1302</v>
       </c>
       <c r="N212" s="1" t="s">
         <v>595</v>
@@ -22707,16 +22716,16 @@
         <v>606</v>
       </c>
       <c r="H213" s="23" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="I213" s="23" t="s">
-        <v>742</v>
+        <v>732</v>
       </c>
       <c r="L213" s="23" t="s">
-        <v>729</v>
+        <v>1302</v>
       </c>
       <c r="M213" s="23" t="s">
-        <v>840</v>
+        <v>813</v>
       </c>
       <c r="N213" s="1" t="s">
         <v>595</v>
@@ -22776,10 +22785,10 @@
         <v>608</v>
       </c>
       <c r="D214" s="23" t="s">
-        <v>1053</v>
+        <v>1020</v>
       </c>
       <c r="E214" s="23" t="s">
-        <v>1223</v>
+        <v>1190</v>
       </c>
       <c r="F214" s="15" t="s">
         <v>610</v>
@@ -22845,10 +22854,10 @@
         <v>612</v>
       </c>
       <c r="D215" s="23" t="s">
-        <v>1054</v>
+        <v>1021</v>
       </c>
       <c r="E215" s="23" t="s">
-        <v>1224</v>
+        <v>1191</v>
       </c>
       <c r="F215" s="15" t="s">
         <v>645</v>
@@ -22860,7 +22869,7 @@
         <v>660</v>
       </c>
       <c r="I215" s="23" t="s">
-        <v>710</v>
+        <v>705</v>
       </c>
       <c r="N215" s="1" t="s">
         <v>594</v>
@@ -22920,10 +22929,10 @@
         <v>328</v>
       </c>
       <c r="D216" s="23" t="s">
-        <v>1055</v>
+        <v>1022</v>
       </c>
       <c r="E216" s="23" t="s">
-        <v>1225</v>
+        <v>1192</v>
       </c>
       <c r="F216" s="2" t="s">
         <v>329</v>
@@ -22935,13 +22944,13 @@
         <v>661</v>
       </c>
       <c r="I216" s="23" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="L216" s="23" t="s">
-        <v>670</v>
+        <v>1300</v>
       </c>
       <c r="M216" s="23" t="s">
-        <v>721</v>
+        <v>712</v>
       </c>
       <c r="N216" s="1" t="s">
         <v>594</v>
@@ -23070,10 +23079,10 @@
         <v>619</v>
       </c>
       <c r="D218" s="23" t="s">
-        <v>1056</v>
+        <v>1023</v>
       </c>
       <c r="E218" s="23" t="s">
-        <v>1226</v>
+        <v>1193</v>
       </c>
       <c r="F218" s="15" t="s">
         <v>198</v>
@@ -23091,10 +23100,10 @@
         <v>668</v>
       </c>
       <c r="L218" s="23" t="s">
-        <v>670</v>
+        <v>1300</v>
       </c>
       <c r="M218" s="23" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="N218" s="1" t="s">
         <v>594</v>
@@ -23154,7 +23163,7 @@
         <v>625</v>
       </c>
       <c r="D219" s="23" t="s">
-        <v>1057</v>
+        <v>1024</v>
       </c>
       <c r="E219" s="23" t="s">
         <v>626</v>
@@ -23223,10 +23232,10 @@
         <v>627</v>
       </c>
       <c r="D220" s="23" t="s">
-        <v>1058</v>
+        <v>1025</v>
       </c>
       <c r="E220" s="23" t="s">
-        <v>1227</v>
+        <v>1194</v>
       </c>
       <c r="F220" s="15" t="s">
         <v>611</v>
@@ -23238,10 +23247,10 @@
         <v>660</v>
       </c>
       <c r="I220" s="23" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="L220" s="23" t="s">
-        <v>713</v>
+        <v>1298</v>
       </c>
       <c r="N220" s="1" t="s">
         <v>594</v>
@@ -23301,10 +23310,10 @@
         <v>628</v>
       </c>
       <c r="D221" s="23" t="s">
-        <v>1059</v>
+        <v>1026</v>
       </c>
       <c r="E221" s="23" t="s">
-        <v>1228</v>
+        <v>1195</v>
       </c>
       <c r="F221" s="15" t="s">
         <v>629</v>
@@ -23439,10 +23448,10 @@
         <v>636</v>
       </c>
       <c r="D223" s="23" t="s">
-        <v>1060</v>
+        <v>1027</v>
       </c>
       <c r="E223" s="23" t="s">
-        <v>1229</v>
+        <v>1196</v>
       </c>
       <c r="F223" s="15" t="s">
         <v>629</v>
@@ -23509,16 +23518,16 @@
         <v>637</v>
       </c>
       <c r="D224" s="23" t="s">
-        <v>1061</v>
+        <v>1028</v>
       </c>
       <c r="E224" s="23" t="s">
-        <v>1230</v>
+        <v>1197</v>
       </c>
       <c r="F224" s="15" t="s">
         <v>638</v>
       </c>
       <c r="G224" s="23" t="s">
-        <v>1254</v>
+        <v>1221</v>
       </c>
       <c r="O224" s="1" t="s">
         <v>549</v>
@@ -23575,10 +23584,10 @@
         <v>639</v>
       </c>
       <c r="D225" s="23" t="s">
-        <v>1062</v>
+        <v>1029</v>
       </c>
       <c r="E225" s="23" t="s">
-        <v>1231</v>
+        <v>1198</v>
       </c>
       <c r="F225" s="15" t="s">
         <v>640</v>
@@ -23662,7 +23671,7 @@
         <v>669</v>
       </c>
       <c r="M226" s="23" t="s">
-        <v>1300</v>
+        <v>1266</v>
       </c>
       <c r="N226" s="1" t="s">
         <v>631</v>
@@ -23725,7 +23734,7 @@
         <v>648</v>
       </c>
       <c r="E227" s="23" t="s">
-        <v>1232</v>
+        <v>1199</v>
       </c>
       <c r="F227" s="15" t="s">
         <v>645</v>
@@ -23740,10 +23749,10 @@
         <v>669</v>
       </c>
       <c r="K227" s="23" t="s">
-        <v>775</v>
+        <v>759</v>
       </c>
       <c r="M227" s="23" t="s">
-        <v>1301</v>
+        <v>1267</v>
       </c>
       <c r="N227" s="1" t="s">
         <v>631</v>
@@ -23800,34 +23809,34 @@
         <v>iruya-rui</v>
       </c>
       <c r="C228" s="24" t="s">
-        <v>722</v>
+        <v>713</v>
       </c>
       <c r="D228" s="23" t="s">
-        <v>1063</v>
+        <v>1030</v>
       </c>
       <c r="E228" s="23" t="s">
-        <v>1233</v>
+        <v>1200</v>
       </c>
       <c r="F228" s="15" t="s">
-        <v>723</v>
+        <v>714</v>
       </c>
       <c r="G228" s="23" t="s">
-        <v>724</v>
+        <v>715</v>
       </c>
       <c r="H228" s="23" t="s">
         <v>660</v>
       </c>
       <c r="I228" s="23" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="K228" s="23" t="s">
-        <v>725</v>
+        <v>716</v>
       </c>
       <c r="L228" s="23" t="s">
-        <v>841</v>
+        <v>1315</v>
       </c>
       <c r="M228" s="23" t="s">
-        <v>842</v>
+        <v>814</v>
       </c>
       <c r="N228" s="1" t="s">
         <v>631</v>
@@ -23884,19 +23893,19 @@
         <v>​hagane-meta</v>
       </c>
       <c r="C229" s="24" t="s">
-        <v>726</v>
+        <v>717</v>
       </c>
       <c r="D229" s="23" t="s">
-        <v>1064</v>
+        <v>1031</v>
       </c>
       <c r="E229" s="23" t="s">
-        <v>1234</v>
+        <v>1201</v>
       </c>
       <c r="F229" s="3" t="s">
-        <v>727</v>
+        <v>718</v>
       </c>
       <c r="G229" s="23" t="s">
-        <v>728</v>
+        <v>719</v>
       </c>
       <c r="H229" s="23" t="s">
         <v>660</v>
@@ -23905,10 +23914,10 @@
         <v>669</v>
       </c>
       <c r="L229" s="23" t="s">
-        <v>729</v>
+        <v>1302</v>
       </c>
       <c r="N229" s="1" t="s">
-        <v>730</v>
+        <v>720</v>
       </c>
       <c r="O229" s="1" t="s">
         <v>549</v>
@@ -23962,28 +23971,28 @@
         <v>the-bard-euphoria</v>
       </c>
       <c r="C230" s="24" t="s">
-        <v>732</v>
+        <v>722</v>
       </c>
       <c r="D230" s="23" t="s">
-        <v>733</v>
+        <v>723</v>
       </c>
       <c r="E230" s="23" t="s">
-        <v>1235</v>
+        <v>1202</v>
       </c>
       <c r="F230" s="29" t="s">
-        <v>736</v>
+        <v>726</v>
       </c>
       <c r="G230" s="23" t="s">
-        <v>735</v>
+        <v>725</v>
       </c>
       <c r="H230" s="23" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="I230" s="23" t="s">
         <v>669</v>
       </c>
       <c r="K230" s="23" t="s">
-        <v>734</v>
+        <v>724</v>
       </c>
       <c r="N230" s="1" t="s">
         <v>631</v>
@@ -24040,34 +24049,34 @@
         <v>arujine-sarasa</v>
       </c>
       <c r="C231" s="24" t="s">
-        <v>737</v>
+        <v>727</v>
       </c>
       <c r="D231" s="23" t="s">
-        <v>1065</v>
+        <v>1032</v>
       </c>
       <c r="E231" s="23" t="s">
-        <v>1236</v>
+        <v>1203</v>
       </c>
       <c r="F231" s="29" t="s">
-        <v>738</v>
+        <v>728</v>
       </c>
       <c r="G231" s="23" t="s">
-        <v>739</v>
+        <v>729</v>
       </c>
       <c r="H231" s="23" t="s">
         <v>661</v>
       </c>
       <c r="I231" s="23" t="s">
-        <v>1266</v>
+        <v>1233</v>
       </c>
       <c r="J231" s="23" t="s">
-        <v>740</v>
+        <v>730</v>
       </c>
       <c r="L231" s="23" t="s">
-        <v>843</v>
+        <v>1310</v>
       </c>
       <c r="M231" s="23" t="s">
-        <v>824</v>
+        <v>799</v>
       </c>
       <c r="N231" s="1" t="s">
         <v>631</v>
@@ -24124,19 +24133,19 @@
         <v>amaga-eru</v>
       </c>
       <c r="C232" s="24" t="s">
-        <v>743</v>
+        <v>733</v>
       </c>
       <c r="D232" s="23" t="s">
-        <v>1066</v>
+        <v>1033</v>
       </c>
       <c r="E232" s="23" t="s">
-        <v>1237</v>
+        <v>1204</v>
       </c>
       <c r="F232" s="29" t="s">
-        <v>744</v>
+        <v>734</v>
       </c>
       <c r="G232" s="23" t="s">
-        <v>745</v>
+        <v>735</v>
       </c>
       <c r="H232" s="23" t="s">
         <v>660</v>
@@ -24145,10 +24154,10 @@
         <v>669</v>
       </c>
       <c r="J232" s="23" t="s">
-        <v>755</v>
+        <v>744</v>
       </c>
       <c r="L232" s="23" t="s">
-        <v>756</v>
+        <v>1304</v>
       </c>
       <c r="N232" s="1" t="s">
         <v>631</v>
@@ -24205,16 +24214,16 @@
         <v>narukami-kyou</v>
       </c>
       <c r="C233" s="24" t="s">
-        <v>747</v>
+        <v>736</v>
       </c>
       <c r="D233" s="23" t="s">
-        <v>1067</v>
+        <v>1034</v>
       </c>
       <c r="E233" s="23" t="s">
-        <v>1238</v>
+        <v>1205</v>
       </c>
       <c r="F233" s="29" t="s">
-        <v>748</v>
+        <v>737</v>
       </c>
       <c r="G233" s="23" t="str">
         <f>テーブル1[[#This Row],[名前]]&amp;"(UTAU)"</f>
@@ -24284,32 +24293,32 @@
         <v>468</v>
       </c>
       <c r="D234" s="23" t="s">
-        <v>1068</v>
+        <v>1035</v>
       </c>
       <c r="E234" s="23" t="s">
-        <v>1239</v>
+        <v>1206</v>
       </c>
       <c r="F234" s="15" t="s">
         <v>122</v>
       </c>
       <c r="G234" s="24" t="s">
-        <v>796</v>
+        <v>778</v>
       </c>
       <c r="H234" s="24" t="s">
         <v>661</v>
       </c>
       <c r="I234" s="24" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="J234" s="24"/>
       <c r="K234" s="24" t="s">
-        <v>792</v>
+        <v>774</v>
       </c>
       <c r="L234" s="24" t="s">
-        <v>791</v>
+        <v>1302</v>
       </c>
       <c r="M234" s="24" t="s">
-        <v>865</v>
+        <v>834</v>
       </c>
       <c r="N234" s="1" t="s">
         <v>631</v>
@@ -24369,32 +24378,32 @@
         <v>469</v>
       </c>
       <c r="D235" s="23" t="s">
-        <v>1069</v>
+        <v>1036</v>
       </c>
       <c r="E235" s="23" t="s">
-        <v>1240</v>
+        <v>1207</v>
       </c>
       <c r="F235" s="15" t="s">
         <v>122</v>
       </c>
       <c r="G235" s="24" t="s">
-        <v>795</v>
+        <v>777</v>
       </c>
       <c r="H235" s="24" t="s">
         <v>661</v>
       </c>
       <c r="I235" s="24" t="s">
-        <v>847</v>
+        <v>817</v>
       </c>
       <c r="J235" s="24"/>
       <c r="K235" s="24" t="s">
-        <v>777</v>
+        <v>761</v>
       </c>
       <c r="L235" s="24" t="s">
-        <v>791</v>
+        <v>1302</v>
       </c>
       <c r="M235" s="24" t="s">
-        <v>848</v>
+        <v>818</v>
       </c>
       <c r="N235" s="1" t="s">
         <v>631</v>
@@ -24451,33 +24460,33 @@
         <v>haizaki-sho</v>
       </c>
       <c r="C236" s="24" t="s">
-        <v>844</v>
+        <v>815</v>
       </c>
       <c r="D236" s="23" t="s">
-        <v>1070</v>
+        <v>1037</v>
       </c>
       <c r="E236" s="23" t="s">
-        <v>1241</v>
+        <v>1208</v>
       </c>
       <c r="F236" s="15" t="s">
         <v>122</v>
       </c>
       <c r="G236" s="24" t="s">
-        <v>795</v>
+        <v>777</v>
       </c>
       <c r="H236" s="24" t="s">
         <v>661</v>
       </c>
       <c r="I236" s="24" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="J236" s="24"/>
       <c r="K236" s="24"/>
       <c r="L236" s="24" t="s">
-        <v>845</v>
+        <v>1302</v>
       </c>
       <c r="M236" s="24" t="s">
-        <v>846</v>
+        <v>816</v>
       </c>
       <c r="N236" s="1" t="s">
         <v>631</v>
@@ -24537,32 +24546,32 @@
         <v>471</v>
       </c>
       <c r="D237" s="23" t="s">
-        <v>1071</v>
+        <v>1038</v>
       </c>
       <c r="E237" s="23" t="s">
-        <v>1242</v>
+        <v>1209</v>
       </c>
       <c r="F237" s="15" t="s">
         <v>122</v>
       </c>
       <c r="G237" s="24" t="s">
-        <v>795</v>
+        <v>777</v>
       </c>
       <c r="H237" s="24" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="I237" s="24" t="s">
-        <v>847</v>
+        <v>817</v>
       </c>
       <c r="J237" s="24" t="s">
-        <v>850</v>
+        <v>820</v>
       </c>
       <c r="K237" s="24"/>
       <c r="L237" s="24" t="s">
-        <v>845</v>
+        <v>1302</v>
       </c>
       <c r="M237" s="24" t="s">
-        <v>709</v>
+        <v>704</v>
       </c>
       <c r="N237" s="1" t="s">
         <v>631</v>
@@ -24631,7 +24640,7 @@
         <v>122</v>
       </c>
       <c r="G238" s="24" t="s">
-        <v>795</v>
+        <v>777</v>
       </c>
       <c r="H238" s="24" t="s">
         <v>661</v>
@@ -24641,7 +24650,7 @@
       <c r="K238" s="24"/>
       <c r="L238" s="24"/>
       <c r="M238" s="24" t="s">
-        <v>851</v>
+        <v>821</v>
       </c>
       <c r="N238" s="1" t="s">
         <v>631</v>
@@ -24710,7 +24719,7 @@
         <v>122</v>
       </c>
       <c r="G239" s="24" t="s">
-        <v>795</v>
+        <v>777</v>
       </c>
       <c r="H239" s="24" t="s">
         <v>661</v>
@@ -24787,7 +24796,7 @@
         <v>122</v>
       </c>
       <c r="G240" s="24" t="s">
-        <v>795</v>
+        <v>777</v>
       </c>
       <c r="H240" s="24" t="s">
         <v>661</v>
@@ -24797,7 +24806,7 @@
       <c r="K240" s="24"/>
       <c r="L240" s="24"/>
       <c r="M240" s="24" t="s">
-        <v>852</v>
+        <v>822</v>
       </c>
       <c r="N240" s="1" t="s">
         <v>631</v>
@@ -24854,28 +24863,28 @@
         <v>kumowatari-tsumugu</v>
       </c>
       <c r="C241" s="24" t="s">
-        <v>853</v>
+        <v>823</v>
       </c>
       <c r="D241" s="23" t="s">
-        <v>1072</v>
+        <v>1039</v>
       </c>
       <c r="E241" s="23" t="s">
-        <v>1243</v>
+        <v>1210</v>
       </c>
       <c r="F241" s="15" t="s">
         <v>122</v>
       </c>
       <c r="G241" s="24" t="s">
-        <v>795</v>
+        <v>777</v>
       </c>
       <c r="H241" s="24" t="s">
         <v>661</v>
       </c>
       <c r="I241" s="24" t="s">
-        <v>854</v>
+        <v>824</v>
       </c>
       <c r="J241" s="23" t="s">
-        <v>855</v>
+        <v>825</v>
       </c>
       <c r="K241" s="24"/>
       <c r="L241" s="24"/>
@@ -24935,30 +24944,30 @@
         <v>hatatappoize</v>
       </c>
       <c r="C242" s="24" t="s">
-        <v>856</v>
+        <v>826</v>
       </c>
       <c r="D242" s="23" t="s">
-        <v>857</v>
+        <v>827</v>
       </c>
       <c r="E242" s="23" t="s">
-        <v>858</v>
+        <v>828</v>
       </c>
       <c r="F242" s="15" t="s">
         <v>122</v>
       </c>
       <c r="G242" s="24" t="s">
-        <v>795</v>
+        <v>777</v>
       </c>
       <c r="H242" s="24" t="s">
         <v>661</v>
       </c>
       <c r="I242" s="24" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="K242" s="24"/>
       <c r="L242" s="24"/>
       <c r="M242" s="24" t="s">
-        <v>861</v>
+        <v>830</v>
       </c>
       <c r="N242" s="1" t="s">
         <v>631</v>
@@ -25015,34 +25024,34 @@
         <v>shiraishi-sakuta</v>
       </c>
       <c r="C243" s="24" t="s">
-        <v>863</v>
+        <v>832</v>
       </c>
       <c r="D243" s="23" t="s">
-        <v>1073</v>
+        <v>1040</v>
       </c>
       <c r="E243" s="23" t="s">
-        <v>1244</v>
+        <v>1211</v>
       </c>
       <c r="F243" s="15" t="s">
         <v>122</v>
       </c>
       <c r="G243" s="24" t="s">
-        <v>795</v>
+        <v>777</v>
       </c>
       <c r="H243" s="24" t="s">
         <v>661</v>
       </c>
       <c r="I243" s="24" t="s">
-        <v>866</v>
+        <v>835</v>
       </c>
       <c r="K243" s="24" t="s">
-        <v>864</v>
+        <v>833</v>
       </c>
       <c r="L243" s="24" t="s">
-        <v>867</v>
+        <v>1311</v>
       </c>
       <c r="M243" s="24" t="s">
-        <v>865</v>
+        <v>834</v>
       </c>
       <c r="N243" s="1" t="s">
         <v>631</v>
@@ -25099,19 +25108,19 @@
         <v>chikusa</v>
       </c>
       <c r="C244" s="24" t="s">
-        <v>868</v>
+        <v>836</v>
       </c>
       <c r="D244" s="23" t="s">
-        <v>868</v>
+        <v>836</v>
       </c>
       <c r="E244" s="23" t="s">
-        <v>869</v>
+        <v>837</v>
       </c>
       <c r="F244" s="15" t="s">
-        <v>870</v>
+        <v>838</v>
       </c>
       <c r="G244" s="24" t="s">
-        <v>871</v>
+        <v>839</v>
       </c>
       <c r="H244" s="24" t="s">
         <v>661</v>
@@ -25120,7 +25129,7 @@
       <c r="K244" s="24"/>
       <c r="L244" s="24"/>
       <c r="M244" s="24" t="s">
-        <v>865</v>
+        <v>834</v>
       </c>
       <c r="N244" s="1" t="s">
         <v>631</v>
@@ -25177,30 +25186,30 @@
         <v>warappoizo</v>
       </c>
       <c r="C245" s="24" t="s">
-        <v>872</v>
+        <v>840</v>
       </c>
       <c r="D245" s="23" t="s">
-        <v>873</v>
+        <v>841</v>
       </c>
       <c r="E245" s="23" t="s">
-        <v>874</v>
+        <v>842</v>
       </c>
       <c r="F245" s="15" t="s">
-        <v>875</v>
+        <v>843</v>
       </c>
       <c r="G245" s="24" t="s">
-        <v>877</v>
+        <v>845</v>
       </c>
       <c r="H245" s="24" t="s">
         <v>661</v>
       </c>
       <c r="I245" s="24" t="s">
-        <v>876</v>
+        <v>844</v>
       </c>
       <c r="K245" s="24"/>
       <c r="L245" s="24"/>
       <c r="N245" s="1" t="s">
-        <v>730</v>
+        <v>720</v>
       </c>
       <c r="O245" s="1" t="s">
         <v>549</v>
@@ -25254,31 +25263,31 @@
         <v>han'ei-xi</v>
       </c>
       <c r="C246" s="24" t="s">
-        <v>878</v>
+        <v>846</v>
       </c>
       <c r="D246" s="23" t="s">
-        <v>1074</v>
+        <v>1041</v>
       </c>
       <c r="E246" s="23" t="s">
-        <v>1245</v>
+        <v>1212</v>
       </c>
       <c r="F246" s="15" t="s">
-        <v>879</v>
+        <v>847</v>
       </c>
       <c r="G246" s="24" t="s">
-        <v>880</v>
+        <v>848</v>
       </c>
       <c r="H246" s="24" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="I246" s="24"/>
       <c r="K246" s="24"/>
       <c r="L246" s="24"/>
       <c r="M246" s="24" t="s">
-        <v>881</v>
+        <v>849</v>
       </c>
       <c r="N246" s="1" t="s">
-        <v>730</v>
+        <v>720</v>
       </c>
       <c r="O246" s="1" t="s">
         <v>549</v>
@@ -25332,33 +25341,33 @@
         <v>aisu-kurimu</v>
       </c>
       <c r="C247" s="24" t="s">
-        <v>882</v>
+        <v>850</v>
       </c>
       <c r="D247" s="23" t="s">
-        <v>1075</v>
+        <v>1042</v>
       </c>
       <c r="E247" s="23" t="s">
-        <v>1246</v>
+        <v>1213</v>
       </c>
       <c r="F247" s="15" t="s">
-        <v>883</v>
+        <v>851</v>
       </c>
       <c r="G247" s="24" t="s">
-        <v>884</v>
+        <v>852</v>
       </c>
       <c r="H247" s="24" t="s">
         <v>660</v>
       </c>
       <c r="I247" s="24" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="J247" s="23" t="s">
-        <v>885</v>
+        <v>853</v>
       </c>
       <c r="K247" s="24"/>
       <c r="L247" s="24"/>
       <c r="M247" s="24" t="s">
-        <v>707</v>
+        <v>702</v>
       </c>
       <c r="N247" s="1" t="s">
         <v>631</v>
@@ -25415,13 +25424,13 @@
         <v>utakata-tsuzuri</v>
       </c>
       <c r="C248" s="24" t="s">
-        <v>886</v>
+        <v>854</v>
       </c>
       <c r="D248" s="23" t="s">
-        <v>1076</v>
+        <v>1043</v>
       </c>
       <c r="E248" s="23" t="s">
-        <v>1247</v>
+        <v>1214</v>
       </c>
       <c r="F248" s="15" t="s">
         <v>235</v>
@@ -25436,7 +25445,7 @@
         <v>669</v>
       </c>
       <c r="K248" s="23" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="L248" s="24"/>
       <c r="M248" s="24"/>
@@ -25495,13 +25504,13 @@
         <v>f-113</v>
       </c>
       <c r="C249" s="24" t="s">
-        <v>887</v>
+        <v>855</v>
       </c>
       <c r="D249" s="23" t="s">
-        <v>1077</v>
+        <v>1044</v>
       </c>
       <c r="E249" s="23" t="s">
-        <v>887</v>
+        <v>855</v>
       </c>
       <c r="F249" s="15" t="s">
         <v>235</v>
@@ -25513,10 +25522,10 @@
         <v>660</v>
       </c>
       <c r="I249" s="24" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="L249" s="24" t="s">
-        <v>867</v>
+        <v>1311</v>
       </c>
       <c r="M249" s="24"/>
       <c r="N249" s="1" t="s">
@@ -25574,22 +25583,22 @@
         <v>apuda</v>
       </c>
       <c r="C250" s="24" t="s">
-        <v>888</v>
+        <v>856</v>
       </c>
       <c r="D250" s="23" t="s">
-        <v>889</v>
+        <v>857</v>
       </c>
       <c r="E250" s="23" t="s">
-        <v>890</v>
+        <v>858</v>
       </c>
       <c r="F250" s="15" t="s">
-        <v>891</v>
+        <v>859</v>
       </c>
       <c r="G250" s="23" t="s">
-        <v>892</v>
+        <v>860</v>
       </c>
       <c r="H250" s="24" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="I250" s="24" t="s">
         <v>669</v>
@@ -25598,10 +25607,10 @@
         <v>668</v>
       </c>
       <c r="L250" s="24" t="s">
-        <v>893</v>
+        <v>1319</v>
       </c>
       <c r="M250" s="24" t="s">
-        <v>797</v>
+        <v>779</v>
       </c>
       <c r="N250" s="1" t="s">
         <v>631</v>
@@ -25658,32 +25667,32 @@
         <v>hebikawa-ren</v>
       </c>
       <c r="C251" s="24" t="s">
-        <v>894</v>
+        <v>861</v>
       </c>
       <c r="D251" s="23" t="s">
-        <v>1078</v>
+        <v>1045</v>
       </c>
       <c r="E251" s="23" t="s">
-        <v>1248</v>
+        <v>1215</v>
       </c>
       <c r="F251" s="15" t="s">
         <v>123</v>
       </c>
       <c r="G251" s="23" t="s">
-        <v>906</v>
+        <v>873</v>
       </c>
       <c r="H251" s="24" t="s">
         <v>661</v>
       </c>
       <c r="I251" s="24" t="s">
-        <v>1266</v>
+        <v>1233</v>
       </c>
       <c r="J251" s="23" t="s">
-        <v>895</v>
+        <v>862</v>
       </c>
       <c r="L251" s="24"/>
       <c r="M251" s="24" t="s">
-        <v>1255</v>
+        <v>1222</v>
       </c>
       <c r="N251" s="1" t="s">
         <v>631</v>
@@ -25740,28 +25749,28 @@
         <v>karasuda-tsubaki</v>
       </c>
       <c r="C252" s="24" t="s">
-        <v>896</v>
+        <v>863</v>
       </c>
       <c r="D252" s="23" t="s">
-        <v>1079</v>
+        <v>1046</v>
       </c>
       <c r="E252" s="23" t="s">
-        <v>1249</v>
+        <v>1216</v>
       </c>
       <c r="F252" s="15" t="s">
         <v>123</v>
       </c>
       <c r="G252" s="24" t="s">
-        <v>903</v>
+        <v>870</v>
       </c>
       <c r="H252" s="24" t="s">
         <v>661</v>
       </c>
       <c r="I252" s="24" t="s">
-        <v>1267</v>
+        <v>1234</v>
       </c>
       <c r="J252" s="23" t="s">
-        <v>907</v>
+        <v>874</v>
       </c>
       <c r="L252" s="24"/>
       <c r="M252" s="24"/>
@@ -25820,32 +25829,32 @@
         <v>the-alien-cat-lyce</v>
       </c>
       <c r="C253" s="24" t="s">
-        <v>897</v>
+        <v>864</v>
       </c>
       <c r="D253" s="23" t="s">
-        <v>912</v>
+        <v>879</v>
       </c>
       <c r="E253" s="23" t="s">
-        <v>1250</v>
+        <v>1217</v>
       </c>
       <c r="F253" s="15" t="s">
-        <v>898</v>
+        <v>865</v>
       </c>
       <c r="G253" s="24" t="s">
-        <v>899</v>
+        <v>866</v>
       </c>
       <c r="H253" s="24" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="I253" s="24" t="s">
-        <v>759</v>
+        <v>747</v>
       </c>
       <c r="J253" s="23" t="s">
-        <v>787</v>
+        <v>771</v>
       </c>
       <c r="L253" s="24"/>
       <c r="M253" s="23" t="s">
-        <v>824</v>
+        <v>799</v>
       </c>
       <c r="N253" s="1" t="s">
         <v>631</v>
@@ -25902,28 +25911,28 @@
         <v>kr-725</v>
       </c>
       <c r="C254" s="24" t="s">
-        <v>908</v>
+        <v>875</v>
       </c>
       <c r="D254" s="23" t="s">
-        <v>909</v>
+        <v>876</v>
       </c>
       <c r="E254" s="23" t="s">
-        <v>908</v>
+        <v>875</v>
       </c>
       <c r="F254" s="15" t="s">
         <v>557</v>
       </c>
       <c r="G254" s="24" t="s">
-        <v>910</v>
+        <v>877</v>
       </c>
       <c r="H254" s="24" t="s">
         <v>660</v>
       </c>
       <c r="I254" s="24" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="K254" s="23" t="s">
-        <v>902</v>
+        <v>869</v>
       </c>
       <c r="L254" s="24"/>
       <c r="M254" s="24" t="s">
@@ -25984,34 +25993,34 @@
         <v>kurumiyaki-yosiyuki</v>
       </c>
       <c r="C255" s="24" t="s">
-        <v>900</v>
+        <v>867</v>
       </c>
       <c r="D255" s="23" t="s">
-        <v>1080</v>
+        <v>1047</v>
       </c>
       <c r="E255" s="23" t="s">
-        <v>1251</v>
+        <v>1218</v>
       </c>
       <c r="F255" s="15" t="s">
-        <v>901</v>
+        <v>868</v>
       </c>
       <c r="G255" s="24" t="s">
-        <v>1270</v>
+        <v>1236</v>
       </c>
       <c r="H255" s="24" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="I255" s="24" t="s">
-        <v>1266</v>
+        <v>1233</v>
       </c>
       <c r="J255" s="23" t="s">
-        <v>1265</v>
+        <v>1232</v>
       </c>
       <c r="L255" s="24" t="s">
-        <v>1268</v>
+        <v>1317</v>
       </c>
       <c r="M255" s="24" t="s">
-        <v>1269</v>
+        <v>1235</v>
       </c>
       <c r="N255" s="1" t="s">
         <v>631</v>
@@ -26068,19 +26077,19 @@
         <v>oumi-kurina</v>
       </c>
       <c r="C256" s="24" t="s">
-        <v>1256</v>
+        <v>1223</v>
       </c>
       <c r="D256" s="23" t="s">
-        <v>1257</v>
+        <v>1224</v>
       </c>
       <c r="E256" s="23" t="s">
-        <v>1258</v>
+        <v>1225</v>
       </c>
       <c r="F256" s="15" t="s">
-        <v>1259</v>
+        <v>1226</v>
       </c>
       <c r="G256" s="24" t="s">
-        <v>1271</v>
+        <v>1237</v>
       </c>
       <c r="H256" s="24" t="s">
         <v>660</v>
@@ -26145,19 +26154,19 @@
         <v>mitama</v>
       </c>
       <c r="C257" s="24" t="s">
-        <v>1260</v>
+        <v>1227</v>
       </c>
       <c r="D257" s="23" t="s">
-        <v>1260</v>
+        <v>1227</v>
       </c>
       <c r="E257" s="23" t="s">
-        <v>1261</v>
+        <v>1228</v>
       </c>
       <c r="F257" s="15" t="s">
-        <v>870</v>
+        <v>838</v>
       </c>
       <c r="G257" s="24" t="s">
-        <v>1272</v>
+        <v>1238</v>
       </c>
       <c r="H257" s="24" t="s">
         <v>660</v>
@@ -26166,10 +26175,10 @@
         <v>669</v>
       </c>
       <c r="L257" s="24" t="s">
-        <v>729</v>
+        <v>1302</v>
       </c>
       <c r="M257" s="24" t="s">
-        <v>846</v>
+        <v>816</v>
       </c>
       <c r="N257" s="1" t="s">
         <v>631</v>
@@ -26226,29 +26235,29 @@
         <v>mirakibo-11-gou</v>
       </c>
       <c r="C258" s="24" t="s">
-        <v>1262</v>
+        <v>1229</v>
       </c>
       <c r="D258" s="23" t="s">
-        <v>1263</v>
+        <v>1230</v>
       </c>
       <c r="E258" s="23" t="s">
-        <v>1264</v>
+        <v>1231</v>
       </c>
       <c r="F258" s="15" t="s">
-        <v>1259</v>
+        <v>1226</v>
       </c>
       <c r="G258" s="24" t="s">
-        <v>1273</v>
+        <v>1239</v>
       </c>
       <c r="H258" s="24" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="I258" s="24" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="L258" s="24"/>
       <c r="M258" s="24" t="s">
-        <v>709</v>
+        <v>704</v>
       </c>
       <c r="N258" s="1" t="s">
         <v>631</v>
@@ -26297,27 +26306,27 @@
       </c>
     </row>
     <row r="259" spans="1:25" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A259" s="34">
+      <c r="A259" s="20">
         <v>258</v>
       </c>
-      <c r="B259" s="32" t="str">
+      <c r="B259" s="23" t="str">
         <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(テーブル1[[#This Row],[Name]])," ","-"),".","-"),"&amp;","-"),"_","-"),"・","-"),"=","-"),"--","-"),"--","-")</f>
         <v>otoya-syuki</v>
       </c>
       <c r="C259" s="24" t="s">
-        <v>1274</v>
+        <v>1240</v>
       </c>
       <c r="D259" s="23" t="s">
-        <v>1275</v>
+        <v>1241</v>
       </c>
       <c r="E259" s="23" t="s">
-        <v>1276</v>
+        <v>1242</v>
       </c>
       <c r="F259" s="29" t="s">
-        <v>1277</v>
+        <v>1243</v>
       </c>
       <c r="G259" s="23" t="s">
-        <v>1278</v>
+        <v>1244</v>
       </c>
       <c r="H259" s="23" t="s">
         <v>661</v>
@@ -26326,13 +26335,13 @@
         <v>669</v>
       </c>
       <c r="K259" s="23" t="s">
-        <v>1279</v>
+        <v>1245</v>
       </c>
       <c r="L259" s="24" t="s">
-        <v>670</v>
+        <v>1300</v>
       </c>
       <c r="M259" s="24" t="s">
-        <v>846</v>
+        <v>816</v>
       </c>
       <c r="N259" s="1" t="s">
         <v>631</v>
@@ -26340,7 +26349,7 @@
       <c r="O259" s="1" t="s">
         <v>549</v>
       </c>
-      <c r="P259" s="33" t="str">
+      <c r="P259" s="24" t="str">
         <f>テーブル1[[#This Row],[リンク]]&amp;テーブル1[[#This Row],[描画状況]]</f>
         <v>https://sikiori.wepage.com済</v>
       </c>
@@ -26352,53 +26361,56 @@
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
         <v/>
       </c>
-      <c r="T259" s="33">
+      <c r="S259" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="T259" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
-        <v>4.0452213999074949E-2</v>
-      </c>
-      <c r="U259" s="32" t="str">
+        <v/>
+      </c>
+      <c r="U259" s="23" t="str">
         <f>"|&amp;image("&amp;テーブル1[[#This Row],[画像]]&amp;".png,width=100,height=100)"</f>
         <v>|&amp;image(otoya-syuki.png,width=100,height=100)</v>
       </c>
-      <c r="V259" s="32" t="str">
+      <c r="V259" s="23" t="str">
         <f>"|MIDDLE:​"&amp;テーブル1[[#This Row],[名前]]</f>
         <v>|MIDDLE:​音夜秋月</v>
       </c>
-      <c r="W259" s="32" t="str">
+      <c r="W259" s="23" t="str">
         <f>"|MIDDLE:​"&amp;テーブル1[[#This Row],[なまえ]]</f>
         <v>|MIDDLE:​おとや しゅうき</v>
       </c>
-      <c r="X259" s="32" t="str">
+      <c r="X259" s="23" t="str">
         <f>"|MIDDLE:​"&amp;テーブル1[[#This Row],[Name]]</f>
         <v>|MIDDLE:​Otoya Syuki</v>
       </c>
-      <c r="Y259" s="32" t="str">
+      <c r="Y259" s="23" t="str">
         <f>"|MIDDLE:​&amp;link(配布所はこちら){​"&amp;テーブル1[[#This Row],[リンク]]&amp;"}|"</f>
         <v>|MIDDLE:​&amp;link(配布所はこちら){​https://sikiori.wepage.com}|</v>
       </c>
     </row>
     <row r="260" spans="1:25" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A260" s="34">
+      <c r="A260" s="20">
         <v>259</v>
       </c>
-      <c r="B260" s="32" t="str">
+      <c r="B260" s="23" t="str">
         <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(テーブル1[[#This Row],[Name]])," ","-"),".","-"),"&amp;","-"),"_","-"),"・","-"),"=","-"),"--","-"),"--","-")</f>
         <v>natsuno-seito</v>
       </c>
       <c r="C260" s="24" t="s">
-        <v>1280</v>
+        <v>1246</v>
       </c>
       <c r="D260" s="23" t="s">
-        <v>1281</v>
+        <v>1247</v>
       </c>
       <c r="E260" s="23" t="s">
-        <v>1282</v>
+        <v>1248</v>
       </c>
       <c r="F260" s="29" t="s">
-        <v>1277</v>
+        <v>1243</v>
       </c>
       <c r="G260" s="23" t="s">
-        <v>1278</v>
+        <v>1244</v>
       </c>
       <c r="H260" s="23" t="s">
         <v>661</v>
@@ -26407,10 +26419,10 @@
         <v>669</v>
       </c>
       <c r="K260" s="23" t="s">
-        <v>1283</v>
+        <v>1249</v>
       </c>
       <c r="M260" s="24" t="s">
-        <v>846</v>
+        <v>816</v>
       </c>
       <c r="N260" s="1" t="s">
         <v>631</v>
@@ -26418,7 +26430,7 @@
       <c r="O260" s="1" t="s">
         <v>549</v>
       </c>
-      <c r="P260" s="33" t="str">
+      <c r="P260" s="24" t="str">
         <f>テーブル1[[#This Row],[リンク]]&amp;テーブル1[[#This Row],[描画状況]]</f>
         <v>https://sikiori.wepage.com済</v>
       </c>
@@ -26430,53 +26442,56 @@
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
         <v/>
       </c>
-      <c r="T260" s="33">
+      <c r="S260" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="T260" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
-        <v>0.4146115591406081</v>
-      </c>
-      <c r="U260" s="32" t="str">
+        <v/>
+      </c>
+      <c r="U260" s="23" t="str">
         <f>"|&amp;image("&amp;テーブル1[[#This Row],[画像]]&amp;".png,width=100,height=100)"</f>
         <v>|&amp;image(natsuno-seito.png,width=100,height=100)</v>
       </c>
-      <c r="V260" s="32" t="str">
+      <c r="V260" s="23" t="str">
         <f>"|MIDDLE:​"&amp;テーブル1[[#This Row],[名前]]</f>
         <v>|MIDDLE:​夏乃星音</v>
       </c>
-      <c r="W260" s="32" t="str">
+      <c r="W260" s="23" t="str">
         <f>"|MIDDLE:​"&amp;テーブル1[[#This Row],[なまえ]]</f>
         <v>|MIDDLE:​なつの せいと</v>
       </c>
-      <c r="X260" s="32" t="str">
+      <c r="X260" s="23" t="str">
         <f>"|MIDDLE:​"&amp;テーブル1[[#This Row],[Name]]</f>
         <v>|MIDDLE:​Natsuno Seito</v>
       </c>
-      <c r="Y260" s="32" t="str">
+      <c r="Y260" s="23" t="str">
         <f>"|MIDDLE:​&amp;link(配布所はこちら){​"&amp;テーブル1[[#This Row],[リンク]]&amp;"}|"</f>
         <v>|MIDDLE:​&amp;link(配布所はこちら){​https://sikiori.wepage.com}|</v>
       </c>
     </row>
     <row r="261" spans="1:25" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A261" s="34">
+      <c r="A261" s="20">
         <v>260</v>
       </c>
-      <c r="B261" s="32" t="str">
+      <c r="B261" s="23" t="str">
         <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(テーブル1[[#This Row],[Name]])," ","-"),".","-"),"&amp;","-"),"_","-"),"・","-"),"=","-"),"--","-"),"--","-")</f>
         <v>makimiya-fuki</v>
       </c>
       <c r="C261" s="24" t="s">
-        <v>1284</v>
+        <v>1250</v>
       </c>
       <c r="D261" s="23" t="s">
-        <v>1285</v>
+        <v>1251</v>
       </c>
       <c r="E261" s="23" t="s">
-        <v>1286</v>
+        <v>1252</v>
       </c>
       <c r="F261" s="29" t="s">
-        <v>1287</v>
+        <v>1253</v>
       </c>
       <c r="G261" s="23" t="s">
-        <v>1303</v>
+        <v>1269</v>
       </c>
       <c r="H261" s="23" t="s">
         <v>661</v>
@@ -26485,10 +26500,10 @@
         <v>669</v>
       </c>
       <c r="K261" s="23" t="s">
-        <v>1305</v>
+        <v>1270</v>
       </c>
       <c r="L261" s="23" t="s">
-        <v>1304</v>
+        <v>1308</v>
       </c>
       <c r="N261" s="1" t="s">
         <v>631</v>
@@ -26496,7 +26511,7 @@
       <c r="O261" s="1" t="s">
         <v>549</v>
       </c>
-      <c r="P261" s="33" t="str">
+      <c r="P261" s="24" t="str">
         <f>テーブル1[[#This Row],[リンク]]&amp;テーブル1[[#This Row],[描画状況]]</f>
         <v>https://mohumohuton.web.fc2.com/makimiya/index.html済</v>
       </c>
@@ -26508,62 +26523,65 @@
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
         <v/>
       </c>
-      <c r="T261" s="33">
+      <c r="S261" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="T261" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
-        <v>0.13814719038225154</v>
-      </c>
-      <c r="U261" s="32" t="str">
+        <v/>
+      </c>
+      <c r="U261" s="23" t="str">
         <f>"|&amp;image("&amp;テーブル1[[#This Row],[画像]]&amp;".png,width=100,height=100)"</f>
         <v>|&amp;image(makimiya-fuki.png,width=100,height=100)</v>
       </c>
-      <c r="V261" s="32" t="str">
+      <c r="V261" s="23" t="str">
         <f>"|MIDDLE:​"&amp;テーブル1[[#This Row],[名前]]</f>
         <v>|MIDDLE:​薪宮風季</v>
       </c>
-      <c r="W261" s="32" t="str">
+      <c r="W261" s="23" t="str">
         <f>"|MIDDLE:​"&amp;テーブル1[[#This Row],[なまえ]]</f>
         <v>|MIDDLE:​まきみや ふうき</v>
       </c>
-      <c r="X261" s="32" t="str">
+      <c r="X261" s="23" t="str">
         <f>"|MIDDLE:​"&amp;テーブル1[[#This Row],[Name]]</f>
         <v>|MIDDLE:​Makimiya Fuki</v>
       </c>
-      <c r="Y261" s="32" t="str">
+      <c r="Y261" s="23" t="str">
         <f>"|MIDDLE:​&amp;link(配布所はこちら){​"&amp;テーブル1[[#This Row],[リンク]]&amp;"}|"</f>
         <v>|MIDDLE:​&amp;link(配布所はこちら){​https://mohumohuton.web.fc2.com/makimiya/index.html}|</v>
       </c>
     </row>
     <row r="262" spans="1:25" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A262" s="34">
+      <c r="A262" s="20">
         <v>261</v>
       </c>
-      <c r="B262" s="32" t="str">
+      <c r="B262" s="23" t="str">
         <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(テーブル1[[#This Row],[Name]])," ","-"),".","-"),"&amp;","-"),"_","-"),"・","-"),"=","-"),"--","-"),"--","-")</f>
         <v>wakunemu-supika</v>
       </c>
       <c r="C262" s="24" t="s">
-        <v>1290</v>
+        <v>1256</v>
       </c>
       <c r="D262" s="23" t="s">
-        <v>1288</v>
+        <v>1254</v>
       </c>
       <c r="E262" s="28" t="s">
-        <v>1289</v>
+        <v>1255</v>
       </c>
       <c r="F262" s="29" t="s">
         <v>645</v>
       </c>
       <c r="G262" s="23" t="s">
-        <v>1299</v>
+        <v>1265</v>
       </c>
       <c r="H262" s="23" t="s">
         <v>660</v>
       </c>
       <c r="I262" s="23" t="s">
-        <v>1266</v>
+        <v>1233</v>
       </c>
       <c r="J262" s="23" t="s">
-        <v>1302</v>
+        <v>1268</v>
       </c>
       <c r="N262" s="1" t="s">
         <v>631</v>
@@ -26571,7 +26589,7 @@
       <c r="O262" s="1" t="s">
         <v>549</v>
       </c>
-      <c r="P262" s="33" t="str">
+      <c r="P262" s="24" t="str">
         <f>テーブル1[[#This Row],[リンク]]&amp;テーブル1[[#This Row],[描画状況]]</f>
         <v>https://bowlroll.net/user/946776済</v>
       </c>
@@ -26583,68 +26601,71 @@
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
         <v/>
       </c>
-      <c r="T262" s="33">
+      <c r="S262" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="T262" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
-        <v>0.33472977357204536</v>
-      </c>
-      <c r="U262" s="32" t="str">
+        <v/>
+      </c>
+      <c r="U262" s="23" t="str">
         <f>"|&amp;image("&amp;テーブル1[[#This Row],[画像]]&amp;".png,width=100,height=100)"</f>
         <v>|&amp;image(wakunemu-supika.png,width=100,height=100)</v>
       </c>
-      <c r="V262" s="32" t="str">
+      <c r="V262" s="23" t="str">
         <f>"|MIDDLE:​"&amp;テーブル1[[#This Row],[名前]]</f>
         <v>|MIDDLE:​わくねむすぴか</v>
       </c>
-      <c r="W262" s="32" t="str">
+      <c r="W262" s="23" t="str">
         <f>"|MIDDLE:​"&amp;テーブル1[[#This Row],[なまえ]]</f>
         <v>|MIDDLE:​わくねむ すぴか</v>
       </c>
-      <c r="X262" s="32" t="str">
+      <c r="X262" s="23" t="str">
         <f>"|MIDDLE:​"&amp;テーブル1[[#This Row],[Name]]</f>
         <v>|MIDDLE:​Wakunemu Supika</v>
       </c>
-      <c r="Y262" s="32" t="str">
+      <c r="Y262" s="23" t="str">
         <f>"|MIDDLE:​&amp;link(配布所はこちら){​"&amp;テーブル1[[#This Row],[リンク]]&amp;"}|"</f>
         <v>|MIDDLE:​&amp;link(配布所はこちら){​https://bowlroll.net/user/946776}|</v>
       </c>
     </row>
     <row r="263" spans="1:25" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A263" s="34">
+      <c r="A263" s="20">
         <v>262</v>
       </c>
-      <c r="B263" s="32" t="str">
+      <c r="B263" s="23" t="str">
         <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(テーブル1[[#This Row],[Name]])," ","-"),".","-"),"&amp;","-"),"_","-"),"・","-"),"=","-"),"--","-"),"--","-")</f>
         <v>sumomone-fueru</v>
       </c>
       <c r="C263" s="24" t="s">
-        <v>1291</v>
+        <v>1257</v>
       </c>
       <c r="D263" s="23" t="s">
-        <v>1292</v>
+        <v>1258</v>
       </c>
       <c r="E263" s="23" t="s">
-        <v>1293</v>
+        <v>1259</v>
       </c>
       <c r="F263" s="29" t="s">
-        <v>1294</v>
+        <v>1260</v>
       </c>
       <c r="G263" s="23" t="s">
-        <v>1298</v>
+        <v>1264</v>
       </c>
       <c r="H263" s="23" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="I263" s="23" t="s">
-        <v>710</v>
+        <v>705</v>
       </c>
       <c r="K263" s="23" t="s">
-        <v>1295</v>
+        <v>1261</v>
       </c>
       <c r="L263" s="23" t="s">
-        <v>1296</v>
+        <v>1262</v>
       </c>
       <c r="M263" s="23" t="s">
-        <v>1297</v>
+        <v>1263</v>
       </c>
       <c r="N263" s="1" t="s">
         <v>631</v>
@@ -26652,7 +26673,7 @@
       <c r="O263" s="1" t="s">
         <v>549</v>
       </c>
-      <c r="P263" s="33" t="str">
+      <c r="P263" s="24" t="str">
         <f>テーブル1[[#This Row],[リンク]]&amp;テーブル1[[#This Row],[描画状況]]</f>
         <v>https://suukedayo.wixsite.com/shiawasefairu済</v>
       </c>
@@ -26664,30 +26685,516 @@
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
         <v/>
       </c>
-      <c r="T263" s="33">
+      <c r="S263" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="T263" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
-        <v>0.42367404479769655</v>
-      </c>
-      <c r="U263" s="32" t="str">
+        <v/>
+      </c>
+      <c r="U263" s="23" t="str">
         <f>"|&amp;image("&amp;テーブル1[[#This Row],[画像]]&amp;".png,width=100,height=100)"</f>
         <v>|&amp;image(sumomone-fueru.png,width=100,height=100)</v>
       </c>
-      <c r="V263" s="32" t="str">
+      <c r="V263" s="23" t="str">
         <f>"|MIDDLE:​"&amp;テーブル1[[#This Row],[名前]]</f>
         <v>|MIDDLE:​李音フヱル</v>
       </c>
-      <c r="W263" s="32" t="str">
+      <c r="W263" s="23" t="str">
         <f>"|MIDDLE:​"&amp;テーブル1[[#This Row],[なまえ]]</f>
         <v>|MIDDLE:​すももね ふえる</v>
       </c>
-      <c r="X263" s="32" t="str">
+      <c r="X263" s="23" t="str">
         <f>"|MIDDLE:​"&amp;テーブル1[[#This Row],[Name]]</f>
         <v>|MIDDLE:​Sumomone Fueru</v>
       </c>
-      <c r="Y263" s="32" t="str">
+      <c r="Y263" s="23" t="str">
         <f>"|MIDDLE:​&amp;link(配布所はこちら){​"&amp;テーブル1[[#This Row],[リンク]]&amp;"}|"</f>
         <v>|MIDDLE:​&amp;link(配布所はこちら){​https://suukedayo.wixsite.com/shiawasefairu}|</v>
       </c>
+    </row>
+    <row r="264" spans="1:25" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A264" s="34">
+        <v>263</v>
+      </c>
+      <c r="B264" s="23" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(テーブル1[[#This Row],[Name]])," ","-"),".","-"),"&amp;","-"),"_","-"),"・","-"),"=","-"),"--","-"),"--","-")</f>
+        <v>ubuon-goe</v>
+      </c>
+      <c r="C264" s="24" t="s">
+        <v>1272</v>
+      </c>
+      <c r="D264" s="23" t="s">
+        <v>1273</v>
+      </c>
+      <c r="E264" s="23" t="s">
+        <v>1274</v>
+      </c>
+      <c r="F264" s="29" t="s">
+        <v>1295</v>
+      </c>
+      <c r="G264" s="23" t="s">
+        <v>1294</v>
+      </c>
+      <c r="H264" s="23" t="s">
+        <v>683</v>
+      </c>
+      <c r="I264" s="23" t="s">
+        <v>783</v>
+      </c>
+      <c r="L264" s="23" t="s">
+        <v>1313</v>
+      </c>
+      <c r="N264" s="1" t="s">
+        <v>631</v>
+      </c>
+      <c r="O264" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="P264" s="24" t="str">
+        <f>テーブル1[[#This Row],[リンク]]&amp;テーブル1[[#This Row],[描画状況]]</f>
+        <v>https://nagimachi.wixsite.com/kairikonomachi済</v>
+      </c>
+      <c r="Q264" s="17">
+        <f>1-(COUNTIF(P:P,_xlfn.TEXTJOIN(",",TRUE,テーブル1[[#This Row],[リンク]],テーブル1[[#This Row],[描画状況]]))/COUNTIF(F:F,テーブル1[[#This Row],[リンク]]))</f>
+        <v>1</v>
+      </c>
+      <c r="R264" s="16" t="str">
+        <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
+        <v/>
+      </c>
+      <c r="T264" s="24">
+        <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
+        <v>0.84773905082587875</v>
+      </c>
+      <c r="U264" s="23" t="str">
+        <f>"|&amp;image("&amp;テーブル1[[#This Row],[画像]]&amp;".png,width=100,height=100)"</f>
+        <v>|&amp;image(ubuon-goe.png,width=100,height=100)</v>
+      </c>
+      <c r="V264" s="23" t="str">
+        <f>"|MIDDLE:​"&amp;テーブル1[[#This Row],[名前]]</f>
+        <v>|MIDDLE:​有部音ゴエμ</v>
+      </c>
+      <c r="W264" s="23" t="str">
+        <f>"|MIDDLE:​"&amp;テーブル1[[#This Row],[なまえ]]</f>
+        <v>|MIDDLE:​うぶおん ごえ</v>
+      </c>
+      <c r="X264" s="23" t="str">
+        <f>"|MIDDLE:​"&amp;テーブル1[[#This Row],[Name]]</f>
+        <v>|MIDDLE:​Ubuon Goe</v>
+      </c>
+      <c r="Y264" s="23" t="str">
+        <f>"|MIDDLE:​&amp;link(配布所はこちら){​"&amp;テーブル1[[#This Row],[リンク]]&amp;"}|"</f>
+        <v>|MIDDLE:​&amp;link(配布所はこちら){​https://nagimachi.wixsite.com/kairikonomachi}|</v>
+      </c>
+    </row>
+    <row r="265" spans="1:25" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A265" s="34">
+        <v>264</v>
+      </c>
+      <c r="B265" s="23" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(テーブル1[[#This Row],[Name]])," ","-"),".","-"),"&amp;","-"),"_","-"),"・","-"),"=","-"),"--","-"),"--","-")</f>
+        <v>shuta-katsue</v>
+      </c>
+      <c r="C265" s="24" t="s">
+        <v>1271</v>
+      </c>
+      <c r="D265" s="23" t="s">
+        <v>1275</v>
+      </c>
+      <c r="E265" s="23" t="s">
+        <v>1276</v>
+      </c>
+      <c r="F265" s="29" t="s">
+        <v>1295</v>
+      </c>
+      <c r="G265" s="23" t="s">
+        <v>1294</v>
+      </c>
+      <c r="H265" s="23" t="s">
+        <v>660</v>
+      </c>
+      <c r="I265" s="23" t="s">
+        <v>669</v>
+      </c>
+      <c r="L265" s="23" t="s">
+        <v>1300</v>
+      </c>
+      <c r="N265" s="1" t="s">
+        <v>631</v>
+      </c>
+      <c r="P265" s="24" t="str">
+        <f>テーブル1[[#This Row],[リンク]]&amp;テーブル1[[#This Row],[描画状況]]</f>
+        <v>https://nagimachi.wixsite.com/kairikonomachi</v>
+      </c>
+      <c r="Q265" s="17">
+        <f>1-(COUNTIF(P:P,_xlfn.TEXTJOIN(",",TRUE,テーブル1[[#This Row],[リンク]],テーブル1[[#This Row],[描画状況]]))/COUNTIF(F:F,テーブル1[[#This Row],[リンク]]))</f>
+        <v>0.25</v>
+      </c>
+      <c r="R265" s="16">
+        <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
+        <v>25.463509101207258</v>
+      </c>
+      <c r="T265" s="24" t="str">
+        <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
+        <v/>
+      </c>
+      <c r="U265" s="23" t="str">
+        <f>"|&amp;image("&amp;テーブル1[[#This Row],[画像]]&amp;".png,width=100,height=100)"</f>
+        <v>|&amp;image(shuta-katsue.png,width=100,height=100)</v>
+      </c>
+      <c r="V265" s="23" t="str">
+        <f>"|MIDDLE:​"&amp;テーブル1[[#This Row],[名前]]</f>
+        <v>|MIDDLE:​終歌カツエα</v>
+      </c>
+      <c r="W265" s="23" t="str">
+        <f>"|MIDDLE:​"&amp;テーブル1[[#This Row],[なまえ]]</f>
+        <v>|MIDDLE:​しゅうた かつえ</v>
+      </c>
+      <c r="X265" s="23" t="str">
+        <f>"|MIDDLE:​"&amp;テーブル1[[#This Row],[Name]]</f>
+        <v>|MIDDLE:​Shuta Katsue</v>
+      </c>
+      <c r="Y265" s="23" t="str">
+        <f>"|MIDDLE:​&amp;link(配布所はこちら){​"&amp;テーブル1[[#This Row],[リンク]]&amp;"}|"</f>
+        <v>|MIDDLE:​&amp;link(配布所はこちら){​https://nagimachi.wixsite.com/kairikonomachi}|</v>
+      </c>
+    </row>
+    <row r="266" spans="1:25" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A266" s="34">
+        <v>265</v>
+      </c>
+      <c r="B266" s="23" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(テーブル1[[#This Row],[Name]])," ","-"),".","-"),"&amp;","-"),"_","-"),"・","-"),"=","-"),"--","-"),"--","-")</f>
+        <v>narune-bell</v>
+      </c>
+      <c r="C266" s="24" t="s">
+        <v>1277</v>
+      </c>
+      <c r="D266" s="23" t="s">
+        <v>1278</v>
+      </c>
+      <c r="E266" s="23" t="s">
+        <v>1279</v>
+      </c>
+      <c r="F266" s="29" t="s">
+        <v>1295</v>
+      </c>
+      <c r="G266" s="23" t="s">
+        <v>1294</v>
+      </c>
+      <c r="H266" s="23" t="s">
+        <v>683</v>
+      </c>
+      <c r="I266" s="23" t="s">
+        <v>678</v>
+      </c>
+      <c r="J266" s="23" t="s">
+        <v>1296</v>
+      </c>
+      <c r="L266" s="23" t="s">
+        <v>1302</v>
+      </c>
+      <c r="N266" s="1" t="s">
+        <v>631</v>
+      </c>
+      <c r="P266" s="24" t="str">
+        <f>テーブル1[[#This Row],[リンク]]&amp;テーブル1[[#This Row],[描画状況]]</f>
+        <v>https://nagimachi.wixsite.com/kairikonomachi</v>
+      </c>
+      <c r="Q266" s="17">
+        <f>1-(COUNTIF(P:P,_xlfn.TEXTJOIN(",",TRUE,テーブル1[[#This Row],[リンク]],テーブル1[[#This Row],[描画状況]]))/COUNTIF(F:F,テーブル1[[#This Row],[リンク]]))</f>
+        <v>0.25</v>
+      </c>
+      <c r="R266" s="16">
+        <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
+        <v>25.303125500354565</v>
+      </c>
+      <c r="T266" s="24" t="str">
+        <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
+        <v/>
+      </c>
+      <c r="U266" s="23" t="str">
+        <f>"|&amp;image("&amp;テーブル1[[#This Row],[画像]]&amp;".png,width=100,height=100)"</f>
+        <v>|&amp;image(narune-bell.png,width=100,height=100)</v>
+      </c>
+      <c r="V266" s="23" t="str">
+        <f>"|MIDDLE:​"&amp;テーブル1[[#This Row],[名前]]</f>
+        <v>|MIDDLE:​鳴音ベルy</v>
+      </c>
+      <c r="W266" s="23" t="str">
+        <f>"|MIDDLE:​"&amp;テーブル1[[#This Row],[なまえ]]</f>
+        <v>|MIDDLE:​なるね べる</v>
+      </c>
+      <c r="X266" s="23" t="str">
+        <f>"|MIDDLE:​"&amp;テーブル1[[#This Row],[Name]]</f>
+        <v>|MIDDLE:​Narune Bell</v>
+      </c>
+      <c r="Y266" s="23" t="str">
+        <f>"|MIDDLE:​&amp;link(配布所はこちら){​"&amp;テーブル1[[#This Row],[リンク]]&amp;"}|"</f>
+        <v>|MIDDLE:​&amp;link(配布所はこちら){​https://nagimachi.wixsite.com/kairikonomachi}|</v>
+      </c>
+    </row>
+    <row r="267" spans="1:25" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A267" s="34">
+        <v>266</v>
+      </c>
+      <c r="B267" s="32" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(テーブル1[[#This Row],[Name]])," ","-"),".","-"),"&amp;","-"),"_","-"),"・","-"),"=","-"),"--","-"),"--","-")</f>
+        <v>keishikibangoα-01</v>
+      </c>
+      <c r="C267" s="24" t="s">
+        <v>1280</v>
+      </c>
+      <c r="D267" s="23" t="s">
+        <v>1281</v>
+      </c>
+      <c r="E267" s="23" t="s">
+        <v>1282</v>
+      </c>
+      <c r="F267" s="29" t="s">
+        <v>1295</v>
+      </c>
+      <c r="G267" s="23" t="s">
+        <v>1294</v>
+      </c>
+      <c r="H267" s="23" t="s">
+        <v>661</v>
+      </c>
+      <c r="I267" s="23" t="s">
+        <v>678</v>
+      </c>
+      <c r="J267" s="23" t="s">
+        <v>1297</v>
+      </c>
+      <c r="L267" s="23" t="s">
+        <v>1305</v>
+      </c>
+      <c r="N267" s="1" t="s">
+        <v>631</v>
+      </c>
+      <c r="P267" s="33" t="str">
+        <f>テーブル1[[#This Row],[リンク]]&amp;テーブル1[[#This Row],[描画状況]]</f>
+        <v>https://nagimachi.wixsite.com/kairikonomachi</v>
+      </c>
+      <c r="Q267" s="17">
+        <f>1-(COUNTIF(P:P,_xlfn.TEXTJOIN(",",TRUE,テーブル1[[#This Row],[リンク]],テーブル1[[#This Row],[描画状況]]))/COUNTIF(F:F,テーブル1[[#This Row],[リンク]]))</f>
+        <v>0.25</v>
+      </c>
+      <c r="R267" s="16">
+        <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
+        <v>25.721952292964257</v>
+      </c>
+      <c r="T267" s="33" t="str">
+        <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
+        <v/>
+      </c>
+      <c r="U267" s="32" t="str">
+        <f>"|&amp;image("&amp;テーブル1[[#This Row],[画像]]&amp;".png,width=100,height=100)"</f>
+        <v>|&amp;image(keishikibangoα-01.png,width=100,height=100)</v>
+      </c>
+      <c r="V267" s="32" t="str">
+        <f>"|MIDDLE:​"&amp;テーブル1[[#This Row],[名前]]</f>
+        <v>|MIDDLE:​型式番号α-01</v>
+      </c>
+      <c r="W267" s="32" t="str">
+        <f>"|MIDDLE:​"&amp;テーブル1[[#This Row],[なまえ]]</f>
+        <v>|MIDDLE:​けいしきばんごうα-01</v>
+      </c>
+      <c r="X267" s="32" t="str">
+        <f>"|MIDDLE:​"&amp;テーブル1[[#This Row],[Name]]</f>
+        <v>|MIDDLE:​keishikibangoα-01</v>
+      </c>
+      <c r="Y267" s="32" t="str">
+        <f>"|MIDDLE:​&amp;link(配布所はこちら){​"&amp;テーブル1[[#This Row],[リンク]]&amp;"}|"</f>
+        <v>|MIDDLE:​&amp;link(配布所はこちら){​https://nagimachi.wixsite.com/kairikonomachi}|</v>
+      </c>
+    </row>
+    <row r="268" spans="1:25" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A268" s="34">
+        <v>267</v>
+      </c>
+      <c r="B268" s="32" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(テーブル1[[#This Row],[Name]])," ","-"),".","-"),"&amp;","-"),"_","-"),"・","-"),"=","-"),"--","-"),"--","-")</f>
+        <v>isshiki-su</v>
+      </c>
+      <c r="C268" s="24" t="s">
+        <v>1283</v>
+      </c>
+      <c r="D268" s="23" t="s">
+        <v>1284</v>
+      </c>
+      <c r="E268" s="23" t="s">
+        <v>1285</v>
+      </c>
+      <c r="F268" s="29" t="s">
+        <v>1291</v>
+      </c>
+      <c r="G268" s="23" t="s">
+        <v>1292</v>
+      </c>
+      <c r="H268" s="23" t="s">
+        <v>661</v>
+      </c>
+      <c r="I268" s="23" t="s">
+        <v>669</v>
+      </c>
+      <c r="K268" s="23" t="s">
+        <v>1293</v>
+      </c>
+      <c r="L268" s="23" t="s">
+        <v>1302</v>
+      </c>
+      <c r="N268" s="1" t="s">
+        <v>631</v>
+      </c>
+      <c r="P268" s="33" t="str">
+        <f>テーブル1[[#This Row],[リンク]]&amp;テーブル1[[#This Row],[描画状況]]</f>
+        <v>http://utau.wikidot.com/utau:isshiki-suu</v>
+      </c>
+      <c r="Q268" s="17">
+        <f>1-(COUNTIF(P:P,_xlfn.TEXTJOIN(",",TRUE,テーブル1[[#This Row],[リンク]],テーブル1[[#This Row],[描画状況]]))/COUNTIF(F:F,テーブル1[[#This Row],[リンク]]))</f>
+        <v>0</v>
+      </c>
+      <c r="R268" s="16">
+        <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
+        <v>0.65513352069163744</v>
+      </c>
+      <c r="T268" s="33" t="str">
+        <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
+        <v/>
+      </c>
+      <c r="U268" s="32" t="str">
+        <f>"|&amp;image("&amp;テーブル1[[#This Row],[画像]]&amp;".png,width=100,height=100)"</f>
+        <v>|&amp;image(isshiki-su.png,width=100,height=100)</v>
+      </c>
+      <c r="V268" s="32" t="str">
+        <f>"|MIDDLE:​"&amp;テーブル1[[#This Row],[名前]]</f>
+        <v>|MIDDLE:​一色スウ</v>
+      </c>
+      <c r="W268" s="32" t="str">
+        <f>"|MIDDLE:​"&amp;テーブル1[[#This Row],[なまえ]]</f>
+        <v>|MIDDLE:​いっしき すう</v>
+      </c>
+      <c r="X268" s="32" t="str">
+        <f>"|MIDDLE:​"&amp;テーブル1[[#This Row],[Name]]</f>
+        <v>|MIDDLE:​Isshiki Su</v>
+      </c>
+      <c r="Y268" s="32" t="str">
+        <f>"|MIDDLE:​&amp;link(配布所はこちら){​"&amp;テーブル1[[#This Row],[リンク]]&amp;"}|"</f>
+        <v>|MIDDLE:​&amp;link(配布所はこちら){​http://utau.wikidot.com/utau:isshiki-suu}|</v>
+      </c>
+    </row>
+    <row r="269" spans="1:25" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A269" s="34">
+        <v>268</v>
+      </c>
+      <c r="B269" s="32" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(テーブル1[[#This Row],[Name]])," ","-"),".","-"),"&amp;","-"),"_","-"),"・","-"),"=","-"),"--","-"),"--","-")</f>
+        <v>tsugine-saiko</v>
+      </c>
+      <c r="C269" s="24" t="s">
+        <v>1286</v>
+      </c>
+      <c r="D269" s="23" t="s">
+        <v>1287</v>
+      </c>
+      <c r="E269" s="28" t="s">
+        <v>1288</v>
+      </c>
+      <c r="F269" s="29" t="s">
+        <v>1289</v>
+      </c>
+      <c r="G269" s="23" t="s">
+        <v>1290</v>
+      </c>
+      <c r="H269" s="23" t="s">
+        <v>660</v>
+      </c>
+      <c r="I269" s="23" t="s">
+        <v>669</v>
+      </c>
+      <c r="K269" s="23" t="s">
+        <v>1270</v>
+      </c>
+      <c r="L269" s="23" t="s">
+        <v>1308</v>
+      </c>
+      <c r="M269" s="23" t="s">
+        <v>807</v>
+      </c>
+      <c r="N269" s="1" t="s">
+        <v>631</v>
+      </c>
+      <c r="P269" s="33" t="str">
+        <f>テーブル1[[#This Row],[リンク]]&amp;テーブル1[[#This Row],[描画状況]]</f>
+        <v>https://aisupiku.wixsite.com/tsuginesaiko</v>
+      </c>
+      <c r="Q269" s="17">
+        <f>1-(COUNTIF(P:P,_xlfn.TEXTJOIN(",",TRUE,テーブル1[[#This Row],[リンク]],テーブル1[[#This Row],[描画状況]]))/COUNTIF(F:F,テーブル1[[#This Row],[リンク]]))</f>
+        <v>0</v>
+      </c>
+      <c r="R269" s="16">
+        <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
+        <v>0.58698733099778566</v>
+      </c>
+      <c r="T269" s="33" t="str">
+        <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
+        <v/>
+      </c>
+      <c r="U269" s="32" t="str">
+        <f>"|&amp;image("&amp;テーブル1[[#This Row],[画像]]&amp;".png,width=100,height=100)"</f>
+        <v>|&amp;image(tsugine-saiko.png,width=100,height=100)</v>
+      </c>
+      <c r="V269" s="32" t="str">
+        <f>"|MIDDLE:​"&amp;テーブル1[[#This Row],[名前]]</f>
+        <v>|MIDDLE:​亜音サイコ</v>
+      </c>
+      <c r="W269" s="32" t="str">
+        <f>"|MIDDLE:​"&amp;テーブル1[[#This Row],[なまえ]]</f>
+        <v>|MIDDLE:​つぎね さいこ</v>
+      </c>
+      <c r="X269" s="32" t="str">
+        <f>"|MIDDLE:​"&amp;テーブル1[[#This Row],[Name]]</f>
+        <v>|MIDDLE:​Tsugine Saiko</v>
+      </c>
+      <c r="Y269" s="32" t="str">
+        <f>"|MIDDLE:​&amp;link(配布所はこちら){​"&amp;テーブル1[[#This Row],[リンク]]&amp;"}|"</f>
+        <v>|MIDDLE:​&amp;link(配布所はこちら){​https://aisupiku.wixsite.com/tsuginesaiko}|</v>
+      </c>
+    </row>
+    <row r="270" spans="1:25" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="M270" s="24"/>
+    </row>
+    <row r="271" spans="1:25" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="M271" s="24"/>
+    </row>
+    <row r="272" spans="1:25" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="M272" s="24"/>
+    </row>
+    <row r="273" spans="13:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="M273" s="24"/>
+    </row>
+    <row r="274" spans="13:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="M274" s="24"/>
+    </row>
+    <row r="275" spans="13:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="M275" s="24"/>
+    </row>
+    <row r="276" spans="13:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="M276" s="24"/>
+    </row>
+    <row r="277" spans="13:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="M277" s="24"/>
+    </row>
+    <row r="278" spans="13:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="M278" s="24"/>
+    </row>
+    <row r="279" spans="13:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="M279" s="24"/>
+    </row>
+    <row r="280" spans="13:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="M280" s="24"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -26706,37 +27213,37 @@
   <conditionalFormatting sqref="G252:G258">
     <cfRule type="duplicateValues" dxfId="1" priority="26"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O1:T1048576">
+  <conditionalFormatting sqref="M278:M279 O1:T1048576">
     <cfRule type="cellIs" dxfId="0" priority="12" operator="equal">
       <formula>"済"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="9">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="I2:I263" xr:uid="{C65A1E30-8F1A-43F7-95C8-9A27EB918408}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="I2:I269" xr:uid="{C65A1E30-8F1A-43F7-95C8-9A27EB918408}">
       <formula1>種族タグ</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="K2:K263" xr:uid="{F4C1FC31-8189-42FE-9CDF-1184FF0909B9}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="K2:K269" xr:uid="{F4C1FC31-8189-42FE-9CDF-1184FF0909B9}">
       <formula1>職業タグ</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="K144 J2:J143 J145:J263" xr:uid="{71D1DCE5-85B0-4960-9B38-ABC74300BCF2}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="K144 J2:J143 J145:J269" xr:uid="{71D1DCE5-85B0-4960-9B38-ABC74300BCF2}">
       <formula1>モチーフタグ</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="M2:M36 L46 M38:M45 M47:M244 M246:M263" xr:uid="{1578619E-9A71-4986-9378-87AD2388468F}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="M2:M36 L46 M38:M45 M47:M244 M246:M269" xr:uid="{1578619E-9A71-4986-9378-87AD2388468F}">
       <formula1>ワンポイントタグ</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S263" xr:uid="{05A634BD-4DB9-4CF6-97DC-6B95FBE6232B}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S269" xr:uid="{05A634BD-4DB9-4CF6-97DC-6B95FBE6232B}">
       <formula1>"済,個別済"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N263" xr:uid="{92493CA5-E237-4453-B08F-89E5ABEEA9EA}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N269" xr:uid="{92493CA5-E237-4453-B08F-89E5ABEEA9EA}">
       <formula1>"〇 / 必要,〇 / 不要,×"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="L2:L263" xr:uid="{6CD751E0-96FF-4645-8251-894B2CC5C15F}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="L2:L269" xr:uid="{6CD751E0-96FF-4645-8251-894B2CC5C15F}">
       <formula1>小物タグ</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H263" xr:uid="{35C507EC-8DB1-4F3E-8DD4-3BFDA6513A59}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H269" xr:uid="{35C507EC-8DB1-4F3E-8DD4-3BFDA6513A59}">
       <formula1>"女性,男性,両性,キメラ,無性別,不明"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O1048576" xr:uid="{1E2E563C-97C6-4274-B6CC-64A3EA5A69C8}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M278:M279 O2:O1048576" xr:uid="{1E2E563C-97C6-4274-B6CC-64A3EA5A69C8}">
       <formula1>"済"</formula1>
     </dataValidation>
   </dataValidations>
@@ -26972,10 +27479,14 @@
     <hyperlink ref="F261" r:id="rId229" xr:uid="{9DE6D681-3406-447E-B911-10C675BB2C86}"/>
     <hyperlink ref="F262" r:id="rId230" xr:uid="{C738A581-A93D-4132-A3C0-11F0A6CD0135}"/>
     <hyperlink ref="F263" r:id="rId231" xr:uid="{BBBDDB5E-5676-4C83-B8D1-F535BF6DF7A6}"/>
+    <hyperlink ref="F269" r:id="rId232" xr:uid="{3E74F0C7-67E2-448E-9F67-E6EFA99883C6}"/>
+    <hyperlink ref="F268" r:id="rId233" xr:uid="{E0DA35B9-3164-4F31-9165-0FF83FD5A473}"/>
+    <hyperlink ref="F264" r:id="rId234" xr:uid="{F26668EA-0337-4454-87F0-0583CCC1DDA3}"/>
+    <hyperlink ref="F265:F267" r:id="rId235" display="https://nagimachi.wixsite.com/kairikonomachi" xr:uid="{9E02321C-FB1F-4E7A-B665-955F0CCBDFAE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId232"/>
+    <tablePart r:id="rId236"/>
   </tableParts>
 </worksheet>
 </file>
@@ -27000,27 +27511,27 @@
       <c r="B4" s="4" t="s">
         <v>411</v>
       </c>
-      <c r="C4" s="7" t="e">
+      <c r="C4" s="7">
         <f ca="1">MATCH(C5,キャラ情報!C:C,0)</f>
-        <v>#N/A</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B5" s="4" t="s">
         <v>408</v>
       </c>
-      <c r="C5" s="6" t="e">
+      <c r="C5" s="6" t="str">
         <f ca="1">INDEX(キャラ情報!C:R,MATCH(MIN(キャラ情報!R:R),キャラ情報!R:R,0),1)</f>
-        <v>#N/A</v>
+        <v>亜音サイコ</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B6" s="4" t="s">
         <v>409</v>
       </c>
-      <c r="C6" s="6" t="e">
+      <c r="C6" s="6" t="str">
         <f ca="1">INDEX(キャラ情報!C:R,MATCH(MIN(キャラ情報!R:R),キャラ情報!R:R,0),4)</f>
-        <v>#N/A</v>
+        <v>https://aisupiku.wixsite.com/tsuginesaiko</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -27035,7 +27546,7 @@
       </c>
       <c r="C11" s="7">
         <f ca="1">MATCH(C12,キャラ情報!C:C,0)</f>
-        <v>259</v>
+        <v>264</v>
       </c>
     </row>
     <row r="12" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -27044,7 +27555,7 @@
       </c>
       <c r="C12" s="6" t="str">
         <f ca="1">INDEX(キャラ情報!C:T,MATCH(MIN(キャラ情報!T:T),キャラ情報!T:T,0),1)</f>
-        <v>音夜秋月</v>
+        <v>有部音ゴエμ</v>
       </c>
     </row>
     <row r="14" spans="2:3" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -27065,17 +27576,17 @@
     <row r="17" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="11" t="str">
         <f>"No."&amp;MAX(キャラ情報!A:A)+1&amp;"｜"</f>
-        <v>No.263｜</v>
+        <v>No.269｜</v>
       </c>
       <c r="C17" s="12" t="str">
         <f ca="1">C12</f>
-        <v>音夜秋月</v>
+        <v>有部音ゴエμ</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B18" s="11" t="str">
         <f ca="1">INDEX(キャラ情報!C:G,MATCH(C12,キャラ情報!C:C,0),5)</f>
-        <v>#四季折宛郵便</v>
+        <v xml:space="preserve">#返り子の町 </v>
       </c>
       <c r="C18" s="12"/>
     </row>
@@ -27091,7 +27602,7 @@
     </row>
     <row r="21" spans="2:3" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B21" s="13" t="s">
-        <v>731</v>
+        <v>721</v>
       </c>
       <c r="C21" s="14"/>
     </row>
@@ -27108,7 +27619,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B38EF37-1F1B-4879-9E5C-37FE8D26AF37}">
-  <dimension ref="A1:M263"/>
+  <dimension ref="A1:M269"/>
   <sheetFormatPr defaultColWidth="9.06640625" defaultRowHeight="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.86328125" style="19" bestFit="1" customWidth="1"/>
@@ -27151,7 +27662,7 @@
         <v>663</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>753</v>
+        <v>742</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>664</v>
@@ -27264,7 +27775,7 @@
       </c>
       <c r="L3" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
-        <v>眼鏡</v>
+        <v>眼部</v>
       </c>
       <c r="M3" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
@@ -27372,7 +27883,7 @@
       </c>
       <c r="L5" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
-        <v>イヤーユニット</v>
+        <v>耳装備</v>
       </c>
       <c r="M5" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
@@ -27426,7 +27937,7 @@
       </c>
       <c r="L6" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
-        <v>仮面</v>
+        <v>仮面・マスク</v>
       </c>
       <c r="M6" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
@@ -27534,7 +28045,7 @@
       </c>
       <c r="L8" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
-        <v>眼鏡</v>
+        <v>眼部</v>
       </c>
       <c r="M8" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
@@ -27642,7 +28153,7 @@
       </c>
       <c r="L10" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
-        <v>ヘアピン</v>
+        <v>髪飾り</v>
       </c>
       <c r="M10" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
@@ -27750,7 +28261,7 @@
       </c>
       <c r="L12" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
-        <v>眼鏡</v>
+        <v>眼部</v>
       </c>
       <c r="M12" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
@@ -27804,7 +28315,7 @@
       </c>
       <c r="L13" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
-        <v>ヘッドセット</v>
+        <v>耳装備</v>
       </c>
       <c r="M13" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
@@ -28020,7 +28531,7 @@
       </c>
       <c r="L17" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
-        <v>鍵</v>
+        <v>道具</v>
       </c>
       <c r="M17" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
@@ -28074,7 +28585,7 @@
       </c>
       <c r="L18" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
-        <v>鍵</v>
+        <v>道具</v>
       </c>
       <c r="M18" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
@@ -28128,7 +28639,7 @@
       </c>
       <c r="L19" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
-        <v>ヘアピン|拡声器</v>
+        <v>髪飾り|道具</v>
       </c>
       <c r="M19" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
@@ -28182,7 +28693,7 @@
       </c>
       <c r="L20" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
-        <v>イヤーユニット</v>
+        <v>耳装備</v>
       </c>
       <c r="M20" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
@@ -28344,7 +28855,7 @@
       </c>
       <c r="L23" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
-        <v>ヘイロー|十字架</v>
+        <v>ヘイロー|首装飾</v>
       </c>
       <c r="M23" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
@@ -28398,7 +28909,7 @@
       </c>
       <c r="L24" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
-        <v>眼鏡</v>
+        <v>眼部</v>
       </c>
       <c r="M24" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
@@ -28452,7 +28963,7 @@
       </c>
       <c r="L25" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
-        <v>ヘアピン|眼鏡</v>
+        <v>髪飾り|眼部</v>
       </c>
       <c r="M25" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
@@ -28722,7 +29233,7 @@
       </c>
       <c r="L30" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
-        <v>銃</v>
+        <v>武器</v>
       </c>
       <c r="M30" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
@@ -28884,7 +29395,7 @@
       </c>
       <c r="L33" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
-        <v>ナイフ</v>
+        <v>武器</v>
       </c>
       <c r="M33" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
@@ -28938,7 +29449,7 @@
       </c>
       <c r="L34" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
-        <v>ピアス|首輪|指輪</v>
+        <v>装身具|首装飾</v>
       </c>
       <c r="M34" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
@@ -28992,7 +29503,7 @@
       </c>
       <c r="L35" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
-        <v>骨</v>
+        <v>モチーフ</v>
       </c>
       <c r="M35" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
@@ -29034,7 +29545,7 @@
       </c>
       <c r="I36" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[種族タグ]],"、","|")</f>
-        <v>宇宙人|元ヤン</v>
+        <v>宇宙人</v>
       </c>
       <c r="J36" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[モチーフタグ]],"、","|")</f>
@@ -29042,11 +29553,11 @@
       </c>
       <c r="K36" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
-        <v>警察官</v>
+        <v>警察官|元ヤン</v>
       </c>
       <c r="L36" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
-        <v>ヘアピン|眼鏡</v>
+        <v>髪飾り|眼部</v>
       </c>
       <c r="M36" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
@@ -29100,7 +29611,7 @@
       </c>
       <c r="L37" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
-        <v>ヘアピン</v>
+        <v>髪飾り</v>
       </c>
       <c r="M37" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
@@ -29370,7 +29881,7 @@
       </c>
       <c r="L42" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
-        <v>ヘイロー|包帯</v>
+        <v>ヘイロー|服飾</v>
       </c>
       <c r="M42" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
@@ -29532,7 +30043,7 @@
       </c>
       <c r="L45" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
-        <v>マスク</v>
+        <v>仮面・マスク</v>
       </c>
       <c r="M45" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
@@ -29586,7 +30097,7 @@
       </c>
       <c r="L46" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
-        <v>リボン|カチューシャ</v>
+        <v>リボン|髪飾り</v>
       </c>
       <c r="M46" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
@@ -30504,7 +31015,7 @@
       </c>
       <c r="L63" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
-        <v>耳標</v>
+        <v>耳装備</v>
       </c>
       <c r="M63" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
@@ -30612,7 +31123,7 @@
       </c>
       <c r="L65" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
-        <v>ヘッドホン</v>
+        <v>耳装備</v>
       </c>
       <c r="M65" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
@@ -31854,7 +32365,7 @@
       </c>
       <c r="L88" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
-        <v>眼鏡</v>
+        <v>眼部</v>
       </c>
       <c r="M88" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
@@ -32016,7 +32527,7 @@
       </c>
       <c r="L91" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
-        <v>ヘアピン</v>
+        <v>髪飾り</v>
       </c>
       <c r="M91" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
@@ -32070,7 +32581,7 @@
       </c>
       <c r="L92" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
-        <v>ヘアピン</v>
+        <v>髪飾り</v>
       </c>
       <c r="M92" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
@@ -32556,7 +33067,7 @@
       </c>
       <c r="L101" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
-        <v>カチューシャ|髪飾り</v>
+        <v>髪飾り</v>
       </c>
       <c r="M101" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
@@ -32610,7 +33121,7 @@
       </c>
       <c r="L102" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
-        <v>ゴーグル</v>
+        <v>眼部</v>
       </c>
       <c r="M102" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
@@ -32718,7 +33229,7 @@
       </c>
       <c r="L104" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
-        <v>眼鏡</v>
+        <v>眼部</v>
       </c>
       <c r="M104" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
@@ -32880,7 +33391,7 @@
       </c>
       <c r="L107" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
-        <v>ヘイロー|十字架</v>
+        <v>ヘイロー|首装飾</v>
       </c>
       <c r="M107" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
@@ -33150,7 +33661,7 @@
       </c>
       <c r="L112" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
-        <v>ゴーグル</v>
+        <v>眼部</v>
       </c>
       <c r="M112" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
@@ -33204,7 +33715,7 @@
       </c>
       <c r="L113" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
-        <v>ヘイロー|カチューシャ</v>
+        <v>ヘイロー|髪飾り</v>
       </c>
       <c r="M113" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
@@ -33420,7 +33931,7 @@
       </c>
       <c r="L117" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
-        <v>イヤーユニット</v>
+        <v>耳装備</v>
       </c>
       <c r="M117" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
@@ -34122,7 +34633,7 @@
       </c>
       <c r="L130" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
-        <v>銃</v>
+        <v>武器</v>
       </c>
       <c r="M130" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
@@ -34554,7 +35065,7 @@
       </c>
       <c r="L138" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
-        <v>アイバンド</v>
+        <v>眼部</v>
       </c>
       <c r="M138" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
@@ -34878,7 +35389,7 @@
       </c>
       <c r="L144" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
-        <v>杖</v>
+        <v>武器</v>
       </c>
       <c r="M144" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
@@ -37092,7 +37603,7 @@
       </c>
       <c r="L185" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
-        <v>ゴーグル</v>
+        <v>眼部</v>
       </c>
       <c r="M185" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
@@ -38550,7 +39061,7 @@
       </c>
       <c r="L212" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
-        <v>ヘッドセット</v>
+        <v>耳装備</v>
       </c>
       <c r="M212" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
@@ -38604,7 +39115,7 @@
       </c>
       <c r="L213" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
-        <v>ヘッドホン</v>
+        <v>耳装備</v>
       </c>
       <c r="M213" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
@@ -38766,7 +39277,7 @@
       </c>
       <c r="L216" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
-        <v>眼鏡</v>
+        <v>眼部</v>
       </c>
       <c r="M216" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
@@ -38874,7 +39385,7 @@
       </c>
       <c r="L218" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
-        <v>眼鏡</v>
+        <v>眼部</v>
       </c>
       <c r="M218" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
@@ -38982,7 +39493,7 @@
       </c>
       <c r="L220" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
-        <v>ヘアピン</v>
+        <v>髪飾り</v>
       </c>
       <c r="M220" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
@@ -39414,7 +39925,7 @@
       </c>
       <c r="L228" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
-        <v>イヤーユニット|鍵</v>
+        <v>耳装備|道具</v>
       </c>
       <c r="M228" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
@@ -39468,7 +39979,7 @@
       </c>
       <c r="L229" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
-        <v>ヘッドホン</v>
+        <v>耳装備</v>
       </c>
       <c r="M229" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
@@ -39576,7 +40087,7 @@
       </c>
       <c r="L231" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
-        <v>ピアス|首輪</v>
+        <v>装身具|首装飾</v>
       </c>
       <c r="M231" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
@@ -39738,7 +40249,7 @@
       </c>
       <c r="L234" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
-        <v>耳標</v>
+        <v>耳装備</v>
       </c>
       <c r="M234" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
@@ -39792,7 +40303,7 @@
       </c>
       <c r="L235" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
-        <v>耳標</v>
+        <v>耳装備</v>
       </c>
       <c r="M235" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
@@ -39846,7 +40357,7 @@
       </c>
       <c r="L236" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
-        <v>耳標</v>
+        <v>耳装備</v>
       </c>
       <c r="M236" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
@@ -39900,7 +40411,7 @@
       </c>
       <c r="L237" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
-        <v>耳標</v>
+        <v>耳装備</v>
       </c>
       <c r="M237" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
@@ -40224,7 +40735,7 @@
       </c>
       <c r="L243" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
-        <v>拳銃</v>
+        <v>武器</v>
       </c>
       <c r="M243" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
@@ -40548,7 +41059,7 @@
       </c>
       <c r="L249" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
-        <v>拳銃</v>
+        <v>武器</v>
       </c>
       <c r="M249" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
@@ -40602,7 +41113,7 @@
       </c>
       <c r="L250" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
-        <v>包帯|注射器</v>
+        <v>服飾|道具</v>
       </c>
       <c r="M250" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
@@ -40872,7 +41383,7 @@
       </c>
       <c r="L255" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
-        <v>ヘイロー|ボタン</v>
+        <v>ヘイロー|服飾</v>
       </c>
       <c r="M255" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
@@ -40980,7 +41491,7 @@
       </c>
       <c r="L257" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
-        <v>ヘッドホン</v>
+        <v>耳装備</v>
       </c>
       <c r="M257" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
@@ -41042,273 +41553,597 @@
       </c>
     </row>
     <row r="259" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A259" s="35">
+      <c r="A259" s="19">
         <f>テーブル1[[#This Row],[番号]]</f>
         <v>258</v>
       </c>
-      <c r="B259" s="35" t="str">
+      <c r="B259" s="19" t="str">
         <f>テーブル1[[#This Row],[名前]]</f>
         <v>音夜秋月</v>
       </c>
-      <c r="C259" s="35" t="str">
+      <c r="C259" s="19" t="str">
         <f>テーブル1[[#This Row],[なまえ]]</f>
         <v>おとや しゅうき</v>
       </c>
-      <c r="D259" s="35" t="str">
+      <c r="D259" s="19" t="str">
         <f>テーブル1[[#This Row],[Name]]</f>
         <v>Otoya Syuki</v>
       </c>
-      <c r="E259" s="35" t="str">
+      <c r="E259" s="19" t="str">
         <f>"image/"&amp;テーブル1[[#This Row],[画像]]&amp;".png"</f>
         <v>image/otoya-syuki.png</v>
       </c>
-      <c r="F259" s="35" t="str">
+      <c r="F259" s="19" t="str">
         <f>テーブル1[[#This Row],[リンク]]</f>
         <v>https://sikiori.wepage.com</v>
       </c>
-      <c r="G259" s="35" t="str">
+      <c r="G259" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[作品タグ]],"、","|")</f>
         <v>#四季折宛郵便</v>
       </c>
-      <c r="H259" s="35" t="str">
+      <c r="H259" s="19" t="str">
         <f>テーブル1[[#This Row],[性別]]&amp;""</f>
         <v>男性</v>
       </c>
-      <c r="I259" s="35" t="str">
+      <c r="I259" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[種族タグ]],"、","|")</f>
         <v>人間</v>
       </c>
-      <c r="J259" s="35" t="str">
+      <c r="J259" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[モチーフタグ]],"、","|")</f>
         <v/>
       </c>
-      <c r="K259" s="35" t="str">
+      <c r="K259" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
         <v>元ヤン|作家</v>
       </c>
-      <c r="L259" s="35" t="str">
+      <c r="L259" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
-        <v>眼鏡</v>
-      </c>
-      <c r="M259" s="35" t="str">
+        <v>眼部</v>
+      </c>
+      <c r="M259" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
         <v>ツートンカラー</v>
       </c>
     </row>
     <row r="260" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A260" s="35">
+      <c r="A260" s="19">
         <f>テーブル1[[#This Row],[番号]]</f>
         <v>259</v>
       </c>
-      <c r="B260" s="35" t="str">
+      <c r="B260" s="19" t="str">
         <f>テーブル1[[#This Row],[名前]]</f>
         <v>夏乃星音</v>
       </c>
-      <c r="C260" s="35" t="str">
+      <c r="C260" s="19" t="str">
         <f>テーブル1[[#This Row],[なまえ]]</f>
         <v>なつの せいと</v>
       </c>
-      <c r="D260" s="35" t="str">
+      <c r="D260" s="19" t="str">
         <f>テーブル1[[#This Row],[Name]]</f>
         <v>Natsuno Seito</v>
       </c>
-      <c r="E260" s="35" t="str">
+      <c r="E260" s="19" t="str">
         <f>"image/"&amp;テーブル1[[#This Row],[画像]]&amp;".png"</f>
         <v>image/natsuno-seito.png</v>
       </c>
-      <c r="F260" s="35" t="str">
+      <c r="F260" s="19" t="str">
         <f>テーブル1[[#This Row],[リンク]]</f>
         <v>https://sikiori.wepage.com</v>
       </c>
-      <c r="G260" s="35" t="str">
+      <c r="G260" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[作品タグ]],"、","|")</f>
         <v>#四季折宛郵便</v>
       </c>
-      <c r="H260" s="35" t="str">
+      <c r="H260" s="19" t="str">
         <f>テーブル1[[#This Row],[性別]]&amp;""</f>
         <v>男性</v>
       </c>
-      <c r="I260" s="35" t="str">
+      <c r="I260" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[種族タグ]],"、","|")</f>
         <v>人間</v>
       </c>
-      <c r="J260" s="35" t="str">
+      <c r="J260" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[モチーフタグ]],"、","|")</f>
         <v/>
       </c>
-      <c r="K260" s="35" t="str">
+      <c r="K260" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
         <v>バーテンダー</v>
       </c>
-      <c r="L260" s="35" t="str">
+      <c r="L260" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
         <v/>
       </c>
-      <c r="M260" s="35" t="str">
+      <c r="M260" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
         <v>ツートンカラー</v>
       </c>
     </row>
     <row r="261" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A261" s="35">
+      <c r="A261" s="19">
         <f>テーブル1[[#This Row],[番号]]</f>
         <v>260</v>
       </c>
-      <c r="B261" s="35" t="str">
+      <c r="B261" s="19" t="str">
         <f>テーブル1[[#This Row],[名前]]</f>
         <v>薪宮風季</v>
       </c>
-      <c r="C261" s="35" t="str">
+      <c r="C261" s="19" t="str">
         <f>テーブル1[[#This Row],[なまえ]]</f>
         <v>まきみや ふうき</v>
       </c>
-      <c r="D261" s="35" t="str">
+      <c r="D261" s="19" t="str">
         <f>テーブル1[[#This Row],[Name]]</f>
         <v>Makimiya Fuki</v>
       </c>
-      <c r="E261" s="35" t="str">
+      <c r="E261" s="19" t="str">
         <f>"image/"&amp;テーブル1[[#This Row],[画像]]&amp;".png"</f>
         <v>image/makimiya-fuki.png</v>
       </c>
-      <c r="F261" s="35" t="str">
+      <c r="F261" s="19" t="str">
         <f>テーブル1[[#This Row],[リンク]]</f>
         <v>https://mohumohuton.web.fc2.com/makimiya/index.html</v>
       </c>
-      <c r="G261" s="35" t="str">
+      <c r="G261" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[作品タグ]],"、","|")</f>
         <v>#薪宮風季</v>
       </c>
-      <c r="H261" s="35" t="str">
+      <c r="H261" s="19" t="str">
         <f>テーブル1[[#This Row],[性別]]&amp;""</f>
         <v>男性</v>
       </c>
-      <c r="I261" s="35" t="str">
+      <c r="I261" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[種族タグ]],"、","|")</f>
         <v>人間</v>
       </c>
-      <c r="J261" s="35" t="str">
+      <c r="J261" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[モチーフタグ]],"、","|")</f>
         <v/>
       </c>
-      <c r="K261" s="35" t="str">
+      <c r="K261" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
         <v>歌手</v>
       </c>
-      <c r="L261" s="35" t="str">
+      <c r="L261" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
-        <v>ヘッドセット|眼鏡|マフラー</v>
-      </c>
-      <c r="M261" s="35" t="str">
+        <v>耳装備|眼部|首装飾</v>
+      </c>
+      <c r="M261" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
         <v/>
       </c>
     </row>
     <row r="262" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A262" s="35">
+      <c r="A262" s="19">
         <f>テーブル1[[#This Row],[番号]]</f>
         <v>261</v>
       </c>
-      <c r="B262" s="35" t="str">
+      <c r="B262" s="19" t="str">
         <f>テーブル1[[#This Row],[名前]]</f>
         <v>わくねむすぴか</v>
       </c>
-      <c r="C262" s="35" t="str">
+      <c r="C262" s="19" t="str">
         <f>テーブル1[[#This Row],[なまえ]]</f>
         <v>わくねむ すぴか</v>
       </c>
-      <c r="D262" s="35" t="str">
+      <c r="D262" s="19" t="str">
         <f>テーブル1[[#This Row],[Name]]</f>
         <v>Wakunemu Supika</v>
       </c>
-      <c r="E262" s="35" t="str">
+      <c r="E262" s="19" t="str">
         <f>"image/"&amp;テーブル1[[#This Row],[画像]]&amp;".png"</f>
         <v>image/wakunemu-supika.png</v>
       </c>
-      <c r="F262" s="35" t="str">
+      <c r="F262" s="19" t="str">
         <f>テーブル1[[#This Row],[リンク]]</f>
         <v>https://bowlroll.net/user/946776</v>
       </c>
-      <c r="G262" s="35" t="str">
+      <c r="G262" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[作品タグ]],"、","|")</f>
         <v>#わくねむすぴか</v>
       </c>
-      <c r="H262" s="35" t="str">
+      <c r="H262" s="19" t="str">
         <f>テーブル1[[#This Row],[性別]]&amp;""</f>
         <v>女性</v>
       </c>
-      <c r="I262" s="35" t="str">
+      <c r="I262" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[種族タグ]],"、","|")</f>
         <v>人型</v>
       </c>
-      <c r="J262" s="35" t="str">
+      <c r="J262" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[モチーフタグ]],"、","|")</f>
         <v>イラスト</v>
       </c>
-      <c r="K262" s="35" t="str">
+      <c r="K262" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
         <v/>
       </c>
-      <c r="L262" s="35" t="str">
+      <c r="L262" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
         <v/>
       </c>
-      <c r="M262" s="35" t="str">
+      <c r="M262" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
         <v/>
       </c>
     </row>
     <row r="263" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A263" s="35">
+      <c r="A263" s="19">
         <f>テーブル1[[#This Row],[番号]]</f>
         <v>262</v>
       </c>
-      <c r="B263" s="35" t="str">
+      <c r="B263" s="19" t="str">
         <f>テーブル1[[#This Row],[名前]]</f>
         <v>李音フヱル</v>
       </c>
-      <c r="C263" s="35" t="str">
+      <c r="C263" s="19" t="str">
         <f>テーブル1[[#This Row],[なまえ]]</f>
         <v>すももね ふえる</v>
       </c>
-      <c r="D263" s="35" t="str">
+      <c r="D263" s="19" t="str">
         <f>テーブル1[[#This Row],[Name]]</f>
         <v>Sumomone Fueru</v>
       </c>
-      <c r="E263" s="35" t="str">
+      <c r="E263" s="19" t="str">
         <f>"image/"&amp;テーブル1[[#This Row],[画像]]&amp;".png"</f>
         <v>image/sumomone-fueru.png</v>
       </c>
-      <c r="F263" s="35" t="str">
+      <c r="F263" s="19" t="str">
         <f>テーブル1[[#This Row],[リンク]]</f>
         <v>https://suukedayo.wixsite.com/shiawasefairu</v>
       </c>
-      <c r="G263" s="35" t="str">
+      <c r="G263" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[作品タグ]],"、","|")</f>
         <v xml:space="preserve">#しあわせふぁいる </v>
       </c>
-      <c r="H263" s="35" t="str">
+      <c r="H263" s="19" t="str">
         <f>テーブル1[[#This Row],[性別]]&amp;""</f>
         <v>無性別</v>
       </c>
-      <c r="I263" s="35" t="str">
+      <c r="I263" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[種族タグ]],"、","|")</f>
         <v>天使</v>
       </c>
-      <c r="J263" s="35" t="str">
+      <c r="J263" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[モチーフタグ]],"、","|")</f>
         <v/>
       </c>
-      <c r="K263" s="35" t="str">
+      <c r="K263" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
         <v>医者</v>
       </c>
-      <c r="L263" s="35" t="str">
+      <c r="L263" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
         <v>ヘイロー</v>
       </c>
-      <c r="M263" s="35" t="str">
+      <c r="M263" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
         <v>羽|多眼</v>
+      </c>
+    </row>
+    <row r="264" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A264" s="35">
+        <f>テーブル1[[#This Row],[番号]]</f>
+        <v>263</v>
+      </c>
+      <c r="B264" s="35" t="str">
+        <f>テーブル1[[#This Row],[名前]]</f>
+        <v>有部音ゴエμ</v>
+      </c>
+      <c r="C264" s="35" t="str">
+        <f>テーブル1[[#This Row],[なまえ]]</f>
+        <v>うぶおん ごえ</v>
+      </c>
+      <c r="D264" s="35" t="str">
+        <f>テーブル1[[#This Row],[Name]]</f>
+        <v>Ubuon Goe</v>
+      </c>
+      <c r="E264" s="35" t="str">
+        <f>"image/"&amp;テーブル1[[#This Row],[画像]]&amp;".png"</f>
+        <v>image/ubuon-goe.png</v>
+      </c>
+      <c r="F264" s="35" t="str">
+        <f>テーブル1[[#This Row],[リンク]]</f>
+        <v>https://nagimachi.wixsite.com/kairikonomachi</v>
+      </c>
+      <c r="G264" s="35" t="str">
+        <f>SUBSTITUTE(テーブル1[[#This Row],[作品タグ]],"、","|")</f>
+        <v xml:space="preserve">#返り子の町 </v>
+      </c>
+      <c r="H264" s="35" t="str">
+        <f>テーブル1[[#This Row],[性別]]&amp;""</f>
+        <v>不明</v>
+      </c>
+      <c r="I264" s="35" t="str">
+        <f>SUBSTITUTE(テーブル1[[#This Row],[種族タグ]],"、","|")</f>
+        <v>故人|幽霊</v>
+      </c>
+      <c r="J264" s="35" t="str">
+        <f>SUBSTITUTE(テーブル1[[#This Row],[モチーフタグ]],"、","|")</f>
+        <v/>
+      </c>
+      <c r="K264" s="35" t="str">
+        <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
+        <v/>
+      </c>
+      <c r="L264" s="35" t="str">
+        <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
+        <v>道具</v>
+      </c>
+      <c r="M264" s="35" t="str">
+        <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="265" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A265" s="35">
+        <f>テーブル1[[#This Row],[番号]]</f>
+        <v>264</v>
+      </c>
+      <c r="B265" s="35" t="str">
+        <f>テーブル1[[#This Row],[名前]]</f>
+        <v>終歌カツエα</v>
+      </c>
+      <c r="C265" s="35" t="str">
+        <f>テーブル1[[#This Row],[なまえ]]</f>
+        <v>しゅうた かつえ</v>
+      </c>
+      <c r="D265" s="35" t="str">
+        <f>テーブル1[[#This Row],[Name]]</f>
+        <v>Shuta Katsue</v>
+      </c>
+      <c r="E265" s="35" t="str">
+        <f>"image/"&amp;テーブル1[[#This Row],[画像]]&amp;".png"</f>
+        <v>image/shuta-katsue.png</v>
+      </c>
+      <c r="F265" s="35" t="str">
+        <f>テーブル1[[#This Row],[リンク]]</f>
+        <v>https://nagimachi.wixsite.com/kairikonomachi</v>
+      </c>
+      <c r="G265" s="35" t="str">
+        <f>SUBSTITUTE(テーブル1[[#This Row],[作品タグ]],"、","|")</f>
+        <v xml:space="preserve">#返り子の町 </v>
+      </c>
+      <c r="H265" s="35" t="str">
+        <f>テーブル1[[#This Row],[性別]]&amp;""</f>
+        <v>女性</v>
+      </c>
+      <c r="I265" s="35" t="str">
+        <f>SUBSTITUTE(テーブル1[[#This Row],[種族タグ]],"、","|")</f>
+        <v>人間</v>
+      </c>
+      <c r="J265" s="35" t="str">
+        <f>SUBSTITUTE(テーブル1[[#This Row],[モチーフタグ]],"、","|")</f>
+        <v/>
+      </c>
+      <c r="K265" s="35" t="str">
+        <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
+        <v/>
+      </c>
+      <c r="L265" s="35" t="str">
+        <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
+        <v>眼部</v>
+      </c>
+      <c r="M265" s="35" t="str">
+        <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="266" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A266" s="35">
+        <f>テーブル1[[#This Row],[番号]]</f>
+        <v>265</v>
+      </c>
+      <c r="B266" s="35" t="str">
+        <f>テーブル1[[#This Row],[名前]]</f>
+        <v>鳴音ベルy</v>
+      </c>
+      <c r="C266" s="35" t="str">
+        <f>テーブル1[[#This Row],[なまえ]]</f>
+        <v>なるね べる</v>
+      </c>
+      <c r="D266" s="35" t="str">
+        <f>テーブル1[[#This Row],[Name]]</f>
+        <v>Narune Bell</v>
+      </c>
+      <c r="E266" s="35" t="str">
+        <f>"image/"&amp;テーブル1[[#This Row],[画像]]&amp;".png"</f>
+        <v>image/narune-bell.png</v>
+      </c>
+      <c r="F266" s="35" t="str">
+        <f>テーブル1[[#This Row],[リンク]]</f>
+        <v>https://nagimachi.wixsite.com/kairikonomachi</v>
+      </c>
+      <c r="G266" s="35" t="str">
+        <f>SUBSTITUTE(テーブル1[[#This Row],[作品タグ]],"、","|")</f>
+        <v xml:space="preserve">#返り子の町 </v>
+      </c>
+      <c r="H266" s="35" t="str">
+        <f>テーブル1[[#This Row],[性別]]&amp;""</f>
+        <v>不明</v>
+      </c>
+      <c r="I266" s="35" t="str">
+        <f>SUBSTITUTE(テーブル1[[#This Row],[種族タグ]],"、","|")</f>
+        <v>機械</v>
+      </c>
+      <c r="J266" s="35" t="str">
+        <f>SUBSTITUTE(テーブル1[[#This Row],[モチーフタグ]],"、","|")</f>
+        <v>ベル</v>
+      </c>
+      <c r="K266" s="35" t="str">
+        <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
+        <v/>
+      </c>
+      <c r="L266" s="35" t="str">
+        <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
+        <v>耳装備</v>
+      </c>
+      <c r="M266" s="35" t="str">
+        <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="267" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A267" s="35">
+        <f>テーブル1[[#This Row],[番号]]</f>
+        <v>266</v>
+      </c>
+      <c r="B267" s="35" t="str">
+        <f>テーブル1[[#This Row],[名前]]</f>
+        <v>型式番号α-01</v>
+      </c>
+      <c r="C267" s="35" t="str">
+        <f>テーブル1[[#This Row],[なまえ]]</f>
+        <v>けいしきばんごうα-01</v>
+      </c>
+      <c r="D267" s="35" t="str">
+        <f>テーブル1[[#This Row],[Name]]</f>
+        <v>keishikibangoα-01</v>
+      </c>
+      <c r="E267" s="35" t="str">
+        <f>"image/"&amp;テーブル1[[#This Row],[画像]]&amp;".png"</f>
+        <v>image/keishikibangoα-01.png</v>
+      </c>
+      <c r="F267" s="35" t="str">
+        <f>テーブル1[[#This Row],[リンク]]</f>
+        <v>https://nagimachi.wixsite.com/kairikonomachi</v>
+      </c>
+      <c r="G267" s="35" t="str">
+        <f>SUBSTITUTE(テーブル1[[#This Row],[作品タグ]],"、","|")</f>
+        <v xml:space="preserve">#返り子の町 </v>
+      </c>
+      <c r="H267" s="35" t="str">
+        <f>テーブル1[[#This Row],[性別]]&amp;""</f>
+        <v>男性</v>
+      </c>
+      <c r="I267" s="35" t="str">
+        <f>SUBSTITUTE(テーブル1[[#This Row],[種族タグ]],"、","|")</f>
+        <v>機械</v>
+      </c>
+      <c r="J267" s="35" t="str">
+        <f>SUBSTITUTE(テーブル1[[#This Row],[モチーフタグ]],"、","|")</f>
+        <v>環境音</v>
+      </c>
+      <c r="K267" s="35" t="str">
+        <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
+        <v/>
+      </c>
+      <c r="L267" s="35" t="str">
+        <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
+        <v>髪飾り|耳装備</v>
+      </c>
+      <c r="M267" s="35" t="str">
+        <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="268" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A268" s="35">
+        <f>テーブル1[[#This Row],[番号]]</f>
+        <v>267</v>
+      </c>
+      <c r="B268" s="35" t="str">
+        <f>テーブル1[[#This Row],[名前]]</f>
+        <v>一色スウ</v>
+      </c>
+      <c r="C268" s="35" t="str">
+        <f>テーブル1[[#This Row],[なまえ]]</f>
+        <v>いっしき すう</v>
+      </c>
+      <c r="D268" s="35" t="str">
+        <f>テーブル1[[#This Row],[Name]]</f>
+        <v>Isshiki Su</v>
+      </c>
+      <c r="E268" s="35" t="str">
+        <f>"image/"&amp;テーブル1[[#This Row],[画像]]&amp;".png"</f>
+        <v>image/isshiki-su.png</v>
+      </c>
+      <c r="F268" s="35" t="str">
+        <f>テーブル1[[#This Row],[リンク]]</f>
+        <v>http://utau.wikidot.com/utau:isshiki-suu</v>
+      </c>
+      <c r="G268" s="35" t="str">
+        <f>SUBSTITUTE(テーブル1[[#This Row],[作品タグ]],"、","|")</f>
+        <v>#一色スウ</v>
+      </c>
+      <c r="H268" s="35" t="str">
+        <f>テーブル1[[#This Row],[性別]]&amp;""</f>
+        <v>男性</v>
+      </c>
+      <c r="I268" s="35" t="str">
+        <f>SUBSTITUTE(テーブル1[[#This Row],[種族タグ]],"、","|")</f>
+        <v>人間</v>
+      </c>
+      <c r="J268" s="35" t="str">
+        <f>SUBSTITUTE(テーブル1[[#This Row],[モチーフタグ]],"、","|")</f>
+        <v/>
+      </c>
+      <c r="K268" s="35" t="str">
+        <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
+        <v>アーティスト</v>
+      </c>
+      <c r="L268" s="35" t="str">
+        <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
+        <v>耳装備</v>
+      </c>
+      <c r="M268" s="35" t="str">
+        <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="269" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A269" s="35">
+        <f>テーブル1[[#This Row],[番号]]</f>
+        <v>268</v>
+      </c>
+      <c r="B269" s="35" t="str">
+        <f>テーブル1[[#This Row],[名前]]</f>
+        <v>亜音サイコ</v>
+      </c>
+      <c r="C269" s="35" t="str">
+        <f>テーブル1[[#This Row],[なまえ]]</f>
+        <v>つぎね さいこ</v>
+      </c>
+      <c r="D269" s="35" t="str">
+        <f>テーブル1[[#This Row],[Name]]</f>
+        <v>Tsugine Saiko</v>
+      </c>
+      <c r="E269" s="35" t="str">
+        <f>"image/"&amp;テーブル1[[#This Row],[画像]]&amp;".png"</f>
+        <v>image/tsugine-saiko.png</v>
+      </c>
+      <c r="F269" s="35" t="str">
+        <f>テーブル1[[#This Row],[リンク]]</f>
+        <v>https://aisupiku.wixsite.com/tsuginesaiko</v>
+      </c>
+      <c r="G269" s="35" t="str">
+        <f>SUBSTITUTE(テーブル1[[#This Row],[作品タグ]],"、","|")</f>
+        <v>#亜音サイコ</v>
+      </c>
+      <c r="H269" s="35" t="str">
+        <f>テーブル1[[#This Row],[性別]]&amp;""</f>
+        <v>女性</v>
+      </c>
+      <c r="I269" s="35" t="str">
+        <f>SUBSTITUTE(テーブル1[[#This Row],[種族タグ]],"、","|")</f>
+        <v>人間</v>
+      </c>
+      <c r="J269" s="35" t="str">
+        <f>SUBSTITUTE(テーブル1[[#This Row],[モチーフタグ]],"、","|")</f>
+        <v/>
+      </c>
+      <c r="K269" s="35" t="str">
+        <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
+        <v>歌手</v>
+      </c>
+      <c r="L269" s="35" t="str">
+        <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
+        <v>耳装備|眼部|首装飾</v>
+      </c>
+      <c r="M269" s="35" t="str">
+        <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
+        <v>メッシュ|尻尾</v>
       </c>
     </row>
   </sheetData>

--- a/data/characters.xlsx
+++ b/data/characters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\モノクロビリーフ\外部リンク\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E078B56-03CA-46F5-A07D-870B5C6EF9E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5DF461E-13F8-4AC0-BA8D-9AB69C883BBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{78CF6334-6F78-4A6F-BD14-CB6FA7AB00CF}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2554" uniqueCount="1322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2554" uniqueCount="1316">
   <si>
     <t>番号</t>
   </si>
@@ -3119,13 +3119,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>狼</t>
-    <rPh sb="0" eb="1">
-      <t>オオカミ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Tくん</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -3161,39 +3154,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>雀</t>
-    <rPh sb="0" eb="1">
-      <t>スズメ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>兎</t>
-    <rPh sb="0" eb="1">
-      <t>ウサギ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>兎</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>モチーフタグ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>磁石</t>
-    <rPh sb="0" eb="2">
-      <t>ジシャク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>蛙</t>
-    <rPh sb="0" eb="1">
-      <t>カエル</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -3215,10 +3176,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>クラゲ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>アイドル</t>
   </si>
   <si>
@@ -3238,13 +3195,6 @@
   </si>
   <si>
     <t>ニート</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>星</t>
-    <rPh sb="0" eb="1">
-      <t>ホシ</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -3289,10 +3239,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>キーボード</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>サポーター</t>
   </si>
   <si>
@@ -3330,27 +3276,6 @@
     </rPh>
     <rPh sb="2" eb="3">
       <t>マ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>犬</t>
-    <rPh sb="0" eb="1">
-      <t>イヌ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>猫</t>
-    <rPh sb="0" eb="1">
-      <t>ネコ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>狐</t>
-    <rPh sb="0" eb="1">
-      <t>キツネ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -3550,16 +3475,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>宇宙、猫</t>
-    <rPh sb="0" eb="2">
-      <t>ウチュウ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>ネコ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>片目隠れ、火傷、ほくろ</t>
     <rPh sb="0" eb="2">
       <t>カタメ</t>
@@ -3586,13 +3501,6 @@
     <t>魔法使い、手品師</t>
     <rPh sb="5" eb="8">
       <t>テジナシ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>兎、さくらんぼ</t>
-    <rPh sb="0" eb="1">
-      <t>ウサギ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -3742,10 +3650,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ギター</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>インナーカラー</t>
   </si>
   <si>
@@ -3764,10 +3668,6 @@
   </si>
   <si>
     <t>怪異</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>女郎蜘蛛</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -3899,10 +3799,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>アイス</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>泡沫綴</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -3932,13 +3828,6 @@
   </si>
   <si>
     <t>蛇川蓮</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>蛇</t>
-    <rPh sb="0" eb="1">
-      <t>ヘビ</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -4000,10 +3889,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>カラス</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>KR-725</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -5259,10 +5144,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>イラスト</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>#薪宮風季</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -5374,17 +5255,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ベル</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>環境音</t>
-    <rPh sb="0" eb="3">
-      <t>カンキョウオン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>髪飾り</t>
   </si>
   <si>
@@ -5469,6 +5339,61 @@
       <t>ケイサツカン</t>
     </rPh>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>哺乳類</t>
+  </si>
+  <si>
+    <t>哺乳類</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>鳥類</t>
+  </si>
+  <si>
+    <t>鳥類</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>爬虫類・両生類</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>魚類・海洋生物</t>
+  </si>
+  <si>
+    <t>昆虫・節足動物</t>
+  </si>
+  <si>
+    <t>宇宙・天体</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>宇宙・天体、哺乳類</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>哺乳類、植物・自然</t>
+  </si>
+  <si>
+    <t>食べ物</t>
+  </si>
+  <si>
+    <t>音楽</t>
+  </si>
+  <si>
+    <t>音楽</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>機械・道具</t>
+  </si>
+  <si>
+    <t>機械・道具</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>芸術・創作</t>
   </si>
 </sst>
 </file>
@@ -5704,7 +5629,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5800,18 +5725,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -7432,7 +7345,7 @@
         <v>663</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>664</v>
@@ -7492,10 +7405,10 @@
         <v>460</v>
       </c>
       <c r="D2" s="23" t="s">
-        <v>880</v>
+        <v>861</v>
       </c>
       <c r="E2" s="23" t="s">
-        <v>1048</v>
+        <v>1029</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>149</v>
@@ -7570,10 +7483,10 @@
         <v>461</v>
       </c>
       <c r="D3" s="23" t="s">
-        <v>881</v>
+        <v>862</v>
       </c>
       <c r="E3" s="23" t="s">
-        <v>1049</v>
+        <v>1030</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>129</v>
@@ -7591,10 +7504,10 @@
         <v>668</v>
       </c>
       <c r="L3" s="23" t="s">
-        <v>1300</v>
+        <v>1278</v>
       </c>
       <c r="M3" s="23" t="s">
-        <v>779</v>
+        <v>767</v>
       </c>
       <c r="O3" s="1" t="s">
         <v>549</v>
@@ -7666,16 +7579,16 @@
         <v>661</v>
       </c>
       <c r="I4" s="23" t="s">
-        <v>780</v>
+        <v>768</v>
       </c>
       <c r="J4" s="23" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="K4" s="23" t="s">
         <v>672</v>
       </c>
       <c r="M4" s="23" t="s">
-        <v>781</v>
+        <v>769</v>
       </c>
       <c r="N4" s="1" t="s">
         <v>595</v>
@@ -7735,10 +7648,10 @@
         <v>142</v>
       </c>
       <c r="D5" s="23" t="s">
-        <v>882</v>
+        <v>863</v>
       </c>
       <c r="E5" s="23" t="s">
-        <v>1050</v>
+        <v>1031</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>143</v>
@@ -7753,7 +7666,7 @@
         <v>678</v>
       </c>
       <c r="L5" s="23" t="s">
-        <v>1302</v>
+        <v>1280</v>
       </c>
       <c r="O5" s="1" t="s">
         <v>549</v>
@@ -7810,10 +7723,10 @@
         <v>230</v>
       </c>
       <c r="D6" s="23" t="s">
-        <v>883</v>
+        <v>864</v>
       </c>
       <c r="E6" s="23" t="s">
-        <v>1051</v>
+        <v>1032</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>231</v>
@@ -7825,13 +7738,13 @@
         <v>660</v>
       </c>
       <c r="I6" s="23" t="s">
-        <v>1233</v>
+        <v>1214</v>
       </c>
       <c r="J6" s="23" t="s">
-        <v>739</v>
+        <v>1303</v>
       </c>
       <c r="L6" s="23" t="s">
-        <v>1301</v>
+        <v>1279</v>
       </c>
       <c r="M6" s="23" t="s">
         <v>679</v>
@@ -7963,10 +7876,10 @@
         <v>197</v>
       </c>
       <c r="D8" s="23" t="s">
-        <v>884</v>
+        <v>865</v>
       </c>
       <c r="E8" s="23" t="s">
-        <v>1052</v>
+        <v>1033</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>198</v>
@@ -7981,7 +7894,7 @@
         <v>675</v>
       </c>
       <c r="L8" s="23" t="s">
-        <v>1300</v>
+        <v>1278</v>
       </c>
       <c r="M8" s="23" t="s">
         <v>686</v>
@@ -8044,10 +7957,10 @@
         <v>248</v>
       </c>
       <c r="D9" s="23" t="s">
-        <v>885</v>
+        <v>866</v>
       </c>
       <c r="E9" s="23" t="s">
-        <v>1053</v>
+        <v>1034</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>249</v>
@@ -8059,7 +7972,7 @@
         <v>660</v>
       </c>
       <c r="I9" s="23" t="s">
-        <v>782</v>
+        <v>770</v>
       </c>
       <c r="M9" s="23" t="s">
         <v>679</v>
@@ -8119,10 +8032,10 @@
         <v>194</v>
       </c>
       <c r="D10" s="23" t="s">
-        <v>886</v>
+        <v>867</v>
       </c>
       <c r="E10" s="23" t="s">
-        <v>1054</v>
+        <v>1035</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>195</v>
@@ -8137,10 +8050,10 @@
         <v>669</v>
       </c>
       <c r="J10" s="23" t="s">
-        <v>740</v>
+        <v>1301</v>
       </c>
       <c r="L10" s="23" t="s">
-        <v>1298</v>
+        <v>1276</v>
       </c>
       <c r="M10" s="23" t="s">
         <v>697</v>
@@ -8215,7 +8128,7 @@
         <v>661</v>
       </c>
       <c r="I11" s="23" t="s">
-        <v>783</v>
+        <v>771</v>
       </c>
       <c r="M11" s="23" t="s">
         <v>698</v>
@@ -8275,10 +8188,10 @@
         <v>234</v>
       </c>
       <c r="D12" s="23" t="s">
-        <v>887</v>
+        <v>868</v>
       </c>
       <c r="E12" s="23" t="s">
-        <v>1055</v>
+        <v>1036</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>235</v>
@@ -8296,7 +8209,7 @@
         <v>701</v>
       </c>
       <c r="L12" s="23" t="s">
-        <v>1300</v>
+        <v>1278</v>
       </c>
       <c r="N12" s="1" t="s">
         <v>631</v>
@@ -8356,10 +8269,10 @@
         <v>274</v>
       </c>
       <c r="D13" s="23" t="s">
-        <v>888</v>
+        <v>869</v>
       </c>
       <c r="E13" s="23" t="s">
-        <v>1056</v>
+        <v>1037</v>
       </c>
       <c r="F13" s="23" t="s">
         <v>279</v>
@@ -8371,7 +8284,7 @@
         <v>660</v>
       </c>
       <c r="L13" s="23" t="s">
-        <v>1302</v>
+        <v>1280</v>
       </c>
       <c r="N13" s="1" t="s">
         <v>592</v>
@@ -8449,7 +8362,7 @@
         <v>703</v>
       </c>
       <c r="J14" s="23" t="s">
-        <v>741</v>
+        <v>1300</v>
       </c>
       <c r="M14" s="23" t="s">
         <v>704</v>
@@ -8509,10 +8422,10 @@
         <v>233</v>
       </c>
       <c r="D15" s="23" t="s">
-        <v>889</v>
+        <v>870</v>
       </c>
       <c r="E15" s="23" t="s">
-        <v>1057</v>
+        <v>1038</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>231</v>
@@ -8524,7 +8437,7 @@
         <v>661</v>
       </c>
       <c r="I15" s="23" t="s">
-        <v>784</v>
+        <v>772</v>
       </c>
       <c r="K15" s="23" t="s">
         <v>680</v>
@@ -8668,10 +8581,10 @@
         <v>593</v>
       </c>
       <c r="D17" s="23" t="s">
-        <v>890</v>
+        <v>871</v>
       </c>
       <c r="E17" s="23" t="s">
-        <v>1058</v>
+        <v>1039</v>
       </c>
       <c r="F17" s="15" t="s">
         <v>611</v>
@@ -8683,10 +8596,10 @@
         <v>684</v>
       </c>
       <c r="I17" s="23" t="s">
-        <v>829</v>
+        <v>813</v>
       </c>
       <c r="L17" s="23" t="s">
-        <v>1314</v>
+        <v>1292</v>
       </c>
       <c r="N17" s="1" t="s">
         <v>594</v>
@@ -8746,10 +8659,10 @@
         <v>277</v>
       </c>
       <c r="D18" s="23" t="s">
-        <v>891</v>
+        <v>872</v>
       </c>
       <c r="E18" s="23" t="s">
-        <v>1059</v>
+        <v>1040</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>611</v>
@@ -8761,13 +8674,13 @@
         <v>684</v>
       </c>
       <c r="I18" s="23" t="s">
-        <v>829</v>
+        <v>813</v>
       </c>
       <c r="K18" s="23" t="s">
         <v>707</v>
       </c>
       <c r="L18" s="23" t="s">
-        <v>1314</v>
+        <v>1292</v>
       </c>
       <c r="N18" s="1" t="s">
         <v>594</v>
@@ -8830,7 +8743,7 @@
         <v>38</v>
       </c>
       <c r="E19" s="23" t="s">
-        <v>1060</v>
+        <v>1041</v>
       </c>
       <c r="F19" s="15" t="s">
         <v>708</v>
@@ -8842,7 +8755,7 @@
         <v>660</v>
       </c>
       <c r="L19" s="23" t="s">
-        <v>1316</v>
+        <v>1294</v>
       </c>
       <c r="N19" s="1" t="s">
         <v>595</v>
@@ -8902,10 +8815,10 @@
         <v>102</v>
       </c>
       <c r="D20" s="23" t="s">
-        <v>892</v>
+        <v>873</v>
       </c>
       <c r="E20" s="23" t="s">
-        <v>1061</v>
+        <v>1042</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>103</v>
@@ -8917,10 +8830,10 @@
         <v>683</v>
       </c>
       <c r="I20" s="23" t="s">
-        <v>785</v>
+        <v>773</v>
       </c>
       <c r="L20" s="23" t="s">
-        <v>1302</v>
+        <v>1280</v>
       </c>
       <c r="O20" s="1" t="s">
         <v>549</v>
@@ -8977,10 +8890,10 @@
         <v>105</v>
       </c>
       <c r="D21" s="23" t="s">
-        <v>893</v>
+        <v>874</v>
       </c>
       <c r="E21" s="23" t="s">
-        <v>1062</v>
+        <v>1043</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>103</v>
@@ -8992,7 +8905,7 @@
         <v>683</v>
       </c>
       <c r="I21" s="23" t="s">
-        <v>785</v>
+        <v>773</v>
       </c>
       <c r="O21" s="1" t="s">
         <v>549</v>
@@ -9049,10 +8962,10 @@
         <v>517</v>
       </c>
       <c r="D22" s="23" t="s">
-        <v>894</v>
+        <v>875</v>
       </c>
       <c r="E22" s="23" t="s">
-        <v>1063</v>
+        <v>1044</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>329</v>
@@ -9067,7 +8980,7 @@
         <v>710</v>
       </c>
       <c r="M22" s="23" t="s">
-        <v>786</v>
+        <v>774</v>
       </c>
       <c r="N22" s="1" t="s">
         <v>594</v>
@@ -9145,10 +9058,10 @@
         <v>669</v>
       </c>
       <c r="K23" s="23" t="s">
-        <v>745</v>
+        <v>739</v>
       </c>
       <c r="L23" s="23" t="s">
-        <v>1309</v>
+        <v>1287</v>
       </c>
       <c r="M23" s="23" t="s">
         <v>692</v>
@@ -9226,10 +9139,10 @@
         <v>683</v>
       </c>
       <c r="I24" s="23" t="s">
-        <v>787</v>
+        <v>775</v>
       </c>
       <c r="L24" s="23" t="s">
-        <v>1300</v>
+        <v>1278</v>
       </c>
       <c r="N24" s="1" t="s">
         <v>594</v>
@@ -9307,7 +9220,7 @@
         <v>678</v>
       </c>
       <c r="L25" s="23" t="s">
-        <v>1303</v>
+        <v>1281</v>
       </c>
       <c r="M25" s="23" t="s">
         <v>692</v>
@@ -9370,10 +9283,10 @@
         <v>85</v>
       </c>
       <c r="D26" s="23" t="s">
-        <v>895</v>
+        <v>876</v>
       </c>
       <c r="E26" s="23" t="s">
-        <v>1064</v>
+        <v>1045</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>86</v>
@@ -9388,10 +9301,10 @@
         <v>669</v>
       </c>
       <c r="K26" s="23" t="s">
-        <v>750</v>
+        <v>743</v>
       </c>
       <c r="M26" s="23" t="s">
-        <v>788</v>
+        <v>776</v>
       </c>
       <c r="N26" s="1" t="s">
         <v>631</v>
@@ -9451,10 +9364,10 @@
         <v>88</v>
       </c>
       <c r="D27" s="23" t="s">
-        <v>896</v>
+        <v>877</v>
       </c>
       <c r="E27" s="23" t="s">
-        <v>1065</v>
+        <v>1046</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>86</v>
@@ -9469,10 +9382,10 @@
         <v>669</v>
       </c>
       <c r="K27" s="23" t="s">
-        <v>750</v>
+        <v>743</v>
       </c>
       <c r="M27" s="23" t="s">
-        <v>752</v>
+        <v>745</v>
       </c>
       <c r="N27" s="1" t="s">
         <v>631</v>
@@ -9532,13 +9445,13 @@
         <v>46</v>
       </c>
       <c r="D28" s="23" t="s">
-        <v>897</v>
+        <v>878</v>
       </c>
       <c r="E28" s="23" t="s">
-        <v>1066</v>
+        <v>1047</v>
       </c>
       <c r="F28" s="15" t="s">
-        <v>753</v>
+        <v>746</v>
       </c>
       <c r="G28" s="23" t="s">
         <v>47</v>
@@ -9550,10 +9463,10 @@
         <v>669</v>
       </c>
       <c r="J28" s="23" t="s">
-        <v>755</v>
+        <v>1307</v>
       </c>
       <c r="K28" s="23" t="s">
-        <v>754</v>
+        <v>747</v>
       </c>
       <c r="N28" s="1" t="s">
         <v>594</v>
@@ -9613,10 +9526,10 @@
         <v>520</v>
       </c>
       <c r="D29" s="23" t="s">
-        <v>898</v>
+        <v>879</v>
       </c>
       <c r="E29" s="23" t="s">
-        <v>1067</v>
+        <v>1048</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>90</v>
@@ -9685,10 +9598,10 @@
         <v>521</v>
       </c>
       <c r="D30" s="23" t="s">
-        <v>899</v>
+        <v>880</v>
       </c>
       <c r="E30" s="23" t="s">
-        <v>1068</v>
+        <v>1049</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>90</v>
@@ -9703,7 +9616,7 @@
         <v>669</v>
       </c>
       <c r="L30" s="23" t="s">
-        <v>1311</v>
+        <v>1289</v>
       </c>
       <c r="O30" s="1" t="s">
         <v>549</v>
@@ -9832,10 +9745,10 @@
         <v>523</v>
       </c>
       <c r="D32" s="23" t="s">
-        <v>900</v>
+        <v>881</v>
       </c>
       <c r="E32" s="23" t="s">
-        <v>1069</v>
+        <v>1050</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>198</v>
@@ -9847,7 +9760,7 @@
         <v>660</v>
       </c>
       <c r="I32" s="23" t="s">
-        <v>789</v>
+        <v>777</v>
       </c>
       <c r="K32" s="23" t="s">
         <v>687</v>
@@ -9916,10 +9829,10 @@
         <v>175</v>
       </c>
       <c r="D33" s="23" t="s">
-        <v>901</v>
+        <v>882</v>
       </c>
       <c r="E33" s="23" t="s">
-        <v>1070</v>
+        <v>1051</v>
       </c>
       <c r="F33" s="15" t="s">
         <v>176</v>
@@ -9931,16 +9844,16 @@
         <v>661</v>
       </c>
       <c r="I33" s="23" t="s">
-        <v>819</v>
+        <v>805</v>
       </c>
       <c r="K33" s="23" t="s">
-        <v>758</v>
+        <v>750</v>
       </c>
       <c r="L33" s="23" t="s">
-        <v>1311</v>
+        <v>1289</v>
       </c>
       <c r="M33" s="23" t="s">
-        <v>790</v>
+        <v>778</v>
       </c>
       <c r="N33" s="1" t="s">
         <v>631</v>
@@ -10000,13 +9913,13 @@
         <v>48</v>
       </c>
       <c r="D34" s="23" t="s">
-        <v>902</v>
+        <v>883</v>
       </c>
       <c r="E34" s="23" t="s">
-        <v>1071</v>
+        <v>1052</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>753</v>
+        <v>746</v>
       </c>
       <c r="G34" s="23" t="s">
         <v>47</v>
@@ -10018,10 +9931,10 @@
         <v>669</v>
       </c>
       <c r="L34" s="23" t="s">
-        <v>1310</v>
+        <v>1288</v>
       </c>
       <c r="M34" s="23" t="s">
-        <v>791</v>
+        <v>779</v>
       </c>
       <c r="N34" s="1" t="s">
         <v>594</v>
@@ -10081,10 +9994,10 @@
         <v>524</v>
       </c>
       <c r="D35" s="23" t="s">
-        <v>903</v>
+        <v>884</v>
       </c>
       <c r="E35" s="23" t="s">
-        <v>1072</v>
+        <v>1053</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>246</v>
@@ -10096,13 +10009,13 @@
         <v>661</v>
       </c>
       <c r="I35" s="23" t="s">
-        <v>783</v>
+        <v>771</v>
       </c>
       <c r="K35" s="23" t="s">
-        <v>757</v>
+        <v>749</v>
       </c>
       <c r="L35" s="23" t="s">
-        <v>1320</v>
+        <v>1298</v>
       </c>
       <c r="M35" s="23" t="s">
         <v>681</v>
@@ -10162,10 +10075,10 @@
         <v>178</v>
       </c>
       <c r="D36" s="23" t="s">
-        <v>904</v>
+        <v>885</v>
       </c>
       <c r="E36" s="23" t="s">
-        <v>1073</v>
+        <v>1054</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>176</v>
@@ -10177,16 +10090,16 @@
         <v>661</v>
       </c>
       <c r="I36" s="23" t="s">
-        <v>747</v>
+        <v>741</v>
       </c>
       <c r="K36" s="23" t="s">
-        <v>1321</v>
+        <v>1299</v>
       </c>
       <c r="L36" s="23" t="s">
-        <v>1303</v>
+        <v>1281</v>
       </c>
       <c r="M36" s="23" t="s">
-        <v>760</v>
+        <v>752</v>
       </c>
       <c r="N36" s="1" t="s">
         <v>631</v>
@@ -10246,16 +10159,16 @@
         <v>71</v>
       </c>
       <c r="D37" s="23" t="s">
-        <v>905</v>
+        <v>886</v>
       </c>
       <c r="E37" s="23" t="s">
-        <v>1074</v>
+        <v>1055</v>
       </c>
       <c r="F37" s="15" t="s">
         <v>72</v>
       </c>
       <c r="G37" s="23" t="s">
-        <v>1219</v>
+        <v>1200</v>
       </c>
       <c r="H37" s="23" t="s">
         <v>661</v>
@@ -10264,10 +10177,10 @@
         <v>669</v>
       </c>
       <c r="K37" s="23" t="s">
-        <v>749</v>
+        <v>742</v>
       </c>
       <c r="L37" s="23" t="s">
-        <v>1298</v>
+        <v>1276</v>
       </c>
       <c r="N37" s="1" t="s">
         <v>594</v>
@@ -10327,10 +10240,10 @@
         <v>525</v>
       </c>
       <c r="D38" s="23" t="s">
-        <v>906</v>
+        <v>887</v>
       </c>
       <c r="E38" s="23" t="s">
-        <v>1075</v>
+        <v>1056</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>167</v>
@@ -10345,10 +10258,10 @@
         <v>678</v>
       </c>
       <c r="K38" s="23" t="s">
-        <v>792</v>
+        <v>780</v>
       </c>
       <c r="M38" s="23" t="s">
-        <v>765</v>
+        <v>756</v>
       </c>
       <c r="N38" s="1" t="s">
         <v>631</v>
@@ -10498,7 +10411,7 @@
         <v>669</v>
       </c>
       <c r="K40" s="23" t="s">
-        <v>761</v>
+        <v>753</v>
       </c>
       <c r="N40" s="1" t="s">
         <v>595</v>
@@ -10558,10 +10471,10 @@
         <v>107</v>
       </c>
       <c r="D41" s="23" t="s">
-        <v>907</v>
+        <v>888</v>
       </c>
       <c r="E41" s="23" t="s">
-        <v>1076</v>
+        <v>1057</v>
       </c>
       <c r="F41" s="30" t="s">
         <v>108</v>
@@ -10648,10 +10561,10 @@
         <v>669</v>
       </c>
       <c r="L42" s="23" t="s">
-        <v>1318</v>
+        <v>1296</v>
       </c>
       <c r="M42" s="23" t="s">
-        <v>746</v>
+        <v>740</v>
       </c>
       <c r="N42" s="1" t="s">
         <v>631</v>
@@ -10786,10 +10699,10 @@
         <v>526</v>
       </c>
       <c r="D44" s="23" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="E44" s="23" t="s">
-        <v>1077</v>
+        <v>1058</v>
       </c>
       <c r="F44" s="27" t="s">
         <v>57</v>
@@ -10801,13 +10714,13 @@
         <v>661</v>
       </c>
       <c r="I44" s="23" t="s">
-        <v>793</v>
+        <v>781</v>
       </c>
       <c r="J44" s="23" t="s">
-        <v>772</v>
+        <v>1301</v>
       </c>
       <c r="M44" s="23" t="s">
-        <v>794</v>
+        <v>782</v>
       </c>
       <c r="N44" s="1" t="s">
         <v>595</v>
@@ -10885,10 +10798,10 @@
         <v>669</v>
       </c>
       <c r="K45" s="23" t="s">
-        <v>761</v>
+        <v>753</v>
       </c>
       <c r="L45" s="23" t="s">
-        <v>1301</v>
+        <v>1279</v>
       </c>
       <c r="O45" s="1" t="s">
         <v>549</v>
@@ -10945,10 +10858,10 @@
         <v>528</v>
       </c>
       <c r="D46" s="23" t="s">
-        <v>909</v>
+        <v>890</v>
       </c>
       <c r="E46" s="23" t="s">
-        <v>1078</v>
+        <v>1059</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>66</v>
@@ -10963,10 +10876,10 @@
         <v>669</v>
       </c>
       <c r="K46" s="23" t="s">
-        <v>795</v>
+        <v>783</v>
       </c>
       <c r="L46" s="23" t="s">
-        <v>1306</v>
+        <v>1284</v>
       </c>
       <c r="N46" s="1" t="s">
         <v>594</v>
@@ -11026,10 +10939,10 @@
         <v>529</v>
       </c>
       <c r="D47" s="23" t="s">
-        <v>910</v>
+        <v>891</v>
       </c>
       <c r="E47" s="23" t="s">
-        <v>1079</v>
+        <v>1060</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>158</v>
@@ -11107,13 +11020,13 @@
         <v>660</v>
       </c>
       <c r="I48" s="23" t="s">
-        <v>766</v>
+        <v>757</v>
       </c>
       <c r="L48" s="23" t="s">
-        <v>1304</v>
+        <v>1282</v>
       </c>
       <c r="M48" s="23" t="s">
-        <v>796</v>
+        <v>784</v>
       </c>
       <c r="N48" s="1" t="s">
         <v>631</v>
@@ -11305,10 +11218,10 @@
         <v>532</v>
       </c>
       <c r="D51" s="23" t="s">
-        <v>911</v>
+        <v>892</v>
       </c>
       <c r="E51" s="23" t="s">
-        <v>1080</v>
+        <v>1061</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>262</v>
@@ -11371,10 +11284,10 @@
         <v>533</v>
       </c>
       <c r="D52" s="23" t="s">
-        <v>912</v>
+        <v>893</v>
       </c>
       <c r="E52" s="23" t="s">
-        <v>1081</v>
+        <v>1062</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>238</v>
@@ -11455,7 +11368,7 @@
         <v>678</v>
       </c>
       <c r="K53" s="23" t="s">
-        <v>763</v>
+        <v>754</v>
       </c>
       <c r="N53" s="1" t="s">
         <v>631</v>
@@ -11515,10 +11428,10 @@
         <v>535</v>
       </c>
       <c r="D54" s="23" t="s">
-        <v>913</v>
+        <v>894</v>
       </c>
       <c r="E54" s="23" t="s">
-        <v>1082</v>
+        <v>1063</v>
       </c>
       <c r="F54" s="15" t="s">
         <v>662</v>
@@ -11605,7 +11518,7 @@
       <c r="K55" s="28"/>
       <c r="L55" s="28"/>
       <c r="M55" s="28" t="s">
-        <v>797</v>
+        <v>785</v>
       </c>
       <c r="N55" s="1" t="s">
         <v>631</v>
@@ -11797,10 +11710,10 @@
         <v>538</v>
       </c>
       <c r="D58" s="23" t="s">
-        <v>914</v>
+        <v>895</v>
       </c>
       <c r="E58" s="23" t="s">
-        <v>1083</v>
+        <v>1064</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>43</v>
@@ -11866,10 +11779,10 @@
         <v>539</v>
       </c>
       <c r="D59" s="23" t="s">
-        <v>915</v>
+        <v>896</v>
       </c>
       <c r="E59" s="23" t="s">
-        <v>1084</v>
+        <v>1065</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>43</v>
@@ -11935,10 +11848,10 @@
         <v>188</v>
       </c>
       <c r="D60" s="23" t="s">
-        <v>916</v>
+        <v>897</v>
       </c>
       <c r="E60" s="23" t="s">
-        <v>1085</v>
+        <v>1066</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>189</v>
@@ -12001,10 +11914,10 @@
         <v>22</v>
       </c>
       <c r="D61" s="23" t="s">
-        <v>917</v>
+        <v>898</v>
       </c>
       <c r="E61" s="23" t="s">
-        <v>1086</v>
+        <v>1067</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>20</v>
@@ -12016,10 +11929,10 @@
         <v>661</v>
       </c>
       <c r="I61" s="23" t="s">
-        <v>769</v>
+        <v>760</v>
       </c>
       <c r="J61" s="23" t="s">
-        <v>770</v>
+        <v>1301</v>
       </c>
       <c r="N61" s="1" t="s">
         <v>595</v>
@@ -12079,10 +11992,10 @@
         <v>563</v>
       </c>
       <c r="D62" s="23" t="s">
-        <v>918</v>
+        <v>899</v>
       </c>
       <c r="E62" s="23" t="s">
-        <v>1087</v>
+        <v>1068</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>191</v>
@@ -12145,34 +12058,34 @@
         <v>470</v>
       </c>
       <c r="D63" s="23" t="s">
-        <v>919</v>
+        <v>900</v>
       </c>
       <c r="E63" s="23" t="s">
-        <v>1088</v>
+        <v>1069</v>
       </c>
       <c r="F63" s="15" t="s">
         <v>122</v>
       </c>
       <c r="G63" s="24" t="s">
-        <v>778</v>
+        <v>766</v>
       </c>
       <c r="H63" s="23" t="s">
         <v>661</v>
       </c>
       <c r="I63" s="23" t="s">
-        <v>831</v>
+        <v>815</v>
       </c>
       <c r="J63" s="23" t="s">
-        <v>775</v>
+        <v>763</v>
       </c>
       <c r="K63" s="23" t="s">
-        <v>761</v>
+        <v>753</v>
       </c>
       <c r="L63" s="24" t="s">
-        <v>1302</v>
+        <v>1280</v>
       </c>
       <c r="M63" s="23" t="s">
-        <v>779</v>
+        <v>767</v>
       </c>
       <c r="N63" s="1" t="s">
         <v>631</v>
@@ -12232,10 +12145,10 @@
         <v>564</v>
       </c>
       <c r="D64" s="23" t="s">
-        <v>920</v>
+        <v>901</v>
       </c>
       <c r="E64" s="23" t="s">
-        <v>1089</v>
+        <v>1070</v>
       </c>
       <c r="F64" s="26" t="s">
         <v>55</v>
@@ -12319,7 +12232,7 @@
         <v>678</v>
       </c>
       <c r="L65" s="23" t="s">
-        <v>1302</v>
+        <v>1280</v>
       </c>
       <c r="N65" s="1" t="s">
         <v>594</v>
@@ -12379,10 +12292,10 @@
         <v>566</v>
       </c>
       <c r="D66" s="23" t="s">
-        <v>921</v>
+        <v>902</v>
       </c>
       <c r="E66" s="23" t="s">
-        <v>1090</v>
+        <v>1071</v>
       </c>
       <c r="F66" s="27" t="s">
         <v>57</v>
@@ -12397,7 +12310,7 @@
         <v>696</v>
       </c>
       <c r="M66" s="23" t="s">
-        <v>798</v>
+        <v>786</v>
       </c>
       <c r="N66" s="1" t="s">
         <v>595</v>
@@ -12457,10 +12370,10 @@
         <v>567</v>
       </c>
       <c r="D67" s="23" t="s">
-        <v>922</v>
+        <v>903</v>
       </c>
       <c r="E67" s="23" t="s">
-        <v>1091</v>
+        <v>1072</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>272</v>
@@ -12523,10 +12436,10 @@
         <v>568</v>
       </c>
       <c r="D68" s="23" t="s">
-        <v>923</v>
+        <v>904</v>
       </c>
       <c r="E68" s="23" t="s">
-        <v>1092</v>
+        <v>1073</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>158</v>
@@ -12589,10 +12502,10 @@
         <v>45</v>
       </c>
       <c r="D69" s="23" t="s">
-        <v>924</v>
+        <v>905</v>
       </c>
       <c r="E69" s="23" t="s">
-        <v>1093</v>
+        <v>1074</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>43</v>
@@ -12658,10 +12571,10 @@
         <v>569</v>
       </c>
       <c r="D70" s="23" t="s">
-        <v>925</v>
+        <v>906</v>
       </c>
       <c r="E70" s="23" t="s">
-        <v>1094</v>
+        <v>1075</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>262</v>
@@ -12724,10 +12637,10 @@
         <v>570</v>
       </c>
       <c r="D71" s="23" t="s">
-        <v>926</v>
+        <v>907</v>
       </c>
       <c r="E71" s="23" t="s">
-        <v>1095</v>
+        <v>1076</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>272</v>
@@ -12790,10 +12703,10 @@
         <v>571</v>
       </c>
       <c r="D72" s="23" t="s">
-        <v>927</v>
+        <v>908</v>
       </c>
       <c r="E72" s="23" t="s">
-        <v>1096</v>
+        <v>1077</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>224</v>
@@ -12856,10 +12769,10 @@
         <v>572</v>
       </c>
       <c r="D73" s="23" t="s">
-        <v>928</v>
+        <v>909</v>
       </c>
       <c r="E73" s="23" t="s">
-        <v>1097</v>
+        <v>1078</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>224</v>
@@ -12922,10 +12835,10 @@
         <v>573</v>
       </c>
       <c r="D74" s="23" t="s">
-        <v>929</v>
+        <v>910</v>
       </c>
       <c r="E74" s="23" t="s">
-        <v>1098</v>
+        <v>1079</v>
       </c>
       <c r="F74" s="2" t="s">
         <v>123</v>
@@ -12988,10 +12901,10 @@
         <v>40</v>
       </c>
       <c r="D75" s="23" t="s">
-        <v>930</v>
+        <v>911</v>
       </c>
       <c r="E75" s="23" t="s">
-        <v>1099</v>
+        <v>1080</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>41</v>
@@ -13201,10 +13114,10 @@
         <v>29</v>
       </c>
       <c r="D78" s="23" t="s">
-        <v>931</v>
+        <v>912</v>
       </c>
       <c r="E78" s="23" t="s">
-        <v>1100</v>
+        <v>1081</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>30</v>
@@ -13270,10 +13183,10 @@
         <v>193</v>
       </c>
       <c r="D79" s="23" t="s">
-        <v>932</v>
+        <v>913</v>
       </c>
       <c r="E79" s="23" t="s">
-        <v>1101</v>
+        <v>1082</v>
       </c>
       <c r="F79" s="2" t="s">
         <v>191</v>
@@ -13336,10 +13249,10 @@
         <v>24</v>
       </c>
       <c r="D80" s="23" t="s">
-        <v>933</v>
+        <v>914</v>
       </c>
       <c r="E80" s="23" t="s">
-        <v>1102</v>
+        <v>1083</v>
       </c>
       <c r="F80" s="2" t="s">
         <v>20</v>
@@ -13351,16 +13264,16 @@
         <v>660</v>
       </c>
       <c r="I80" s="23" t="s">
-        <v>1233</v>
+        <v>1214</v>
       </c>
       <c r="J80" s="23" t="s">
-        <v>771</v>
+        <v>1301</v>
       </c>
       <c r="L80" s="23" t="s">
         <v>688</v>
       </c>
       <c r="M80" s="23" t="s">
-        <v>799</v>
+        <v>787</v>
       </c>
       <c r="N80" s="1" t="s">
         <v>595</v>
@@ -13420,10 +13333,10 @@
         <v>134</v>
       </c>
       <c r="D81" s="23" t="s">
-        <v>934</v>
+        <v>915</v>
       </c>
       <c r="E81" s="23" t="s">
-        <v>1103</v>
+        <v>1084</v>
       </c>
       <c r="F81" s="2" t="s">
         <v>135</v>
@@ -13501,13 +13414,13 @@
         <v>684</v>
       </c>
       <c r="I82" s="23" t="s">
-        <v>747</v>
+        <v>741</v>
       </c>
       <c r="J82" s="23" t="s">
-        <v>800</v>
+        <v>1308</v>
       </c>
       <c r="M82" s="23" t="s">
-        <v>872</v>
+        <v>854</v>
       </c>
       <c r="N82" s="1" t="s">
         <v>631</v>
@@ -13567,10 +13480,10 @@
         <v>226</v>
       </c>
       <c r="D83" s="23" t="s">
-        <v>935</v>
+        <v>916</v>
       </c>
       <c r="E83" s="23" t="s">
-        <v>1104</v>
+        <v>1085</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>227</v>
@@ -13633,10 +13546,10 @@
         <v>229</v>
       </c>
       <c r="D84" s="23" t="s">
-        <v>936</v>
+        <v>917</v>
       </c>
       <c r="E84" s="23" t="s">
-        <v>1105</v>
+        <v>1086</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>227</v>
@@ -13765,10 +13678,10 @@
         <v>278</v>
       </c>
       <c r="D86" s="23" t="s">
-        <v>937</v>
+        <v>918</v>
       </c>
       <c r="E86" s="23" t="s">
-        <v>1106</v>
+        <v>1087</v>
       </c>
       <c r="F86" s="23" t="s">
         <v>279</v>
@@ -13838,7 +13751,7 @@
         <v>205</v>
       </c>
       <c r="E87" s="23" t="s">
-        <v>1107</v>
+        <v>1088</v>
       </c>
       <c r="F87" s="2" t="s">
         <v>198</v>
@@ -13850,7 +13763,7 @@
         <v>661</v>
       </c>
       <c r="I87" s="23" t="s">
-        <v>789</v>
+        <v>777</v>
       </c>
       <c r="K87" s="23" t="s">
         <v>687</v>
@@ -13937,7 +13850,7 @@
         <v>669</v>
       </c>
       <c r="L88" s="23" t="s">
-        <v>1300</v>
+        <v>1278</v>
       </c>
       <c r="M88" s="23" t="s">
         <v>692</v>
@@ -14069,10 +13982,10 @@
         <v>241</v>
       </c>
       <c r="D90" s="23" t="s">
-        <v>938</v>
+        <v>919</v>
       </c>
       <c r="E90" s="23" t="s">
-        <v>1108</v>
+        <v>1089</v>
       </c>
       <c r="F90" s="2" t="s">
         <v>242</v>
@@ -14135,10 +14048,10 @@
         <v>184</v>
       </c>
       <c r="D91" s="23" t="s">
-        <v>939</v>
+        <v>920</v>
       </c>
       <c r="E91" s="23" t="s">
-        <v>1109</v>
+        <v>1090</v>
       </c>
       <c r="F91" s="2" t="s">
         <v>176</v>
@@ -14150,13 +14063,13 @@
         <v>660</v>
       </c>
       <c r="I91" s="23" t="s">
-        <v>747</v>
+        <v>741</v>
       </c>
       <c r="K91" s="23" t="s">
-        <v>761</v>
+        <v>753</v>
       </c>
       <c r="L91" s="23" t="s">
-        <v>1298</v>
+        <v>1276</v>
       </c>
       <c r="N91" s="1" t="s">
         <v>631</v>
@@ -14216,10 +14129,10 @@
         <v>186</v>
       </c>
       <c r="D92" s="23" t="s">
-        <v>940</v>
+        <v>921</v>
       </c>
       <c r="E92" s="23" t="s">
-        <v>1110</v>
+        <v>1091</v>
       </c>
       <c r="F92" s="2" t="s">
         <v>176</v>
@@ -14231,13 +14144,13 @@
         <v>660</v>
       </c>
       <c r="I92" s="23" t="s">
-        <v>747</v>
+        <v>741</v>
       </c>
       <c r="K92" s="23" t="s">
-        <v>759</v>
+        <v>751</v>
       </c>
       <c r="L92" s="23" t="s">
-        <v>1298</v>
+        <v>1276</v>
       </c>
       <c r="N92" s="1" t="s">
         <v>631</v>
@@ -14297,10 +14210,10 @@
         <v>68</v>
       </c>
       <c r="D93" s="23" t="s">
-        <v>941</v>
+        <v>922</v>
       </c>
       <c r="E93" s="23" t="s">
-        <v>1111</v>
+        <v>1092</v>
       </c>
       <c r="F93" s="2" t="s">
         <v>69</v>
@@ -14384,7 +14297,7 @@
         <v>669</v>
       </c>
       <c r="K94" s="23" t="s">
-        <v>761</v>
+        <v>753</v>
       </c>
       <c r="N94" s="1" t="s">
         <v>595</v>
@@ -14582,10 +14495,10 @@
         <v>173</v>
       </c>
       <c r="D97" s="23" t="s">
-        <v>942</v>
+        <v>923</v>
       </c>
       <c r="E97" s="23" t="s">
-        <v>1112</v>
+        <v>1093</v>
       </c>
       <c r="F97" s="2" t="s">
         <v>167</v>
@@ -14600,10 +14513,10 @@
         <v>669</v>
       </c>
       <c r="K97" s="23" t="s">
-        <v>767</v>
+        <v>758</v>
       </c>
       <c r="M97" s="23" t="s">
-        <v>801</v>
+        <v>788</v>
       </c>
       <c r="N97" s="1" t="s">
         <v>631</v>
@@ -14663,10 +14576,10 @@
         <v>269</v>
       </c>
       <c r="D98" s="23" t="s">
-        <v>943</v>
+        <v>924</v>
       </c>
       <c r="E98" s="23" t="s">
-        <v>1113</v>
+        <v>1094</v>
       </c>
       <c r="F98" s="2" t="s">
         <v>270</v>
@@ -14747,7 +14660,7 @@
         <v>669</v>
       </c>
       <c r="M99" s="23" t="s">
-        <v>773</v>
+        <v>761</v>
       </c>
       <c r="O99" s="1" t="s">
         <v>549</v>
@@ -14804,7 +14717,7 @@
         <v>260</v>
       </c>
       <c r="D100" s="23" t="s">
-        <v>944</v>
+        <v>925</v>
       </c>
       <c r="E100" s="23" t="s">
         <v>261</v>
@@ -14819,10 +14732,10 @@
         <v>684</v>
       </c>
       <c r="I100" s="23" t="s">
-        <v>802</v>
+        <v>789</v>
       </c>
       <c r="K100" s="23" t="s">
-        <v>803</v>
+        <v>790</v>
       </c>
       <c r="O100" s="1" t="s">
         <v>549</v>
@@ -14879,10 +14792,10 @@
         <v>251</v>
       </c>
       <c r="D101" s="23" t="s">
-        <v>945</v>
+        <v>926</v>
       </c>
       <c r="E101" s="23" t="s">
-        <v>1114</v>
+        <v>1095</v>
       </c>
       <c r="F101" s="2" t="s">
         <v>249</v>
@@ -14897,13 +14810,13 @@
         <v>696</v>
       </c>
       <c r="J101" s="23" t="s">
-        <v>804</v>
+        <v>1309</v>
       </c>
       <c r="K101" s="23" t="s">
-        <v>756</v>
+        <v>748</v>
       </c>
       <c r="L101" s="23" t="s">
-        <v>1298</v>
+        <v>1276</v>
       </c>
       <c r="O101" s="1" t="s">
         <v>549</v>
@@ -14978,7 +14891,7 @@
         <v>678</v>
       </c>
       <c r="L102" s="23" t="s">
-        <v>1299</v>
+        <v>1277</v>
       </c>
       <c r="M102" s="23" t="s">
         <v>681</v>
@@ -15041,10 +14954,10 @@
         <v>54</v>
       </c>
       <c r="D103" s="23" t="s">
-        <v>946</v>
+        <v>927</v>
       </c>
       <c r="E103" s="23" t="s">
-        <v>1115</v>
+        <v>1096</v>
       </c>
       <c r="F103" s="27" t="s">
         <v>662</v>
@@ -15110,10 +15023,10 @@
         <v>237</v>
       </c>
       <c r="D104" s="23" t="s">
-        <v>947</v>
+        <v>928</v>
       </c>
       <c r="E104" s="23" t="s">
-        <v>1116</v>
+        <v>1097</v>
       </c>
       <c r="F104" s="2" t="s">
         <v>235</v>
@@ -15131,7 +15044,7 @@
         <v>701</v>
       </c>
       <c r="L104" s="23" t="s">
-        <v>1300</v>
+        <v>1278</v>
       </c>
       <c r="N104" s="1" t="s">
         <v>631</v>
@@ -15191,10 +15104,10 @@
         <v>160</v>
       </c>
       <c r="D105" s="23" t="s">
-        <v>948</v>
+        <v>929</v>
       </c>
       <c r="E105" s="23" t="s">
-        <v>1117</v>
+        <v>1098</v>
       </c>
       <c r="F105" s="2" t="s">
         <v>161</v>
@@ -15257,10 +15170,10 @@
         <v>280</v>
       </c>
       <c r="D106" s="23" t="s">
-        <v>949</v>
+        <v>930</v>
       </c>
       <c r="E106" s="23" t="s">
-        <v>1118</v>
+        <v>1099</v>
       </c>
       <c r="F106" s="15" t="s">
         <v>516</v>
@@ -15323,10 +15236,10 @@
         <v>174</v>
       </c>
       <c r="D107" s="23" t="s">
-        <v>950</v>
+        <v>931</v>
       </c>
       <c r="E107" s="23" t="s">
-        <v>1119</v>
+        <v>1100</v>
       </c>
       <c r="F107" s="2" t="s">
         <v>167</v>
@@ -15338,16 +15251,16 @@
         <v>660</v>
       </c>
       <c r="I107" s="23" t="s">
-        <v>805</v>
+        <v>791</v>
       </c>
       <c r="K107" s="23" t="s">
-        <v>768</v>
+        <v>759</v>
       </c>
       <c r="L107" s="23" t="s">
-        <v>1309</v>
+        <v>1287</v>
       </c>
       <c r="M107" s="23" t="s">
-        <v>779</v>
+        <v>767</v>
       </c>
       <c r="N107" s="1" t="s">
         <v>631</v>
@@ -15473,10 +15386,10 @@
         <v>209</v>
       </c>
       <c r="D109" s="23" t="s">
-        <v>951</v>
+        <v>932</v>
       </c>
       <c r="E109" s="23" t="s">
-        <v>1120</v>
+        <v>1101</v>
       </c>
       <c r="F109" s="2" t="s">
         <v>198</v>
@@ -15569,7 +15482,7 @@
         <v>661</v>
       </c>
       <c r="M110" s="23" t="s">
-        <v>751</v>
+        <v>744</v>
       </c>
       <c r="N110" s="1" t="s">
         <v>631</v>
@@ -15629,10 +15542,10 @@
         <v>240</v>
       </c>
       <c r="D111" s="23" t="s">
-        <v>952</v>
+        <v>933</v>
       </c>
       <c r="E111" s="23" t="s">
-        <v>1121</v>
+        <v>1102</v>
       </c>
       <c r="F111" s="2" t="s">
         <v>238</v>
@@ -15716,7 +15629,7 @@
         <v>711</v>
       </c>
       <c r="L112" s="23" t="s">
-        <v>1299</v>
+        <v>1277</v>
       </c>
       <c r="M112" s="23" t="s">
         <v>681</v>
@@ -15800,10 +15713,10 @@
         <v>673</v>
       </c>
       <c r="L113" s="23" t="s">
-        <v>1307</v>
+        <v>1285</v>
       </c>
       <c r="M113" s="23" t="s">
-        <v>806</v>
+        <v>792</v>
       </c>
       <c r="N113" s="1" t="s">
         <v>595</v>
@@ -15863,10 +15776,10 @@
         <v>580</v>
       </c>
       <c r="D114" s="23" t="s">
-        <v>953</v>
+        <v>934</v>
       </c>
       <c r="E114" s="23" t="s">
-        <v>1122</v>
+        <v>1103</v>
       </c>
       <c r="F114" s="2" t="s">
         <v>43</v>
@@ -15932,10 +15845,10 @@
         <v>418</v>
       </c>
       <c r="D115" s="23" t="s">
-        <v>954</v>
+        <v>935</v>
       </c>
       <c r="E115" s="23" t="s">
-        <v>1123</v>
+        <v>1104</v>
       </c>
       <c r="F115" s="15" t="s">
         <v>419</v>
@@ -16002,16 +15915,16 @@
         <v>334</v>
       </c>
       <c r="D116" s="23" t="s">
-        <v>955</v>
+        <v>936</v>
       </c>
       <c r="E116" s="23" t="s">
-        <v>1124</v>
+        <v>1105</v>
       </c>
       <c r="F116" s="2" t="s">
         <v>165</v>
       </c>
       <c r="G116" s="23" t="s">
-        <v>1220</v>
+        <v>1201</v>
       </c>
       <c r="O116" s="1" t="s">
         <v>549</v>
@@ -16083,19 +15996,19 @@
         <v>661</v>
       </c>
       <c r="I117" s="23" t="s">
-        <v>780</v>
+        <v>768</v>
       </c>
       <c r="J117" s="23" t="s">
-        <v>743</v>
+        <v>1314</v>
       </c>
       <c r="K117" s="23" t="s">
         <v>674</v>
       </c>
       <c r="L117" s="23" t="s">
-        <v>1302</v>
+        <v>1280</v>
       </c>
       <c r="M117" s="23" t="s">
-        <v>807</v>
+        <v>793</v>
       </c>
       <c r="N117" s="1" t="s">
         <v>595</v>
@@ -16224,10 +16137,10 @@
         <v>385</v>
       </c>
       <c r="D119" s="23" t="s">
-        <v>956</v>
+        <v>937</v>
       </c>
       <c r="E119" s="23" t="s">
-        <v>1125</v>
+        <v>1106</v>
       </c>
       <c r="F119" s="15" t="s">
         <v>386</v>
@@ -16293,10 +16206,10 @@
         <v>581</v>
       </c>
       <c r="D120" s="23" t="s">
-        <v>957</v>
+        <v>938</v>
       </c>
       <c r="E120" s="23" t="s">
-        <v>1126</v>
+        <v>1107</v>
       </c>
       <c r="F120" s="2" t="s">
         <v>43</v>
@@ -16428,10 +16341,10 @@
         <v>399</v>
       </c>
       <c r="D122" s="23" t="s">
-        <v>958</v>
+        <v>939</v>
       </c>
       <c r="E122" s="23" t="s">
-        <v>1127</v>
+        <v>1108</v>
       </c>
       <c r="F122" s="2" t="s">
         <v>397</v>
@@ -16494,10 +16407,10 @@
         <v>582</v>
       </c>
       <c r="D123" s="23" t="s">
-        <v>959</v>
+        <v>940</v>
       </c>
       <c r="E123" s="23" t="s">
-        <v>1128</v>
+        <v>1109</v>
       </c>
       <c r="F123" s="2" t="s">
         <v>43</v>
@@ -16563,10 +16476,10 @@
         <v>302</v>
       </c>
       <c r="D124" s="23" t="s">
-        <v>960</v>
+        <v>941</v>
       </c>
       <c r="E124" s="23" t="s">
-        <v>1129</v>
+        <v>1110</v>
       </c>
       <c r="F124" s="15" t="s">
         <v>161</v>
@@ -16896,10 +16809,10 @@
         <v>584</v>
       </c>
       <c r="D129" s="23" t="s">
-        <v>961</v>
+        <v>942</v>
       </c>
       <c r="E129" s="23" t="s">
-        <v>1130</v>
+        <v>1111</v>
       </c>
       <c r="F129" s="2" t="s">
         <v>43</v>
@@ -16965,10 +16878,10 @@
         <v>322</v>
       </c>
       <c r="D130" s="23" t="s">
-        <v>962</v>
+        <v>943</v>
       </c>
       <c r="E130" s="23" t="s">
-        <v>1131</v>
+        <v>1112</v>
       </c>
       <c r="F130" s="2" t="s">
         <v>90</v>
@@ -16983,7 +16896,7 @@
         <v>669</v>
       </c>
       <c r="L130" s="23" t="s">
-        <v>1311</v>
+        <v>1289</v>
       </c>
       <c r="O130" s="1" t="s">
         <v>549</v>
@@ -17112,10 +17025,10 @@
         <v>394</v>
       </c>
       <c r="D132" s="23" t="s">
-        <v>963</v>
+        <v>944</v>
       </c>
       <c r="E132" s="23" t="s">
-        <v>1132</v>
+        <v>1113</v>
       </c>
       <c r="F132" s="2" t="s">
         <v>393</v>
@@ -17178,10 +17091,10 @@
         <v>326</v>
       </c>
       <c r="D133" s="23" t="s">
-        <v>964</v>
+        <v>945</v>
       </c>
       <c r="E133" s="23" t="s">
-        <v>1133</v>
+        <v>1114</v>
       </c>
       <c r="F133" s="2" t="s">
         <v>224</v>
@@ -17244,10 +17157,10 @@
         <v>301</v>
       </c>
       <c r="D134" s="23" t="s">
-        <v>965</v>
+        <v>946</v>
       </c>
       <c r="E134" s="23" t="s">
-        <v>1134</v>
+        <v>1115</v>
       </c>
       <c r="F134" s="2" t="s">
         <v>161</v>
@@ -17310,10 +17223,10 @@
         <v>457</v>
       </c>
       <c r="D135" s="23" t="s">
-        <v>966</v>
+        <v>947</v>
       </c>
       <c r="E135" s="23" t="s">
-        <v>1135</v>
+        <v>1116</v>
       </c>
       <c r="F135" s="2" t="s">
         <v>456</v>
@@ -17376,10 +17289,10 @@
         <v>313</v>
       </c>
       <c r="D136" s="23" t="s">
-        <v>967</v>
+        <v>948</v>
       </c>
       <c r="E136" s="23" t="s">
-        <v>1136</v>
+        <v>1117</v>
       </c>
       <c r="F136" s="2" t="s">
         <v>314</v>
@@ -17442,10 +17355,10 @@
         <v>327</v>
       </c>
       <c r="D137" s="23" t="s">
-        <v>968</v>
+        <v>949</v>
       </c>
       <c r="E137" s="23" t="s">
-        <v>1137</v>
+        <v>1118</v>
       </c>
       <c r="F137" s="2" t="s">
         <v>224</v>
@@ -17508,10 +17421,10 @@
         <v>350</v>
       </c>
       <c r="D138" s="23" t="s">
-        <v>969</v>
+        <v>950</v>
       </c>
       <c r="E138" s="23" t="s">
-        <v>1138</v>
+        <v>1119</v>
       </c>
       <c r="F138" s="2" t="s">
         <v>83</v>
@@ -17523,13 +17436,13 @@
         <v>660</v>
       </c>
       <c r="I138" s="23" t="s">
-        <v>808</v>
+        <v>794</v>
       </c>
       <c r="L138" s="23" t="s">
-        <v>1299</v>
+        <v>1277</v>
       </c>
       <c r="M138" s="23" t="s">
-        <v>809</v>
+        <v>795</v>
       </c>
       <c r="O138" s="1" t="s">
         <v>549</v>
@@ -17586,10 +17499,10 @@
         <v>445</v>
       </c>
       <c r="D139" s="23" t="s">
-        <v>970</v>
+        <v>951</v>
       </c>
       <c r="E139" s="23" t="s">
-        <v>1139</v>
+        <v>1120</v>
       </c>
       <c r="F139" s="2" t="s">
         <v>389</v>
@@ -17655,10 +17568,10 @@
         <v>283</v>
       </c>
       <c r="D140" s="23" t="s">
-        <v>971</v>
+        <v>952</v>
       </c>
       <c r="E140" s="23" t="s">
-        <v>1140</v>
+        <v>1121</v>
       </c>
       <c r="F140" s="2" t="s">
         <v>43</v>
@@ -17724,10 +17637,10 @@
         <v>335</v>
       </c>
       <c r="D141" s="23" t="s">
-        <v>972</v>
+        <v>953</v>
       </c>
       <c r="E141" s="23" t="s">
-        <v>1141</v>
+        <v>1122</v>
       </c>
       <c r="F141" s="2" t="s">
         <v>336</v>
@@ -17793,10 +17706,10 @@
         <v>367</v>
       </c>
       <c r="D142" s="23" t="s">
-        <v>973</v>
+        <v>954</v>
       </c>
       <c r="E142" s="23" t="s">
-        <v>1142</v>
+        <v>1123</v>
       </c>
       <c r="F142" s="2" t="s">
         <v>365</v>
@@ -17859,10 +17772,10 @@
         <v>339</v>
       </c>
       <c r="D143" s="23" t="s">
-        <v>974</v>
+        <v>955</v>
       </c>
       <c r="E143" s="23" t="s">
-        <v>1143</v>
+        <v>1124</v>
       </c>
       <c r="F143" s="2" t="s">
         <v>338</v>
@@ -17929,13 +17842,13 @@
         <v>447</v>
       </c>
       <c r="D144" s="23" t="s">
-        <v>975</v>
+        <v>956</v>
       </c>
       <c r="E144" s="23" t="s">
-        <v>1144</v>
+        <v>1125</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>753</v>
+        <v>746</v>
       </c>
       <c r="G144" s="23" t="s">
         <v>47</v>
@@ -17944,13 +17857,13 @@
         <v>660</v>
       </c>
       <c r="I144" s="23" t="s">
-        <v>810</v>
+        <v>796</v>
       </c>
       <c r="K144" s="23" t="s">
-        <v>756</v>
+        <v>748</v>
       </c>
       <c r="L144" s="23" t="s">
-        <v>1312</v>
+        <v>1290</v>
       </c>
       <c r="N144" s="1" t="s">
         <v>594</v>
@@ -18010,10 +17923,10 @@
         <v>585</v>
       </c>
       <c r="D145" s="23" t="s">
-        <v>976</v>
+        <v>957</v>
       </c>
       <c r="E145" s="23" t="s">
-        <v>1145</v>
+        <v>1126</v>
       </c>
       <c r="F145" s="2" t="s">
         <v>43</v>
@@ -18079,10 +17992,10 @@
         <v>358</v>
       </c>
       <c r="D146" s="23" t="s">
-        <v>977</v>
+        <v>958</v>
       </c>
       <c r="E146" s="23" t="s">
-        <v>1146</v>
+        <v>1127</v>
       </c>
       <c r="F146" s="2" t="s">
         <v>356</v>
@@ -18145,10 +18058,10 @@
         <v>388</v>
       </c>
       <c r="D147" s="23" t="s">
-        <v>978</v>
+        <v>959</v>
       </c>
       <c r="E147" s="23" t="s">
-        <v>1147</v>
+        <v>1128</v>
       </c>
       <c r="F147" s="2" t="s">
         <v>389</v>
@@ -18214,10 +18127,10 @@
         <v>349</v>
       </c>
       <c r="D148" s="23" t="s">
-        <v>979</v>
+        <v>960</v>
       </c>
       <c r="E148" s="23" t="s">
-        <v>1148</v>
+        <v>1129</v>
       </c>
       <c r="F148" s="2" t="s">
         <v>83</v>
@@ -18232,7 +18145,7 @@
         <v>669</v>
       </c>
       <c r="J148" s="23" t="s">
-        <v>740</v>
+        <v>1301</v>
       </c>
       <c r="M148" s="23" t="s">
         <v>700</v>
@@ -18362,10 +18275,10 @@
         <v>508</v>
       </c>
       <c r="D150" s="23" t="s">
-        <v>980</v>
+        <v>961</v>
       </c>
       <c r="E150" s="23" t="s">
-        <v>1149</v>
+        <v>1130</v>
       </c>
       <c r="F150" s="15" t="s">
         <v>509</v>
@@ -18431,10 +18344,10 @@
         <v>396</v>
       </c>
       <c r="D151" s="23" t="s">
-        <v>981</v>
+        <v>962</v>
       </c>
       <c r="E151" s="23" t="s">
-        <v>1150</v>
+        <v>1131</v>
       </c>
       <c r="F151" s="2" t="s">
         <v>397</v>
@@ -18497,10 +18410,10 @@
         <v>586</v>
       </c>
       <c r="D152" s="23" t="s">
-        <v>982</v>
+        <v>963</v>
       </c>
       <c r="E152" s="23" t="s">
-        <v>1151</v>
+        <v>1132</v>
       </c>
       <c r="F152" s="2" t="s">
         <v>43</v>
@@ -18632,10 +18545,10 @@
         <v>436</v>
       </c>
       <c r="D154" s="23" t="s">
-        <v>983</v>
+        <v>964</v>
       </c>
       <c r="E154" s="23" t="s">
-        <v>1152</v>
+        <v>1133</v>
       </c>
       <c r="F154" s="2" t="s">
         <v>434</v>
@@ -18698,10 +18611,10 @@
         <v>348</v>
       </c>
       <c r="D155" s="23" t="s">
-        <v>984</v>
+        <v>965</v>
       </c>
       <c r="E155" s="23" t="s">
-        <v>1153</v>
+        <v>1134</v>
       </c>
       <c r="F155" s="2" t="s">
         <v>346</v>
@@ -18767,10 +18680,10 @@
         <v>321</v>
       </c>
       <c r="D156" s="23" t="s">
-        <v>985</v>
+        <v>966</v>
       </c>
       <c r="E156" s="23" t="s">
-        <v>1154</v>
+        <v>1135</v>
       </c>
       <c r="F156" s="2" t="s">
         <v>90</v>
@@ -18782,7 +18695,7 @@
         <v>660</v>
       </c>
       <c r="I156" s="23" t="s">
-        <v>802</v>
+        <v>789</v>
       </c>
       <c r="O156" s="1" t="s">
         <v>549</v>
@@ -18839,10 +18752,10 @@
         <v>319</v>
       </c>
       <c r="D157" s="23" t="s">
-        <v>986</v>
+        <v>967</v>
       </c>
       <c r="E157" s="23" t="s">
-        <v>1155</v>
+        <v>1136</v>
       </c>
       <c r="F157" s="2" t="s">
         <v>317</v>
@@ -18926,10 +18839,10 @@
         <v>678</v>
       </c>
       <c r="J158" s="23" t="s">
-        <v>762</v>
+        <v>1313</v>
       </c>
       <c r="K158" s="23" t="s">
-        <v>764</v>
+        <v>755</v>
       </c>
       <c r="M158" s="23" t="s">
         <v>704</v>
@@ -18992,10 +18905,10 @@
         <v>448</v>
       </c>
       <c r="D159" s="23" t="s">
-        <v>987</v>
+        <v>968</v>
       </c>
       <c r="E159" s="24" t="s">
-        <v>1156</v>
+        <v>1137</v>
       </c>
       <c r="F159" s="15" t="s">
         <v>386</v>
@@ -19061,10 +18974,10 @@
         <v>400</v>
       </c>
       <c r="D160" s="23" t="s">
-        <v>988</v>
+        <v>969</v>
       </c>
       <c r="E160" s="23" t="s">
-        <v>1157</v>
+        <v>1138</v>
       </c>
       <c r="F160" s="2" t="s">
         <v>401</v>
@@ -19128,10 +19041,10 @@
         <v>284</v>
       </c>
       <c r="D161" s="23" t="s">
-        <v>989</v>
+        <v>970</v>
       </c>
       <c r="E161" s="23" t="s">
-        <v>1158</v>
+        <v>1139</v>
       </c>
       <c r="F161" s="2" t="s">
         <v>43</v>
@@ -19197,10 +19110,10 @@
         <v>391</v>
       </c>
       <c r="D162" s="23" t="s">
-        <v>990</v>
+        <v>971</v>
       </c>
       <c r="E162" s="23" t="s">
-        <v>1159</v>
+        <v>1140</v>
       </c>
       <c r="F162" s="2" t="s">
         <v>392</v>
@@ -19330,10 +19243,10 @@
         <v>515</v>
       </c>
       <c r="D164" s="23" t="s">
-        <v>991</v>
+        <v>972</v>
       </c>
       <c r="E164" s="23" t="s">
-        <v>1160</v>
+        <v>1141</v>
       </c>
       <c r="F164" s="15" t="s">
         <v>481</v>
@@ -19396,10 +19309,10 @@
         <v>511</v>
       </c>
       <c r="D165" s="23" t="s">
-        <v>992</v>
+        <v>973</v>
       </c>
       <c r="E165" s="23" t="s">
-        <v>1161</v>
+        <v>1142</v>
       </c>
       <c r="F165" s="2" t="s">
         <v>512</v>
@@ -19595,10 +19508,10 @@
         <v>433</v>
       </c>
       <c r="D168" s="23" t="s">
-        <v>993</v>
+        <v>974</v>
       </c>
       <c r="E168" s="23" t="s">
-        <v>1162</v>
+        <v>1143</v>
       </c>
       <c r="F168" s="2" t="s">
         <v>434</v>
@@ -19727,10 +19640,10 @@
         <v>442</v>
       </c>
       <c r="D170" s="23" t="s">
-        <v>994</v>
+        <v>975</v>
       </c>
       <c r="E170" s="23" t="s">
-        <v>1163</v>
+        <v>1144</v>
       </c>
       <c r="F170" s="2" t="s">
         <v>440</v>
@@ -19811,7 +19724,7 @@
         <v>676</v>
       </c>
       <c r="L171" s="23" t="s">
-        <v>776</v>
+        <v>764</v>
       </c>
       <c r="M171" s="23" t="s">
         <v>677</v>
@@ -19874,10 +19787,10 @@
         <v>364</v>
       </c>
       <c r="D172" s="23" t="s">
-        <v>995</v>
+        <v>976</v>
       </c>
       <c r="E172" s="23" t="s">
-        <v>1164</v>
+        <v>1145</v>
       </c>
       <c r="F172" s="2" t="s">
         <v>365</v>
@@ -20072,10 +19985,10 @@
         <v>316</v>
       </c>
       <c r="D175" s="23" t="s">
-        <v>996</v>
+        <v>977</v>
       </c>
       <c r="E175" s="23" t="s">
-        <v>1165</v>
+        <v>1146</v>
       </c>
       <c r="F175" s="2" t="s">
         <v>317</v>
@@ -20141,10 +20054,10 @@
         <v>443</v>
       </c>
       <c r="D176" s="23" t="s">
-        <v>997</v>
+        <v>978</v>
       </c>
       <c r="E176" s="23" t="s">
-        <v>1166</v>
+        <v>1147</v>
       </c>
       <c r="F176" s="15" t="s">
         <v>502</v>
@@ -20273,10 +20186,10 @@
         <v>588</v>
       </c>
       <c r="D178" s="23" t="s">
-        <v>998</v>
+        <v>979</v>
       </c>
       <c r="E178" s="23" t="s">
-        <v>1167</v>
+        <v>1148</v>
       </c>
       <c r="F178" s="2" t="s">
         <v>43</v>
@@ -20342,10 +20255,10 @@
         <v>402</v>
       </c>
       <c r="D179" s="23" t="s">
-        <v>999</v>
+        <v>980</v>
       </c>
       <c r="E179" s="23" t="s">
-        <v>1168</v>
+        <v>1149</v>
       </c>
       <c r="F179" s="2" t="s">
         <v>401</v>
@@ -20475,10 +20388,10 @@
         <v>438</v>
       </c>
       <c r="D181" s="23" t="s">
-        <v>1000</v>
+        <v>981</v>
       </c>
       <c r="E181" s="23" t="s">
-        <v>1169</v>
+        <v>1150</v>
       </c>
       <c r="F181" s="15" t="s">
         <v>437</v>
@@ -20541,10 +20454,10 @@
         <v>490</v>
       </c>
       <c r="D182" s="23" t="s">
-        <v>1001</v>
+        <v>982</v>
       </c>
       <c r="E182" s="23" t="s">
-        <v>1170</v>
+        <v>1151</v>
       </c>
       <c r="F182" s="15" t="s">
         <v>491</v>
@@ -20607,10 +20520,10 @@
         <v>541</v>
       </c>
       <c r="D183" s="23" t="s">
-        <v>1002</v>
+        <v>983</v>
       </c>
       <c r="E183" s="23" t="s">
-        <v>1171</v>
+        <v>1152</v>
       </c>
       <c r="F183" s="15" t="s">
         <v>540</v>
@@ -20673,10 +20586,10 @@
         <v>446</v>
       </c>
       <c r="D184" s="23" t="s">
-        <v>1003</v>
+        <v>984</v>
       </c>
       <c r="E184" s="23" t="s">
-        <v>1172</v>
+        <v>1153</v>
       </c>
       <c r="F184" s="2" t="s">
         <v>389</v>
@@ -20742,10 +20655,10 @@
         <v>330</v>
       </c>
       <c r="D185" s="23" t="s">
-        <v>1004</v>
+        <v>985</v>
       </c>
       <c r="E185" s="23" t="s">
-        <v>1173</v>
+        <v>1154</v>
       </c>
       <c r="F185" s="2" t="s">
         <v>329</v>
@@ -20763,7 +20676,7 @@
         <v>668</v>
       </c>
       <c r="L185" s="23" t="s">
-        <v>1299</v>
+        <v>1277</v>
       </c>
       <c r="M185" s="23" t="s">
         <v>681</v>
@@ -20826,10 +20739,10 @@
         <v>285</v>
       </c>
       <c r="D186" s="23" t="s">
-        <v>1005</v>
+        <v>986</v>
       </c>
       <c r="E186" s="23" t="s">
-        <v>1174</v>
+        <v>1155</v>
       </c>
       <c r="F186" s="2" t="s">
         <v>43</v>
@@ -20910,7 +20823,7 @@
         <v>683</v>
       </c>
       <c r="I187" s="23" t="s">
-        <v>811</v>
+        <v>797</v>
       </c>
       <c r="K187" s="23" t="s">
         <v>694</v>
@@ -21039,10 +20952,10 @@
         <v>589</v>
       </c>
       <c r="D189" s="23" t="s">
-        <v>1006</v>
+        <v>987</v>
       </c>
       <c r="E189" s="23" t="s">
-        <v>1175</v>
+        <v>1156</v>
       </c>
       <c r="F189" s="2" t="s">
         <v>43</v>
@@ -21177,10 +21090,10 @@
         <v>412</v>
       </c>
       <c r="D191" s="23" t="s">
-        <v>1007</v>
+        <v>988</v>
       </c>
       <c r="E191" s="23" t="s">
-        <v>1176</v>
+        <v>1157</v>
       </c>
       <c r="F191" s="15" t="s">
         <v>413</v>
@@ -21312,10 +21225,10 @@
         <v>590</v>
       </c>
       <c r="D193" s="23" t="s">
-        <v>1008</v>
+        <v>989</v>
       </c>
       <c r="E193" s="23" t="s">
-        <v>1177</v>
+        <v>1158</v>
       </c>
       <c r="F193" s="2" t="s">
         <v>43</v>
@@ -21396,13 +21309,13 @@
         <v>660</v>
       </c>
       <c r="I194" s="23" t="s">
-        <v>747</v>
+        <v>741</v>
       </c>
       <c r="J194" s="23" t="s">
-        <v>748</v>
+        <v>1305</v>
       </c>
       <c r="M194" s="23" t="s">
-        <v>812</v>
+        <v>798</v>
       </c>
       <c r="N194" s="1" t="s">
         <v>631</v>
@@ -21462,10 +21375,10 @@
         <v>591</v>
       </c>
       <c r="D195" s="23" t="s">
-        <v>1009</v>
+        <v>990</v>
       </c>
       <c r="E195" s="23" t="s">
-        <v>1178</v>
+        <v>1159</v>
       </c>
       <c r="F195" s="2" t="s">
         <v>43</v>
@@ -21597,10 +21510,10 @@
         <v>377</v>
       </c>
       <c r="D197" s="23" t="s">
-        <v>1010</v>
+        <v>991</v>
       </c>
       <c r="E197" s="23" t="s">
-        <v>1179</v>
+        <v>1160</v>
       </c>
       <c r="F197" s="2" t="s">
         <v>378</v>
@@ -21663,10 +21576,10 @@
         <v>282</v>
       </c>
       <c r="D198" s="23" t="s">
-        <v>1011</v>
+        <v>992</v>
       </c>
       <c r="E198" s="23" t="s">
-        <v>1180</v>
+        <v>1161</v>
       </c>
       <c r="F198" s="2" t="s">
         <v>43</v>
@@ -21732,10 +21645,10 @@
         <v>420</v>
       </c>
       <c r="D199" s="23" t="s">
-        <v>1012</v>
+        <v>993</v>
       </c>
       <c r="E199" s="23" t="s">
-        <v>1181</v>
+        <v>1162</v>
       </c>
       <c r="F199" s="15" t="s">
         <v>421</v>
@@ -21801,10 +21714,10 @@
         <v>451</v>
       </c>
       <c r="D200" s="23" t="s">
-        <v>1013</v>
+        <v>994</v>
       </c>
       <c r="E200" s="23" t="s">
-        <v>1182</v>
+        <v>1163</v>
       </c>
       <c r="F200" s="15" t="s">
         <v>449</v>
@@ -21933,10 +21846,10 @@
         <v>577</v>
       </c>
       <c r="D202" s="23" t="s">
-        <v>1014</v>
+        <v>995</v>
       </c>
       <c r="E202" s="23" t="s">
-        <v>1183</v>
+        <v>1164</v>
       </c>
       <c r="F202" s="2" t="s">
         <v>578</v>
@@ -21999,10 +21912,10 @@
         <v>559</v>
       </c>
       <c r="D203" s="23" t="s">
-        <v>1015</v>
+        <v>996</v>
       </c>
       <c r="E203" s="23" t="s">
-        <v>1184</v>
+        <v>1165</v>
       </c>
       <c r="F203" s="15" t="s">
         <v>560</v>
@@ -22134,13 +22047,13 @@
         <v>575</v>
       </c>
       <c r="D205" s="23" t="s">
-        <v>1016</v>
+        <v>997</v>
       </c>
       <c r="E205" s="23" t="s">
-        <v>1185</v>
+        <v>1166</v>
       </c>
       <c r="F205" s="30" t="s">
-        <v>878</v>
+        <v>859</v>
       </c>
       <c r="G205" s="23" t="s">
         <v>576</v>
@@ -22200,10 +22113,10 @@
         <v>545</v>
       </c>
       <c r="D206" s="23" t="s">
-        <v>1017</v>
+        <v>998</v>
       </c>
       <c r="E206" s="23" t="s">
-        <v>1186</v>
+        <v>1167</v>
       </c>
       <c r="F206" s="15" t="s">
         <v>540</v>
@@ -22285,7 +22198,7 @@
         <v>683</v>
       </c>
       <c r="I207" s="23" t="s">
-        <v>871</v>
+        <v>853</v>
       </c>
       <c r="N207" s="1" t="s">
         <v>631</v>
@@ -22412,10 +22325,10 @@
         <v>286</v>
       </c>
       <c r="D209" s="23" t="s">
-        <v>1018</v>
+        <v>999</v>
       </c>
       <c r="E209" s="23" t="s">
-        <v>1187</v>
+        <v>1168</v>
       </c>
       <c r="F209" s="2" t="s">
         <v>43</v>
@@ -22481,10 +22394,10 @@
         <v>562</v>
       </c>
       <c r="D210" s="23" t="s">
-        <v>1019</v>
+        <v>1000</v>
       </c>
       <c r="E210" s="23" t="s">
-        <v>1188</v>
+        <v>1169</v>
       </c>
       <c r="F210" s="15" t="s">
         <v>557</v>
@@ -22623,13 +22536,13 @@
         <v>t-kun</v>
       </c>
       <c r="C212" s="24" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="D212" s="23" t="s">
         <v>602</v>
       </c>
       <c r="E212" s="23" t="s">
-        <v>1189</v>
+        <v>1170</v>
       </c>
       <c r="F212" s="15" t="s">
         <v>603</v>
@@ -22644,7 +22557,7 @@
         <v>669</v>
       </c>
       <c r="L212" s="23" t="s">
-        <v>1302</v>
+        <v>1280</v>
       </c>
       <c r="N212" s="1" t="s">
         <v>595</v>
@@ -22719,13 +22632,13 @@
         <v>684</v>
       </c>
       <c r="I213" s="23" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="L213" s="23" t="s">
-        <v>1302</v>
+        <v>1280</v>
       </c>
       <c r="M213" s="23" t="s">
-        <v>813</v>
+        <v>799</v>
       </c>
       <c r="N213" s="1" t="s">
         <v>595</v>
@@ -22785,10 +22698,10 @@
         <v>608</v>
       </c>
       <c r="D214" s="23" t="s">
-        <v>1020</v>
+        <v>1001</v>
       </c>
       <c r="E214" s="23" t="s">
-        <v>1190</v>
+        <v>1171</v>
       </c>
       <c r="F214" s="15" t="s">
         <v>610</v>
@@ -22854,10 +22767,10 @@
         <v>612</v>
       </c>
       <c r="D215" s="23" t="s">
-        <v>1021</v>
+        <v>1002</v>
       </c>
       <c r="E215" s="23" t="s">
-        <v>1191</v>
+        <v>1172</v>
       </c>
       <c r="F215" s="15" t="s">
         <v>645</v>
@@ -22929,10 +22842,10 @@
         <v>328</v>
       </c>
       <c r="D216" s="23" t="s">
-        <v>1022</v>
+        <v>1003</v>
       </c>
       <c r="E216" s="23" t="s">
-        <v>1192</v>
+        <v>1173</v>
       </c>
       <c r="F216" s="2" t="s">
         <v>329</v>
@@ -22947,7 +22860,7 @@
         <v>675</v>
       </c>
       <c r="L216" s="23" t="s">
-        <v>1300</v>
+        <v>1278</v>
       </c>
       <c r="M216" s="23" t="s">
         <v>712</v>
@@ -23079,10 +22992,10 @@
         <v>619</v>
       </c>
       <c r="D218" s="23" t="s">
-        <v>1023</v>
+        <v>1004</v>
       </c>
       <c r="E218" s="23" t="s">
-        <v>1193</v>
+        <v>1174</v>
       </c>
       <c r="F218" s="15" t="s">
         <v>198</v>
@@ -23100,7 +23013,7 @@
         <v>668</v>
       </c>
       <c r="L218" s="23" t="s">
-        <v>1300</v>
+        <v>1278</v>
       </c>
       <c r="M218" s="23" t="s">
         <v>695</v>
@@ -23163,7 +23076,7 @@
         <v>625</v>
       </c>
       <c r="D219" s="23" t="s">
-        <v>1024</v>
+        <v>1005</v>
       </c>
       <c r="E219" s="23" t="s">
         <v>626</v>
@@ -23232,10 +23145,10 @@
         <v>627</v>
       </c>
       <c r="D220" s="23" t="s">
-        <v>1025</v>
+        <v>1006</v>
       </c>
       <c r="E220" s="23" t="s">
-        <v>1194</v>
+        <v>1175</v>
       </c>
       <c r="F220" s="15" t="s">
         <v>611</v>
@@ -23250,7 +23163,7 @@
         <v>675</v>
       </c>
       <c r="L220" s="23" t="s">
-        <v>1298</v>
+        <v>1276</v>
       </c>
       <c r="N220" s="1" t="s">
         <v>594</v>
@@ -23310,10 +23223,10 @@
         <v>628</v>
       </c>
       <c r="D221" s="23" t="s">
-        <v>1026</v>
+        <v>1007</v>
       </c>
       <c r="E221" s="23" t="s">
-        <v>1195</v>
+        <v>1176</v>
       </c>
       <c r="F221" s="15" t="s">
         <v>629</v>
@@ -23448,10 +23361,10 @@
         <v>636</v>
       </c>
       <c r="D223" s="23" t="s">
-        <v>1027</v>
+        <v>1008</v>
       </c>
       <c r="E223" s="23" t="s">
-        <v>1196</v>
+        <v>1177</v>
       </c>
       <c r="F223" s="15" t="s">
         <v>629</v>
@@ -23518,16 +23431,16 @@
         <v>637</v>
       </c>
       <c r="D224" s="23" t="s">
-        <v>1028</v>
+        <v>1009</v>
       </c>
       <c r="E224" s="23" t="s">
-        <v>1197</v>
+        <v>1178</v>
       </c>
       <c r="F224" s="15" t="s">
         <v>638</v>
       </c>
       <c r="G224" s="23" t="s">
-        <v>1221</v>
+        <v>1202</v>
       </c>
       <c r="O224" s="1" t="s">
         <v>549</v>
@@ -23584,10 +23497,10 @@
         <v>639</v>
       </c>
       <c r="D225" s="23" t="s">
-        <v>1029</v>
+        <v>1010</v>
       </c>
       <c r="E225" s="23" t="s">
-        <v>1198</v>
+        <v>1179</v>
       </c>
       <c r="F225" s="15" t="s">
         <v>640</v>
@@ -23671,7 +23584,7 @@
         <v>669</v>
       </c>
       <c r="M226" s="23" t="s">
-        <v>1266</v>
+        <v>1247</v>
       </c>
       <c r="N226" s="1" t="s">
         <v>631</v>
@@ -23734,7 +23647,7 @@
         <v>648</v>
       </c>
       <c r="E227" s="23" t="s">
-        <v>1199</v>
+        <v>1180</v>
       </c>
       <c r="F227" s="15" t="s">
         <v>645</v>
@@ -23749,10 +23662,10 @@
         <v>669</v>
       </c>
       <c r="K227" s="23" t="s">
-        <v>759</v>
+        <v>751</v>
       </c>
       <c r="M227" s="23" t="s">
-        <v>1267</v>
+        <v>1248</v>
       </c>
       <c r="N227" s="1" t="s">
         <v>631</v>
@@ -23812,10 +23725,10 @@
         <v>713</v>
       </c>
       <c r="D228" s="23" t="s">
-        <v>1030</v>
+        <v>1011</v>
       </c>
       <c r="E228" s="23" t="s">
-        <v>1200</v>
+        <v>1181</v>
       </c>
       <c r="F228" s="15" t="s">
         <v>714</v>
@@ -23833,10 +23746,10 @@
         <v>716</v>
       </c>
       <c r="L228" s="23" t="s">
-        <v>1315</v>
+        <v>1293</v>
       </c>
       <c r="M228" s="23" t="s">
-        <v>814</v>
+        <v>800</v>
       </c>
       <c r="N228" s="1" t="s">
         <v>631</v>
@@ -23896,10 +23809,10 @@
         <v>717</v>
       </c>
       <c r="D229" s="23" t="s">
-        <v>1031</v>
+        <v>1012</v>
       </c>
       <c r="E229" s="23" t="s">
-        <v>1201</v>
+        <v>1182</v>
       </c>
       <c r="F229" s="3" t="s">
         <v>718</v>
@@ -23914,7 +23827,7 @@
         <v>669</v>
       </c>
       <c r="L229" s="23" t="s">
-        <v>1302</v>
+        <v>1280</v>
       </c>
       <c r="N229" s="1" t="s">
         <v>720</v>
@@ -23977,7 +23890,7 @@
         <v>723</v>
       </c>
       <c r="E230" s="23" t="s">
-        <v>1202</v>
+        <v>1183</v>
       </c>
       <c r="F230" s="29" t="s">
         <v>726</v>
@@ -24052,10 +23965,10 @@
         <v>727</v>
       </c>
       <c r="D231" s="23" t="s">
-        <v>1032</v>
+        <v>1013</v>
       </c>
       <c r="E231" s="23" t="s">
-        <v>1203</v>
+        <v>1184</v>
       </c>
       <c r="F231" s="29" t="s">
         <v>728</v>
@@ -24067,16 +23980,16 @@
         <v>661</v>
       </c>
       <c r="I231" s="23" t="s">
-        <v>1233</v>
+        <v>1214</v>
       </c>
       <c r="J231" s="23" t="s">
-        <v>730</v>
+        <v>1301</v>
       </c>
       <c r="L231" s="23" t="s">
-        <v>1310</v>
+        <v>1288</v>
       </c>
       <c r="M231" s="23" t="s">
-        <v>799</v>
+        <v>787</v>
       </c>
       <c r="N231" s="1" t="s">
         <v>631</v>
@@ -24133,19 +24046,19 @@
         <v>amaga-eru</v>
       </c>
       <c r="C232" s="24" t="s">
+        <v>732</v>
+      </c>
+      <c r="D232" s="23" t="s">
+        <v>1014</v>
+      </c>
+      <c r="E232" s="23" t="s">
+        <v>1185</v>
+      </c>
+      <c r="F232" s="29" t="s">
         <v>733</v>
       </c>
-      <c r="D232" s="23" t="s">
-        <v>1033</v>
-      </c>
-      <c r="E232" s="23" t="s">
-        <v>1204</v>
-      </c>
-      <c r="F232" s="29" t="s">
+      <c r="G232" s="23" t="s">
         <v>734</v>
-      </c>
-      <c r="G232" s="23" t="s">
-        <v>735</v>
       </c>
       <c r="H232" s="23" t="s">
         <v>660</v>
@@ -24154,10 +24067,10 @@
         <v>669</v>
       </c>
       <c r="J232" s="23" t="s">
-        <v>744</v>
+        <v>1304</v>
       </c>
       <c r="L232" s="23" t="s">
-        <v>1304</v>
+        <v>1282</v>
       </c>
       <c r="N232" s="1" t="s">
         <v>631</v>
@@ -24214,16 +24127,16 @@
         <v>narukami-kyou</v>
       </c>
       <c r="C233" s="24" t="s">
+        <v>735</v>
+      </c>
+      <c r="D233" s="23" t="s">
+        <v>1015</v>
+      </c>
+      <c r="E233" s="23" t="s">
+        <v>1186</v>
+      </c>
+      <c r="F233" s="29" t="s">
         <v>736</v>
-      </c>
-      <c r="D233" s="23" t="s">
-        <v>1034</v>
-      </c>
-      <c r="E233" s="23" t="s">
-        <v>1205</v>
-      </c>
-      <c r="F233" s="29" t="s">
-        <v>737</v>
       </c>
       <c r="G233" s="23" t="str">
         <f>テーブル1[[#This Row],[名前]]&amp;"(UTAU)"</f>
@@ -24293,16 +24206,16 @@
         <v>468</v>
       </c>
       <c r="D234" s="23" t="s">
-        <v>1035</v>
+        <v>1016</v>
       </c>
       <c r="E234" s="23" t="s">
-        <v>1206</v>
+        <v>1187</v>
       </c>
       <c r="F234" s="15" t="s">
         <v>122</v>
       </c>
       <c r="G234" s="24" t="s">
-        <v>778</v>
+        <v>766</v>
       </c>
       <c r="H234" s="24" t="s">
         <v>661</v>
@@ -24312,13 +24225,13 @@
       </c>
       <c r="J234" s="24"/>
       <c r="K234" s="24" t="s">
-        <v>774</v>
+        <v>762</v>
       </c>
       <c r="L234" s="24" t="s">
-        <v>1302</v>
+        <v>1280</v>
       </c>
       <c r="M234" s="24" t="s">
-        <v>834</v>
+        <v>818</v>
       </c>
       <c r="N234" s="1" t="s">
         <v>631</v>
@@ -24378,32 +24291,32 @@
         <v>469</v>
       </c>
       <c r="D235" s="23" t="s">
-        <v>1036</v>
+        <v>1017</v>
       </c>
       <c r="E235" s="23" t="s">
-        <v>1207</v>
+        <v>1188</v>
       </c>
       <c r="F235" s="15" t="s">
         <v>122</v>
       </c>
       <c r="G235" s="24" t="s">
-        <v>777</v>
+        <v>765</v>
       </c>
       <c r="H235" s="24" t="s">
         <v>661</v>
       </c>
       <c r="I235" s="24" t="s">
-        <v>817</v>
+        <v>803</v>
       </c>
       <c r="J235" s="24"/>
       <c r="K235" s="24" t="s">
-        <v>761</v>
+        <v>753</v>
       </c>
       <c r="L235" s="24" t="s">
-        <v>1302</v>
+        <v>1280</v>
       </c>
       <c r="M235" s="24" t="s">
-        <v>818</v>
+        <v>804</v>
       </c>
       <c r="N235" s="1" t="s">
         <v>631</v>
@@ -24460,19 +24373,19 @@
         <v>haizaki-sho</v>
       </c>
       <c r="C236" s="24" t="s">
-        <v>815</v>
+        <v>801</v>
       </c>
       <c r="D236" s="23" t="s">
-        <v>1037</v>
+        <v>1018</v>
       </c>
       <c r="E236" s="23" t="s">
-        <v>1208</v>
+        <v>1189</v>
       </c>
       <c r="F236" s="15" t="s">
         <v>122</v>
       </c>
       <c r="G236" s="24" t="s">
-        <v>777</v>
+        <v>765</v>
       </c>
       <c r="H236" s="24" t="s">
         <v>661</v>
@@ -24483,10 +24396,10 @@
       <c r="J236" s="24"/>
       <c r="K236" s="24"/>
       <c r="L236" s="24" t="s">
-        <v>1302</v>
+        <v>1280</v>
       </c>
       <c r="M236" s="24" t="s">
-        <v>816</v>
+        <v>802</v>
       </c>
       <c r="N236" s="1" t="s">
         <v>631</v>
@@ -24546,29 +24459,29 @@
         <v>471</v>
       </c>
       <c r="D237" s="23" t="s">
-        <v>1038</v>
+        <v>1019</v>
       </c>
       <c r="E237" s="23" t="s">
-        <v>1209</v>
+        <v>1190</v>
       </c>
       <c r="F237" s="15" t="s">
         <v>122</v>
       </c>
       <c r="G237" s="24" t="s">
-        <v>777</v>
+        <v>765</v>
       </c>
       <c r="H237" s="24" t="s">
         <v>684</v>
       </c>
       <c r="I237" s="24" t="s">
-        <v>817</v>
+        <v>803</v>
       </c>
       <c r="J237" s="24" t="s">
-        <v>820</v>
+        <v>1311</v>
       </c>
       <c r="K237" s="24"/>
       <c r="L237" s="24" t="s">
-        <v>1302</v>
+        <v>1280</v>
       </c>
       <c r="M237" s="24" t="s">
         <v>704</v>
@@ -24640,7 +24553,7 @@
         <v>122</v>
       </c>
       <c r="G238" s="24" t="s">
-        <v>777</v>
+        <v>765</v>
       </c>
       <c r="H238" s="24" t="s">
         <v>661</v>
@@ -24650,7 +24563,7 @@
       <c r="K238" s="24"/>
       <c r="L238" s="24"/>
       <c r="M238" s="24" t="s">
-        <v>821</v>
+        <v>806</v>
       </c>
       <c r="N238" s="1" t="s">
         <v>631</v>
@@ -24719,7 +24632,7 @@
         <v>122</v>
       </c>
       <c r="G239" s="24" t="s">
-        <v>777</v>
+        <v>765</v>
       </c>
       <c r="H239" s="24" t="s">
         <v>661</v>
@@ -24796,7 +24709,7 @@
         <v>122</v>
       </c>
       <c r="G240" s="24" t="s">
-        <v>777</v>
+        <v>765</v>
       </c>
       <c r="H240" s="24" t="s">
         <v>661</v>
@@ -24806,7 +24719,7 @@
       <c r="K240" s="24"/>
       <c r="L240" s="24"/>
       <c r="M240" s="24" t="s">
-        <v>822</v>
+        <v>807</v>
       </c>
       <c r="N240" s="1" t="s">
         <v>631</v>
@@ -24863,28 +24776,28 @@
         <v>kumowatari-tsumugu</v>
       </c>
       <c r="C241" s="24" t="s">
-        <v>823</v>
+        <v>808</v>
       </c>
       <c r="D241" s="23" t="s">
-        <v>1039</v>
+        <v>1020</v>
       </c>
       <c r="E241" s="23" t="s">
-        <v>1210</v>
+        <v>1191</v>
       </c>
       <c r="F241" s="15" t="s">
         <v>122</v>
       </c>
       <c r="G241" s="24" t="s">
-        <v>777</v>
+        <v>765</v>
       </c>
       <c r="H241" s="24" t="s">
         <v>661</v>
       </c>
       <c r="I241" s="24" t="s">
-        <v>824</v>
+        <v>809</v>
       </c>
       <c r="J241" s="23" t="s">
-        <v>825</v>
+        <v>1306</v>
       </c>
       <c r="K241" s="24"/>
       <c r="L241" s="24"/>
@@ -24944,19 +24857,19 @@
         <v>hatatappoize</v>
       </c>
       <c r="C242" s="24" t="s">
-        <v>826</v>
+        <v>810</v>
       </c>
       <c r="D242" s="23" t="s">
-        <v>827</v>
+        <v>811</v>
       </c>
       <c r="E242" s="23" t="s">
-        <v>828</v>
+        <v>812</v>
       </c>
       <c r="F242" s="15" t="s">
         <v>122</v>
       </c>
       <c r="G242" s="24" t="s">
-        <v>777</v>
+        <v>765</v>
       </c>
       <c r="H242" s="24" t="s">
         <v>661</v>
@@ -24967,7 +24880,7 @@
       <c r="K242" s="24"/>
       <c r="L242" s="24"/>
       <c r="M242" s="24" t="s">
-        <v>830</v>
+        <v>814</v>
       </c>
       <c r="N242" s="1" t="s">
         <v>631</v>
@@ -25024,34 +24937,34 @@
         <v>shiraishi-sakuta</v>
       </c>
       <c r="C243" s="24" t="s">
-        <v>832</v>
+        <v>816</v>
       </c>
       <c r="D243" s="23" t="s">
-        <v>1040</v>
+        <v>1021</v>
       </c>
       <c r="E243" s="23" t="s">
-        <v>1211</v>
+        <v>1192</v>
       </c>
       <c r="F243" s="15" t="s">
         <v>122</v>
       </c>
       <c r="G243" s="24" t="s">
-        <v>777</v>
+        <v>765</v>
       </c>
       <c r="H243" s="24" t="s">
         <v>661</v>
       </c>
       <c r="I243" s="24" t="s">
-        <v>835</v>
+        <v>819</v>
       </c>
       <c r="K243" s="24" t="s">
-        <v>833</v>
+        <v>817</v>
       </c>
       <c r="L243" s="24" t="s">
-        <v>1311</v>
+        <v>1289</v>
       </c>
       <c r="M243" s="24" t="s">
-        <v>834</v>
+        <v>818</v>
       </c>
       <c r="N243" s="1" t="s">
         <v>631</v>
@@ -25108,19 +25021,19 @@
         <v>chikusa</v>
       </c>
       <c r="C244" s="24" t="s">
-        <v>836</v>
+        <v>820</v>
       </c>
       <c r="D244" s="23" t="s">
-        <v>836</v>
+        <v>820</v>
       </c>
       <c r="E244" s="23" t="s">
-        <v>837</v>
+        <v>821</v>
       </c>
       <c r="F244" s="15" t="s">
-        <v>838</v>
+        <v>822</v>
       </c>
       <c r="G244" s="24" t="s">
-        <v>839</v>
+        <v>823</v>
       </c>
       <c r="H244" s="24" t="s">
         <v>661</v>
@@ -25129,7 +25042,7 @@
       <c r="K244" s="24"/>
       <c r="L244" s="24"/>
       <c r="M244" s="24" t="s">
-        <v>834</v>
+        <v>818</v>
       </c>
       <c r="N244" s="1" t="s">
         <v>631</v>
@@ -25186,25 +25099,25 @@
         <v>warappoizo</v>
       </c>
       <c r="C245" s="24" t="s">
-        <v>840</v>
+        <v>824</v>
       </c>
       <c r="D245" s="23" t="s">
-        <v>841</v>
+        <v>825</v>
       </c>
       <c r="E245" s="23" t="s">
-        <v>842</v>
+        <v>826</v>
       </c>
       <c r="F245" s="15" t="s">
-        <v>843</v>
+        <v>827</v>
       </c>
       <c r="G245" s="24" t="s">
-        <v>845</v>
+        <v>829</v>
       </c>
       <c r="H245" s="24" t="s">
         <v>661</v>
       </c>
       <c r="I245" s="24" t="s">
-        <v>844</v>
+        <v>828</v>
       </c>
       <c r="K245" s="24"/>
       <c r="L245" s="24"/>
@@ -25263,19 +25176,19 @@
         <v>han'ei-xi</v>
       </c>
       <c r="C246" s="24" t="s">
-        <v>846</v>
+        <v>830</v>
       </c>
       <c r="D246" s="23" t="s">
-        <v>1041</v>
+        <v>1022</v>
       </c>
       <c r="E246" s="23" t="s">
-        <v>1212</v>
+        <v>1193</v>
       </c>
       <c r="F246" s="15" t="s">
-        <v>847</v>
+        <v>831</v>
       </c>
       <c r="G246" s="24" t="s">
-        <v>848</v>
+        <v>832</v>
       </c>
       <c r="H246" s="24" t="s">
         <v>683</v>
@@ -25284,7 +25197,7 @@
       <c r="K246" s="24"/>
       <c r="L246" s="24"/>
       <c r="M246" s="24" t="s">
-        <v>849</v>
+        <v>833</v>
       </c>
       <c r="N246" s="1" t="s">
         <v>720</v>
@@ -25341,19 +25254,19 @@
         <v>aisu-kurimu</v>
       </c>
       <c r="C247" s="24" t="s">
-        <v>850</v>
+        <v>834</v>
       </c>
       <c r="D247" s="23" t="s">
-        <v>1042</v>
+        <v>1023</v>
       </c>
       <c r="E247" s="23" t="s">
-        <v>1213</v>
+        <v>1194</v>
       </c>
       <c r="F247" s="15" t="s">
-        <v>851</v>
+        <v>835</v>
       </c>
       <c r="G247" s="24" t="s">
-        <v>852</v>
+        <v>836</v>
       </c>
       <c r="H247" s="24" t="s">
         <v>660</v>
@@ -25362,7 +25275,7 @@
         <v>678</v>
       </c>
       <c r="J247" s="23" t="s">
-        <v>853</v>
+        <v>1310</v>
       </c>
       <c r="K247" s="24"/>
       <c r="L247" s="24"/>
@@ -25424,13 +25337,13 @@
         <v>utakata-tsuzuri</v>
       </c>
       <c r="C248" s="24" t="s">
-        <v>854</v>
+        <v>837</v>
       </c>
       <c r="D248" s="23" t="s">
-        <v>1043</v>
+        <v>1024</v>
       </c>
       <c r="E248" s="23" t="s">
-        <v>1214</v>
+        <v>1195</v>
       </c>
       <c r="F248" s="15" t="s">
         <v>235</v>
@@ -25504,13 +25417,13 @@
         <v>f-113</v>
       </c>
       <c r="C249" s="24" t="s">
-        <v>855</v>
+        <v>838</v>
       </c>
       <c r="D249" s="23" t="s">
-        <v>1044</v>
+        <v>1025</v>
       </c>
       <c r="E249" s="23" t="s">
-        <v>855</v>
+        <v>838</v>
       </c>
       <c r="F249" s="15" t="s">
         <v>235</v>
@@ -25525,7 +25438,7 @@
         <v>678</v>
       </c>
       <c r="L249" s="24" t="s">
-        <v>1311</v>
+        <v>1289</v>
       </c>
       <c r="M249" s="24"/>
       <c r="N249" s="1" t="s">
@@ -25583,19 +25496,19 @@
         <v>apuda</v>
       </c>
       <c r="C250" s="24" t="s">
-        <v>856</v>
+        <v>839</v>
       </c>
       <c r="D250" s="23" t="s">
-        <v>857</v>
+        <v>840</v>
       </c>
       <c r="E250" s="23" t="s">
-        <v>858</v>
+        <v>841</v>
       </c>
       <c r="F250" s="15" t="s">
-        <v>859</v>
+        <v>842</v>
       </c>
       <c r="G250" s="23" t="s">
-        <v>860</v>
+        <v>843</v>
       </c>
       <c r="H250" s="24" t="s">
         <v>683</v>
@@ -25607,10 +25520,10 @@
         <v>668</v>
       </c>
       <c r="L250" s="24" t="s">
-        <v>1319</v>
+        <v>1297</v>
       </c>
       <c r="M250" s="24" t="s">
-        <v>779</v>
+        <v>767</v>
       </c>
       <c r="N250" s="1" t="s">
         <v>631</v>
@@ -25667,32 +25580,32 @@
         <v>hebikawa-ren</v>
       </c>
       <c r="C251" s="24" t="s">
-        <v>861</v>
+        <v>844</v>
       </c>
       <c r="D251" s="23" t="s">
-        <v>1045</v>
+        <v>1026</v>
       </c>
       <c r="E251" s="23" t="s">
-        <v>1215</v>
+        <v>1196</v>
       </c>
       <c r="F251" s="15" t="s">
         <v>123</v>
       </c>
       <c r="G251" s="23" t="s">
-        <v>873</v>
+        <v>855</v>
       </c>
       <c r="H251" s="24" t="s">
         <v>661</v>
       </c>
       <c r="I251" s="24" t="s">
-        <v>1233</v>
+        <v>1214</v>
       </c>
       <c r="J251" s="23" t="s">
-        <v>862</v>
+        <v>1304</v>
       </c>
       <c r="L251" s="24"/>
       <c r="M251" s="24" t="s">
-        <v>1222</v>
+        <v>1203</v>
       </c>
       <c r="N251" s="1" t="s">
         <v>631</v>
@@ -25749,28 +25662,28 @@
         <v>karasuda-tsubaki</v>
       </c>
       <c r="C252" s="24" t="s">
-        <v>863</v>
+        <v>845</v>
       </c>
       <c r="D252" s="23" t="s">
-        <v>1046</v>
+        <v>1027</v>
       </c>
       <c r="E252" s="23" t="s">
-        <v>1216</v>
+        <v>1197</v>
       </c>
       <c r="F252" s="15" t="s">
         <v>123</v>
       </c>
       <c r="G252" s="24" t="s">
-        <v>870</v>
+        <v>852</v>
       </c>
       <c r="H252" s="24" t="s">
         <v>661</v>
       </c>
       <c r="I252" s="24" t="s">
-        <v>1234</v>
+        <v>1215</v>
       </c>
       <c r="J252" s="23" t="s">
-        <v>874</v>
+        <v>1302</v>
       </c>
       <c r="L252" s="24"/>
       <c r="M252" s="24"/>
@@ -25829,32 +25742,32 @@
         <v>the-alien-cat-lyce</v>
       </c>
       <c r="C253" s="24" t="s">
-        <v>864</v>
+        <v>846</v>
       </c>
       <c r="D253" s="23" t="s">
-        <v>879</v>
+        <v>860</v>
       </c>
       <c r="E253" s="23" t="s">
-        <v>1217</v>
+        <v>1198</v>
       </c>
       <c r="F253" s="15" t="s">
-        <v>865</v>
+        <v>847</v>
       </c>
       <c r="G253" s="24" t="s">
-        <v>866</v>
+        <v>848</v>
       </c>
       <c r="H253" s="24" t="s">
         <v>684</v>
       </c>
       <c r="I253" s="24" t="s">
-        <v>747</v>
+        <v>741</v>
       </c>
       <c r="J253" s="23" t="s">
-        <v>771</v>
+        <v>1301</v>
       </c>
       <c r="L253" s="24"/>
       <c r="M253" s="23" t="s">
-        <v>799</v>
+        <v>787</v>
       </c>
       <c r="N253" s="1" t="s">
         <v>631</v>
@@ -25911,19 +25824,19 @@
         <v>kr-725</v>
       </c>
       <c r="C254" s="24" t="s">
-        <v>875</v>
+        <v>856</v>
       </c>
       <c r="D254" s="23" t="s">
-        <v>876</v>
+        <v>857</v>
       </c>
       <c r="E254" s="23" t="s">
-        <v>875</v>
+        <v>856</v>
       </c>
       <c r="F254" s="15" t="s">
         <v>557</v>
       </c>
       <c r="G254" s="24" t="s">
-        <v>877</v>
+        <v>858</v>
       </c>
       <c r="H254" s="24" t="s">
         <v>660</v>
@@ -25932,7 +25845,7 @@
         <v>678</v>
       </c>
       <c r="K254" s="23" t="s">
-        <v>869</v>
+        <v>851</v>
       </c>
       <c r="L254" s="24"/>
       <c r="M254" s="24" t="s">
@@ -25993,34 +25906,34 @@
         <v>kurumiyaki-yosiyuki</v>
       </c>
       <c r="C255" s="24" t="s">
-        <v>867</v>
+        <v>849</v>
       </c>
       <c r="D255" s="23" t="s">
-        <v>1047</v>
+        <v>1028</v>
       </c>
       <c r="E255" s="23" t="s">
-        <v>1218</v>
+        <v>1199</v>
       </c>
       <c r="F255" s="15" t="s">
-        <v>868</v>
+        <v>850</v>
       </c>
       <c r="G255" s="24" t="s">
-        <v>1236</v>
+        <v>1217</v>
       </c>
       <c r="H255" s="24" t="s">
         <v>683</v>
       </c>
       <c r="I255" s="24" t="s">
-        <v>1233</v>
+        <v>1214</v>
       </c>
       <c r="J255" s="23" t="s">
-        <v>1232</v>
+        <v>1213</v>
       </c>
       <c r="L255" s="24" t="s">
-        <v>1317</v>
+        <v>1295</v>
       </c>
       <c r="M255" s="24" t="s">
-        <v>1235</v>
+        <v>1216</v>
       </c>
       <c r="N255" s="1" t="s">
         <v>631</v>
@@ -26077,19 +25990,19 @@
         <v>oumi-kurina</v>
       </c>
       <c r="C256" s="24" t="s">
-        <v>1223</v>
+        <v>1204</v>
       </c>
       <c r="D256" s="23" t="s">
-        <v>1224</v>
+        <v>1205</v>
       </c>
       <c r="E256" s="23" t="s">
-        <v>1225</v>
+        <v>1206</v>
       </c>
       <c r="F256" s="15" t="s">
-        <v>1226</v>
+        <v>1207</v>
       </c>
       <c r="G256" s="24" t="s">
-        <v>1237</v>
+        <v>1218</v>
       </c>
       <c r="H256" s="24" t="s">
         <v>660</v>
@@ -26154,19 +26067,19 @@
         <v>mitama</v>
       </c>
       <c r="C257" s="24" t="s">
-        <v>1227</v>
+        <v>1208</v>
       </c>
       <c r="D257" s="23" t="s">
-        <v>1227</v>
+        <v>1208</v>
       </c>
       <c r="E257" s="23" t="s">
-        <v>1228</v>
+        <v>1209</v>
       </c>
       <c r="F257" s="15" t="s">
-        <v>838</v>
+        <v>822</v>
       </c>
       <c r="G257" s="24" t="s">
-        <v>1238</v>
+        <v>1219</v>
       </c>
       <c r="H257" s="24" t="s">
         <v>660</v>
@@ -26175,10 +26088,10 @@
         <v>669</v>
       </c>
       <c r="L257" s="24" t="s">
-        <v>1302</v>
+        <v>1280</v>
       </c>
       <c r="M257" s="24" t="s">
-        <v>816</v>
+        <v>802</v>
       </c>
       <c r="N257" s="1" t="s">
         <v>631</v>
@@ -26235,19 +26148,19 @@
         <v>mirakibo-11-gou</v>
       </c>
       <c r="C258" s="24" t="s">
-        <v>1229</v>
+        <v>1210</v>
       </c>
       <c r="D258" s="23" t="s">
-        <v>1230</v>
+        <v>1211</v>
       </c>
       <c r="E258" s="23" t="s">
-        <v>1231</v>
+        <v>1212</v>
       </c>
       <c r="F258" s="15" t="s">
-        <v>1226</v>
+        <v>1207</v>
       </c>
       <c r="G258" s="24" t="s">
-        <v>1239</v>
+        <v>1220</v>
       </c>
       <c r="H258" s="24" t="s">
         <v>683</v>
@@ -26314,19 +26227,19 @@
         <v>otoya-syuki</v>
       </c>
       <c r="C259" s="24" t="s">
-        <v>1240</v>
+        <v>1221</v>
       </c>
       <c r="D259" s="23" t="s">
-        <v>1241</v>
+        <v>1222</v>
       </c>
       <c r="E259" s="23" t="s">
-        <v>1242</v>
+        <v>1223</v>
       </c>
       <c r="F259" s="29" t="s">
-        <v>1243</v>
+        <v>1224</v>
       </c>
       <c r="G259" s="23" t="s">
-        <v>1244</v>
+        <v>1225</v>
       </c>
       <c r="H259" s="23" t="s">
         <v>661</v>
@@ -26335,13 +26248,13 @@
         <v>669</v>
       </c>
       <c r="K259" s="23" t="s">
-        <v>1245</v>
+        <v>1226</v>
       </c>
       <c r="L259" s="24" t="s">
-        <v>1300</v>
+        <v>1278</v>
       </c>
       <c r="M259" s="24" t="s">
-        <v>816</v>
+        <v>802</v>
       </c>
       <c r="N259" s="1" t="s">
         <v>631</v>
@@ -26398,19 +26311,19 @@
         <v>natsuno-seito</v>
       </c>
       <c r="C260" s="24" t="s">
-        <v>1246</v>
+        <v>1227</v>
       </c>
       <c r="D260" s="23" t="s">
-        <v>1247</v>
+        <v>1228</v>
       </c>
       <c r="E260" s="23" t="s">
-        <v>1248</v>
+        <v>1229</v>
       </c>
       <c r="F260" s="29" t="s">
-        <v>1243</v>
+        <v>1224</v>
       </c>
       <c r="G260" s="23" t="s">
-        <v>1244</v>
+        <v>1225</v>
       </c>
       <c r="H260" s="23" t="s">
         <v>661</v>
@@ -26419,10 +26332,10 @@
         <v>669</v>
       </c>
       <c r="K260" s="23" t="s">
-        <v>1249</v>
+        <v>1230</v>
       </c>
       <c r="M260" s="24" t="s">
-        <v>816</v>
+        <v>802</v>
       </c>
       <c r="N260" s="1" t="s">
         <v>631</v>
@@ -26479,19 +26392,19 @@
         <v>makimiya-fuki</v>
       </c>
       <c r="C261" s="24" t="s">
-        <v>1250</v>
+        <v>1231</v>
       </c>
       <c r="D261" s="23" t="s">
-        <v>1251</v>
+        <v>1232</v>
       </c>
       <c r="E261" s="23" t="s">
-        <v>1252</v>
+        <v>1233</v>
       </c>
       <c r="F261" s="29" t="s">
-        <v>1253</v>
+        <v>1234</v>
       </c>
       <c r="G261" s="23" t="s">
-        <v>1269</v>
+        <v>1249</v>
       </c>
       <c r="H261" s="23" t="s">
         <v>661</v>
@@ -26500,10 +26413,10 @@
         <v>669</v>
       </c>
       <c r="K261" s="23" t="s">
-        <v>1270</v>
+        <v>1250</v>
       </c>
       <c r="L261" s="23" t="s">
-        <v>1308</v>
+        <v>1286</v>
       </c>
       <c r="N261" s="1" t="s">
         <v>631</v>
@@ -26560,28 +26473,28 @@
         <v>wakunemu-supika</v>
       </c>
       <c r="C262" s="24" t="s">
-        <v>1256</v>
+        <v>1237</v>
       </c>
       <c r="D262" s="23" t="s">
-        <v>1254</v>
+        <v>1235</v>
       </c>
       <c r="E262" s="28" t="s">
-        <v>1255</v>
+        <v>1236</v>
       </c>
       <c r="F262" s="29" t="s">
         <v>645</v>
       </c>
       <c r="G262" s="23" t="s">
-        <v>1265</v>
+        <v>1246</v>
       </c>
       <c r="H262" s="23" t="s">
         <v>660</v>
       </c>
       <c r="I262" s="23" t="s">
-        <v>1233</v>
+        <v>1214</v>
       </c>
       <c r="J262" s="23" t="s">
-        <v>1268</v>
+        <v>1315</v>
       </c>
       <c r="N262" s="1" t="s">
         <v>631</v>
@@ -26638,19 +26551,19 @@
         <v>sumomone-fueru</v>
       </c>
       <c r="C263" s="24" t="s">
-        <v>1257</v>
+        <v>1238</v>
       </c>
       <c r="D263" s="23" t="s">
-        <v>1258</v>
+        <v>1239</v>
       </c>
       <c r="E263" s="23" t="s">
-        <v>1259</v>
+        <v>1240</v>
       </c>
       <c r="F263" s="29" t="s">
-        <v>1260</v>
+        <v>1241</v>
       </c>
       <c r="G263" s="23" t="s">
-        <v>1264</v>
+        <v>1245</v>
       </c>
       <c r="H263" s="23" t="s">
         <v>684</v>
@@ -26659,13 +26572,13 @@
         <v>705</v>
       </c>
       <c r="K263" s="23" t="s">
-        <v>1261</v>
+        <v>1242</v>
       </c>
       <c r="L263" s="23" t="s">
-        <v>1262</v>
+        <v>1243</v>
       </c>
       <c r="M263" s="23" t="s">
-        <v>1263</v>
+        <v>1244</v>
       </c>
       <c r="N263" s="1" t="s">
         <v>631</v>
@@ -26714,7 +26627,7 @@
       </c>
     </row>
     <row r="264" spans="1:25" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A264" s="34">
+      <c r="A264" s="20">
         <v>263</v>
       </c>
       <c r="B264" s="23" t="str">
@@ -26722,28 +26635,28 @@
         <v>ubuon-goe</v>
       </c>
       <c r="C264" s="24" t="s">
-        <v>1272</v>
+        <v>1252</v>
       </c>
       <c r="D264" s="23" t="s">
-        <v>1273</v>
+        <v>1253</v>
       </c>
       <c r="E264" s="23" t="s">
+        <v>1254</v>
+      </c>
+      <c r="F264" s="29" t="s">
+        <v>1275</v>
+      </c>
+      <c r="G264" s="23" t="s">
         <v>1274</v>
-      </c>
-      <c r="F264" s="29" t="s">
-        <v>1295</v>
-      </c>
-      <c r="G264" s="23" t="s">
-        <v>1294</v>
       </c>
       <c r="H264" s="23" t="s">
         <v>683</v>
       </c>
       <c r="I264" s="23" t="s">
-        <v>783</v>
+        <v>771</v>
       </c>
       <c r="L264" s="23" t="s">
-        <v>1313</v>
+        <v>1291</v>
       </c>
       <c r="N264" s="1" t="s">
         <v>631</v>
@@ -26765,7 +26678,7 @@
       </c>
       <c r="T264" s="24">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
-        <v>0.84773905082587875</v>
+        <v>0.13442594873170854</v>
       </c>
       <c r="U264" s="23" t="str">
         <f>"|&amp;image("&amp;テーブル1[[#This Row],[画像]]&amp;".png,width=100,height=100)"</f>
@@ -26789,7 +26702,7 @@
       </c>
     </row>
     <row r="265" spans="1:25" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A265" s="34">
+      <c r="A265" s="20">
         <v>264</v>
       </c>
       <c r="B265" s="23" t="str">
@@ -26797,19 +26710,19 @@
         <v>shuta-katsue</v>
       </c>
       <c r="C265" s="24" t="s">
-        <v>1271</v>
+        <v>1251</v>
       </c>
       <c r="D265" s="23" t="s">
+        <v>1255</v>
+      </c>
+      <c r="E265" s="23" t="s">
+        <v>1256</v>
+      </c>
+      <c r="F265" s="29" t="s">
         <v>1275</v>
       </c>
-      <c r="E265" s="23" t="s">
-        <v>1276</v>
-      </c>
-      <c r="F265" s="29" t="s">
-        <v>1295</v>
-      </c>
       <c r="G265" s="23" t="s">
-        <v>1294</v>
+        <v>1274</v>
       </c>
       <c r="H265" s="23" t="s">
         <v>660</v>
@@ -26818,7 +26731,7 @@
         <v>669</v>
       </c>
       <c r="L265" s="23" t="s">
-        <v>1300</v>
+        <v>1278</v>
       </c>
       <c r="N265" s="1" t="s">
         <v>631</v>
@@ -26833,7 +26746,7 @@
       </c>
       <c r="R265" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>25.463509101207258</v>
+        <v>25.415788342329659</v>
       </c>
       <c r="T265" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -26861,7 +26774,7 @@
       </c>
     </row>
     <row r="266" spans="1:25" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A266" s="34">
+      <c r="A266" s="20">
         <v>265</v>
       </c>
       <c r="B266" s="23" t="str">
@@ -26869,19 +26782,19 @@
         <v>narune-bell</v>
       </c>
       <c r="C266" s="24" t="s">
-        <v>1277</v>
+        <v>1257</v>
       </c>
       <c r="D266" s="23" t="s">
-        <v>1278</v>
+        <v>1258</v>
       </c>
       <c r="E266" s="23" t="s">
-        <v>1279</v>
+        <v>1259</v>
       </c>
       <c r="F266" s="29" t="s">
-        <v>1295</v>
+        <v>1275</v>
       </c>
       <c r="G266" s="23" t="s">
-        <v>1294</v>
+        <v>1274</v>
       </c>
       <c r="H266" s="23" t="s">
         <v>683</v>
@@ -26890,10 +26803,10 @@
         <v>678</v>
       </c>
       <c r="J266" s="23" t="s">
-        <v>1296</v>
+        <v>1311</v>
       </c>
       <c r="L266" s="23" t="s">
-        <v>1302</v>
+        <v>1280</v>
       </c>
       <c r="N266" s="1" t="s">
         <v>631</v>
@@ -26908,7 +26821,7 @@
       </c>
       <c r="R266" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>25.303125500354565</v>
+        <v>25.845956120115581</v>
       </c>
       <c r="T266" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -26936,27 +26849,27 @@
       </c>
     </row>
     <row r="267" spans="1:25" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A267" s="34">
+      <c r="A267" s="20">
         <v>266</v>
       </c>
-      <c r="B267" s="32" t="str">
+      <c r="B267" s="23" t="str">
         <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(テーブル1[[#This Row],[Name]])," ","-"),".","-"),"&amp;","-"),"_","-"),"・","-"),"=","-"),"--","-"),"--","-")</f>
         <v>keishikibangoα-01</v>
       </c>
       <c r="C267" s="24" t="s">
-        <v>1280</v>
+        <v>1260</v>
       </c>
       <c r="D267" s="23" t="s">
-        <v>1281</v>
+        <v>1261</v>
       </c>
       <c r="E267" s="23" t="s">
-        <v>1282</v>
+        <v>1262</v>
       </c>
       <c r="F267" s="29" t="s">
-        <v>1295</v>
+        <v>1275</v>
       </c>
       <c r="G267" s="23" t="s">
-        <v>1294</v>
+        <v>1274</v>
       </c>
       <c r="H267" s="23" t="s">
         <v>661</v>
@@ -26965,15 +26878,15 @@
         <v>678</v>
       </c>
       <c r="J267" s="23" t="s">
-        <v>1297</v>
+        <v>1312</v>
       </c>
       <c r="L267" s="23" t="s">
-        <v>1305</v>
+        <v>1283</v>
       </c>
       <c r="N267" s="1" t="s">
         <v>631</v>
       </c>
-      <c r="P267" s="33" t="str">
+      <c r="P267" s="24" t="str">
         <f>テーブル1[[#This Row],[リンク]]&amp;テーブル1[[#This Row],[描画状況]]</f>
         <v>https://nagimachi.wixsite.com/kairikonomachi</v>
       </c>
@@ -26983,55 +26896,55 @@
       </c>
       <c r="R267" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>25.721952292964257</v>
-      </c>
-      <c r="T267" s="33" t="str">
+        <v>25.884154811222359</v>
+      </c>
+      <c r="T267" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
         <v/>
       </c>
-      <c r="U267" s="32" t="str">
+      <c r="U267" s="23" t="str">
         <f>"|&amp;image("&amp;テーブル1[[#This Row],[画像]]&amp;".png,width=100,height=100)"</f>
         <v>|&amp;image(keishikibangoα-01.png,width=100,height=100)</v>
       </c>
-      <c r="V267" s="32" t="str">
+      <c r="V267" s="23" t="str">
         <f>"|MIDDLE:​"&amp;テーブル1[[#This Row],[名前]]</f>
         <v>|MIDDLE:​型式番号α-01</v>
       </c>
-      <c r="W267" s="32" t="str">
+      <c r="W267" s="23" t="str">
         <f>"|MIDDLE:​"&amp;テーブル1[[#This Row],[なまえ]]</f>
         <v>|MIDDLE:​けいしきばんごうα-01</v>
       </c>
-      <c r="X267" s="32" t="str">
+      <c r="X267" s="23" t="str">
         <f>"|MIDDLE:​"&amp;テーブル1[[#This Row],[Name]]</f>
         <v>|MIDDLE:​keishikibangoα-01</v>
       </c>
-      <c r="Y267" s="32" t="str">
+      <c r="Y267" s="23" t="str">
         <f>"|MIDDLE:​&amp;link(配布所はこちら){​"&amp;テーブル1[[#This Row],[リンク]]&amp;"}|"</f>
         <v>|MIDDLE:​&amp;link(配布所はこちら){​https://nagimachi.wixsite.com/kairikonomachi}|</v>
       </c>
     </row>
     <row r="268" spans="1:25" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A268" s="34">
+      <c r="A268" s="20">
         <v>267</v>
       </c>
-      <c r="B268" s="32" t="str">
+      <c r="B268" s="23" t="str">
         <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(テーブル1[[#This Row],[Name]])," ","-"),".","-"),"&amp;","-"),"_","-"),"・","-"),"=","-"),"--","-"),"--","-")</f>
         <v>isshiki-su</v>
       </c>
       <c r="C268" s="24" t="s">
-        <v>1283</v>
+        <v>1263</v>
       </c>
       <c r="D268" s="23" t="s">
-        <v>1284</v>
+        <v>1264</v>
       </c>
       <c r="E268" s="23" t="s">
-        <v>1285</v>
+        <v>1265</v>
       </c>
       <c r="F268" s="29" t="s">
-        <v>1291</v>
+        <v>1271</v>
       </c>
       <c r="G268" s="23" t="s">
-        <v>1292</v>
+        <v>1272</v>
       </c>
       <c r="H268" s="23" t="s">
         <v>661</v>
@@ -27040,15 +26953,15 @@
         <v>669</v>
       </c>
       <c r="K268" s="23" t="s">
-        <v>1293</v>
+        <v>1273</v>
       </c>
       <c r="L268" s="23" t="s">
-        <v>1302</v>
+        <v>1280</v>
       </c>
       <c r="N268" s="1" t="s">
         <v>631</v>
       </c>
-      <c r="P268" s="33" t="str">
+      <c r="P268" s="24" t="str">
         <f>テーブル1[[#This Row],[リンク]]&amp;テーブル1[[#This Row],[描画状況]]</f>
         <v>http://utau.wikidot.com/utau:isshiki-suu</v>
       </c>
@@ -27058,55 +26971,55 @@
       </c>
       <c r="R268" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.65513352069163744</v>
-      </c>
-      <c r="T268" s="33" t="str">
+        <v>6.1353744413322642E-2</v>
+      </c>
+      <c r="T268" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
         <v/>
       </c>
-      <c r="U268" s="32" t="str">
+      <c r="U268" s="23" t="str">
         <f>"|&amp;image("&amp;テーブル1[[#This Row],[画像]]&amp;".png,width=100,height=100)"</f>
         <v>|&amp;image(isshiki-su.png,width=100,height=100)</v>
       </c>
-      <c r="V268" s="32" t="str">
+      <c r="V268" s="23" t="str">
         <f>"|MIDDLE:​"&amp;テーブル1[[#This Row],[名前]]</f>
         <v>|MIDDLE:​一色スウ</v>
       </c>
-      <c r="W268" s="32" t="str">
+      <c r="W268" s="23" t="str">
         <f>"|MIDDLE:​"&amp;テーブル1[[#This Row],[なまえ]]</f>
         <v>|MIDDLE:​いっしき すう</v>
       </c>
-      <c r="X268" s="32" t="str">
+      <c r="X268" s="23" t="str">
         <f>"|MIDDLE:​"&amp;テーブル1[[#This Row],[Name]]</f>
         <v>|MIDDLE:​Isshiki Su</v>
       </c>
-      <c r="Y268" s="32" t="str">
+      <c r="Y268" s="23" t="str">
         <f>"|MIDDLE:​&amp;link(配布所はこちら){​"&amp;テーブル1[[#This Row],[リンク]]&amp;"}|"</f>
         <v>|MIDDLE:​&amp;link(配布所はこちら){​http://utau.wikidot.com/utau:isshiki-suu}|</v>
       </c>
     </row>
     <row r="269" spans="1:25" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A269" s="34">
+      <c r="A269" s="20">
         <v>268</v>
       </c>
-      <c r="B269" s="32" t="str">
+      <c r="B269" s="23" t="str">
         <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(テーブル1[[#This Row],[Name]])," ","-"),".","-"),"&amp;","-"),"_","-"),"・","-"),"=","-"),"--","-"),"--","-")</f>
         <v>tsugine-saiko</v>
       </c>
       <c r="C269" s="24" t="s">
-        <v>1286</v>
+        <v>1266</v>
       </c>
       <c r="D269" s="23" t="s">
-        <v>1287</v>
+        <v>1267</v>
       </c>
       <c r="E269" s="28" t="s">
-        <v>1288</v>
+        <v>1268</v>
       </c>
       <c r="F269" s="29" t="s">
-        <v>1289</v>
+        <v>1269</v>
       </c>
       <c r="G269" s="23" t="s">
-        <v>1290</v>
+        <v>1270</v>
       </c>
       <c r="H269" s="23" t="s">
         <v>660</v>
@@ -27115,18 +27028,18 @@
         <v>669</v>
       </c>
       <c r="K269" s="23" t="s">
-        <v>1270</v>
+        <v>1250</v>
       </c>
       <c r="L269" s="23" t="s">
-        <v>1308</v>
+        <v>1286</v>
       </c>
       <c r="M269" s="23" t="s">
-        <v>807</v>
+        <v>793</v>
       </c>
       <c r="N269" s="1" t="s">
         <v>631</v>
       </c>
-      <c r="P269" s="33" t="str">
+      <c r="P269" s="24" t="str">
         <f>テーブル1[[#This Row],[リンク]]&amp;テーブル1[[#This Row],[描画状況]]</f>
         <v>https://aisupiku.wixsite.com/tsuginesaiko</v>
       </c>
@@ -27136,29 +27049,29 @@
       </c>
       <c r="R269" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.58698733099778566</v>
-      </c>
-      <c r="T269" s="33" t="str">
+        <v>0.72687767731210373</v>
+      </c>
+      <c r="T269" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
         <v/>
       </c>
-      <c r="U269" s="32" t="str">
+      <c r="U269" s="23" t="str">
         <f>"|&amp;image("&amp;テーブル1[[#This Row],[画像]]&amp;".png,width=100,height=100)"</f>
         <v>|&amp;image(tsugine-saiko.png,width=100,height=100)</v>
       </c>
-      <c r="V269" s="32" t="str">
+      <c r="V269" s="23" t="str">
         <f>"|MIDDLE:​"&amp;テーブル1[[#This Row],[名前]]</f>
         <v>|MIDDLE:​亜音サイコ</v>
       </c>
-      <c r="W269" s="32" t="str">
+      <c r="W269" s="23" t="str">
         <f>"|MIDDLE:​"&amp;テーブル1[[#This Row],[なまえ]]</f>
         <v>|MIDDLE:​つぎね さいこ</v>
       </c>
-      <c r="X269" s="32" t="str">
+      <c r="X269" s="23" t="str">
         <f>"|MIDDLE:​"&amp;テーブル1[[#This Row],[Name]]</f>
         <v>|MIDDLE:​Tsugine Saiko</v>
       </c>
-      <c r="Y269" s="32" t="str">
+      <c r="Y269" s="23" t="str">
         <f>"|MIDDLE:​&amp;link(配布所はこちら){​"&amp;テーブル1[[#This Row],[リンク]]&amp;"}|"</f>
         <v>|MIDDLE:​&amp;link(配布所はこちら){​https://aisupiku.wixsite.com/tsuginesaiko}|</v>
       </c>
@@ -27213,7 +27126,7 @@
   <conditionalFormatting sqref="G252:G258">
     <cfRule type="duplicateValues" dxfId="1" priority="26"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M278:M279 O1:T1048576">
+  <conditionalFormatting sqref="O1:T1048576 M278:M279">
     <cfRule type="cellIs" dxfId="0" priority="12" operator="equal">
       <formula>"済"</formula>
     </cfRule>
@@ -27513,7 +27426,7 @@
       </c>
       <c r="C4" s="7">
         <f ca="1">MATCH(C5,キャラ情報!C:C,0)</f>
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -27522,7 +27435,7 @@
       </c>
       <c r="C5" s="6" t="str">
         <f ca="1">INDEX(キャラ情報!C:R,MATCH(MIN(キャラ情報!R:R),キャラ情報!R:R,0),1)</f>
-        <v>亜音サイコ</v>
+        <v>一色スウ</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -27531,7 +27444,7 @@
       </c>
       <c r="C6" s="6" t="str">
         <f ca="1">INDEX(キャラ情報!C:R,MATCH(MIN(キャラ情報!R:R),キャラ情報!R:R,0),4)</f>
-        <v>https://aisupiku.wixsite.com/tsuginesaiko</v>
+        <v>http://utau.wikidot.com/utau:isshiki-suu</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -27662,7 +27575,7 @@
         <v>663</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>664</v>
@@ -27929,7 +27842,7 @@
       </c>
       <c r="J6" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[モチーフタグ]],"、","|")</f>
-        <v>雀</v>
+        <v>鳥類</v>
       </c>
       <c r="K6" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
@@ -28145,7 +28058,7 @@
       </c>
       <c r="J10" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[モチーフタグ]],"、","|")</f>
-        <v>兎</v>
+        <v>哺乳類</v>
       </c>
       <c r="K10" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
@@ -28361,7 +28274,7 @@
       </c>
       <c r="J14" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[モチーフタグ]],"、","|")</f>
-        <v>兎</v>
+        <v>哺乳類</v>
       </c>
       <c r="K14" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
@@ -29117,7 +29030,7 @@
       </c>
       <c r="J28" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[モチーフタグ]],"、","|")</f>
-        <v>星</v>
+        <v>宇宙・天体</v>
       </c>
       <c r="K28" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
@@ -29981,7 +29894,7 @@
       </c>
       <c r="J44" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[モチーフタグ]],"、","|")</f>
-        <v>狐</v>
+        <v>哺乳類</v>
       </c>
       <c r="K44" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
@@ -30899,7 +30812,7 @@
       </c>
       <c r="J61" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[モチーフタグ]],"、","|")</f>
-        <v>犬</v>
+        <v>哺乳類</v>
       </c>
       <c r="K61" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
@@ -31925,7 +31838,7 @@
       </c>
       <c r="J80" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[モチーフタグ]],"、","|")</f>
-        <v>猫</v>
+        <v>哺乳類</v>
       </c>
       <c r="K80" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
@@ -32033,7 +31946,7 @@
       </c>
       <c r="J82" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[モチーフタグ]],"、","|")</f>
-        <v>宇宙|猫</v>
+        <v>宇宙・天体|哺乳類</v>
       </c>
       <c r="K82" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
@@ -33059,7 +32972,7 @@
       </c>
       <c r="J101" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[モチーフタグ]],"、","|")</f>
-        <v>兎|さくらんぼ</v>
+        <v>哺乳類|植物・自然</v>
       </c>
       <c r="K101" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
@@ -33923,7 +33836,7 @@
       </c>
       <c r="J117" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[モチーフタグ]],"、","|")</f>
-        <v>磁石</v>
+        <v>機械・道具</v>
       </c>
       <c r="K117" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
@@ -35597,7 +35510,7 @@
       </c>
       <c r="J148" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[モチーフタグ]],"、","|")</f>
-        <v>兎</v>
+        <v>哺乳類</v>
       </c>
       <c r="K148" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
@@ -36137,7 +36050,7 @@
       </c>
       <c r="J158" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[モチーフタグ]],"、","|")</f>
-        <v>キーボード</v>
+        <v>機械・道具</v>
       </c>
       <c r="K158" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
@@ -38081,7 +37994,7 @@
       </c>
       <c r="J194" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[モチーフタグ]],"、","|")</f>
-        <v>クラゲ</v>
+        <v>魚類・海洋生物</v>
       </c>
       <c r="K194" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
@@ -40079,7 +39992,7 @@
       </c>
       <c r="J231" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[モチーフタグ]],"、","|")</f>
-        <v>狼</v>
+        <v>哺乳類</v>
       </c>
       <c r="K231" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
@@ -40133,7 +40046,7 @@
       </c>
       <c r="J232" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[モチーフタグ]],"、","|")</f>
-        <v>蛙</v>
+        <v>爬虫類・両生類</v>
       </c>
       <c r="K232" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
@@ -40403,7 +40316,7 @@
       </c>
       <c r="J237" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[モチーフタグ]],"、","|")</f>
-        <v>ギター</v>
+        <v>音楽</v>
       </c>
       <c r="K237" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
@@ -40619,7 +40532,7 @@
       </c>
       <c r="J241" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[モチーフタグ]],"、","|")</f>
-        <v>女郎蜘蛛</v>
+        <v>昆虫・節足動物</v>
       </c>
       <c r="K241" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
@@ -40943,7 +40856,7 @@
       </c>
       <c r="J247" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[モチーフタグ]],"、","|")</f>
-        <v>アイス</v>
+        <v>食べ物</v>
       </c>
       <c r="K247" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
@@ -41159,7 +41072,7 @@
       </c>
       <c r="J251" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[モチーフタグ]],"、","|")</f>
-        <v>蛇</v>
+        <v>爬虫類・両生類</v>
       </c>
       <c r="K251" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
@@ -41213,7 +41126,7 @@
       </c>
       <c r="J252" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[モチーフタグ]],"、","|")</f>
-        <v>カラス</v>
+        <v>鳥類</v>
       </c>
       <c r="K252" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
@@ -41267,7 +41180,7 @@
       </c>
       <c r="J253" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[モチーフタグ]],"、","|")</f>
-        <v>猫</v>
+        <v>哺乳類</v>
       </c>
       <c r="K253" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
@@ -41753,7 +41666,7 @@
       </c>
       <c r="J262" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[モチーフタグ]],"、","|")</f>
-        <v>イラスト</v>
+        <v>芸術・創作</v>
       </c>
       <c r="K262" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
@@ -41823,325 +41736,325 @@
       </c>
     </row>
     <row r="264" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A264" s="35">
+      <c r="A264" s="19">
         <f>テーブル1[[#This Row],[番号]]</f>
         <v>263</v>
       </c>
-      <c r="B264" s="35" t="str">
+      <c r="B264" s="19" t="str">
         <f>テーブル1[[#This Row],[名前]]</f>
         <v>有部音ゴエμ</v>
       </c>
-      <c r="C264" s="35" t="str">
+      <c r="C264" s="19" t="str">
         <f>テーブル1[[#This Row],[なまえ]]</f>
         <v>うぶおん ごえ</v>
       </c>
-      <c r="D264" s="35" t="str">
+      <c r="D264" s="19" t="str">
         <f>テーブル1[[#This Row],[Name]]</f>
         <v>Ubuon Goe</v>
       </c>
-      <c r="E264" s="35" t="str">
+      <c r="E264" s="19" t="str">
         <f>"image/"&amp;テーブル1[[#This Row],[画像]]&amp;".png"</f>
         <v>image/ubuon-goe.png</v>
       </c>
-      <c r="F264" s="35" t="str">
+      <c r="F264" s="19" t="str">
         <f>テーブル1[[#This Row],[リンク]]</f>
         <v>https://nagimachi.wixsite.com/kairikonomachi</v>
       </c>
-      <c r="G264" s="35" t="str">
+      <c r="G264" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[作品タグ]],"、","|")</f>
         <v xml:space="preserve">#返り子の町 </v>
       </c>
-      <c r="H264" s="35" t="str">
+      <c r="H264" s="19" t="str">
         <f>テーブル1[[#This Row],[性別]]&amp;""</f>
         <v>不明</v>
       </c>
-      <c r="I264" s="35" t="str">
+      <c r="I264" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[種族タグ]],"、","|")</f>
         <v>故人|幽霊</v>
       </c>
-      <c r="J264" s="35" t="str">
+      <c r="J264" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[モチーフタグ]],"、","|")</f>
         <v/>
       </c>
-      <c r="K264" s="35" t="str">
+      <c r="K264" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
         <v/>
       </c>
-      <c r="L264" s="35" t="str">
+      <c r="L264" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
         <v>道具</v>
       </c>
-      <c r="M264" s="35" t="str">
+      <c r="M264" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
         <v/>
       </c>
     </row>
     <row r="265" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A265" s="35">
+      <c r="A265" s="19">
         <f>テーブル1[[#This Row],[番号]]</f>
         <v>264</v>
       </c>
-      <c r="B265" s="35" t="str">
+      <c r="B265" s="19" t="str">
         <f>テーブル1[[#This Row],[名前]]</f>
         <v>終歌カツエα</v>
       </c>
-      <c r="C265" s="35" t="str">
+      <c r="C265" s="19" t="str">
         <f>テーブル1[[#This Row],[なまえ]]</f>
         <v>しゅうた かつえ</v>
       </c>
-      <c r="D265" s="35" t="str">
+      <c r="D265" s="19" t="str">
         <f>テーブル1[[#This Row],[Name]]</f>
         <v>Shuta Katsue</v>
       </c>
-      <c r="E265" s="35" t="str">
+      <c r="E265" s="19" t="str">
         <f>"image/"&amp;テーブル1[[#This Row],[画像]]&amp;".png"</f>
         <v>image/shuta-katsue.png</v>
       </c>
-      <c r="F265" s="35" t="str">
+      <c r="F265" s="19" t="str">
         <f>テーブル1[[#This Row],[リンク]]</f>
         <v>https://nagimachi.wixsite.com/kairikonomachi</v>
       </c>
-      <c r="G265" s="35" t="str">
+      <c r="G265" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[作品タグ]],"、","|")</f>
         <v xml:space="preserve">#返り子の町 </v>
       </c>
-      <c r="H265" s="35" t="str">
+      <c r="H265" s="19" t="str">
         <f>テーブル1[[#This Row],[性別]]&amp;""</f>
         <v>女性</v>
       </c>
-      <c r="I265" s="35" t="str">
+      <c r="I265" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[種族タグ]],"、","|")</f>
         <v>人間</v>
       </c>
-      <c r="J265" s="35" t="str">
+      <c r="J265" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[モチーフタグ]],"、","|")</f>
         <v/>
       </c>
-      <c r="K265" s="35" t="str">
+      <c r="K265" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
         <v/>
       </c>
-      <c r="L265" s="35" t="str">
+      <c r="L265" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
         <v>眼部</v>
       </c>
-      <c r="M265" s="35" t="str">
+      <c r="M265" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
         <v/>
       </c>
     </row>
     <row r="266" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A266" s="35">
+      <c r="A266" s="19">
         <f>テーブル1[[#This Row],[番号]]</f>
         <v>265</v>
       </c>
-      <c r="B266" s="35" t="str">
+      <c r="B266" s="19" t="str">
         <f>テーブル1[[#This Row],[名前]]</f>
         <v>鳴音ベルy</v>
       </c>
-      <c r="C266" s="35" t="str">
+      <c r="C266" s="19" t="str">
         <f>テーブル1[[#This Row],[なまえ]]</f>
         <v>なるね べる</v>
       </c>
-      <c r="D266" s="35" t="str">
+      <c r="D266" s="19" t="str">
         <f>テーブル1[[#This Row],[Name]]</f>
         <v>Narune Bell</v>
       </c>
-      <c r="E266" s="35" t="str">
+      <c r="E266" s="19" t="str">
         <f>"image/"&amp;テーブル1[[#This Row],[画像]]&amp;".png"</f>
         <v>image/narune-bell.png</v>
       </c>
-      <c r="F266" s="35" t="str">
+      <c r="F266" s="19" t="str">
         <f>テーブル1[[#This Row],[リンク]]</f>
         <v>https://nagimachi.wixsite.com/kairikonomachi</v>
       </c>
-      <c r="G266" s="35" t="str">
+      <c r="G266" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[作品タグ]],"、","|")</f>
         <v xml:space="preserve">#返り子の町 </v>
       </c>
-      <c r="H266" s="35" t="str">
+      <c r="H266" s="19" t="str">
         <f>テーブル1[[#This Row],[性別]]&amp;""</f>
         <v>不明</v>
       </c>
-      <c r="I266" s="35" t="str">
+      <c r="I266" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[種族タグ]],"、","|")</f>
         <v>機械</v>
       </c>
-      <c r="J266" s="35" t="str">
+      <c r="J266" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[モチーフタグ]],"、","|")</f>
-        <v>ベル</v>
-      </c>
-      <c r="K266" s="35" t="str">
+        <v>音楽</v>
+      </c>
+      <c r="K266" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
         <v/>
       </c>
-      <c r="L266" s="35" t="str">
+      <c r="L266" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
         <v>耳装備</v>
       </c>
-      <c r="M266" s="35" t="str">
+      <c r="M266" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
         <v/>
       </c>
     </row>
     <row r="267" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A267" s="35">
+      <c r="A267" s="19">
         <f>テーブル1[[#This Row],[番号]]</f>
         <v>266</v>
       </c>
-      <c r="B267" s="35" t="str">
+      <c r="B267" s="19" t="str">
         <f>テーブル1[[#This Row],[名前]]</f>
         <v>型式番号α-01</v>
       </c>
-      <c r="C267" s="35" t="str">
+      <c r="C267" s="19" t="str">
         <f>テーブル1[[#This Row],[なまえ]]</f>
         <v>けいしきばんごうα-01</v>
       </c>
-      <c r="D267" s="35" t="str">
+      <c r="D267" s="19" t="str">
         <f>テーブル1[[#This Row],[Name]]</f>
         <v>keishikibangoα-01</v>
       </c>
-      <c r="E267" s="35" t="str">
+      <c r="E267" s="19" t="str">
         <f>"image/"&amp;テーブル1[[#This Row],[画像]]&amp;".png"</f>
         <v>image/keishikibangoα-01.png</v>
       </c>
-      <c r="F267" s="35" t="str">
+      <c r="F267" s="19" t="str">
         <f>テーブル1[[#This Row],[リンク]]</f>
         <v>https://nagimachi.wixsite.com/kairikonomachi</v>
       </c>
-      <c r="G267" s="35" t="str">
+      <c r="G267" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[作品タグ]],"、","|")</f>
         <v xml:space="preserve">#返り子の町 </v>
       </c>
-      <c r="H267" s="35" t="str">
+      <c r="H267" s="19" t="str">
         <f>テーブル1[[#This Row],[性別]]&amp;""</f>
         <v>男性</v>
       </c>
-      <c r="I267" s="35" t="str">
+      <c r="I267" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[種族タグ]],"、","|")</f>
         <v>機械</v>
       </c>
-      <c r="J267" s="35" t="str">
+      <c r="J267" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[モチーフタグ]],"、","|")</f>
-        <v>環境音</v>
-      </c>
-      <c r="K267" s="35" t="str">
+        <v>音楽</v>
+      </c>
+      <c r="K267" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
         <v/>
       </c>
-      <c r="L267" s="35" t="str">
+      <c r="L267" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
         <v>髪飾り|耳装備</v>
       </c>
-      <c r="M267" s="35" t="str">
+      <c r="M267" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
         <v/>
       </c>
     </row>
     <row r="268" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A268" s="35">
+      <c r="A268" s="19">
         <f>テーブル1[[#This Row],[番号]]</f>
         <v>267</v>
       </c>
-      <c r="B268" s="35" t="str">
+      <c r="B268" s="19" t="str">
         <f>テーブル1[[#This Row],[名前]]</f>
         <v>一色スウ</v>
       </c>
-      <c r="C268" s="35" t="str">
+      <c r="C268" s="19" t="str">
         <f>テーブル1[[#This Row],[なまえ]]</f>
         <v>いっしき すう</v>
       </c>
-      <c r="D268" s="35" t="str">
+      <c r="D268" s="19" t="str">
         <f>テーブル1[[#This Row],[Name]]</f>
         <v>Isshiki Su</v>
       </c>
-      <c r="E268" s="35" t="str">
+      <c r="E268" s="19" t="str">
         <f>"image/"&amp;テーブル1[[#This Row],[画像]]&amp;".png"</f>
         <v>image/isshiki-su.png</v>
       </c>
-      <c r="F268" s="35" t="str">
+      <c r="F268" s="19" t="str">
         <f>テーブル1[[#This Row],[リンク]]</f>
         <v>http://utau.wikidot.com/utau:isshiki-suu</v>
       </c>
-      <c r="G268" s="35" t="str">
+      <c r="G268" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[作品タグ]],"、","|")</f>
         <v>#一色スウ</v>
       </c>
-      <c r="H268" s="35" t="str">
+      <c r="H268" s="19" t="str">
         <f>テーブル1[[#This Row],[性別]]&amp;""</f>
         <v>男性</v>
       </c>
-      <c r="I268" s="35" t="str">
+      <c r="I268" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[種族タグ]],"、","|")</f>
         <v>人間</v>
       </c>
-      <c r="J268" s="35" t="str">
+      <c r="J268" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[モチーフタグ]],"、","|")</f>
         <v/>
       </c>
-      <c r="K268" s="35" t="str">
+      <c r="K268" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
         <v>アーティスト</v>
       </c>
-      <c r="L268" s="35" t="str">
+      <c r="L268" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
         <v>耳装備</v>
       </c>
-      <c r="M268" s="35" t="str">
+      <c r="M268" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
         <v/>
       </c>
     </row>
     <row r="269" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A269" s="35">
+      <c r="A269" s="19">
         <f>テーブル1[[#This Row],[番号]]</f>
         <v>268</v>
       </c>
-      <c r="B269" s="35" t="str">
+      <c r="B269" s="19" t="str">
         <f>テーブル1[[#This Row],[名前]]</f>
         <v>亜音サイコ</v>
       </c>
-      <c r="C269" s="35" t="str">
+      <c r="C269" s="19" t="str">
         <f>テーブル1[[#This Row],[なまえ]]</f>
         <v>つぎね さいこ</v>
       </c>
-      <c r="D269" s="35" t="str">
+      <c r="D269" s="19" t="str">
         <f>テーブル1[[#This Row],[Name]]</f>
         <v>Tsugine Saiko</v>
       </c>
-      <c r="E269" s="35" t="str">
+      <c r="E269" s="19" t="str">
         <f>"image/"&amp;テーブル1[[#This Row],[画像]]&amp;".png"</f>
         <v>image/tsugine-saiko.png</v>
       </c>
-      <c r="F269" s="35" t="str">
+      <c r="F269" s="19" t="str">
         <f>テーブル1[[#This Row],[リンク]]</f>
         <v>https://aisupiku.wixsite.com/tsuginesaiko</v>
       </c>
-      <c r="G269" s="35" t="str">
+      <c r="G269" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[作品タグ]],"、","|")</f>
         <v>#亜音サイコ</v>
       </c>
-      <c r="H269" s="35" t="str">
+      <c r="H269" s="19" t="str">
         <f>テーブル1[[#This Row],[性別]]&amp;""</f>
         <v>女性</v>
       </c>
-      <c r="I269" s="35" t="str">
+      <c r="I269" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[種族タグ]],"、","|")</f>
         <v>人間</v>
       </c>
-      <c r="J269" s="35" t="str">
+      <c r="J269" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[モチーフタグ]],"、","|")</f>
         <v/>
       </c>
-      <c r="K269" s="35" t="str">
+      <c r="K269" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
         <v>歌手</v>
       </c>
-      <c r="L269" s="35" t="str">
+      <c r="L269" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
         <v>耳装備|眼部|首装飾</v>
       </c>
-      <c r="M269" s="35" t="str">
+      <c r="M269" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
         <v>メッシュ|尻尾</v>
       </c>

--- a/data/characters.xlsx
+++ b/data/characters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\モノクロビリーフ\外部リンク\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5DF461E-13F8-4AC0-BA8D-9AB69C883BBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3B88F45-495E-446A-8C54-DFD18031B38A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{78CF6334-6F78-4A6F-BD14-CB6FA7AB00CF}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2554" uniqueCount="1316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2555" uniqueCount="1270">
   <si>
     <t>番号</t>
   </si>
@@ -2789,13 +2789,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>科学者</t>
-    <rPh sb="0" eb="3">
-      <t>カガクシャ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>人間</t>
     <rPh sb="0" eb="2">
       <t>ニンゲン</t>
@@ -2803,42 +2796,10 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>眼鏡</t>
-    <rPh sb="0" eb="2">
-      <t>メガネ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>尖耳</t>
-    <rPh sb="0" eb="1">
-      <t>トガ</t>
-    </rPh>
-    <rPh sb="1" eb="2">
-      <t>ミミ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>機械整備士</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ソーイングスタッフ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>地磁気調査</t>
-  </si>
-  <si>
     <t>バーチャル</t>
   </si>
   <si>
     <t>バーチャル</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>メッシュ</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -2849,27 +2810,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>羽</t>
-    <rPh sb="0" eb="1">
-      <t>ハネ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>腹話術師</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>両目隠れ</t>
-    <rPh sb="0" eb="2">
-      <t>リョウメ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>カク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>女性</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -2880,32 +2820,7 @@
     <t>無性別</t>
   </si>
   <si>
-    <t>オッドアイ</t>
-  </si>
-  <si>
-    <t>オッドアイ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>サーカス団員</t>
-    <rPh sb="4" eb="6">
-      <t>ダンイン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>リボン</t>
-  </si>
-  <si>
-    <t>リボン</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ギザ歯</t>
-    <rPh sb="2" eb="3">
-      <t>ハ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>人形</t>
@@ -2915,77 +2830,10 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>片目隠れ</t>
-    <rPh sb="0" eb="2">
-      <t>カタメ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>カク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>執事</t>
-    <rPh sb="0" eb="2">
-      <t>シツジ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>元ヤン</t>
-    <rPh sb="0" eb="1">
-      <t>モト</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>褐色肌</t>
-    <rPh sb="0" eb="2">
-      <t>カッショク</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>ハダ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>吸血鬼</t>
   </si>
   <si>
-    <t>渦巻き目、アホ毛</t>
-  </si>
-  <si>
-    <t>ツートンカラー</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>セクションカラー</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>グラデーションカラー</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>書店員</t>
-    <rPh sb="0" eb="3">
-      <t>ショテンイン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ヘッドセット</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>フィギュア</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>尻尾</t>
-    <rPh sb="0" eb="2">
-      <t>シッポ</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -2996,14 +2844,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>クリエイター</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ヤンキー</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>https://ameutaulii.wixsite.com/telepathycapsule</t>
   </si>
   <si>
@@ -3021,20 +2861,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>司書</t>
-    <rPh sb="0" eb="2">
-      <t>シショ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>黒肌</t>
-    <rPh sb="0" eb="2">
-      <t>クロハダ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>いるやるい</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -3044,10 +2870,6 @@
   </si>
   <si>
     <t>#LCLCみてみて</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>オタク</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -3095,10 +2917,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>吟遊詩人</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>#ムジカの友人たち</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -3150,22 +2968,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ドラゴン</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>モチーフタグ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>司祭</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>アホ毛</t>
-    <rPh sb="2" eb="3">
-      <t>ゲ</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -3176,97 +2979,14 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>アイドル</t>
-  </si>
-  <si>
-    <t>アイドル</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ほくろ</t>
-  </si>
-  <si>
-    <t>ほくろ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>https://kinomihautaimas.wixsite.com/dongurihiroba</t>
     <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ニート</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>魔法使い</t>
-    <rPh sb="0" eb="2">
-      <t>マホウ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>ツカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>人喰い</t>
-    <rPh sb="0" eb="2">
-      <t>ヒトク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>犯罪者</t>
-    <rPh sb="0" eb="3">
-      <t>ハンザイシャ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>警察官</t>
-    <rPh sb="0" eb="3">
-      <t>ケイサツカン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>グラデーションカラー</t>
-  </si>
-  <si>
-    <t>学生</t>
-    <rPh sb="0" eb="2">
-      <t>ガクセイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>サポーター</t>
-  </si>
-  <si>
-    <t>サポーター</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>メッシュ</t>
   </si>
   <si>
     <t>悪魔</t>
     <rPh sb="0" eb="2">
       <t>アクマ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>殺し屋</t>
-    <rPh sb="0" eb="1">
-      <t>コロ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>ヤ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>カウンセラー</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -3280,18 +3000,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>隻眼</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>メイド</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ドッペルゲンガー</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ヘイロー</t>
   </si>
   <si>
@@ -3299,16 +3007,6 @@
   </si>
   <si>
     <t>#廻音怪譚</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>インナーカラー、片目隠れ</t>
-    <rPh sb="8" eb="10">
-      <t>カタメ</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>カク</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -3322,19 +3020,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>角(ツノ)、羽、尻尾</t>
-    <rPh sb="0" eb="1">
-      <t>ツノ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>ハネ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>シッポ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>人間、天使</t>
   </si>
   <si>
@@ -3361,27 +3046,11 @@
     <t>バーチャル、キメラ</t>
   </si>
   <si>
-    <t>両目隠れ、羽</t>
-    <rPh sb="0" eb="2">
-      <t>リョウメ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>カク</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>ハネ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>人間、双子</t>
     <rPh sb="0" eb="2">
       <t>ニンゲン</t>
     </rPh>
     <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>オッドアイ、ほくろ</t>
   </si>
   <si>
     <t>妖精、双子</t>
@@ -3394,29 +3063,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>傷、ほくろ</t>
-    <rPh sb="0" eb="1">
-      <t>キズ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>黒ベタ目、高身長、ボディペイント</t>
-    <rPh sb="0" eb="1">
-      <t>クロ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>メ</t>
-    </rPh>
-    <rPh sb="5" eb="8">
-      <t>コウシンチョウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>サポーター、カウンセラー</t>
-  </si>
-  <si>
     <t>妖怪、長寿</t>
     <rPh sb="0" eb="2">
       <t>ヨウカイ</t>
@@ -3427,67 +3073,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ケモ耳、メッシュ、尻尾</t>
-    <rPh sb="2" eb="3">
-      <t>ミミ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>シッポ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>学生、アイドル</t>
-    <rPh sb="0" eb="2">
-      <t>ガクセイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>インナーカラー、羽</t>
-    <rPh sb="8" eb="9">
-      <t>ハネ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>オッドアイ、アホ毛</t>
-    <rPh sb="8" eb="9">
-      <t>ゲ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>アホ毛、メッシュ</t>
-    <rPh sb="2" eb="3">
-      <t>ゲ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ケモ耳、尻尾</t>
-    <rPh sb="2" eb="3">
-      <t>ミミ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>シッポ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>片目隠れ、火傷、ほくろ</t>
-    <rPh sb="0" eb="2">
-      <t>カタメ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>カク</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ヤケド</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>人間、長寿</t>
     <rPh sb="0" eb="2">
       <t>ニンゲン</t>
@@ -3498,13 +3083,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>魔法使い、手品師</t>
-    <rPh sb="5" eb="8">
-      <t>テジナシ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>天使、長寿</t>
     <rPh sb="0" eb="2">
       <t>テンシ</t>
@@ -3515,42 +3093,9 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>羽、尖耳、ギザ歯</t>
-    <rPh sb="0" eb="1">
-      <t>ハネ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>トガ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>ミミ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>ハ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>メッシュ、尻尾</t>
-    <rPh sb="5" eb="7">
-      <t>シッポ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>故人、ゾンビ</t>
     <rPh sb="0" eb="2">
       <t>コジン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ツートンカラー、片目隠れ</t>
-    <rPh sb="8" eb="10">
-      <t>カタメ</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>カク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -3581,55 +3126,13 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>アホ毛、両目隠れ</t>
-    <rPh sb="2" eb="3">
-      <t>ゲ</t>
-    </rPh>
-    <rPh sb="4" eb="7">
-      <t>リョウメカク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>アホ毛、オッドアイ、特殊肌、尻尾</t>
-    <rPh sb="2" eb="3">
-      <t>ゲ</t>
-    </rPh>
-    <rPh sb="10" eb="13">
-      <t>トクシュハダ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>シッポ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>グラデーションカラー、まろ眉</t>
-  </si>
-  <si>
     <t>灰咲囁</t>
     <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ツートンカラー</t>
   </si>
   <si>
     <t>神</t>
     <rPh sb="0" eb="1">
       <t>カミ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>アホ毛、メッシュ、インナーカラー、両目隠れ</t>
-    <rPh sb="2" eb="3">
-      <t>ゲ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>リョウメ</t>
-    </rPh>
-    <rPh sb="19" eb="20">
-      <t>カク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -3650,19 +3153,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>インナーカラー</t>
-  </si>
-  <si>
-    <t>メッシュ、インナーカラー、両目隠れ、高身長</t>
-    <rPh sb="13" eb="15">
-      <t>リョウメ</t>
-    </rPh>
-    <rPh sb="15" eb="16">
-      <t>カク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>蜘渡紡</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -3690,31 +3180,10 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>メッシュ、両目隠れ</t>
-    <rPh sb="5" eb="7">
-      <t>リョウメ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>カク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>怪異</t>
   </si>
   <si>
     <t>白石朔汰</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>教員</t>
-    <rPh sb="0" eb="2">
-      <t>キョウイン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>グラデーションカラー、オッドアイ</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -3783,10 +3252,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ツートンカラー、オッドアイ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>愛須栗无</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -3851,13 +3316,6 @@
   </si>
   <si>
     <t>https://hatonosuke5.booth.pm</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>家政婦</t>
-    <rPh sb="0" eb="3">
-      <t>カセイフ</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -3875,16 +3333,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ケモ耳、髭、尻尾</t>
-    <rPh sb="4" eb="5">
-      <t>ヒゲ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>シッポ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>蛇川蓮(UTAU)</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -4934,10 +4382,6 @@
     <t>#通音トオ、#utau_tonetoo</t>
   </si>
   <si>
-    <t>刺青、高身長</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>大海クリナ</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -4974,426 +4418,484 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>人型</t>
+  </si>
+  <si>
+    <t>人型</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>#ボタン太の子、#クルミヤキ吉行</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>#大海クリナ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>#みたま_UTAU</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>#みらきぼ11号</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>音夜秋月</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>おとや しゅうき</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Otoya Syuki</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://sikiori.wepage.com</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>#四季折宛郵便</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>夏乃星音</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>なつの せいと</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Natsuno Seito</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>薪宮風季</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>まきみや ふうき</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Makimiya Fuki</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://mohumohuton.web.fc2.com/makimiya/index.html</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>わくねむ すぴか</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Wakunemu Supika</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>わくねむすぴか</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>李音フヱル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>すももね ふえる</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Sumomone Fueru</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://suukedayo.wixsite.com/shiawasefairu</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">#しあわせふぁいる </t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>#わくねむすぴか</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>#薪宮風季</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>終歌カツエα</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>有部音ゴエμ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>うぶおん ごえ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Ubuon Goe</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>しゅうた かつえ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Shuta Katsue</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>鳴音ベルy</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>なるね べる</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Narune Bell</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>型式番号α-01</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>けいしきばんごうα-01</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>keishikibangoα-01</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>一色スウ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>いっしき すう</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Isshiki Su</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>亜音サイコ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>つぎね さいこ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Tsugine Saiko</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://aisupiku.wixsite.com/tsuginesaiko</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>#亜音サイコ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>http://utau.wikidot.com/utau:isshiki-suu</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>#一色スウ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">#返り子の町 </t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://nagimachi.wixsite.com/kairikonomachi</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>髪飾り</t>
+  </si>
+  <si>
+    <t>眼部</t>
+  </si>
+  <si>
+    <t>仮面・マスク</t>
+  </si>
+  <si>
+    <t>耳装備</t>
+  </si>
+  <si>
+    <t>髪飾り、眼部</t>
+  </si>
+  <si>
+    <t>髪飾り、耳装備</t>
+  </si>
+  <si>
+    <t>リボン、髪飾り</t>
+  </si>
+  <si>
+    <t>ヘイロー、髪飾り</t>
+  </si>
+  <si>
+    <t>耳装備、眼部、首装飾</t>
+  </si>
+  <si>
+    <t>装身具、首装飾</t>
+  </si>
+  <si>
+    <t>武器</t>
+  </si>
+  <si>
+    <t>道具</t>
+  </si>
+  <si>
+    <t>ヘイロー、服飾</t>
+  </si>
+  <si>
+    <t>哺乳類</t>
+  </si>
+  <si>
+    <t>鳥類</t>
+  </si>
+  <si>
+    <t>魚類・海洋生物</t>
+  </si>
+  <si>
+    <t>昆虫・節足動物</t>
+  </si>
+  <si>
+    <t>哺乳類、植物・自然</t>
+  </si>
+  <si>
+    <t>食べ物</t>
+  </si>
+  <si>
+    <t>音楽</t>
+  </si>
+  <si>
+    <t>機械・道具</t>
+  </si>
+  <si>
+    <t>芸術・創作</t>
+  </si>
+  <si>
+    <t>耳</t>
+  </si>
+  <si>
+    <t>科学・技術</t>
+  </si>
+  <si>
+    <t>ドラゴン</t>
+  </si>
+  <si>
+    <t>翼</t>
+  </si>
+  <si>
+    <t>目</t>
+  </si>
+  <si>
+    <t>髪色・カラー</t>
+  </si>
+  <si>
+    <t>接客・販売</t>
+  </si>
+  <si>
+    <t>尻尾</t>
+  </si>
+  <si>
+    <t>舞台・パフォーマンス</t>
+  </si>
+  <si>
+    <t>目隠れ</t>
+  </si>
+  <si>
+    <t>創作</t>
+  </si>
+  <si>
+    <t>ヤンキー</t>
+  </si>
+  <si>
+    <t>宗教・ファンタジー</t>
+  </si>
+  <si>
+    <t>芸能</t>
+  </si>
+  <si>
+    <t>模様・装飾</t>
+  </si>
+  <si>
+    <t>宇宙・天体</t>
+  </si>
+  <si>
+    <t>ニート</t>
+  </si>
+  <si>
+    <t>口元</t>
+  </si>
+  <si>
+    <t>裏社会</t>
+  </si>
+  <si>
+    <t>モチーフ</t>
+  </si>
+  <si>
+    <t>医療・支援</t>
+  </si>
+  <si>
+    <t>教育</t>
+  </si>
+  <si>
+    <t>髪型・髪の特徴</t>
+  </si>
+  <si>
+    <t>ドッペルゲンガー</t>
+  </si>
+  <si>
+    <t>治安</t>
+  </si>
+  <si>
+    <t>使用人・家事</t>
+  </si>
+  <si>
+    <t>司書</t>
+  </si>
+  <si>
+    <t>ソーイングスタッフ</t>
+  </si>
+  <si>
+    <t>元ヤン</t>
+  </si>
+  <si>
+    <t>肌</t>
+  </si>
+  <si>
+    <t>オタク</t>
+  </si>
+  <si>
+    <t>爬虫類・両生類</t>
+  </si>
+  <si>
+    <t>ヘッドセット</t>
+  </si>
+  <si>
+    <t>眼鏡</t>
+  </si>
+  <si>
     <t>架空生物</t>
-    <rPh sb="0" eb="4">
-      <t>カクウセイブツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>人型</t>
-  </si>
-  <si>
-    <t>人型</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ケモ耳、片目隠れ、尻尾</t>
-    <rPh sb="4" eb="6">
-      <t>カタメ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>カク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>#ボタン太の子、#クルミヤキ吉行</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>#大海クリナ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>#みたま_UTAU</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>#みらきぼ11号</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>音夜秋月</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>おとや しゅうき</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Otoya Syuki</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>https://sikiori.wepage.com</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>#四季折宛郵便</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>元ヤン、作家</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>夏乃星音</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>なつの せいと</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Natsuno Seito</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>バーテンダー</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>薪宮風季</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>まきみや ふうき</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Makimiya Fuki</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>https://mohumohuton.web.fc2.com/makimiya/index.html</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>わくねむ すぴか</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Wakunemu Supika</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>わくねむすぴか</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>李音フヱル</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>すももね ふえる</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Sumomone Fueru</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>https://suukedayo.wixsite.com/shiawasefairu</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>医者</t>
-    <rPh sb="0" eb="2">
-      <t>イシャ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ヘイロー</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>羽、多眼</t>
-    <rPh sb="0" eb="1">
-      <t>ハネ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>タガン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t xml:space="preserve">#しあわせふぁいる </t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>#わくねむすぴか</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>出血、ほくろ、ギザ歯</t>
-    <rPh sb="0" eb="2">
-      <t>シュッケツ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>ハ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>義眼</t>
-    <rPh sb="0" eb="2">
-      <t>ギガン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>#薪宮風季</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>歌手</t>
-    <rPh sb="0" eb="2">
-      <t>カシュ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>終歌カツエα</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>有部音ゴエμ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>うぶおん ごえ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Ubuon Goe</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>しゅうた かつえ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Shuta Katsue</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>鳴音ベルy</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>なるね べる</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Narune Bell</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>型式番号α-01</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>けいしきばんごうα-01</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>keishikibangoα-01</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>一色スウ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>いっしき すう</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Isshiki Su</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>亜音サイコ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>つぎね さいこ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Tsugine Saiko</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>https://aisupiku.wixsite.com/tsuginesaiko</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>#亜音サイコ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>http://utau.wikidot.com/utau:isshiki-suu</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>#一色スウ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>アーティスト</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t xml:space="preserve">#返り子の町 </t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>https://nagimachi.wixsite.com/kairikonomachi</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>髪飾り</t>
-  </si>
-  <si>
-    <t>眼部</t>
-  </si>
-  <si>
-    <t>眼部</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>仮面・マスク</t>
-  </si>
-  <si>
-    <t>耳装備</t>
-  </si>
-  <si>
-    <t>髪飾り、眼部</t>
-  </si>
-  <si>
-    <t>髪飾り</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>髪飾り、耳装備</t>
-  </si>
-  <si>
-    <t>リボン、髪飾り</t>
-  </si>
-  <si>
-    <t>ヘイロー、髪飾り</t>
-  </si>
-  <si>
-    <t>耳装備、眼部、首装飾</t>
+  </si>
+  <si>
+    <t>髪色・カラー、目隠れ</t>
+  </si>
+  <si>
+    <t>角(つの)、翼、尻尾</t>
+  </si>
+  <si>
+    <t>目、髪型・髪の特徴</t>
+  </si>
+  <si>
+    <t>髪飾り、道具</t>
+  </si>
+  <si>
+    <t>目隠れ、翼</t>
   </si>
   <si>
     <t>ヘイロー、首装飾</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>装身具、首装飾</t>
-  </si>
-  <si>
-    <t>武器</t>
-  </si>
-  <si>
-    <t>武器</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>道具</t>
-  </si>
-  <si>
-    <t>道具</t>
-    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>目、模様・装飾</t>
+  </si>
+  <si>
+    <t>傷・痕、模様・装飾</t>
+  </si>
+  <si>
+    <t>目、体格、模様・装飾</t>
+  </si>
+  <si>
+    <t>治安、元ヤン</t>
+  </si>
+  <si>
+    <t>耳、髪色・カラー、尻尾</t>
+  </si>
+  <si>
+    <t>教育、芸能</t>
+  </si>
+  <si>
+    <t>髪色・カラー、翼</t>
+  </si>
+  <si>
+    <t>髪型・髪の特徴、髪色・カラー</t>
+  </si>
+  <si>
+    <t>耳、尻尾</t>
+  </si>
+  <si>
+    <t>宇宙・天体、哺乳類</t>
+  </si>
+  <si>
+    <t>耳、髭、尻尾</t>
+  </si>
+  <si>
+    <t>目隠れ、傷・痕、模様・装飾</t>
+  </si>
+  <si>
+    <t>宗教・ファンタジー、舞台・パフォーマンス</t>
+  </si>
+  <si>
+    <t>翼、耳、口元</t>
+  </si>
+  <si>
+    <t>髪色・カラー、尻尾</t>
+  </si>
+  <si>
+    <t>髪型・髪の特徴、目隠れ</t>
+  </si>
+  <si>
+    <t>髪型・髪の特徴、目、肌、尻尾</t>
+  </si>
+  <si>
+    <t>傷・痕、模様・装飾、口元</t>
   </si>
   <si>
     <t>耳装備、道具</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>髪飾り、道具</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ヘイロー、服飾</t>
-  </si>
-  <si>
-    <t>ヘイロー、服飾</t>
-    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>髪色・カラー、眉</t>
+  </si>
+  <si>
+    <t>髪色・カラー、目</t>
+  </si>
+  <si>
+    <t>髪型・髪の特徴、髪色・カラー、目隠れ</t>
+  </si>
+  <si>
+    <t>髪色・カラー、目隠れ、体格</t>
   </si>
   <si>
     <t>服飾、道具</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>モチーフ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>警察官、元ヤン</t>
-    <rPh sb="0" eb="3">
-      <t>ケイサツカン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>哺乳類</t>
-  </si>
-  <si>
-    <t>哺乳類</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>鳥類</t>
-  </si>
-  <si>
-    <t>鳥類</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>爬虫類・両生類</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>魚類・海洋生物</t>
-  </si>
-  <si>
-    <t>昆虫・節足動物</t>
-  </si>
-  <si>
-    <t>宇宙・天体</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>宇宙・天体、哺乳類</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>哺乳類、植物・自然</t>
-  </si>
-  <si>
-    <t>食べ物</t>
-  </si>
-  <si>
-    <t>音楽</t>
-  </si>
-  <si>
-    <t>音楽</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>機械・道具</t>
-  </si>
-  <si>
-    <t>機械・道具</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>芸術・創作</t>
+  </si>
+  <si>
+    <t>模様・装飾、体格</t>
+  </si>
+  <si>
+    <t>耳、目隠れ、尻尾</t>
+  </si>
+  <si>
+    <t>元ヤン、創作</t>
+  </si>
+  <si>
+    <t>翼、目</t>
   </si>
 </sst>
 </file>
@@ -7345,7 +6847,7 @@
         <v>663</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>738</v>
+        <v>705</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>664</v>
@@ -7405,10 +6907,10 @@
         <v>460</v>
       </c>
       <c r="D2" s="23" t="s">
-        <v>861</v>
+        <v>776</v>
       </c>
       <c r="E2" s="23" t="s">
-        <v>1029</v>
+        <v>944</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>149</v>
@@ -7423,7 +6925,7 @@
         <v>667</v>
       </c>
       <c r="M2" s="23" t="s">
-        <v>671</v>
+        <v>1201</v>
       </c>
       <c r="N2" s="1" t="s">
         <v>594</v>
@@ -7483,10 +6985,10 @@
         <v>461</v>
       </c>
       <c r="D3" s="23" t="s">
-        <v>862</v>
+        <v>777</v>
       </c>
       <c r="E3" s="23" t="s">
-        <v>1030</v>
+        <v>945</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>129</v>
@@ -7498,16 +7000,16 @@
         <v>661</v>
       </c>
       <c r="I3" s="23" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="K3" s="23" t="s">
-        <v>668</v>
+        <v>1202</v>
       </c>
       <c r="L3" s="23" t="s">
-        <v>1278</v>
+        <v>1180</v>
       </c>
       <c r="M3" s="23" t="s">
-        <v>767</v>
+        <v>1236</v>
       </c>
       <c r="O3" s="1" t="s">
         <v>549</v>
@@ -7579,16 +7081,16 @@
         <v>661</v>
       </c>
       <c r="I4" s="23" t="s">
-        <v>768</v>
+        <v>713</v>
       </c>
       <c r="J4" s="23" t="s">
-        <v>737</v>
+        <v>1203</v>
       </c>
       <c r="K4" s="23" t="s">
-        <v>672</v>
+        <v>1202</v>
       </c>
       <c r="M4" s="23" t="s">
-        <v>769</v>
+        <v>1237</v>
       </c>
       <c r="N4" s="1" t="s">
         <v>595</v>
@@ -7648,10 +7150,10 @@
         <v>142</v>
       </c>
       <c r="D5" s="23" t="s">
-        <v>863</v>
+        <v>778</v>
       </c>
       <c r="E5" s="23" t="s">
-        <v>1031</v>
+        <v>946</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>143</v>
@@ -7663,10 +7165,10 @@
         <v>660</v>
       </c>
       <c r="I5" s="23" t="s">
-        <v>678</v>
+        <v>671</v>
       </c>
       <c r="L5" s="23" t="s">
-        <v>1280</v>
+        <v>1182</v>
       </c>
       <c r="O5" s="1" t="s">
         <v>549</v>
@@ -7723,10 +7225,10 @@
         <v>230</v>
       </c>
       <c r="D6" s="23" t="s">
-        <v>864</v>
+        <v>779</v>
       </c>
       <c r="E6" s="23" t="s">
-        <v>1032</v>
+        <v>947</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>231</v>
@@ -7738,16 +7240,16 @@
         <v>660</v>
       </c>
       <c r="I6" s="23" t="s">
-        <v>1214</v>
+        <v>1127</v>
       </c>
       <c r="J6" s="23" t="s">
-        <v>1303</v>
+        <v>1193</v>
       </c>
       <c r="L6" s="23" t="s">
-        <v>1279</v>
+        <v>1181</v>
       </c>
       <c r="M6" s="23" t="s">
-        <v>679</v>
+        <v>1204</v>
       </c>
       <c r="O6" s="1" t="s">
         <v>549</v>
@@ -7816,10 +7318,10 @@
         <v>113</v>
       </c>
       <c r="H7" s="23" t="s">
-        <v>682</v>
+        <v>672</v>
       </c>
       <c r="I7" s="23" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="O7" s="1" t="s">
         <v>549</v>
@@ -7876,10 +7378,10 @@
         <v>197</v>
       </c>
       <c r="D8" s="23" t="s">
-        <v>865</v>
+        <v>780</v>
       </c>
       <c r="E8" s="23" t="s">
-        <v>1033</v>
+        <v>948</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>198</v>
@@ -7888,16 +7390,16 @@
         <v>199</v>
       </c>
       <c r="H8" s="23" t="s">
-        <v>684</v>
+        <v>674</v>
       </c>
       <c r="I8" s="23" t="s">
-        <v>675</v>
+        <v>669</v>
       </c>
       <c r="L8" s="23" t="s">
-        <v>1278</v>
+        <v>1180</v>
       </c>
       <c r="M8" s="23" t="s">
-        <v>686</v>
+        <v>1205</v>
       </c>
       <c r="N8" s="1" t="s">
         <v>594</v>
@@ -7957,10 +7459,10 @@
         <v>248</v>
       </c>
       <c r="D9" s="23" t="s">
-        <v>866</v>
+        <v>781</v>
       </c>
       <c r="E9" s="23" t="s">
-        <v>1034</v>
+        <v>949</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>249</v>
@@ -7972,10 +7474,10 @@
         <v>660</v>
       </c>
       <c r="I9" s="23" t="s">
-        <v>770</v>
+        <v>714</v>
       </c>
       <c r="M9" s="23" t="s">
-        <v>679</v>
+        <v>1204</v>
       </c>
       <c r="O9" s="1" t="s">
         <v>549</v>
@@ -8032,10 +7534,10 @@
         <v>194</v>
       </c>
       <c r="D10" s="23" t="s">
-        <v>867</v>
+        <v>782</v>
       </c>
       <c r="E10" s="23" t="s">
-        <v>1035</v>
+        <v>950</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>195</v>
@@ -8047,16 +7549,16 @@
         <v>660</v>
       </c>
       <c r="I10" s="23" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="J10" s="23" t="s">
-        <v>1301</v>
+        <v>1192</v>
       </c>
       <c r="L10" s="23" t="s">
-        <v>1276</v>
+        <v>1179</v>
       </c>
       <c r="M10" s="23" t="s">
-        <v>697</v>
+        <v>1238</v>
       </c>
       <c r="O10" s="1" t="s">
         <v>549</v>
@@ -8128,10 +7630,10 @@
         <v>661</v>
       </c>
       <c r="I11" s="23" t="s">
-        <v>771</v>
+        <v>715</v>
       </c>
       <c r="M11" s="23" t="s">
-        <v>698</v>
+        <v>1206</v>
       </c>
       <c r="O11" s="1" t="s">
         <v>549</v>
@@ -8188,10 +7690,10 @@
         <v>234</v>
       </c>
       <c r="D12" s="23" t="s">
-        <v>868</v>
+        <v>783</v>
       </c>
       <c r="E12" s="23" t="s">
-        <v>1036</v>
+        <v>951</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>235</v>
@@ -8203,13 +7705,13 @@
         <v>660</v>
       </c>
       <c r="I12" s="23" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="K12" s="23" t="s">
-        <v>701</v>
+        <v>1207</v>
       </c>
       <c r="L12" s="23" t="s">
-        <v>1278</v>
+        <v>1180</v>
       </c>
       <c r="N12" s="1" t="s">
         <v>631</v>
@@ -8269,10 +7771,10 @@
         <v>274</v>
       </c>
       <c r="D13" s="23" t="s">
-        <v>869</v>
+        <v>784</v>
       </c>
       <c r="E13" s="23" t="s">
-        <v>1037</v>
+        <v>952</v>
       </c>
       <c r="F13" s="23" t="s">
         <v>279</v>
@@ -8284,7 +7786,7 @@
         <v>660</v>
       </c>
       <c r="L13" s="23" t="s">
-        <v>1280</v>
+        <v>1182</v>
       </c>
       <c r="N13" s="1" t="s">
         <v>592</v>
@@ -8359,13 +7861,13 @@
         <v>660</v>
       </c>
       <c r="I14" s="23" t="s">
-        <v>703</v>
+        <v>678</v>
       </c>
       <c r="J14" s="23" t="s">
-        <v>1300</v>
+        <v>1192</v>
       </c>
       <c r="M14" s="23" t="s">
-        <v>704</v>
+        <v>1208</v>
       </c>
       <c r="O14" s="1" t="s">
         <v>549</v>
@@ -8422,10 +7924,10 @@
         <v>233</v>
       </c>
       <c r="D15" s="23" t="s">
-        <v>870</v>
+        <v>785</v>
       </c>
       <c r="E15" s="23" t="s">
-        <v>1038</v>
+        <v>953</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>231</v>
@@ -8437,13 +7939,13 @@
         <v>661</v>
       </c>
       <c r="I15" s="23" t="s">
-        <v>772</v>
+        <v>716</v>
       </c>
       <c r="K15" s="23" t="s">
-        <v>680</v>
+        <v>1209</v>
       </c>
       <c r="M15" s="23" t="s">
-        <v>681</v>
+        <v>1210</v>
       </c>
       <c r="O15" s="1" t="s">
         <v>549</v>
@@ -8515,13 +8017,13 @@
         <v>660</v>
       </c>
       <c r="I16" s="23" t="s">
-        <v>705</v>
+        <v>679</v>
       </c>
       <c r="K16" s="23" t="s">
-        <v>706</v>
+        <v>1211</v>
       </c>
       <c r="M16" s="23" t="s">
-        <v>677</v>
+        <v>1206</v>
       </c>
       <c r="N16" s="1" t="s">
         <v>594</v>
@@ -8581,10 +8083,10 @@
         <v>593</v>
       </c>
       <c r="D17" s="23" t="s">
-        <v>871</v>
+        <v>786</v>
       </c>
       <c r="E17" s="23" t="s">
-        <v>1039</v>
+        <v>954</v>
       </c>
       <c r="F17" s="15" t="s">
         <v>611</v>
@@ -8593,13 +8095,13 @@
         <v>276</v>
       </c>
       <c r="H17" s="23" t="s">
-        <v>684</v>
+        <v>674</v>
       </c>
       <c r="I17" s="23" t="s">
-        <v>813</v>
+        <v>734</v>
       </c>
       <c r="L17" s="23" t="s">
-        <v>1292</v>
+        <v>1190</v>
       </c>
       <c r="N17" s="1" t="s">
         <v>594</v>
@@ -8659,10 +8161,10 @@
         <v>277</v>
       </c>
       <c r="D18" s="23" t="s">
-        <v>872</v>
+        <v>787</v>
       </c>
       <c r="E18" s="23" t="s">
-        <v>1040</v>
+        <v>955</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>611</v>
@@ -8671,16 +8173,16 @@
         <v>276</v>
       </c>
       <c r="H18" s="23" t="s">
-        <v>684</v>
+        <v>674</v>
       </c>
       <c r="I18" s="23" t="s">
-        <v>813</v>
+        <v>734</v>
       </c>
       <c r="K18" s="23" t="s">
-        <v>707</v>
+        <v>1212</v>
       </c>
       <c r="L18" s="23" t="s">
-        <v>1292</v>
+        <v>1190</v>
       </c>
       <c r="N18" s="1" t="s">
         <v>594</v>
@@ -8743,10 +8245,10 @@
         <v>38</v>
       </c>
       <c r="E19" s="23" t="s">
-        <v>1041</v>
+        <v>956</v>
       </c>
       <c r="F19" s="15" t="s">
-        <v>708</v>
+        <v>680</v>
       </c>
       <c r="G19" s="23" t="s">
         <v>39</v>
@@ -8755,7 +8257,7 @@
         <v>660</v>
       </c>
       <c r="L19" s="23" t="s">
-        <v>1294</v>
+        <v>1239</v>
       </c>
       <c r="N19" s="1" t="s">
         <v>595</v>
@@ -8815,10 +8317,10 @@
         <v>102</v>
       </c>
       <c r="D20" s="23" t="s">
-        <v>873</v>
+        <v>788</v>
       </c>
       <c r="E20" s="23" t="s">
-        <v>1042</v>
+        <v>957</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>103</v>
@@ -8827,13 +8329,13 @@
         <v>104</v>
       </c>
       <c r="H20" s="23" t="s">
-        <v>683</v>
+        <v>673</v>
       </c>
       <c r="I20" s="23" t="s">
-        <v>773</v>
+        <v>717</v>
       </c>
       <c r="L20" s="23" t="s">
-        <v>1280</v>
+        <v>1182</v>
       </c>
       <c r="O20" s="1" t="s">
         <v>549</v>
@@ -8890,10 +8392,10 @@
         <v>105</v>
       </c>
       <c r="D21" s="23" t="s">
-        <v>874</v>
+        <v>789</v>
       </c>
       <c r="E21" s="23" t="s">
-        <v>1043</v>
+        <v>958</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>103</v>
@@ -8902,10 +8404,10 @@
         <v>106</v>
       </c>
       <c r="H21" s="23" t="s">
-        <v>683</v>
+        <v>673</v>
       </c>
       <c r="I21" s="23" t="s">
-        <v>773</v>
+        <v>717</v>
       </c>
       <c r="O21" s="1" t="s">
         <v>549</v>
@@ -8962,10 +8464,10 @@
         <v>517</v>
       </c>
       <c r="D22" s="23" t="s">
-        <v>875</v>
+        <v>790</v>
       </c>
       <c r="E22" s="23" t="s">
-        <v>1044</v>
+        <v>959</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>329</v>
@@ -8977,10 +8479,10 @@
         <v>660</v>
       </c>
       <c r="I22" s="23" t="s">
-        <v>710</v>
+        <v>682</v>
       </c>
       <c r="M22" s="23" t="s">
-        <v>774</v>
+        <v>1240</v>
       </c>
       <c r="N22" s="1" t="s">
         <v>594</v>
@@ -9055,16 +8557,16 @@
         <v>661</v>
       </c>
       <c r="I23" s="23" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="K23" s="23" t="s">
-        <v>739</v>
+        <v>1213</v>
       </c>
       <c r="L23" s="23" t="s">
-        <v>1287</v>
+        <v>1241</v>
       </c>
       <c r="M23" s="23" t="s">
-        <v>692</v>
+        <v>1210</v>
       </c>
       <c r="N23" s="1" t="s">
         <v>631</v>
@@ -9136,13 +8638,13 @@
         <v>199</v>
       </c>
       <c r="H24" s="23" t="s">
-        <v>683</v>
+        <v>673</v>
       </c>
       <c r="I24" s="23" t="s">
-        <v>775</v>
+        <v>718</v>
       </c>
       <c r="L24" s="23" t="s">
-        <v>1278</v>
+        <v>1180</v>
       </c>
       <c r="N24" s="1" t="s">
         <v>594</v>
@@ -9217,13 +8719,13 @@
         <v>661</v>
       </c>
       <c r="I25" s="23" t="s">
-        <v>678</v>
+        <v>671</v>
       </c>
       <c r="L25" s="23" t="s">
-        <v>1281</v>
+        <v>1183</v>
       </c>
       <c r="M25" s="23" t="s">
-        <v>692</v>
+        <v>1210</v>
       </c>
       <c r="N25" s="1" t="s">
         <v>631</v>
@@ -9283,10 +8785,10 @@
         <v>85</v>
       </c>
       <c r="D26" s="23" t="s">
-        <v>876</v>
+        <v>791</v>
       </c>
       <c r="E26" s="23" t="s">
-        <v>1045</v>
+        <v>960</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>86</v>
@@ -9298,13 +8800,13 @@
         <v>660</v>
       </c>
       <c r="I26" s="23" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="K26" s="23" t="s">
-        <v>743</v>
+        <v>1214</v>
       </c>
       <c r="M26" s="23" t="s">
-        <v>776</v>
+        <v>1242</v>
       </c>
       <c r="N26" s="1" t="s">
         <v>631</v>
@@ -9364,10 +8866,10 @@
         <v>88</v>
       </c>
       <c r="D27" s="23" t="s">
-        <v>877</v>
+        <v>792</v>
       </c>
       <c r="E27" s="23" t="s">
-        <v>1046</v>
+        <v>961</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>86</v>
@@ -9379,13 +8881,13 @@
         <v>661</v>
       </c>
       <c r="I27" s="23" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="K27" s="23" t="s">
-        <v>743</v>
+        <v>1214</v>
       </c>
       <c r="M27" s="23" t="s">
-        <v>745</v>
+        <v>1215</v>
       </c>
       <c r="N27" s="1" t="s">
         <v>631</v>
@@ -9445,28 +8947,28 @@
         <v>46</v>
       </c>
       <c r="D28" s="23" t="s">
-        <v>878</v>
+        <v>793</v>
       </c>
       <c r="E28" s="23" t="s">
-        <v>1047</v>
+        <v>962</v>
       </c>
       <c r="F28" s="15" t="s">
-        <v>746</v>
+        <v>707</v>
       </c>
       <c r="G28" s="23" t="s">
         <v>47</v>
       </c>
       <c r="H28" s="23" t="s">
-        <v>683</v>
+        <v>673</v>
       </c>
       <c r="I28" s="23" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="J28" s="23" t="s">
-        <v>1307</v>
+        <v>1216</v>
       </c>
       <c r="K28" s="23" t="s">
-        <v>747</v>
+        <v>1217</v>
       </c>
       <c r="N28" s="1" t="s">
         <v>594</v>
@@ -9526,10 +9028,10 @@
         <v>520</v>
       </c>
       <c r="D29" s="23" t="s">
-        <v>879</v>
+        <v>794</v>
       </c>
       <c r="E29" s="23" t="s">
-        <v>1048</v>
+        <v>963</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>90</v>
@@ -9541,7 +9043,7 @@
         <v>660</v>
       </c>
       <c r="I29" s="23" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="O29" s="1" t="s">
         <v>549</v>
@@ -9598,10 +9100,10 @@
         <v>521</v>
       </c>
       <c r="D30" s="23" t="s">
-        <v>880</v>
+        <v>795</v>
       </c>
       <c r="E30" s="23" t="s">
-        <v>1049</v>
+        <v>964</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>90</v>
@@ -9610,13 +9112,13 @@
         <v>91</v>
       </c>
       <c r="H30" s="23" t="s">
-        <v>684</v>
+        <v>674</v>
       </c>
       <c r="I30" s="23" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="L30" s="23" t="s">
-        <v>1289</v>
+        <v>1189</v>
       </c>
       <c r="O30" s="1" t="s">
         <v>549</v>
@@ -9688,7 +9190,7 @@
         <v>660</v>
       </c>
       <c r="I31" s="23" t="s">
-        <v>709</v>
+        <v>681</v>
       </c>
       <c r="O31" s="1" t="s">
         <v>549</v>
@@ -9745,10 +9247,10 @@
         <v>523</v>
       </c>
       <c r="D32" s="23" t="s">
-        <v>881</v>
+        <v>796</v>
       </c>
       <c r="E32" s="23" t="s">
-        <v>1050</v>
+        <v>965</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>198</v>
@@ -9760,16 +9262,16 @@
         <v>660</v>
       </c>
       <c r="I32" s="23" t="s">
-        <v>777</v>
+        <v>719</v>
       </c>
       <c r="K32" s="23" t="s">
-        <v>687</v>
+        <v>1209</v>
       </c>
       <c r="L32" s="23" t="s">
-        <v>689</v>
+        <v>675</v>
       </c>
       <c r="M32" s="23" t="s">
-        <v>690</v>
+        <v>1218</v>
       </c>
       <c r="N32" s="1" t="s">
         <v>594</v>
@@ -9829,10 +9331,10 @@
         <v>175</v>
       </c>
       <c r="D33" s="23" t="s">
-        <v>882</v>
+        <v>797</v>
       </c>
       <c r="E33" s="23" t="s">
-        <v>1051</v>
+        <v>966</v>
       </c>
       <c r="F33" s="15" t="s">
         <v>176</v>
@@ -9844,16 +9346,16 @@
         <v>661</v>
       </c>
       <c r="I33" s="23" t="s">
-        <v>805</v>
+        <v>728</v>
       </c>
       <c r="K33" s="23" t="s">
-        <v>750</v>
+        <v>1219</v>
       </c>
       <c r="L33" s="23" t="s">
-        <v>1289</v>
+        <v>1189</v>
       </c>
       <c r="M33" s="23" t="s">
-        <v>778</v>
+        <v>1243</v>
       </c>
       <c r="N33" s="1" t="s">
         <v>631</v>
@@ -9913,13 +9415,13 @@
         <v>48</v>
       </c>
       <c r="D34" s="23" t="s">
-        <v>883</v>
+        <v>798</v>
       </c>
       <c r="E34" s="23" t="s">
-        <v>1052</v>
+        <v>967</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>746</v>
+        <v>707</v>
       </c>
       <c r="G34" s="23" t="s">
         <v>47</v>
@@ -9928,13 +9430,13 @@
         <v>660</v>
       </c>
       <c r="I34" s="23" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="L34" s="23" t="s">
-        <v>1288</v>
+        <v>1188</v>
       </c>
       <c r="M34" s="23" t="s">
-        <v>779</v>
+        <v>1244</v>
       </c>
       <c r="N34" s="1" t="s">
         <v>594</v>
@@ -9994,10 +9496,10 @@
         <v>524</v>
       </c>
       <c r="D35" s="23" t="s">
-        <v>884</v>
+        <v>799</v>
       </c>
       <c r="E35" s="23" t="s">
-        <v>1053</v>
+        <v>968</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>246</v>
@@ -10009,16 +9511,16 @@
         <v>661</v>
       </c>
       <c r="I35" s="23" t="s">
-        <v>771</v>
+        <v>715</v>
       </c>
       <c r="K35" s="23" t="s">
-        <v>749</v>
+        <v>1219</v>
       </c>
       <c r="L35" s="23" t="s">
-        <v>1298</v>
+        <v>1220</v>
       </c>
       <c r="M35" s="23" t="s">
-        <v>681</v>
+        <v>1210</v>
       </c>
       <c r="O35" s="1" t="s">
         <v>549</v>
@@ -10075,10 +9577,10 @@
         <v>178</v>
       </c>
       <c r="D36" s="23" t="s">
-        <v>885</v>
+        <v>800</v>
       </c>
       <c r="E36" s="23" t="s">
-        <v>1054</v>
+        <v>969</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>176</v>
@@ -10090,16 +9592,16 @@
         <v>661</v>
       </c>
       <c r="I36" s="23" t="s">
-        <v>741</v>
+        <v>706</v>
       </c>
       <c r="K36" s="23" t="s">
-        <v>1299</v>
+        <v>1245</v>
       </c>
       <c r="L36" s="23" t="s">
-        <v>1281</v>
+        <v>1183</v>
       </c>
       <c r="M36" s="23" t="s">
-        <v>752</v>
+        <v>1206</v>
       </c>
       <c r="N36" s="1" t="s">
         <v>631</v>
@@ -10159,28 +9661,28 @@
         <v>71</v>
       </c>
       <c r="D37" s="23" t="s">
-        <v>886</v>
+        <v>801</v>
       </c>
       <c r="E37" s="23" t="s">
-        <v>1055</v>
+        <v>970</v>
       </c>
       <c r="F37" s="15" t="s">
         <v>72</v>
       </c>
       <c r="G37" s="23" t="s">
-        <v>1200</v>
+        <v>1115</v>
       </c>
       <c r="H37" s="23" t="s">
         <v>661</v>
       </c>
       <c r="I37" s="23" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="K37" s="23" t="s">
-        <v>742</v>
+        <v>1214</v>
       </c>
       <c r="L37" s="23" t="s">
-        <v>1276</v>
+        <v>1179</v>
       </c>
       <c r="N37" s="1" t="s">
         <v>594</v>
@@ -10240,10 +9742,10 @@
         <v>525</v>
       </c>
       <c r="D38" s="23" t="s">
-        <v>887</v>
+        <v>802</v>
       </c>
       <c r="E38" s="23" t="s">
-        <v>1056</v>
+        <v>971</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>167</v>
@@ -10255,13 +9757,13 @@
         <v>660</v>
       </c>
       <c r="I38" s="23" t="s">
-        <v>678</v>
+        <v>671</v>
       </c>
       <c r="K38" s="23" t="s">
-        <v>780</v>
+        <v>1221</v>
       </c>
       <c r="M38" s="23" t="s">
-        <v>756</v>
+        <v>1206</v>
       </c>
       <c r="N38" s="1" t="s">
         <v>631</v>
@@ -10336,7 +9838,7 @@
         <v>661</v>
       </c>
       <c r="I39" s="23" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="O39" s="1" t="s">
         <v>549</v>
@@ -10408,10 +9910,10 @@
         <v>661</v>
       </c>
       <c r="I40" s="23" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="K40" s="23" t="s">
-        <v>753</v>
+        <v>1222</v>
       </c>
       <c r="N40" s="1" t="s">
         <v>595</v>
@@ -10471,10 +9973,10 @@
         <v>107</v>
       </c>
       <c r="D41" s="23" t="s">
-        <v>888</v>
+        <v>803</v>
       </c>
       <c r="E41" s="23" t="s">
-        <v>1057</v>
+        <v>972</v>
       </c>
       <c r="F41" s="30" t="s">
         <v>108</v>
@@ -10486,7 +9988,7 @@
         <v>661</v>
       </c>
       <c r="I41" s="23" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="O41" s="1" t="s">
         <v>549</v>
@@ -10558,13 +10060,13 @@
         <v>660</v>
       </c>
       <c r="I42" s="23" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="L42" s="23" t="s">
-        <v>1296</v>
+        <v>1191</v>
       </c>
       <c r="M42" s="23" t="s">
-        <v>740</v>
+        <v>1223</v>
       </c>
       <c r="N42" s="1" t="s">
         <v>631</v>
@@ -10639,7 +10141,7 @@
         <v>661</v>
       </c>
       <c r="I43" s="23" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="N43" s="1" t="s">
         <v>631</v>
@@ -10699,10 +10201,10 @@
         <v>526</v>
       </c>
       <c r="D44" s="23" t="s">
-        <v>889</v>
+        <v>804</v>
       </c>
       <c r="E44" s="23" t="s">
-        <v>1058</v>
+        <v>973</v>
       </c>
       <c r="F44" s="27" t="s">
         <v>57</v>
@@ -10714,13 +10216,13 @@
         <v>661</v>
       </c>
       <c r="I44" s="23" t="s">
-        <v>781</v>
+        <v>720</v>
       </c>
       <c r="J44" s="23" t="s">
-        <v>1301</v>
+        <v>1192</v>
       </c>
       <c r="M44" s="23" t="s">
-        <v>782</v>
+        <v>1246</v>
       </c>
       <c r="N44" s="1" t="s">
         <v>595</v>
@@ -10795,13 +10297,13 @@
         <v>660</v>
       </c>
       <c r="I45" s="23" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="K45" s="23" t="s">
-        <v>753</v>
+        <v>1222</v>
       </c>
       <c r="L45" s="23" t="s">
-        <v>1279</v>
+        <v>1181</v>
       </c>
       <c r="O45" s="1" t="s">
         <v>549</v>
@@ -10858,10 +10360,10 @@
         <v>528</v>
       </c>
       <c r="D46" s="23" t="s">
-        <v>890</v>
+        <v>805</v>
       </c>
       <c r="E46" s="23" t="s">
-        <v>1059</v>
+        <v>974</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>66</v>
@@ -10873,13 +10375,13 @@
         <v>660</v>
       </c>
       <c r="I46" s="23" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="K46" s="23" t="s">
-        <v>783</v>
+        <v>1247</v>
       </c>
       <c r="L46" s="23" t="s">
-        <v>1284</v>
+        <v>1185</v>
       </c>
       <c r="N46" s="1" t="s">
         <v>594</v>
@@ -10939,10 +10441,10 @@
         <v>529</v>
       </c>
       <c r="D47" s="23" t="s">
-        <v>891</v>
+        <v>806</v>
       </c>
       <c r="E47" s="23" t="s">
-        <v>1060</v>
+        <v>975</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>158</v>
@@ -11020,13 +10522,13 @@
         <v>660</v>
       </c>
       <c r="I48" s="23" t="s">
-        <v>757</v>
+        <v>708</v>
       </c>
       <c r="L48" s="23" t="s">
-        <v>1282</v>
+        <v>1179</v>
       </c>
       <c r="M48" s="23" t="s">
-        <v>784</v>
+        <v>1248</v>
       </c>
       <c r="N48" s="1" t="s">
         <v>631</v>
@@ -11218,10 +10720,10 @@
         <v>532</v>
       </c>
       <c r="D51" s="23" t="s">
-        <v>892</v>
+        <v>807</v>
       </c>
       <c r="E51" s="23" t="s">
-        <v>1061</v>
+        <v>976</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>262</v>
@@ -11284,10 +10786,10 @@
         <v>533</v>
       </c>
       <c r="D52" s="23" t="s">
-        <v>893</v>
+        <v>808</v>
       </c>
       <c r="E52" s="23" t="s">
-        <v>1062</v>
+        <v>977</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>238</v>
@@ -11365,10 +10867,10 @@
         <v>661</v>
       </c>
       <c r="I53" s="23" t="s">
-        <v>678</v>
+        <v>671</v>
       </c>
       <c r="K53" s="23" t="s">
-        <v>754</v>
+        <v>1221</v>
       </c>
       <c r="N53" s="1" t="s">
         <v>631</v>
@@ -11428,10 +10930,10 @@
         <v>535</v>
       </c>
       <c r="D54" s="23" t="s">
-        <v>894</v>
+        <v>809</v>
       </c>
       <c r="E54" s="23" t="s">
-        <v>1063</v>
+        <v>978</v>
       </c>
       <c r="F54" s="15" t="s">
         <v>662</v>
@@ -11512,13 +11014,13 @@
         <v>660</v>
       </c>
       <c r="I55" s="28" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="J55" s="28"/>
       <c r="K55" s="28"/>
       <c r="L55" s="28"/>
       <c r="M55" s="28" t="s">
-        <v>785</v>
+        <v>1238</v>
       </c>
       <c r="N55" s="1" t="s">
         <v>631</v>
@@ -11710,10 +11212,10 @@
         <v>538</v>
       </c>
       <c r="D58" s="23" t="s">
-        <v>895</v>
+        <v>810</v>
       </c>
       <c r="E58" s="23" t="s">
-        <v>1064</v>
+        <v>979</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>43</v>
@@ -11779,10 +11281,10 @@
         <v>539</v>
       </c>
       <c r="D59" s="23" t="s">
-        <v>896</v>
+        <v>811</v>
       </c>
       <c r="E59" s="23" t="s">
-        <v>1065</v>
+        <v>980</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>43</v>
@@ -11848,10 +11350,10 @@
         <v>188</v>
       </c>
       <c r="D60" s="23" t="s">
-        <v>897</v>
+        <v>812</v>
       </c>
       <c r="E60" s="23" t="s">
-        <v>1066</v>
+        <v>981</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>189</v>
@@ -11914,10 +11416,10 @@
         <v>22</v>
       </c>
       <c r="D61" s="23" t="s">
-        <v>898</v>
+        <v>813</v>
       </c>
       <c r="E61" s="23" t="s">
-        <v>1067</v>
+        <v>982</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>20</v>
@@ -11929,10 +11431,10 @@
         <v>661</v>
       </c>
       <c r="I61" s="23" t="s">
-        <v>760</v>
+        <v>709</v>
       </c>
       <c r="J61" s="23" t="s">
-        <v>1301</v>
+        <v>1192</v>
       </c>
       <c r="N61" s="1" t="s">
         <v>595</v>
@@ -11992,10 +11494,10 @@
         <v>563</v>
       </c>
       <c r="D62" s="23" t="s">
-        <v>899</v>
+        <v>814</v>
       </c>
       <c r="E62" s="23" t="s">
-        <v>1068</v>
+        <v>983</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>191</v>
@@ -12058,34 +11560,34 @@
         <v>470</v>
       </c>
       <c r="D63" s="23" t="s">
-        <v>900</v>
+        <v>815</v>
       </c>
       <c r="E63" s="23" t="s">
-        <v>1069</v>
+        <v>984</v>
       </c>
       <c r="F63" s="15" t="s">
         <v>122</v>
       </c>
       <c r="G63" s="24" t="s">
-        <v>766</v>
+        <v>712</v>
       </c>
       <c r="H63" s="23" t="s">
         <v>661</v>
       </c>
       <c r="I63" s="23" t="s">
-        <v>815</v>
+        <v>735</v>
       </c>
       <c r="J63" s="23" t="s">
-        <v>763</v>
+        <v>1224</v>
       </c>
       <c r="K63" s="23" t="s">
-        <v>753</v>
+        <v>1222</v>
       </c>
       <c r="L63" s="24" t="s">
-        <v>1280</v>
+        <v>1182</v>
       </c>
       <c r="M63" s="23" t="s">
-        <v>767</v>
+        <v>1236</v>
       </c>
       <c r="N63" s="1" t="s">
         <v>631</v>
@@ -12145,10 +11647,10 @@
         <v>564</v>
       </c>
       <c r="D64" s="23" t="s">
-        <v>901</v>
+        <v>816</v>
       </c>
       <c r="E64" s="23" t="s">
-        <v>1070</v>
+        <v>985</v>
       </c>
       <c r="F64" s="26" t="s">
         <v>55</v>
@@ -12229,10 +11731,10 @@
         <v>661</v>
       </c>
       <c r="I65" s="23" t="s">
-        <v>678</v>
+        <v>671</v>
       </c>
       <c r="L65" s="23" t="s">
-        <v>1280</v>
+        <v>1182</v>
       </c>
       <c r="N65" s="1" t="s">
         <v>594</v>
@@ -12292,10 +11794,10 @@
         <v>566</v>
       </c>
       <c r="D66" s="23" t="s">
-        <v>902</v>
+        <v>817</v>
       </c>
       <c r="E66" s="23" t="s">
-        <v>1071</v>
+        <v>986</v>
       </c>
       <c r="F66" s="27" t="s">
         <v>57</v>
@@ -12307,10 +11809,10 @@
         <v>660</v>
       </c>
       <c r="I66" s="23" t="s">
-        <v>696</v>
+        <v>677</v>
       </c>
       <c r="M66" s="23" t="s">
-        <v>786</v>
+        <v>1249</v>
       </c>
       <c r="N66" s="1" t="s">
         <v>595</v>
@@ -12370,10 +11872,10 @@
         <v>567</v>
       </c>
       <c r="D67" s="23" t="s">
-        <v>903</v>
+        <v>818</v>
       </c>
       <c r="E67" s="23" t="s">
-        <v>1072</v>
+        <v>987</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>272</v>
@@ -12436,10 +11938,10 @@
         <v>568</v>
       </c>
       <c r="D68" s="23" t="s">
-        <v>904</v>
+        <v>819</v>
       </c>
       <c r="E68" s="23" t="s">
-        <v>1073</v>
+        <v>988</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>158</v>
@@ -12502,10 +12004,10 @@
         <v>45</v>
       </c>
       <c r="D69" s="23" t="s">
-        <v>905</v>
+        <v>820</v>
       </c>
       <c r="E69" s="23" t="s">
-        <v>1074</v>
+        <v>989</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>43</v>
@@ -12571,10 +12073,10 @@
         <v>569</v>
       </c>
       <c r="D70" s="23" t="s">
-        <v>906</v>
+        <v>821</v>
       </c>
       <c r="E70" s="23" t="s">
-        <v>1075</v>
+        <v>990</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>262</v>
@@ -12637,10 +12139,10 @@
         <v>570</v>
       </c>
       <c r="D71" s="23" t="s">
-        <v>907</v>
+        <v>822</v>
       </c>
       <c r="E71" s="23" t="s">
-        <v>1076</v>
+        <v>991</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>272</v>
@@ -12703,10 +12205,10 @@
         <v>571</v>
       </c>
       <c r="D72" s="23" t="s">
-        <v>908</v>
+        <v>823</v>
       </c>
       <c r="E72" s="23" t="s">
-        <v>1077</v>
+        <v>992</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>224</v>
@@ -12769,10 +12271,10 @@
         <v>572</v>
       </c>
       <c r="D73" s="23" t="s">
-        <v>909</v>
+        <v>824</v>
       </c>
       <c r="E73" s="23" t="s">
-        <v>1078</v>
+        <v>993</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>224</v>
@@ -12835,10 +12337,10 @@
         <v>573</v>
       </c>
       <c r="D74" s="23" t="s">
-        <v>910</v>
+        <v>825</v>
       </c>
       <c r="E74" s="23" t="s">
-        <v>1079</v>
+        <v>994</v>
       </c>
       <c r="F74" s="2" t="s">
         <v>123</v>
@@ -12901,10 +12403,10 @@
         <v>40</v>
       </c>
       <c r="D75" s="23" t="s">
-        <v>911</v>
+        <v>826</v>
       </c>
       <c r="E75" s="23" t="s">
-        <v>1080</v>
+        <v>995</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>41</v>
@@ -12985,10 +12487,10 @@
         <v>660</v>
       </c>
       <c r="I76" s="23" t="s">
-        <v>691</v>
+        <v>676</v>
       </c>
       <c r="L76" s="23" t="s">
-        <v>688</v>
+        <v>675</v>
       </c>
       <c r="N76" s="1" t="s">
         <v>594</v>
@@ -13114,10 +12616,10 @@
         <v>29</v>
       </c>
       <c r="D78" s="23" t="s">
-        <v>912</v>
+        <v>827</v>
       </c>
       <c r="E78" s="23" t="s">
-        <v>1081</v>
+        <v>996</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>30</v>
@@ -13183,10 +12685,10 @@
         <v>193</v>
       </c>
       <c r="D79" s="23" t="s">
-        <v>913</v>
+        <v>828</v>
       </c>
       <c r="E79" s="23" t="s">
-        <v>1082</v>
+        <v>997</v>
       </c>
       <c r="F79" s="2" t="s">
         <v>191</v>
@@ -13249,10 +12751,10 @@
         <v>24</v>
       </c>
       <c r="D80" s="23" t="s">
-        <v>914</v>
+        <v>829</v>
       </c>
       <c r="E80" s="23" t="s">
-        <v>1083</v>
+        <v>998</v>
       </c>
       <c r="F80" s="2" t="s">
         <v>20</v>
@@ -13264,16 +12766,16 @@
         <v>660</v>
       </c>
       <c r="I80" s="23" t="s">
-        <v>1214</v>
+        <v>1127</v>
       </c>
       <c r="J80" s="23" t="s">
-        <v>1301</v>
+        <v>1192</v>
       </c>
       <c r="L80" s="23" t="s">
-        <v>688</v>
+        <v>675</v>
       </c>
       <c r="M80" s="23" t="s">
-        <v>787</v>
+        <v>1250</v>
       </c>
       <c r="N80" s="1" t="s">
         <v>595</v>
@@ -13333,10 +12835,10 @@
         <v>134</v>
       </c>
       <c r="D81" s="23" t="s">
-        <v>915</v>
+        <v>830</v>
       </c>
       <c r="E81" s="23" t="s">
-        <v>1084</v>
+        <v>999</v>
       </c>
       <c r="F81" s="2" t="s">
         <v>135</v>
@@ -13411,16 +12913,16 @@
         <v>183</v>
       </c>
       <c r="H82" s="23" t="s">
-        <v>684</v>
+        <v>674</v>
       </c>
       <c r="I82" s="23" t="s">
-        <v>741</v>
+        <v>706</v>
       </c>
       <c r="J82" s="23" t="s">
-        <v>1308</v>
+        <v>1251</v>
       </c>
       <c r="M82" s="23" t="s">
-        <v>854</v>
+        <v>1252</v>
       </c>
       <c r="N82" s="1" t="s">
         <v>631</v>
@@ -13480,10 +12982,10 @@
         <v>226</v>
       </c>
       <c r="D83" s="23" t="s">
-        <v>916</v>
+        <v>831</v>
       </c>
       <c r="E83" s="23" t="s">
-        <v>1085</v>
+        <v>1000</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>227</v>
@@ -13546,10 +13048,10 @@
         <v>229</v>
       </c>
       <c r="D84" s="23" t="s">
-        <v>917</v>
+        <v>832</v>
       </c>
       <c r="E84" s="23" t="s">
-        <v>1086</v>
+        <v>1001</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>227</v>
@@ -13678,10 +13180,10 @@
         <v>278</v>
       </c>
       <c r="D86" s="23" t="s">
-        <v>918</v>
+        <v>833</v>
       </c>
       <c r="E86" s="23" t="s">
-        <v>1087</v>
+        <v>1002</v>
       </c>
       <c r="F86" s="23" t="s">
         <v>279</v>
@@ -13751,7 +13253,7 @@
         <v>205</v>
       </c>
       <c r="E87" s="23" t="s">
-        <v>1088</v>
+        <v>1003</v>
       </c>
       <c r="F87" s="2" t="s">
         <v>198</v>
@@ -13763,16 +13265,16 @@
         <v>661</v>
       </c>
       <c r="I87" s="23" t="s">
-        <v>777</v>
+        <v>719</v>
       </c>
       <c r="K87" s="23" t="s">
-        <v>687</v>
+        <v>1209</v>
       </c>
       <c r="L87" s="23" t="s">
-        <v>689</v>
+        <v>675</v>
       </c>
       <c r="M87" s="23" t="s">
-        <v>690</v>
+        <v>1218</v>
       </c>
       <c r="N87" s="1" t="s">
         <v>594</v>
@@ -13847,13 +13349,13 @@
         <v>661</v>
       </c>
       <c r="I88" s="23" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="L88" s="23" t="s">
-        <v>1278</v>
+        <v>1180</v>
       </c>
       <c r="M88" s="23" t="s">
-        <v>692</v>
+        <v>1210</v>
       </c>
       <c r="N88" s="1" t="s">
         <v>594</v>
@@ -13982,10 +13484,10 @@
         <v>241</v>
       </c>
       <c r="D90" s="23" t="s">
-        <v>919</v>
+        <v>834</v>
       </c>
       <c r="E90" s="23" t="s">
-        <v>1089</v>
+        <v>1004</v>
       </c>
       <c r="F90" s="2" t="s">
         <v>242</v>
@@ -14048,10 +13550,10 @@
         <v>184</v>
       </c>
       <c r="D91" s="23" t="s">
-        <v>920</v>
+        <v>835</v>
       </c>
       <c r="E91" s="23" t="s">
-        <v>1090</v>
+        <v>1005</v>
       </c>
       <c r="F91" s="2" t="s">
         <v>176</v>
@@ -14063,13 +13565,13 @@
         <v>660</v>
       </c>
       <c r="I91" s="23" t="s">
-        <v>741</v>
+        <v>706</v>
       </c>
       <c r="K91" s="23" t="s">
-        <v>753</v>
+        <v>1222</v>
       </c>
       <c r="L91" s="23" t="s">
-        <v>1276</v>
+        <v>1179</v>
       </c>
       <c r="N91" s="1" t="s">
         <v>631</v>
@@ -14129,10 +13631,10 @@
         <v>186</v>
       </c>
       <c r="D92" s="23" t="s">
-        <v>921</v>
+        <v>836</v>
       </c>
       <c r="E92" s="23" t="s">
-        <v>1091</v>
+        <v>1006</v>
       </c>
       <c r="F92" s="2" t="s">
         <v>176</v>
@@ -14144,13 +13646,13 @@
         <v>660</v>
       </c>
       <c r="I92" s="23" t="s">
-        <v>741</v>
+        <v>706</v>
       </c>
       <c r="K92" s="23" t="s">
-        <v>751</v>
+        <v>1225</v>
       </c>
       <c r="L92" s="23" t="s">
-        <v>1276</v>
+        <v>1179</v>
       </c>
       <c r="N92" s="1" t="s">
         <v>631</v>
@@ -14210,10 +13712,10 @@
         <v>68</v>
       </c>
       <c r="D93" s="23" t="s">
-        <v>922</v>
+        <v>837</v>
       </c>
       <c r="E93" s="23" t="s">
-        <v>1092</v>
+        <v>1007</v>
       </c>
       <c r="F93" s="2" t="s">
         <v>69</v>
@@ -14294,10 +13796,10 @@
         <v>660</v>
       </c>
       <c r="I94" s="23" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="K94" s="23" t="s">
-        <v>753</v>
+        <v>1222</v>
       </c>
       <c r="N94" s="1" t="s">
         <v>595</v>
@@ -14495,10 +13997,10 @@
         <v>173</v>
       </c>
       <c r="D97" s="23" t="s">
-        <v>923</v>
+        <v>838</v>
       </c>
       <c r="E97" s="23" t="s">
-        <v>1093</v>
+        <v>1008</v>
       </c>
       <c r="F97" s="2" t="s">
         <v>167</v>
@@ -14510,13 +14012,13 @@
         <v>660</v>
       </c>
       <c r="I97" s="23" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="K97" s="23" t="s">
-        <v>758</v>
+        <v>1219</v>
       </c>
       <c r="M97" s="23" t="s">
-        <v>788</v>
+        <v>1253</v>
       </c>
       <c r="N97" s="1" t="s">
         <v>631</v>
@@ -14576,10 +14078,10 @@
         <v>269</v>
       </c>
       <c r="D98" s="23" t="s">
-        <v>924</v>
+        <v>839</v>
       </c>
       <c r="E98" s="23" t="s">
-        <v>1094</v>
+        <v>1009</v>
       </c>
       <c r="F98" s="2" t="s">
         <v>270</v>
@@ -14657,10 +14159,10 @@
         <v>661</v>
       </c>
       <c r="I99" s="23" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="M99" s="23" t="s">
-        <v>761</v>
+        <v>1205</v>
       </c>
       <c r="O99" s="1" t="s">
         <v>549</v>
@@ -14717,7 +14219,7 @@
         <v>260</v>
       </c>
       <c r="D100" s="23" t="s">
-        <v>925</v>
+        <v>840</v>
       </c>
       <c r="E100" s="23" t="s">
         <v>261</v>
@@ -14729,13 +14231,13 @@
         <v>256</v>
       </c>
       <c r="H100" s="23" t="s">
-        <v>684</v>
+        <v>674</v>
       </c>
       <c r="I100" s="23" t="s">
-        <v>789</v>
+        <v>721</v>
       </c>
       <c r="K100" s="23" t="s">
-        <v>790</v>
+        <v>1254</v>
       </c>
       <c r="O100" s="1" t="s">
         <v>549</v>
@@ -14792,10 +14294,10 @@
         <v>251</v>
       </c>
       <c r="D101" s="23" t="s">
-        <v>926</v>
+        <v>841</v>
       </c>
       <c r="E101" s="23" t="s">
-        <v>1095</v>
+        <v>1010</v>
       </c>
       <c r="F101" s="2" t="s">
         <v>249</v>
@@ -14807,16 +14309,16 @@
         <v>660</v>
       </c>
       <c r="I101" s="23" t="s">
-        <v>696</v>
+        <v>677</v>
       </c>
       <c r="J101" s="23" t="s">
-        <v>1309</v>
+        <v>1196</v>
       </c>
       <c r="K101" s="23" t="s">
-        <v>748</v>
+        <v>1213</v>
       </c>
       <c r="L101" s="23" t="s">
-        <v>1276</v>
+        <v>1179</v>
       </c>
       <c r="O101" s="1" t="s">
         <v>549</v>
@@ -14888,13 +14390,13 @@
         <v>661</v>
       </c>
       <c r="I102" s="23" t="s">
-        <v>678</v>
+        <v>671</v>
       </c>
       <c r="L102" s="23" t="s">
-        <v>1277</v>
+        <v>1180</v>
       </c>
       <c r="M102" s="23" t="s">
-        <v>681</v>
+        <v>1210</v>
       </c>
       <c r="N102" s="1" t="s">
         <v>631</v>
@@ -14954,10 +14456,10 @@
         <v>54</v>
       </c>
       <c r="D103" s="23" t="s">
-        <v>927</v>
+        <v>842</v>
       </c>
       <c r="E103" s="23" t="s">
-        <v>1096</v>
+        <v>1011</v>
       </c>
       <c r="F103" s="27" t="s">
         <v>662</v>
@@ -15023,10 +14525,10 @@
         <v>237</v>
       </c>
       <c r="D104" s="23" t="s">
-        <v>928</v>
+        <v>843</v>
       </c>
       <c r="E104" s="23" t="s">
-        <v>1097</v>
+        <v>1012</v>
       </c>
       <c r="F104" s="2" t="s">
         <v>235</v>
@@ -15038,13 +14540,13 @@
         <v>661</v>
       </c>
       <c r="I104" s="23" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="K104" s="23" t="s">
-        <v>701</v>
+        <v>1207</v>
       </c>
       <c r="L104" s="23" t="s">
-        <v>1278</v>
+        <v>1180</v>
       </c>
       <c r="N104" s="1" t="s">
         <v>631</v>
@@ -15104,10 +14606,10 @@
         <v>160</v>
       </c>
       <c r="D105" s="23" t="s">
-        <v>929</v>
+        <v>844</v>
       </c>
       <c r="E105" s="23" t="s">
-        <v>1098</v>
+        <v>1013</v>
       </c>
       <c r="F105" s="2" t="s">
         <v>161</v>
@@ -15170,10 +14672,10 @@
         <v>280</v>
       </c>
       <c r="D106" s="23" t="s">
-        <v>930</v>
+        <v>845</v>
       </c>
       <c r="E106" s="23" t="s">
-        <v>1099</v>
+        <v>1014</v>
       </c>
       <c r="F106" s="15" t="s">
         <v>516</v>
@@ -15236,10 +14738,10 @@
         <v>174</v>
       </c>
       <c r="D107" s="23" t="s">
-        <v>931</v>
+        <v>846</v>
       </c>
       <c r="E107" s="23" t="s">
-        <v>1100</v>
+        <v>1015</v>
       </c>
       <c r="F107" s="2" t="s">
         <v>167</v>
@@ -15251,16 +14753,16 @@
         <v>660</v>
       </c>
       <c r="I107" s="23" t="s">
-        <v>791</v>
+        <v>722</v>
       </c>
       <c r="K107" s="23" t="s">
-        <v>759</v>
+        <v>1221</v>
       </c>
       <c r="L107" s="23" t="s">
-        <v>1287</v>
+        <v>1241</v>
       </c>
       <c r="M107" s="23" t="s">
-        <v>767</v>
+        <v>1236</v>
       </c>
       <c r="N107" s="1" t="s">
         <v>631</v>
@@ -15386,10 +14888,10 @@
         <v>209</v>
       </c>
       <c r="D109" s="23" t="s">
-        <v>932</v>
+        <v>847</v>
       </c>
       <c r="E109" s="23" t="s">
-        <v>1101</v>
+        <v>1016</v>
       </c>
       <c r="F109" s="2" t="s">
         <v>198</v>
@@ -15401,13 +14903,13 @@
         <v>661</v>
       </c>
       <c r="I109" s="23" t="s">
-        <v>678</v>
+        <v>671</v>
       </c>
       <c r="K109" s="23" t="s">
-        <v>693</v>
+        <v>1226</v>
       </c>
       <c r="M109" s="23" t="s">
-        <v>685</v>
+        <v>1205</v>
       </c>
       <c r="N109" s="1" t="s">
         <v>594</v>
@@ -15482,7 +14984,7 @@
         <v>661</v>
       </c>
       <c r="M110" s="23" t="s">
-        <v>744</v>
+        <v>1215</v>
       </c>
       <c r="N110" s="1" t="s">
         <v>631</v>
@@ -15542,10 +15044,10 @@
         <v>240</v>
       </c>
       <c r="D111" s="23" t="s">
-        <v>933</v>
+        <v>848</v>
       </c>
       <c r="E111" s="23" t="s">
-        <v>1102</v>
+        <v>1017</v>
       </c>
       <c r="F111" s="2" t="s">
         <v>238</v>
@@ -15623,16 +15125,16 @@
         <v>661</v>
       </c>
       <c r="I112" s="23" t="s">
-        <v>678</v>
+        <v>671</v>
       </c>
       <c r="K112" s="23" t="s">
-        <v>711</v>
+        <v>1227</v>
       </c>
       <c r="L112" s="23" t="s">
-        <v>1277</v>
+        <v>1180</v>
       </c>
       <c r="M112" s="23" t="s">
-        <v>681</v>
+        <v>1210</v>
       </c>
       <c r="N112" s="1" t="s">
         <v>594</v>
@@ -15707,16 +15209,16 @@
         <v>660</v>
       </c>
       <c r="I113" s="23" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="K113" s="23" t="s">
-        <v>673</v>
+        <v>1228</v>
       </c>
       <c r="L113" s="23" t="s">
-        <v>1285</v>
+        <v>1186</v>
       </c>
       <c r="M113" s="23" t="s">
-        <v>792</v>
+        <v>1255</v>
       </c>
       <c r="N113" s="1" t="s">
         <v>595</v>
@@ -15776,10 +15278,10 @@
         <v>580</v>
       </c>
       <c r="D114" s="23" t="s">
-        <v>934</v>
+        <v>849</v>
       </c>
       <c r="E114" s="23" t="s">
-        <v>1103</v>
+        <v>1018</v>
       </c>
       <c r="F114" s="2" t="s">
         <v>43</v>
@@ -15845,10 +15347,10 @@
         <v>418</v>
       </c>
       <c r="D115" s="23" t="s">
-        <v>935</v>
+        <v>850</v>
       </c>
       <c r="E115" s="23" t="s">
-        <v>1104</v>
+        <v>1019</v>
       </c>
       <c r="F115" s="15" t="s">
         <v>419</v>
@@ -15915,16 +15417,16 @@
         <v>334</v>
       </c>
       <c r="D116" s="23" t="s">
-        <v>936</v>
+        <v>851</v>
       </c>
       <c r="E116" s="23" t="s">
-        <v>1105</v>
+        <v>1020</v>
       </c>
       <c r="F116" s="2" t="s">
         <v>165</v>
       </c>
       <c r="G116" s="23" t="s">
-        <v>1201</v>
+        <v>1116</v>
       </c>
       <c r="O116" s="1" t="s">
         <v>549</v>
@@ -15996,19 +15498,19 @@
         <v>661</v>
       </c>
       <c r="I117" s="23" t="s">
-        <v>768</v>
+        <v>713</v>
       </c>
       <c r="J117" s="23" t="s">
-        <v>1314</v>
+        <v>1199</v>
       </c>
       <c r="K117" s="23" t="s">
-        <v>674</v>
+        <v>1202</v>
       </c>
       <c r="L117" s="23" t="s">
-        <v>1280</v>
+        <v>1182</v>
       </c>
       <c r="M117" s="23" t="s">
-        <v>793</v>
+        <v>1256</v>
       </c>
       <c r="N117" s="1" t="s">
         <v>595</v>
@@ -16137,10 +15639,10 @@
         <v>385</v>
       </c>
       <c r="D119" s="23" t="s">
-        <v>937</v>
+        <v>852</v>
       </c>
       <c r="E119" s="23" t="s">
-        <v>1106</v>
+        <v>1021</v>
       </c>
       <c r="F119" s="15" t="s">
         <v>386</v>
@@ -16206,10 +15708,10 @@
         <v>581</v>
       </c>
       <c r="D120" s="23" t="s">
-        <v>938</v>
+        <v>853</v>
       </c>
       <c r="E120" s="23" t="s">
-        <v>1107</v>
+        <v>1022</v>
       </c>
       <c r="F120" s="2" t="s">
         <v>43</v>
@@ -16341,10 +15843,10 @@
         <v>399</v>
       </c>
       <c r="D122" s="23" t="s">
-        <v>939</v>
+        <v>854</v>
       </c>
       <c r="E122" s="23" t="s">
-        <v>1108</v>
+        <v>1023</v>
       </c>
       <c r="F122" s="2" t="s">
         <v>397</v>
@@ -16407,10 +15909,10 @@
         <v>582</v>
       </c>
       <c r="D123" s="23" t="s">
-        <v>940</v>
+        <v>855</v>
       </c>
       <c r="E123" s="23" t="s">
-        <v>1109</v>
+        <v>1024</v>
       </c>
       <c r="F123" s="2" t="s">
         <v>43</v>
@@ -16476,10 +15978,10 @@
         <v>302</v>
       </c>
       <c r="D124" s="23" t="s">
-        <v>941</v>
+        <v>856</v>
       </c>
       <c r="E124" s="23" t="s">
-        <v>1110</v>
+        <v>1025</v>
       </c>
       <c r="F124" s="15" t="s">
         <v>161</v>
@@ -16809,10 +16311,10 @@
         <v>584</v>
       </c>
       <c r="D129" s="23" t="s">
-        <v>942</v>
+        <v>857</v>
       </c>
       <c r="E129" s="23" t="s">
-        <v>1111</v>
+        <v>1026</v>
       </c>
       <c r="F129" s="2" t="s">
         <v>43</v>
@@ -16878,10 +16380,10 @@
         <v>322</v>
       </c>
       <c r="D130" s="23" t="s">
-        <v>943</v>
+        <v>858</v>
       </c>
       <c r="E130" s="23" t="s">
-        <v>1112</v>
+        <v>1027</v>
       </c>
       <c r="F130" s="2" t="s">
         <v>90</v>
@@ -16893,10 +16395,10 @@
         <v>661</v>
       </c>
       <c r="I130" s="23" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="L130" s="23" t="s">
-        <v>1289</v>
+        <v>1189</v>
       </c>
       <c r="O130" s="1" t="s">
         <v>549</v>
@@ -16968,7 +16470,7 @@
         <v>661</v>
       </c>
       <c r="I131" s="23" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="O131" s="1" t="s">
         <v>549</v>
@@ -17025,10 +16527,10 @@
         <v>394</v>
       </c>
       <c r="D132" s="23" t="s">
-        <v>944</v>
+        <v>859</v>
       </c>
       <c r="E132" s="23" t="s">
-        <v>1113</v>
+        <v>1028</v>
       </c>
       <c r="F132" s="2" t="s">
         <v>393</v>
@@ -17091,10 +16593,10 @@
         <v>326</v>
       </c>
       <c r="D133" s="23" t="s">
-        <v>945</v>
+        <v>860</v>
       </c>
       <c r="E133" s="23" t="s">
-        <v>1114</v>
+        <v>1029</v>
       </c>
       <c r="F133" s="2" t="s">
         <v>224</v>
@@ -17157,10 +16659,10 @@
         <v>301</v>
       </c>
       <c r="D134" s="23" t="s">
-        <v>946</v>
+        <v>861</v>
       </c>
       <c r="E134" s="23" t="s">
-        <v>1115</v>
+        <v>1030</v>
       </c>
       <c r="F134" s="2" t="s">
         <v>161</v>
@@ -17223,10 +16725,10 @@
         <v>457</v>
       </c>
       <c r="D135" s="23" t="s">
-        <v>947</v>
+        <v>862</v>
       </c>
       <c r="E135" s="23" t="s">
-        <v>1116</v>
+        <v>1031</v>
       </c>
       <c r="F135" s="2" t="s">
         <v>456</v>
@@ -17289,10 +16791,10 @@
         <v>313</v>
       </c>
       <c r="D136" s="23" t="s">
-        <v>948</v>
+        <v>863</v>
       </c>
       <c r="E136" s="23" t="s">
-        <v>1117</v>
+        <v>1032</v>
       </c>
       <c r="F136" s="2" t="s">
         <v>314</v>
@@ -17355,10 +16857,10 @@
         <v>327</v>
       </c>
       <c r="D137" s="23" t="s">
-        <v>949</v>
+        <v>864</v>
       </c>
       <c r="E137" s="23" t="s">
-        <v>1118</v>
+        <v>1033</v>
       </c>
       <c r="F137" s="2" t="s">
         <v>224</v>
@@ -17421,10 +16923,10 @@
         <v>350</v>
       </c>
       <c r="D138" s="23" t="s">
-        <v>950</v>
+        <v>865</v>
       </c>
       <c r="E138" s="23" t="s">
-        <v>1119</v>
+        <v>1034</v>
       </c>
       <c r="F138" s="2" t="s">
         <v>83</v>
@@ -17436,13 +16938,13 @@
         <v>660</v>
       </c>
       <c r="I138" s="23" t="s">
-        <v>794</v>
+        <v>723</v>
       </c>
       <c r="L138" s="23" t="s">
-        <v>1277</v>
+        <v>1180</v>
       </c>
       <c r="M138" s="23" t="s">
-        <v>795</v>
+        <v>1236</v>
       </c>
       <c r="O138" s="1" t="s">
         <v>549</v>
@@ -17499,10 +17001,10 @@
         <v>445</v>
       </c>
       <c r="D139" s="23" t="s">
-        <v>951</v>
+        <v>866</v>
       </c>
       <c r="E139" s="23" t="s">
-        <v>1120</v>
+        <v>1035</v>
       </c>
       <c r="F139" s="2" t="s">
         <v>389</v>
@@ -17568,10 +17070,10 @@
         <v>283</v>
       </c>
       <c r="D140" s="23" t="s">
-        <v>952</v>
+        <v>867</v>
       </c>
       <c r="E140" s="23" t="s">
-        <v>1121</v>
+        <v>1036</v>
       </c>
       <c r="F140" s="2" t="s">
         <v>43</v>
@@ -17637,10 +17139,10 @@
         <v>335</v>
       </c>
       <c r="D141" s="23" t="s">
-        <v>953</v>
+        <v>868</v>
       </c>
       <c r="E141" s="23" t="s">
-        <v>1122</v>
+        <v>1037</v>
       </c>
       <c r="F141" s="2" t="s">
         <v>336</v>
@@ -17706,10 +17208,10 @@
         <v>367</v>
       </c>
       <c r="D142" s="23" t="s">
-        <v>954</v>
+        <v>869</v>
       </c>
       <c r="E142" s="23" t="s">
-        <v>1123</v>
+        <v>1038</v>
       </c>
       <c r="F142" s="2" t="s">
         <v>365</v>
@@ -17772,10 +17274,10 @@
         <v>339</v>
       </c>
       <c r="D143" s="23" t="s">
-        <v>955</v>
+        <v>870</v>
       </c>
       <c r="E143" s="23" t="s">
-        <v>1124</v>
+        <v>1039</v>
       </c>
       <c r="F143" s="2" t="s">
         <v>338</v>
@@ -17842,13 +17344,13 @@
         <v>447</v>
       </c>
       <c r="D144" s="23" t="s">
-        <v>956</v>
+        <v>871</v>
       </c>
       <c r="E144" s="23" t="s">
-        <v>1125</v>
+        <v>1040</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>746</v>
+        <v>707</v>
       </c>
       <c r="G144" s="23" t="s">
         <v>47</v>
@@ -17857,13 +17359,13 @@
         <v>660</v>
       </c>
       <c r="I144" s="23" t="s">
-        <v>796</v>
+        <v>724</v>
       </c>
       <c r="K144" s="23" t="s">
-        <v>748</v>
+        <v>1213</v>
       </c>
       <c r="L144" s="23" t="s">
-        <v>1290</v>
+        <v>1189</v>
       </c>
       <c r="N144" s="1" t="s">
         <v>594</v>
@@ -17923,10 +17425,10 @@
         <v>585</v>
       </c>
       <c r="D145" s="23" t="s">
-        <v>957</v>
+        <v>872</v>
       </c>
       <c r="E145" s="23" t="s">
-        <v>1126</v>
+        <v>1041</v>
       </c>
       <c r="F145" s="2" t="s">
         <v>43</v>
@@ -17992,10 +17494,10 @@
         <v>358</v>
       </c>
       <c r="D146" s="23" t="s">
-        <v>958</v>
+        <v>873</v>
       </c>
       <c r="E146" s="23" t="s">
-        <v>1127</v>
+        <v>1042</v>
       </c>
       <c r="F146" s="2" t="s">
         <v>356</v>
@@ -18058,10 +17560,10 @@
         <v>388</v>
       </c>
       <c r="D147" s="23" t="s">
-        <v>959</v>
+        <v>874</v>
       </c>
       <c r="E147" s="23" t="s">
-        <v>1128</v>
+        <v>1043</v>
       </c>
       <c r="F147" s="2" t="s">
         <v>389</v>
@@ -18127,10 +17629,10 @@
         <v>349</v>
       </c>
       <c r="D148" s="23" t="s">
-        <v>960</v>
+        <v>875</v>
       </c>
       <c r="E148" s="23" t="s">
-        <v>1129</v>
+        <v>1044</v>
       </c>
       <c r="F148" s="2" t="s">
         <v>83</v>
@@ -18142,13 +17644,13 @@
         <v>660</v>
       </c>
       <c r="I148" s="23" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="J148" s="23" t="s">
-        <v>1301</v>
+        <v>1192</v>
       </c>
       <c r="M148" s="23" t="s">
-        <v>700</v>
+        <v>1206</v>
       </c>
       <c r="O148" s="1" t="s">
         <v>549</v>
@@ -18275,10 +17777,10 @@
         <v>508</v>
       </c>
       <c r="D150" s="23" t="s">
-        <v>961</v>
+        <v>876</v>
       </c>
       <c r="E150" s="23" t="s">
-        <v>1130</v>
+        <v>1045</v>
       </c>
       <c r="F150" s="15" t="s">
         <v>509</v>
@@ -18344,10 +17846,10 @@
         <v>396</v>
       </c>
       <c r="D151" s="23" t="s">
-        <v>962</v>
+        <v>877</v>
       </c>
       <c r="E151" s="23" t="s">
-        <v>1131</v>
+        <v>1046</v>
       </c>
       <c r="F151" s="2" t="s">
         <v>397</v>
@@ -18410,10 +17912,10 @@
         <v>586</v>
       </c>
       <c r="D152" s="23" t="s">
-        <v>963</v>
+        <v>878</v>
       </c>
       <c r="E152" s="23" t="s">
-        <v>1132</v>
+        <v>1047</v>
       </c>
       <c r="F152" s="2" t="s">
         <v>43</v>
@@ -18545,10 +18047,10 @@
         <v>436</v>
       </c>
       <c r="D154" s="23" t="s">
-        <v>964</v>
+        <v>879</v>
       </c>
       <c r="E154" s="23" t="s">
-        <v>1133</v>
+        <v>1048</v>
       </c>
       <c r="F154" s="2" t="s">
         <v>434</v>
@@ -18611,10 +18113,10 @@
         <v>348</v>
       </c>
       <c r="D155" s="23" t="s">
-        <v>965</v>
+        <v>880</v>
       </c>
       <c r="E155" s="23" t="s">
-        <v>1134</v>
+        <v>1049</v>
       </c>
       <c r="F155" s="2" t="s">
         <v>346</v>
@@ -18680,10 +18182,10 @@
         <v>321</v>
       </c>
       <c r="D156" s="23" t="s">
-        <v>966</v>
+        <v>881</v>
       </c>
       <c r="E156" s="23" t="s">
-        <v>1135</v>
+        <v>1050</v>
       </c>
       <c r="F156" s="2" t="s">
         <v>90</v>
@@ -18695,7 +18197,7 @@
         <v>660</v>
       </c>
       <c r="I156" s="23" t="s">
-        <v>789</v>
+        <v>721</v>
       </c>
       <c r="O156" s="1" t="s">
         <v>549</v>
@@ -18752,10 +18254,10 @@
         <v>319</v>
       </c>
       <c r="D157" s="23" t="s">
-        <v>967</v>
+        <v>882</v>
       </c>
       <c r="E157" s="23" t="s">
-        <v>1136</v>
+        <v>1051</v>
       </c>
       <c r="F157" s="2" t="s">
         <v>317</v>
@@ -18833,19 +18335,19 @@
         <v>405</v>
       </c>
       <c r="H158" s="23" t="s">
-        <v>684</v>
+        <v>674</v>
       </c>
       <c r="I158" s="23" t="s">
-        <v>678</v>
+        <v>671</v>
       </c>
       <c r="J158" s="23" t="s">
-        <v>1313</v>
+        <v>1199</v>
       </c>
       <c r="K158" s="23" t="s">
-        <v>755</v>
+        <v>1221</v>
       </c>
       <c r="M158" s="23" t="s">
-        <v>704</v>
+        <v>1208</v>
       </c>
       <c r="N158" s="1" t="s">
         <v>631</v>
@@ -18905,10 +18407,10 @@
         <v>448</v>
       </c>
       <c r="D159" s="23" t="s">
-        <v>968</v>
+        <v>883</v>
       </c>
       <c r="E159" s="24" t="s">
-        <v>1137</v>
+        <v>1052</v>
       </c>
       <c r="F159" s="15" t="s">
         <v>386</v>
@@ -18974,10 +18476,10 @@
         <v>400</v>
       </c>
       <c r="D160" s="23" t="s">
-        <v>969</v>
+        <v>884</v>
       </c>
       <c r="E160" s="23" t="s">
-        <v>1138</v>
+        <v>1053</v>
       </c>
       <c r="F160" s="2" t="s">
         <v>401</v>
@@ -19041,10 +18543,10 @@
         <v>284</v>
       </c>
       <c r="D161" s="23" t="s">
-        <v>970</v>
+        <v>885</v>
       </c>
       <c r="E161" s="23" t="s">
-        <v>1139</v>
+        <v>1054</v>
       </c>
       <c r="F161" s="2" t="s">
         <v>43</v>
@@ -19110,10 +18612,10 @@
         <v>391</v>
       </c>
       <c r="D162" s="23" t="s">
-        <v>971</v>
+        <v>886</v>
       </c>
       <c r="E162" s="23" t="s">
-        <v>1140</v>
+        <v>1055</v>
       </c>
       <c r="F162" s="2" t="s">
         <v>392</v>
@@ -19243,10 +18745,10 @@
         <v>515</v>
       </c>
       <c r="D164" s="23" t="s">
-        <v>972</v>
+        <v>887</v>
       </c>
       <c r="E164" s="23" t="s">
-        <v>1141</v>
+        <v>1056</v>
       </c>
       <c r="F164" s="15" t="s">
         <v>481</v>
@@ -19309,10 +18811,10 @@
         <v>511</v>
       </c>
       <c r="D165" s="23" t="s">
-        <v>973</v>
+        <v>888</v>
       </c>
       <c r="E165" s="23" t="s">
-        <v>1142</v>
+        <v>1057</v>
       </c>
       <c r="F165" s="2" t="s">
         <v>512</v>
@@ -19508,10 +19010,10 @@
         <v>433</v>
       </c>
       <c r="D168" s="23" t="s">
-        <v>974</v>
+        <v>889</v>
       </c>
       <c r="E168" s="23" t="s">
-        <v>1143</v>
+        <v>1058</v>
       </c>
       <c r="F168" s="2" t="s">
         <v>434</v>
@@ -19640,10 +19142,10 @@
         <v>442</v>
       </c>
       <c r="D170" s="23" t="s">
-        <v>975</v>
+        <v>890</v>
       </c>
       <c r="E170" s="23" t="s">
-        <v>1144</v>
+        <v>1059</v>
       </c>
       <c r="F170" s="2" t="s">
         <v>440</v>
@@ -19721,13 +19223,13 @@
         <v>661</v>
       </c>
       <c r="I171" s="23" t="s">
-        <v>676</v>
+        <v>670</v>
       </c>
       <c r="L171" s="23" t="s">
-        <v>764</v>
+        <v>710</v>
       </c>
       <c r="M171" s="23" t="s">
-        <v>677</v>
+        <v>1206</v>
       </c>
       <c r="N171" s="1" t="s">
         <v>595</v>
@@ -19787,10 +19289,10 @@
         <v>364</v>
       </c>
       <c r="D172" s="23" t="s">
-        <v>976</v>
+        <v>891</v>
       </c>
       <c r="E172" s="23" t="s">
-        <v>1145</v>
+        <v>1060</v>
       </c>
       <c r="F172" s="2" t="s">
         <v>365</v>
@@ -19985,10 +19487,10 @@
         <v>316</v>
       </c>
       <c r="D175" s="23" t="s">
-        <v>977</v>
+        <v>892</v>
       </c>
       <c r="E175" s="23" t="s">
-        <v>1146</v>
+        <v>1061</v>
       </c>
       <c r="F175" s="2" t="s">
         <v>317</v>
@@ -20054,10 +19556,10 @@
         <v>443</v>
       </c>
       <c r="D176" s="23" t="s">
-        <v>978</v>
+        <v>893</v>
       </c>
       <c r="E176" s="23" t="s">
-        <v>1147</v>
+        <v>1062</v>
       </c>
       <c r="F176" s="15" t="s">
         <v>502</v>
@@ -20186,10 +19688,10 @@
         <v>588</v>
       </c>
       <c r="D178" s="23" t="s">
-        <v>979</v>
+        <v>894</v>
       </c>
       <c r="E178" s="23" t="s">
-        <v>1148</v>
+        <v>1063</v>
       </c>
       <c r="F178" s="2" t="s">
         <v>43</v>
@@ -20255,10 +19757,10 @@
         <v>402</v>
       </c>
       <c r="D179" s="23" t="s">
-        <v>980</v>
+        <v>895</v>
       </c>
       <c r="E179" s="23" t="s">
-        <v>1149</v>
+        <v>1064</v>
       </c>
       <c r="F179" s="2" t="s">
         <v>401</v>
@@ -20388,10 +19890,10 @@
         <v>438</v>
       </c>
       <c r="D181" s="23" t="s">
-        <v>981</v>
+        <v>896</v>
       </c>
       <c r="E181" s="23" t="s">
-        <v>1150</v>
+        <v>1065</v>
       </c>
       <c r="F181" s="15" t="s">
         <v>437</v>
@@ -20454,10 +19956,10 @@
         <v>490</v>
       </c>
       <c r="D182" s="23" t="s">
-        <v>982</v>
+        <v>897</v>
       </c>
       <c r="E182" s="23" t="s">
-        <v>1151</v>
+        <v>1066</v>
       </c>
       <c r="F182" s="15" t="s">
         <v>491</v>
@@ -20520,10 +20022,10 @@
         <v>541</v>
       </c>
       <c r="D183" s="23" t="s">
-        <v>983</v>
+        <v>898</v>
       </c>
       <c r="E183" s="23" t="s">
-        <v>1152</v>
+        <v>1067</v>
       </c>
       <c r="F183" s="15" t="s">
         <v>540</v>
@@ -20586,10 +20088,10 @@
         <v>446</v>
       </c>
       <c r="D184" s="23" t="s">
-        <v>984</v>
+        <v>899</v>
       </c>
       <c r="E184" s="23" t="s">
-        <v>1153</v>
+        <v>1068</v>
       </c>
       <c r="F184" s="2" t="s">
         <v>389</v>
@@ -20655,10 +20157,10 @@
         <v>330</v>
       </c>
       <c r="D185" s="23" t="s">
-        <v>985</v>
+        <v>900</v>
       </c>
       <c r="E185" s="23" t="s">
-        <v>1154</v>
+        <v>1069</v>
       </c>
       <c r="F185" s="2" t="s">
         <v>329</v>
@@ -20670,16 +20172,16 @@
         <v>661</v>
       </c>
       <c r="I185" s="23" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="K185" s="23" t="s">
-        <v>668</v>
+        <v>1202</v>
       </c>
       <c r="L185" s="23" t="s">
-        <v>1277</v>
+        <v>1180</v>
       </c>
       <c r="M185" s="23" t="s">
-        <v>681</v>
+        <v>1210</v>
       </c>
       <c r="N185" s="1" t="s">
         <v>594</v>
@@ -20739,10 +20241,10 @@
         <v>285</v>
       </c>
       <c r="D186" s="23" t="s">
-        <v>986</v>
+        <v>901</v>
       </c>
       <c r="E186" s="23" t="s">
-        <v>1155</v>
+        <v>1070</v>
       </c>
       <c r="F186" s="2" t="s">
         <v>43</v>
@@ -20820,13 +20322,13 @@
         <v>199</v>
       </c>
       <c r="H187" s="23" t="s">
-        <v>683</v>
+        <v>673</v>
       </c>
       <c r="I187" s="23" t="s">
-        <v>797</v>
+        <v>725</v>
       </c>
       <c r="K187" s="23" t="s">
-        <v>694</v>
+        <v>1229</v>
       </c>
       <c r="N187" s="1" t="s">
         <v>594</v>
@@ -20952,10 +20454,10 @@
         <v>589</v>
       </c>
       <c r="D189" s="23" t="s">
-        <v>987</v>
+        <v>902</v>
       </c>
       <c r="E189" s="23" t="s">
-        <v>1156</v>
+        <v>1071</v>
       </c>
       <c r="F189" s="2" t="s">
         <v>43</v>
@@ -21090,10 +20592,10 @@
         <v>412</v>
       </c>
       <c r="D191" s="23" t="s">
-        <v>988</v>
+        <v>903</v>
       </c>
       <c r="E191" s="23" t="s">
-        <v>1157</v>
+        <v>1072</v>
       </c>
       <c r="F191" s="15" t="s">
         <v>413</v>
@@ -21225,10 +20727,10 @@
         <v>590</v>
       </c>
       <c r="D193" s="23" t="s">
-        <v>989</v>
+        <v>904</v>
       </c>
       <c r="E193" s="23" t="s">
-        <v>1158</v>
+        <v>1073</v>
       </c>
       <c r="F193" s="2" t="s">
         <v>43</v>
@@ -21309,13 +20811,13 @@
         <v>660</v>
       </c>
       <c r="I194" s="23" t="s">
-        <v>741</v>
+        <v>706</v>
       </c>
       <c r="J194" s="23" t="s">
-        <v>1305</v>
+        <v>1194</v>
       </c>
       <c r="M194" s="23" t="s">
-        <v>798</v>
+        <v>1257</v>
       </c>
       <c r="N194" s="1" t="s">
         <v>631</v>
@@ -21375,10 +20877,10 @@
         <v>591</v>
       </c>
       <c r="D195" s="23" t="s">
-        <v>990</v>
+        <v>905</v>
       </c>
       <c r="E195" s="23" t="s">
-        <v>1159</v>
+        <v>1074</v>
       </c>
       <c r="F195" s="2" t="s">
         <v>43</v>
@@ -21510,10 +21012,10 @@
         <v>377</v>
       </c>
       <c r="D197" s="23" t="s">
-        <v>991</v>
+        <v>906</v>
       </c>
       <c r="E197" s="23" t="s">
-        <v>1160</v>
+        <v>1075</v>
       </c>
       <c r="F197" s="2" t="s">
         <v>378</v>
@@ -21576,10 +21078,10 @@
         <v>282</v>
       </c>
       <c r="D198" s="23" t="s">
-        <v>992</v>
+        <v>907</v>
       </c>
       <c r="E198" s="23" t="s">
-        <v>1161</v>
+        <v>1076</v>
       </c>
       <c r="F198" s="2" t="s">
         <v>43</v>
@@ -21645,10 +21147,10 @@
         <v>420</v>
       </c>
       <c r="D199" s="23" t="s">
-        <v>993</v>
+        <v>908</v>
       </c>
       <c r="E199" s="23" t="s">
-        <v>1162</v>
+        <v>1077</v>
       </c>
       <c r="F199" s="15" t="s">
         <v>421</v>
@@ -21714,10 +21216,10 @@
         <v>451</v>
       </c>
       <c r="D200" s="23" t="s">
-        <v>994</v>
+        <v>909</v>
       </c>
       <c r="E200" s="23" t="s">
-        <v>1163</v>
+        <v>1078</v>
       </c>
       <c r="F200" s="15" t="s">
         <v>449</v>
@@ -21846,10 +21348,10 @@
         <v>577</v>
       </c>
       <c r="D202" s="23" t="s">
-        <v>995</v>
+        <v>910</v>
       </c>
       <c r="E202" s="23" t="s">
-        <v>1164</v>
+        <v>1079</v>
       </c>
       <c r="F202" s="2" t="s">
         <v>578</v>
@@ -21912,10 +21414,10 @@
         <v>559</v>
       </c>
       <c r="D203" s="23" t="s">
-        <v>996</v>
+        <v>911</v>
       </c>
       <c r="E203" s="23" t="s">
-        <v>1165</v>
+        <v>1080</v>
       </c>
       <c r="F203" s="15" t="s">
         <v>560</v>
@@ -22047,13 +21549,13 @@
         <v>575</v>
       </c>
       <c r="D205" s="23" t="s">
-        <v>997</v>
+        <v>912</v>
       </c>
       <c r="E205" s="23" t="s">
-        <v>1166</v>
+        <v>1081</v>
       </c>
       <c r="F205" s="30" t="s">
-        <v>859</v>
+        <v>774</v>
       </c>
       <c r="G205" s="23" t="s">
         <v>576</v>
@@ -22113,10 +21615,10 @@
         <v>545</v>
       </c>
       <c r="D206" s="23" t="s">
-        <v>998</v>
+        <v>913</v>
       </c>
       <c r="E206" s="23" t="s">
-        <v>1167</v>
+        <v>1082</v>
       </c>
       <c r="F206" s="15" t="s">
         <v>540</v>
@@ -22125,7 +21627,7 @@
         <v>546</v>
       </c>
       <c r="M206" s="23" t="s">
-        <v>699</v>
+        <v>1206</v>
       </c>
       <c r="O206" s="1" t="s">
         <v>549</v>
@@ -22195,10 +21697,10 @@
         <v>16号(UTAU)</v>
       </c>
       <c r="H207" s="23" t="s">
-        <v>683</v>
+        <v>673</v>
       </c>
       <c r="I207" s="23" t="s">
-        <v>853</v>
+        <v>769</v>
       </c>
       <c r="N207" s="1" t="s">
         <v>631</v>
@@ -22325,10 +21827,10 @@
         <v>286</v>
       </c>
       <c r="D209" s="23" t="s">
-        <v>999</v>
+        <v>914</v>
       </c>
       <c r="E209" s="23" t="s">
-        <v>1168</v>
+        <v>1083</v>
       </c>
       <c r="F209" s="2" t="s">
         <v>43</v>
@@ -22394,10 +21896,10 @@
         <v>562</v>
       </c>
       <c r="D210" s="23" t="s">
-        <v>1000</v>
+        <v>915</v>
       </c>
       <c r="E210" s="23" t="s">
-        <v>1169</v>
+        <v>1084</v>
       </c>
       <c r="F210" s="15" t="s">
         <v>557</v>
@@ -22407,10 +21909,10 @@
         <v>ろんく1号(UTAU)</v>
       </c>
       <c r="H210" s="23" t="s">
-        <v>684</v>
+        <v>674</v>
       </c>
       <c r="I210" s="23" t="s">
-        <v>678</v>
+        <v>671</v>
       </c>
       <c r="N210" s="1" t="s">
         <v>631</v>
@@ -22536,13 +22038,13 @@
         <v>t-kun</v>
       </c>
       <c r="C212" s="24" t="s">
-        <v>730</v>
+        <v>698</v>
       </c>
       <c r="D212" s="23" t="s">
         <v>602</v>
       </c>
       <c r="E212" s="23" t="s">
-        <v>1170</v>
+        <v>1085</v>
       </c>
       <c r="F212" s="15" t="s">
         <v>603</v>
@@ -22554,10 +22056,10 @@
         <v>661</v>
       </c>
       <c r="I212" s="23" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="L212" s="23" t="s">
-        <v>1280</v>
+        <v>1182</v>
       </c>
       <c r="N212" s="1" t="s">
         <v>595</v>
@@ -22629,16 +22131,16 @@
         <v>606</v>
       </c>
       <c r="H213" s="23" t="s">
-        <v>684</v>
+        <v>674</v>
       </c>
       <c r="I213" s="23" t="s">
-        <v>731</v>
+        <v>699</v>
       </c>
       <c r="L213" s="23" t="s">
-        <v>1280</v>
+        <v>1182</v>
       </c>
       <c r="M213" s="23" t="s">
-        <v>799</v>
+        <v>1258</v>
       </c>
       <c r="N213" s="1" t="s">
         <v>595</v>
@@ -22698,10 +22200,10 @@
         <v>608</v>
       </c>
       <c r="D214" s="23" t="s">
-        <v>1001</v>
+        <v>916</v>
       </c>
       <c r="E214" s="23" t="s">
-        <v>1171</v>
+        <v>1086</v>
       </c>
       <c r="F214" s="15" t="s">
         <v>610</v>
@@ -22767,10 +22269,10 @@
         <v>612</v>
       </c>
       <c r="D215" s="23" t="s">
-        <v>1002</v>
+        <v>917</v>
       </c>
       <c r="E215" s="23" t="s">
-        <v>1172</v>
+        <v>1087</v>
       </c>
       <c r="F215" s="15" t="s">
         <v>645</v>
@@ -22782,7 +22284,7 @@
         <v>660</v>
       </c>
       <c r="I215" s="23" t="s">
-        <v>705</v>
+        <v>679</v>
       </c>
       <c r="N215" s="1" t="s">
         <v>594</v>
@@ -22842,10 +22344,10 @@
         <v>328</v>
       </c>
       <c r="D216" s="23" t="s">
-        <v>1003</v>
+        <v>918</v>
       </c>
       <c r="E216" s="23" t="s">
-        <v>1173</v>
+        <v>1088</v>
       </c>
       <c r="F216" s="2" t="s">
         <v>329</v>
@@ -22857,13 +22359,13 @@
         <v>661</v>
       </c>
       <c r="I216" s="23" t="s">
-        <v>675</v>
+        <v>669</v>
       </c>
       <c r="L216" s="23" t="s">
-        <v>1278</v>
+        <v>1180</v>
       </c>
       <c r="M216" s="23" t="s">
-        <v>712</v>
+        <v>1230</v>
       </c>
       <c r="N216" s="1" t="s">
         <v>594</v>
@@ -22992,10 +22494,10 @@
         <v>619</v>
       </c>
       <c r="D218" s="23" t="s">
-        <v>1004</v>
+        <v>919</v>
       </c>
       <c r="E218" s="23" t="s">
-        <v>1174</v>
+        <v>1089</v>
       </c>
       <c r="F218" s="15" t="s">
         <v>198</v>
@@ -23007,16 +22509,16 @@
         <v>661</v>
       </c>
       <c r="I218" s="23" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="K218" s="23" t="s">
-        <v>668</v>
+        <v>1202</v>
       </c>
       <c r="L218" s="23" t="s">
-        <v>1278</v>
+        <v>1180</v>
       </c>
       <c r="M218" s="23" t="s">
-        <v>695</v>
+        <v>1230</v>
       </c>
       <c r="N218" s="1" t="s">
         <v>594</v>
@@ -23076,7 +22578,7 @@
         <v>625</v>
       </c>
       <c r="D219" s="23" t="s">
-        <v>1005</v>
+        <v>920</v>
       </c>
       <c r="E219" s="23" t="s">
         <v>626</v>
@@ -23145,10 +22647,10 @@
         <v>627</v>
       </c>
       <c r="D220" s="23" t="s">
-        <v>1006</v>
+        <v>921</v>
       </c>
       <c r="E220" s="23" t="s">
-        <v>1175</v>
+        <v>1090</v>
       </c>
       <c r="F220" s="15" t="s">
         <v>611</v>
@@ -23160,10 +22662,10 @@
         <v>660</v>
       </c>
       <c r="I220" s="23" t="s">
-        <v>675</v>
+        <v>669</v>
       </c>
       <c r="L220" s="23" t="s">
-        <v>1276</v>
+        <v>1179</v>
       </c>
       <c r="N220" s="1" t="s">
         <v>594</v>
@@ -23223,10 +22725,10 @@
         <v>628</v>
       </c>
       <c r="D221" s="23" t="s">
-        <v>1007</v>
+        <v>922</v>
       </c>
       <c r="E221" s="23" t="s">
-        <v>1176</v>
+        <v>1091</v>
       </c>
       <c r="F221" s="15" t="s">
         <v>629</v>
@@ -23361,10 +22863,10 @@
         <v>636</v>
       </c>
       <c r="D223" s="23" t="s">
-        <v>1008</v>
+        <v>923</v>
       </c>
       <c r="E223" s="23" t="s">
-        <v>1177</v>
+        <v>1092</v>
       </c>
       <c r="F223" s="15" t="s">
         <v>629</v>
@@ -23431,16 +22933,16 @@
         <v>637</v>
       </c>
       <c r="D224" s="23" t="s">
-        <v>1009</v>
+        <v>924</v>
       </c>
       <c r="E224" s="23" t="s">
-        <v>1178</v>
+        <v>1093</v>
       </c>
       <c r="F224" s="15" t="s">
         <v>638</v>
       </c>
       <c r="G224" s="23" t="s">
-        <v>1202</v>
+        <v>1117</v>
       </c>
       <c r="O224" s="1" t="s">
         <v>549</v>
@@ -23497,10 +22999,10 @@
         <v>639</v>
       </c>
       <c r="D225" s="23" t="s">
-        <v>1010</v>
+        <v>925</v>
       </c>
       <c r="E225" s="23" t="s">
-        <v>1179</v>
+        <v>1094</v>
       </c>
       <c r="F225" s="15" t="s">
         <v>640</v>
@@ -23581,10 +23083,10 @@
         <v>661</v>
       </c>
       <c r="I226" s="23" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="M226" s="23" t="s">
-        <v>1247</v>
+        <v>1259</v>
       </c>
       <c r="N226" s="1" t="s">
         <v>631</v>
@@ -23647,7 +23149,7 @@
         <v>648</v>
       </c>
       <c r="E227" s="23" t="s">
-        <v>1180</v>
+        <v>1095</v>
       </c>
       <c r="F227" s="15" t="s">
         <v>645</v>
@@ -23659,13 +23161,13 @@
         <v>660</v>
       </c>
       <c r="I227" s="23" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="K227" s="23" t="s">
-        <v>751</v>
+        <v>1225</v>
       </c>
       <c r="M227" s="23" t="s">
-        <v>1248</v>
+        <v>1205</v>
       </c>
       <c r="N227" s="1" t="s">
         <v>631</v>
@@ -23722,34 +23224,34 @@
         <v>iruya-rui</v>
       </c>
       <c r="C228" s="24" t="s">
-        <v>713</v>
+        <v>683</v>
       </c>
       <c r="D228" s="23" t="s">
-        <v>1011</v>
+        <v>926</v>
       </c>
       <c r="E228" s="23" t="s">
-        <v>1181</v>
+        <v>1096</v>
       </c>
       <c r="F228" s="15" t="s">
-        <v>714</v>
+        <v>684</v>
       </c>
       <c r="G228" s="23" t="s">
-        <v>715</v>
+        <v>685</v>
       </c>
       <c r="H228" s="23" t="s">
         <v>660</v>
       </c>
       <c r="I228" s="23" t="s">
-        <v>675</v>
+        <v>669</v>
       </c>
       <c r="K228" s="23" t="s">
-        <v>716</v>
+        <v>1231</v>
       </c>
       <c r="L228" s="23" t="s">
-        <v>1293</v>
+        <v>1260</v>
       </c>
       <c r="M228" s="23" t="s">
-        <v>800</v>
+        <v>1261</v>
       </c>
       <c r="N228" s="1" t="s">
         <v>631</v>
@@ -23806,31 +23308,31 @@
         <v>​hagane-meta</v>
       </c>
       <c r="C229" s="24" t="s">
-        <v>717</v>
+        <v>686</v>
       </c>
       <c r="D229" s="23" t="s">
-        <v>1012</v>
+        <v>927</v>
       </c>
       <c r="E229" s="23" t="s">
-        <v>1182</v>
+        <v>1097</v>
       </c>
       <c r="F229" s="3" t="s">
-        <v>718</v>
+        <v>687</v>
       </c>
       <c r="G229" s="23" t="s">
-        <v>719</v>
+        <v>688</v>
       </c>
       <c r="H229" s="23" t="s">
         <v>660</v>
       </c>
       <c r="I229" s="23" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="L229" s="23" t="s">
-        <v>1280</v>
+        <v>1182</v>
       </c>
       <c r="N229" s="1" t="s">
-        <v>720</v>
+        <v>689</v>
       </c>
       <c r="O229" s="1" t="s">
         <v>549</v>
@@ -23884,28 +23386,28 @@
         <v>the-bard-euphoria</v>
       </c>
       <c r="C230" s="24" t="s">
-        <v>722</v>
+        <v>691</v>
       </c>
       <c r="D230" s="23" t="s">
-        <v>723</v>
+        <v>692</v>
       </c>
       <c r="E230" s="23" t="s">
-        <v>1183</v>
+        <v>1098</v>
       </c>
       <c r="F230" s="29" t="s">
-        <v>726</v>
+        <v>694</v>
       </c>
       <c r="G230" s="23" t="s">
-        <v>725</v>
+        <v>693</v>
       </c>
       <c r="H230" s="23" t="s">
-        <v>683</v>
+        <v>673</v>
       </c>
       <c r="I230" s="23" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="K230" s="23" t="s">
-        <v>724</v>
+        <v>1209</v>
       </c>
       <c r="N230" s="1" t="s">
         <v>631</v>
@@ -23962,34 +23464,34 @@
         <v>arujine-sarasa</v>
       </c>
       <c r="C231" s="24" t="s">
-        <v>727</v>
+        <v>695</v>
       </c>
       <c r="D231" s="23" t="s">
-        <v>1013</v>
+        <v>928</v>
       </c>
       <c r="E231" s="23" t="s">
-        <v>1184</v>
+        <v>1099</v>
       </c>
       <c r="F231" s="29" t="s">
-        <v>728</v>
+        <v>696</v>
       </c>
       <c r="G231" s="23" t="s">
-        <v>729</v>
+        <v>697</v>
       </c>
       <c r="H231" s="23" t="s">
         <v>661</v>
       </c>
       <c r="I231" s="23" t="s">
-        <v>1214</v>
+        <v>1127</v>
       </c>
       <c r="J231" s="23" t="s">
-        <v>1301</v>
+        <v>1192</v>
       </c>
       <c r="L231" s="23" t="s">
-        <v>1288</v>
+        <v>1188</v>
       </c>
       <c r="M231" s="23" t="s">
-        <v>787</v>
+        <v>1250</v>
       </c>
       <c r="N231" s="1" t="s">
         <v>631</v>
@@ -24046,31 +23548,31 @@
         <v>amaga-eru</v>
       </c>
       <c r="C232" s="24" t="s">
-        <v>732</v>
+        <v>700</v>
       </c>
       <c r="D232" s="23" t="s">
-        <v>1014</v>
+        <v>929</v>
       </c>
       <c r="E232" s="23" t="s">
-        <v>1185</v>
+        <v>1100</v>
       </c>
       <c r="F232" s="29" t="s">
-        <v>733</v>
+        <v>701</v>
       </c>
       <c r="G232" s="23" t="s">
-        <v>734</v>
+        <v>702</v>
       </c>
       <c r="H232" s="23" t="s">
         <v>660</v>
       </c>
       <c r="I232" s="23" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="J232" s="23" t="s">
-        <v>1304</v>
+        <v>1232</v>
       </c>
       <c r="L232" s="23" t="s">
-        <v>1282</v>
+        <v>1179</v>
       </c>
       <c r="N232" s="1" t="s">
         <v>631</v>
@@ -24127,16 +23629,16 @@
         <v>narukami-kyou</v>
       </c>
       <c r="C233" s="24" t="s">
-        <v>735</v>
+        <v>703</v>
       </c>
       <c r="D233" s="23" t="s">
-        <v>1015</v>
+        <v>930</v>
       </c>
       <c r="E233" s="23" t="s">
-        <v>1186</v>
+        <v>1101</v>
       </c>
       <c r="F233" s="29" t="s">
-        <v>736</v>
+        <v>704</v>
       </c>
       <c r="G233" s="23" t="str">
         <f>テーブル1[[#This Row],[名前]]&amp;"(UTAU)"</f>
@@ -24146,7 +23648,7 @@
         <v>661</v>
       </c>
       <c r="I233" s="23" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="N233" s="1" t="s">
         <v>631</v>
@@ -24206,32 +23708,32 @@
         <v>468</v>
       </c>
       <c r="D234" s="23" t="s">
-        <v>1016</v>
+        <v>931</v>
       </c>
       <c r="E234" s="23" t="s">
-        <v>1187</v>
+        <v>1102</v>
       </c>
       <c r="F234" s="15" t="s">
         <v>122</v>
       </c>
       <c r="G234" s="24" t="s">
-        <v>766</v>
+        <v>712</v>
       </c>
       <c r="H234" s="24" t="s">
         <v>661</v>
       </c>
       <c r="I234" s="24" t="s">
-        <v>678</v>
+        <v>671</v>
       </c>
       <c r="J234" s="24"/>
       <c r="K234" s="24" t="s">
-        <v>762</v>
+        <v>1226</v>
       </c>
       <c r="L234" s="24" t="s">
-        <v>1280</v>
+        <v>1182</v>
       </c>
       <c r="M234" s="24" t="s">
-        <v>818</v>
+        <v>1262</v>
       </c>
       <c r="N234" s="1" t="s">
         <v>631</v>
@@ -24291,32 +23793,32 @@
         <v>469</v>
       </c>
       <c r="D235" s="23" t="s">
-        <v>1017</v>
+        <v>932</v>
       </c>
       <c r="E235" s="23" t="s">
-        <v>1188</v>
+        <v>1103</v>
       </c>
       <c r="F235" s="15" t="s">
         <v>122</v>
       </c>
       <c r="G235" s="24" t="s">
-        <v>765</v>
+        <v>711</v>
       </c>
       <c r="H235" s="24" t="s">
         <v>661</v>
       </c>
       <c r="I235" s="24" t="s">
-        <v>803</v>
+        <v>727</v>
       </c>
       <c r="J235" s="24"/>
       <c r="K235" s="24" t="s">
-        <v>753</v>
+        <v>1222</v>
       </c>
       <c r="L235" s="24" t="s">
-        <v>1280</v>
+        <v>1182</v>
       </c>
       <c r="M235" s="24" t="s">
-        <v>804</v>
+        <v>1263</v>
       </c>
       <c r="N235" s="1" t="s">
         <v>631</v>
@@ -24373,33 +23875,33 @@
         <v>haizaki-sho</v>
       </c>
       <c r="C236" s="24" t="s">
-        <v>801</v>
+        <v>726</v>
       </c>
       <c r="D236" s="23" t="s">
-        <v>1018</v>
+        <v>933</v>
       </c>
       <c r="E236" s="23" t="s">
-        <v>1189</v>
+        <v>1104</v>
       </c>
       <c r="F236" s="15" t="s">
         <v>122</v>
       </c>
       <c r="G236" s="24" t="s">
-        <v>765</v>
+        <v>711</v>
       </c>
       <c r="H236" s="24" t="s">
         <v>661</v>
       </c>
       <c r="I236" s="24" t="s">
-        <v>696</v>
+        <v>677</v>
       </c>
       <c r="J236" s="24"/>
       <c r="K236" s="24"/>
       <c r="L236" s="24" t="s">
-        <v>1280</v>
+        <v>1182</v>
       </c>
       <c r="M236" s="24" t="s">
-        <v>802</v>
+        <v>1206</v>
       </c>
       <c r="N236" s="1" t="s">
         <v>631</v>
@@ -24459,32 +23961,32 @@
         <v>471</v>
       </c>
       <c r="D237" s="23" t="s">
-        <v>1019</v>
+        <v>934</v>
       </c>
       <c r="E237" s="23" t="s">
-        <v>1190</v>
+        <v>1105</v>
       </c>
       <c r="F237" s="15" t="s">
         <v>122</v>
       </c>
       <c r="G237" s="24" t="s">
-        <v>765</v>
+        <v>711</v>
       </c>
       <c r="H237" s="24" t="s">
-        <v>684</v>
+        <v>674</v>
       </c>
       <c r="I237" s="24" t="s">
-        <v>803</v>
+        <v>727</v>
       </c>
       <c r="J237" s="24" t="s">
-        <v>1311</v>
+        <v>1198</v>
       </c>
       <c r="K237" s="24"/>
       <c r="L237" s="24" t="s">
-        <v>1280</v>
+        <v>1182</v>
       </c>
       <c r="M237" s="24" t="s">
-        <v>704</v>
+        <v>1208</v>
       </c>
       <c r="N237" s="1" t="s">
         <v>631</v>
@@ -24553,7 +24055,7 @@
         <v>122</v>
       </c>
       <c r="G238" s="24" t="s">
-        <v>765</v>
+        <v>711</v>
       </c>
       <c r="H238" s="24" t="s">
         <v>661</v>
@@ -24563,7 +24065,7 @@
       <c r="K238" s="24"/>
       <c r="L238" s="24"/>
       <c r="M238" s="24" t="s">
-        <v>806</v>
+        <v>1206</v>
       </c>
       <c r="N238" s="1" t="s">
         <v>631</v>
@@ -24632,7 +24134,7 @@
         <v>122</v>
       </c>
       <c r="G239" s="24" t="s">
-        <v>765</v>
+        <v>711</v>
       </c>
       <c r="H239" s="24" t="s">
         <v>661</v>
@@ -24709,7 +24211,7 @@
         <v>122</v>
       </c>
       <c r="G240" s="24" t="s">
-        <v>765</v>
+        <v>711</v>
       </c>
       <c r="H240" s="24" t="s">
         <v>661</v>
@@ -24719,7 +24221,7 @@
       <c r="K240" s="24"/>
       <c r="L240" s="24"/>
       <c r="M240" s="24" t="s">
-        <v>807</v>
+        <v>1264</v>
       </c>
       <c r="N240" s="1" t="s">
         <v>631</v>
@@ -24776,28 +24278,28 @@
         <v>kumowatari-tsumugu</v>
       </c>
       <c r="C241" s="24" t="s">
-        <v>808</v>
+        <v>729</v>
       </c>
       <c r="D241" s="23" t="s">
-        <v>1020</v>
+        <v>935</v>
       </c>
       <c r="E241" s="23" t="s">
-        <v>1191</v>
+        <v>1106</v>
       </c>
       <c r="F241" s="15" t="s">
         <v>122</v>
       </c>
       <c r="G241" s="24" t="s">
-        <v>765</v>
+        <v>711</v>
       </c>
       <c r="H241" s="24" t="s">
         <v>661</v>
       </c>
       <c r="I241" s="24" t="s">
-        <v>809</v>
+        <v>730</v>
       </c>
       <c r="J241" s="23" t="s">
-        <v>1306</v>
+        <v>1195</v>
       </c>
       <c r="K241" s="24"/>
       <c r="L241" s="24"/>
@@ -24857,30 +24359,30 @@
         <v>hatatappoize</v>
       </c>
       <c r="C242" s="24" t="s">
-        <v>810</v>
+        <v>731</v>
       </c>
       <c r="D242" s="23" t="s">
-        <v>811</v>
+        <v>732</v>
       </c>
       <c r="E242" s="23" t="s">
-        <v>812</v>
+        <v>733</v>
       </c>
       <c r="F242" s="15" t="s">
         <v>122</v>
       </c>
       <c r="G242" s="24" t="s">
-        <v>765</v>
+        <v>711</v>
       </c>
       <c r="H242" s="24" t="s">
         <v>661</v>
       </c>
       <c r="I242" s="24" t="s">
-        <v>678</v>
+        <v>671</v>
       </c>
       <c r="K242" s="24"/>
       <c r="L242" s="24"/>
       <c r="M242" s="24" t="s">
-        <v>814</v>
+        <v>1236</v>
       </c>
       <c r="N242" s="1" t="s">
         <v>631</v>
@@ -24937,34 +24439,34 @@
         <v>shiraishi-sakuta</v>
       </c>
       <c r="C243" s="24" t="s">
-        <v>816</v>
+        <v>736</v>
       </c>
       <c r="D243" s="23" t="s">
-        <v>1021</v>
+        <v>936</v>
       </c>
       <c r="E243" s="23" t="s">
-        <v>1192</v>
+        <v>1107</v>
       </c>
       <c r="F243" s="15" t="s">
         <v>122</v>
       </c>
       <c r="G243" s="24" t="s">
-        <v>765</v>
+        <v>711</v>
       </c>
       <c r="H243" s="24" t="s">
         <v>661</v>
       </c>
       <c r="I243" s="24" t="s">
-        <v>819</v>
+        <v>737</v>
       </c>
       <c r="K243" s="24" t="s">
-        <v>817</v>
+        <v>1222</v>
       </c>
       <c r="L243" s="24" t="s">
-        <v>1289</v>
+        <v>1189</v>
       </c>
       <c r="M243" s="24" t="s">
-        <v>818</v>
+        <v>1262</v>
       </c>
       <c r="N243" s="1" t="s">
         <v>631</v>
@@ -25021,19 +24523,19 @@
         <v>chikusa</v>
       </c>
       <c r="C244" s="24" t="s">
-        <v>820</v>
+        <v>738</v>
       </c>
       <c r="D244" s="23" t="s">
-        <v>820</v>
+        <v>738</v>
       </c>
       <c r="E244" s="23" t="s">
-        <v>821</v>
+        <v>739</v>
       </c>
       <c r="F244" s="15" t="s">
-        <v>822</v>
+        <v>740</v>
       </c>
       <c r="G244" s="24" t="s">
-        <v>823</v>
+        <v>741</v>
       </c>
       <c r="H244" s="24" t="s">
         <v>661</v>
@@ -25042,7 +24544,7 @@
       <c r="K244" s="24"/>
       <c r="L244" s="24"/>
       <c r="M244" s="24" t="s">
-        <v>818</v>
+        <v>1262</v>
       </c>
       <c r="N244" s="1" t="s">
         <v>631</v>
@@ -25099,30 +24601,30 @@
         <v>warappoizo</v>
       </c>
       <c r="C245" s="24" t="s">
-        <v>824</v>
+        <v>742</v>
       </c>
       <c r="D245" s="23" t="s">
-        <v>825</v>
+        <v>743</v>
       </c>
       <c r="E245" s="23" t="s">
-        <v>826</v>
+        <v>744</v>
       </c>
       <c r="F245" s="15" t="s">
-        <v>827</v>
+        <v>745</v>
       </c>
       <c r="G245" s="24" t="s">
-        <v>829</v>
+        <v>747</v>
       </c>
       <c r="H245" s="24" t="s">
         <v>661</v>
       </c>
       <c r="I245" s="24" t="s">
-        <v>828</v>
+        <v>746</v>
       </c>
       <c r="K245" s="24"/>
       <c r="L245" s="24"/>
       <c r="N245" s="1" t="s">
-        <v>720</v>
+        <v>689</v>
       </c>
       <c r="O245" s="1" t="s">
         <v>549</v>
@@ -25176,31 +24678,31 @@
         <v>han'ei-xi</v>
       </c>
       <c r="C246" s="24" t="s">
-        <v>830</v>
+        <v>748</v>
       </c>
       <c r="D246" s="23" t="s">
-        <v>1022</v>
+        <v>937</v>
       </c>
       <c r="E246" s="23" t="s">
-        <v>1193</v>
+        <v>1108</v>
       </c>
       <c r="F246" s="15" t="s">
-        <v>831</v>
+        <v>749</v>
       </c>
       <c r="G246" s="24" t="s">
-        <v>832</v>
+        <v>750</v>
       </c>
       <c r="H246" s="24" t="s">
-        <v>683</v>
+        <v>673</v>
       </c>
       <c r="I246" s="24"/>
       <c r="K246" s="24"/>
       <c r="L246" s="24"/>
       <c r="M246" s="24" t="s">
-        <v>833</v>
+        <v>1262</v>
       </c>
       <c r="N246" s="1" t="s">
-        <v>720</v>
+        <v>689</v>
       </c>
       <c r="O246" s="1" t="s">
         <v>549</v>
@@ -25254,33 +24756,33 @@
         <v>aisu-kurimu</v>
       </c>
       <c r="C247" s="24" t="s">
-        <v>834</v>
+        <v>751</v>
       </c>
       <c r="D247" s="23" t="s">
-        <v>1023</v>
+        <v>938</v>
       </c>
       <c r="E247" s="23" t="s">
-        <v>1194</v>
+        <v>1109</v>
       </c>
       <c r="F247" s="15" t="s">
-        <v>835</v>
+        <v>752</v>
       </c>
       <c r="G247" s="24" t="s">
-        <v>836</v>
+        <v>753</v>
       </c>
       <c r="H247" s="24" t="s">
         <v>660</v>
       </c>
       <c r="I247" s="24" t="s">
-        <v>678</v>
+        <v>671</v>
       </c>
       <c r="J247" s="23" t="s">
-        <v>1310</v>
+        <v>1197</v>
       </c>
       <c r="K247" s="24"/>
       <c r="L247" s="24"/>
       <c r="M247" s="24" t="s">
-        <v>702</v>
+        <v>1233</v>
       </c>
       <c r="N247" s="1" t="s">
         <v>631</v>
@@ -25337,13 +24839,13 @@
         <v>utakata-tsuzuri</v>
       </c>
       <c r="C248" s="24" t="s">
-        <v>837</v>
+        <v>754</v>
       </c>
       <c r="D248" s="23" t="s">
-        <v>1024</v>
+        <v>939</v>
       </c>
       <c r="E248" s="23" t="s">
-        <v>1195</v>
+        <v>1110</v>
       </c>
       <c r="F248" s="15" t="s">
         <v>235</v>
@@ -25355,10 +24857,10 @@
         <v>660</v>
       </c>
       <c r="I248" s="24" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="K248" s="23" t="s">
-        <v>701</v>
+        <v>1207</v>
       </c>
       <c r="L248" s="24"/>
       <c r="M248" s="24"/>
@@ -25417,13 +24919,13 @@
         <v>f-113</v>
       </c>
       <c r="C249" s="24" t="s">
-        <v>838</v>
+        <v>755</v>
       </c>
       <c r="D249" s="23" t="s">
-        <v>1025</v>
+        <v>940</v>
       </c>
       <c r="E249" s="23" t="s">
-        <v>838</v>
+        <v>755</v>
       </c>
       <c r="F249" s="15" t="s">
         <v>235</v>
@@ -25435,10 +24937,10 @@
         <v>660</v>
       </c>
       <c r="I249" s="24" t="s">
-        <v>678</v>
+        <v>671</v>
       </c>
       <c r="L249" s="24" t="s">
-        <v>1289</v>
+        <v>1189</v>
       </c>
       <c r="M249" s="24"/>
       <c r="N249" s="1" t="s">
@@ -25496,34 +24998,34 @@
         <v>apuda</v>
       </c>
       <c r="C250" s="24" t="s">
-        <v>839</v>
+        <v>756</v>
       </c>
       <c r="D250" s="23" t="s">
-        <v>840</v>
+        <v>757</v>
       </c>
       <c r="E250" s="23" t="s">
-        <v>841</v>
+        <v>758</v>
       </c>
       <c r="F250" s="15" t="s">
-        <v>842</v>
+        <v>759</v>
       </c>
       <c r="G250" s="23" t="s">
-        <v>843</v>
+        <v>760</v>
       </c>
       <c r="H250" s="24" t="s">
-        <v>683</v>
+        <v>673</v>
       </c>
       <c r="I250" s="24" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="K250" s="23" t="s">
-        <v>668</v>
+        <v>1202</v>
       </c>
       <c r="L250" s="24" t="s">
-        <v>1297</v>
+        <v>1265</v>
       </c>
       <c r="M250" s="24" t="s">
-        <v>767</v>
+        <v>1236</v>
       </c>
       <c r="N250" s="1" t="s">
         <v>631</v>
@@ -25580,32 +25082,32 @@
         <v>hebikawa-ren</v>
       </c>
       <c r="C251" s="24" t="s">
-        <v>844</v>
+        <v>761</v>
       </c>
       <c r="D251" s="23" t="s">
-        <v>1026</v>
+        <v>941</v>
       </c>
       <c r="E251" s="23" t="s">
-        <v>1196</v>
+        <v>1111</v>
       </c>
       <c r="F251" s="15" t="s">
         <v>123</v>
       </c>
       <c r="G251" s="23" t="s">
-        <v>855</v>
+        <v>770</v>
       </c>
       <c r="H251" s="24" t="s">
         <v>661</v>
       </c>
       <c r="I251" s="24" t="s">
-        <v>1214</v>
+        <v>1127</v>
       </c>
       <c r="J251" s="23" t="s">
-        <v>1304</v>
+        <v>1232</v>
       </c>
       <c r="L251" s="24"/>
       <c r="M251" s="24" t="s">
-        <v>1203</v>
+        <v>1266</v>
       </c>
       <c r="N251" s="1" t="s">
         <v>631</v>
@@ -25662,28 +25164,28 @@
         <v>karasuda-tsubaki</v>
       </c>
       <c r="C252" s="24" t="s">
-        <v>845</v>
+        <v>762</v>
       </c>
       <c r="D252" s="23" t="s">
-        <v>1027</v>
+        <v>942</v>
       </c>
       <c r="E252" s="23" t="s">
-        <v>1197</v>
+        <v>1112</v>
       </c>
       <c r="F252" s="15" t="s">
         <v>123</v>
       </c>
       <c r="G252" s="24" t="s">
-        <v>852</v>
+        <v>768</v>
       </c>
       <c r="H252" s="24" t="s">
         <v>661</v>
       </c>
       <c r="I252" s="24" t="s">
-        <v>1215</v>
+        <v>1128</v>
       </c>
       <c r="J252" s="23" t="s">
-        <v>1302</v>
+        <v>1193</v>
       </c>
       <c r="L252" s="24"/>
       <c r="M252" s="24"/>
@@ -25742,32 +25244,32 @@
         <v>the-alien-cat-lyce</v>
       </c>
       <c r="C253" s="24" t="s">
-        <v>846</v>
+        <v>763</v>
       </c>
       <c r="D253" s="23" t="s">
-        <v>860</v>
+        <v>775</v>
       </c>
       <c r="E253" s="23" t="s">
-        <v>1198</v>
+        <v>1113</v>
       </c>
       <c r="F253" s="15" t="s">
-        <v>847</v>
+        <v>764</v>
       </c>
       <c r="G253" s="24" t="s">
-        <v>848</v>
+        <v>765</v>
       </c>
       <c r="H253" s="24" t="s">
-        <v>684</v>
+        <v>674</v>
       </c>
       <c r="I253" s="24" t="s">
-        <v>741</v>
+        <v>706</v>
       </c>
       <c r="J253" s="23" t="s">
-        <v>1301</v>
+        <v>1192</v>
       </c>
       <c r="L253" s="24"/>
       <c r="M253" s="23" t="s">
-        <v>787</v>
+        <v>1250</v>
       </c>
       <c r="N253" s="1" t="s">
         <v>631</v>
@@ -25824,32 +25326,32 @@
         <v>kr-725</v>
       </c>
       <c r="C254" s="24" t="s">
-        <v>856</v>
+        <v>771</v>
       </c>
       <c r="D254" s="23" t="s">
-        <v>857</v>
+        <v>772</v>
       </c>
       <c r="E254" s="23" t="s">
-        <v>856</v>
+        <v>771</v>
       </c>
       <c r="F254" s="15" t="s">
         <v>557</v>
       </c>
       <c r="G254" s="24" t="s">
-        <v>858</v>
+        <v>773</v>
       </c>
       <c r="H254" s="24" t="s">
         <v>660</v>
       </c>
       <c r="I254" s="24" t="s">
-        <v>678</v>
+        <v>671</v>
       </c>
       <c r="K254" s="23" t="s">
-        <v>851</v>
+        <v>1226</v>
       </c>
       <c r="L254" s="24"/>
       <c r="M254" s="24" t="s">
-        <v>670</v>
+        <v>1234</v>
       </c>
       <c r="N254" s="1" t="s">
         <v>631</v>
@@ -25906,34 +25408,34 @@
         <v>kurumiyaki-yosiyuki</v>
       </c>
       <c r="C255" s="24" t="s">
-        <v>849</v>
+        <v>766</v>
       </c>
       <c r="D255" s="23" t="s">
-        <v>1028</v>
+        <v>943</v>
       </c>
       <c r="E255" s="23" t="s">
-        <v>1199</v>
+        <v>1114</v>
       </c>
       <c r="F255" s="15" t="s">
-        <v>850</v>
+        <v>767</v>
       </c>
       <c r="G255" s="24" t="s">
-        <v>1217</v>
+        <v>1129</v>
       </c>
       <c r="H255" s="24" t="s">
-        <v>683</v>
+        <v>673</v>
       </c>
       <c r="I255" s="24" t="s">
-        <v>1214</v>
+        <v>1127</v>
       </c>
       <c r="J255" s="23" t="s">
-        <v>1213</v>
+        <v>1235</v>
       </c>
       <c r="L255" s="24" t="s">
-        <v>1295</v>
+        <v>1191</v>
       </c>
       <c r="M255" s="24" t="s">
-        <v>1216</v>
+        <v>1267</v>
       </c>
       <c r="N255" s="1" t="s">
         <v>631</v>
@@ -25990,25 +25492,25 @@
         <v>oumi-kurina</v>
       </c>
       <c r="C256" s="24" t="s">
-        <v>1204</v>
+        <v>1118</v>
       </c>
       <c r="D256" s="23" t="s">
-        <v>1205</v>
+        <v>1119</v>
       </c>
       <c r="E256" s="23" t="s">
-        <v>1206</v>
+        <v>1120</v>
       </c>
       <c r="F256" s="15" t="s">
-        <v>1207</v>
+        <v>1121</v>
       </c>
       <c r="G256" s="24" t="s">
-        <v>1218</v>
+        <v>1130</v>
       </c>
       <c r="H256" s="24" t="s">
         <v>660</v>
       </c>
       <c r="I256" s="24" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="L256" s="24"/>
       <c r="M256" s="24"/>
@@ -26067,31 +25569,31 @@
         <v>mitama</v>
       </c>
       <c r="C257" s="24" t="s">
-        <v>1208</v>
+        <v>1122</v>
       </c>
       <c r="D257" s="23" t="s">
-        <v>1208</v>
+        <v>1122</v>
       </c>
       <c r="E257" s="23" t="s">
-        <v>1209</v>
+        <v>1123</v>
       </c>
       <c r="F257" s="15" t="s">
-        <v>822</v>
+        <v>740</v>
       </c>
       <c r="G257" s="24" t="s">
-        <v>1219</v>
+        <v>1131</v>
       </c>
       <c r="H257" s="24" t="s">
         <v>660</v>
       </c>
       <c r="I257" s="24" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="L257" s="24" t="s">
-        <v>1280</v>
+        <v>1182</v>
       </c>
       <c r="M257" s="24" t="s">
-        <v>802</v>
+        <v>1206</v>
       </c>
       <c r="N257" s="1" t="s">
         <v>631</v>
@@ -26148,29 +25650,29 @@
         <v>mirakibo-11-gou</v>
       </c>
       <c r="C258" s="24" t="s">
-        <v>1210</v>
+        <v>1124</v>
       </c>
       <c r="D258" s="23" t="s">
-        <v>1211</v>
+        <v>1125</v>
       </c>
       <c r="E258" s="23" t="s">
-        <v>1212</v>
+        <v>1126</v>
       </c>
       <c r="F258" s="15" t="s">
-        <v>1207</v>
+        <v>1121</v>
       </c>
       <c r="G258" s="24" t="s">
-        <v>1220</v>
+        <v>1132</v>
       </c>
       <c r="H258" s="24" t="s">
-        <v>683</v>
+        <v>673</v>
       </c>
       <c r="I258" s="24" t="s">
-        <v>678</v>
+        <v>671</v>
       </c>
       <c r="L258" s="24"/>
       <c r="M258" s="24" t="s">
-        <v>704</v>
+        <v>1208</v>
       </c>
       <c r="N258" s="1" t="s">
         <v>631</v>
@@ -26227,34 +25729,34 @@
         <v>otoya-syuki</v>
       </c>
       <c r="C259" s="24" t="s">
-        <v>1221</v>
+        <v>1133</v>
       </c>
       <c r="D259" s="23" t="s">
-        <v>1222</v>
+        <v>1134</v>
       </c>
       <c r="E259" s="23" t="s">
-        <v>1223</v>
+        <v>1135</v>
       </c>
       <c r="F259" s="29" t="s">
-        <v>1224</v>
+        <v>1136</v>
       </c>
       <c r="G259" s="23" t="s">
-        <v>1225</v>
+        <v>1137</v>
       </c>
       <c r="H259" s="23" t="s">
         <v>661</v>
       </c>
       <c r="I259" s="23" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="K259" s="23" t="s">
-        <v>1226</v>
+        <v>1268</v>
       </c>
       <c r="L259" s="24" t="s">
-        <v>1278</v>
+        <v>1180</v>
       </c>
       <c r="M259" s="24" t="s">
-        <v>802</v>
+        <v>1206</v>
       </c>
       <c r="N259" s="1" t="s">
         <v>631</v>
@@ -26311,31 +25813,31 @@
         <v>natsuno-seito</v>
       </c>
       <c r="C260" s="24" t="s">
-        <v>1227</v>
+        <v>1138</v>
       </c>
       <c r="D260" s="23" t="s">
-        <v>1228</v>
+        <v>1139</v>
       </c>
       <c r="E260" s="23" t="s">
-        <v>1229</v>
+        <v>1140</v>
       </c>
       <c r="F260" s="29" t="s">
-        <v>1224</v>
+        <v>1136</v>
       </c>
       <c r="G260" s="23" t="s">
-        <v>1225</v>
+        <v>1137</v>
       </c>
       <c r="H260" s="23" t="s">
         <v>661</v>
       </c>
       <c r="I260" s="23" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="K260" s="23" t="s">
-        <v>1230</v>
+        <v>1207</v>
       </c>
       <c r="M260" s="24" t="s">
-        <v>802</v>
+        <v>1206</v>
       </c>
       <c r="N260" s="1" t="s">
         <v>631</v>
@@ -26392,31 +25894,31 @@
         <v>makimiya-fuki</v>
       </c>
       <c r="C261" s="24" t="s">
-        <v>1231</v>
+        <v>1141</v>
       </c>
       <c r="D261" s="23" t="s">
-        <v>1232</v>
+        <v>1142</v>
       </c>
       <c r="E261" s="23" t="s">
-        <v>1233</v>
+        <v>1143</v>
       </c>
       <c r="F261" s="29" t="s">
-        <v>1234</v>
+        <v>1144</v>
       </c>
       <c r="G261" s="23" t="s">
-        <v>1249</v>
+        <v>1154</v>
       </c>
       <c r="H261" s="23" t="s">
         <v>661</v>
       </c>
       <c r="I261" s="23" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="K261" s="23" t="s">
-        <v>1250</v>
+        <v>1214</v>
       </c>
       <c r="L261" s="23" t="s">
-        <v>1286</v>
+        <v>1187</v>
       </c>
       <c r="N261" s="1" t="s">
         <v>631</v>
@@ -26473,28 +25975,28 @@
         <v>wakunemu-supika</v>
       </c>
       <c r="C262" s="24" t="s">
-        <v>1237</v>
+        <v>1147</v>
       </c>
       <c r="D262" s="23" t="s">
-        <v>1235</v>
+        <v>1145</v>
       </c>
       <c r="E262" s="28" t="s">
-        <v>1236</v>
+        <v>1146</v>
       </c>
       <c r="F262" s="29" t="s">
         <v>645</v>
       </c>
       <c r="G262" s="23" t="s">
-        <v>1246</v>
+        <v>1153</v>
       </c>
       <c r="H262" s="23" t="s">
         <v>660</v>
       </c>
       <c r="I262" s="23" t="s">
-        <v>1214</v>
+        <v>1127</v>
       </c>
       <c r="J262" s="23" t="s">
-        <v>1315</v>
+        <v>1200</v>
       </c>
       <c r="N262" s="1" t="s">
         <v>631</v>
@@ -26551,34 +26053,34 @@
         <v>sumomone-fueru</v>
       </c>
       <c r="C263" s="24" t="s">
-        <v>1238</v>
+        <v>1148</v>
       </c>
       <c r="D263" s="23" t="s">
-        <v>1239</v>
+        <v>1149</v>
       </c>
       <c r="E263" s="23" t="s">
-        <v>1240</v>
+        <v>1150</v>
       </c>
       <c r="F263" s="29" t="s">
-        <v>1241</v>
+        <v>1151</v>
       </c>
       <c r="G263" s="23" t="s">
-        <v>1245</v>
+        <v>1152</v>
       </c>
       <c r="H263" s="23" t="s">
-        <v>684</v>
+        <v>674</v>
       </c>
       <c r="I263" s="23" t="s">
-        <v>705</v>
+        <v>679</v>
       </c>
       <c r="K263" s="23" t="s">
-        <v>1242</v>
+        <v>1221</v>
       </c>
       <c r="L263" s="23" t="s">
-        <v>1243</v>
+        <v>710</v>
       </c>
       <c r="M263" s="23" t="s">
-        <v>1244</v>
+        <v>1269</v>
       </c>
       <c r="N263" s="1" t="s">
         <v>631</v>
@@ -26635,28 +26137,31 @@
         <v>ubuon-goe</v>
       </c>
       <c r="C264" s="24" t="s">
-        <v>1252</v>
+        <v>1156</v>
       </c>
       <c r="D264" s="23" t="s">
-        <v>1253</v>
+        <v>1157</v>
       </c>
       <c r="E264" s="23" t="s">
-        <v>1254</v>
+        <v>1158</v>
       </c>
       <c r="F264" s="29" t="s">
-        <v>1275</v>
+        <v>1178</v>
       </c>
       <c r="G264" s="23" t="s">
-        <v>1274</v>
+        <v>1177</v>
       </c>
       <c r="H264" s="23" t="s">
-        <v>683</v>
+        <v>673</v>
       </c>
       <c r="I264" s="23" t="s">
-        <v>771</v>
+        <v>715</v>
+      </c>
+      <c r="K264" s="23" t="s">
+        <v>1222</v>
       </c>
       <c r="L264" s="23" t="s">
-        <v>1291</v>
+        <v>1190</v>
       </c>
       <c r="N264" s="1" t="s">
         <v>631</v>
@@ -26678,7 +26183,7 @@
       </c>
       <c r="T264" s="24">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
-        <v>0.13442594873170854</v>
+        <v>0.47203991779917243</v>
       </c>
       <c r="U264" s="23" t="str">
         <f>"|&amp;image("&amp;テーブル1[[#This Row],[画像]]&amp;".png,width=100,height=100)"</f>
@@ -26710,28 +26215,28 @@
         <v>shuta-katsue</v>
       </c>
       <c r="C265" s="24" t="s">
-        <v>1251</v>
+        <v>1155</v>
       </c>
       <c r="D265" s="23" t="s">
-        <v>1255</v>
+        <v>1159</v>
       </c>
       <c r="E265" s="23" t="s">
-        <v>1256</v>
+        <v>1160</v>
       </c>
       <c r="F265" s="29" t="s">
-        <v>1275</v>
+        <v>1178</v>
       </c>
       <c r="G265" s="23" t="s">
-        <v>1274</v>
+        <v>1177</v>
       </c>
       <c r="H265" s="23" t="s">
         <v>660</v>
       </c>
       <c r="I265" s="23" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="L265" s="23" t="s">
-        <v>1278</v>
+        <v>1180</v>
       </c>
       <c r="N265" s="1" t="s">
         <v>631</v>
@@ -26746,7 +26251,7 @@
       </c>
       <c r="R265" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>25.415788342329659</v>
+        <v>25.269332498552579</v>
       </c>
       <c r="T265" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -26782,31 +26287,31 @@
         <v>narune-bell</v>
       </c>
       <c r="C266" s="24" t="s">
-        <v>1257</v>
+        <v>1161</v>
       </c>
       <c r="D266" s="23" t="s">
-        <v>1258</v>
+        <v>1162</v>
       </c>
       <c r="E266" s="23" t="s">
-        <v>1259</v>
+        <v>1163</v>
       </c>
       <c r="F266" s="29" t="s">
-        <v>1275</v>
+        <v>1178</v>
       </c>
       <c r="G266" s="23" t="s">
-        <v>1274</v>
+        <v>1177</v>
       </c>
       <c r="H266" s="23" t="s">
-        <v>683</v>
+        <v>673</v>
       </c>
       <c r="I266" s="23" t="s">
-        <v>678</v>
+        <v>671</v>
       </c>
       <c r="J266" s="23" t="s">
-        <v>1311</v>
+        <v>1198</v>
       </c>
       <c r="L266" s="23" t="s">
-        <v>1280</v>
+        <v>1182</v>
       </c>
       <c r="N266" s="1" t="s">
         <v>631</v>
@@ -26821,7 +26326,7 @@
       </c>
       <c r="R266" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>25.845956120115581</v>
+        <v>25.868310083332428</v>
       </c>
       <c r="T266" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -26857,31 +26362,31 @@
         <v>keishikibangoα-01</v>
       </c>
       <c r="C267" s="24" t="s">
-        <v>1260</v>
+        <v>1164</v>
       </c>
       <c r="D267" s="23" t="s">
-        <v>1261</v>
+        <v>1165</v>
       </c>
       <c r="E267" s="23" t="s">
-        <v>1262</v>
+        <v>1166</v>
       </c>
       <c r="F267" s="29" t="s">
-        <v>1275</v>
+        <v>1178</v>
       </c>
       <c r="G267" s="23" t="s">
-        <v>1274</v>
+        <v>1177</v>
       </c>
       <c r="H267" s="23" t="s">
         <v>661</v>
       </c>
       <c r="I267" s="23" t="s">
-        <v>678</v>
+        <v>671</v>
       </c>
       <c r="J267" s="23" t="s">
-        <v>1312</v>
+        <v>1198</v>
       </c>
       <c r="L267" s="23" t="s">
-        <v>1283</v>
+        <v>1184</v>
       </c>
       <c r="N267" s="1" t="s">
         <v>631</v>
@@ -26896,7 +26401,7 @@
       </c>
       <c r="R267" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>25.884154811222359</v>
+        <v>25.377767532864596</v>
       </c>
       <c r="T267" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -26932,31 +26437,31 @@
         <v>isshiki-su</v>
       </c>
       <c r="C268" s="24" t="s">
-        <v>1263</v>
+        <v>1167</v>
       </c>
       <c r="D268" s="23" t="s">
-        <v>1264</v>
+        <v>1168</v>
       </c>
       <c r="E268" s="23" t="s">
-        <v>1265</v>
+        <v>1169</v>
       </c>
       <c r="F268" s="29" t="s">
-        <v>1271</v>
+        <v>1175</v>
       </c>
       <c r="G268" s="23" t="s">
-        <v>1272</v>
+        <v>1176</v>
       </c>
       <c r="H268" s="23" t="s">
         <v>661</v>
       </c>
       <c r="I268" s="23" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="K268" s="23" t="s">
-        <v>1273</v>
+        <v>1214</v>
       </c>
       <c r="L268" s="23" t="s">
-        <v>1280</v>
+        <v>1182</v>
       </c>
       <c r="N268" s="1" t="s">
         <v>631</v>
@@ -26971,7 +26476,7 @@
       </c>
       <c r="R268" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>6.1353744413322642E-2</v>
+        <v>0.83469291817736047</v>
       </c>
       <c r="T268" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27007,34 +26512,34 @@
         <v>tsugine-saiko</v>
       </c>
       <c r="C269" s="24" t="s">
-        <v>1266</v>
+        <v>1170</v>
       </c>
       <c r="D269" s="23" t="s">
-        <v>1267</v>
+        <v>1171</v>
       </c>
       <c r="E269" s="28" t="s">
-        <v>1268</v>
+        <v>1172</v>
       </c>
       <c r="F269" s="29" t="s">
-        <v>1269</v>
+        <v>1173</v>
       </c>
       <c r="G269" s="23" t="s">
-        <v>1270</v>
+        <v>1174</v>
       </c>
       <c r="H269" s="23" t="s">
         <v>660</v>
       </c>
       <c r="I269" s="23" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="K269" s="23" t="s">
-        <v>1250</v>
+        <v>1214</v>
       </c>
       <c r="L269" s="23" t="s">
-        <v>1286</v>
+        <v>1187</v>
       </c>
       <c r="M269" s="23" t="s">
-        <v>793</v>
+        <v>1256</v>
       </c>
       <c r="N269" s="1" t="s">
         <v>631</v>
@@ -27049,7 +26554,7 @@
       </c>
       <c r="R269" s="16">
         <f ca="1">IFERROR(IF(テーブル1[[#This Row],[描画状況]]="",RAND()+(テーブル1[[#This Row],[列2]]*100),""),RAND())</f>
-        <v>0.72687767731210373</v>
+        <v>0.34931790145826414</v>
       </c>
       <c r="T269" s="24" t="str">
         <f ca="1">IF(AND(テーブル1[[#This Row],[描画状況]]="済",テーブル1[[#This Row],[投稿状況]]=""),RAND(),"")</f>
@@ -27426,7 +26931,7 @@
       </c>
       <c r="C4" s="7">
         <f ca="1">MATCH(C5,キャラ情報!C:C,0)</f>
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -27435,7 +26940,7 @@
       </c>
       <c r="C5" s="6" t="str">
         <f ca="1">INDEX(キャラ情報!C:R,MATCH(MIN(キャラ情報!R:R),キャラ情報!R:R,0),1)</f>
-        <v>一色スウ</v>
+        <v>亜音サイコ</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -27444,7 +26949,7 @@
       </c>
       <c r="C6" s="6" t="str">
         <f ca="1">INDEX(キャラ情報!C:R,MATCH(MIN(キャラ情報!R:R),キャラ情報!R:R,0),4)</f>
-        <v>http://utau.wikidot.com/utau:isshiki-suu</v>
+        <v>https://aisupiku.wixsite.com/tsuginesaiko</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -27515,7 +27020,7 @@
     </row>
     <row r="21" spans="2:3" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B21" s="13" t="s">
-        <v>721</v>
+        <v>690</v>
       </c>
       <c r="C21" s="14"/>
     </row>
@@ -27575,7 +27080,7 @@
         <v>663</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>738</v>
+        <v>705</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>664</v>
@@ -27638,7 +27143,7 @@
       </c>
       <c r="M2" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
-        <v>尖耳</v>
+        <v>耳</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -27684,7 +27189,7 @@
       </c>
       <c r="K3" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
-        <v>科学者</v>
+        <v>科学・技術</v>
       </c>
       <c r="L3" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
@@ -27692,7 +27197,7 @@
       </c>
       <c r="M3" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
-        <v>インナーカラー|片目隠れ</v>
+        <v>髪色・カラー|目隠れ</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -27738,7 +27243,7 @@
       </c>
       <c r="K4" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
-        <v>機械整備士</v>
+        <v>科学・技術</v>
       </c>
       <c r="L4" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
@@ -27746,7 +27251,7 @@
       </c>
       <c r="M4" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
-        <v>角(ツノ)|羽|尻尾</v>
+        <v>角(つの)|翼|尻尾</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -27854,7 +27359,7 @@
       </c>
       <c r="M6" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
-        <v>羽</v>
+        <v>翼</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -27962,7 +27467,7 @@
       </c>
       <c r="M8" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
-        <v>オッドアイ</v>
+        <v>目</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -28016,7 +27521,7 @@
       </c>
       <c r="M9" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
-        <v>羽</v>
+        <v>翼</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -28070,7 +27575,7 @@
       </c>
       <c r="M10" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
-        <v>渦巻き目|アホ毛</v>
+        <v>目|髪型・髪の特徴</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -28124,7 +27629,7 @@
       </c>
       <c r="M11" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
-        <v>ツートンカラー</v>
+        <v>髪色・カラー</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -28170,7 +27675,7 @@
       </c>
       <c r="K12" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
-        <v>書店員</v>
+        <v>接客・販売</v>
       </c>
       <c r="L12" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
@@ -28332,7 +27837,7 @@
       </c>
       <c r="K15" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
-        <v>腹話術師</v>
+        <v>舞台・パフォーマンス</v>
       </c>
       <c r="L15" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
@@ -28340,7 +27845,7 @@
       </c>
       <c r="M15" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
-        <v>両目隠れ</v>
+        <v>目隠れ</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -28386,7 +27891,7 @@
       </c>
       <c r="K16" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
-        <v>クリエイター</v>
+        <v>創作</v>
       </c>
       <c r="L16" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
@@ -28394,7 +27899,7 @@
       </c>
       <c r="M16" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
-        <v>メッシュ</v>
+        <v>髪色・カラー</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -28718,7 +28223,7 @@
       </c>
       <c r="M22" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
-        <v>両目隠れ|羽</v>
+        <v>目隠れ|翼</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -28764,7 +28269,7 @@
       </c>
       <c r="K23" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
-        <v>司祭</v>
+        <v>宗教・ファンタジー</v>
       </c>
       <c r="L23" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
@@ -28772,7 +28277,7 @@
       </c>
       <c r="M23" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
-        <v>片目隠れ</v>
+        <v>目隠れ</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -28880,7 +28385,7 @@
       </c>
       <c r="M25" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
-        <v>片目隠れ</v>
+        <v>目隠れ</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -28926,7 +28431,7 @@
       </c>
       <c r="K26" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
-        <v>アイドル</v>
+        <v>芸能</v>
       </c>
       <c r="L26" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
@@ -28934,7 +28439,7 @@
       </c>
       <c r="M26" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
-        <v>オッドアイ|ほくろ</v>
+        <v>目|模様・装飾</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -28980,7 +28485,7 @@
       </c>
       <c r="K27" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
-        <v>アイドル</v>
+        <v>芸能</v>
       </c>
       <c r="L27" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
@@ -28988,7 +28493,7 @@
       </c>
       <c r="M27" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
-        <v>ほくろ</v>
+        <v>模様・装飾</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -29250,7 +28755,7 @@
       </c>
       <c r="K32" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
-        <v>サーカス団員</v>
+        <v>舞台・パフォーマンス</v>
       </c>
       <c r="L32" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
@@ -29258,7 +28763,7 @@
       </c>
       <c r="M32" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
-        <v>ギザ歯</v>
+        <v>口元</v>
       </c>
     </row>
     <row r="33" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -29304,7 +28809,7 @@
       </c>
       <c r="K33" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
-        <v>犯罪者</v>
+        <v>裏社会</v>
       </c>
       <c r="L33" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
@@ -29312,7 +28817,7 @@
       </c>
       <c r="M33" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
-        <v>傷|ほくろ</v>
+        <v>傷・痕|模様・装飾</v>
       </c>
     </row>
     <row r="34" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -29366,7 +28871,7 @@
       </c>
       <c r="M34" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
-        <v>黒ベタ目|高身長|ボディペイント</v>
+        <v>目|体格|模様・装飾</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -29412,7 +28917,7 @@
       </c>
       <c r="K35" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
-        <v>人喰い</v>
+        <v>裏社会</v>
       </c>
       <c r="L35" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
@@ -29420,7 +28925,7 @@
       </c>
       <c r="M35" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
-        <v>両目隠れ</v>
+        <v>目隠れ</v>
       </c>
     </row>
     <row r="36" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -29466,7 +28971,7 @@
       </c>
       <c r="K36" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
-        <v>警察官|元ヤン</v>
+        <v>治安|元ヤン</v>
       </c>
       <c r="L36" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
@@ -29474,7 +28979,7 @@
       </c>
       <c r="M36" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
-        <v>グラデーションカラー</v>
+        <v>髪色・カラー</v>
       </c>
     </row>
     <row r="37" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -29520,7 +29025,7 @@
       </c>
       <c r="K37" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
-        <v>アイドル</v>
+        <v>芸能</v>
       </c>
       <c r="L37" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
@@ -29574,7 +29079,7 @@
       </c>
       <c r="K38" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
-        <v>サポーター|カウンセラー</v>
+        <v>医療・支援</v>
       </c>
       <c r="L38" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
@@ -29582,7 +29087,7 @@
       </c>
       <c r="M38" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
-        <v>メッシュ</v>
+        <v>髪色・カラー</v>
       </c>
     </row>
     <row r="39" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -29682,7 +29187,7 @@
       </c>
       <c r="K40" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
-        <v>学生</v>
+        <v>教育</v>
       </c>
       <c r="L40" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
@@ -29798,7 +29303,7 @@
       </c>
       <c r="M42" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
-        <v>アホ毛</v>
+        <v>髪型・髪の特徴</v>
       </c>
     </row>
     <row r="43" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -29906,7 +29411,7 @@
       </c>
       <c r="M44" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
-        <v>ケモ耳|メッシュ|尻尾</v>
+        <v>耳|髪色・カラー|尻尾</v>
       </c>
     </row>
     <row r="45" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -29952,7 +29457,7 @@
       </c>
       <c r="K45" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
-        <v>学生</v>
+        <v>教育</v>
       </c>
       <c r="L45" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
@@ -30006,7 +29511,7 @@
       </c>
       <c r="K46" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
-        <v>学生|アイドル</v>
+        <v>教育|芸能</v>
       </c>
       <c r="L46" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
@@ -30122,7 +29627,7 @@
       </c>
       <c r="M48" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
-        <v>インナーカラー|羽</v>
+        <v>髪色・カラー|翼</v>
       </c>
     </row>
     <row r="49" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -30384,7 +29889,7 @@
       </c>
       <c r="K53" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
-        <v>サポーター</v>
+        <v>医療・支援</v>
       </c>
       <c r="L53" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
@@ -30500,7 +30005,7 @@
       </c>
       <c r="M55" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
-        <v>オッドアイ|アホ毛</v>
+        <v>目|髪型・髪の特徴</v>
       </c>
     </row>
     <row r="56" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -30924,7 +30429,7 @@
       </c>
       <c r="K63" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
-        <v>学生</v>
+        <v>教育</v>
       </c>
       <c r="L63" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
@@ -30932,7 +30437,7 @@
       </c>
       <c r="M63" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
-        <v>インナーカラー|片目隠れ</v>
+        <v>髪色・カラー|目隠れ</v>
       </c>
     </row>
     <row r="64" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -31094,7 +30599,7 @@
       </c>
       <c r="M66" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
-        <v>アホ毛|メッシュ</v>
+        <v>髪型・髪の特徴|髪色・カラー</v>
       </c>
     </row>
     <row r="67" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -31850,7 +31355,7 @@
       </c>
       <c r="M80" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
-        <v>ケモ耳|尻尾</v>
+        <v>耳|尻尾</v>
       </c>
     </row>
     <row r="81" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -31958,7 +31463,7 @@
       </c>
       <c r="M82" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
-        <v>ケモ耳|髭|尻尾</v>
+        <v>耳|髭|尻尾</v>
       </c>
     </row>
     <row r="83" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -32220,7 +31725,7 @@
       </c>
       <c r="K87" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
-        <v>サーカス団員</v>
+        <v>舞台・パフォーマンス</v>
       </c>
       <c r="L87" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
@@ -32228,7 +31733,7 @@
       </c>
       <c r="M87" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
-        <v>ギザ歯</v>
+        <v>口元</v>
       </c>
     </row>
     <row r="88" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -32282,7 +31787,7 @@
       </c>
       <c r="M88" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
-        <v>片目隠れ</v>
+        <v>目隠れ</v>
       </c>
     </row>
     <row r="89" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -32436,7 +31941,7 @@
       </c>
       <c r="K91" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
-        <v>学生</v>
+        <v>教育</v>
       </c>
       <c r="L91" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
@@ -32490,7 +31995,7 @@
       </c>
       <c r="K92" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
-        <v>警察官</v>
+        <v>治安</v>
       </c>
       <c r="L92" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
@@ -32598,7 +32103,7 @@
       </c>
       <c r="K94" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
-        <v>学生</v>
+        <v>教育</v>
       </c>
       <c r="L94" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
@@ -32760,7 +32265,7 @@
       </c>
       <c r="K97" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
-        <v>殺し屋</v>
+        <v>裏社会</v>
       </c>
       <c r="L97" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
@@ -32768,7 +32273,7 @@
       </c>
       <c r="M97" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
-        <v>片目隠れ|火傷|ほくろ</v>
+        <v>目隠れ|傷・痕|模様・装飾</v>
       </c>
     </row>
     <row r="98" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -32876,7 +32381,7 @@
       </c>
       <c r="M99" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
-        <v>隻眼</v>
+        <v>目</v>
       </c>
     </row>
     <row r="100" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -32922,7 +32427,7 @@
       </c>
       <c r="K100" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
-        <v>魔法使い|手品師</v>
+        <v>宗教・ファンタジー|舞台・パフォーマンス</v>
       </c>
       <c r="L100" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
@@ -32976,7 +32481,7 @@
       </c>
       <c r="K101" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
-        <v>魔法使い</v>
+        <v>宗教・ファンタジー</v>
       </c>
       <c r="L101" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
@@ -33038,7 +32543,7 @@
       </c>
       <c r="M102" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
-        <v>両目隠れ</v>
+        <v>目隠れ</v>
       </c>
     </row>
     <row r="103" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -33138,7 +32643,7 @@
       </c>
       <c r="K104" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
-        <v>書店員</v>
+        <v>接客・販売</v>
       </c>
       <c r="L104" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
@@ -33300,7 +32805,7 @@
       </c>
       <c r="K107" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
-        <v>カウンセラー</v>
+        <v>医療・支援</v>
       </c>
       <c r="L107" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
@@ -33308,7 +32813,7 @@
       </c>
       <c r="M107" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
-        <v>インナーカラー|片目隠れ</v>
+        <v>髪色・カラー|目隠れ</v>
       </c>
     </row>
     <row r="108" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -33408,7 +32913,7 @@
       </c>
       <c r="K109" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
-        <v>執事</v>
+        <v>使用人・家事</v>
       </c>
       <c r="L109" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
@@ -33416,7 +32921,7 @@
       </c>
       <c r="M109" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
-        <v>オッドアイ</v>
+        <v>目</v>
       </c>
     </row>
     <row r="110" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -33470,7 +32975,7 @@
       </c>
       <c r="M110" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
-        <v>ほくろ</v>
+        <v>模様・装飾</v>
       </c>
     </row>
     <row r="111" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -33578,7 +33083,7 @@
       </c>
       <c r="M112" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
-        <v>両目隠れ</v>
+        <v>目隠れ</v>
       </c>
     </row>
     <row r="113" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -33632,7 +33137,7 @@
       </c>
       <c r="M113" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
-        <v>羽|尖耳|ギザ歯</v>
+        <v>翼|耳|口元</v>
       </c>
     </row>
     <row r="114" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -33840,7 +33345,7 @@
       </c>
       <c r="K117" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
-        <v>地磁気調査</v>
+        <v>科学・技術</v>
       </c>
       <c r="L117" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
@@ -33848,7 +33353,7 @@
       </c>
       <c r="M117" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
-        <v>メッシュ|尻尾</v>
+        <v>髪色・カラー|尻尾</v>
       </c>
     </row>
     <row r="118" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -34982,7 +34487,7 @@
       </c>
       <c r="M138" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
-        <v>ツートンカラー|片目隠れ</v>
+        <v>髪色・カラー|目隠れ</v>
       </c>
     </row>
     <row r="139" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -35298,7 +34803,7 @@
       </c>
       <c r="K144" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
-        <v>魔法使い</v>
+        <v>宗教・ファンタジー</v>
       </c>
       <c r="L144" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
@@ -35522,7 +35027,7 @@
       </c>
       <c r="M148" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
-        <v>グラデーションカラー</v>
+        <v>髪色・カラー</v>
       </c>
     </row>
     <row r="149" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -36054,7 +35559,7 @@
       </c>
       <c r="K158" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
-        <v>サポーター</v>
+        <v>医療・支援</v>
       </c>
       <c r="L158" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
@@ -36764,7 +36269,7 @@
       </c>
       <c r="M171" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
-        <v>メッシュ</v>
+        <v>髪色・カラー</v>
       </c>
     </row>
     <row r="172" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -37512,7 +37017,7 @@
       </c>
       <c r="K185" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
-        <v>科学者</v>
+        <v>科学・技術</v>
       </c>
       <c r="L185" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
@@ -37520,7 +37025,7 @@
       </c>
       <c r="M185" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
-        <v>両目隠れ</v>
+        <v>目隠れ</v>
       </c>
     </row>
     <row r="186" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -38006,7 +37511,7 @@
       </c>
       <c r="M194" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
-        <v>アホ毛|両目隠れ</v>
+        <v>髪型・髪の特徴|目隠れ</v>
       </c>
     </row>
     <row r="195" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -38654,7 +38159,7 @@
       </c>
       <c r="M206" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
-        <v>セクションカラー</v>
+        <v>髪色・カラー</v>
       </c>
     </row>
     <row r="207" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -39032,7 +38537,7 @@
       </c>
       <c r="M213" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
-        <v>アホ毛|オッドアイ|特殊肌|尻尾</v>
+        <v>髪型・髪の特徴|目|肌|尻尾</v>
       </c>
     </row>
     <row r="214" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -39194,7 +38699,7 @@
       </c>
       <c r="M216" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
-        <v>黒肌</v>
+        <v>肌</v>
       </c>
     </row>
     <row r="217" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -39294,7 +38799,7 @@
       </c>
       <c r="K218" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
-        <v>科学者</v>
+        <v>科学・技術</v>
       </c>
       <c r="L218" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
@@ -39302,7 +38807,7 @@
       </c>
       <c r="M218" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
-        <v>褐色肌</v>
+        <v>肌</v>
       </c>
     </row>
     <row r="219" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -39734,7 +39239,7 @@
       </c>
       <c r="M226" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
-        <v>出血|ほくろ|ギザ歯</v>
+        <v>傷・痕|模様・装飾|口元</v>
       </c>
     </row>
     <row r="227" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -39780,7 +39285,7 @@
       </c>
       <c r="K227" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
-        <v>警察官</v>
+        <v>治安</v>
       </c>
       <c r="L227" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
@@ -39788,7 +39293,7 @@
       </c>
       <c r="M227" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
-        <v>義眼</v>
+        <v>目</v>
       </c>
     </row>
     <row r="228" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -39842,7 +39347,7 @@
       </c>
       <c r="M228" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
-        <v>グラデーションカラー|まろ眉</v>
+        <v>髪色・カラー|眉</v>
       </c>
     </row>
     <row r="229" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -39942,7 +39447,7 @@
       </c>
       <c r="K230" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
-        <v>吟遊詩人</v>
+        <v>舞台・パフォーマンス</v>
       </c>
       <c r="L230" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
@@ -40004,7 +39509,7 @@
       </c>
       <c r="M231" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
-        <v>ケモ耳|尻尾</v>
+        <v>耳|尻尾</v>
       </c>
     </row>
     <row r="232" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -40158,7 +39663,7 @@
       </c>
       <c r="K234" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
-        <v>メイド</v>
+        <v>使用人・家事</v>
       </c>
       <c r="L234" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
@@ -40166,7 +39671,7 @@
       </c>
       <c r="M234" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
-        <v>グラデーションカラー|オッドアイ</v>
+        <v>髪色・カラー|目</v>
       </c>
     </row>
     <row r="235" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -40212,7 +39717,7 @@
       </c>
       <c r="K235" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
-        <v>学生</v>
+        <v>教育</v>
       </c>
       <c r="L235" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
@@ -40220,7 +39725,7 @@
       </c>
       <c r="M235" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
-        <v>アホ毛|メッシュ|インナーカラー|両目隠れ</v>
+        <v>髪型・髪の特徴|髪色・カラー|目隠れ</v>
       </c>
     </row>
     <row r="236" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -40274,7 +39779,7 @@
       </c>
       <c r="M236" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
-        <v>ツートンカラー</v>
+        <v>髪色・カラー</v>
       </c>
     </row>
     <row r="237" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -40382,7 +39887,7 @@
       </c>
       <c r="M238" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
-        <v>インナーカラー</v>
+        <v>髪色・カラー</v>
       </c>
     </row>
     <row r="239" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -40490,7 +39995,7 @@
       </c>
       <c r="M240" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
-        <v>メッシュ|インナーカラー|両目隠れ|高身長</v>
+        <v>髪色・カラー|目隠れ|体格</v>
       </c>
     </row>
     <row r="241" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -40598,7 +40103,7 @@
       </c>
       <c r="M242" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
-        <v>メッシュ|両目隠れ</v>
+        <v>髪色・カラー|目隠れ</v>
       </c>
     </row>
     <row r="243" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -40644,7 +40149,7 @@
       </c>
       <c r="K243" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
-        <v>教員</v>
+        <v>教育</v>
       </c>
       <c r="L243" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
@@ -40652,7 +40157,7 @@
       </c>
       <c r="M243" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
-        <v>グラデーションカラー|オッドアイ</v>
+        <v>髪色・カラー|目</v>
       </c>
     </row>
     <row r="244" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -40706,7 +40211,7 @@
       </c>
       <c r="M244" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
-        <v>グラデーションカラー|オッドアイ</v>
+        <v>髪色・カラー|目</v>
       </c>
     </row>
     <row r="245" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -40814,7 +40319,7 @@
       </c>
       <c r="M246" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
-        <v>ツートンカラー|オッドアイ</v>
+        <v>髪色・カラー|目</v>
       </c>
     </row>
     <row r="247" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -40914,7 +40419,7 @@
       </c>
       <c r="K248" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
-        <v>書店員</v>
+        <v>接客・販売</v>
       </c>
       <c r="L248" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
@@ -41022,7 +40527,7 @@
       </c>
       <c r="K250" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
-        <v>科学者</v>
+        <v>科学・技術</v>
       </c>
       <c r="L250" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
@@ -41030,7 +40535,7 @@
       </c>
       <c r="M250" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
-        <v>インナーカラー|片目隠れ</v>
+        <v>髪色・カラー|目隠れ</v>
       </c>
     </row>
     <row r="251" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -41084,7 +40589,7 @@
       </c>
       <c r="M251" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
-        <v>刺青|高身長</v>
+        <v>模様・装飾|体格</v>
       </c>
     </row>
     <row r="252" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -41192,7 +40697,7 @@
       </c>
       <c r="M253" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
-        <v>ケモ耳|尻尾</v>
+        <v>耳|尻尾</v>
       </c>
     </row>
     <row r="254" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -41238,7 +40743,7 @@
       </c>
       <c r="K254" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
-        <v>家政婦</v>
+        <v>使用人・家事</v>
       </c>
       <c r="L254" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
@@ -41300,7 +40805,7 @@
       </c>
       <c r="M255" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
-        <v>ケモ耳|片目隠れ|尻尾</v>
+        <v>耳|目隠れ|尻尾</v>
       </c>
     </row>
     <row r="256" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -41408,7 +40913,7 @@
       </c>
       <c r="M257" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
-        <v>ツートンカラー</v>
+        <v>髪色・カラー</v>
       </c>
     </row>
     <row r="258" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -41508,7 +41013,7 @@
       </c>
       <c r="K259" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
-        <v>元ヤン|作家</v>
+        <v>元ヤン|創作</v>
       </c>
       <c r="L259" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
@@ -41516,7 +41021,7 @@
       </c>
       <c r="M259" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
-        <v>ツートンカラー</v>
+        <v>髪色・カラー</v>
       </c>
     </row>
     <row r="260" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -41562,7 +41067,7 @@
       </c>
       <c r="K260" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
-        <v>バーテンダー</v>
+        <v>接客・販売</v>
       </c>
       <c r="L260" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
@@ -41570,7 +41075,7 @@
       </c>
       <c r="M260" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
-        <v>ツートンカラー</v>
+        <v>髪色・カラー</v>
       </c>
     </row>
     <row r="261" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -41616,7 +41121,7 @@
       </c>
       <c r="K261" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
-        <v>歌手</v>
+        <v>芸能</v>
       </c>
       <c r="L261" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
@@ -41724,7 +41229,7 @@
       </c>
       <c r="K263" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
-        <v>医者</v>
+        <v>医療・支援</v>
       </c>
       <c r="L263" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
@@ -41732,7 +41237,7 @@
       </c>
       <c r="M263" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
-        <v>羽|多眼</v>
+        <v>翼|目</v>
       </c>
     </row>
     <row r="264" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -41778,7 +41283,7 @@
       </c>
       <c r="K264" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
-        <v/>
+        <v>教育</v>
       </c>
       <c r="L264" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
@@ -41994,7 +41499,7 @@
       </c>
       <c r="K268" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
-        <v>アーティスト</v>
+        <v>芸能</v>
       </c>
       <c r="L268" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
@@ -42048,7 +41553,7 @@
       </c>
       <c r="K269" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[職業タグ]],"、","|")</f>
-        <v>歌手</v>
+        <v>芸能</v>
       </c>
       <c r="L269" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[小物タグ]],"、","|")</f>
@@ -42056,7 +41561,7 @@
       </c>
       <c r="M269" s="19" t="str">
         <f>SUBSTITUTE(テーブル1[[#This Row],[ワンポイントタグ]],"、","|")</f>
-        <v>メッシュ|尻尾</v>
+        <v>髪色・カラー|尻尾</v>
       </c>
     </row>
   </sheetData>
